--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="200">
   <si>
     <t>Controle de pagamentos</t>
   </si>
@@ -403,7 +403,7 @@
     <t>Módulo III – Orçamento 19 GPS</t>
   </si>
   <si>
-    <t>Aprovado e aguardando itens.</t>
+    <t>2025NE001065</t>
   </si>
   <si>
     <t>Saldo</t>
@@ -636,9 +636,6 @@
   </si>
   <si>
     <t>219C</t>
-  </si>
-  <si>
-    <t>2025NE001065</t>
   </si>
   <si>
     <r>
@@ -3210,13 +3207,19 @@
         <v>122</v>
       </c>
       <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="60"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="61" t="s">
+      <c r="F39" s="56">
+        <v>1882.0</v>
+      </c>
+      <c r="G39" s="60">
+        <v>46199.0</v>
+      </c>
+      <c r="H39" s="56" t="s">
         <v>123</v>
       </c>
-      <c r="J39" s="60"/>
+      <c r="I39" s="61"/>
+      <c r="J39" s="60">
+        <v>46233.0</v>
+      </c>
       <c r="K39" s="36">
         <v>58868.35</v>
       </c>
@@ -8645,13 +8648,13 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="12" t="s">
         <v>158</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>159</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>127</v>
@@ -8694,10 +8697,10 @@
         <v>59</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>161</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>127</v>
@@ -8736,13 +8739,13 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="C15" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>164</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>127</v>
@@ -8781,13 +8784,13 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="C16" s="12" t="s">
         <v>166</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>167</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>127</v>
@@ -8826,13 +8829,13 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="C17" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>127</v>
@@ -8874,10 +8877,10 @@
         <v>110</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>171</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>172</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>127</v>
@@ -8916,13 +8919,13 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="C19" s="12" t="s">
         <v>174</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>175</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>127</v>
@@ -8961,13 +8964,13 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="C20" s="12" t="s">
         <v>177</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>178</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>127</v>
@@ -9006,13 +9009,13 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="C21" s="12" t="s">
         <v>180</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>181</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>127</v>
@@ -9054,10 +9057,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>182</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>183</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>127</v>
@@ -9099,10 +9102,10 @@
         <v>114</v>
       </c>
       <c r="B23" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="12" t="s">
         <v>184</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>185</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>127</v>
@@ -9120,7 +9123,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -9141,13 +9144,13 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="12" t="s">
         <v>188</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>189</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>127</v>
@@ -9189,10 +9192,10 @@
         <v>105</v>
       </c>
       <c r="B25" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>190</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>191</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>127</v>
@@ -9210,7 +9213,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -9231,13 +9234,13 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="C26" s="12" t="s">
         <v>193</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>194</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>127</v>
@@ -9276,13 +9279,13 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="C27" s="12" t="s">
         <v>196</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>197</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>127</v>
@@ -9321,13 +9324,13 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="C28" s="12" t="s">
         <v>199</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>200</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>127</v>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="198">
   <si>
     <t>Controle de pagamentos</t>
   </si>
@@ -412,14 +412,7 @@
     <t>2025NE000005</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25375</t>
-    </r>
+    <t>C25375</t>
   </si>
   <si>
     <t>Ordenador de Despesas</t>
@@ -431,93 +424,34 @@
     <t>2025NE000367</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25512</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0385</t>
-    </r>
+    <t>C25512</t>
+  </si>
+  <si>
+    <t>25E0385</t>
   </si>
   <si>
     <t>2025NE000369</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25516</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0387</t>
-    </r>
+    <t>C25516</t>
+  </si>
+  <si>
+    <t>25E0387</t>
   </si>
   <si>
     <t>2025NE000371</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25516</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0389</t>
-    </r>
+    <t>25E0389</t>
   </si>
   <si>
     <t>2025NE000413</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25501</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0403</t>
-    </r>
+    <t>C25501</t>
+  </si>
+  <si>
+    <t>25E0403</t>
   </si>
   <si>
     <t>20SP</t>
@@ -526,354 +460,106 @@
     <t>2025NE000414</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25525</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0431</t>
-    </r>
+    <t>C25525</t>
+  </si>
+  <si>
+    <t>25E0431</t>
   </si>
   <si>
     <t>21EM</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25545</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0524</t>
-    </r>
+    <t>C25545</t>
+  </si>
+  <si>
+    <t>25E0524</t>
   </si>
   <si>
     <t>20X7</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25512</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0731</t>
-    </r>
+    <t>25E0731</t>
   </si>
   <si>
     <t>2025NE000774</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25516</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0737</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25630</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0787</t>
-    </r>
+    <t>25E0737</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
+    <t>25E0787</t>
   </si>
   <si>
     <t>219C</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25512</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E0999</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25590</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1128</t>
-    </r>
+    <t>25E0999</t>
+  </si>
+  <si>
+    <t>C25590</t>
+  </si>
+  <si>
+    <t>25E1128</t>
   </si>
   <si>
     <t>2025NE001598</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25814</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1446</t>
-    </r>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
   </si>
   <si>
     <t>2025NE001627</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25512</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1475</t>
-    </r>
+    <t>25E1475</t>
   </si>
   <si>
     <t>2025NE001629</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25820</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1477</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25590</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1535</t>
-    </r>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
+  </si>
+  <si>
+    <t>25E1535</t>
   </si>
   <si>
     <t>2025NE001688</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25630</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1536</t>
-    </r>
+    <t>25E1536</t>
   </si>
   <si>
     <t>2025NE001689</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25512</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1537</t>
-    </r>
+    <t>25E1537</t>
   </si>
   <si>
     <t>2025NE001690</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25516</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1538</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25865</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1666</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25869</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1667</t>
-    </r>
+    <t>25E1538</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
   </si>
   <si>
     <t>20YJ</t>
@@ -882,113 +568,64 @@
     <t>2025NE001830</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25516</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E1669</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25863</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E2021</t>
-    </r>
+    <t>25E1669</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
   </si>
   <si>
     <t>2025NE002237</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C25512</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>25E2058</t>
-    </r>
+    <t>25E2058</t>
   </si>
   <si>
     <t>2026NE000330</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C26163</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>26E0320</t>
-    </r>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
   </si>
   <si>
     <t>2026NE000388</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>C26193</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <color rgb="FF1155CC"/>
-        <u/>
-      </rPr>
-      <t>26E0375</t>
-    </r>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
+  </si>
+  <si>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
   </si>
 </sst>
 </file>
@@ -8182,7 +7819,7 @@
     </row>
     <row r="2">
       <c r="A2" s="66">
-        <v>46154.0</v>
+        <v>46212.0</v>
       </c>
       <c r="L2" s="67" t="s">
         <v>124</v>
@@ -8335,10 +7972,10 @@
         <v>135</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>137</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>127</v>
@@ -8377,13 +8014,13 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="C7" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>140</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>127</v>
@@ -8401,7 +8038,7 @@
         <v>339039.0</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J7" s="14">
         <v>949835.78</v>
@@ -8422,13 +8059,13 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="C8" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>144</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>127</v>
@@ -8446,7 +8083,7 @@
         <v>339039.0</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J8" s="14">
         <v>524584.95</v>
@@ -8471,10 +8108,10 @@
         <v>91</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>146</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>147</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>127</v>
@@ -8492,7 +8129,7 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J9" s="14">
         <v>211614.23</v>
@@ -8516,10 +8153,10 @@
         <v>98</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>127</v>
@@ -8558,13 +8195,13 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>127</v>
@@ -8606,10 +8243,10 @@
         <v>50</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>127</v>
@@ -8627,7 +8264,7 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8651,10 +8288,10 @@
         <v>123</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>127</v>
@@ -8678,10 +8315,10 @@
         <v>2364771.07</v>
       </c>
       <c r="K13" s="14">
-        <v>259050.36</v>
+        <v>1867169.54</v>
       </c>
       <c r="L13" s="14">
-        <v>2105720.71</v>
+        <v>497601.53</v>
       </c>
       <c r="M13" s="72"/>
       <c r="AB13" s="65"/>
@@ -8697,10 +8334,10 @@
         <v>59</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>127</v>
@@ -8718,7 +8355,7 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J14" s="14">
         <v>968237.39</v>
@@ -8739,13 +8376,13 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>127</v>
@@ -8763,7 +8400,7 @@
         <v>339039.0</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J15" s="14">
         <v>1011677.95</v>
@@ -8784,13 +8421,13 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>127</v>
@@ -8829,13 +8466,13 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>127</v>
@@ -8877,10 +8514,10 @@
         <v>110</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>127</v>
@@ -8898,7 +8535,7 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J18" s="14">
         <v>63746.85</v>
@@ -8919,13 +8556,13 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>127</v>
@@ -8943,7 +8580,7 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8964,13 +8601,13 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>127</v>
@@ -9009,13 +8646,13 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>127</v>
@@ -9057,10 +8694,10 @@
         <v>74</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>127</v>
@@ -9102,10 +8739,10 @@
         <v>114</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>127</v>
@@ -9123,7 +8760,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -9144,13 +8781,13 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>127</v>
@@ -9192,10 +8829,10 @@
         <v>105</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>127</v>
@@ -9213,7 +8850,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -9234,13 +8871,13 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>192</v>
+        <v>130</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D26" s="12" t="s">
         <v>127</v>
@@ -9279,13 +8916,13 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="D27" s="12" t="s">
         <v>127</v>
@@ -9324,13 +8961,13 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>127</v>
@@ -9348,7 +8985,7 @@
         <v>339039.0</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J28" s="14">
         <v>1912292.52</v>
@@ -9368,6 +9005,42 @@
       <c r="AH28" s="65"/>
     </row>
     <row r="29">
+      <c r="A29" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="66">
+        <v>46196.0</v>
+      </c>
+      <c r="F29" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="67">
+        <v>12.0</v>
+      </c>
+      <c r="H29" s="67">
+        <v>339039.0</v>
+      </c>
+      <c r="I29" s="67">
+        <v>2048.0</v>
+      </c>
+      <c r="J29" s="55">
+        <v>1496713.48</v>
+      </c>
+      <c r="K29" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="55">
+        <v>1496713.48</v>
+      </c>
       <c r="AB29" s="65"/>
       <c r="AC29" s="65"/>
       <c r="AD29" s="65"/>
@@ -9377,6 +9050,42 @@
       <c r="AH29" s="65"/>
     </row>
     <row r="30">
+      <c r="A30" s="67" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="D30" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="66">
+        <v>46205.0</v>
+      </c>
+      <c r="F30" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="67">
+        <v>12.0</v>
+      </c>
+      <c r="H30" s="67">
+        <v>339039.0</v>
+      </c>
+      <c r="I30" s="67" t="s">
+        <v>140</v>
+      </c>
+      <c r="J30" s="55">
+        <v>624166.14</v>
+      </c>
+      <c r="K30" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="55">
+        <v>624166.14</v>
+      </c>
       <c r="AB30" s="65"/>
       <c r="AC30" s="65"/>
       <c r="AD30" s="65"/>
@@ -9386,6 +9095,42 @@
       <c r="AH30" s="65"/>
     </row>
     <row r="31">
+      <c r="A31" s="67" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="67" t="s">
+        <v>196</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" s="66">
+        <v>46205.0</v>
+      </c>
+      <c r="F31" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="67">
+        <v>12.0</v>
+      </c>
+      <c r="H31" s="67">
+        <v>339039.0</v>
+      </c>
+      <c r="I31" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="J31" s="55">
+        <v>18462.36</v>
+      </c>
+      <c r="K31" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="55">
+        <v>18462.36</v>
+      </c>
       <c r="AB31" s="65"/>
       <c r="AC31" s="65"/>
       <c r="AD31" s="65"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="199">
   <si>
     <t>Controle de pagamentos</t>
   </si>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>Aprovado e aguardando itens</t>
+  </si>
+  <si>
+    <t>Módulo II – Orçamento 03/26</t>
   </si>
   <si>
     <t>Módulo III – Orçamento 17 Manuais</t>
@@ -2755,7 +2758,7 @@
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="16"/>
       <c r="B37" s="16"/>
-      <c r="C37" s="47"/>
+      <c r="C37" s="32"/>
       <c r="D37" s="52" t="s">
         <v>119</v>
       </c>
@@ -2792,34 +2795,22 @@
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
-      <c r="C38" s="24">
-        <v>3.0</v>
-      </c>
+      <c r="C38" s="47"/>
       <c r="D38" s="52" t="s">
         <v>121</v>
       </c>
       <c r="E38" s="56"/>
-      <c r="F38" s="56">
-        <v>1465.0</v>
-      </c>
-      <c r="G38" s="60">
-        <v>46104.0</v>
-      </c>
-      <c r="H38" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="I38" s="61"/>
-      <c r="J38" s="60">
-        <v>46106.0</v>
-      </c>
-      <c r="K38" s="36">
-        <v>27801.11</v>
-      </c>
+      <c r="F38" s="56"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="36"/>
       <c r="L38" s="26"/>
-      <c r="M38" s="62">
-        <v>27801.11</v>
-      </c>
-      <c r="N38" s="41"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="41">
+        <v>24962.38</v>
+      </c>
       <c r="O38" s="18"/>
       <c r="P38" s="20"/>
       <c r="Q38" s="20"/>
@@ -2837,42 +2828,81 @@
       <c r="AC38" s="20"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="32"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="24">
+        <v>3.0</v>
+      </c>
       <c r="D39" s="52" t="s">
         <v>122</v>
       </c>
       <c r="E39" s="56"/>
       <c r="F39" s="56">
-        <v>1882.0</v>
+        <v>1465.0</v>
       </c>
       <c r="G39" s="60">
-        <v>46199.0</v>
+        <v>46104.0</v>
       </c>
       <c r="H39" s="56" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="I39" s="61"/>
       <c r="J39" s="60">
-        <v>46233.0</v>
+        <v>46106.0</v>
       </c>
       <c r="K39" s="36">
-        <v>58868.35</v>
+        <v>27801.11</v>
       </c>
       <c r="L39" s="26"/>
       <c r="M39" s="62">
-        <v>58868.35</v>
+        <v>27801.11</v>
       </c>
       <c r="N39" s="41"/>
-      <c r="V39" s="2"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+      <c r="R39" s="20"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="42"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="20"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="32"/>
-      <c r="K40" s="63"/>
-      <c r="M40" s="63"/>
+      <c r="D40" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56">
+        <v>1882.0</v>
+      </c>
+      <c r="G40" s="60">
+        <v>46199.0</v>
+      </c>
+      <c r="H40" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="I40" s="61"/>
+      <c r="J40" s="60">
+        <v>46233.0</v>
+      </c>
+      <c r="K40" s="36">
+        <v>58868.35</v>
+      </c>
+      <c r="L40" s="26"/>
+      <c r="M40" s="62">
+        <v>58868.35</v>
+      </c>
+      <c r="N40" s="41"/>
       <c r="V40" s="2"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
@@ -2887,6 +2917,8 @@
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="32"/>
+      <c r="K42" s="63"/>
+      <c r="M42" s="63"/>
       <c r="V42" s="2"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
@@ -2910,38 +2942,40 @@
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
-      <c r="C46" s="47"/>
-      <c r="K46" s="63"/>
-      <c r="M46" s="63"/>
+      <c r="C46" s="32"/>
       <c r="V46" s="2"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="64"/>
-      <c r="Q47" s="64"/>
-      <c r="R47" s="64"/>
-      <c r="S47" s="64"/>
-      <c r="T47" s="64"/>
-      <c r="U47" s="64"/>
+      <c r="C47" s="47"/>
+      <c r="K47" s="63"/>
+      <c r="M47" s="63"/>
       <c r="V47" s="2"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="64"/>
+      <c r="Q48" s="64"/>
+      <c r="R48" s="64"/>
+      <c r="S48" s="64"/>
+      <c r="T48" s="64"/>
+      <c r="U48" s="64"/>
+      <c r="V48" s="2"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="8"/>
@@ -3154,7 +3188,6 @@
     <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
-      <c r="L101" s="15"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="8"/>
@@ -7771,12 +7804,17 @@
       <c r="B1024" s="8"/>
       <c r="L1024" s="15"/>
     </row>
+    <row r="1025" ht="12.75" customHeight="1">
+      <c r="A1025" s="8"/>
+      <c r="B1025" s="8"/>
+      <c r="L1025" s="15"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:U2"/>
     <mergeCell ref="C9:C26"/>
-    <mergeCell ref="C28:C37"/>
-    <mergeCell ref="C38:C46"/>
+    <mergeCell ref="C28:C38"/>
+    <mergeCell ref="C39:C47"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.7875" footer="0.0" header="0.0" left="0.7875" right="0.7875" top="0.7875"/>
@@ -7822,7 +7860,7 @@
         <v>46212.0</v>
       </c>
       <c r="L2" s="67" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AB2" s="65"/>
       <c r="AC2" s="65"/>
@@ -7834,22 +7872,22 @@
     </row>
     <row r="3">
       <c r="A3" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" s="68">
         <v>2.5E32</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" s="69">
         <v>45686.0</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G3" s="12">
         <v>12.0</v>
@@ -7879,22 +7917,22 @@
     </row>
     <row r="4">
       <c r="A4" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E4" s="69">
         <v>45762.0</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G4" s="12">
         <v>12.0</v>
@@ -7924,22 +7962,22 @@
     </row>
     <row r="5">
       <c r="A5" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E5" s="69">
         <v>45762.0</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G5" s="12">
         <v>12.0</v>
@@ -7969,22 +8007,22 @@
     </row>
     <row r="6">
       <c r="A6" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6" s="69">
         <v>45762.0</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G6" s="12">
         <v>12.0</v>
@@ -8014,22 +8052,22 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E7" s="69">
         <v>45763.0</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G7" s="12">
         <v>12.0</v>
@@ -8038,7 +8076,7 @@
         <v>339039.0</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J7" s="14">
         <v>949835.78</v>
@@ -8059,22 +8097,22 @@
     </row>
     <row r="8">
       <c r="A8" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E8" s="69">
         <v>45763.0</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G8" s="12">
         <v>12.0</v>
@@ -8083,7 +8121,7 @@
         <v>339039.0</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J8" s="14">
         <v>524584.95</v>
@@ -8108,19 +8146,19 @@
         <v>91</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E9" s="69">
         <v>45792.0</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G9" s="12">
         <v>12.0</v>
@@ -8129,7 +8167,7 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J9" s="14">
         <v>211614.23</v>
@@ -8153,19 +8191,19 @@
         <v>98</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E10" s="69">
         <v>45825.0</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G10" s="12">
         <v>12.0</v>
@@ -8195,22 +8233,22 @@
     </row>
     <row r="11">
       <c r="A11" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" s="69">
         <v>45825.0</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G11" s="12">
         <v>12.0</v>
@@ -8243,19 +8281,19 @@
         <v>50</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12" s="69">
         <v>45832.0</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G12" s="12">
         <v>12.0</v>
@@ -8264,7 +8302,7 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8285,22 +8323,22 @@
     </row>
     <row r="13">
       <c r="A13" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" s="69">
         <v>45863.0</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G13" s="12">
         <v>12.0</v>
@@ -8334,19 +8372,19 @@
         <v>59</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14" s="69">
         <v>45887.0</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G14" s="12">
         <v>12.0</v>
@@ -8355,7 +8393,7 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J14" s="14">
         <v>968237.39</v>
@@ -8376,22 +8414,22 @@
     </row>
     <row r="15">
       <c r="A15" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E15" s="69">
         <v>45924.0</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G15" s="12">
         <v>12.0</v>
@@ -8400,7 +8438,7 @@
         <v>339039.0</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J15" s="14">
         <v>1011677.95</v>
@@ -8421,22 +8459,22 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E16" s="69">
         <v>45929.0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G16" s="12">
         <v>12.0</v>
@@ -8466,22 +8504,22 @@
     </row>
     <row r="17">
       <c r="A17" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" s="69">
         <v>45930.0</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G17" s="12">
         <v>12.0</v>
@@ -8514,19 +8552,19 @@
         <v>110</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E18" s="69">
         <v>45938.0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G18" s="12">
         <v>12.0</v>
@@ -8535,7 +8573,7 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J18" s="14">
         <v>63746.85</v>
@@ -8556,22 +8594,22 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19" s="69">
         <v>45938.0</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G19" s="12">
         <v>12.0</v>
@@ -8580,7 +8618,7 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8601,22 +8639,22 @@
     </row>
     <row r="20">
       <c r="A20" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E20" s="69">
         <v>45938.0</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G20" s="12">
         <v>12.0</v>
@@ -8646,22 +8684,22 @@
     </row>
     <row r="21">
       <c r="A21" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E21" s="69">
         <v>45938.0</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G21" s="12">
         <v>12.0</v>
@@ -8694,19 +8732,19 @@
         <v>74</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E22" s="73">
         <v>45953.0</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G22" s="12">
         <v>12.0</v>
@@ -8739,19 +8777,19 @@
         <v>114</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E23" s="73">
         <v>45953.0</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G23" s="12">
         <v>12.0</v>
@@ -8760,7 +8798,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -8781,22 +8819,22 @@
     </row>
     <row r="24">
       <c r="A24" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E24" s="73">
         <v>45953.0</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G24" s="12">
         <v>12.0</v>
@@ -8829,19 +8867,19 @@
         <v>105</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E25" s="73">
         <v>45975.0</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G25" s="12">
         <v>12.0</v>
@@ -8850,7 +8888,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -8871,22 +8909,22 @@
     </row>
     <row r="26">
       <c r="A26" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E26" s="73">
         <v>45989.0</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G26" s="12">
         <v>12.0</v>
@@ -8916,22 +8954,22 @@
     </row>
     <row r="27">
       <c r="A27" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E27" s="69">
         <v>46104.0</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G27" s="12">
         <v>12.0</v>
@@ -8961,22 +8999,22 @@
     </row>
     <row r="28">
       <c r="A28" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E28" s="69">
         <v>46120.0</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G28" s="12">
         <v>12.0</v>
@@ -8985,7 +9023,7 @@
         <v>339039.0</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J28" s="14">
         <v>1912292.52</v>
@@ -9006,22 +9044,22 @@
     </row>
     <row r="29">
       <c r="A29" s="67" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B29" s="67" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="67" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="67" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E29" s="66">
         <v>46196.0</v>
       </c>
       <c r="F29" s="67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G29" s="67">
         <v>12.0</v>
@@ -9051,22 +9089,22 @@
     </row>
     <row r="30">
       <c r="A30" s="67" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="67" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C30" s="67" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D30" s="67" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E30" s="66">
         <v>46205.0</v>
       </c>
       <c r="F30" s="67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G30" s="67">
         <v>12.0</v>
@@ -9075,7 +9113,7 @@
         <v>339039.0</v>
       </c>
       <c r="I30" s="67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J30" s="55">
         <v>624166.14</v>
@@ -9096,22 +9134,22 @@
     </row>
     <row r="31">
       <c r="A31" s="67" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B31" s="67" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C31" s="67" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D31" s="67" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E31" s="66">
         <v>46205.0</v>
       </c>
       <c r="F31" s="67" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G31" s="67">
         <v>12.0</v>
@@ -9120,7 +9158,7 @@
         <v>339039.0</v>
       </c>
       <c r="I31" s="67" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J31" s="55">
         <v>18462.36</v>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="201">
   <si>
     <t>Controle de pagamentos</t>
   </si>
@@ -629,6 +629,12 @@
   </si>
   <si>
     <t>26E0777</t>
+  </si>
+  <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
   </si>
 </sst>
 </file>
@@ -9178,7 +9184,42 @@
       <c r="AH31" s="65"/>
     </row>
     <row r="32">
-      <c r="C32" s="55"/>
+      <c r="A32" s="67" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>197</v>
+      </c>
+      <c r="C32" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="67" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="66">
+        <v>46213.0</v>
+      </c>
+      <c r="F32" s="67" t="s">
+        <v>129</v>
+      </c>
+      <c r="G32" s="67">
+        <v>12.0</v>
+      </c>
+      <c r="H32" s="67">
+        <v>339039.0</v>
+      </c>
+      <c r="I32" s="67" t="s">
+        <v>177</v>
+      </c>
+      <c r="J32" s="55">
+        <v>1530656.62</v>
+      </c>
+      <c r="K32" s="67">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="55">
+        <v>1530656.62</v>
+      </c>
       <c r="AB32" s="65"/>
       <c r="AC32" s="65"/>
       <c r="AD32" s="65"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,12 +30,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="204">
   <si>
+    <t>Saldo</t>
+  </si>
+  <si>
     <t>Controle de pagamentos</t>
   </si>
   <si>
-    <t>Saldo</t>
-  </si>
-  <si>
     <t>2025NE000005</t>
   </si>
   <si>
@@ -72,6 +72,15 @@
     <t>Prazo Final de Execução</t>
   </si>
   <si>
+    <t>2025NE000369</t>
+  </si>
+  <si>
+    <t>C25516</t>
+  </si>
+  <si>
+    <t>25E0387</t>
+  </si>
+  <si>
     <t>Prazo Final de Vigência</t>
   </si>
   <si>
@@ -90,21 +99,12 @@
     <t>Valor Total do Contrato</t>
   </si>
   <si>
-    <t>2025NE000369</t>
-  </si>
-  <si>
     <t>Valor a Empenhar</t>
   </si>
   <si>
-    <t>C25516</t>
-  </si>
-  <si>
     <t>Valor Empenhado</t>
   </si>
   <si>
-    <t>25E0387</t>
-  </si>
-  <si>
     <t>Valor Liquidado</t>
   </si>
   <si>
@@ -120,12 +120,12 @@
     <t>Abrir</t>
   </si>
   <si>
+    <t>2025NE000371</t>
+  </si>
+  <si>
     <t>Editar</t>
   </si>
   <si>
-    <t>2025NE000371</t>
-  </si>
-  <si>
     <t>25E0389</t>
   </si>
   <si>
@@ -138,6 +138,15 @@
     <t>PAMALS</t>
   </si>
   <si>
+    <t>2025NE000413</t>
+  </si>
+  <si>
+    <t>C25501</t>
+  </si>
+  <si>
+    <t>25E0403</t>
+  </si>
+  <si>
     <t>Vigente</t>
   </si>
   <si>
@@ -147,24 +156,15 @@
     <t>67101.001510/2024-12</t>
   </si>
   <si>
+    <t>20SP</t>
+  </si>
+  <si>
     <t>R$</t>
   </si>
   <si>
-    <t>2025NE000413</t>
-  </si>
-  <si>
-    <t>C25501</t>
-  </si>
-  <si>
-    <t>25E0403</t>
-  </si>
-  <si>
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
-    <t>20SP</t>
-  </si>
-  <si>
     <t>2025NE000414</t>
   </si>
   <si>
@@ -177,22 +177,46 @@
     <t>21EM</t>
   </si>
   <si>
+    <t>2025NE000559</t>
+  </si>
+  <si>
+    <t>C25545</t>
+  </si>
+  <si>
+    <t>25E0524</t>
+  </si>
+  <si>
+    <t>20X7</t>
+  </si>
+  <si>
+    <t>2025NE000770</t>
+  </si>
+  <si>
+    <t>25E0731</t>
+  </si>
+  <si>
     <t>Módulo</t>
   </si>
   <si>
+    <t>2025NE000774</t>
+  </si>
+  <si>
+    <t>25E0737</t>
+  </si>
+  <si>
     <t>Referência</t>
   </si>
   <si>
-    <t>2025NE000559</t>
-  </si>
-  <si>
     <t>Nº recibo</t>
   </si>
   <si>
-    <t>C25545</t>
-  </si>
-  <si>
-    <t>25E0524</t>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
+    <t>25E0787</t>
   </si>
   <si>
     <t>Nº</t>
@@ -201,12 +225,12 @@
     <t>Data</t>
   </si>
   <si>
+    <t>219C</t>
+  </si>
+  <si>
     <t>Empenho</t>
   </si>
   <si>
-    <t>20X7</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
@@ -219,10 +243,10 @@
     <t>Ordem de Pagamento</t>
   </si>
   <si>
-    <t>2025NE000770</t>
-  </si>
-  <si>
-    <t>25E0731</t>
+    <t>2025NE001065</t>
+  </si>
+  <si>
+    <t>25E0999</t>
   </si>
   <si>
     <t>Faturado</t>
@@ -231,10 +255,13 @@
     <t>Pendente</t>
   </si>
   <si>
-    <t>2025NE000774</t>
-  </si>
-  <si>
-    <t>25E0737</t>
+    <t>2025NE001200</t>
+  </si>
+  <si>
+    <t>C25590</t>
+  </si>
+  <si>
+    <t>25E1128</t>
   </si>
   <si>
     <t>FEV/25</t>
@@ -243,40 +270,61 @@
     <t>-</t>
   </si>
   <si>
-    <t>2025NE000843</t>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
+  </si>
+  <si>
+    <t>2025NE001627</t>
+  </si>
+  <si>
+    <t>25E1475</t>
   </si>
   <si>
     <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
-  </si>
-  <si>
-    <t>219C</t>
+    <t>2025NE001629</t>
+  </si>
+  <si>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
   </si>
   <si>
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
+    <t>2025NE001687</t>
+  </si>
+  <si>
+    <t>25E1535</t>
+  </si>
+  <si>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
+  </si>
+  <si>
+    <t>2025NE001689</t>
+  </si>
+  <si>
+    <t>25E1537</t>
   </si>
   <si>
     <t>MAR/25</t>
   </si>
   <si>
-    <t>2025NE001200</t>
-  </si>
-  <si>
-    <t>C25590</t>
-  </si>
-  <si>
-    <t>25E1128</t>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
   </si>
   <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
@@ -285,58 +333,100 @@
     <t>2025NP001979</t>
   </si>
   <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>25E1446</t>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
+  </si>
+  <si>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
   </si>
   <si>
     <t>ABR/25</t>
   </si>
   <si>
+    <t>2025NE001830</t>
+  </si>
+  <si>
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>2025NE001627</t>
-  </si>
-  <si>
-    <t>25E1475</t>
+    <t>25E1669</t>
   </si>
   <si>
     <t>2025NP002341</t>
   </si>
   <si>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
+  </si>
+  <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>2025NE001629</t>
-  </si>
-  <si>
-    <t>C25820</t>
-  </si>
-  <si>
-    <t>25E1477</t>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
+  </si>
+  <si>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
+  </si>
+  <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
   </si>
   <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>2025NE001687</t>
-  </si>
-  <si>
-    <t>25E1535</t>
+    <t>26E0375</t>
+  </si>
+  <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
   </si>
   <si>
     <t>JUN/25</t>
   </si>
   <si>
-    <t>2025NE001688</t>
-  </si>
-  <si>
-    <t>25E1536</t>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -348,176 +438,86 @@
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2025NE001689</t>
-  </si>
-  <si>
-    <t>25E1537</t>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
   </si>
   <si>
     <t>JUL/25</t>
   </si>
   <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
+  </si>
+  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
-  </si>
-  <si>
     <t>AGO/25</t>
   </si>
   <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
-  </si>
-  <si>
     <t>2025NP004558</t>
   </si>
   <si>
     <t>SET/25</t>
-  </si>
-  <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
   </si>
   <si>
     <t>2025NE001688 
 2025NE001828</t>
   </si>
   <si>
-    <t>20YJ</t>
-  </si>
-  <si>
     <t>2025NP004897</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
-  </si>
-  <si>
     <t>OUT/25</t>
   </si>
   <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
-  </si>
-  <si>
     <t>2025NP004932</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
-  </si>
-  <si>
     <t>NOV/25</t>
   </si>
   <si>
     <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
   </si>
   <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
-  </si>
-  <si>
     <t>2026NP400440</t>
   </si>
   <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
     <t>DEZ/25</t>
   </si>
   <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
     <t>2025NE001065, 2025NE002200</t>
   </si>
   <si>
     <t>2026NP400412</t>
   </si>
   <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
     <t>JAN/26</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
     <t>2026NP401035</t>
   </si>
   <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
     <t>FEV/26</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
     <t>2025NE001627, 2025NE001629, 2025NE001823</t>
   </si>
   <si>
     <t>2026NP402272</t>
-  </si>
-  <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
   </si>
   <si>
     <t>MAR/26</t>
@@ -656,8 +656,8 @@
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="MM/DD/YY"/>
-    <numFmt numFmtId="170" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
     <numFmt numFmtId="171" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12">
@@ -852,35 +852,35 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -907,6 +907,9 @@
     <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -919,9 +922,6 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -931,6 +931,7 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -955,15 +956,17 @@
     <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -975,23 +978,20 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1400,42 +1400,42 @@
       <c r="V1" s="3"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="9"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
       <c r="V3" s="3"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -1457,28 +1457,28 @@
         <v>13</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P4" s="18" t="s">
         <v>25</v>
@@ -1496,7 +1496,7 @@
         <v>29</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V4" s="3"/>
     </row>
@@ -1504,16 +1504,16 @@
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="19"/>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="8" t="s">
         <v>35</v>
       </c>
       <c r="H5" s="20">
@@ -1522,17 +1522,17 @@
       <c r="I5" s="20">
         <v>1564.0</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" s="10" t="s">
+      <c r="J5" s="8" t="s">
         <v>39</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="N5" s="14">
         <v>9.165159737E7</v>
@@ -1549,8 +1549,8 @@
       <c r="R5" s="14">
         <v>1.085943044E7</v>
       </c>
-      <c r="S5" s="10" t="s">
-        <v>43</v>
+      <c r="S5" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="V5" s="3"/>
     </row>
@@ -1563,829 +1563,829 @@
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="26"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="27"/>
       <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="22"/>
       <c r="B8" s="22"/>
       <c r="C8" s="28" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I8" s="29" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="O8" s="28"/>
-      <c r="P8" s="26"/>
+      <c r="P8" s="27"/>
       <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="22"/>
       <c r="B9" s="22"/>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <v>1.0</v>
       </c>
-      <c r="D9" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="34">
+      <c r="D9" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="35">
         <v>594.0</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="36">
         <v>45740.0</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35">
+      <c r="H9" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36">
         <v>45778.0</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="37">
         <v>748504.24</v>
       </c>
-      <c r="L9" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="M9" s="37">
+      <c r="L9" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="38">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
-      <c r="N9" s="38"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="26"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="27"/>
       <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
       <c r="A10" s="22"/>
       <c r="B10" s="22"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <v>620.0</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="36">
         <v>45775.0</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35">
+      <c r="H10" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36">
         <v>45806.0</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="37">
         <v>1110378.24</v>
       </c>
-      <c r="L10" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="M10" s="37">
+      <c r="L10" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="M10" s="38">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
-      <c r="N10" s="41"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="26"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="27"/>
       <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="22"/>
       <c r="B11" s="22"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="D11" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="35">
         <v>634.0</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <v>45799.0</v>
       </c>
-      <c r="H11" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35">
+      <c r="H11" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36">
         <v>45844.0</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="37">
         <v>974557.12</v>
       </c>
-      <c r="L11" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="M11" s="37">
+      <c r="L11" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="M11" s="38">
         <v>974557.12</v>
       </c>
-      <c r="N11" s="41"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="26"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="27"/>
       <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="33">
+      <c r="D12" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="34">
         <v>660.0</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <v>45856.0</v>
       </c>
-      <c r="H12" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35">
+      <c r="H12" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36">
         <v>45891.0</v>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="45">
         <v>1402001.34</v>
       </c>
-      <c r="L12" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="M12" s="37">
+      <c r="L12" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="M12" s="38">
         <v>1402001.34</v>
       </c>
-      <c r="N12" s="46"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="26"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="27"/>
       <c r="V12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="22"/>
       <c r="B13" s="22"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="47" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="34">
+      <c r="D13" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="35">
         <v>661.0</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <v>45856.0</v>
       </c>
-      <c r="H13" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42">
+      <c r="H13" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43">
         <v>45891.0</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="45">
         <v>1223702.3</v>
       </c>
-      <c r="L13" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="M13" s="37">
+      <c r="L13" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="M13" s="38">
         <v>1223702.3</v>
       </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="48"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="50"/>
       <c r="V13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="33">
+      <c r="D14" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" s="34">
         <v>688.0</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="36">
         <v>45901.0</v>
       </c>
-      <c r="H14" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42">
+      <c r="H14" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="45">
         <v>1011677.95</v>
       </c>
-      <c r="L14" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="M14" s="37">
+      <c r="L14" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="M14" s="38">
         <v>1011677.95</v>
       </c>
-      <c r="N14" s="41"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="26"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="27"/>
       <c r="V14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="22"/>
       <c r="B15" s="22"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="33">
+      <c r="D15" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="34">
         <v>696.0</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="36">
         <v>45923.0</v>
       </c>
-      <c r="H15" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42">
+      <c r="H15" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="45">
         <v>896744.06</v>
       </c>
-      <c r="L15" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="M15" s="37">
+      <c r="L15" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="M15" s="38">
         <v>896744.06</v>
       </c>
-      <c r="N15" s="46"/>
-      <c r="O15" s="24"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="25"/>
       <c r="V15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="47" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="33">
+      <c r="D16" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="34">
         <v>704.0</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="36">
         <v>45957.0</v>
       </c>
-      <c r="H16" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42">
+      <c r="H16" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43">
         <v>46003.0</v>
       </c>
-      <c r="K16" s="44">
+      <c r="K16" s="45">
         <v>919329.06</v>
       </c>
-      <c r="L16" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="M16" s="37">
+      <c r="L16" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="M16" s="38">
         <v>919329.06</v>
       </c>
-      <c r="N16" s="41"/>
-      <c r="O16" s="24"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="25"/>
       <c r="V16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33">
+      <c r="D17" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34">
         <v>705.0</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="43">
         <v>45972.0</v>
       </c>
-      <c r="H17" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="42">
+      <c r="H17" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="I17" s="34"/>
+      <c r="J17" s="43">
         <v>46016.0</v>
       </c>
-      <c r="K17" s="44">
+      <c r="K17" s="45">
         <v>1157009.26</v>
       </c>
-      <c r="L17" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="M17" s="37">
+      <c r="L17" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="M17" s="38">
         <v>1157009.26</v>
       </c>
-      <c r="N17" s="50"/>
-      <c r="O17" s="24"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="25"/>
       <c r="V17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="33">
+      <c r="D18" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="34">
         <v>728.0</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="43">
         <v>46008.0</v>
       </c>
-      <c r="H18" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="42">
+      <c r="H18" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="43">
         <v>46040.0</v>
       </c>
-      <c r="K18" s="44">
+      <c r="K18" s="45">
         <v>1214597.952</v>
       </c>
-      <c r="L18" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="M18" s="37">
+      <c r="L18" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="M18" s="38">
         <v>1214597.952</v>
       </c>
-      <c r="N18" s="50"/>
-      <c r="O18" s="24"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="51"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="25"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="52"/>
     </row>
     <row r="19">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="40"/>
-      <c r="D19" s="47" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="33">
+      <c r="D19" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="34">
         <v>278.0</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="43">
         <v>46042.0</v>
       </c>
-      <c r="H19" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42">
+      <c r="H19" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43">
         <v>46074.0</v>
       </c>
-      <c r="K19" s="44">
+      <c r="K19" s="45">
         <v>967082.09</v>
       </c>
-      <c r="L19" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="M19" s="37">
+      <c r="L19" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="M19" s="38">
         <v>967082.09</v>
       </c>
-      <c r="N19" s="50"/>
-      <c r="O19" s="24"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="51"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="25"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="52"/>
     </row>
     <row r="20">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33">
+      <c r="D20" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34">
         <v>10.0</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="43">
         <v>46078.0</v>
       </c>
-      <c r="H20" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42">
+      <c r="H20" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43">
         <v>46106.0</v>
       </c>
-      <c r="K20" s="44">
+      <c r="K20" s="45">
         <v>719561.08</v>
       </c>
-      <c r="L20" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="M20" s="37">
+      <c r="L20" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="M20" s="38">
         <v>719561.08</v>
       </c>
-      <c r="N20" s="50"/>
-      <c r="O20" s="24"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="51"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="25"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="52"/>
     </row>
     <row r="21">
       <c r="A21" s="22"/>
       <c r="B21" s="22"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="47" t="s">
-        <v>154</v>
-      </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33">
+      <c r="D21" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34">
         <v>15.0</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="43">
         <v>46094.0</v>
       </c>
-      <c r="H21" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42">
+      <c r="H21" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43">
         <v>46128.0</v>
       </c>
-      <c r="K21" s="44">
+      <c r="K21" s="45">
         <v>885881.08</v>
       </c>
-      <c r="L21" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="M21" s="37">
+      <c r="L21" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="M21" s="38">
         <v>885881.08</v>
       </c>
-      <c r="N21" s="50"/>
-      <c r="O21" s="24"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="51"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="25"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
+      <c r="V21" s="52"/>
     </row>
     <row r="22">
       <c r="A22" s="22"/>
       <c r="B22" s="22"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33">
+      <c r="E22" s="34"/>
+      <c r="F22" s="34">
         <v>28.0</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="43">
         <v>46128.0</v>
       </c>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42">
+      <c r="I22" s="43"/>
+      <c r="J22" s="43">
         <v>46164.0</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="L22" s="33" t="s">
+      <c r="L22" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="M22" s="37" t="s">
+      <c r="M22" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="N22" s="50"/>
-      <c r="O22" s="24"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="51"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="25"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="52"/>
     </row>
     <row r="23">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="40"/>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33">
+      <c r="E23" s="34"/>
+      <c r="F23" s="34">
         <v>33.0</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="43">
         <v>46156.0</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42">
+      <c r="I23" s="43"/>
+      <c r="J23" s="43">
         <v>46191.0</v>
       </c>
-      <c r="K23" s="44">
+      <c r="K23" s="45">
         <v>1108954.4358333333</v>
       </c>
-      <c r="L23" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="M23" s="37">
+      <c r="L23" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="M23" s="38">
         <v>1108954.4358333333</v>
       </c>
       <c r="N23" s="53"/>
-      <c r="O23" s="24"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
-      <c r="V23" s="51"/>
+      <c r="O23" s="25"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="52"/>
     </row>
     <row r="24">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33">
+      <c r="E24" s="34"/>
+      <c r="F24" s="34">
         <v>29.0</v>
       </c>
-      <c r="G24" s="42">
+      <c r="G24" s="43">
         <v>46149.0</v>
       </c>
-      <c r="H24" s="33" t="s">
+      <c r="H24" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42">
+      <c r="I24" s="43"/>
+      <c r="J24" s="43">
         <v>46185.0</v>
       </c>
-      <c r="K24" s="44">
+      <c r="K24" s="45">
         <v>218206.1</v>
       </c>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="M24" s="37">
+      <c r="M24" s="38">
         <v>218206.1</v>
       </c>
       <c r="N24" s="54"/>
-      <c r="O24" s="24"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="51"/>
+      <c r="O24" s="25"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="52"/>
     </row>
     <row r="25">
       <c r="A25" s="22"/>
       <c r="B25" s="22"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="33"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="55">
         <v>40.0</v>
       </c>
-      <c r="G25" s="42">
+      <c r="G25" s="43">
         <v>46156.0</v>
       </c>
       <c r="H25" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="42"/>
+      <c r="I25" s="43"/>
       <c r="J25" s="56">
         <v>46191.0</v>
       </c>
-      <c r="K25" s="44">
+      <c r="K25" s="45">
         <v>1549250.84</v>
       </c>
-      <c r="L25" s="33" t="s">
+      <c r="L25" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="38">
         <v>1549250.84</v>
       </c>
       <c r="N25" s="53"/>
-      <c r="O25" s="24"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="51"/>
+      <c r="O25" s="25"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="57"/>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="33"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="55"/>
-      <c r="G26" s="42"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="55"/>
-      <c r="I26" s="42"/>
+      <c r="I26" s="43"/>
       <c r="J26" s="56"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="37" t="s">
+      <c r="K26" s="45"/>
+      <c r="L26" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="M26" s="38" t="s">
         <v>173</v>
       </c>
       <c r="N26" s="53"/>
-      <c r="O26" s="24"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="51"/>
+      <c r="O26" s="25"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
       <c r="A27" s="22"/>
       <c r="B27" s="22"/>
       <c r="C27" s="28" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G27" s="28"/>
       <c r="H27" s="28" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
       <c r="K27" s="58" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="L27" s="30" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M27" s="59" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="N27" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="O27" s="24"/>
-      <c r="P27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
-      <c r="V27" s="51"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="26"/>
+        <v>74</v>
+      </c>
+      <c r="O27" s="25"/>
+      <c r="P27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>2.0</v>
       </c>
       <c r="D28" s="60" t="s">
         <v>174</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34">
+      <c r="E28" s="35"/>
+      <c r="F28" s="35">
         <v>402.0</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="36">
         <v>45791.0</v>
       </c>
-      <c r="H28" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35">
+      <c r="H28" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36">
         <v>45834.0</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="37">
         <v>188246.17</v>
       </c>
-      <c r="L28" s="33" t="s">
+      <c r="L28" s="34" t="s">
         <v>175</v>
       </c>
       <c r="M28" s="61">
         <v>188246.17</v>
       </c>
-      <c r="N28" s="50"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="51"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="26"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="26"/>
-      <c r="AC28" s="26"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="52"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
     </row>
     <row r="29">
       <c r="A29" s="22"/>
@@ -2397,44 +2397,44 @@
       <c r="E29" s="55">
         <v>46.0</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="35">
         <v>447.0</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="36">
         <v>45814.0</v>
       </c>
-      <c r="H29" s="33" t="s">
+      <c r="H29" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42">
+      <c r="I29" s="43"/>
+      <c r="J29" s="43">
         <v>45955.0</v>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="37">
         <v>112720.77</v>
       </c>
-      <c r="L29" s="33" t="s">
+      <c r="L29" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="38">
         <v>112720.77</v>
       </c>
-      <c r="N29" s="50"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="51"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="26"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="52"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="22"/>
@@ -2446,44 +2446,44 @@
       <c r="E30" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>529.0</v>
       </c>
       <c r="G30" s="64">
         <v>45853.0</v>
       </c>
-      <c r="H30" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42">
+      <c r="H30" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43">
         <v>45939.0</v>
       </c>
-      <c r="K30" s="44">
+      <c r="K30" s="45">
         <v>378307.61</v>
       </c>
-      <c r="L30" s="33" t="s">
+      <c r="L30" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="38">
         <v>378307.61</v>
       </c>
-      <c r="N30" s="50"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="51"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="26"/>
-      <c r="Y30" s="26"/>
-      <c r="Z30" s="26"/>
-      <c r="AA30" s="26"/>
-      <c r="AB30" s="26"/>
-      <c r="AC30" s="26"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="52"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="27"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="27"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
       <c r="A31" s="22"/>
@@ -2495,44 +2495,44 @@
       <c r="E31" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>691.0</v>
       </c>
       <c r="G31" s="64">
         <v>45910.0</v>
       </c>
-      <c r="H31" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42">
+      <c r="H31" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43">
         <v>45941.0</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>3315.0471000000252</v>
       </c>
-      <c r="L31" s="33" t="s">
+      <c r="L31" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="38">
         <v>3315.04710000003</v>
       </c>
-      <c r="N31" s="50"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="52"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="51"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="26"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="52"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="27"/>
+      <c r="AB31" s="27"/>
+      <c r="AC31" s="27"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="22"/>
@@ -2544,44 +2544,44 @@
       <c r="E32" s="65">
         <v>135.0</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="34">
         <v>677.0</v>
       </c>
       <c r="G32" s="64">
         <v>45904.0</v>
       </c>
-      <c r="H32" s="33" t="s">
-        <v>71</v>
+      <c r="H32" s="34" t="s">
+        <v>60</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K32" s="44">
+      <c r="K32" s="45">
         <v>198332.75</v>
       </c>
-      <c r="L32" s="33" t="s">
+      <c r="L32" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="M32" s="37">
+      <c r="M32" s="38">
         <v>198332.75</v>
       </c>
-      <c r="N32" s="50"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="51"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="26"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="26"/>
-      <c r="AC32" s="26"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="48"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="27"/>
+      <c r="AB32" s="27"/>
+      <c r="AC32" s="27"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="22"/>
@@ -2593,20 +2593,20 @@
       <c r="E33" s="65">
         <v>40.0</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>278.0</v>
       </c>
       <c r="G33" s="64">
         <v>46008.0</v>
       </c>
-      <c r="H33" s="33" t="s">
-        <v>128</v>
+      <c r="H33" s="34" t="s">
+        <v>113</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
         <v>46066.0</v>
       </c>
-      <c r="K33" s="44">
+      <c r="K33" s="45">
         <v>1528.62</v>
       </c>
       <c r="L33" s="67" t="s">
@@ -2615,22 +2615,22 @@
       <c r="M33" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="N33" s="50"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="52"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="51"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="26"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
-      <c r="AA33" s="26"/>
-      <c r="AB33" s="26"/>
-      <c r="AC33" s="26"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="52"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27"/>
+      <c r="Y33" s="27"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="27"/>
+      <c r="AB33" s="27"/>
+      <c r="AC33" s="27"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="22"/>
@@ -2642,44 +2642,44 @@
       <c r="E34" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>748.0</v>
       </c>
       <c r="G34" s="64">
         <v>45930.0</v>
       </c>
-      <c r="H34" s="33" t="s">
-        <v>98</v>
+      <c r="H34" s="34" t="s">
+        <v>90</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K34" s="44">
+      <c r="K34" s="45">
         <v>38718.58</v>
       </c>
-      <c r="L34" s="33" t="s">
+      <c r="L34" s="34" t="s">
         <v>191</v>
       </c>
       <c r="M34" s="61" t="s">
         <v>192</v>
       </c>
-      <c r="N34" s="50"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="52"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
-      <c r="V34" s="51"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="26"/>
-      <c r="Y34" s="26"/>
-      <c r="Z34" s="26"/>
-      <c r="AA34" s="26"/>
-      <c r="AB34" s="26"/>
-      <c r="AC34" s="26"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="48"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="52"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="27"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="27"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="22"/>
@@ -2691,44 +2691,44 @@
       <c r="E35" s="65">
         <v>154.0</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>822.0</v>
       </c>
       <c r="G35" s="64">
         <v>45968.0</v>
       </c>
-      <c r="H35" s="33" t="s">
-        <v>118</v>
+      <c r="H35" s="34" t="s">
+        <v>104</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K35" s="44">
+      <c r="K35" s="45">
         <v>133124.11</v>
       </c>
-      <c r="L35" s="33" t="s">
+      <c r="L35" s="34" t="s">
         <v>194</v>
       </c>
       <c r="M35" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="N35" s="50"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
-      <c r="V35" s="51"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="26"/>
-      <c r="Y35" s="26"/>
-      <c r="Z35" s="26"/>
-      <c r="AA35" s="26"/>
-      <c r="AB35" s="26"/>
-      <c r="AC35" s="26"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="27"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="27"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="22"/>
@@ -2747,37 +2747,37 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
         <v>46075.0</v>
       </c>
-      <c r="K36" s="44">
+      <c r="K36" s="45">
         <v>11372.9</v>
       </c>
-      <c r="L36" s="33" t="s">
+      <c r="L36" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="M36" s="37">
+      <c r="M36" s="38">
         <v>11372.9</v>
       </c>
-      <c r="N36" s="50"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="51"/>
-      <c r="W36" s="26"/>
-      <c r="X36" s="26"/>
-      <c r="Y36" s="26"/>
-      <c r="Z36" s="26"/>
-      <c r="AA36" s="26"/>
-      <c r="AB36" s="26"/>
-      <c r="AC36" s="26"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="27"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
+      <c r="Z36" s="27"/>
+      <c r="AA36" s="27"/>
+      <c r="AB36" s="27"/>
+      <c r="AC36" s="27"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="22"/>
@@ -2794,27 +2794,27 @@
         <v>199</v>
       </c>
       <c r="J37" s="69"/>
-      <c r="K37" s="44"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="50">
+      <c r="K37" s="45"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="51">
         <v>15854.78</v>
       </c>
-      <c r="O37" s="24"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="51"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="26"/>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="26"/>
-      <c r="AA37" s="26"/>
-      <c r="AB37" s="26"/>
-      <c r="AC37" s="26"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="22"/>
@@ -2831,32 +2831,32 @@
         <v>199</v>
       </c>
       <c r="J38" s="69"/>
-      <c r="K38" s="44"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="37"/>
-      <c r="N38" s="50">
+      <c r="K38" s="45"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="51">
         <v>24962.38</v>
       </c>
-      <c r="O38" s="24"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="26"/>
-      <c r="Y38" s="26"/>
-      <c r="Z38" s="26"/>
-      <c r="AA38" s="26"/>
-      <c r="AB38" s="26"/>
-      <c r="AC38" s="26"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27"/>
+      <c r="Y38" s="27"/>
+      <c r="Z38" s="27"/>
+      <c r="AA38" s="27"/>
+      <c r="AB38" s="27"/>
+      <c r="AC38" s="27"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="22"/>
       <c r="B39" s="22"/>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>3.0</v>
       </c>
       <c r="D39" s="62" t="s">
@@ -2870,13 +2870,13 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
         <v>46106.0</v>
       </c>
-      <c r="K39" s="44">
+      <c r="K39" s="45">
         <v>27801.11</v>
       </c>
       <c r="L39" s="71" t="s">
@@ -2885,22 +2885,22 @@
       <c r="M39" s="72">
         <v>27801.11</v>
       </c>
-      <c r="N39" s="50"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="26"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
-      <c r="V39" s="51"/>
-      <c r="W39" s="26"/>
-      <c r="X39" s="26"/>
-      <c r="Y39" s="26"/>
-      <c r="Z39" s="26"/>
-      <c r="AA39" s="26"/>
-      <c r="AB39" s="26"/>
-      <c r="AC39" s="26"/>
+      <c r="N39" s="51"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="27"/>
+      <c r="X39" s="27"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="27"/>
+      <c r="AA39" s="27"/>
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="27"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="16"/>
@@ -2917,22 +2917,22 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
         <v>46233.0</v>
       </c>
-      <c r="K40" s="44">
+      <c r="K40" s="45">
         <v>58868.35</v>
       </c>
-      <c r="L40" s="33" t="s">
-        <v>65</v>
+      <c r="L40" s="34" t="s">
+        <v>73</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
       </c>
-      <c r="N40" s="50"/>
+      <c r="N40" s="51"/>
       <c r="V40" s="3"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
@@ -7886,11 +7886,11 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>1</v>
+      <c r="L2" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -7901,31 +7901,31 @@
       <c r="AH2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>2.5E32</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>45686.0</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <v>12.0</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="8">
         <v>2048.0</v>
       </c>
       <c r="J3" s="14">
@@ -7946,31 +7946,31 @@
       <c r="AH3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <v>12.0</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>2048.0</v>
       </c>
       <c r="J4" s="14">
@@ -7991,31 +7991,31 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="A5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>12.0</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="8">
         <v>2048.0</v>
       </c>
       <c r="J5" s="14">
@@ -8036,31 +8036,31 @@
       <c r="AH5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="A6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="8">
         <v>12.0</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="8">
         <v>2048.0</v>
       </c>
       <c r="J6" s="14">
@@ -8081,32 +8081,32 @@
       <c r="AH6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="A7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="12">
+        <v>45763.0</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="8">
+        <v>12.0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>339039.0</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="13">
-        <v>45763.0</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>12.0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>339039.0</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="J7" s="14">
         <v>949835.78</v>
@@ -8126,31 +8126,31 @@
       <c r="AH7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>45763.0</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="8">
         <v>12.0</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>48</v>
       </c>
       <c r="J8" s="14">
@@ -8162,7 +8162,7 @@
       <c r="L8" s="15">
         <v>0.0</v>
       </c>
-      <c r="O8" s="27"/>
+      <c r="O8" s="23"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8172,32 +8172,32 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>45792.0</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>12.0</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>58</v>
+      <c r="I9" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="J9" s="14">
         <v>211614.23</v>
@@ -8217,31 +8217,31 @@
       <c r="AH9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>45825.0</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="8">
         <v>12.0</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="8">
         <v>2048.0</v>
       </c>
       <c r="J10" s="14">
@@ -8262,31 +8262,31 @@
       <c r="AH10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="A11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>45825.0</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="8">
         <v>12.0</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="8">
         <v>2048.0</v>
       </c>
       <c r="J11" s="14">
@@ -8307,32 +8307,32 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="A12" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>45832.0</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="8">
         <v>12.0</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>75</v>
+      <c r="I12" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8352,31 +8352,31 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>45863.0</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>12.0</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <v>2048.0</v>
       </c>
       <c r="J13" s="14">
@@ -8388,7 +8388,7 @@
       <c r="L13" s="14">
         <v>497601.53</v>
       </c>
-      <c r="M13" s="39"/>
+      <c r="M13" s="31"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8398,32 +8398,32 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="A14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>45887.0</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="8">
         <v>12.0</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>58</v>
+      <c r="I14" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="J14" s="14">
         <v>968237.39</v>
@@ -8443,32 +8443,32 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="A15" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>45924.0</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="8">
         <v>12.0</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>44</v>
+      <c r="I15" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="J15" s="14">
         <v>1011677.95</v>
@@ -8488,31 +8488,31 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>45929.0</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="8">
         <v>12.0</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="8">
         <v>2048.0</v>
       </c>
       <c r="J16" s="14">
@@ -8533,31 +8533,31 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="A17" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <v>45930.0</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="8">
         <v>12.0</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="8">
         <v>2048.0</v>
       </c>
       <c r="J17" s="14">
@@ -8578,32 +8578,32 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="A18" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="8">
         <v>12.0</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I18" s="10" t="s">
-        <v>58</v>
+      <c r="I18" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="J18" s="14">
         <v>63746.85</v>
@@ -8623,32 +8623,32 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="A19" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="8">
         <v>12.0</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>75</v>
+      <c r="I19" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8668,31 +8668,31 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="10" t="s">
+      <c r="A20" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="8">
         <v>12.0</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="8">
         <v>2048.0</v>
       </c>
       <c r="J20" s="14">
@@ -8713,31 +8713,31 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="A21" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="8">
         <v>12.0</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="8">
         <v>2048.0</v>
       </c>
       <c r="J21" s="14">
@@ -8758,31 +8758,31 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="A22" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="41">
         <v>45953.0</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="8">
         <v>12.0</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="8">
         <v>2000.0</v>
       </c>
       <c r="J22" s="14">
@@ -8803,32 +8803,32 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="A23" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="41">
         <v>45953.0</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="8">
         <v>12.0</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>122</v>
+      <c r="I23" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -8848,31 +8848,31 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="A24" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="41">
         <v>45953.0</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="8">
         <v>12.0</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="8">
         <v>2048.0</v>
       </c>
       <c r="J24" s="14">
@@ -8893,32 +8893,32 @@
       <c r="AH24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="A25" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="41">
         <v>45975.0</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="8">
         <v>12.0</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>122</v>
+      <c r="I25" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -8938,31 +8938,31 @@
       <c r="AH25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B26" s="10" t="s">
+      <c r="A26" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="41">
         <v>45989.0</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="8">
         <v>12.0</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="8">
         <v>2048.0</v>
       </c>
       <c r="J26" s="14">
@@ -8983,31 +8983,31 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="A27" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <v>46104.0</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="8">
         <v>12.0</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="8">
         <v>2048.0</v>
       </c>
       <c r="J27" s="14">
@@ -9028,31 +9028,31 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="A28" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="12">
         <v>46120.0</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="8">
         <v>12.0</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="8" t="s">
         <v>48</v>
       </c>
       <c r="J28" s="14">
@@ -9073,40 +9073,40 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="7" t="s">
+      <c r="A29" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>46196.0</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="6">
         <v>12.0</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="6">
         <v>339039.0</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="6">
         <v>2048.0</v>
       </c>
-      <c r="J29" s="52">
+      <c r="J29" s="48">
         <v>1496713.48</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="6">
         <v>0.0</v>
       </c>
-      <c r="L29" s="52">
+      <c r="L29" s="48">
         <v>1496713.48</v>
       </c>
       <c r="AB29" s="2"/>
@@ -9118,40 +9118,40 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="A30" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>46205.0</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="6">
         <v>12.0</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="6">
         <v>339039.0</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="52">
+      <c r="I30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="48">
         <v>624166.14</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="6">
         <v>0.0</v>
       </c>
-      <c r="L30" s="52">
+      <c r="L30" s="48">
         <v>624166.14</v>
       </c>
       <c r="AB30" s="2"/>
@@ -9163,40 +9163,40 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="A31" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>46205.0</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="6">
         <v>12.0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="6">
         <v>339039.0</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="J31" s="52">
+      <c r="I31" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J31" s="48">
         <v>18462.36</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="6">
         <v>0.0</v>
       </c>
-      <c r="L31" s="52">
+      <c r="L31" s="48">
         <v>18462.36</v>
       </c>
       <c r="AB31" s="2"/>
@@ -9208,40 +9208,40 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="C32" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="A32" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>46213.0</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="6">
         <v>12.0</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="6">
         <v>339039.0</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="J32" s="52">
+      <c r="I32" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J32" s="48">
         <v>1530656.62</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="6">
         <v>0.0</v>
       </c>
-      <c r="L32" s="52">
+      <c r="L32" s="48">
         <v>1530656.62</v>
       </c>
       <c r="AB32" s="2"/>
@@ -9253,7 +9253,7 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="C33" s="52"/>
+      <c r="C33" s="48"/>
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -57,12 +57,48 @@
     <t>25E0385</t>
   </si>
   <si>
+    <t>2025NE000369</t>
+  </si>
+  <si>
+    <t>C25516</t>
+  </si>
+  <si>
+    <t>25E0387</t>
+  </si>
+  <si>
+    <t>2025NE000371</t>
+  </si>
+  <si>
+    <t>25E0389</t>
+  </si>
+  <si>
+    <t>2025NE000413</t>
+  </si>
+  <si>
+    <t>C25501</t>
+  </si>
+  <si>
+    <t>25E0403</t>
+  </si>
+  <si>
+    <t>20SP</t>
+  </si>
+  <si>
     <t>Número Contrato</t>
   </si>
   <si>
+    <t>2025NE000414</t>
+  </si>
+  <si>
+    <t>C25525</t>
+  </si>
+  <si>
     <t>UG Executora</t>
   </si>
   <si>
+    <t>25E0431</t>
+  </si>
+  <si>
     <t>UG Responsável</t>
   </si>
   <si>
@@ -72,18 +108,12 @@
     <t>Prazo Final de Execução</t>
   </si>
   <si>
-    <t>2025NE000369</t>
-  </si>
-  <si>
-    <t>C25516</t>
-  </si>
-  <si>
-    <t>25E0387</t>
-  </si>
-  <si>
     <t>Prazo Final de Vigência</t>
   </si>
   <si>
+    <t>21EM</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -120,13 +150,16 @@
     <t>Abrir</t>
   </si>
   <si>
-    <t>2025NE000371</t>
-  </si>
-  <si>
     <t>Editar</t>
   </si>
   <si>
-    <t>25E0389</t>
+    <t>2025NE000559</t>
+  </si>
+  <si>
+    <t>C25545</t>
+  </si>
+  <si>
+    <t>25E0524</t>
   </si>
   <si>
     <t>005/CELOG-PAMALS/2025</t>
@@ -138,13 +171,10 @@
     <t>PAMALS</t>
   </si>
   <si>
-    <t>2025NE000413</t>
-  </si>
-  <si>
-    <t>C25501</t>
-  </si>
-  <si>
-    <t>25E0403</t>
+    <t>20X7</t>
+  </si>
+  <si>
+    <t>2025NE000770</t>
   </si>
   <si>
     <t>Vigente</t>
@@ -153,81 +183,66 @@
     <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
   </si>
   <si>
+    <t>25E0731</t>
+  </si>
+  <si>
     <t>67101.001510/2024-12</t>
   </si>
   <si>
-    <t>20SP</t>
-  </si>
-  <si>
     <t>R$</t>
   </si>
   <si>
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
-    <t>2025NE000414</t>
-  </si>
-  <si>
-    <t>C25525</t>
-  </si>
-  <si>
-    <t>25E0431</t>
-  </si>
-  <si>
-    <t>21EM</t>
-  </si>
-  <si>
-    <t>2025NE000559</t>
-  </si>
-  <si>
-    <t>C25545</t>
-  </si>
-  <si>
-    <t>25E0524</t>
-  </si>
-  <si>
-    <t>20X7</t>
-  </si>
-  <si>
-    <t>2025NE000770</t>
-  </si>
-  <si>
-    <t>25E0731</t>
+    <t>2025NE000774</t>
+  </si>
+  <si>
+    <t>25E0737</t>
+  </si>
+  <si>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
+    <t>25E0787</t>
+  </si>
+  <si>
+    <t>219C</t>
+  </si>
+  <si>
+    <t>2025NE001065</t>
+  </si>
+  <si>
+    <t>25E0999</t>
   </si>
   <si>
     <t>Módulo</t>
   </si>
   <si>
-    <t>2025NE000774</t>
-  </si>
-  <si>
-    <t>25E0737</t>
+    <t>2025NE001200</t>
   </si>
   <si>
     <t>Referência</t>
   </si>
   <si>
+    <t>C25590</t>
+  </si>
+  <si>
+    <t>25E1128</t>
+  </si>
+  <si>
     <t>Nº recibo</t>
   </si>
   <si>
-    <t>2025NE000843</t>
-  </si>
-  <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
-  </si>
-  <si>
     <t>Nº</t>
   </si>
   <si>
     <t>Data</t>
   </si>
   <si>
-    <t>219C</t>
-  </si>
-  <si>
     <t>Empenho</t>
   </si>
   <si>
@@ -237,31 +252,40 @@
     <t>Vencimento</t>
   </si>
   <si>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
     <t>Valor das Nfs</t>
   </si>
   <si>
+    <t>25E1446</t>
+  </si>
+  <si>
     <t>Ordem de Pagamento</t>
   </si>
   <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
-  </si>
-  <si>
     <t>Faturado</t>
   </si>
   <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>2025NE001200</t>
-  </si>
-  <si>
-    <t>C25590</t>
-  </si>
-  <si>
-    <t>25E1128</t>
+    <t>2025NE001627</t>
+  </si>
+  <si>
+    <t>25E1475</t>
+  </si>
+  <si>
+    <t>2025NE001629</t>
+  </si>
+  <si>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
   </si>
   <si>
     <t>FEV/25</t>
@@ -270,61 +294,64 @@
     <t>-</t>
   </si>
   <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>25E1446</t>
-  </si>
-  <si>
-    <t>2025NE001627</t>
-  </si>
-  <si>
-    <t>25E1475</t>
+    <t>2025NE001687</t>
+  </si>
+  <si>
+    <t>25E1535</t>
+  </si>
+  <si>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
   </si>
   <si>
     <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
-    <t>2025NE001629</t>
-  </si>
-  <si>
-    <t>C25820</t>
-  </si>
-  <si>
-    <t>25E1477</t>
+    <t>2025NE001689</t>
+  </si>
+  <si>
+    <t>25E1537</t>
   </si>
   <si>
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>2025NE001687</t>
-  </si>
-  <si>
-    <t>25E1535</t>
-  </si>
-  <si>
-    <t>2025NE001688</t>
-  </si>
-  <si>
-    <t>25E1536</t>
-  </si>
-  <si>
-    <t>2025NE001689</t>
-  </si>
-  <si>
-    <t>25E1537</t>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
+  </si>
+  <si>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
+  </si>
+  <si>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
   </si>
   <si>
     <t>MAR/25</t>
   </si>
   <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
   </si>
   <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
@@ -333,100 +360,88 @@
     <t>2025NP001979</t>
   </si>
   <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
-  </si>
-  <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
-    <t>20YJ</t>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
+  </si>
+  <si>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
   </si>
   <si>
     <t>ABR/25</t>
   </si>
   <si>
-    <t>2025NE001830</t>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
   </si>
   <si>
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>25E1669</t>
-  </si>
-  <si>
     <t>2025NP002341</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
   </si>
   <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
-  </si>
-  <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
-  </si>
-  <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
+  </si>
+  <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
   </si>
   <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>26E0375</t>
-  </si>
-  <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
     <t>JUN/25</t>
-  </si>
-  <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -438,22 +453,7 @@
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
     <t>JUL/25</t>
-  </si>
-  <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
   </si>
   <si>
     <t>2025NE000843, 2025NE001200</t>
@@ -655,8 +655,8 @@
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
-    <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="168" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="169" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
     <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
     <numFmt numFmtId="171" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -692,15 +692,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -851,36 +851,24 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -888,12 +876,27 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
@@ -904,24 +907,22 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -931,7 +932,6 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -953,15 +953,18 @@
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf borderId="1" fillId="8" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -975,22 +978,19 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="9" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1048,7 +1048,7 @@
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="5" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -1397,172 +1397,172 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="3"/>
+      <c r="V1" s="4"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="9"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="3"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15"/>
+      <c r="R3" s="15"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="15"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="4"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="17" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="V4" s="4"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="20">
+      <c r="C5" s="20"/>
+      <c r="D5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="21">
         <v>1564.0</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="21">
         <v>1564.0</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="14">
+      <c r="J5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="10">
         <v>9.165159737E7</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="10">
         <v>7.254367932E7</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="10">
         <v>1.910791805E7</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="10">
         <v>8248487.61</v>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="10">
         <v>1.085943044E7</v>
       </c>
-      <c r="S5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="V5" s="3"/>
+      <c r="S5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="V5" s="4"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
-      <c r="L6" s="21"/>
-      <c r="V6" s="3"/>
+      <c r="L6" s="22"/>
+      <c r="V6" s="4"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
@@ -1577,62 +1577,62 @@
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
       <c r="P7" s="27"/>
-      <c r="V7" s="3"/>
+      <c r="V7" s="4"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="28" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" s="28" t="s">
+      <c r="D8" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="F8" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="30" t="s">
+      <c r="G8" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="M8" s="29" t="s">
+      <c r="H8" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="O8" s="28"/>
+      <c r="K8" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="O8" s="29"/>
       <c r="P8" s="27"/>
-      <c r="V8" s="3"/>
+      <c r="V8" s="4"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="32">
         <v>1.0</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F9" s="35">
         <v>594.0</v>
@@ -1641,7 +1641,7 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I9" s="36"/>
       <c r="J9" s="36">
@@ -1651,26 +1651,26 @@
         <v>748504.24</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="M9" s="38">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
-      <c r="N9" s="39"/>
+      <c r="N9" s="40"/>
       <c r="O9" s="25"/>
       <c r="P9" s="27"/>
-      <c r="V9" s="3"/>
+      <c r="V9" s="4"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="40"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="33" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F10" s="35">
         <v>620.0</v>
@@ -1679,7 +1679,7 @@
         <v>45775.0</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I10" s="36"/>
       <c r="J10" s="36">
@@ -1689,7 +1689,7 @@
         <v>1110378.24</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="M10" s="38">
         <f t="shared" si="1"/>
@@ -1698,17 +1698,17 @@
       <c r="N10" s="42"/>
       <c r="O10" s="25"/>
       <c r="P10" s="27"/>
-      <c r="V10" s="3"/>
+      <c r="V10" s="4"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="40"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="33" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F11" s="35">
         <v>634.0</v>
@@ -1717,7 +1717,7 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36">
@@ -1727,7 +1727,7 @@
         <v>974557.12</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M11" s="38">
         <v>974557.12</v>
@@ -1735,54 +1735,54 @@
       <c r="N11" s="42"/>
       <c r="O11" s="25"/>
       <c r="P11" s="27"/>
-      <c r="V11" s="3"/>
+      <c r="V11" s="4"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="40"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="33" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F12" s="34">
         <v>660.0</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <v>45856.0</v>
       </c>
-      <c r="H12" s="44" t="s">
-        <v>60</v>
+      <c r="H12" s="45" t="s">
+        <v>57</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36">
         <v>45891.0</v>
       </c>
-      <c r="K12" s="45">
+      <c r="K12" s="46">
         <v>1402001.34</v>
       </c>
-      <c r="L12" s="46" t="s">
-        <v>124</v>
+      <c r="L12" s="47" t="s">
+        <v>136</v>
       </c>
       <c r="M12" s="38">
         <v>1402001.34</v>
       </c>
-      <c r="N12" s="47"/>
+      <c r="N12" s="48"/>
       <c r="O12" s="25"/>
       <c r="P12" s="27"/>
-      <c r="V12" s="3"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="40"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="49" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F13" s="35">
         <v>661.0</v>
@@ -1791,35 +1791,35 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43">
+        <v>138</v>
+      </c>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44">
         <v>45891.0</v>
       </c>
-      <c r="K13" s="45">
+      <c r="K13" s="46">
         <v>1223702.3</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="M13" s="38">
         <v>1223702.3</v>
       </c>
-      <c r="N13" s="47"/>
+      <c r="N13" s="48"/>
       <c r="O13" s="25"/>
       <c r="P13" s="50"/>
-      <c r="V13" s="3"/>
+      <c r="V13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="40"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="49" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F14" s="34">
         <v>688.0</v>
@@ -1830,11 +1830,11 @@
       <c r="H14" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43">
+      <c r="I14" s="44"/>
+      <c r="J14" s="44">
         <v>45938.0</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="46">
         <v>1011677.95</v>
       </c>
       <c r="L14" s="34" t="s">
@@ -1846,17 +1846,17 @@
       <c r="N14" s="42"/>
       <c r="O14" s="25"/>
       <c r="P14" s="27"/>
-      <c r="V14" s="3"/>
+      <c r="V14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="40"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="49" t="s">
         <v>143</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F15" s="34">
         <v>696.0</v>
@@ -1865,13 +1865,13 @@
         <v>45923.0</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43">
+        <v>64</v>
+      </c>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44">
         <v>45938.0</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="46">
         <v>896744.06</v>
       </c>
       <c r="L15" s="34" t="s">
@@ -1880,19 +1880,19 @@
       <c r="M15" s="38">
         <v>896744.06</v>
       </c>
-      <c r="N15" s="47"/>
+      <c r="N15" s="48"/>
       <c r="O15" s="25"/>
-      <c r="V15" s="3"/>
+      <c r="V15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="40"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="49" t="s">
         <v>145</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F16" s="34">
         <v>704.0</v>
@@ -1903,11 +1903,11 @@
       <c r="H16" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43">
+      <c r="I16" s="44"/>
+      <c r="J16" s="44">
         <v>46003.0</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="46">
         <v>919329.06</v>
       </c>
       <c r="L16" s="34" t="s">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="N16" s="42"/>
       <c r="O16" s="25"/>
-      <c r="V16" s="3"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="40"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
         <v>148</v>
       </c>
@@ -1931,17 +1931,17 @@
       <c r="F17" s="34">
         <v>705.0</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="44">
         <v>45972.0</v>
       </c>
       <c r="H17" s="34" t="s">
         <v>149</v>
       </c>
       <c r="I17" s="34"/>
-      <c r="J17" s="43">
+      <c r="J17" s="44">
         <v>46016.0</v>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="46">
         <v>1157009.26</v>
       </c>
       <c r="L17" s="34" t="s">
@@ -1952,32 +1952,32 @@
       </c>
       <c r="N17" s="51"/>
       <c r="O17" s="25"/>
-      <c r="V17" s="3"/>
+      <c r="V17" s="4"/>
     </row>
     <row r="18">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="40"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="49" t="s">
         <v>151</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F18" s="34">
         <v>728.0</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <v>46008.0</v>
       </c>
       <c r="H18" s="34" t="s">
         <v>152</v>
       </c>
       <c r="I18" s="34"/>
-      <c r="J18" s="43">
+      <c r="J18" s="44">
         <v>46040.0</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="46">
         <v>1214597.952</v>
       </c>
       <c r="L18" s="34" t="s">
@@ -1995,29 +1995,29 @@
       <c r="V18" s="52"/>
     </row>
     <row r="19">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="40"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="49" t="s">
         <v>154</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="F19" s="34">
         <v>278.0</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="44">
         <v>46042.0</v>
       </c>
       <c r="H19" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43">
+      <c r="I19" s="44"/>
+      <c r="J19" s="44">
         <v>46074.0</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="46">
         <v>967082.09</v>
       </c>
       <c r="L19" s="34" t="s">
@@ -2035,9 +2035,9 @@
       <c r="V19" s="52"/>
     </row>
     <row r="20">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="40"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="49" t="s">
         <v>157</v>
       </c>
@@ -2045,17 +2045,17 @@
       <c r="F20" s="34">
         <v>10.0</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="44">
         <v>46078.0</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43">
+        <v>98</v>
+      </c>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44">
         <v>46106.0</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="46">
         <v>719561.08</v>
       </c>
       <c r="L20" s="34" t="s">
@@ -2073,9 +2073,9 @@
       <c r="V20" s="52"/>
     </row>
     <row r="21">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="40"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="49" t="s">
         <v>159</v>
       </c>
@@ -2083,17 +2083,17 @@
       <c r="F21" s="34">
         <v>15.0</v>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="44">
         <v>46094.0</v>
       </c>
       <c r="H21" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43">
+      <c r="I21" s="44"/>
+      <c r="J21" s="44">
         <v>46128.0</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="46">
         <v>885881.08</v>
       </c>
       <c r="L21" s="34" t="s">
@@ -2111,9 +2111,9 @@
       <c r="V21" s="52"/>
     </row>
     <row r="22">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="40"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="49" t="s">
         <v>162</v>
       </c>
@@ -2121,17 +2121,17 @@
       <c r="F22" s="34">
         <v>28.0</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <v>46128.0</v>
       </c>
       <c r="H22" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43">
+      <c r="I22" s="44"/>
+      <c r="J22" s="44">
         <v>46164.0</v>
       </c>
-      <c r="K22" s="45" t="s">
+      <c r="K22" s="46" t="s">
         <v>164</v>
       </c>
       <c r="L22" s="34" t="s">
@@ -2149,9 +2149,9 @@
       <c r="V22" s="52"/>
     </row>
     <row r="23">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="40"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="41"/>
       <c r="D23" s="49" t="s">
         <v>166</v>
       </c>
@@ -2159,17 +2159,17 @@
       <c r="F23" s="34">
         <v>33.0</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="44">
         <v>46156.0</v>
       </c>
       <c r="H23" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43">
+      <c r="I23" s="44"/>
+      <c r="J23" s="44">
         <v>46191.0</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="46">
         <v>1108954.4358333333</v>
       </c>
       <c r="L23" s="34" t="s">
@@ -2187,9 +2187,9 @@
       <c r="V23" s="52"/>
     </row>
     <row r="24">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="40"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="41"/>
       <c r="D24" s="49" t="s">
         <v>168</v>
       </c>
@@ -2197,17 +2197,17 @@
       <c r="F24" s="34">
         <v>29.0</v>
       </c>
-      <c r="G24" s="43">
+      <c r="G24" s="44">
         <v>46149.0</v>
       </c>
       <c r="H24" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43">
+      <c r="I24" s="44"/>
+      <c r="J24" s="44">
         <v>46185.0</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="46">
         <v>218206.1</v>
       </c>
       <c r="L24" s="34" t="s">
@@ -2225,9 +2225,9 @@
       <c r="V24" s="52"/>
     </row>
     <row r="25">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="40"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="49" t="s">
         <v>170</v>
       </c>
@@ -2235,17 +2235,17 @@
       <c r="F25" s="55">
         <v>40.0</v>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="44">
         <v>46156.0</v>
       </c>
       <c r="H25" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="43"/>
+      <c r="I25" s="44"/>
       <c r="J25" s="56">
         <v>46191.0</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="46">
         <v>1549250.84</v>
       </c>
       <c r="L25" s="34" t="s">
@@ -2263,21 +2263,21 @@
       <c r="V25" s="52"/>
     </row>
     <row r="26">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="57"/>
       <c r="D26" s="49" t="s">
         <v>172</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="55"/>
-      <c r="G26" s="43"/>
+      <c r="G26" s="44"/>
       <c r="H26" s="55"/>
-      <c r="I26" s="43"/>
+      <c r="I26" s="44"/>
       <c r="J26" s="56"/>
-      <c r="K26" s="45"/>
+      <c r="K26" s="46"/>
       <c r="L26" s="34" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M26" s="38" t="s">
         <v>173</v>
@@ -2291,37 +2291,37 @@
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="28" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+      <c r="D27" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
       <c r="K27" s="58" t="s">
-        <v>69</v>
-      </c>
-      <c r="L27" s="30" t="s">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>78</v>
       </c>
       <c r="M27" s="59" t="s">
-        <v>73</v>
-      </c>
-      <c r="N27" s="28" t="s">
-        <v>74</v>
+        <v>79</v>
+      </c>
+      <c r="N27" s="29" t="s">
+        <v>80</v>
       </c>
       <c r="O27" s="25"/>
       <c r="P27" s="27"/>
@@ -2339,8 +2339,8 @@
       <c r="AC27" s="27"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
       <c r="C28" s="32">
         <v>2.0</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>45791.0</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I28" s="36"/>
       <c r="J28" s="36">
@@ -2388,9 +2388,9 @@
       <c r="AC28" s="27"/>
     </row>
     <row r="29">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="40"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="41"/>
       <c r="D29" s="60" t="s">
         <v>176</v>
       </c>
@@ -2406,8 +2406,8 @@
       <c r="H29" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43">
+      <c r="I29" s="44"/>
+      <c r="J29" s="44">
         <v>45955.0</v>
       </c>
       <c r="K29" s="37">
@@ -2437,9 +2437,9 @@
       <c r="AC29" s="27"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="40"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="62" t="s">
         <v>179</v>
       </c>
@@ -2453,13 +2453,13 @@
         <v>45853.0</v>
       </c>
       <c r="H30" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43">
+        <v>48</v>
+      </c>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44">
         <v>45939.0</v>
       </c>
-      <c r="K30" s="45">
+      <c r="K30" s="46">
         <v>378307.61</v>
       </c>
       <c r="L30" s="34" t="s">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="N30" s="51"/>
       <c r="O30" s="25"/>
-      <c r="P30" s="48"/>
+      <c r="P30" s="43"/>
       <c r="Q30" s="27"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
@@ -2486,9 +2486,9 @@
       <c r="AC30" s="27"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="40"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="62" t="s">
         <v>182</v>
       </c>
@@ -2502,10 +2502,10 @@
         <v>45910.0</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>53</v>
-      </c>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43">
+        <v>48</v>
+      </c>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44">
         <v>45941.0</v>
       </c>
       <c r="K31" s="37">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="N31" s="51"/>
       <c r="O31" s="25"/>
-      <c r="P31" s="48"/>
+      <c r="P31" s="43"/>
       <c r="Q31" s="27"/>
       <c r="R31" s="27"/>
       <c r="S31" s="27"/>
@@ -2535,9 +2535,9 @@
       <c r="AC31" s="27"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="40"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="41"/>
       <c r="D32" s="62" t="s">
         <v>184</v>
       </c>
@@ -2551,13 +2551,13 @@
         <v>45904.0</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K32" s="45">
+      <c r="K32" s="46">
         <v>198332.75</v>
       </c>
       <c r="L32" s="34" t="s">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="N32" s="51"/>
       <c r="O32" s="25"/>
-      <c r="P32" s="48"/>
+      <c r="P32" s="43"/>
       <c r="Q32" s="27"/>
       <c r="R32" s="27"/>
       <c r="S32" s="27"/>
@@ -2584,9 +2584,9 @@
       <c r="AC32" s="27"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="40"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="41"/>
       <c r="D33" s="62" t="s">
         <v>186</v>
       </c>
@@ -2600,13 +2600,13 @@
         <v>46008.0</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
         <v>46066.0</v>
       </c>
-      <c r="K33" s="45">
+      <c r="K33" s="46">
         <v>1528.62</v>
       </c>
       <c r="L33" s="67" t="s">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="N33" s="51"/>
       <c r="O33" s="25"/>
-      <c r="P33" s="48"/>
+      <c r="P33" s="43"/>
       <c r="Q33" s="27"/>
       <c r="R33" s="27"/>
       <c r="S33" s="27"/>
@@ -2633,9 +2633,9 @@
       <c r="AC33" s="27"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="40"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="41"/>
       <c r="D34" s="62" t="s">
         <v>189</v>
       </c>
@@ -2649,13 +2649,13 @@
         <v>45930.0</v>
       </c>
       <c r="H34" s="34" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="46">
         <v>38718.58</v>
       </c>
       <c r="L34" s="34" t="s">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="N34" s="51"/>
       <c r="O34" s="25"/>
-      <c r="P34" s="48"/>
+      <c r="P34" s="43"/>
       <c r="Q34" s="27"/>
       <c r="R34" s="27"/>
       <c r="S34" s="27"/>
@@ -2682,9 +2682,9 @@
       <c r="AC34" s="27"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="40"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="41"/>
       <c r="D35" s="62" t="s">
         <v>193</v>
       </c>
@@ -2698,13 +2698,13 @@
         <v>45968.0</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K35" s="45">
+      <c r="K35" s="46">
         <v>133124.11</v>
       </c>
       <c r="L35" s="34" t="s">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="N35" s="51"/>
       <c r="O35" s="25"/>
-      <c r="P35" s="48"/>
+      <c r="P35" s="43"/>
       <c r="Q35" s="27"/>
       <c r="R35" s="27"/>
       <c r="S35" s="27"/>
@@ -2731,9 +2731,9 @@
       <c r="AC35" s="27"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="40"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="62" t="s">
         <v>196</v>
       </c>
@@ -2747,13 +2747,13 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
         <v>46075.0</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="46">
         <v>11372.9</v>
       </c>
       <c r="L36" s="34" t="s">
@@ -2780,9 +2780,9 @@
       <c r="AC36" s="27"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="40"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="41"/>
       <c r="D37" s="62" t="s">
         <v>198</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>199</v>
       </c>
       <c r="J37" s="69"/>
-      <c r="K37" s="45"/>
+      <c r="K37" s="46"/>
       <c r="L37" s="34"/>
       <c r="M37" s="38"/>
       <c r="N37" s="51">
@@ -2817,8 +2817,8 @@
       <c r="AC37" s="27"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
       <c r="C38" s="57"/>
       <c r="D38" s="62" t="s">
         <v>200</v>
@@ -2831,7 +2831,7 @@
         <v>199</v>
       </c>
       <c r="J38" s="69"/>
-      <c r="K38" s="45"/>
+      <c r="K38" s="46"/>
       <c r="L38" s="34"/>
       <c r="M38" s="38"/>
       <c r="N38" s="51">
@@ -2854,8 +2854,8 @@
       <c r="AC38" s="27"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
       <c r="C39" s="32">
         <v>3.0</v>
       </c>
@@ -2870,13 +2870,13 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
         <v>46106.0</v>
       </c>
-      <c r="K39" s="45">
+      <c r="K39" s="46">
         <v>27801.11</v>
       </c>
       <c r="L39" s="71" t="s">
@@ -2905,7 +2905,7 @@
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="16"/>
       <c r="B40" s="16"/>
-      <c r="C40" s="40"/>
+      <c r="C40" s="41"/>
       <c r="D40" s="62" t="s">
         <v>203</v>
       </c>
@@ -2917,63 +2917,63 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
         <v>46233.0</v>
       </c>
-      <c r="K40" s="45">
+      <c r="K40" s="46">
         <v>58868.35</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
       </c>
       <c r="N40" s="51"/>
-      <c r="V40" s="3"/>
+      <c r="V40" s="4"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="16"/>
       <c r="B41" s="16"/>
-      <c r="C41" s="40"/>
+      <c r="C41" s="41"/>
       <c r="K41" s="73"/>
       <c r="M41" s="73"/>
-      <c r="V41" s="3"/>
+      <c r="V41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
-      <c r="C42" s="40"/>
+      <c r="C42" s="41"/>
       <c r="K42" s="73"/>
       <c r="M42" s="73"/>
-      <c r="V42" s="3"/>
+      <c r="V42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="16"/>
       <c r="B43" s="16"/>
-      <c r="C43" s="40"/>
-      <c r="V43" s="3"/>
+      <c r="C43" s="41"/>
+      <c r="V43" s="4"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="16"/>
       <c r="B44" s="16"/>
-      <c r="C44" s="40"/>
-      <c r="V44" s="3"/>
+      <c r="C44" s="41"/>
+      <c r="V44" s="4"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="16"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="40"/>
-      <c r="V45" s="3"/>
+      <c r="C45" s="41"/>
+      <c r="V45" s="4"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
-      <c r="C46" s="40"/>
-      <c r="V46" s="3"/>
+      <c r="C46" s="41"/>
+      <c r="V46" s="4"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="16"/>
@@ -2981,7 +2981,7 @@
       <c r="C47" s="57"/>
       <c r="K47" s="73"/>
       <c r="M47" s="73"/>
-      <c r="V47" s="3"/>
+      <c r="V47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="16"/>
@@ -3005,7 +3005,7 @@
       <c r="S48" s="74"/>
       <c r="T48" s="74"/>
       <c r="U48" s="74"/>
-      <c r="V48" s="3"/>
+      <c r="V48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="16"/>
@@ -3222,4622 +3222,4622 @@
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="16"/>
       <c r="B102" s="16"/>
-      <c r="L102" s="21"/>
+      <c r="L102" s="22"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="16"/>
       <c r="B103" s="16"/>
-      <c r="L103" s="21"/>
+      <c r="L103" s="22"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="16"/>
       <c r="B104" s="16"/>
-      <c r="L104" s="21"/>
+      <c r="L104" s="22"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="16"/>
-      <c r="L105" s="21"/>
+      <c r="L105" s="22"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
-      <c r="L106" s="21"/>
+      <c r="L106" s="22"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
-      <c r="L107" s="21"/>
+      <c r="L107" s="22"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
-      <c r="L108" s="21"/>
+      <c r="L108" s="22"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
-      <c r="L109" s="21"/>
+      <c r="L109" s="22"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
-      <c r="L110" s="21"/>
+      <c r="L110" s="22"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
-      <c r="L111" s="21"/>
+      <c r="L111" s="22"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
-      <c r="L112" s="21"/>
+      <c r="L112" s="22"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="16"/>
       <c r="B113" s="16"/>
-      <c r="L113" s="21"/>
+      <c r="L113" s="22"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="16"/>
       <c r="B114" s="16"/>
-      <c r="L114" s="21"/>
+      <c r="L114" s="22"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="16"/>
       <c r="B115" s="16"/>
-      <c r="L115" s="21"/>
+      <c r="L115" s="22"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="16"/>
       <c r="B116" s="16"/>
-      <c r="L116" s="21"/>
+      <c r="L116" s="22"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="16"/>
       <c r="B117" s="16"/>
-      <c r="L117" s="21"/>
+      <c r="L117" s="22"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="16"/>
       <c r="B118" s="16"/>
-      <c r="L118" s="21"/>
+      <c r="L118" s="22"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="16"/>
       <c r="B119" s="16"/>
-      <c r="L119" s="21"/>
+      <c r="L119" s="22"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="16"/>
       <c r="B120" s="16"/>
-      <c r="L120" s="21"/>
+      <c r="L120" s="22"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="16"/>
       <c r="B121" s="16"/>
-      <c r="L121" s="21"/>
+      <c r="L121" s="22"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="16"/>
       <c r="B122" s="16"/>
-      <c r="L122" s="21"/>
+      <c r="L122" s="22"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="16"/>
       <c r="B123" s="16"/>
-      <c r="L123" s="21"/>
+      <c r="L123" s="22"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="16"/>
       <c r="B124" s="16"/>
-      <c r="L124" s="21"/>
+      <c r="L124" s="22"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="16"/>
       <c r="B125" s="16"/>
-      <c r="L125" s="21"/>
+      <c r="L125" s="22"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="16"/>
       <c r="B126" s="16"/>
-      <c r="L126" s="21"/>
+      <c r="L126" s="22"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="16"/>
       <c r="B127" s="16"/>
-      <c r="L127" s="21"/>
+      <c r="L127" s="22"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="16"/>
       <c r="B128" s="16"/>
-      <c r="L128" s="21"/>
+      <c r="L128" s="22"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="16"/>
       <c r="B129" s="16"/>
-      <c r="L129" s="21"/>
+      <c r="L129" s="22"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="16"/>
       <c r="B130" s="16"/>
-      <c r="L130" s="21"/>
+      <c r="L130" s="22"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="16"/>
       <c r="B131" s="16"/>
-      <c r="L131" s="21"/>
+      <c r="L131" s="22"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="16"/>
       <c r="B132" s="16"/>
-      <c r="L132" s="21"/>
+      <c r="L132" s="22"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="16"/>
-      <c r="L133" s="21"/>
+      <c r="L133" s="22"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="16"/>
-      <c r="L134" s="21"/>
+      <c r="L134" s="22"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="16"/>
       <c r="B135" s="16"/>
-      <c r="L135" s="21"/>
+      <c r="L135" s="22"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="16"/>
       <c r="B136" s="16"/>
-      <c r="L136" s="21"/>
+      <c r="L136" s="22"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="16"/>
       <c r="B137" s="16"/>
-      <c r="L137" s="21"/>
+      <c r="L137" s="22"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="16"/>
       <c r="B138" s="16"/>
-      <c r="L138" s="21"/>
+      <c r="L138" s="22"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="16"/>
       <c r="B139" s="16"/>
-      <c r="L139" s="21"/>
+      <c r="L139" s="22"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="16"/>
       <c r="B140" s="16"/>
-      <c r="L140" s="21"/>
+      <c r="L140" s="22"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="16"/>
       <c r="B141" s="16"/>
-      <c r="L141" s="21"/>
+      <c r="L141" s="22"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="16"/>
       <c r="B142" s="16"/>
-      <c r="L142" s="21"/>
+      <c r="L142" s="22"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="16"/>
       <c r="B143" s="16"/>
-      <c r="L143" s="21"/>
+      <c r="L143" s="22"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="16"/>
       <c r="B144" s="16"/>
-      <c r="L144" s="21"/>
+      <c r="L144" s="22"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="16"/>
       <c r="B145" s="16"/>
-      <c r="L145" s="21"/>
+      <c r="L145" s="22"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="16"/>
       <c r="B146" s="16"/>
-      <c r="L146" s="21"/>
+      <c r="L146" s="22"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="16"/>
       <c r="B147" s="16"/>
-      <c r="L147" s="21"/>
+      <c r="L147" s="22"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="16"/>
       <c r="B148" s="16"/>
-      <c r="L148" s="21"/>
+      <c r="L148" s="22"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="16"/>
       <c r="B149" s="16"/>
-      <c r="L149" s="21"/>
+      <c r="L149" s="22"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="16"/>
       <c r="B150" s="16"/>
-      <c r="L150" s="21"/>
+      <c r="L150" s="22"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="16"/>
       <c r="B151" s="16"/>
-      <c r="L151" s="21"/>
+      <c r="L151" s="22"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="16"/>
       <c r="B152" s="16"/>
-      <c r="L152" s="21"/>
+      <c r="L152" s="22"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="16"/>
       <c r="B153" s="16"/>
-      <c r="L153" s="21"/>
+      <c r="L153" s="22"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="16"/>
       <c r="B154" s="16"/>
-      <c r="L154" s="21"/>
+      <c r="L154" s="22"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="16"/>
       <c r="B155" s="16"/>
-      <c r="L155" s="21"/>
+      <c r="L155" s="22"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="16"/>
       <c r="B156" s="16"/>
-      <c r="L156" s="21"/>
+      <c r="L156" s="22"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="16"/>
       <c r="B157" s="16"/>
-      <c r="L157" s="21"/>
+      <c r="L157" s="22"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="16"/>
       <c r="B158" s="16"/>
-      <c r="L158" s="21"/>
+      <c r="L158" s="22"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="16"/>
       <c r="B159" s="16"/>
-      <c r="L159" s="21"/>
+      <c r="L159" s="22"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="16"/>
       <c r="B160" s="16"/>
-      <c r="L160" s="21"/>
+      <c r="L160" s="22"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="16"/>
       <c r="B161" s="16"/>
-      <c r="L161" s="21"/>
+      <c r="L161" s="22"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="16"/>
       <c r="B162" s="16"/>
-      <c r="L162" s="21"/>
+      <c r="L162" s="22"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="16"/>
       <c r="B163" s="16"/>
-      <c r="L163" s="21"/>
+      <c r="L163" s="22"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="16"/>
       <c r="B164" s="16"/>
-      <c r="L164" s="21"/>
+      <c r="L164" s="22"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="16"/>
       <c r="B165" s="16"/>
-      <c r="L165" s="21"/>
+      <c r="L165" s="22"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="16"/>
       <c r="B166" s="16"/>
-      <c r="L166" s="21"/>
+      <c r="L166" s="22"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="16"/>
       <c r="B167" s="16"/>
-      <c r="L167" s="21"/>
+      <c r="L167" s="22"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="16"/>
       <c r="B168" s="16"/>
-      <c r="L168" s="21"/>
+      <c r="L168" s="22"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="16"/>
       <c r="B169" s="16"/>
-      <c r="L169" s="21"/>
+      <c r="L169" s="22"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="16"/>
       <c r="B170" s="16"/>
-      <c r="L170" s="21"/>
+      <c r="L170" s="22"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="16"/>
       <c r="B171" s="16"/>
-      <c r="L171" s="21"/>
+      <c r="L171" s="22"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="16"/>
       <c r="B172" s="16"/>
-      <c r="L172" s="21"/>
+      <c r="L172" s="22"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="16"/>
       <c r="B173" s="16"/>
-      <c r="L173" s="21"/>
+      <c r="L173" s="22"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="16"/>
       <c r="B174" s="16"/>
-      <c r="L174" s="21"/>
+      <c r="L174" s="22"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="16"/>
       <c r="B175" s="16"/>
-      <c r="L175" s="21"/>
+      <c r="L175" s="22"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="16"/>
       <c r="B176" s="16"/>
-      <c r="L176" s="21"/>
+      <c r="L176" s="22"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="16"/>
       <c r="B177" s="16"/>
-      <c r="L177" s="21"/>
+      <c r="L177" s="22"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="16"/>
       <c r="B178" s="16"/>
-      <c r="L178" s="21"/>
+      <c r="L178" s="22"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="16"/>
       <c r="B179" s="16"/>
-      <c r="L179" s="21"/>
+      <c r="L179" s="22"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="16"/>
       <c r="B180" s="16"/>
-      <c r="L180" s="21"/>
+      <c r="L180" s="22"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="16"/>
       <c r="B181" s="16"/>
-      <c r="L181" s="21"/>
+      <c r="L181" s="22"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="16"/>
       <c r="B182" s="16"/>
-      <c r="L182" s="21"/>
+      <c r="L182" s="22"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="16"/>
       <c r="B183" s="16"/>
-      <c r="L183" s="21"/>
+      <c r="L183" s="22"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="16"/>
       <c r="B184" s="16"/>
-      <c r="L184" s="21"/>
+      <c r="L184" s="22"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="16"/>
       <c r="B185" s="16"/>
-      <c r="L185" s="21"/>
+      <c r="L185" s="22"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="16"/>
       <c r="B186" s="16"/>
-      <c r="L186" s="21"/>
+      <c r="L186" s="22"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="16"/>
       <c r="B187" s="16"/>
-      <c r="L187" s="21"/>
+      <c r="L187" s="22"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="16"/>
       <c r="B188" s="16"/>
-      <c r="L188" s="21"/>
+      <c r="L188" s="22"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="16"/>
       <c r="B189" s="16"/>
-      <c r="L189" s="21"/>
+      <c r="L189" s="22"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="16"/>
       <c r="B190" s="16"/>
-      <c r="L190" s="21"/>
+      <c r="L190" s="22"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="16"/>
       <c r="B191" s="16"/>
-      <c r="L191" s="21"/>
+      <c r="L191" s="22"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="16"/>
       <c r="B192" s="16"/>
-      <c r="L192" s="21"/>
+      <c r="L192" s="22"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="16"/>
       <c r="B193" s="16"/>
-      <c r="L193" s="21"/>
+      <c r="L193" s="22"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="16"/>
       <c r="B194" s="16"/>
-      <c r="L194" s="21"/>
+      <c r="L194" s="22"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="16"/>
       <c r="B195" s="16"/>
-      <c r="L195" s="21"/>
+      <c r="L195" s="22"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="16"/>
       <c r="B196" s="16"/>
-      <c r="L196" s="21"/>
+      <c r="L196" s="22"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="16"/>
       <c r="B197" s="16"/>
-      <c r="L197" s="21"/>
+      <c r="L197" s="22"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="16"/>
       <c r="B198" s="16"/>
-      <c r="L198" s="21"/>
+      <c r="L198" s="22"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="16"/>
       <c r="B199" s="16"/>
-      <c r="L199" s="21"/>
+      <c r="L199" s="22"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="16"/>
       <c r="B200" s="16"/>
-      <c r="L200" s="21"/>
+      <c r="L200" s="22"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="16"/>
       <c r="B201" s="16"/>
-      <c r="L201" s="21"/>
+      <c r="L201" s="22"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="16"/>
       <c r="B202" s="16"/>
-      <c r="L202" s="21"/>
+      <c r="L202" s="22"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="16"/>
       <c r="B203" s="16"/>
-      <c r="L203" s="21"/>
+      <c r="L203" s="22"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="16"/>
       <c r="B204" s="16"/>
-      <c r="L204" s="21"/>
+      <c r="L204" s="22"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="16"/>
       <c r="B205" s="16"/>
-      <c r="L205" s="21"/>
+      <c r="L205" s="22"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="16"/>
       <c r="B206" s="16"/>
-      <c r="L206" s="21"/>
+      <c r="L206" s="22"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="16"/>
       <c r="B207" s="16"/>
-      <c r="L207" s="21"/>
+      <c r="L207" s="22"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="16"/>
       <c r="B208" s="16"/>
-      <c r="L208" s="21"/>
+      <c r="L208" s="22"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="16"/>
       <c r="B209" s="16"/>
-      <c r="L209" s="21"/>
+      <c r="L209" s="22"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="16"/>
       <c r="B210" s="16"/>
-      <c r="L210" s="21"/>
+      <c r="L210" s="22"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="16"/>
       <c r="B211" s="16"/>
-      <c r="L211" s="21"/>
+      <c r="L211" s="22"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="16"/>
       <c r="B212" s="16"/>
-      <c r="L212" s="21"/>
+      <c r="L212" s="22"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="16"/>
       <c r="B213" s="16"/>
-      <c r="L213" s="21"/>
+      <c r="L213" s="22"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="16"/>
       <c r="B214" s="16"/>
-      <c r="L214" s="21"/>
+      <c r="L214" s="22"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="16"/>
       <c r="B215" s="16"/>
-      <c r="L215" s="21"/>
+      <c r="L215" s="22"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="16"/>
       <c r="B216" s="16"/>
-      <c r="L216" s="21"/>
+      <c r="L216" s="22"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="16"/>
       <c r="B217" s="16"/>
-      <c r="L217" s="21"/>
+      <c r="L217" s="22"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="16"/>
       <c r="B218" s="16"/>
-      <c r="L218" s="21"/>
+      <c r="L218" s="22"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="16"/>
       <c r="B219" s="16"/>
-      <c r="L219" s="21"/>
+      <c r="L219" s="22"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="16"/>
       <c r="B220" s="16"/>
-      <c r="L220" s="21"/>
+      <c r="L220" s="22"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="16"/>
       <c r="B221" s="16"/>
-      <c r="L221" s="21"/>
+      <c r="L221" s="22"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="16"/>
       <c r="B222" s="16"/>
-      <c r="L222" s="21"/>
+      <c r="L222" s="22"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="16"/>
       <c r="B223" s="16"/>
-      <c r="L223" s="21"/>
+      <c r="L223" s="22"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="16"/>
       <c r="B224" s="16"/>
-      <c r="L224" s="21"/>
+      <c r="L224" s="22"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="16"/>
       <c r="B225" s="16"/>
-      <c r="L225" s="21"/>
+      <c r="L225" s="22"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="16"/>
       <c r="B226" s="16"/>
-      <c r="L226" s="21"/>
+      <c r="L226" s="22"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
       <c r="A227" s="16"/>
       <c r="B227" s="16"/>
-      <c r="L227" s="21"/>
+      <c r="L227" s="22"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="16"/>
       <c r="B228" s="16"/>
-      <c r="L228" s="21"/>
+      <c r="L228" s="22"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="A229" s="16"/>
       <c r="B229" s="16"/>
-      <c r="L229" s="21"/>
+      <c r="L229" s="22"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="16"/>
       <c r="B230" s="16"/>
-      <c r="L230" s="21"/>
+      <c r="L230" s="22"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="16"/>
       <c r="B231" s="16"/>
-      <c r="L231" s="21"/>
+      <c r="L231" s="22"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="16"/>
       <c r="B232" s="16"/>
-      <c r="L232" s="21"/>
+      <c r="L232" s="22"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="16"/>
       <c r="B233" s="16"/>
-      <c r="L233" s="21"/>
+      <c r="L233" s="22"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="16"/>
       <c r="B234" s="16"/>
-      <c r="L234" s="21"/>
+      <c r="L234" s="22"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
       <c r="A235" s="16"/>
       <c r="B235" s="16"/>
-      <c r="L235" s="21"/>
+      <c r="L235" s="22"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
       <c r="A236" s="16"/>
       <c r="B236" s="16"/>
-      <c r="L236" s="21"/>
+      <c r="L236" s="22"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
       <c r="A237" s="16"/>
       <c r="B237" s="16"/>
-      <c r="L237" s="21"/>
+      <c r="L237" s="22"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="A238" s="16"/>
       <c r="B238" s="16"/>
-      <c r="L238" s="21"/>
+      <c r="L238" s="22"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
       <c r="A239" s="16"/>
       <c r="B239" s="16"/>
-      <c r="L239" s="21"/>
+      <c r="L239" s="22"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
       <c r="A240" s="16"/>
       <c r="B240" s="16"/>
-      <c r="L240" s="21"/>
+      <c r="L240" s="22"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
       <c r="A241" s="16"/>
       <c r="B241" s="16"/>
-      <c r="L241" s="21"/>
+      <c r="L241" s="22"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="A242" s="16"/>
       <c r="B242" s="16"/>
-      <c r="L242" s="21"/>
+      <c r="L242" s="22"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
       <c r="A243" s="16"/>
       <c r="B243" s="16"/>
-      <c r="L243" s="21"/>
+      <c r="L243" s="22"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
       <c r="A244" s="16"/>
       <c r="B244" s="16"/>
-      <c r="L244" s="21"/>
+      <c r="L244" s="22"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="A245" s="16"/>
       <c r="B245" s="16"/>
-      <c r="L245" s="21"/>
+      <c r="L245" s="22"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="A246" s="16"/>
       <c r="B246" s="16"/>
-      <c r="L246" s="21"/>
+      <c r="L246" s="22"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
       <c r="A247" s="16"/>
       <c r="B247" s="16"/>
-      <c r="L247" s="21"/>
+      <c r="L247" s="22"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
       <c r="A248" s="16"/>
       <c r="B248" s="16"/>
-      <c r="L248" s="21"/>
+      <c r="L248" s="22"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
       <c r="A249" s="16"/>
       <c r="B249" s="16"/>
-      <c r="L249" s="21"/>
+      <c r="L249" s="22"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="A250" s="16"/>
       <c r="B250" s="16"/>
-      <c r="L250" s="21"/>
+      <c r="L250" s="22"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
       <c r="A251" s="16"/>
       <c r="B251" s="16"/>
-      <c r="L251" s="21"/>
+      <c r="L251" s="22"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
       <c r="A252" s="16"/>
       <c r="B252" s="16"/>
-      <c r="L252" s="21"/>
+      <c r="L252" s="22"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
       <c r="A253" s="16"/>
       <c r="B253" s="16"/>
-      <c r="L253" s="21"/>
+      <c r="L253" s="22"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="A254" s="16"/>
       <c r="B254" s="16"/>
-      <c r="L254" s="21"/>
+      <c r="L254" s="22"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
       <c r="A255" s="16"/>
       <c r="B255" s="16"/>
-      <c r="L255" s="21"/>
+      <c r="L255" s="22"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
       <c r="A256" s="16"/>
       <c r="B256" s="16"/>
-      <c r="L256" s="21"/>
+      <c r="L256" s="22"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="A257" s="16"/>
       <c r="B257" s="16"/>
-      <c r="L257" s="21"/>
+      <c r="L257" s="22"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="A258" s="16"/>
       <c r="B258" s="16"/>
-      <c r="L258" s="21"/>
+      <c r="L258" s="22"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
       <c r="A259" s="16"/>
       <c r="B259" s="16"/>
-      <c r="L259" s="21"/>
+      <c r="L259" s="22"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
       <c r="A260" s="16"/>
       <c r="B260" s="16"/>
-      <c r="L260" s="21"/>
+      <c r="L260" s="22"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="A261" s="16"/>
       <c r="B261" s="16"/>
-      <c r="L261" s="21"/>
+      <c r="L261" s="22"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="A262" s="16"/>
       <c r="B262" s="16"/>
-      <c r="L262" s="21"/>
+      <c r="L262" s="22"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
       <c r="A263" s="16"/>
       <c r="B263" s="16"/>
-      <c r="L263" s="21"/>
+      <c r="L263" s="22"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
       <c r="A264" s="16"/>
       <c r="B264" s="16"/>
-      <c r="L264" s="21"/>
+      <c r="L264" s="22"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="A265" s="16"/>
       <c r="B265" s="16"/>
-      <c r="L265" s="21"/>
+      <c r="L265" s="22"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="A266" s="16"/>
       <c r="B266" s="16"/>
-      <c r="L266" s="21"/>
+      <c r="L266" s="22"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
       <c r="A267" s="16"/>
       <c r="B267" s="16"/>
-      <c r="L267" s="21"/>
+      <c r="L267" s="22"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
       <c r="A268" s="16"/>
       <c r="B268" s="16"/>
-      <c r="L268" s="21"/>
+      <c r="L268" s="22"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="A269" s="16"/>
       <c r="B269" s="16"/>
-      <c r="L269" s="21"/>
+      <c r="L269" s="22"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="A270" s="16"/>
       <c r="B270" s="16"/>
-      <c r="L270" s="21"/>
+      <c r="L270" s="22"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
       <c r="A271" s="16"/>
       <c r="B271" s="16"/>
-      <c r="L271" s="21"/>
+      <c r="L271" s="22"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
       <c r="A272" s="16"/>
       <c r="B272" s="16"/>
-      <c r="L272" s="21"/>
+      <c r="L272" s="22"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="A273" s="16"/>
       <c r="B273" s="16"/>
-      <c r="L273" s="21"/>
+      <c r="L273" s="22"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="A274" s="16"/>
       <c r="B274" s="16"/>
-      <c r="L274" s="21"/>
+      <c r="L274" s="22"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
       <c r="A275" s="16"/>
       <c r="B275" s="16"/>
-      <c r="L275" s="21"/>
+      <c r="L275" s="22"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
       <c r="A276" s="16"/>
       <c r="B276" s="16"/>
-      <c r="L276" s="21"/>
+      <c r="L276" s="22"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
       <c r="A277" s="16"/>
       <c r="B277" s="16"/>
-      <c r="L277" s="21"/>
+      <c r="L277" s="22"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="A278" s="16"/>
       <c r="B278" s="16"/>
-      <c r="L278" s="21"/>
+      <c r="L278" s="22"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
       <c r="A279" s="16"/>
       <c r="B279" s="16"/>
-      <c r="L279" s="21"/>
+      <c r="L279" s="22"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
       <c r="A280" s="16"/>
       <c r="B280" s="16"/>
-      <c r="L280" s="21"/>
+      <c r="L280" s="22"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
       <c r="A281" s="16"/>
       <c r="B281" s="16"/>
-      <c r="L281" s="21"/>
+      <c r="L281" s="22"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="A282" s="16"/>
       <c r="B282" s="16"/>
-      <c r="L282" s="21"/>
+      <c r="L282" s="22"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
       <c r="A283" s="16"/>
       <c r="B283" s="16"/>
-      <c r="L283" s="21"/>
+      <c r="L283" s="22"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
       <c r="A284" s="16"/>
       <c r="B284" s="16"/>
-      <c r="L284" s="21"/>
+      <c r="L284" s="22"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
       <c r="A285" s="16"/>
       <c r="B285" s="16"/>
-      <c r="L285" s="21"/>
+      <c r="L285" s="22"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="A286" s="16"/>
       <c r="B286" s="16"/>
-      <c r="L286" s="21"/>
+      <c r="L286" s="22"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
       <c r="A287" s="16"/>
       <c r="B287" s="16"/>
-      <c r="L287" s="21"/>
+      <c r="L287" s="22"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
       <c r="A288" s="16"/>
       <c r="B288" s="16"/>
-      <c r="L288" s="21"/>
+      <c r="L288" s="22"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="A289" s="16"/>
       <c r="B289" s="16"/>
-      <c r="L289" s="21"/>
+      <c r="L289" s="22"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="A290" s="16"/>
       <c r="B290" s="16"/>
-      <c r="L290" s="21"/>
+      <c r="L290" s="22"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
       <c r="A291" s="16"/>
       <c r="B291" s="16"/>
-      <c r="L291" s="21"/>
+      <c r="L291" s="22"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
       <c r="A292" s="16"/>
       <c r="B292" s="16"/>
-      <c r="L292" s="21"/>
+      <c r="L292" s="22"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
       <c r="A293" s="16"/>
       <c r="B293" s="16"/>
-      <c r="L293" s="21"/>
+      <c r="L293" s="22"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
       <c r="A294" s="16"/>
       <c r="B294" s="16"/>
-      <c r="L294" s="21"/>
+      <c r="L294" s="22"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
       <c r="A295" s="16"/>
       <c r="B295" s="16"/>
-      <c r="L295" s="21"/>
+      <c r="L295" s="22"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
       <c r="A296" s="16"/>
       <c r="B296" s="16"/>
-      <c r="L296" s="21"/>
+      <c r="L296" s="22"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
       <c r="A297" s="16"/>
       <c r="B297" s="16"/>
-      <c r="L297" s="21"/>
+      <c r="L297" s="22"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="A298" s="16"/>
       <c r="B298" s="16"/>
-      <c r="L298" s="21"/>
+      <c r="L298" s="22"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
       <c r="A299" s="16"/>
       <c r="B299" s="16"/>
-      <c r="L299" s="21"/>
+      <c r="L299" s="22"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
       <c r="A300" s="16"/>
       <c r="B300" s="16"/>
-      <c r="L300" s="21"/>
+      <c r="L300" s="22"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
       <c r="A301" s="16"/>
       <c r="B301" s="16"/>
-      <c r="L301" s="21"/>
+      <c r="L301" s="22"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="A302" s="16"/>
       <c r="B302" s="16"/>
-      <c r="L302" s="21"/>
+      <c r="L302" s="22"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
       <c r="A303" s="16"/>
       <c r="B303" s="16"/>
-      <c r="L303" s="21"/>
+      <c r="L303" s="22"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
       <c r="A304" s="16"/>
       <c r="B304" s="16"/>
-      <c r="L304" s="21"/>
+      <c r="L304" s="22"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
       <c r="A305" s="16"/>
       <c r="B305" s="16"/>
-      <c r="L305" s="21"/>
+      <c r="L305" s="22"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="A306" s="16"/>
       <c r="B306" s="16"/>
-      <c r="L306" s="21"/>
+      <c r="L306" s="22"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
       <c r="A307" s="16"/>
       <c r="B307" s="16"/>
-      <c r="L307" s="21"/>
+      <c r="L307" s="22"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
       <c r="A308" s="16"/>
       <c r="B308" s="16"/>
-      <c r="L308" s="21"/>
+      <c r="L308" s="22"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
       <c r="A309" s="16"/>
       <c r="B309" s="16"/>
-      <c r="L309" s="21"/>
+      <c r="L309" s="22"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="A310" s="16"/>
       <c r="B310" s="16"/>
-      <c r="L310" s="21"/>
+      <c r="L310" s="22"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
       <c r="A311" s="16"/>
       <c r="B311" s="16"/>
-      <c r="L311" s="21"/>
+      <c r="L311" s="22"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
       <c r="A312" s="16"/>
       <c r="B312" s="16"/>
-      <c r="L312" s="21"/>
+      <c r="L312" s="22"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
       <c r="A313" s="16"/>
       <c r="B313" s="16"/>
-      <c r="L313" s="21"/>
+      <c r="L313" s="22"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="A314" s="16"/>
       <c r="B314" s="16"/>
-      <c r="L314" s="21"/>
+      <c r="L314" s="22"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
       <c r="A315" s="16"/>
       <c r="B315" s="16"/>
-      <c r="L315" s="21"/>
+      <c r="L315" s="22"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="A316" s="16"/>
       <c r="B316" s="16"/>
-      <c r="L316" s="21"/>
+      <c r="L316" s="22"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="A317" s="16"/>
       <c r="B317" s="16"/>
-      <c r="L317" s="21"/>
+      <c r="L317" s="22"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="A318" s="16"/>
       <c r="B318" s="16"/>
-      <c r="L318" s="21"/>
+      <c r="L318" s="22"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
       <c r="A319" s="16"/>
       <c r="B319" s="16"/>
-      <c r="L319" s="21"/>
+      <c r="L319" s="22"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="A320" s="16"/>
       <c r="B320" s="16"/>
-      <c r="L320" s="21"/>
+      <c r="L320" s="22"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="A321" s="16"/>
       <c r="B321" s="16"/>
-      <c r="L321" s="21"/>
+      <c r="L321" s="22"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="A322" s="16"/>
       <c r="B322" s="16"/>
-      <c r="L322" s="21"/>
+      <c r="L322" s="22"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
       <c r="A323" s="16"/>
       <c r="B323" s="16"/>
-      <c r="L323" s="21"/>
+      <c r="L323" s="22"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="A324" s="16"/>
       <c r="B324" s="16"/>
-      <c r="L324" s="21"/>
+      <c r="L324" s="22"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="A325" s="16"/>
       <c r="B325" s="16"/>
-      <c r="L325" s="21"/>
+      <c r="L325" s="22"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="A326" s="16"/>
       <c r="B326" s="16"/>
-      <c r="L326" s="21"/>
+      <c r="L326" s="22"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
       <c r="A327" s="16"/>
       <c r="B327" s="16"/>
-      <c r="L327" s="21"/>
+      <c r="L327" s="22"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="A328" s="16"/>
       <c r="B328" s="16"/>
-      <c r="L328" s="21"/>
+      <c r="L328" s="22"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="A329" s="16"/>
       <c r="B329" s="16"/>
-      <c r="L329" s="21"/>
+      <c r="L329" s="22"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="A330" s="16"/>
       <c r="B330" s="16"/>
-      <c r="L330" s="21"/>
+      <c r="L330" s="22"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
       <c r="A331" s="16"/>
       <c r="B331" s="16"/>
-      <c r="L331" s="21"/>
+      <c r="L331" s="22"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="A332" s="16"/>
       <c r="B332" s="16"/>
-      <c r="L332" s="21"/>
+      <c r="L332" s="22"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="A333" s="16"/>
       <c r="B333" s="16"/>
-      <c r="L333" s="21"/>
+      <c r="L333" s="22"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="A334" s="16"/>
       <c r="B334" s="16"/>
-      <c r="L334" s="21"/>
+      <c r="L334" s="22"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
       <c r="A335" s="16"/>
       <c r="B335" s="16"/>
-      <c r="L335" s="21"/>
+      <c r="L335" s="22"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="A336" s="16"/>
       <c r="B336" s="16"/>
-      <c r="L336" s="21"/>
+      <c r="L336" s="22"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="A337" s="16"/>
       <c r="B337" s="16"/>
-      <c r="L337" s="21"/>
+      <c r="L337" s="22"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="A338" s="16"/>
       <c r="B338" s="16"/>
-      <c r="L338" s="21"/>
+      <c r="L338" s="22"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
       <c r="A339" s="16"/>
       <c r="B339" s="16"/>
-      <c r="L339" s="21"/>
+      <c r="L339" s="22"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="A340" s="16"/>
       <c r="B340" s="16"/>
-      <c r="L340" s="21"/>
+      <c r="L340" s="22"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="A341" s="16"/>
       <c r="B341" s="16"/>
-      <c r="L341" s="21"/>
+      <c r="L341" s="22"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="A342" s="16"/>
       <c r="B342" s="16"/>
-      <c r="L342" s="21"/>
+      <c r="L342" s="22"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
       <c r="A343" s="16"/>
       <c r="B343" s="16"/>
-      <c r="L343" s="21"/>
+      <c r="L343" s="22"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="A344" s="16"/>
       <c r="B344" s="16"/>
-      <c r="L344" s="21"/>
+      <c r="L344" s="22"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="A345" s="16"/>
       <c r="B345" s="16"/>
-      <c r="L345" s="21"/>
+      <c r="L345" s="22"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="A346" s="16"/>
       <c r="B346" s="16"/>
-      <c r="L346" s="21"/>
+      <c r="L346" s="22"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
       <c r="A347" s="16"/>
       <c r="B347" s="16"/>
-      <c r="L347" s="21"/>
+      <c r="L347" s="22"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="A348" s="16"/>
       <c r="B348" s="16"/>
-      <c r="L348" s="21"/>
+      <c r="L348" s="22"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="A349" s="16"/>
       <c r="B349" s="16"/>
-      <c r="L349" s="21"/>
+      <c r="L349" s="22"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="A350" s="16"/>
       <c r="B350" s="16"/>
-      <c r="L350" s="21"/>
+      <c r="L350" s="22"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
       <c r="A351" s="16"/>
       <c r="B351" s="16"/>
-      <c r="L351" s="21"/>
+      <c r="L351" s="22"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="A352" s="16"/>
       <c r="B352" s="16"/>
-      <c r="L352" s="21"/>
+      <c r="L352" s="22"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="A353" s="16"/>
       <c r="B353" s="16"/>
-      <c r="L353" s="21"/>
+      <c r="L353" s="22"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="A354" s="16"/>
       <c r="B354" s="16"/>
-      <c r="L354" s="21"/>
+      <c r="L354" s="22"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
       <c r="A355" s="16"/>
       <c r="B355" s="16"/>
-      <c r="L355" s="21"/>
+      <c r="L355" s="22"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="A356" s="16"/>
       <c r="B356" s="16"/>
-      <c r="L356" s="21"/>
+      <c r="L356" s="22"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="A357" s="16"/>
       <c r="B357" s="16"/>
-      <c r="L357" s="21"/>
+      <c r="L357" s="22"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="A358" s="16"/>
       <c r="B358" s="16"/>
-      <c r="L358" s="21"/>
+      <c r="L358" s="22"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="A359" s="16"/>
       <c r="B359" s="16"/>
-      <c r="L359" s="21"/>
+      <c r="L359" s="22"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="A360" s="16"/>
       <c r="B360" s="16"/>
-      <c r="L360" s="21"/>
+      <c r="L360" s="22"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="A361" s="16"/>
       <c r="B361" s="16"/>
-      <c r="L361" s="21"/>
+      <c r="L361" s="22"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="A362" s="16"/>
       <c r="B362" s="16"/>
-      <c r="L362" s="21"/>
+      <c r="L362" s="22"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
       <c r="A363" s="16"/>
       <c r="B363" s="16"/>
-      <c r="L363" s="21"/>
+      <c r="L363" s="22"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="A364" s="16"/>
       <c r="B364" s="16"/>
-      <c r="L364" s="21"/>
+      <c r="L364" s="22"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="A365" s="16"/>
       <c r="B365" s="16"/>
-      <c r="L365" s="21"/>
+      <c r="L365" s="22"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="A366" s="16"/>
       <c r="B366" s="16"/>
-      <c r="L366" s="21"/>
+      <c r="L366" s="22"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="A367" s="16"/>
       <c r="B367" s="16"/>
-      <c r="L367" s="21"/>
+      <c r="L367" s="22"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="A368" s="16"/>
       <c r="B368" s="16"/>
-      <c r="L368" s="21"/>
+      <c r="L368" s="22"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="A369" s="16"/>
       <c r="B369" s="16"/>
-      <c r="L369" s="21"/>
+      <c r="L369" s="22"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="A370" s="16"/>
       <c r="B370" s="16"/>
-      <c r="L370" s="21"/>
+      <c r="L370" s="22"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
       <c r="A371" s="16"/>
       <c r="B371" s="16"/>
-      <c r="L371" s="21"/>
+      <c r="L371" s="22"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="A372" s="16"/>
       <c r="B372" s="16"/>
-      <c r="L372" s="21"/>
+      <c r="L372" s="22"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="A373" s="16"/>
       <c r="B373" s="16"/>
-      <c r="L373" s="21"/>
+      <c r="L373" s="22"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="A374" s="16"/>
       <c r="B374" s="16"/>
-      <c r="L374" s="21"/>
+      <c r="L374" s="22"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="A375" s="16"/>
       <c r="B375" s="16"/>
-      <c r="L375" s="21"/>
+      <c r="L375" s="22"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="A376" s="16"/>
       <c r="B376" s="16"/>
-      <c r="L376" s="21"/>
+      <c r="L376" s="22"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="A377" s="16"/>
       <c r="B377" s="16"/>
-      <c r="L377" s="21"/>
+      <c r="L377" s="22"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="A378" s="16"/>
       <c r="B378" s="16"/>
-      <c r="L378" s="21"/>
+      <c r="L378" s="22"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="A379" s="16"/>
       <c r="B379" s="16"/>
-      <c r="L379" s="21"/>
+      <c r="L379" s="22"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="A380" s="16"/>
       <c r="B380" s="16"/>
-      <c r="L380" s="21"/>
+      <c r="L380" s="22"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="A381" s="16"/>
       <c r="B381" s="16"/>
-      <c r="L381" s="21"/>
+      <c r="L381" s="22"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="A382" s="16"/>
       <c r="B382" s="16"/>
-      <c r="L382" s="21"/>
+      <c r="L382" s="22"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
       <c r="A383" s="16"/>
       <c r="B383" s="16"/>
-      <c r="L383" s="21"/>
+      <c r="L383" s="22"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="A384" s="16"/>
       <c r="B384" s="16"/>
-      <c r="L384" s="21"/>
+      <c r="L384" s="22"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="A385" s="16"/>
       <c r="B385" s="16"/>
-      <c r="L385" s="21"/>
+      <c r="L385" s="22"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="A386" s="16"/>
       <c r="B386" s="16"/>
-      <c r="L386" s="21"/>
+      <c r="L386" s="22"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
       <c r="A387" s="16"/>
       <c r="B387" s="16"/>
-      <c r="L387" s="21"/>
+      <c r="L387" s="22"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
       <c r="A388" s="16"/>
       <c r="B388" s="16"/>
-      <c r="L388" s="21"/>
+      <c r="L388" s="22"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
       <c r="A389" s="16"/>
       <c r="B389" s="16"/>
-      <c r="L389" s="21"/>
+      <c r="L389" s="22"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
       <c r="A390" s="16"/>
       <c r="B390" s="16"/>
-      <c r="L390" s="21"/>
+      <c r="L390" s="22"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
       <c r="A391" s="16"/>
       <c r="B391" s="16"/>
-      <c r="L391" s="21"/>
+      <c r="L391" s="22"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
       <c r="A392" s="16"/>
       <c r="B392" s="16"/>
-      <c r="L392" s="21"/>
+      <c r="L392" s="22"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
       <c r="A393" s="16"/>
       <c r="B393" s="16"/>
-      <c r="L393" s="21"/>
+      <c r="L393" s="22"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
       <c r="A394" s="16"/>
       <c r="B394" s="16"/>
-      <c r="L394" s="21"/>
+      <c r="L394" s="22"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
       <c r="A395" s="16"/>
       <c r="B395" s="16"/>
-      <c r="L395" s="21"/>
+      <c r="L395" s="22"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
       <c r="A396" s="16"/>
       <c r="B396" s="16"/>
-      <c r="L396" s="21"/>
+      <c r="L396" s="22"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
       <c r="A397" s="16"/>
       <c r="B397" s="16"/>
-      <c r="L397" s="21"/>
+      <c r="L397" s="22"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
       <c r="A398" s="16"/>
       <c r="B398" s="16"/>
-      <c r="L398" s="21"/>
+      <c r="L398" s="22"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
       <c r="A399" s="16"/>
       <c r="B399" s="16"/>
-      <c r="L399" s="21"/>
+      <c r="L399" s="22"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
       <c r="A400" s="16"/>
       <c r="B400" s="16"/>
-      <c r="L400" s="21"/>
+      <c r="L400" s="22"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
       <c r="A401" s="16"/>
       <c r="B401" s="16"/>
-      <c r="L401" s="21"/>
+      <c r="L401" s="22"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
       <c r="A402" s="16"/>
       <c r="B402" s="16"/>
-      <c r="L402" s="21"/>
+      <c r="L402" s="22"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
       <c r="A403" s="16"/>
       <c r="B403" s="16"/>
-      <c r="L403" s="21"/>
+      <c r="L403" s="22"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
       <c r="A404" s="16"/>
       <c r="B404" s="16"/>
-      <c r="L404" s="21"/>
+      <c r="L404" s="22"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
       <c r="A405" s="16"/>
       <c r="B405" s="16"/>
-      <c r="L405" s="21"/>
+      <c r="L405" s="22"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
       <c r="A406" s="16"/>
       <c r="B406" s="16"/>
-      <c r="L406" s="21"/>
+      <c r="L406" s="22"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
       <c r="A407" s="16"/>
       <c r="B407" s="16"/>
-      <c r="L407" s="21"/>
+      <c r="L407" s="22"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="A408" s="16"/>
       <c r="B408" s="16"/>
-      <c r="L408" s="21"/>
+      <c r="L408" s="22"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
       <c r="A409" s="16"/>
       <c r="B409" s="16"/>
-      <c r="L409" s="21"/>
+      <c r="L409" s="22"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="A410" s="16"/>
       <c r="B410" s="16"/>
-      <c r="L410" s="21"/>
+      <c r="L410" s="22"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
       <c r="A411" s="16"/>
       <c r="B411" s="16"/>
-      <c r="L411" s="21"/>
+      <c r="L411" s="22"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
       <c r="A412" s="16"/>
       <c r="B412" s="16"/>
-      <c r="L412" s="21"/>
+      <c r="L412" s="22"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
       <c r="A413" s="16"/>
       <c r="B413" s="16"/>
-      <c r="L413" s="21"/>
+      <c r="L413" s="22"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
       <c r="A414" s="16"/>
       <c r="B414" s="16"/>
-      <c r="L414" s="21"/>
+      <c r="L414" s="22"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
       <c r="A415" s="16"/>
       <c r="B415" s="16"/>
-      <c r="L415" s="21"/>
+      <c r="L415" s="22"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="A416" s="16"/>
       <c r="B416" s="16"/>
-      <c r="L416" s="21"/>
+      <c r="L416" s="22"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
       <c r="A417" s="16"/>
       <c r="B417" s="16"/>
-      <c r="L417" s="21"/>
+      <c r="L417" s="22"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="A418" s="16"/>
       <c r="B418" s="16"/>
-      <c r="L418" s="21"/>
+      <c r="L418" s="22"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
       <c r="A419" s="16"/>
       <c r="B419" s="16"/>
-      <c r="L419" s="21"/>
+      <c r="L419" s="22"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
       <c r="A420" s="16"/>
       <c r="B420" s="16"/>
-      <c r="L420" s="21"/>
+      <c r="L420" s="22"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
       <c r="A421" s="16"/>
       <c r="B421" s="16"/>
-      <c r="L421" s="21"/>
+      <c r="L421" s="22"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
       <c r="A422" s="16"/>
       <c r="B422" s="16"/>
-      <c r="L422" s="21"/>
+      <c r="L422" s="22"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
       <c r="A423" s="16"/>
       <c r="B423" s="16"/>
-      <c r="L423" s="21"/>
+      <c r="L423" s="22"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
       <c r="A424" s="16"/>
       <c r="B424" s="16"/>
-      <c r="L424" s="21"/>
+      <c r="L424" s="22"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
       <c r="A425" s="16"/>
       <c r="B425" s="16"/>
-      <c r="L425" s="21"/>
+      <c r="L425" s="22"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
       <c r="A426" s="16"/>
       <c r="B426" s="16"/>
-      <c r="L426" s="21"/>
+      <c r="L426" s="22"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="A427" s="16"/>
       <c r="B427" s="16"/>
-      <c r="L427" s="21"/>
+      <c r="L427" s="22"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="A428" s="16"/>
       <c r="B428" s="16"/>
-      <c r="L428" s="21"/>
+      <c r="L428" s="22"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="A429" s="16"/>
       <c r="B429" s="16"/>
-      <c r="L429" s="21"/>
+      <c r="L429" s="22"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="A430" s="16"/>
       <c r="B430" s="16"/>
-      <c r="L430" s="21"/>
+      <c r="L430" s="22"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="A431" s="16"/>
       <c r="B431" s="16"/>
-      <c r="L431" s="21"/>
+      <c r="L431" s="22"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="A432" s="16"/>
       <c r="B432" s="16"/>
-      <c r="L432" s="21"/>
+      <c r="L432" s="22"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="A433" s="16"/>
       <c r="B433" s="16"/>
-      <c r="L433" s="21"/>
+      <c r="L433" s="22"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="A434" s="16"/>
       <c r="B434" s="16"/>
-      <c r="L434" s="21"/>
+      <c r="L434" s="22"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="A435" s="16"/>
       <c r="B435" s="16"/>
-      <c r="L435" s="21"/>
+      <c r="L435" s="22"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="A436" s="16"/>
       <c r="B436" s="16"/>
-      <c r="L436" s="21"/>
+      <c r="L436" s="22"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="A437" s="16"/>
       <c r="B437" s="16"/>
-      <c r="L437" s="21"/>
+      <c r="L437" s="22"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="A438" s="16"/>
       <c r="B438" s="16"/>
-      <c r="L438" s="21"/>
+      <c r="L438" s="22"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
       <c r="A439" s="16"/>
       <c r="B439" s="16"/>
-      <c r="L439" s="21"/>
+      <c r="L439" s="22"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="A440" s="16"/>
       <c r="B440" s="16"/>
-      <c r="L440" s="21"/>
+      <c r="L440" s="22"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="A441" s="16"/>
       <c r="B441" s="16"/>
-      <c r="L441" s="21"/>
+      <c r="L441" s="22"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="A442" s="16"/>
       <c r="B442" s="16"/>
-      <c r="L442" s="21"/>
+      <c r="L442" s="22"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
       <c r="A443" s="16"/>
       <c r="B443" s="16"/>
-      <c r="L443" s="21"/>
+      <c r="L443" s="22"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="A444" s="16"/>
       <c r="B444" s="16"/>
-      <c r="L444" s="21"/>
+      <c r="L444" s="22"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="A445" s="16"/>
       <c r="B445" s="16"/>
-      <c r="L445" s="21"/>
+      <c r="L445" s="22"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="A446" s="16"/>
       <c r="B446" s="16"/>
-      <c r="L446" s="21"/>
+      <c r="L446" s="22"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="A447" s="16"/>
       <c r="B447" s="16"/>
-      <c r="L447" s="21"/>
+      <c r="L447" s="22"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="A448" s="16"/>
       <c r="B448" s="16"/>
-      <c r="L448" s="21"/>
+      <c r="L448" s="22"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="A449" s="16"/>
       <c r="B449" s="16"/>
-      <c r="L449" s="21"/>
+      <c r="L449" s="22"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="A450" s="16"/>
       <c r="B450" s="16"/>
-      <c r="L450" s="21"/>
+      <c r="L450" s="22"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="A451" s="16"/>
       <c r="B451" s="16"/>
-      <c r="L451" s="21"/>
+      <c r="L451" s="22"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="A452" s="16"/>
       <c r="B452" s="16"/>
-      <c r="L452" s="21"/>
+      <c r="L452" s="22"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="A453" s="16"/>
       <c r="B453" s="16"/>
-      <c r="L453" s="21"/>
+      <c r="L453" s="22"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="A454" s="16"/>
       <c r="B454" s="16"/>
-      <c r="L454" s="21"/>
+      <c r="L454" s="22"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="A455" s="16"/>
       <c r="B455" s="16"/>
-      <c r="L455" s="21"/>
+      <c r="L455" s="22"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="A456" s="16"/>
       <c r="B456" s="16"/>
-      <c r="L456" s="21"/>
+      <c r="L456" s="22"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="A457" s="16"/>
       <c r="B457" s="16"/>
-      <c r="L457" s="21"/>
+      <c r="L457" s="22"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="A458" s="16"/>
       <c r="B458" s="16"/>
-      <c r="L458" s="21"/>
+      <c r="L458" s="22"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="A459" s="16"/>
       <c r="B459" s="16"/>
-      <c r="L459" s="21"/>
+      <c r="L459" s="22"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="A460" s="16"/>
       <c r="B460" s="16"/>
-      <c r="L460" s="21"/>
+      <c r="L460" s="22"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="A461" s="16"/>
       <c r="B461" s="16"/>
-      <c r="L461" s="21"/>
+      <c r="L461" s="22"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="A462" s="16"/>
       <c r="B462" s="16"/>
-      <c r="L462" s="21"/>
+      <c r="L462" s="22"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
       <c r="A463" s="16"/>
       <c r="B463" s="16"/>
-      <c r="L463" s="21"/>
+      <c r="L463" s="22"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="A464" s="16"/>
       <c r="B464" s="16"/>
-      <c r="L464" s="21"/>
+      <c r="L464" s="22"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="A465" s="16"/>
       <c r="B465" s="16"/>
-      <c r="L465" s="21"/>
+      <c r="L465" s="22"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="A466" s="16"/>
       <c r="B466" s="16"/>
-      <c r="L466" s="21"/>
+      <c r="L466" s="22"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="A467" s="16"/>
       <c r="B467" s="16"/>
-      <c r="L467" s="21"/>
+      <c r="L467" s="22"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="A468" s="16"/>
       <c r="B468" s="16"/>
-      <c r="L468" s="21"/>
+      <c r="L468" s="22"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="A469" s="16"/>
       <c r="B469" s="16"/>
-      <c r="L469" s="21"/>
+      <c r="L469" s="22"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="A470" s="16"/>
       <c r="B470" s="16"/>
-      <c r="L470" s="21"/>
+      <c r="L470" s="22"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
       <c r="A471" s="16"/>
       <c r="B471" s="16"/>
-      <c r="L471" s="21"/>
+      <c r="L471" s="22"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="A472" s="16"/>
       <c r="B472" s="16"/>
-      <c r="L472" s="21"/>
+      <c r="L472" s="22"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="A473" s="16"/>
       <c r="B473" s="16"/>
-      <c r="L473" s="21"/>
+      <c r="L473" s="22"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="A474" s="16"/>
       <c r="B474" s="16"/>
-      <c r="L474" s="21"/>
+      <c r="L474" s="22"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
       <c r="A475" s="16"/>
       <c r="B475" s="16"/>
-      <c r="L475" s="21"/>
+      <c r="L475" s="22"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="A476" s="16"/>
       <c r="B476" s="16"/>
-      <c r="L476" s="21"/>
+      <c r="L476" s="22"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="A477" s="16"/>
       <c r="B477" s="16"/>
-      <c r="L477" s="21"/>
+      <c r="L477" s="22"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="A478" s="16"/>
       <c r="B478" s="16"/>
-      <c r="L478" s="21"/>
+      <c r="L478" s="22"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
       <c r="A479" s="16"/>
       <c r="B479" s="16"/>
-      <c r="L479" s="21"/>
+      <c r="L479" s="22"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="A480" s="16"/>
       <c r="B480" s="16"/>
-      <c r="L480" s="21"/>
+      <c r="L480" s="22"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="A481" s="16"/>
       <c r="B481" s="16"/>
-      <c r="L481" s="21"/>
+      <c r="L481" s="22"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="A482" s="16"/>
       <c r="B482" s="16"/>
-      <c r="L482" s="21"/>
+      <c r="L482" s="22"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="16"/>
       <c r="B483" s="16"/>
-      <c r="L483" s="21"/>
+      <c r="L483" s="22"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="A484" s="16"/>
       <c r="B484" s="16"/>
-      <c r="L484" s="21"/>
+      <c r="L484" s="22"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="A485" s="16"/>
       <c r="B485" s="16"/>
-      <c r="L485" s="21"/>
+      <c r="L485" s="22"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="A486" s="16"/>
       <c r="B486" s="16"/>
-      <c r="L486" s="21"/>
+      <c r="L486" s="22"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
       <c r="A487" s="16"/>
       <c r="B487" s="16"/>
-      <c r="L487" s="21"/>
+      <c r="L487" s="22"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="A488" s="16"/>
       <c r="B488" s="16"/>
-      <c r="L488" s="21"/>
+      <c r="L488" s="22"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="A489" s="16"/>
       <c r="B489" s="16"/>
-      <c r="L489" s="21"/>
+      <c r="L489" s="22"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="A490" s="16"/>
       <c r="B490" s="16"/>
-      <c r="L490" s="21"/>
+      <c r="L490" s="22"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
       <c r="A491" s="16"/>
       <c r="B491" s="16"/>
-      <c r="L491" s="21"/>
+      <c r="L491" s="22"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="A492" s="16"/>
       <c r="B492" s="16"/>
-      <c r="L492" s="21"/>
+      <c r="L492" s="22"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="A493" s="16"/>
       <c r="B493" s="16"/>
-      <c r="L493" s="21"/>
+      <c r="L493" s="22"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="A494" s="16"/>
       <c r="B494" s="16"/>
-      <c r="L494" s="21"/>
+      <c r="L494" s="22"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="A495" s="16"/>
       <c r="B495" s="16"/>
-      <c r="L495" s="21"/>
+      <c r="L495" s="22"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
       <c r="A496" s="16"/>
       <c r="B496" s="16"/>
-      <c r="L496" s="21"/>
+      <c r="L496" s="22"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
       <c r="A497" s="16"/>
       <c r="B497" s="16"/>
-      <c r="L497" s="21"/>
+      <c r="L497" s="22"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="A498" s="16"/>
       <c r="B498" s="16"/>
-      <c r="L498" s="21"/>
+      <c r="L498" s="22"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="A499" s="16"/>
       <c r="B499" s="16"/>
-      <c r="L499" s="21"/>
+      <c r="L499" s="22"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="A500" s="16"/>
       <c r="B500" s="16"/>
-      <c r="L500" s="21"/>
+      <c r="L500" s="22"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="A501" s="16"/>
       <c r="B501" s="16"/>
-      <c r="L501" s="21"/>
+      <c r="L501" s="22"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="A502" s="16"/>
       <c r="B502" s="16"/>
-      <c r="L502" s="21"/>
+      <c r="L502" s="22"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
       <c r="A503" s="16"/>
       <c r="B503" s="16"/>
-      <c r="L503" s="21"/>
+      <c r="L503" s="22"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="A504" s="16"/>
       <c r="B504" s="16"/>
-      <c r="L504" s="21"/>
+      <c r="L504" s="22"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="A505" s="16"/>
       <c r="B505" s="16"/>
-      <c r="L505" s="21"/>
+      <c r="L505" s="22"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="A506" s="16"/>
       <c r="B506" s="16"/>
-      <c r="L506" s="21"/>
+      <c r="L506" s="22"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="A507" s="16"/>
       <c r="B507" s="16"/>
-      <c r="L507" s="21"/>
+      <c r="L507" s="22"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="A508" s="16"/>
       <c r="B508" s="16"/>
-      <c r="L508" s="21"/>
+      <c r="L508" s="22"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="A509" s="16"/>
       <c r="B509" s="16"/>
-      <c r="L509" s="21"/>
+      <c r="L509" s="22"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="A510" s="16"/>
       <c r="B510" s="16"/>
-      <c r="L510" s="21"/>
+      <c r="L510" s="22"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="A511" s="16"/>
       <c r="B511" s="16"/>
-      <c r="L511" s="21"/>
+      <c r="L511" s="22"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="A512" s="16"/>
       <c r="B512" s="16"/>
-      <c r="L512" s="21"/>
+      <c r="L512" s="22"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="A513" s="16"/>
       <c r="B513" s="16"/>
-      <c r="L513" s="21"/>
+      <c r="L513" s="22"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="A514" s="16"/>
       <c r="B514" s="16"/>
-      <c r="L514" s="21"/>
+      <c r="L514" s="22"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="A515" s="16"/>
       <c r="B515" s="16"/>
-      <c r="L515" s="21"/>
+      <c r="L515" s="22"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="A516" s="16"/>
       <c r="B516" s="16"/>
-      <c r="L516" s="21"/>
+      <c r="L516" s="22"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="A517" s="16"/>
       <c r="B517" s="16"/>
-      <c r="L517" s="21"/>
+      <c r="L517" s="22"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="A518" s="16"/>
       <c r="B518" s="16"/>
-      <c r="L518" s="21"/>
+      <c r="L518" s="22"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="A519" s="16"/>
       <c r="B519" s="16"/>
-      <c r="L519" s="21"/>
+      <c r="L519" s="22"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="A520" s="16"/>
       <c r="B520" s="16"/>
-      <c r="L520" s="21"/>
+      <c r="L520" s="22"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="A521" s="16"/>
       <c r="B521" s="16"/>
-      <c r="L521" s="21"/>
+      <c r="L521" s="22"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="A522" s="16"/>
       <c r="B522" s="16"/>
-      <c r="L522" s="21"/>
+      <c r="L522" s="22"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="A523" s="16"/>
       <c r="B523" s="16"/>
-      <c r="L523" s="21"/>
+      <c r="L523" s="22"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
       <c r="A524" s="16"/>
       <c r="B524" s="16"/>
-      <c r="L524" s="21"/>
+      <c r="L524" s="22"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
       <c r="A525" s="16"/>
       <c r="B525" s="16"/>
-      <c r="L525" s="21"/>
+      <c r="L525" s="22"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="A526" s="16"/>
       <c r="B526" s="16"/>
-      <c r="L526" s="21"/>
+      <c r="L526" s="22"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="A527" s="16"/>
       <c r="B527" s="16"/>
-      <c r="L527" s="21"/>
+      <c r="L527" s="22"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
       <c r="A528" s="16"/>
       <c r="B528" s="16"/>
-      <c r="L528" s="21"/>
+      <c r="L528" s="22"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
       <c r="A529" s="16"/>
       <c r="B529" s="16"/>
-      <c r="L529" s="21"/>
+      <c r="L529" s="22"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="A530" s="16"/>
       <c r="B530" s="16"/>
-      <c r="L530" s="21"/>
+      <c r="L530" s="22"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="A531" s="16"/>
       <c r="B531" s="16"/>
-      <c r="L531" s="21"/>
+      <c r="L531" s="22"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
       <c r="A532" s="16"/>
       <c r="B532" s="16"/>
-      <c r="L532" s="21"/>
+      <c r="L532" s="22"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
       <c r="A533" s="16"/>
       <c r="B533" s="16"/>
-      <c r="L533" s="21"/>
+      <c r="L533" s="22"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
       <c r="A534" s="16"/>
       <c r="B534" s="16"/>
-      <c r="L534" s="21"/>
+      <c r="L534" s="22"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="A535" s="16"/>
       <c r="B535" s="16"/>
-      <c r="L535" s="21"/>
+      <c r="L535" s="22"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="A536" s="16"/>
       <c r="B536" s="16"/>
-      <c r="L536" s="21"/>
+      <c r="L536" s="22"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
       <c r="A537" s="16"/>
       <c r="B537" s="16"/>
-      <c r="L537" s="21"/>
+      <c r="L537" s="22"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
       <c r="A538" s="16"/>
       <c r="B538" s="16"/>
-      <c r="L538" s="21"/>
+      <c r="L538" s="22"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
       <c r="A539" s="16"/>
       <c r="B539" s="16"/>
-      <c r="L539" s="21"/>
+      <c r="L539" s="22"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
       <c r="A540" s="16"/>
       <c r="B540" s="16"/>
-      <c r="L540" s="21"/>
+      <c r="L540" s="22"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
       <c r="A541" s="16"/>
       <c r="B541" s="16"/>
-      <c r="L541" s="21"/>
+      <c r="L541" s="22"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
       <c r="A542" s="16"/>
       <c r="B542" s="16"/>
-      <c r="L542" s="21"/>
+      <c r="L542" s="22"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
       <c r="A543" s="16"/>
       <c r="B543" s="16"/>
-      <c r="L543" s="21"/>
+      <c r="L543" s="22"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="A544" s="16"/>
       <c r="B544" s="16"/>
-      <c r="L544" s="21"/>
+      <c r="L544" s="22"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="A545" s="16"/>
       <c r="B545" s="16"/>
-      <c r="L545" s="21"/>
+      <c r="L545" s="22"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="A546" s="16"/>
       <c r="B546" s="16"/>
-      <c r="L546" s="21"/>
+      <c r="L546" s="22"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="A547" s="16"/>
       <c r="B547" s="16"/>
-      <c r="L547" s="21"/>
+      <c r="L547" s="22"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="A548" s="16"/>
       <c r="B548" s="16"/>
-      <c r="L548" s="21"/>
+      <c r="L548" s="22"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="A549" s="16"/>
       <c r="B549" s="16"/>
-      <c r="L549" s="21"/>
+      <c r="L549" s="22"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="A550" s="16"/>
       <c r="B550" s="16"/>
-      <c r="L550" s="21"/>
+      <c r="L550" s="22"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="A551" s="16"/>
       <c r="B551" s="16"/>
-      <c r="L551" s="21"/>
+      <c r="L551" s="22"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="A552" s="16"/>
       <c r="B552" s="16"/>
-      <c r="L552" s="21"/>
+      <c r="L552" s="22"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="A553" s="16"/>
       <c r="B553" s="16"/>
-      <c r="L553" s="21"/>
+      <c r="L553" s="22"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="A554" s="16"/>
       <c r="B554" s="16"/>
-      <c r="L554" s="21"/>
+      <c r="L554" s="22"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="A555" s="16"/>
       <c r="B555" s="16"/>
-      <c r="L555" s="21"/>
+      <c r="L555" s="22"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="A556" s="16"/>
       <c r="B556" s="16"/>
-      <c r="L556" s="21"/>
+      <c r="L556" s="22"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="A557" s="16"/>
       <c r="B557" s="16"/>
-      <c r="L557" s="21"/>
+      <c r="L557" s="22"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="A558" s="16"/>
       <c r="B558" s="16"/>
-      <c r="L558" s="21"/>
+      <c r="L558" s="22"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="A559" s="16"/>
       <c r="B559" s="16"/>
-      <c r="L559" s="21"/>
+      <c r="L559" s="22"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="A560" s="16"/>
       <c r="B560" s="16"/>
-      <c r="L560" s="21"/>
+      <c r="L560" s="22"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="A561" s="16"/>
       <c r="B561" s="16"/>
-      <c r="L561" s="21"/>
+      <c r="L561" s="22"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="A562" s="16"/>
       <c r="B562" s="16"/>
-      <c r="L562" s="21"/>
+      <c r="L562" s="22"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
       <c r="A563" s="16"/>
       <c r="B563" s="16"/>
-      <c r="L563" s="21"/>
+      <c r="L563" s="22"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
       <c r="A564" s="16"/>
       <c r="B564" s="16"/>
-      <c r="L564" s="21"/>
+      <c r="L564" s="22"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
       <c r="A565" s="16"/>
       <c r="B565" s="16"/>
-      <c r="L565" s="21"/>
+      <c r="L565" s="22"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
       <c r="A566" s="16"/>
       <c r="B566" s="16"/>
-      <c r="L566" s="21"/>
+      <c r="L566" s="22"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
       <c r="A567" s="16"/>
       <c r="B567" s="16"/>
-      <c r="L567" s="21"/>
+      <c r="L567" s="22"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
       <c r="A568" s="16"/>
       <c r="B568" s="16"/>
-      <c r="L568" s="21"/>
+      <c r="L568" s="22"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
       <c r="A569" s="16"/>
       <c r="B569" s="16"/>
-      <c r="L569" s="21"/>
+      <c r="L569" s="22"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
       <c r="A570" s="16"/>
       <c r="B570" s="16"/>
-      <c r="L570" s="21"/>
+      <c r="L570" s="22"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
       <c r="A571" s="16"/>
       <c r="B571" s="16"/>
-      <c r="L571" s="21"/>
+      <c r="L571" s="22"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
       <c r="A572" s="16"/>
       <c r="B572" s="16"/>
-      <c r="L572" s="21"/>
+      <c r="L572" s="22"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
       <c r="A573" s="16"/>
       <c r="B573" s="16"/>
-      <c r="L573" s="21"/>
+      <c r="L573" s="22"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
       <c r="A574" s="16"/>
       <c r="B574" s="16"/>
-      <c r="L574" s="21"/>
+      <c r="L574" s="22"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
       <c r="A575" s="16"/>
       <c r="B575" s="16"/>
-      <c r="L575" s="21"/>
+      <c r="L575" s="22"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
       <c r="A576" s="16"/>
       <c r="B576" s="16"/>
-      <c r="L576" s="21"/>
+      <c r="L576" s="22"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
       <c r="A577" s="16"/>
       <c r="B577" s="16"/>
-      <c r="L577" s="21"/>
+      <c r="L577" s="22"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
       <c r="A578" s="16"/>
       <c r="B578" s="16"/>
-      <c r="L578" s="21"/>
+      <c r="L578" s="22"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
       <c r="A579" s="16"/>
       <c r="B579" s="16"/>
-      <c r="L579" s="21"/>
+      <c r="L579" s="22"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
       <c r="A580" s="16"/>
       <c r="B580" s="16"/>
-      <c r="L580" s="21"/>
+      <c r="L580" s="22"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
       <c r="A581" s="16"/>
       <c r="B581" s="16"/>
-      <c r="L581" s="21"/>
+      <c r="L581" s="22"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
       <c r="A582" s="16"/>
       <c r="B582" s="16"/>
-      <c r="L582" s="21"/>
+      <c r="L582" s="22"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
       <c r="A583" s="16"/>
       <c r="B583" s="16"/>
-      <c r="L583" s="21"/>
+      <c r="L583" s="22"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
       <c r="A584" s="16"/>
       <c r="B584" s="16"/>
-      <c r="L584" s="21"/>
+      <c r="L584" s="22"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
       <c r="A585" s="16"/>
       <c r="B585" s="16"/>
-      <c r="L585" s="21"/>
+      <c r="L585" s="22"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
       <c r="A586" s="16"/>
       <c r="B586" s="16"/>
-      <c r="L586" s="21"/>
+      <c r="L586" s="22"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="A587" s="16"/>
       <c r="B587" s="16"/>
-      <c r="L587" s="21"/>
+      <c r="L587" s="22"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="A588" s="16"/>
       <c r="B588" s="16"/>
-      <c r="L588" s="21"/>
+      <c r="L588" s="22"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="A589" s="16"/>
       <c r="B589" s="16"/>
-      <c r="L589" s="21"/>
+      <c r="L589" s="22"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="A590" s="16"/>
       <c r="B590" s="16"/>
-      <c r="L590" s="21"/>
+      <c r="L590" s="22"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="A591" s="16"/>
       <c r="B591" s="16"/>
-      <c r="L591" s="21"/>
+      <c r="L591" s="22"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
       <c r="A592" s="16"/>
       <c r="B592" s="16"/>
-      <c r="L592" s="21"/>
+      <c r="L592" s="22"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
       <c r="A593" s="16"/>
       <c r="B593" s="16"/>
-      <c r="L593" s="21"/>
+      <c r="L593" s="22"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="A594" s="16"/>
       <c r="B594" s="16"/>
-      <c r="L594" s="21"/>
+      <c r="L594" s="22"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="A595" s="16"/>
       <c r="B595" s="16"/>
-      <c r="L595" s="21"/>
+      <c r="L595" s="22"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="A596" s="16"/>
       <c r="B596" s="16"/>
-      <c r="L596" s="21"/>
+      <c r="L596" s="22"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="A597" s="16"/>
       <c r="B597" s="16"/>
-      <c r="L597" s="21"/>
+      <c r="L597" s="22"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="A598" s="16"/>
       <c r="B598" s="16"/>
-      <c r="L598" s="21"/>
+      <c r="L598" s="22"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="A599" s="16"/>
       <c r="B599" s="16"/>
-      <c r="L599" s="21"/>
+      <c r="L599" s="22"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
       <c r="A600" s="16"/>
       <c r="B600" s="16"/>
-      <c r="L600" s="21"/>
+      <c r="L600" s="22"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
       <c r="A601" s="16"/>
       <c r="B601" s="16"/>
-      <c r="L601" s="21"/>
+      <c r="L601" s="22"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
       <c r="A602" s="16"/>
       <c r="B602" s="16"/>
-      <c r="L602" s="21"/>
+      <c r="L602" s="22"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
       <c r="A603" s="16"/>
       <c r="B603" s="16"/>
-      <c r="L603" s="21"/>
+      <c r="L603" s="22"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="A604" s="16"/>
       <c r="B604" s="16"/>
-      <c r="L604" s="21"/>
+      <c r="L604" s="22"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="A605" s="16"/>
       <c r="B605" s="16"/>
-      <c r="L605" s="21"/>
+      <c r="L605" s="22"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="A606" s="16"/>
       <c r="B606" s="16"/>
-      <c r="L606" s="21"/>
+      <c r="L606" s="22"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="A607" s="16"/>
       <c r="B607" s="16"/>
-      <c r="L607" s="21"/>
+      <c r="L607" s="22"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
       <c r="A608" s="16"/>
       <c r="B608" s="16"/>
-      <c r="L608" s="21"/>
+      <c r="L608" s="22"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
       <c r="A609" s="16"/>
       <c r="B609" s="16"/>
-      <c r="L609" s="21"/>
+      <c r="L609" s="22"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
       <c r="A610" s="16"/>
       <c r="B610" s="16"/>
-      <c r="L610" s="21"/>
+      <c r="L610" s="22"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="A611" s="16"/>
       <c r="B611" s="16"/>
-      <c r="L611" s="21"/>
+      <c r="L611" s="22"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="A612" s="16"/>
       <c r="B612" s="16"/>
-      <c r="L612" s="21"/>
+      <c r="L612" s="22"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="A613" s="16"/>
       <c r="B613" s="16"/>
-      <c r="L613" s="21"/>
+      <c r="L613" s="22"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="A614" s="16"/>
       <c r="B614" s="16"/>
-      <c r="L614" s="21"/>
+      <c r="L614" s="22"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="A615" s="16"/>
       <c r="B615" s="16"/>
-      <c r="L615" s="21"/>
+      <c r="L615" s="22"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
       <c r="A616" s="16"/>
       <c r="B616" s="16"/>
-      <c r="L616" s="21"/>
+      <c r="L616" s="22"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
       <c r="A617" s="16"/>
       <c r="B617" s="16"/>
-      <c r="L617" s="21"/>
+      <c r="L617" s="22"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
       <c r="A618" s="16"/>
       <c r="B618" s="16"/>
-      <c r="L618" s="21"/>
+      <c r="L618" s="22"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="A619" s="16"/>
       <c r="B619" s="16"/>
-      <c r="L619" s="21"/>
+      <c r="L619" s="22"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="A620" s="16"/>
       <c r="B620" s="16"/>
-      <c r="L620" s="21"/>
+      <c r="L620" s="22"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="A621" s="16"/>
       <c r="B621" s="16"/>
-      <c r="L621" s="21"/>
+      <c r="L621" s="22"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="A622" s="16"/>
       <c r="B622" s="16"/>
-      <c r="L622" s="21"/>
+      <c r="L622" s="22"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
       <c r="A623" s="16"/>
       <c r="B623" s="16"/>
-      <c r="L623" s="21"/>
+      <c r="L623" s="22"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="A624" s="16"/>
       <c r="B624" s="16"/>
-      <c r="L624" s="21"/>
+      <c r="L624" s="22"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
       <c r="A625" s="16"/>
       <c r="B625" s="16"/>
-      <c r="L625" s="21"/>
+      <c r="L625" s="22"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="A626" s="16"/>
       <c r="B626" s="16"/>
-      <c r="L626" s="21"/>
+      <c r="L626" s="22"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="A627" s="16"/>
       <c r="B627" s="16"/>
-      <c r="L627" s="21"/>
+      <c r="L627" s="22"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="A628" s="16"/>
       <c r="B628" s="16"/>
-      <c r="L628" s="21"/>
+      <c r="L628" s="22"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="A629" s="16"/>
       <c r="B629" s="16"/>
-      <c r="L629" s="21"/>
+      <c r="L629" s="22"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="A630" s="16"/>
       <c r="B630" s="16"/>
-      <c r="L630" s="21"/>
+      <c r="L630" s="22"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="A631" s="16"/>
       <c r="B631" s="16"/>
-      <c r="L631" s="21"/>
+      <c r="L631" s="22"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
       <c r="A632" s="16"/>
       <c r="B632" s="16"/>
-      <c r="L632" s="21"/>
+      <c r="L632" s="22"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
       <c r="A633" s="16"/>
       <c r="B633" s="16"/>
-      <c r="L633" s="21"/>
+      <c r="L633" s="22"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
       <c r="A634" s="16"/>
       <c r="B634" s="16"/>
-      <c r="L634" s="21"/>
+      <c r="L634" s="22"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="A635" s="16"/>
       <c r="B635" s="16"/>
-      <c r="L635" s="21"/>
+      <c r="L635" s="22"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="A636" s="16"/>
       <c r="B636" s="16"/>
-      <c r="L636" s="21"/>
+      <c r="L636" s="22"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="A637" s="16"/>
       <c r="B637" s="16"/>
-      <c r="L637" s="21"/>
+      <c r="L637" s="22"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="A638" s="16"/>
       <c r="B638" s="16"/>
-      <c r="L638" s="21"/>
+      <c r="L638" s="22"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="A639" s="16"/>
       <c r="B639" s="16"/>
-      <c r="L639" s="21"/>
+      <c r="L639" s="22"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="A640" s="16"/>
       <c r="B640" s="16"/>
-      <c r="L640" s="21"/>
+      <c r="L640" s="22"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="A641" s="16"/>
       <c r="B641" s="16"/>
-      <c r="L641" s="21"/>
+      <c r="L641" s="22"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="A642" s="16"/>
       <c r="B642" s="16"/>
-      <c r="L642" s="21"/>
+      <c r="L642" s="22"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
       <c r="A643" s="16"/>
       <c r="B643" s="16"/>
-      <c r="L643" s="21"/>
+      <c r="L643" s="22"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
       <c r="A644" s="16"/>
       <c r="B644" s="16"/>
-      <c r="L644" s="21"/>
+      <c r="L644" s="22"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
       <c r="A645" s="16"/>
       <c r="B645" s="16"/>
-      <c r="L645" s="21"/>
+      <c r="L645" s="22"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
       <c r="A646" s="16"/>
       <c r="B646" s="16"/>
-      <c r="L646" s="21"/>
+      <c r="L646" s="22"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
       <c r="A647" s="16"/>
       <c r="B647" s="16"/>
-      <c r="L647" s="21"/>
+      <c r="L647" s="22"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
       <c r="A648" s="16"/>
       <c r="B648" s="16"/>
-      <c r="L648" s="21"/>
+      <c r="L648" s="22"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
       <c r="A649" s="16"/>
       <c r="B649" s="16"/>
-      <c r="L649" s="21"/>
+      <c r="L649" s="22"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
       <c r="A650" s="16"/>
       <c r="B650" s="16"/>
-      <c r="L650" s="21"/>
+      <c r="L650" s="22"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
       <c r="A651" s="16"/>
       <c r="B651" s="16"/>
-      <c r="L651" s="21"/>
+      <c r="L651" s="22"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
       <c r="A652" s="16"/>
       <c r="B652" s="16"/>
-      <c r="L652" s="21"/>
+      <c r="L652" s="22"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
       <c r="A653" s="16"/>
       <c r="B653" s="16"/>
-      <c r="L653" s="21"/>
+      <c r="L653" s="22"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
       <c r="A654" s="16"/>
       <c r="B654" s="16"/>
-      <c r="L654" s="21"/>
+      <c r="L654" s="22"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
       <c r="A655" s="16"/>
       <c r="B655" s="16"/>
-      <c r="L655" s="21"/>
+      <c r="L655" s="22"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
       <c r="A656" s="16"/>
       <c r="B656" s="16"/>
-      <c r="L656" s="21"/>
+      <c r="L656" s="22"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
       <c r="A657" s="16"/>
       <c r="B657" s="16"/>
-      <c r="L657" s="21"/>
+      <c r="L657" s="22"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
       <c r="A658" s="16"/>
       <c r="B658" s="16"/>
-      <c r="L658" s="21"/>
+      <c r="L658" s="22"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
       <c r="A659" s="16"/>
       <c r="B659" s="16"/>
-      <c r="L659" s="21"/>
+      <c r="L659" s="22"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
       <c r="A660" s="16"/>
       <c r="B660" s="16"/>
-      <c r="L660" s="21"/>
+      <c r="L660" s="22"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
       <c r="A661" s="16"/>
       <c r="B661" s="16"/>
-      <c r="L661" s="21"/>
+      <c r="L661" s="22"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
       <c r="A662" s="16"/>
       <c r="B662" s="16"/>
-      <c r="L662" s="21"/>
+      <c r="L662" s="22"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
       <c r="A663" s="16"/>
       <c r="B663" s="16"/>
-      <c r="L663" s="21"/>
+      <c r="L663" s="22"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
       <c r="A664" s="16"/>
       <c r="B664" s="16"/>
-      <c r="L664" s="21"/>
+      <c r="L664" s="22"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
       <c r="A665" s="16"/>
       <c r="B665" s="16"/>
-      <c r="L665" s="21"/>
+      <c r="L665" s="22"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
       <c r="A666" s="16"/>
       <c r="B666" s="16"/>
-      <c r="L666" s="21"/>
+      <c r="L666" s="22"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
       <c r="A667" s="16"/>
       <c r="B667" s="16"/>
-      <c r="L667" s="21"/>
+      <c r="L667" s="22"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
       <c r="A668" s="16"/>
       <c r="B668" s="16"/>
-      <c r="L668" s="21"/>
+      <c r="L668" s="22"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
       <c r="A669" s="16"/>
       <c r="B669" s="16"/>
-      <c r="L669" s="21"/>
+      <c r="L669" s="22"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
       <c r="A670" s="16"/>
       <c r="B670" s="16"/>
-      <c r="L670" s="21"/>
+      <c r="L670" s="22"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
       <c r="A671" s="16"/>
       <c r="B671" s="16"/>
-      <c r="L671" s="21"/>
+      <c r="L671" s="22"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
       <c r="A672" s="16"/>
       <c r="B672" s="16"/>
-      <c r="L672" s="21"/>
+      <c r="L672" s="22"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
       <c r="A673" s="16"/>
       <c r="B673" s="16"/>
-      <c r="L673" s="21"/>
+      <c r="L673" s="22"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
       <c r="A674" s="16"/>
       <c r="B674" s="16"/>
-      <c r="L674" s="21"/>
+      <c r="L674" s="22"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
       <c r="A675" s="16"/>
       <c r="B675" s="16"/>
-      <c r="L675" s="21"/>
+      <c r="L675" s="22"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
       <c r="A676" s="16"/>
       <c r="B676" s="16"/>
-      <c r="L676" s="21"/>
+      <c r="L676" s="22"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
       <c r="A677" s="16"/>
       <c r="B677" s="16"/>
-      <c r="L677" s="21"/>
+      <c r="L677" s="22"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
       <c r="A678" s="16"/>
       <c r="B678" s="16"/>
-      <c r="L678" s="21"/>
+      <c r="L678" s="22"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
       <c r="A679" s="16"/>
       <c r="B679" s="16"/>
-      <c r="L679" s="21"/>
+      <c r="L679" s="22"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
       <c r="A680" s="16"/>
       <c r="B680" s="16"/>
-      <c r="L680" s="21"/>
+      <c r="L680" s="22"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
       <c r="A681" s="16"/>
       <c r="B681" s="16"/>
-      <c r="L681" s="21"/>
+      <c r="L681" s="22"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
       <c r="A682" s="16"/>
       <c r="B682" s="16"/>
-      <c r="L682" s="21"/>
+      <c r="L682" s="22"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
       <c r="A683" s="16"/>
       <c r="B683" s="16"/>
-      <c r="L683" s="21"/>
+      <c r="L683" s="22"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
       <c r="A684" s="16"/>
       <c r="B684" s="16"/>
-      <c r="L684" s="21"/>
+      <c r="L684" s="22"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
       <c r="A685" s="16"/>
       <c r="B685" s="16"/>
-      <c r="L685" s="21"/>
+      <c r="L685" s="22"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
       <c r="A686" s="16"/>
       <c r="B686" s="16"/>
-      <c r="L686" s="21"/>
+      <c r="L686" s="22"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
       <c r="A687" s="16"/>
       <c r="B687" s="16"/>
-      <c r="L687" s="21"/>
+      <c r="L687" s="22"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
       <c r="A688" s="16"/>
       <c r="B688" s="16"/>
-      <c r="L688" s="21"/>
+      <c r="L688" s="22"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
       <c r="A689" s="16"/>
       <c r="B689" s="16"/>
-      <c r="L689" s="21"/>
+      <c r="L689" s="22"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
       <c r="A690" s="16"/>
       <c r="B690" s="16"/>
-      <c r="L690" s="21"/>
+      <c r="L690" s="22"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
       <c r="A691" s="16"/>
       <c r="B691" s="16"/>
-      <c r="L691" s="21"/>
+      <c r="L691" s="22"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
       <c r="A692" s="16"/>
       <c r="B692" s="16"/>
-      <c r="L692" s="21"/>
+      <c r="L692" s="22"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
       <c r="A693" s="16"/>
       <c r="B693" s="16"/>
-      <c r="L693" s="21"/>
+      <c r="L693" s="22"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
       <c r="A694" s="16"/>
       <c r="B694" s="16"/>
-      <c r="L694" s="21"/>
+      <c r="L694" s="22"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
       <c r="A695" s="16"/>
       <c r="B695" s="16"/>
-      <c r="L695" s="21"/>
+      <c r="L695" s="22"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
       <c r="A696" s="16"/>
       <c r="B696" s="16"/>
-      <c r="L696" s="21"/>
+      <c r="L696" s="22"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
       <c r="A697" s="16"/>
       <c r="B697" s="16"/>
-      <c r="L697" s="21"/>
+      <c r="L697" s="22"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
       <c r="A698" s="16"/>
       <c r="B698" s="16"/>
-      <c r="L698" s="21"/>
+      <c r="L698" s="22"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
       <c r="A699" s="16"/>
       <c r="B699" s="16"/>
-      <c r="L699" s="21"/>
+      <c r="L699" s="22"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
       <c r="A700" s="16"/>
       <c r="B700" s="16"/>
-      <c r="L700" s="21"/>
+      <c r="L700" s="22"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
       <c r="A701" s="16"/>
       <c r="B701" s="16"/>
-      <c r="L701" s="21"/>
+      <c r="L701" s="22"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
       <c r="A702" s="16"/>
       <c r="B702" s="16"/>
-      <c r="L702" s="21"/>
+      <c r="L702" s="22"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
       <c r="A703" s="16"/>
       <c r="B703" s="16"/>
-      <c r="L703" s="21"/>
+      <c r="L703" s="22"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
       <c r="A704" s="16"/>
       <c r="B704" s="16"/>
-      <c r="L704" s="21"/>
+      <c r="L704" s="22"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
       <c r="A705" s="16"/>
       <c r="B705" s="16"/>
-      <c r="L705" s="21"/>
+      <c r="L705" s="22"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
       <c r="A706" s="16"/>
       <c r="B706" s="16"/>
-      <c r="L706" s="21"/>
+      <c r="L706" s="22"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
       <c r="A707" s="16"/>
       <c r="B707" s="16"/>
-      <c r="L707" s="21"/>
+      <c r="L707" s="22"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
       <c r="A708" s="16"/>
       <c r="B708" s="16"/>
-      <c r="L708" s="21"/>
+      <c r="L708" s="22"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
       <c r="A709" s="16"/>
       <c r="B709" s="16"/>
-      <c r="L709" s="21"/>
+      <c r="L709" s="22"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
       <c r="A710" s="16"/>
       <c r="B710" s="16"/>
-      <c r="L710" s="21"/>
+      <c r="L710" s="22"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
       <c r="A711" s="16"/>
       <c r="B711" s="16"/>
-      <c r="L711" s="21"/>
+      <c r="L711" s="22"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
       <c r="A712" s="16"/>
       <c r="B712" s="16"/>
-      <c r="L712" s="21"/>
+      <c r="L712" s="22"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
       <c r="A713" s="16"/>
       <c r="B713" s="16"/>
-      <c r="L713" s="21"/>
+      <c r="L713" s="22"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
       <c r="A714" s="16"/>
       <c r="B714" s="16"/>
-      <c r="L714" s="21"/>
+      <c r="L714" s="22"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
       <c r="A715" s="16"/>
       <c r="B715" s="16"/>
-      <c r="L715" s="21"/>
+      <c r="L715" s="22"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
       <c r="A716" s="16"/>
       <c r="B716" s="16"/>
-      <c r="L716" s="21"/>
+      <c r="L716" s="22"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
       <c r="A717" s="16"/>
       <c r="B717" s="16"/>
-      <c r="L717" s="21"/>
+      <c r="L717" s="22"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
       <c r="A718" s="16"/>
       <c r="B718" s="16"/>
-      <c r="L718" s="21"/>
+      <c r="L718" s="22"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
       <c r="A719" s="16"/>
       <c r="B719" s="16"/>
-      <c r="L719" s="21"/>
+      <c r="L719" s="22"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
       <c r="A720" s="16"/>
       <c r="B720" s="16"/>
-      <c r="L720" s="21"/>
+      <c r="L720" s="22"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
       <c r="A721" s="16"/>
       <c r="B721" s="16"/>
-      <c r="L721" s="21"/>
+      <c r="L721" s="22"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
       <c r="A722" s="16"/>
       <c r="B722" s="16"/>
-      <c r="L722" s="21"/>
+      <c r="L722" s="22"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
       <c r="A723" s="16"/>
       <c r="B723" s="16"/>
-      <c r="L723" s="21"/>
+      <c r="L723" s="22"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
       <c r="A724" s="16"/>
       <c r="B724" s="16"/>
-      <c r="L724" s="21"/>
+      <c r="L724" s="22"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
       <c r="A725" s="16"/>
       <c r="B725" s="16"/>
-      <c r="L725" s="21"/>
+      <c r="L725" s="22"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
       <c r="A726" s="16"/>
       <c r="B726" s="16"/>
-      <c r="L726" s="21"/>
+      <c r="L726" s="22"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
       <c r="A727" s="16"/>
       <c r="B727" s="16"/>
-      <c r="L727" s="21"/>
+      <c r="L727" s="22"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
       <c r="A728" s="16"/>
       <c r="B728" s="16"/>
-      <c r="L728" s="21"/>
+      <c r="L728" s="22"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
       <c r="A729" s="16"/>
       <c r="B729" s="16"/>
-      <c r="L729" s="21"/>
+      <c r="L729" s="22"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
       <c r="A730" s="16"/>
       <c r="B730" s="16"/>
-      <c r="L730" s="21"/>
+      <c r="L730" s="22"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
       <c r="A731" s="16"/>
       <c r="B731" s="16"/>
-      <c r="L731" s="21"/>
+      <c r="L731" s="22"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
       <c r="A732" s="16"/>
       <c r="B732" s="16"/>
-      <c r="L732" s="21"/>
+      <c r="L732" s="22"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
       <c r="A733" s="16"/>
       <c r="B733" s="16"/>
-      <c r="L733" s="21"/>
+      <c r="L733" s="22"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
       <c r="A734" s="16"/>
       <c r="B734" s="16"/>
-      <c r="L734" s="21"/>
+      <c r="L734" s="22"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
       <c r="A735" s="16"/>
       <c r="B735" s="16"/>
-      <c r="L735" s="21"/>
+      <c r="L735" s="22"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
       <c r="A736" s="16"/>
       <c r="B736" s="16"/>
-      <c r="L736" s="21"/>
+      <c r="L736" s="22"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
       <c r="A737" s="16"/>
       <c r="B737" s="16"/>
-      <c r="L737" s="21"/>
+      <c r="L737" s="22"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
       <c r="A738" s="16"/>
       <c r="B738" s="16"/>
-      <c r="L738" s="21"/>
+      <c r="L738" s="22"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
       <c r="A739" s="16"/>
       <c r="B739" s="16"/>
-      <c r="L739" s="21"/>
+      <c r="L739" s="22"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
       <c r="A740" s="16"/>
       <c r="B740" s="16"/>
-      <c r="L740" s="21"/>
+      <c r="L740" s="22"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
       <c r="A741" s="16"/>
       <c r="B741" s="16"/>
-      <c r="L741" s="21"/>
+      <c r="L741" s="22"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
       <c r="A742" s="16"/>
       <c r="B742" s="16"/>
-      <c r="L742" s="21"/>
+      <c r="L742" s="22"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
       <c r="A743" s="16"/>
       <c r="B743" s="16"/>
-      <c r="L743" s="21"/>
+      <c r="L743" s="22"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
       <c r="A744" s="16"/>
       <c r="B744" s="16"/>
-      <c r="L744" s="21"/>
+      <c r="L744" s="22"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
       <c r="A745" s="16"/>
       <c r="B745" s="16"/>
-      <c r="L745" s="21"/>
+      <c r="L745" s="22"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
       <c r="A746" s="16"/>
       <c r="B746" s="16"/>
-      <c r="L746" s="21"/>
+      <c r="L746" s="22"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
       <c r="A747" s="16"/>
       <c r="B747" s="16"/>
-      <c r="L747" s="21"/>
+      <c r="L747" s="22"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
       <c r="A748" s="16"/>
       <c r="B748" s="16"/>
-      <c r="L748" s="21"/>
+      <c r="L748" s="22"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
       <c r="A749" s="16"/>
       <c r="B749" s="16"/>
-      <c r="L749" s="21"/>
+      <c r="L749" s="22"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
       <c r="A750" s="16"/>
       <c r="B750" s="16"/>
-      <c r="L750" s="21"/>
+      <c r="L750" s="22"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
       <c r="A751" s="16"/>
       <c r="B751" s="16"/>
-      <c r="L751" s="21"/>
+      <c r="L751" s="22"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
       <c r="A752" s="16"/>
       <c r="B752" s="16"/>
-      <c r="L752" s="21"/>
+      <c r="L752" s="22"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
       <c r="A753" s="16"/>
       <c r="B753" s="16"/>
-      <c r="L753" s="21"/>
+      <c r="L753" s="22"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
       <c r="A754" s="16"/>
       <c r="B754" s="16"/>
-      <c r="L754" s="21"/>
+      <c r="L754" s="22"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
       <c r="A755" s="16"/>
       <c r="B755" s="16"/>
-      <c r="L755" s="21"/>
+      <c r="L755" s="22"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
       <c r="A756" s="16"/>
       <c r="B756" s="16"/>
-      <c r="L756" s="21"/>
+      <c r="L756" s="22"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
       <c r="A757" s="16"/>
       <c r="B757" s="16"/>
-      <c r="L757" s="21"/>
+      <c r="L757" s="22"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
       <c r="A758" s="16"/>
       <c r="B758" s="16"/>
-      <c r="L758" s="21"/>
+      <c r="L758" s="22"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
       <c r="A759" s="16"/>
       <c r="B759" s="16"/>
-      <c r="L759" s="21"/>
+      <c r="L759" s="22"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
       <c r="A760" s="16"/>
       <c r="B760" s="16"/>
-      <c r="L760" s="21"/>
+      <c r="L760" s="22"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
       <c r="A761" s="16"/>
       <c r="B761" s="16"/>
-      <c r="L761" s="21"/>
+      <c r="L761" s="22"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
       <c r="A762" s="16"/>
       <c r="B762" s="16"/>
-      <c r="L762" s="21"/>
+      <c r="L762" s="22"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
       <c r="A763" s="16"/>
       <c r="B763" s="16"/>
-      <c r="L763" s="21"/>
+      <c r="L763" s="22"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
       <c r="A764" s="16"/>
       <c r="B764" s="16"/>
-      <c r="L764" s="21"/>
+      <c r="L764" s="22"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
       <c r="A765" s="16"/>
       <c r="B765" s="16"/>
-      <c r="L765" s="21"/>
+      <c r="L765" s="22"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
       <c r="A766" s="16"/>
       <c r="B766" s="16"/>
-      <c r="L766" s="21"/>
+      <c r="L766" s="22"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
       <c r="A767" s="16"/>
       <c r="B767" s="16"/>
-      <c r="L767" s="21"/>
+      <c r="L767" s="22"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
       <c r="A768" s="16"/>
       <c r="B768" s="16"/>
-      <c r="L768" s="21"/>
+      <c r="L768" s="22"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
       <c r="A769" s="16"/>
       <c r="B769" s="16"/>
-      <c r="L769" s="21"/>
+      <c r="L769" s="22"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
       <c r="A770" s="16"/>
       <c r="B770" s="16"/>
-      <c r="L770" s="21"/>
+      <c r="L770" s="22"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
       <c r="A771" s="16"/>
       <c r="B771" s="16"/>
-      <c r="L771" s="21"/>
+      <c r="L771" s="22"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
       <c r="A772" s="16"/>
       <c r="B772" s="16"/>
-      <c r="L772" s="21"/>
+      <c r="L772" s="22"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
       <c r="A773" s="16"/>
       <c r="B773" s="16"/>
-      <c r="L773" s="21"/>
+      <c r="L773" s="22"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
       <c r="A774" s="16"/>
       <c r="B774" s="16"/>
-      <c r="L774" s="21"/>
+      <c r="L774" s="22"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
       <c r="A775" s="16"/>
       <c r="B775" s="16"/>
-      <c r="L775" s="21"/>
+      <c r="L775" s="22"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
       <c r="A776" s="16"/>
       <c r="B776" s="16"/>
-      <c r="L776" s="21"/>
+      <c r="L776" s="22"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
       <c r="A777" s="16"/>
       <c r="B777" s="16"/>
-      <c r="L777" s="21"/>
+      <c r="L777" s="22"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
       <c r="A778" s="16"/>
       <c r="B778" s="16"/>
-      <c r="L778" s="21"/>
+      <c r="L778" s="22"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
       <c r="A779" s="16"/>
       <c r="B779" s="16"/>
-      <c r="L779" s="21"/>
+      <c r="L779" s="22"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
       <c r="A780" s="16"/>
       <c r="B780" s="16"/>
-      <c r="L780" s="21"/>
+      <c r="L780" s="22"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
       <c r="A781" s="16"/>
       <c r="B781" s="16"/>
-      <c r="L781" s="21"/>
+      <c r="L781" s="22"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
       <c r="A782" s="16"/>
       <c r="B782" s="16"/>
-      <c r="L782" s="21"/>
+      <c r="L782" s="22"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
       <c r="A783" s="16"/>
       <c r="B783" s="16"/>
-      <c r="L783" s="21"/>
+      <c r="L783" s="22"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
       <c r="A784" s="16"/>
       <c r="B784" s="16"/>
-      <c r="L784" s="21"/>
+      <c r="L784" s="22"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
       <c r="A785" s="16"/>
       <c r="B785" s="16"/>
-      <c r="L785" s="21"/>
+      <c r="L785" s="22"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
       <c r="A786" s="16"/>
       <c r="B786" s="16"/>
-      <c r="L786" s="21"/>
+      <c r="L786" s="22"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
       <c r="A787" s="16"/>
       <c r="B787" s="16"/>
-      <c r="L787" s="21"/>
+      <c r="L787" s="22"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
       <c r="A788" s="16"/>
       <c r="B788" s="16"/>
-      <c r="L788" s="21"/>
+      <c r="L788" s="22"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
       <c r="A789" s="16"/>
       <c r="B789" s="16"/>
-      <c r="L789" s="21"/>
+      <c r="L789" s="22"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
       <c r="A790" s="16"/>
       <c r="B790" s="16"/>
-      <c r="L790" s="21"/>
+      <c r="L790" s="22"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
       <c r="A791" s="16"/>
       <c r="B791" s="16"/>
-      <c r="L791" s="21"/>
+      <c r="L791" s="22"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
       <c r="A792" s="16"/>
       <c r="B792" s="16"/>
-      <c r="L792" s="21"/>
+      <c r="L792" s="22"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
       <c r="A793" s="16"/>
       <c r="B793" s="16"/>
-      <c r="L793" s="21"/>
+      <c r="L793" s="22"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
       <c r="A794" s="16"/>
       <c r="B794" s="16"/>
-      <c r="L794" s="21"/>
+      <c r="L794" s="22"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
       <c r="A795" s="16"/>
       <c r="B795" s="16"/>
-      <c r="L795" s="21"/>
+      <c r="L795" s="22"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
       <c r="A796" s="16"/>
       <c r="B796" s="16"/>
-      <c r="L796" s="21"/>
+      <c r="L796" s="22"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
       <c r="A797" s="16"/>
       <c r="B797" s="16"/>
-      <c r="L797" s="21"/>
+      <c r="L797" s="22"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
       <c r="A798" s="16"/>
       <c r="B798" s="16"/>
-      <c r="L798" s="21"/>
+      <c r="L798" s="22"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
       <c r="A799" s="16"/>
       <c r="B799" s="16"/>
-      <c r="L799" s="21"/>
+      <c r="L799" s="22"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
       <c r="A800" s="16"/>
       <c r="B800" s="16"/>
-      <c r="L800" s="21"/>
+      <c r="L800" s="22"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
       <c r="A801" s="16"/>
       <c r="B801" s="16"/>
-      <c r="L801" s="21"/>
+      <c r="L801" s="22"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
       <c r="A802" s="16"/>
       <c r="B802" s="16"/>
-      <c r="L802" s="21"/>
+      <c r="L802" s="22"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
       <c r="A803" s="16"/>
       <c r="B803" s="16"/>
-      <c r="L803" s="21"/>
+      <c r="L803" s="22"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
       <c r="A804" s="16"/>
       <c r="B804" s="16"/>
-      <c r="L804" s="21"/>
+      <c r="L804" s="22"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
       <c r="A805" s="16"/>
       <c r="B805" s="16"/>
-      <c r="L805" s="21"/>
+      <c r="L805" s="22"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
       <c r="A806" s="16"/>
       <c r="B806" s="16"/>
-      <c r="L806" s="21"/>
+      <c r="L806" s="22"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
       <c r="A807" s="16"/>
       <c r="B807" s="16"/>
-      <c r="L807" s="21"/>
+      <c r="L807" s="22"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
       <c r="A808" s="16"/>
       <c r="B808" s="16"/>
-      <c r="L808" s="21"/>
+      <c r="L808" s="22"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
       <c r="A809" s="16"/>
       <c r="B809" s="16"/>
-      <c r="L809" s="21"/>
+      <c r="L809" s="22"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
       <c r="A810" s="16"/>
       <c r="B810" s="16"/>
-      <c r="L810" s="21"/>
+      <c r="L810" s="22"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
       <c r="A811" s="16"/>
       <c r="B811" s="16"/>
-      <c r="L811" s="21"/>
+      <c r="L811" s="22"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
       <c r="A812" s="16"/>
       <c r="B812" s="16"/>
-      <c r="L812" s="21"/>
+      <c r="L812" s="22"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
       <c r="A813" s="16"/>
       <c r="B813" s="16"/>
-      <c r="L813" s="21"/>
+      <c r="L813" s="22"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
       <c r="A814" s="16"/>
       <c r="B814" s="16"/>
-      <c r="L814" s="21"/>
+      <c r="L814" s="22"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
       <c r="A815" s="16"/>
       <c r="B815" s="16"/>
-      <c r="L815" s="21"/>
+      <c r="L815" s="22"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
       <c r="A816" s="16"/>
       <c r="B816" s="16"/>
-      <c r="L816" s="21"/>
+      <c r="L816" s="22"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
       <c r="A817" s="16"/>
       <c r="B817" s="16"/>
-      <c r="L817" s="21"/>
+      <c r="L817" s="22"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
       <c r="A818" s="16"/>
       <c r="B818" s="16"/>
-      <c r="L818" s="21"/>
+      <c r="L818" s="22"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
       <c r="A819" s="16"/>
       <c r="B819" s="16"/>
-      <c r="L819" s="21"/>
+      <c r="L819" s="22"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
       <c r="A820" s="16"/>
       <c r="B820" s="16"/>
-      <c r="L820" s="21"/>
+      <c r="L820" s="22"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
       <c r="A821" s="16"/>
       <c r="B821" s="16"/>
-      <c r="L821" s="21"/>
+      <c r="L821" s="22"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
       <c r="A822" s="16"/>
       <c r="B822" s="16"/>
-      <c r="L822" s="21"/>
+      <c r="L822" s="22"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
       <c r="A823" s="16"/>
       <c r="B823" s="16"/>
-      <c r="L823" s="21"/>
+      <c r="L823" s="22"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
       <c r="A824" s="16"/>
       <c r="B824" s="16"/>
-      <c r="L824" s="21"/>
+      <c r="L824" s="22"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
       <c r="A825" s="16"/>
       <c r="B825" s="16"/>
-      <c r="L825" s="21"/>
+      <c r="L825" s="22"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
       <c r="A826" s="16"/>
       <c r="B826" s="16"/>
-      <c r="L826" s="21"/>
+      <c r="L826" s="22"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
       <c r="A827" s="16"/>
       <c r="B827" s="16"/>
-      <c r="L827" s="21"/>
+      <c r="L827" s="22"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
       <c r="A828" s="16"/>
       <c r="B828" s="16"/>
-      <c r="L828" s="21"/>
+      <c r="L828" s="22"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
       <c r="A829" s="16"/>
       <c r="B829" s="16"/>
-      <c r="L829" s="21"/>
+      <c r="L829" s="22"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
       <c r="A830" s="16"/>
       <c r="B830" s="16"/>
-      <c r="L830" s="21"/>
+      <c r="L830" s="22"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
       <c r="A831" s="16"/>
       <c r="B831" s="16"/>
-      <c r="L831" s="21"/>
+      <c r="L831" s="22"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
       <c r="A832" s="16"/>
       <c r="B832" s="16"/>
-      <c r="L832" s="21"/>
+      <c r="L832" s="22"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
       <c r="A833" s="16"/>
       <c r="B833" s="16"/>
-      <c r="L833" s="21"/>
+      <c r="L833" s="22"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
       <c r="A834" s="16"/>
       <c r="B834" s="16"/>
-      <c r="L834" s="21"/>
+      <c r="L834" s="22"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
       <c r="A835" s="16"/>
       <c r="B835" s="16"/>
-      <c r="L835" s="21"/>
+      <c r="L835" s="22"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
       <c r="A836" s="16"/>
       <c r="B836" s="16"/>
-      <c r="L836" s="21"/>
+      <c r="L836" s="22"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
       <c r="A837" s="16"/>
       <c r="B837" s="16"/>
-      <c r="L837" s="21"/>
+      <c r="L837" s="22"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
       <c r="A838" s="16"/>
       <c r="B838" s="16"/>
-      <c r="L838" s="21"/>
+      <c r="L838" s="22"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
       <c r="A839" s="16"/>
       <c r="B839" s="16"/>
-      <c r="L839" s="21"/>
+      <c r="L839" s="22"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
       <c r="A840" s="16"/>
       <c r="B840" s="16"/>
-      <c r="L840" s="21"/>
+      <c r="L840" s="22"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
       <c r="A841" s="16"/>
       <c r="B841" s="16"/>
-      <c r="L841" s="21"/>
+      <c r="L841" s="22"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
       <c r="A842" s="16"/>
       <c r="B842" s="16"/>
-      <c r="L842" s="21"/>
+      <c r="L842" s="22"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
       <c r="A843" s="16"/>
       <c r="B843" s="16"/>
-      <c r="L843" s="21"/>
+      <c r="L843" s="22"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
       <c r="A844" s="16"/>
       <c r="B844" s="16"/>
-      <c r="L844" s="21"/>
+      <c r="L844" s="22"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
       <c r="A845" s="16"/>
       <c r="B845" s="16"/>
-      <c r="L845" s="21"/>
+      <c r="L845" s="22"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
       <c r="A846" s="16"/>
       <c r="B846" s="16"/>
-      <c r="L846" s="21"/>
+      <c r="L846" s="22"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
       <c r="A847" s="16"/>
       <c r="B847" s="16"/>
-      <c r="L847" s="21"/>
+      <c r="L847" s="22"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
       <c r="A848" s="16"/>
       <c r="B848" s="16"/>
-      <c r="L848" s="21"/>
+      <c r="L848" s="22"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
       <c r="A849" s="16"/>
       <c r="B849" s="16"/>
-      <c r="L849" s="21"/>
+      <c r="L849" s="22"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
       <c r="A850" s="16"/>
       <c r="B850" s="16"/>
-      <c r="L850" s="21"/>
+      <c r="L850" s="22"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
       <c r="A851" s="16"/>
       <c r="B851" s="16"/>
-      <c r="L851" s="21"/>
+      <c r="L851" s="22"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
       <c r="A852" s="16"/>
       <c r="B852" s="16"/>
-      <c r="L852" s="21"/>
+      <c r="L852" s="22"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
       <c r="A853" s="16"/>
       <c r="B853" s="16"/>
-      <c r="L853" s="21"/>
+      <c r="L853" s="22"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
       <c r="A854" s="16"/>
       <c r="B854" s="16"/>
-      <c r="L854" s="21"/>
+      <c r="L854" s="22"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
       <c r="A855" s="16"/>
       <c r="B855" s="16"/>
-      <c r="L855" s="21"/>
+      <c r="L855" s="22"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
       <c r="A856" s="16"/>
       <c r="B856" s="16"/>
-      <c r="L856" s="21"/>
+      <c r="L856" s="22"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
       <c r="A857" s="16"/>
       <c r="B857" s="16"/>
-      <c r="L857" s="21"/>
+      <c r="L857" s="22"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
       <c r="A858" s="16"/>
       <c r="B858" s="16"/>
-      <c r="L858" s="21"/>
+      <c r="L858" s="22"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
       <c r="A859" s="16"/>
       <c r="B859" s="16"/>
-      <c r="L859" s="21"/>
+      <c r="L859" s="22"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
       <c r="A860" s="16"/>
       <c r="B860" s="16"/>
-      <c r="L860" s="21"/>
+      <c r="L860" s="22"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
       <c r="A861" s="16"/>
       <c r="B861" s="16"/>
-      <c r="L861" s="21"/>
+      <c r="L861" s="22"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
       <c r="A862" s="16"/>
       <c r="B862" s="16"/>
-      <c r="L862" s="21"/>
+      <c r="L862" s="22"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
       <c r="A863" s="16"/>
       <c r="B863" s="16"/>
-      <c r="L863" s="21"/>
+      <c r="L863" s="22"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
       <c r="A864" s="16"/>
       <c r="B864" s="16"/>
-      <c r="L864" s="21"/>
+      <c r="L864" s="22"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
       <c r="A865" s="16"/>
       <c r="B865" s="16"/>
-      <c r="L865" s="21"/>
+      <c r="L865" s="22"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
       <c r="A866" s="16"/>
       <c r="B866" s="16"/>
-      <c r="L866" s="21"/>
+      <c r="L866" s="22"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
       <c r="A867" s="16"/>
       <c r="B867" s="16"/>
-      <c r="L867" s="21"/>
+      <c r="L867" s="22"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
       <c r="A868" s="16"/>
       <c r="B868" s="16"/>
-      <c r="L868" s="21"/>
+      <c r="L868" s="22"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
       <c r="A869" s="16"/>
       <c r="B869" s="16"/>
-      <c r="L869" s="21"/>
+      <c r="L869" s="22"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
       <c r="A870" s="16"/>
       <c r="B870" s="16"/>
-      <c r="L870" s="21"/>
+      <c r="L870" s="22"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
       <c r="A871" s="16"/>
       <c r="B871" s="16"/>
-      <c r="L871" s="21"/>
+      <c r="L871" s="22"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
       <c r="A872" s="16"/>
       <c r="B872" s="16"/>
-      <c r="L872" s="21"/>
+      <c r="L872" s="22"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
       <c r="A873" s="16"/>
       <c r="B873" s="16"/>
-      <c r="L873" s="21"/>
+      <c r="L873" s="22"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
       <c r="A874" s="16"/>
       <c r="B874" s="16"/>
-      <c r="L874" s="21"/>
+      <c r="L874" s="22"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
       <c r="A875" s="16"/>
       <c r="B875" s="16"/>
-      <c r="L875" s="21"/>
+      <c r="L875" s="22"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
       <c r="A876" s="16"/>
       <c r="B876" s="16"/>
-      <c r="L876" s="21"/>
+      <c r="L876" s="22"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
       <c r="A877" s="16"/>
       <c r="B877" s="16"/>
-      <c r="L877" s="21"/>
+      <c r="L877" s="22"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
       <c r="A878" s="16"/>
       <c r="B878" s="16"/>
-      <c r="L878" s="21"/>
+      <c r="L878" s="22"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
       <c r="A879" s="16"/>
       <c r="B879" s="16"/>
-      <c r="L879" s="21"/>
+      <c r="L879" s="22"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
       <c r="A880" s="16"/>
       <c r="B880" s="16"/>
-      <c r="L880" s="21"/>
+      <c r="L880" s="22"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
       <c r="A881" s="16"/>
       <c r="B881" s="16"/>
-      <c r="L881" s="21"/>
+      <c r="L881" s="22"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
       <c r="A882" s="16"/>
       <c r="B882" s="16"/>
-      <c r="L882" s="21"/>
+      <c r="L882" s="22"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
       <c r="A883" s="16"/>
       <c r="B883" s="16"/>
-      <c r="L883" s="21"/>
+      <c r="L883" s="22"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
       <c r="A884" s="16"/>
       <c r="B884" s="16"/>
-      <c r="L884" s="21"/>
+      <c r="L884" s="22"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
       <c r="A885" s="16"/>
       <c r="B885" s="16"/>
-      <c r="L885" s="21"/>
+      <c r="L885" s="22"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
       <c r="A886" s="16"/>
       <c r="B886" s="16"/>
-      <c r="L886" s="21"/>
+      <c r="L886" s="22"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
       <c r="A887" s="16"/>
       <c r="B887" s="16"/>
-      <c r="L887" s="21"/>
+      <c r="L887" s="22"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
       <c r="A888" s="16"/>
       <c r="B888" s="16"/>
-      <c r="L888" s="21"/>
+      <c r="L888" s="22"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
       <c r="A889" s="16"/>
       <c r="B889" s="16"/>
-      <c r="L889" s="21"/>
+      <c r="L889" s="22"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
       <c r="A890" s="16"/>
       <c r="B890" s="16"/>
-      <c r="L890" s="21"/>
+      <c r="L890" s="22"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
       <c r="A891" s="16"/>
       <c r="B891" s="16"/>
-      <c r="L891" s="21"/>
+      <c r="L891" s="22"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
       <c r="A892" s="16"/>
       <c r="B892" s="16"/>
-      <c r="L892" s="21"/>
+      <c r="L892" s="22"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
       <c r="A893" s="16"/>
       <c r="B893" s="16"/>
-      <c r="L893" s="21"/>
+      <c r="L893" s="22"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
       <c r="A894" s="16"/>
       <c r="B894" s="16"/>
-      <c r="L894" s="21"/>
+      <c r="L894" s="22"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
       <c r="A895" s="16"/>
       <c r="B895" s="16"/>
-      <c r="L895" s="21"/>
+      <c r="L895" s="22"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
       <c r="A896" s="16"/>
       <c r="B896" s="16"/>
-      <c r="L896" s="21"/>
+      <c r="L896" s="22"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
       <c r="A897" s="16"/>
       <c r="B897" s="16"/>
-      <c r="L897" s="21"/>
+      <c r="L897" s="22"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
       <c r="A898" s="16"/>
       <c r="B898" s="16"/>
-      <c r="L898" s="21"/>
+      <c r="L898" s="22"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
       <c r="A899" s="16"/>
       <c r="B899" s="16"/>
-      <c r="L899" s="21"/>
+      <c r="L899" s="22"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
       <c r="A900" s="16"/>
       <c r="B900" s="16"/>
-      <c r="L900" s="21"/>
+      <c r="L900" s="22"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
       <c r="A901" s="16"/>
       <c r="B901" s="16"/>
-      <c r="L901" s="21"/>
+      <c r="L901" s="22"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
       <c r="A902" s="16"/>
       <c r="B902" s="16"/>
-      <c r="L902" s="21"/>
+      <c r="L902" s="22"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
       <c r="A903" s="16"/>
       <c r="B903" s="16"/>
-      <c r="L903" s="21"/>
+      <c r="L903" s="22"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
       <c r="A904" s="16"/>
       <c r="B904" s="16"/>
-      <c r="L904" s="21"/>
+      <c r="L904" s="22"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
       <c r="A905" s="16"/>
       <c r="B905" s="16"/>
-      <c r="L905" s="21"/>
+      <c r="L905" s="22"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
       <c r="A906" s="16"/>
       <c r="B906" s="16"/>
-      <c r="L906" s="21"/>
+      <c r="L906" s="22"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
       <c r="A907" s="16"/>
       <c r="B907" s="16"/>
-      <c r="L907" s="21"/>
+      <c r="L907" s="22"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
       <c r="A908" s="16"/>
       <c r="B908" s="16"/>
-      <c r="L908" s="21"/>
+      <c r="L908" s="22"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
       <c r="A909" s="16"/>
       <c r="B909" s="16"/>
-      <c r="L909" s="21"/>
+      <c r="L909" s="22"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
       <c r="A910" s="16"/>
       <c r="B910" s="16"/>
-      <c r="L910" s="21"/>
+      <c r="L910" s="22"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
       <c r="A911" s="16"/>
       <c r="B911" s="16"/>
-      <c r="L911" s="21"/>
+      <c r="L911" s="22"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
       <c r="A912" s="16"/>
       <c r="B912" s="16"/>
-      <c r="L912" s="21"/>
+      <c r="L912" s="22"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
       <c r="A913" s="16"/>
       <c r="B913" s="16"/>
-      <c r="L913" s="21"/>
+      <c r="L913" s="22"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
       <c r="A914" s="16"/>
       <c r="B914" s="16"/>
-      <c r="L914" s="21"/>
+      <c r="L914" s="22"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
       <c r="A915" s="16"/>
       <c r="B915" s="16"/>
-      <c r="L915" s="21"/>
+      <c r="L915" s="22"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
       <c r="A916" s="16"/>
       <c r="B916" s="16"/>
-      <c r="L916" s="21"/>
+      <c r="L916" s="22"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
       <c r="A917" s="16"/>
       <c r="B917" s="16"/>
-      <c r="L917" s="21"/>
+      <c r="L917" s="22"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
       <c r="A918" s="16"/>
       <c r="B918" s="16"/>
-      <c r="L918" s="21"/>
+      <c r="L918" s="22"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
       <c r="A919" s="16"/>
       <c r="B919" s="16"/>
-      <c r="L919" s="21"/>
+      <c r="L919" s="22"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
       <c r="A920" s="16"/>
       <c r="B920" s="16"/>
-      <c r="L920" s="21"/>
+      <c r="L920" s="22"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
       <c r="A921" s="16"/>
       <c r="B921" s="16"/>
-      <c r="L921" s="21"/>
+      <c r="L921" s="22"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
       <c r="A922" s="16"/>
       <c r="B922" s="16"/>
-      <c r="L922" s="21"/>
+      <c r="L922" s="22"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
       <c r="A923" s="16"/>
       <c r="B923" s="16"/>
-      <c r="L923" s="21"/>
+      <c r="L923" s="22"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
       <c r="A924" s="16"/>
       <c r="B924" s="16"/>
-      <c r="L924" s="21"/>
+      <c r="L924" s="22"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
       <c r="A925" s="16"/>
       <c r="B925" s="16"/>
-      <c r="L925" s="21"/>
+      <c r="L925" s="22"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
       <c r="A926" s="16"/>
       <c r="B926" s="16"/>
-      <c r="L926" s="21"/>
+      <c r="L926" s="22"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
       <c r="A927" s="16"/>
       <c r="B927" s="16"/>
-      <c r="L927" s="21"/>
+      <c r="L927" s="22"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
       <c r="A928" s="16"/>
       <c r="B928" s="16"/>
-      <c r="L928" s="21"/>
+      <c r="L928" s="22"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
       <c r="A929" s="16"/>
       <c r="B929" s="16"/>
-      <c r="L929" s="21"/>
+      <c r="L929" s="22"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
       <c r="A930" s="16"/>
       <c r="B930" s="16"/>
-      <c r="L930" s="21"/>
+      <c r="L930" s="22"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
       <c r="A931" s="16"/>
       <c r="B931" s="16"/>
-      <c r="L931" s="21"/>
+      <c r="L931" s="22"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
       <c r="A932" s="16"/>
       <c r="B932" s="16"/>
-      <c r="L932" s="21"/>
+      <c r="L932" s="22"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
       <c r="A933" s="16"/>
       <c r="B933" s="16"/>
-      <c r="L933" s="21"/>
+      <c r="L933" s="22"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
       <c r="A934" s="16"/>
       <c r="B934" s="16"/>
-      <c r="L934" s="21"/>
+      <c r="L934" s="22"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
       <c r="A935" s="16"/>
       <c r="B935" s="16"/>
-      <c r="L935" s="21"/>
+      <c r="L935" s="22"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
       <c r="A936" s="16"/>
       <c r="B936" s="16"/>
-      <c r="L936" s="21"/>
+      <c r="L936" s="22"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
       <c r="A937" s="16"/>
       <c r="B937" s="16"/>
-      <c r="L937" s="21"/>
+      <c r="L937" s="22"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
       <c r="A938" s="16"/>
       <c r="B938" s="16"/>
-      <c r="L938" s="21"/>
+      <c r="L938" s="22"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
       <c r="A939" s="16"/>
       <c r="B939" s="16"/>
-      <c r="L939" s="21"/>
+      <c r="L939" s="22"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
       <c r="A940" s="16"/>
       <c r="B940" s="16"/>
-      <c r="L940" s="21"/>
+      <c r="L940" s="22"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
       <c r="A941" s="16"/>
       <c r="B941" s="16"/>
-      <c r="L941" s="21"/>
+      <c r="L941" s="22"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
       <c r="A942" s="16"/>
       <c r="B942" s="16"/>
-      <c r="L942" s="21"/>
+      <c r="L942" s="22"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
       <c r="A943" s="16"/>
       <c r="B943" s="16"/>
-      <c r="L943" s="21"/>
+      <c r="L943" s="22"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
       <c r="A944" s="16"/>
       <c r="B944" s="16"/>
-      <c r="L944" s="21"/>
+      <c r="L944" s="22"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
       <c r="A945" s="16"/>
       <c r="B945" s="16"/>
-      <c r="L945" s="21"/>
+      <c r="L945" s="22"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
       <c r="A946" s="16"/>
       <c r="B946" s="16"/>
-      <c r="L946" s="21"/>
+      <c r="L946" s="22"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
       <c r="A947" s="16"/>
       <c r="B947" s="16"/>
-      <c r="L947" s="21"/>
+      <c r="L947" s="22"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
       <c r="A948" s="16"/>
       <c r="B948" s="16"/>
-      <c r="L948" s="21"/>
+      <c r="L948" s="22"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
       <c r="A949" s="16"/>
       <c r="B949" s="16"/>
-      <c r="L949" s="21"/>
+      <c r="L949" s="22"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
       <c r="A950" s="16"/>
       <c r="B950" s="16"/>
-      <c r="L950" s="21"/>
+      <c r="L950" s="22"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
       <c r="A951" s="16"/>
       <c r="B951" s="16"/>
-      <c r="L951" s="21"/>
+      <c r="L951" s="22"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
       <c r="A952" s="16"/>
       <c r="B952" s="16"/>
-      <c r="L952" s="21"/>
+      <c r="L952" s="22"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
       <c r="A953" s="16"/>
       <c r="B953" s="16"/>
-      <c r="L953" s="21"/>
+      <c r="L953" s="22"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
       <c r="A954" s="16"/>
       <c r="B954" s="16"/>
-      <c r="L954" s="21"/>
+      <c r="L954" s="22"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
       <c r="A955" s="16"/>
       <c r="B955" s="16"/>
-      <c r="L955" s="21"/>
+      <c r="L955" s="22"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
       <c r="A956" s="16"/>
       <c r="B956" s="16"/>
-      <c r="L956" s="21"/>
+      <c r="L956" s="22"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
       <c r="A957" s="16"/>
       <c r="B957" s="16"/>
-      <c r="L957" s="21"/>
+      <c r="L957" s="22"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
       <c r="A958" s="16"/>
       <c r="B958" s="16"/>
-      <c r="L958" s="21"/>
+      <c r="L958" s="22"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
       <c r="A959" s="16"/>
       <c r="B959" s="16"/>
-      <c r="L959" s="21"/>
+      <c r="L959" s="22"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
       <c r="A960" s="16"/>
       <c r="B960" s="16"/>
-      <c r="L960" s="21"/>
+      <c r="L960" s="22"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
       <c r="A961" s="16"/>
       <c r="B961" s="16"/>
-      <c r="L961" s="21"/>
+      <c r="L961" s="22"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
       <c r="A962" s="16"/>
       <c r="B962" s="16"/>
-      <c r="L962" s="21"/>
+      <c r="L962" s="22"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
       <c r="A963" s="16"/>
       <c r="B963" s="16"/>
-      <c r="L963" s="21"/>
+      <c r="L963" s="22"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
       <c r="A964" s="16"/>
       <c r="B964" s="16"/>
-      <c r="L964" s="21"/>
+      <c r="L964" s="22"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
       <c r="A965" s="16"/>
       <c r="B965" s="16"/>
-      <c r="L965" s="21"/>
+      <c r="L965" s="22"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
       <c r="A966" s="16"/>
       <c r="B966" s="16"/>
-      <c r="L966" s="21"/>
+      <c r="L966" s="22"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
       <c r="A967" s="16"/>
       <c r="B967" s="16"/>
-      <c r="L967" s="21"/>
+      <c r="L967" s="22"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
       <c r="A968" s="16"/>
       <c r="B968" s="16"/>
-      <c r="L968" s="21"/>
+      <c r="L968" s="22"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
       <c r="A969" s="16"/>
       <c r="B969" s="16"/>
-      <c r="L969" s="21"/>
+      <c r="L969" s="22"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
       <c r="A970" s="16"/>
       <c r="B970" s="16"/>
-      <c r="L970" s="21"/>
+      <c r="L970" s="22"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
       <c r="A971" s="16"/>
       <c r="B971" s="16"/>
-      <c r="L971" s="21"/>
+      <c r="L971" s="22"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
       <c r="A972" s="16"/>
       <c r="B972" s="16"/>
-      <c r="L972" s="21"/>
+      <c r="L972" s="22"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
       <c r="A973" s="16"/>
       <c r="B973" s="16"/>
-      <c r="L973" s="21"/>
+      <c r="L973" s="22"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
       <c r="A974" s="16"/>
       <c r="B974" s="16"/>
-      <c r="L974" s="21"/>
+      <c r="L974" s="22"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
       <c r="A975" s="16"/>
       <c r="B975" s="16"/>
-      <c r="L975" s="21"/>
+      <c r="L975" s="22"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
       <c r="A976" s="16"/>
       <c r="B976" s="16"/>
-      <c r="L976" s="21"/>
+      <c r="L976" s="22"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
       <c r="A977" s="16"/>
       <c r="B977" s="16"/>
-      <c r="L977" s="21"/>
+      <c r="L977" s="22"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
       <c r="A978" s="16"/>
       <c r="B978" s="16"/>
-      <c r="L978" s="21"/>
+      <c r="L978" s="22"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
       <c r="A979" s="16"/>
       <c r="B979" s="16"/>
-      <c r="L979" s="21"/>
+      <c r="L979" s="22"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
       <c r="A980" s="16"/>
       <c r="B980" s="16"/>
-      <c r="L980" s="21"/>
+      <c r="L980" s="22"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
       <c r="A981" s="16"/>
       <c r="B981" s="16"/>
-      <c r="L981" s="21"/>
+      <c r="L981" s="22"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
       <c r="A982" s="16"/>
       <c r="B982" s="16"/>
-      <c r="L982" s="21"/>
+      <c r="L982" s="22"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
       <c r="A983" s="16"/>
       <c r="B983" s="16"/>
-      <c r="L983" s="21"/>
+      <c r="L983" s="22"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
       <c r="A984" s="16"/>
       <c r="B984" s="16"/>
-      <c r="L984" s="21"/>
+      <c r="L984" s="22"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
       <c r="A985" s="16"/>
       <c r="B985" s="16"/>
-      <c r="L985" s="21"/>
+      <c r="L985" s="22"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
       <c r="A986" s="16"/>
       <c r="B986" s="16"/>
-      <c r="L986" s="21"/>
+      <c r="L986" s="22"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
       <c r="A987" s="16"/>
       <c r="B987" s="16"/>
-      <c r="L987" s="21"/>
+      <c r="L987" s="22"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
       <c r="A988" s="16"/>
       <c r="B988" s="16"/>
-      <c r="L988" s="21"/>
+      <c r="L988" s="22"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
       <c r="A989" s="16"/>
       <c r="B989" s="16"/>
-      <c r="L989" s="21"/>
+      <c r="L989" s="22"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
       <c r="A990" s="16"/>
       <c r="B990" s="16"/>
-      <c r="L990" s="21"/>
+      <c r="L990" s="22"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
       <c r="A991" s="16"/>
       <c r="B991" s="16"/>
-      <c r="L991" s="21"/>
+      <c r="L991" s="22"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
       <c r="A992" s="16"/>
       <c r="B992" s="16"/>
-      <c r="L992" s="21"/>
+      <c r="L992" s="22"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
       <c r="A993" s="16"/>
       <c r="B993" s="16"/>
-      <c r="L993" s="21"/>
+      <c r="L993" s="22"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
       <c r="A994" s="16"/>
       <c r="B994" s="16"/>
-      <c r="L994" s="21"/>
+      <c r="L994" s="22"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
       <c r="A995" s="16"/>
       <c r="B995" s="16"/>
-      <c r="L995" s="21"/>
+      <c r="L995" s="22"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
       <c r="A996" s="16"/>
       <c r="B996" s="16"/>
-      <c r="L996" s="21"/>
+      <c r="L996" s="22"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
       <c r="A997" s="16"/>
       <c r="B997" s="16"/>
-      <c r="L997" s="21"/>
+      <c r="L997" s="22"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
       <c r="A998" s="16"/>
       <c r="B998" s="16"/>
-      <c r="L998" s="21"/>
+      <c r="L998" s="22"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
       <c r="A999" s="16"/>
       <c r="B999" s="16"/>
-      <c r="L999" s="21"/>
+      <c r="L999" s="22"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
       <c r="A1000" s="16"/>
       <c r="B1000" s="16"/>
-      <c r="L1000" s="21"/>
+      <c r="L1000" s="22"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
       <c r="A1001" s="16"/>
       <c r="B1001" s="16"/>
-      <c r="L1001" s="21"/>
+      <c r="L1001" s="22"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
       <c r="A1002" s="16"/>
       <c r="B1002" s="16"/>
-      <c r="L1002" s="21"/>
+      <c r="L1002" s="22"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
       <c r="A1003" s="16"/>
       <c r="B1003" s="16"/>
-      <c r="L1003" s="21"/>
+      <c r="L1003" s="22"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
       <c r="A1004" s="16"/>
       <c r="B1004" s="16"/>
-      <c r="L1004" s="21"/>
+      <c r="L1004" s="22"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
       <c r="A1005" s="16"/>
       <c r="B1005" s="16"/>
-      <c r="L1005" s="21"/>
+      <c r="L1005" s="22"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
       <c r="A1006" s="16"/>
       <c r="B1006" s="16"/>
-      <c r="L1006" s="21"/>
+      <c r="L1006" s="22"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
       <c r="A1007" s="16"/>
       <c r="B1007" s="16"/>
-      <c r="L1007" s="21"/>
+      <c r="L1007" s="22"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
       <c r="A1008" s="16"/>
       <c r="B1008" s="16"/>
-      <c r="L1008" s="21"/>
+      <c r="L1008" s="22"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
       <c r="A1009" s="16"/>
       <c r="B1009" s="16"/>
-      <c r="L1009" s="21"/>
+      <c r="L1009" s="22"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
       <c r="A1010" s="16"/>
       <c r="B1010" s="16"/>
-      <c r="L1010" s="21"/>
+      <c r="L1010" s="22"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
       <c r="A1011" s="16"/>
       <c r="B1011" s="16"/>
-      <c r="L1011" s="21"/>
+      <c r="L1011" s="22"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
       <c r="A1012" s="16"/>
       <c r="B1012" s="16"/>
-      <c r="L1012" s="21"/>
+      <c r="L1012" s="22"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
       <c r="A1013" s="16"/>
       <c r="B1013" s="16"/>
-      <c r="L1013" s="21"/>
+      <c r="L1013" s="22"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
       <c r="A1014" s="16"/>
       <c r="B1014" s="16"/>
-      <c r="L1014" s="21"/>
+      <c r="L1014" s="22"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
       <c r="A1015" s="16"/>
       <c r="B1015" s="16"/>
-      <c r="L1015" s="21"/>
+      <c r="L1015" s="22"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
       <c r="A1016" s="16"/>
       <c r="B1016" s="16"/>
-      <c r="L1016" s="21"/>
+      <c r="L1016" s="22"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
       <c r="A1017" s="16"/>
       <c r="B1017" s="16"/>
-      <c r="L1017" s="21"/>
+      <c r="L1017" s="22"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
       <c r="A1018" s="16"/>
       <c r="B1018" s="16"/>
-      <c r="L1018" s="21"/>
+      <c r="L1018" s="22"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
       <c r="A1019" s="16"/>
       <c r="B1019" s="16"/>
-      <c r="L1019" s="21"/>
+      <c r="L1019" s="22"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
       <c r="A1020" s="16"/>
       <c r="B1020" s="16"/>
-      <c r="L1020" s="21"/>
+      <c r="L1020" s="22"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
       <c r="A1021" s="16"/>
       <c r="B1021" s="16"/>
-      <c r="L1021" s="21"/>
+      <c r="L1021" s="22"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
       <c r="A1022" s="16"/>
       <c r="B1022" s="16"/>
-      <c r="L1022" s="21"/>
+      <c r="L1022" s="22"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
       <c r="A1023" s="16"/>
       <c r="B1023" s="16"/>
-      <c r="L1023" s="21"/>
+      <c r="L1023" s="22"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
       <c r="A1024" s="16"/>
       <c r="B1024" s="16"/>
-      <c r="L1024" s="21"/>
+      <c r="L1024" s="22"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
       <c r="A1025" s="16"/>
       <c r="B1025" s="16"/>
-      <c r="L1025" s="21"/>
+      <c r="L1025" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7886,10 +7886,10 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="AB2" s="2"/>
@@ -7901,40 +7901,40 @@
       <c r="AH2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="8">
         <v>2.5E32</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="9">
         <v>45686.0</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>12.0</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="10">
         <v>1000.0</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="10">
         <v>1000.0</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="11">
         <v>0.0</v>
       </c>
       <c r="AB3" s="2"/>
@@ -7946,40 +7946,40 @@
       <c r="AH3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="9">
         <v>45762.0</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>12.0</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="10">
         <v>52250.04</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="10">
         <v>52250.04</v>
       </c>
-      <c r="L4" s="15">
+      <c r="L4" s="11">
         <v>0.0</v>
       </c>
       <c r="AB4" s="2"/>
@@ -7991,40 +7991,40 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="A5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="9">
         <v>45762.0</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>12.0</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>881914.18</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="10">
         <v>881914.18</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="11">
         <v>0.0</v>
       </c>
       <c r="AB5" s="2"/>
@@ -8036,40 +8036,40 @@
       <c r="AH5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="A6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <v>45762.0</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>12.0</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>750000.0</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="10">
         <v>750000.0</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="11">
         <v>0.0</v>
       </c>
       <c r="AB6" s="2"/>
@@ -8081,40 +8081,40 @@
       <c r="AH6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="9">
         <v>45763.0</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>12.0</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="14">
+      <c r="I7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="10">
         <v>949835.78</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="10">
         <v>949835.78</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="11">
         <v>0.0</v>
       </c>
       <c r="AB7" s="2"/>
@@ -8126,43 +8126,43 @@
       <c r="AH7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="8" t="s">
+      <c r="A8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="9">
         <v>45763.0</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>12.0</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="14">
+      <c r="I8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="10">
         <v>524584.95</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="10">
         <v>524584.95</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="11">
         <v>0.0</v>
       </c>
-      <c r="O8" s="23"/>
+      <c r="O8" s="19"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8172,40 +8172,40 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="9">
         <v>45792.0</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>12.0</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="14">
+      <c r="I9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="10">
         <v>211614.23</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="10">
         <v>211614.23</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="11">
         <v>0.0</v>
       </c>
       <c r="AB9" s="2"/>
@@ -8217,40 +8217,40 @@
       <c r="AH9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <v>45825.0</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>12.0</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="10">
         <v>2391157.42</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="10">
         <v>2391157.41</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="10">
         <v>0.01</v>
       </c>
       <c r="AB10" s="2"/>
@@ -8262,40 +8262,40 @@
       <c r="AH10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="9">
         <v>45825.0</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>12.0</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="10">
         <v>618154.39</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="10">
         <v>618154.38</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="11">
         <v>0.01</v>
       </c>
       <c r="AB11" s="2"/>
@@ -8307,40 +8307,40 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="9">
+        <v>45832.0</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="7">
+        <v>12.0</v>
+      </c>
+      <c r="H12" s="7">
+        <v>339039.0</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="12">
-        <v>45832.0</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>339039.0</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="14">
+      <c r="J12" s="10">
         <v>1600334.09</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="10">
         <v>1600334.09</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="11">
         <v>0.0</v>
       </c>
       <c r="AB12" s="2"/>
@@ -8352,43 +8352,43 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="C13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="9">
         <v>45863.0</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>12.0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="10">
         <v>2364771.07</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="10">
         <v>1867169.54</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="10">
         <v>497601.53</v>
       </c>
-      <c r="M13" s="31"/>
+      <c r="M13" s="28"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8398,40 +8398,40 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="A14" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="9">
         <v>45887.0</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <v>12.0</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="14">
+      <c r="I14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="10">
         <v>968237.39</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="10">
         <v>968237.39</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="11">
         <v>0.0</v>
       </c>
       <c r="AB14" s="2"/>
@@ -8443,40 +8443,40 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="A15" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="9">
         <v>45924.0</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="7">
         <v>12.0</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J15" s="14">
+      <c r="I15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="10">
         <v>1011677.95</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="10">
         <v>1011677.95</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="11">
         <v>0.0</v>
       </c>
       <c r="AB15" s="2"/>
@@ -8488,40 +8488,40 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="C16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="9">
         <v>45929.0</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>12.0</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="10">
         <v>1580293.02</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="10">
         <v>1580293.02</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="10">
         <v>0.0</v>
       </c>
       <c r="AB16" s="2"/>
@@ -8533,40 +8533,40 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="A17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="9">
         <v>45930.0</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>12.0</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="10">
         <v>34065.36</v>
       </c>
-      <c r="K17" s="15">
+      <c r="K17" s="11">
         <v>0.0</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="10">
         <v>34065.36</v>
       </c>
       <c r="AB17" s="2"/>
@@ -8578,40 +8578,40 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="A18" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>12.0</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="14">
+      <c r="I18" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="10">
         <v>63746.85</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="10">
         <v>63746.85</v>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="11">
         <v>0.0</v>
       </c>
       <c r="AB18" s="2"/>
@@ -8623,40 +8623,40 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="A19" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>12.0</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="J19" s="14">
+      <c r="I19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="10">
         <v>947931.1</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="10">
         <v>947931.1</v>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="11">
         <v>0.0</v>
       </c>
       <c r="AB19" s="2"/>
@@ -8668,40 +8668,40 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="7">
         <v>12.0</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="10">
         <v>259790.57</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="10">
         <v>259790.57</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="11">
         <v>0.0</v>
       </c>
       <c r="AB20" s="2"/>
@@ -8713,40 +8713,40 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="7">
         <v>12.0</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="10">
         <v>170479.3</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="10">
         <v>170479.3</v>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="11">
         <v>0.0</v>
       </c>
       <c r="AB21" s="2"/>
@@ -8758,40 +8758,40 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="A22" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="39">
         <v>45953.0</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="7">
         <v>12.0</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="7">
         <v>2000.0</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="10">
         <v>1500000.0</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="10">
         <v>1500000.0</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="10">
         <v>0.0</v>
       </c>
       <c r="AB22" s="2"/>
@@ -8803,40 +8803,40 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="39">
+        <v>45953.0</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="7">
+        <v>12.0</v>
+      </c>
+      <c r="H23" s="7">
+        <v>339039.0</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="41">
-        <v>45953.0</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="H23" s="8">
-        <v>339039.0</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J23" s="14">
+      <c r="J23" s="10">
         <v>1000001.64</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="10">
         <v>1000001.64</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="11">
         <v>0.0</v>
       </c>
       <c r="AB23" s="2"/>
@@ -8848,40 +8848,40 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="A24" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="39">
         <v>45953.0</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="7">
         <v>12.0</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="10">
         <v>68405.66</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="10">
         <v>68405.66</v>
       </c>
-      <c r="L24" s="15">
+      <c r="L24" s="11">
         <v>0.0</v>
       </c>
       <c r="AB24" s="2"/>
@@ -8893,40 +8893,40 @@
       <c r="AH24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="A25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="39">
         <v>45975.0</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="7">
         <v>12.0</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" s="14">
+      <c r="I25" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="10">
         <v>1157673.06</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="10">
         <v>1157673.06</v>
       </c>
-      <c r="L25" s="15">
+      <c r="L25" s="11">
         <v>0.0</v>
       </c>
       <c r="AB25" s="2"/>
@@ -8938,40 +8938,40 @@
       <c r="AH25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="A26" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="39">
         <v>45989.0</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="7">
         <v>12.0</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="10">
         <v>34065.36</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="10">
         <v>34065.36</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="11">
         <v>0.0</v>
       </c>
       <c r="AB26" s="2"/>
@@ -8983,40 +8983,40 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="A27" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="9">
         <v>46104.0</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="7">
         <v>12.0</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="10">
         <v>1770880.5</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="11">
         <v>0.0</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="10">
         <v>1770880.5</v>
       </c>
       <c r="AB27" s="2"/>
@@ -9028,40 +9028,40 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="9">
         <v>46120.0</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="7">
         <v>12.0</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J28" s="14">
+      <c r="I28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="10">
         <v>1912292.52</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K28" s="11">
         <v>0.0</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="10">
         <v>1912292.52</v>
       </c>
       <c r="AB28" s="2"/>
@@ -9073,40 +9073,40 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="3">
         <v>46196.0</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>12.0</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>339039.0</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="5">
         <v>2048.0</v>
       </c>
-      <c r="J29" s="48">
+      <c r="J29" s="43">
         <v>1496713.48</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>0.0</v>
       </c>
-      <c r="L29" s="48">
+      <c r="L29" s="43">
         <v>1496713.48</v>
       </c>
       <c r="AB29" s="2"/>
@@ -9118,40 +9118,40 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="6" t="s">
+      <c r="A30" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="3">
         <v>46205.0</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>12.0</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>339039.0</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J30" s="48">
+      <c r="I30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="43">
         <v>624166.14</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>0.0</v>
       </c>
-      <c r="L30" s="48">
+      <c r="L30" s="43">
         <v>624166.14</v>
       </c>
       <c r="AB30" s="2"/>
@@ -9163,40 +9163,40 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="A31" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="3">
         <v>46205.0</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>12.0</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="5">
         <v>339039.0</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J31" s="48">
+      <c r="I31" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J31" s="43">
         <v>18462.36</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>0.0</v>
       </c>
-      <c r="L31" s="48">
+      <c r="L31" s="43">
         <v>18462.36</v>
       </c>
       <c r="AB31" s="2"/>
@@ -9208,40 +9208,40 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C32" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" s="6" t="s">
+      <c r="A32" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>46213.0</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>12.0</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="5">
         <v>339039.0</v>
       </c>
-      <c r="I32" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="J32" s="48">
+      <c r="I32" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J32" s="43">
         <v>1530656.62</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>0.0</v>
       </c>
-      <c r="L32" s="48">
+      <c r="L32" s="43">
         <v>1530656.62</v>
       </c>
       <c r="AB32" s="2"/>
@@ -9253,7 +9253,7 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="C33" s="48"/>
+      <c r="C33" s="43"/>
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -57,6 +57,15 @@
     <t>25E0385</t>
   </si>
   <si>
+    <t>2025NE000369</t>
+  </si>
+  <si>
+    <t>C25516</t>
+  </si>
+  <si>
+    <t>25E0387</t>
+  </si>
+  <si>
     <t>Número Contrato</t>
   </si>
   <si>
@@ -66,21 +75,18 @@
     <t>UG Responsável</t>
   </si>
   <si>
-    <t>2025NE000369</t>
+    <t>2025NE000371</t>
   </si>
   <si>
     <t>UG Fiscalizadora</t>
   </si>
   <si>
-    <t>C25516</t>
+    <t>25E0389</t>
   </si>
   <si>
     <t>Prazo Final de Execução</t>
   </si>
   <si>
-    <t>25E0387</t>
-  </si>
-  <si>
     <t>Prazo Final de Vigência</t>
   </si>
   <si>
@@ -111,9 +117,18 @@
     <t>Saldo (Valor a Faturar)</t>
   </si>
   <si>
+    <t>2025NE000413</t>
+  </si>
+  <si>
+    <t>C25501</t>
+  </si>
+  <si>
     <t>Fornecedor</t>
   </si>
   <si>
+    <t>25E0403</t>
+  </si>
+  <si>
     <t>Tipo Despesa /Receita</t>
   </si>
   <si>
@@ -123,10 +138,7 @@
     <t>Editar</t>
   </si>
   <si>
-    <t>2025NE000371</t>
-  </si>
-  <si>
-    <t>25E0389</t>
+    <t>20SP</t>
   </si>
   <si>
     <t>005/CELOG-PAMALS/2025</t>
@@ -135,9 +147,21 @@
     <t>CELOG</t>
   </si>
   <si>
+    <t>2025NE000414</t>
+  </si>
+  <si>
     <t>PAMALS</t>
   </si>
   <si>
+    <t>C25525</t>
+  </si>
+  <si>
+    <t>25E0431</t>
+  </si>
+  <si>
+    <t>21EM</t>
+  </si>
+  <si>
     <t>Vigente</t>
   </si>
   <si>
@@ -150,49 +174,58 @@
     <t>R$</t>
   </si>
   <si>
-    <t>2025NE000413</t>
-  </si>
-  <si>
-    <t>C25501</t>
-  </si>
-  <si>
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
-    <t>25E0403</t>
-  </si>
-  <si>
-    <t>20SP</t>
-  </si>
-  <si>
-    <t>2025NE000414</t>
-  </si>
-  <si>
-    <t>C25525</t>
-  </si>
-  <si>
-    <t>25E0431</t>
-  </si>
-  <si>
-    <t>21EM</t>
+    <t>2025NE000559</t>
+  </si>
+  <si>
+    <t>C25545</t>
+  </si>
+  <si>
+    <t>25E0524</t>
+  </si>
+  <si>
+    <t>20X7</t>
+  </si>
+  <si>
+    <t>2025NE000770</t>
+  </si>
+  <si>
+    <t>25E0731</t>
+  </si>
+  <si>
+    <t>2025NE000774</t>
+  </si>
+  <si>
+    <t>25E0737</t>
+  </si>
+  <si>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
+    <t>25E0787</t>
   </si>
   <si>
     <t>Módulo</t>
   </si>
   <si>
+    <t>219C</t>
+  </si>
+  <si>
     <t>Referência</t>
   </si>
   <si>
-    <t>2025NE000559</t>
-  </si>
-  <si>
-    <t>C25545</t>
+    <t>2025NE001065</t>
   </si>
   <si>
     <t>Nº recibo</t>
   </si>
   <si>
-    <t>25E0524</t>
+    <t>25E0999</t>
   </si>
   <si>
     <t>Nº</t>
@@ -207,166 +240,157 @@
     <t>Observações</t>
   </si>
   <si>
-    <t>20X7</t>
-  </si>
-  <si>
     <t>Vencimento</t>
   </si>
   <si>
     <t>Valor das Nfs</t>
   </si>
   <si>
+    <t>2025NE001200</t>
+  </si>
+  <si>
     <t>Ordem de Pagamento</t>
   </si>
   <si>
+    <t>C25590</t>
+  </si>
+  <si>
+    <t>25E1128</t>
+  </si>
+  <si>
     <t>Faturado</t>
   </si>
   <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>2025NE000770</t>
-  </si>
-  <si>
-    <t>25E0731</t>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
+  </si>
+  <si>
+    <t>2025NE001627</t>
   </si>
   <si>
     <t>FEV/25</t>
   </si>
   <si>
+    <t>25E1475</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>2025NE000774</t>
-  </si>
-  <si>
-    <t>25E0737</t>
+    <t>2025NE001629</t>
+  </si>
+  <si>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
   </si>
   <si>
     <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
-    <t>2025NE000843</t>
-  </si>
-  <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
+    <t>2025NE001687</t>
+  </si>
+  <si>
+    <t>25E1535</t>
   </si>
   <si>
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>219C</t>
-  </si>
-  <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
-  </si>
-  <si>
-    <t>2025NE001200</t>
-  </si>
-  <si>
-    <t>C25590</t>
-  </si>
-  <si>
-    <t>25E1128</t>
-  </si>
-  <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
+  </si>
+  <si>
+    <t>2025NE001689</t>
+  </si>
+  <si>
+    <t>25E1537</t>
   </si>
   <si>
     <t>MAR/25</t>
   </si>
   <si>
-    <t>25E1446</t>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
   </si>
   <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
   </si>
   <si>
-    <t>2025NE001627</t>
-  </si>
-  <si>
     <t>2025NP001979</t>
   </si>
   <si>
-    <t>25E1475</t>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
   </si>
   <si>
     <t>ABR/25</t>
   </si>
   <si>
-    <t>2025NE001629</t>
-  </si>
-  <si>
-    <t>C25820</t>
-  </si>
-  <si>
-    <t>25E1477</t>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
   </si>
   <si>
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>2025NE001687</t>
-  </si>
-  <si>
-    <t>25E1535</t>
-  </si>
-  <si>
     <t>2025NP002341</t>
   </si>
   <si>
-    <t>2025NE001688</t>
-  </si>
-  <si>
-    <t>25E1536</t>
+    <t>20YJ</t>
+  </si>
+  <si>
+    <t>2025NE001830</t>
   </si>
   <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>2025NE001689</t>
-  </si>
-  <si>
-    <t>25E1537</t>
-  </si>
-  <si>
-    <t>2025NE001690</t>
+    <t>25E1669</t>
+  </si>
+  <si>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
   </si>
   <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>25E1538</t>
-  </si>
-  <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
   </si>
   <si>
     <t>JUN/25</t>
-  </si>
-  <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -375,34 +399,43 @@
 2025NE000774</t>
   </si>
   <si>
-    <t>20YJ</t>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
   </si>
   <si>
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
-  </si>
-  <si>
     <t>JUL/25</t>
   </si>
   <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
   </si>
   <si>
     <t>AGO/25</t>
@@ -411,10 +444,13 @@
     <t>2025NP004558</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
   </si>
   <si>
     <t>SET/25</t>
@@ -424,63 +460,42 @@
 2025NE001828</t>
   </si>
   <si>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
     <t>2025NP004897</t>
   </si>
   <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
+    <t>26E0777</t>
   </si>
   <si>
     <t>OUT/25</t>
   </si>
   <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
+    <t>26E0803</t>
+  </si>
+  <si>
     <t>2025NP004932</t>
   </si>
   <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
     <t>NOV/25</t>
   </si>
   <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
     <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
   </si>
   <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
     <t>2026NP400440</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
     <t>DEZ/25</t>
   </si>
   <si>
@@ -490,22 +505,7 @@
     <t>2026NP400412</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
     <t>JAN/26</t>
-  </si>
-  <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
   </si>
   <si>
     <t>2026NP401035</t>
@@ -656,8 +656,8 @@
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="MM/DD/YY"/>
-    <numFmt numFmtId="170" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
     <numFmt numFmtId="171" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12">
@@ -692,15 +692,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -901,26 +901,26 @@
     <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -928,6 +928,7 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -952,18 +953,20 @@
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -975,22 +978,19 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1442,61 +1442,61 @@
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
       <c r="C4" s="17" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="V4" s="3"/>
     </row>
@@ -1505,16 +1505,16 @@
       <c r="B5" s="16"/>
       <c r="C5" s="19"/>
       <c r="D5" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1523,16 +1523,16 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="N5" s="13">
         <v>9.165159737E7</v>
@@ -1550,846 +1550,846 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="V5" s="3"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="22"/>
       <c r="V6" s="3"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="26"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="27"/>
       <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
       <c r="C8" s="28" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I8" s="29" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="30" t="s">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>73</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="O8" s="28"/>
-      <c r="P8" s="26"/>
+      <c r="P8" s="27"/>
       <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="31">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="32">
         <v>1.0</v>
       </c>
-      <c r="D9" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="34">
+      <c r="D9" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="35">
         <v>594.0</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="36">
         <v>45740.0</v>
       </c>
-      <c r="H9" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35">
+      <c r="H9" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36">
         <v>45778.0</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="37">
         <v>748504.24</v>
       </c>
-      <c r="L9" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" s="37">
+      <c r="L9" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="M9" s="38">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
       <c r="N9" s="39"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="26"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="27"/>
       <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <v>620.0</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="36">
         <v>45775.0</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35">
+      <c r="H10" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36">
         <v>45806.0</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="37">
         <v>1110378.24</v>
       </c>
-      <c r="L10" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="M10" s="37">
+      <c r="L10" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="M10" s="38">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
-      <c r="N10" s="41"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="26"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="27"/>
       <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="D11" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="35">
         <v>634.0</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <v>45799.0</v>
       </c>
-      <c r="H11" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="35">
+      <c r="H11" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36">
         <v>45844.0</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="37">
         <v>974557.12</v>
       </c>
-      <c r="L11" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="M11" s="37">
+      <c r="L11" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="M11" s="38">
         <v>974557.12</v>
       </c>
-      <c r="N11" s="41"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="26"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="27"/>
       <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="33">
+      <c r="D12" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="34">
         <v>660.0</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="43">
         <v>45856.0</v>
       </c>
-      <c r="H12" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35">
+      <c r="H12" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36">
         <v>45891.0</v>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="45">
         <v>1402001.34</v>
       </c>
-      <c r="L12" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="M12" s="37">
+      <c r="L12" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="M12" s="38">
         <v>1402001.34</v>
       </c>
-      <c r="N12" s="46"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="26"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="27"/>
       <c r="V12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
       <c r="C13" s="40"/>
       <c r="D13" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="34">
+        <v>120</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="35">
         <v>661.0</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <v>45856.0</v>
       </c>
-      <c r="H13" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42">
+      <c r="H13" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43">
         <v>45891.0</v>
       </c>
-      <c r="K13" s="44">
+      <c r="K13" s="45">
         <v>1223702.3</v>
       </c>
-      <c r="L13" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="M13" s="37">
+      <c r="L13" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="M13" s="38">
         <v>1223702.3</v>
       </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="24"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="25"/>
       <c r="P13" s="49"/>
       <c r="V13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
       <c r="C14" s="40"/>
       <c r="D14" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="33">
+        <v>126</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="34">
         <v>688.0</v>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="36">
         <v>45901.0</v>
       </c>
-      <c r="H14" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42">
+      <c r="H14" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K14" s="44">
+      <c r="K14" s="45">
         <v>1011677.95</v>
       </c>
-      <c r="L14" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="M14" s="37">
+      <c r="L14" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="M14" s="38">
         <v>1011677.95</v>
       </c>
-      <c r="N14" s="41"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="26"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="27"/>
       <c r="V14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="40"/>
       <c r="D15" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="33">
+        <v>135</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="34">
         <v>696.0</v>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="36">
         <v>45923.0</v>
       </c>
-      <c r="H15" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42">
+      <c r="H15" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K15" s="44">
+      <c r="K15" s="45">
         <v>896744.06</v>
       </c>
-      <c r="L15" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="M15" s="37">
+      <c r="L15" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="M15" s="38">
         <v>896744.06</v>
       </c>
-      <c r="N15" s="46"/>
-      <c r="O15" s="24"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="25"/>
       <c r="V15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="40"/>
       <c r="D16" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="33">
+        <v>140</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" s="34">
         <v>704.0</v>
       </c>
-      <c r="G16" s="35">
+      <c r="G16" s="36">
         <v>45957.0</v>
       </c>
-      <c r="H16" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42">
+      <c r="H16" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43">
         <v>46003.0</v>
       </c>
-      <c r="K16" s="44">
+      <c r="K16" s="45">
         <v>919329.06</v>
       </c>
-      <c r="L16" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="M16" s="37">
+      <c r="L16" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="M16" s="38">
         <v>919329.06</v>
       </c>
-      <c r="N16" s="41"/>
-      <c r="O16" s="24"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="25"/>
       <c r="V16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="40"/>
       <c r="D17" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33">
+        <v>146</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34">
         <v>705.0</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="43">
         <v>45972.0</v>
       </c>
-      <c r="H17" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="42">
+      <c r="H17" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="I17" s="34"/>
+      <c r="J17" s="43">
         <v>46016.0</v>
       </c>
-      <c r="K17" s="44">
+      <c r="K17" s="45">
         <v>1157009.26</v>
       </c>
-      <c r="L17" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="M17" s="37">
+      <c r="L17" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="M17" s="38">
         <v>1157009.26</v>
       </c>
-      <c r="N17" s="50"/>
-      <c r="O17" s="24"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="25"/>
       <c r="V17" s="3"/>
     </row>
     <row r="18">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="40"/>
       <c r="D18" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="33">
+        <v>151</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="34">
         <v>728.0</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="43">
         <v>46008.0</v>
       </c>
-      <c r="H18" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="42">
+      <c r="H18" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="43">
         <v>46040.0</v>
       </c>
-      <c r="K18" s="44">
+      <c r="K18" s="45">
         <v>1214597.952</v>
       </c>
-      <c r="L18" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="M18" s="37">
+      <c r="L18" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="M18" s="38">
         <v>1214597.952</v>
       </c>
-      <c r="N18" s="50"/>
-      <c r="O18" s="24"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="25"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
       <c r="V18" s="52"/>
     </row>
     <row r="19">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="40"/>
       <c r="D19" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="33">
+        <v>154</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="34">
         <v>278.0</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="43">
         <v>46042.0</v>
       </c>
-      <c r="H19" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42">
+      <c r="H19" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43">
         <v>46074.0</v>
       </c>
-      <c r="K19" s="44">
+      <c r="K19" s="45">
         <v>967082.09</v>
       </c>
-      <c r="L19" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="M19" s="37">
+      <c r="L19" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="M19" s="38">
         <v>967082.09</v>
       </c>
-      <c r="N19" s="50"/>
-      <c r="O19" s="24"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="25"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
       <c r="V19" s="52"/>
     </row>
     <row r="20">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
       <c r="C20" s="40"/>
       <c r="D20" s="48" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33">
+        <v>157</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34">
         <v>10.0</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="43">
         <v>46078.0</v>
       </c>
-      <c r="H20" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42">
+      <c r="H20" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43">
         <v>46106.0</v>
       </c>
-      <c r="K20" s="44">
+      <c r="K20" s="45">
         <v>719561.08</v>
       </c>
-      <c r="L20" s="33" t="s">
+      <c r="L20" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="M20" s="37">
+      <c r="M20" s="38">
         <v>719561.08</v>
       </c>
-      <c r="N20" s="50"/>
-      <c r="O20" s="24"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="25"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
       <c r="V20" s="52"/>
     </row>
     <row r="21">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="40"/>
       <c r="D21" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33">
+      <c r="E21" s="34"/>
+      <c r="F21" s="34">
         <v>15.0</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="43">
         <v>46094.0</v>
       </c>
-      <c r="H21" s="33" t="s">
+      <c r="H21" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42">
+      <c r="I21" s="43"/>
+      <c r="J21" s="43">
         <v>46128.0</v>
       </c>
-      <c r="K21" s="44">
+      <c r="K21" s="45">
         <v>885881.08</v>
       </c>
-      <c r="L21" s="33" t="s">
+      <c r="L21" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="38">
         <v>885881.08</v>
       </c>
-      <c r="N21" s="50"/>
-      <c r="O21" s="24"/>
-      <c r="R21" s="26"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="25"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
       <c r="V21" s="52"/>
     </row>
     <row r="22">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
       <c r="C22" s="40"/>
       <c r="D22" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33">
+      <c r="E22" s="34"/>
+      <c r="F22" s="34">
         <v>28.0</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="43">
         <v>46128.0</v>
       </c>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42">
+      <c r="I22" s="43"/>
+      <c r="J22" s="43">
         <v>46164.0</v>
       </c>
-      <c r="K22" s="44" t="s">
+      <c r="K22" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="L22" s="33" t="s">
+      <c r="L22" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="M22" s="37" t="s">
+      <c r="M22" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="N22" s="50"/>
-      <c r="O22" s="24"/>
-      <c r="R22" s="26"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="25"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
       <c r="V22" s="52"/>
     </row>
     <row r="23">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
       <c r="C23" s="40"/>
       <c r="D23" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33">
+      <c r="E23" s="34"/>
+      <c r="F23" s="34">
         <v>33.0</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="43">
         <v>46156.0</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42">
+      <c r="I23" s="43"/>
+      <c r="J23" s="43">
         <v>46191.0</v>
       </c>
-      <c r="K23" s="44">
+      <c r="K23" s="45">
         <v>1108954.4358333333</v>
       </c>
-      <c r="L23" s="33" t="s">
+      <c r="L23" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="M23" s="37">
+      <c r="M23" s="38">
         <v>1108954.4358333333</v>
       </c>
       <c r="N23" s="53"/>
-      <c r="O23" s="24"/>
-      <c r="R23" s="26"/>
-      <c r="S23" s="26"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="26"/>
+      <c r="O23" s="25"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
       <c r="V23" s="52"/>
     </row>
     <row r="24">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
       <c r="C24" s="40"/>
       <c r="D24" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33">
+      <c r="E24" s="34"/>
+      <c r="F24" s="34">
         <v>29.0</v>
       </c>
-      <c r="G24" s="42">
+      <c r="G24" s="43">
         <v>46149.0</v>
       </c>
-      <c r="H24" s="33" t="s">
+      <c r="H24" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42">
+      <c r="I24" s="43"/>
+      <c r="J24" s="43">
         <v>46185.0</v>
       </c>
-      <c r="K24" s="44">
+      <c r="K24" s="45">
         <v>218206.1</v>
       </c>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="M24" s="37">
+      <c r="M24" s="38">
         <v>218206.1</v>
       </c>
       <c r="N24" s="54"/>
-      <c r="O24" s="24"/>
-      <c r="R24" s="26"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
+      <c r="O24" s="25"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
       <c r="V24" s="52"/>
     </row>
     <row r="25">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="40"/>
       <c r="D25" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="E25" s="33"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="55">
         <v>40.0</v>
       </c>
-      <c r="G25" s="42">
+      <c r="G25" s="43">
         <v>46156.0</v>
       </c>
       <c r="H25" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="42"/>
+      <c r="I25" s="43"/>
       <c r="J25" s="56">
         <v>46191.0</v>
       </c>
-      <c r="K25" s="44">
+      <c r="K25" s="45">
         <v>1549250.84</v>
       </c>
-      <c r="L25" s="33" t="s">
+      <c r="L25" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="38">
         <v>1549250.84</v>
       </c>
       <c r="N25" s="53"/>
-      <c r="O25" s="24"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
+      <c r="O25" s="25"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
       <c r="V25" s="52"/>
     </row>
     <row r="26">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="57"/>
       <c r="D26" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="33"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="55"/>
-      <c r="G26" s="42"/>
+      <c r="G26" s="43"/>
       <c r="H26" s="55"/>
-      <c r="I26" s="42"/>
+      <c r="I26" s="43"/>
       <c r="J26" s="56"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="M26" s="37" t="s">
+      <c r="K26" s="45"/>
+      <c r="L26" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="M26" s="38" t="s">
         <v>173</v>
       </c>
       <c r="N26" s="53"/>
-      <c r="O26" s="24"/>
-      <c r="R26" s="26"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
+      <c r="O26" s="25"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="28" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="G27" s="28"/>
       <c r="H27" s="28" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
       <c r="K27" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" s="30" t="s">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>73</v>
       </c>
       <c r="M27" s="59" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="N27" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="O27" s="24"/>
-      <c r="P27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26"/>
+        <v>77</v>
+      </c>
+      <c r="O27" s="25"/>
+      <c r="P27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
       <c r="V27" s="52"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="26"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="31">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="32">
         <v>2.0</v>
       </c>
       <c r="D28" s="60" t="s">
         <v>174</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34">
+      <c r="E28" s="35"/>
+      <c r="F28" s="35">
         <v>402.0</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="36">
         <v>45791.0</v>
       </c>
-      <c r="H28" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35">
+      <c r="H28" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36">
         <v>45834.0</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="37">
         <v>188246.17</v>
       </c>
-      <c r="L28" s="33" t="s">
+      <c r="L28" s="34" t="s">
         <v>175</v>
       </c>
       <c r="M28" s="61">
         <v>188246.17</v>
       </c>
-      <c r="N28" s="50"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
       <c r="V28" s="52"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="26"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="26"/>
-      <c r="AC28" s="26"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
     </row>
     <row r="29">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
       <c r="C29" s="40"/>
       <c r="D29" s="60" t="s">
         <v>176</v>
@@ -2397,48 +2397,48 @@
       <c r="E29" s="55">
         <v>46.0</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="35">
         <v>447.0</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="36">
         <v>45814.0</v>
       </c>
-      <c r="H29" s="33" t="s">
+      <c r="H29" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42">
+      <c r="I29" s="43"/>
+      <c r="J29" s="43">
         <v>45955.0</v>
       </c>
-      <c r="K29" s="36">
+      <c r="K29" s="37">
         <v>112720.77</v>
       </c>
-      <c r="L29" s="33" t="s">
+      <c r="L29" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="38">
         <v>112720.77</v>
       </c>
-      <c r="N29" s="50"/>
-      <c r="O29" s="24"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
       <c r="V29" s="52"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="26"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
       <c r="C30" s="40"/>
       <c r="D30" s="62" t="s">
         <v>179</v>
@@ -2446,48 +2446,48 @@
       <c r="E30" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <v>529.0</v>
       </c>
       <c r="G30" s="64">
         <v>45853.0</v>
       </c>
-      <c r="H30" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42">
+      <c r="H30" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43">
         <v>45939.0</v>
       </c>
-      <c r="K30" s="44">
+      <c r="K30" s="45">
         <v>378307.61</v>
       </c>
-      <c r="L30" s="33" t="s">
+      <c r="L30" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="38">
         <v>378307.61</v>
       </c>
-      <c r="N30" s="50"/>
-      <c r="O30" s="24"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
       <c r="V30" s="52"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="26"/>
-      <c r="Y30" s="26"/>
-      <c r="Z30" s="26"/>
-      <c r="AA30" s="26"/>
-      <c r="AB30" s="26"/>
-      <c r="AC30" s="26"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="27"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="27"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
-      <c r="A31" s="22"/>
-      <c r="B31" s="22"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
       <c r="C31" s="40"/>
       <c r="D31" s="62" t="s">
         <v>182</v>
@@ -2495,48 +2495,48 @@
       <c r="E31" s="63" t="s">
         <v>180</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>691.0</v>
       </c>
       <c r="G31" s="64">
         <v>45910.0</v>
       </c>
-      <c r="H31" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42">
+      <c r="H31" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43">
         <v>45941.0</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>3315.0471000000252</v>
       </c>
-      <c r="L31" s="33" t="s">
+      <c r="L31" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="38">
         <v>3315.04710000003</v>
       </c>
-      <c r="N31" s="50"/>
-      <c r="O31" s="24"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
       <c r="V31" s="52"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="26"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="27"/>
+      <c r="AB31" s="27"/>
+      <c r="AC31" s="27"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
       <c r="C32" s="40"/>
       <c r="D32" s="62" t="s">
         <v>184</v>
@@ -2544,48 +2544,48 @@
       <c r="E32" s="65">
         <v>135.0</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="34">
         <v>677.0</v>
       </c>
       <c r="G32" s="64">
         <v>45904.0</v>
       </c>
-      <c r="H32" s="33" t="s">
-        <v>72</v>
+      <c r="H32" s="34" t="s">
+        <v>57</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K32" s="44">
+      <c r="K32" s="45">
         <v>198332.75</v>
       </c>
-      <c r="L32" s="33" t="s">
+      <c r="L32" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="M32" s="37">
+      <c r="M32" s="38">
         <v>198332.75</v>
       </c>
-      <c r="N32" s="50"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
       <c r="V32" s="52"/>
-      <c r="W32" s="26"/>
-      <c r="X32" s="26"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="26"/>
-      <c r="AC32" s="26"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="27"/>
+      <c r="AB32" s="27"/>
+      <c r="AC32" s="27"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
       <c r="C33" s="40"/>
       <c r="D33" s="62" t="s">
         <v>186</v>
@@ -2593,20 +2593,20 @@
       <c r="E33" s="65">
         <v>40.0</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>278.0</v>
       </c>
       <c r="G33" s="64">
         <v>46008.0</v>
       </c>
-      <c r="H33" s="33" t="s">
-        <v>121</v>
+      <c r="H33" s="34" t="s">
+        <v>114</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
         <v>46066.0</v>
       </c>
-      <c r="K33" s="44">
+      <c r="K33" s="45">
         <v>1528.62</v>
       </c>
       <c r="L33" s="67" t="s">
@@ -2615,26 +2615,26 @@
       <c r="M33" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="N33" s="50"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="26"/>
-      <c r="R33" s="26"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="27"/>
       <c r="V33" s="52"/>
-      <c r="W33" s="26"/>
-      <c r="X33" s="26"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
-      <c r="AA33" s="26"/>
-      <c r="AB33" s="26"/>
-      <c r="AC33" s="26"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27"/>
+      <c r="Y33" s="27"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="27"/>
+      <c r="AB33" s="27"/>
+      <c r="AC33" s="27"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
       <c r="C34" s="40"/>
       <c r="D34" s="62" t="s">
         <v>189</v>
@@ -2642,48 +2642,48 @@
       <c r="E34" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>748.0</v>
       </c>
       <c r="G34" s="64">
         <v>45930.0</v>
       </c>
-      <c r="H34" s="33" t="s">
-        <v>95</v>
+      <c r="H34" s="34" t="s">
+        <v>89</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K34" s="44">
+      <c r="K34" s="45">
         <v>38718.58</v>
       </c>
-      <c r="L34" s="33" t="s">
+      <c r="L34" s="34" t="s">
         <v>191</v>
       </c>
       <c r="M34" s="61" t="s">
         <v>192</v>
       </c>
-      <c r="N34" s="50"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="26"/>
-      <c r="R34" s="26"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="26"/>
-      <c r="U34" s="26"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="50"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="27"/>
       <c r="V34" s="52"/>
-      <c r="W34" s="26"/>
-      <c r="X34" s="26"/>
-      <c r="Y34" s="26"/>
-      <c r="Z34" s="26"/>
-      <c r="AA34" s="26"/>
-      <c r="AB34" s="26"/>
-      <c r="AC34" s="26"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="27"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="27"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="22"/>
-      <c r="B35" s="22"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
       <c r="C35" s="40"/>
       <c r="D35" s="62" t="s">
         <v>193</v>
@@ -2691,48 +2691,48 @@
       <c r="E35" s="65">
         <v>154.0</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>822.0</v>
       </c>
       <c r="G35" s="64">
         <v>45968.0</v>
       </c>
-      <c r="H35" s="33" t="s">
-        <v>110</v>
+      <c r="H35" s="34" t="s">
+        <v>105</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K35" s="44">
+      <c r="K35" s="45">
         <v>133124.11</v>
       </c>
-      <c r="L35" s="33" t="s">
+      <c r="L35" s="34" t="s">
         <v>194</v>
       </c>
       <c r="M35" s="61" t="s">
         <v>195</v>
       </c>
-      <c r="N35" s="50"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="26"/>
-      <c r="R35" s="26"/>
-      <c r="S35" s="26"/>
-      <c r="T35" s="26"/>
-      <c r="U35" s="26"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="27"/>
       <c r="V35" s="52"/>
-      <c r="W35" s="26"/>
-      <c r="X35" s="26"/>
-      <c r="Y35" s="26"/>
-      <c r="Z35" s="26"/>
-      <c r="AA35" s="26"/>
-      <c r="AB35" s="26"/>
-      <c r="AC35" s="26"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="27"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="27"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
       <c r="C36" s="40"/>
       <c r="D36" s="62" t="s">
         <v>196</v>
@@ -2747,41 +2747,41 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
         <v>46075.0</v>
       </c>
-      <c r="K36" s="44">
+      <c r="K36" s="45">
         <v>11372.9</v>
       </c>
-      <c r="L36" s="33" t="s">
+      <c r="L36" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="M36" s="37">
+      <c r="M36" s="38">
         <v>11372.9</v>
       </c>
-      <c r="N36" s="50"/>
-      <c r="O36" s="24"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="27"/>
       <c r="V36" s="52"/>
-      <c r="W36" s="26"/>
-      <c r="X36" s="26"/>
-      <c r="Y36" s="26"/>
-      <c r="Z36" s="26"/>
-      <c r="AA36" s="26"/>
-      <c r="AB36" s="26"/>
-      <c r="AC36" s="26"/>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
+      <c r="Z36" s="27"/>
+      <c r="AA36" s="27"/>
+      <c r="AB36" s="27"/>
+      <c r="AC36" s="27"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="22"/>
-      <c r="B37" s="22"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
       <c r="C37" s="40"/>
       <c r="D37" s="62" t="s">
         <v>198</v>
@@ -2794,31 +2794,31 @@
         <v>199</v>
       </c>
       <c r="J37" s="69"/>
-      <c r="K37" s="44"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="50">
+      <c r="K37" s="45"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="51">
         <v>15854.78</v>
       </c>
-      <c r="O37" s="24"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
       <c r="V37" s="52"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="26"/>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="26"/>
-      <c r="AA37" s="26"/>
-      <c r="AB37" s="26"/>
-      <c r="AC37" s="26"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="22"/>
-      <c r="B38" s="22"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
       <c r="C38" s="57"/>
       <c r="D38" s="62" t="s">
         <v>200</v>
@@ -2831,32 +2831,32 @@
         <v>199</v>
       </c>
       <c r="J38" s="69"/>
-      <c r="K38" s="44"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="37"/>
-      <c r="N38" s="50">
+      <c r="K38" s="45"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="51">
         <v>24962.38</v>
       </c>
-      <c r="O38" s="24"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
       <c r="V38" s="52"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="26"/>
-      <c r="Y38" s="26"/>
-      <c r="Z38" s="26"/>
-      <c r="AA38" s="26"/>
-      <c r="AB38" s="26"/>
-      <c r="AC38" s="26"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27"/>
+      <c r="Y38" s="27"/>
+      <c r="Z38" s="27"/>
+      <c r="AA38" s="27"/>
+      <c r="AB38" s="27"/>
+      <c r="AC38" s="27"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="22"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="31">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="32">
         <v>3.0</v>
       </c>
       <c r="D39" s="62" t="s">
@@ -2870,13 +2870,13 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
         <v>46106.0</v>
       </c>
-      <c r="K39" s="44">
+      <c r="K39" s="45">
         <v>27801.11</v>
       </c>
       <c r="L39" s="71" t="s">
@@ -2885,22 +2885,22 @@
       <c r="M39" s="72">
         <v>27801.11</v>
       </c>
-      <c r="N39" s="50"/>
-      <c r="O39" s="24"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="S39" s="26"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
+      <c r="N39" s="51"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27"/>
       <c r="V39" s="52"/>
-      <c r="W39" s="26"/>
-      <c r="X39" s="26"/>
-      <c r="Y39" s="26"/>
-      <c r="Z39" s="26"/>
-      <c r="AA39" s="26"/>
-      <c r="AB39" s="26"/>
-      <c r="AC39" s="26"/>
+      <c r="W39" s="27"/>
+      <c r="X39" s="27"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="27"/>
+      <c r="AA39" s="27"/>
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="27"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="16"/>
@@ -2917,22 +2917,22 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
         <v>46233.0</v>
       </c>
-      <c r="K40" s="44">
+      <c r="K40" s="45">
         <v>58868.35</v>
       </c>
-      <c r="L40" s="33" t="s">
-        <v>63</v>
+      <c r="L40" s="34" t="s">
+        <v>76</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
       </c>
-      <c r="N40" s="50"/>
+      <c r="N40" s="51"/>
       <c r="V40" s="3"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
@@ -3222,4622 +3222,4622 @@
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="16"/>
       <c r="B102" s="16"/>
-      <c r="L102" s="21"/>
+      <c r="L102" s="22"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="16"/>
       <c r="B103" s="16"/>
-      <c r="L103" s="21"/>
+      <c r="L103" s="22"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="16"/>
       <c r="B104" s="16"/>
-      <c r="L104" s="21"/>
+      <c r="L104" s="22"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="16"/>
       <c r="B105" s="16"/>
-      <c r="L105" s="21"/>
+      <c r="L105" s="22"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="16"/>
       <c r="B106" s="16"/>
-      <c r="L106" s="21"/>
+      <c r="L106" s="22"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="16"/>
       <c r="B107" s="16"/>
-      <c r="L107" s="21"/>
+      <c r="L107" s="22"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="16"/>
       <c r="B108" s="16"/>
-      <c r="L108" s="21"/>
+      <c r="L108" s="22"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="16"/>
       <c r="B109" s="16"/>
-      <c r="L109" s="21"/>
+      <c r="L109" s="22"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="16"/>
       <c r="B110" s="16"/>
-      <c r="L110" s="21"/>
+      <c r="L110" s="22"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="16"/>
       <c r="B111" s="16"/>
-      <c r="L111" s="21"/>
+      <c r="L111" s="22"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="16"/>
       <c r="B112" s="16"/>
-      <c r="L112" s="21"/>
+      <c r="L112" s="22"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="16"/>
       <c r="B113" s="16"/>
-      <c r="L113" s="21"/>
+      <c r="L113" s="22"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="16"/>
       <c r="B114" s="16"/>
-      <c r="L114" s="21"/>
+      <c r="L114" s="22"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="16"/>
       <c r="B115" s="16"/>
-      <c r="L115" s="21"/>
+      <c r="L115" s="22"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="16"/>
       <c r="B116" s="16"/>
-      <c r="L116" s="21"/>
+      <c r="L116" s="22"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="16"/>
       <c r="B117" s="16"/>
-      <c r="L117" s="21"/>
+      <c r="L117" s="22"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="16"/>
       <c r="B118" s="16"/>
-      <c r="L118" s="21"/>
+      <c r="L118" s="22"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="16"/>
       <c r="B119" s="16"/>
-      <c r="L119" s="21"/>
+      <c r="L119" s="22"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="16"/>
       <c r="B120" s="16"/>
-      <c r="L120" s="21"/>
+      <c r="L120" s="22"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="16"/>
       <c r="B121" s="16"/>
-      <c r="L121" s="21"/>
+      <c r="L121" s="22"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="16"/>
       <c r="B122" s="16"/>
-      <c r="L122" s="21"/>
+      <c r="L122" s="22"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="16"/>
       <c r="B123" s="16"/>
-      <c r="L123" s="21"/>
+      <c r="L123" s="22"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="16"/>
       <c r="B124" s="16"/>
-      <c r="L124" s="21"/>
+      <c r="L124" s="22"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="16"/>
       <c r="B125" s="16"/>
-      <c r="L125" s="21"/>
+      <c r="L125" s="22"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="16"/>
       <c r="B126" s="16"/>
-      <c r="L126" s="21"/>
+      <c r="L126" s="22"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="16"/>
       <c r="B127" s="16"/>
-      <c r="L127" s="21"/>
+      <c r="L127" s="22"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="16"/>
       <c r="B128" s="16"/>
-      <c r="L128" s="21"/>
+      <c r="L128" s="22"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="16"/>
       <c r="B129" s="16"/>
-      <c r="L129" s="21"/>
+      <c r="L129" s="22"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="16"/>
       <c r="B130" s="16"/>
-      <c r="L130" s="21"/>
+      <c r="L130" s="22"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="16"/>
       <c r="B131" s="16"/>
-      <c r="L131" s="21"/>
+      <c r="L131" s="22"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="16"/>
       <c r="B132" s="16"/>
-      <c r="L132" s="21"/>
+      <c r="L132" s="22"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="16"/>
       <c r="B133" s="16"/>
-      <c r="L133" s="21"/>
+      <c r="L133" s="22"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="16"/>
       <c r="B134" s="16"/>
-      <c r="L134" s="21"/>
+      <c r="L134" s="22"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="16"/>
       <c r="B135" s="16"/>
-      <c r="L135" s="21"/>
+      <c r="L135" s="22"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="16"/>
       <c r="B136" s="16"/>
-      <c r="L136" s="21"/>
+      <c r="L136" s="22"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="16"/>
       <c r="B137" s="16"/>
-      <c r="L137" s="21"/>
+      <c r="L137" s="22"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="16"/>
       <c r="B138" s="16"/>
-      <c r="L138" s="21"/>
+      <c r="L138" s="22"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="16"/>
       <c r="B139" s="16"/>
-      <c r="L139" s="21"/>
+      <c r="L139" s="22"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="16"/>
       <c r="B140" s="16"/>
-      <c r="L140" s="21"/>
+      <c r="L140" s="22"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="16"/>
       <c r="B141" s="16"/>
-      <c r="L141" s="21"/>
+      <c r="L141" s="22"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="16"/>
       <c r="B142" s="16"/>
-      <c r="L142" s="21"/>
+      <c r="L142" s="22"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="16"/>
       <c r="B143" s="16"/>
-      <c r="L143" s="21"/>
+      <c r="L143" s="22"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="16"/>
       <c r="B144" s="16"/>
-      <c r="L144" s="21"/>
+      <c r="L144" s="22"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="16"/>
       <c r="B145" s="16"/>
-      <c r="L145" s="21"/>
+      <c r="L145" s="22"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="16"/>
       <c r="B146" s="16"/>
-      <c r="L146" s="21"/>
+      <c r="L146" s="22"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="16"/>
       <c r="B147" s="16"/>
-      <c r="L147" s="21"/>
+      <c r="L147" s="22"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="16"/>
       <c r="B148" s="16"/>
-      <c r="L148" s="21"/>
+      <c r="L148" s="22"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="16"/>
       <c r="B149" s="16"/>
-      <c r="L149" s="21"/>
+      <c r="L149" s="22"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="16"/>
       <c r="B150" s="16"/>
-      <c r="L150" s="21"/>
+      <c r="L150" s="22"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="16"/>
       <c r="B151" s="16"/>
-      <c r="L151" s="21"/>
+      <c r="L151" s="22"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="16"/>
       <c r="B152" s="16"/>
-      <c r="L152" s="21"/>
+      <c r="L152" s="22"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="16"/>
       <c r="B153" s="16"/>
-      <c r="L153" s="21"/>
+      <c r="L153" s="22"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="16"/>
       <c r="B154" s="16"/>
-      <c r="L154" s="21"/>
+      <c r="L154" s="22"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="16"/>
       <c r="B155" s="16"/>
-      <c r="L155" s="21"/>
+      <c r="L155" s="22"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="16"/>
       <c r="B156" s="16"/>
-      <c r="L156" s="21"/>
+      <c r="L156" s="22"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="16"/>
       <c r="B157" s="16"/>
-      <c r="L157" s="21"/>
+      <c r="L157" s="22"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="16"/>
       <c r="B158" s="16"/>
-      <c r="L158" s="21"/>
+      <c r="L158" s="22"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="16"/>
       <c r="B159" s="16"/>
-      <c r="L159" s="21"/>
+      <c r="L159" s="22"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="16"/>
       <c r="B160" s="16"/>
-      <c r="L160" s="21"/>
+      <c r="L160" s="22"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="16"/>
       <c r="B161" s="16"/>
-      <c r="L161" s="21"/>
+      <c r="L161" s="22"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="16"/>
       <c r="B162" s="16"/>
-      <c r="L162" s="21"/>
+      <c r="L162" s="22"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="16"/>
       <c r="B163" s="16"/>
-      <c r="L163" s="21"/>
+      <c r="L163" s="22"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="16"/>
       <c r="B164" s="16"/>
-      <c r="L164" s="21"/>
+      <c r="L164" s="22"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="16"/>
       <c r="B165" s="16"/>
-      <c r="L165" s="21"/>
+      <c r="L165" s="22"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="16"/>
       <c r="B166" s="16"/>
-      <c r="L166" s="21"/>
+      <c r="L166" s="22"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="16"/>
       <c r="B167" s="16"/>
-      <c r="L167" s="21"/>
+      <c r="L167" s="22"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="16"/>
       <c r="B168" s="16"/>
-      <c r="L168" s="21"/>
+      <c r="L168" s="22"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="16"/>
       <c r="B169" s="16"/>
-      <c r="L169" s="21"/>
+      <c r="L169" s="22"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="16"/>
       <c r="B170" s="16"/>
-      <c r="L170" s="21"/>
+      <c r="L170" s="22"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="16"/>
       <c r="B171" s="16"/>
-      <c r="L171" s="21"/>
+      <c r="L171" s="22"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="16"/>
       <c r="B172" s="16"/>
-      <c r="L172" s="21"/>
+      <c r="L172" s="22"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="16"/>
       <c r="B173" s="16"/>
-      <c r="L173" s="21"/>
+      <c r="L173" s="22"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="16"/>
       <c r="B174" s="16"/>
-      <c r="L174" s="21"/>
+      <c r="L174" s="22"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="16"/>
       <c r="B175" s="16"/>
-      <c r="L175" s="21"/>
+      <c r="L175" s="22"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="16"/>
       <c r="B176" s="16"/>
-      <c r="L176" s="21"/>
+      <c r="L176" s="22"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="16"/>
       <c r="B177" s="16"/>
-      <c r="L177" s="21"/>
+      <c r="L177" s="22"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="16"/>
       <c r="B178" s="16"/>
-      <c r="L178" s="21"/>
+      <c r="L178" s="22"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="16"/>
       <c r="B179" s="16"/>
-      <c r="L179" s="21"/>
+      <c r="L179" s="22"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="16"/>
       <c r="B180" s="16"/>
-      <c r="L180" s="21"/>
+      <c r="L180" s="22"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="16"/>
       <c r="B181" s="16"/>
-      <c r="L181" s="21"/>
+      <c r="L181" s="22"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="16"/>
       <c r="B182" s="16"/>
-      <c r="L182" s="21"/>
+      <c r="L182" s="22"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="16"/>
       <c r="B183" s="16"/>
-      <c r="L183" s="21"/>
+      <c r="L183" s="22"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="16"/>
       <c r="B184" s="16"/>
-      <c r="L184" s="21"/>
+      <c r="L184" s="22"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="16"/>
       <c r="B185" s="16"/>
-      <c r="L185" s="21"/>
+      <c r="L185" s="22"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="16"/>
       <c r="B186" s="16"/>
-      <c r="L186" s="21"/>
+      <c r="L186" s="22"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="16"/>
       <c r="B187" s="16"/>
-      <c r="L187" s="21"/>
+      <c r="L187" s="22"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="16"/>
       <c r="B188" s="16"/>
-      <c r="L188" s="21"/>
+      <c r="L188" s="22"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="16"/>
       <c r="B189" s="16"/>
-      <c r="L189" s="21"/>
+      <c r="L189" s="22"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="16"/>
       <c r="B190" s="16"/>
-      <c r="L190" s="21"/>
+      <c r="L190" s="22"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="16"/>
       <c r="B191" s="16"/>
-      <c r="L191" s="21"/>
+      <c r="L191" s="22"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="16"/>
       <c r="B192" s="16"/>
-      <c r="L192" s="21"/>
+      <c r="L192" s="22"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="16"/>
       <c r="B193" s="16"/>
-      <c r="L193" s="21"/>
+      <c r="L193" s="22"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="16"/>
       <c r="B194" s="16"/>
-      <c r="L194" s="21"/>
+      <c r="L194" s="22"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="16"/>
       <c r="B195" s="16"/>
-      <c r="L195" s="21"/>
+      <c r="L195" s="22"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="16"/>
       <c r="B196" s="16"/>
-      <c r="L196" s="21"/>
+      <c r="L196" s="22"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="16"/>
       <c r="B197" s="16"/>
-      <c r="L197" s="21"/>
+      <c r="L197" s="22"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="16"/>
       <c r="B198" s="16"/>
-      <c r="L198" s="21"/>
+      <c r="L198" s="22"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="16"/>
       <c r="B199" s="16"/>
-      <c r="L199" s="21"/>
+      <c r="L199" s="22"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="16"/>
       <c r="B200" s="16"/>
-      <c r="L200" s="21"/>
+      <c r="L200" s="22"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="16"/>
       <c r="B201" s="16"/>
-      <c r="L201" s="21"/>
+      <c r="L201" s="22"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="16"/>
       <c r="B202" s="16"/>
-      <c r="L202" s="21"/>
+      <c r="L202" s="22"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="16"/>
       <c r="B203" s="16"/>
-      <c r="L203" s="21"/>
+      <c r="L203" s="22"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="16"/>
       <c r="B204" s="16"/>
-      <c r="L204" s="21"/>
+      <c r="L204" s="22"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="16"/>
       <c r="B205" s="16"/>
-      <c r="L205" s="21"/>
+      <c r="L205" s="22"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="16"/>
       <c r="B206" s="16"/>
-      <c r="L206" s="21"/>
+      <c r="L206" s="22"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="16"/>
       <c r="B207" s="16"/>
-      <c r="L207" s="21"/>
+      <c r="L207" s="22"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="16"/>
       <c r="B208" s="16"/>
-      <c r="L208" s="21"/>
+      <c r="L208" s="22"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="16"/>
       <c r="B209" s="16"/>
-      <c r="L209" s="21"/>
+      <c r="L209" s="22"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="16"/>
       <c r="B210" s="16"/>
-      <c r="L210" s="21"/>
+      <c r="L210" s="22"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="16"/>
       <c r="B211" s="16"/>
-      <c r="L211" s="21"/>
+      <c r="L211" s="22"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="16"/>
       <c r="B212" s="16"/>
-      <c r="L212" s="21"/>
+      <c r="L212" s="22"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="16"/>
       <c r="B213" s="16"/>
-      <c r="L213" s="21"/>
+      <c r="L213" s="22"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="16"/>
       <c r="B214" s="16"/>
-      <c r="L214" s="21"/>
+      <c r="L214" s="22"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="16"/>
       <c r="B215" s="16"/>
-      <c r="L215" s="21"/>
+      <c r="L215" s="22"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="16"/>
       <c r="B216" s="16"/>
-      <c r="L216" s="21"/>
+      <c r="L216" s="22"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="16"/>
       <c r="B217" s="16"/>
-      <c r="L217" s="21"/>
+      <c r="L217" s="22"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="16"/>
       <c r="B218" s="16"/>
-      <c r="L218" s="21"/>
+      <c r="L218" s="22"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="16"/>
       <c r="B219" s="16"/>
-      <c r="L219" s="21"/>
+      <c r="L219" s="22"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="16"/>
       <c r="B220" s="16"/>
-      <c r="L220" s="21"/>
+      <c r="L220" s="22"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="16"/>
       <c r="B221" s="16"/>
-      <c r="L221" s="21"/>
+      <c r="L221" s="22"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="16"/>
       <c r="B222" s="16"/>
-      <c r="L222" s="21"/>
+      <c r="L222" s="22"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="16"/>
       <c r="B223" s="16"/>
-      <c r="L223" s="21"/>
+      <c r="L223" s="22"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="16"/>
       <c r="B224" s="16"/>
-      <c r="L224" s="21"/>
+      <c r="L224" s="22"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="16"/>
       <c r="B225" s="16"/>
-      <c r="L225" s="21"/>
+      <c r="L225" s="22"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="16"/>
       <c r="B226" s="16"/>
-      <c r="L226" s="21"/>
+      <c r="L226" s="22"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
       <c r="A227" s="16"/>
       <c r="B227" s="16"/>
-      <c r="L227" s="21"/>
+      <c r="L227" s="22"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="16"/>
       <c r="B228" s="16"/>
-      <c r="L228" s="21"/>
+      <c r="L228" s="22"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="A229" s="16"/>
       <c r="B229" s="16"/>
-      <c r="L229" s="21"/>
+      <c r="L229" s="22"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="16"/>
       <c r="B230" s="16"/>
-      <c r="L230" s="21"/>
+      <c r="L230" s="22"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="16"/>
       <c r="B231" s="16"/>
-      <c r="L231" s="21"/>
+      <c r="L231" s="22"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="16"/>
       <c r="B232" s="16"/>
-      <c r="L232" s="21"/>
+      <c r="L232" s="22"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="16"/>
       <c r="B233" s="16"/>
-      <c r="L233" s="21"/>
+      <c r="L233" s="22"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="16"/>
       <c r="B234" s="16"/>
-      <c r="L234" s="21"/>
+      <c r="L234" s="22"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
       <c r="A235" s="16"/>
       <c r="B235" s="16"/>
-      <c r="L235" s="21"/>
+      <c r="L235" s="22"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
       <c r="A236" s="16"/>
       <c r="B236" s="16"/>
-      <c r="L236" s="21"/>
+      <c r="L236" s="22"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
       <c r="A237" s="16"/>
       <c r="B237" s="16"/>
-      <c r="L237" s="21"/>
+      <c r="L237" s="22"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="A238" s="16"/>
       <c r="B238" s="16"/>
-      <c r="L238" s="21"/>
+      <c r="L238" s="22"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
       <c r="A239" s="16"/>
       <c r="B239" s="16"/>
-      <c r="L239" s="21"/>
+      <c r="L239" s="22"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
       <c r="A240" s="16"/>
       <c r="B240" s="16"/>
-      <c r="L240" s="21"/>
+      <c r="L240" s="22"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
       <c r="A241" s="16"/>
       <c r="B241" s="16"/>
-      <c r="L241" s="21"/>
+      <c r="L241" s="22"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="A242" s="16"/>
       <c r="B242" s="16"/>
-      <c r="L242" s="21"/>
+      <c r="L242" s="22"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
       <c r="A243" s="16"/>
       <c r="B243" s="16"/>
-      <c r="L243" s="21"/>
+      <c r="L243" s="22"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
       <c r="A244" s="16"/>
       <c r="B244" s="16"/>
-      <c r="L244" s="21"/>
+      <c r="L244" s="22"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="A245" s="16"/>
       <c r="B245" s="16"/>
-      <c r="L245" s="21"/>
+      <c r="L245" s="22"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="A246" s="16"/>
       <c r="B246" s="16"/>
-      <c r="L246" s="21"/>
+      <c r="L246" s="22"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
       <c r="A247" s="16"/>
       <c r="B247" s="16"/>
-      <c r="L247" s="21"/>
+      <c r="L247" s="22"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
       <c r="A248" s="16"/>
       <c r="B248" s="16"/>
-      <c r="L248" s="21"/>
+      <c r="L248" s="22"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
       <c r="A249" s="16"/>
       <c r="B249" s="16"/>
-      <c r="L249" s="21"/>
+      <c r="L249" s="22"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="A250" s="16"/>
       <c r="B250" s="16"/>
-      <c r="L250" s="21"/>
+      <c r="L250" s="22"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
       <c r="A251" s="16"/>
       <c r="B251" s="16"/>
-      <c r="L251" s="21"/>
+      <c r="L251" s="22"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
       <c r="A252" s="16"/>
       <c r="B252" s="16"/>
-      <c r="L252" s="21"/>
+      <c r="L252" s="22"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
       <c r="A253" s="16"/>
       <c r="B253" s="16"/>
-      <c r="L253" s="21"/>
+      <c r="L253" s="22"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="A254" s="16"/>
       <c r="B254" s="16"/>
-      <c r="L254" s="21"/>
+      <c r="L254" s="22"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
       <c r="A255" s="16"/>
       <c r="B255" s="16"/>
-      <c r="L255" s="21"/>
+      <c r="L255" s="22"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
       <c r="A256" s="16"/>
       <c r="B256" s="16"/>
-      <c r="L256" s="21"/>
+      <c r="L256" s="22"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="A257" s="16"/>
       <c r="B257" s="16"/>
-      <c r="L257" s="21"/>
+      <c r="L257" s="22"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="A258" s="16"/>
       <c r="B258" s="16"/>
-      <c r="L258" s="21"/>
+      <c r="L258" s="22"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
       <c r="A259" s="16"/>
       <c r="B259" s="16"/>
-      <c r="L259" s="21"/>
+      <c r="L259" s="22"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
       <c r="A260" s="16"/>
       <c r="B260" s="16"/>
-      <c r="L260" s="21"/>
+      <c r="L260" s="22"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="A261" s="16"/>
       <c r="B261" s="16"/>
-      <c r="L261" s="21"/>
+      <c r="L261" s="22"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="A262" s="16"/>
       <c r="B262" s="16"/>
-      <c r="L262" s="21"/>
+      <c r="L262" s="22"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
       <c r="A263" s="16"/>
       <c r="B263" s="16"/>
-      <c r="L263" s="21"/>
+      <c r="L263" s="22"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
       <c r="A264" s="16"/>
       <c r="B264" s="16"/>
-      <c r="L264" s="21"/>
+      <c r="L264" s="22"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="A265" s="16"/>
       <c r="B265" s="16"/>
-      <c r="L265" s="21"/>
+      <c r="L265" s="22"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="A266" s="16"/>
       <c r="B266" s="16"/>
-      <c r="L266" s="21"/>
+      <c r="L266" s="22"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
       <c r="A267" s="16"/>
       <c r="B267" s="16"/>
-      <c r="L267" s="21"/>
+      <c r="L267" s="22"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
       <c r="A268" s="16"/>
       <c r="B268" s="16"/>
-      <c r="L268" s="21"/>
+      <c r="L268" s="22"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="A269" s="16"/>
       <c r="B269" s="16"/>
-      <c r="L269" s="21"/>
+      <c r="L269" s="22"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="A270" s="16"/>
       <c r="B270" s="16"/>
-      <c r="L270" s="21"/>
+      <c r="L270" s="22"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
       <c r="A271" s="16"/>
       <c r="B271" s="16"/>
-      <c r="L271" s="21"/>
+      <c r="L271" s="22"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
       <c r="A272" s="16"/>
       <c r="B272" s="16"/>
-      <c r="L272" s="21"/>
+      <c r="L272" s="22"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="A273" s="16"/>
       <c r="B273" s="16"/>
-      <c r="L273" s="21"/>
+      <c r="L273" s="22"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="A274" s="16"/>
       <c r="B274" s="16"/>
-      <c r="L274" s="21"/>
+      <c r="L274" s="22"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
       <c r="A275" s="16"/>
       <c r="B275" s="16"/>
-      <c r="L275" s="21"/>
+      <c r="L275" s="22"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
       <c r="A276" s="16"/>
       <c r="B276" s="16"/>
-      <c r="L276" s="21"/>
+      <c r="L276" s="22"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
       <c r="A277" s="16"/>
       <c r="B277" s="16"/>
-      <c r="L277" s="21"/>
+      <c r="L277" s="22"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="A278" s="16"/>
       <c r="B278" s="16"/>
-      <c r="L278" s="21"/>
+      <c r="L278" s="22"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
       <c r="A279" s="16"/>
       <c r="B279" s="16"/>
-      <c r="L279" s="21"/>
+      <c r="L279" s="22"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
       <c r="A280" s="16"/>
       <c r="B280" s="16"/>
-      <c r="L280" s="21"/>
+      <c r="L280" s="22"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
       <c r="A281" s="16"/>
       <c r="B281" s="16"/>
-      <c r="L281" s="21"/>
+      <c r="L281" s="22"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="A282" s="16"/>
       <c r="B282" s="16"/>
-      <c r="L282" s="21"/>
+      <c r="L282" s="22"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
       <c r="A283" s="16"/>
       <c r="B283" s="16"/>
-      <c r="L283" s="21"/>
+      <c r="L283" s="22"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
       <c r="A284" s="16"/>
       <c r="B284" s="16"/>
-      <c r="L284" s="21"/>
+      <c r="L284" s="22"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
       <c r="A285" s="16"/>
       <c r="B285" s="16"/>
-      <c r="L285" s="21"/>
+      <c r="L285" s="22"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="A286" s="16"/>
       <c r="B286" s="16"/>
-      <c r="L286" s="21"/>
+      <c r="L286" s="22"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
       <c r="A287" s="16"/>
       <c r="B287" s="16"/>
-      <c r="L287" s="21"/>
+      <c r="L287" s="22"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
       <c r="A288" s="16"/>
       <c r="B288" s="16"/>
-      <c r="L288" s="21"/>
+      <c r="L288" s="22"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="A289" s="16"/>
       <c r="B289" s="16"/>
-      <c r="L289" s="21"/>
+      <c r="L289" s="22"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="A290" s="16"/>
       <c r="B290" s="16"/>
-      <c r="L290" s="21"/>
+      <c r="L290" s="22"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
       <c r="A291" s="16"/>
       <c r="B291" s="16"/>
-      <c r="L291" s="21"/>
+      <c r="L291" s="22"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
       <c r="A292" s="16"/>
       <c r="B292" s="16"/>
-      <c r="L292" s="21"/>
+      <c r="L292" s="22"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
       <c r="A293" s="16"/>
       <c r="B293" s="16"/>
-      <c r="L293" s="21"/>
+      <c r="L293" s="22"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
       <c r="A294" s="16"/>
       <c r="B294" s="16"/>
-      <c r="L294" s="21"/>
+      <c r="L294" s="22"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
       <c r="A295" s="16"/>
       <c r="B295" s="16"/>
-      <c r="L295" s="21"/>
+      <c r="L295" s="22"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
       <c r="A296" s="16"/>
       <c r="B296" s="16"/>
-      <c r="L296" s="21"/>
+      <c r="L296" s="22"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
       <c r="A297" s="16"/>
       <c r="B297" s="16"/>
-      <c r="L297" s="21"/>
+      <c r="L297" s="22"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="A298" s="16"/>
       <c r="B298" s="16"/>
-      <c r="L298" s="21"/>
+      <c r="L298" s="22"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
       <c r="A299" s="16"/>
       <c r="B299" s="16"/>
-      <c r="L299" s="21"/>
+      <c r="L299" s="22"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
       <c r="A300" s="16"/>
       <c r="B300" s="16"/>
-      <c r="L300" s="21"/>
+      <c r="L300" s="22"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
       <c r="A301" s="16"/>
       <c r="B301" s="16"/>
-      <c r="L301" s="21"/>
+      <c r="L301" s="22"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="A302" s="16"/>
       <c r="B302" s="16"/>
-      <c r="L302" s="21"/>
+      <c r="L302" s="22"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
       <c r="A303" s="16"/>
       <c r="B303" s="16"/>
-      <c r="L303" s="21"/>
+      <c r="L303" s="22"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
       <c r="A304" s="16"/>
       <c r="B304" s="16"/>
-      <c r="L304" s="21"/>
+      <c r="L304" s="22"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
       <c r="A305" s="16"/>
       <c r="B305" s="16"/>
-      <c r="L305" s="21"/>
+      <c r="L305" s="22"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="A306" s="16"/>
       <c r="B306" s="16"/>
-      <c r="L306" s="21"/>
+      <c r="L306" s="22"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
       <c r="A307" s="16"/>
       <c r="B307" s="16"/>
-      <c r="L307" s="21"/>
+      <c r="L307" s="22"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
       <c r="A308" s="16"/>
       <c r="B308" s="16"/>
-      <c r="L308" s="21"/>
+      <c r="L308" s="22"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
       <c r="A309" s="16"/>
       <c r="B309" s="16"/>
-      <c r="L309" s="21"/>
+      <c r="L309" s="22"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="A310" s="16"/>
       <c r="B310" s="16"/>
-      <c r="L310" s="21"/>
+      <c r="L310" s="22"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
       <c r="A311" s="16"/>
       <c r="B311" s="16"/>
-      <c r="L311" s="21"/>
+      <c r="L311" s="22"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
       <c r="A312" s="16"/>
       <c r="B312" s="16"/>
-      <c r="L312" s="21"/>
+      <c r="L312" s="22"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
       <c r="A313" s="16"/>
       <c r="B313" s="16"/>
-      <c r="L313" s="21"/>
+      <c r="L313" s="22"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="A314" s="16"/>
       <c r="B314" s="16"/>
-      <c r="L314" s="21"/>
+      <c r="L314" s="22"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
       <c r="A315" s="16"/>
       <c r="B315" s="16"/>
-      <c r="L315" s="21"/>
+      <c r="L315" s="22"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="A316" s="16"/>
       <c r="B316" s="16"/>
-      <c r="L316" s="21"/>
+      <c r="L316" s="22"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="A317" s="16"/>
       <c r="B317" s="16"/>
-      <c r="L317" s="21"/>
+      <c r="L317" s="22"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="A318" s="16"/>
       <c r="B318" s="16"/>
-      <c r="L318" s="21"/>
+      <c r="L318" s="22"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
       <c r="A319" s="16"/>
       <c r="B319" s="16"/>
-      <c r="L319" s="21"/>
+      <c r="L319" s="22"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="A320" s="16"/>
       <c r="B320" s="16"/>
-      <c r="L320" s="21"/>
+      <c r="L320" s="22"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="A321" s="16"/>
       <c r="B321" s="16"/>
-      <c r="L321" s="21"/>
+      <c r="L321" s="22"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="A322" s="16"/>
       <c r="B322" s="16"/>
-      <c r="L322" s="21"/>
+      <c r="L322" s="22"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
       <c r="A323" s="16"/>
       <c r="B323" s="16"/>
-      <c r="L323" s="21"/>
+      <c r="L323" s="22"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="A324" s="16"/>
       <c r="B324" s="16"/>
-      <c r="L324" s="21"/>
+      <c r="L324" s="22"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="A325" s="16"/>
       <c r="B325" s="16"/>
-      <c r="L325" s="21"/>
+      <c r="L325" s="22"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="A326" s="16"/>
       <c r="B326" s="16"/>
-      <c r="L326" s="21"/>
+      <c r="L326" s="22"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
       <c r="A327" s="16"/>
       <c r="B327" s="16"/>
-      <c r="L327" s="21"/>
+      <c r="L327" s="22"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="A328" s="16"/>
       <c r="B328" s="16"/>
-      <c r="L328" s="21"/>
+      <c r="L328" s="22"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="A329" s="16"/>
       <c r="B329" s="16"/>
-      <c r="L329" s="21"/>
+      <c r="L329" s="22"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="A330" s="16"/>
       <c r="B330" s="16"/>
-      <c r="L330" s="21"/>
+      <c r="L330" s="22"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
       <c r="A331" s="16"/>
       <c r="B331" s="16"/>
-      <c r="L331" s="21"/>
+      <c r="L331" s="22"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="A332" s="16"/>
       <c r="B332" s="16"/>
-      <c r="L332" s="21"/>
+      <c r="L332" s="22"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="A333" s="16"/>
       <c r="B333" s="16"/>
-      <c r="L333" s="21"/>
+      <c r="L333" s="22"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="A334" s="16"/>
       <c r="B334" s="16"/>
-      <c r="L334" s="21"/>
+      <c r="L334" s="22"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
       <c r="A335" s="16"/>
       <c r="B335" s="16"/>
-      <c r="L335" s="21"/>
+      <c r="L335" s="22"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="A336" s="16"/>
       <c r="B336" s="16"/>
-      <c r="L336" s="21"/>
+      <c r="L336" s="22"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="A337" s="16"/>
       <c r="B337" s="16"/>
-      <c r="L337" s="21"/>
+      <c r="L337" s="22"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="A338" s="16"/>
       <c r="B338" s="16"/>
-      <c r="L338" s="21"/>
+      <c r="L338" s="22"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
       <c r="A339" s="16"/>
       <c r="B339" s="16"/>
-      <c r="L339" s="21"/>
+      <c r="L339" s="22"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="A340" s="16"/>
       <c r="B340" s="16"/>
-      <c r="L340" s="21"/>
+      <c r="L340" s="22"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="A341" s="16"/>
       <c r="B341" s="16"/>
-      <c r="L341" s="21"/>
+      <c r="L341" s="22"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="A342" s="16"/>
       <c r="B342" s="16"/>
-      <c r="L342" s="21"/>
+      <c r="L342" s="22"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
       <c r="A343" s="16"/>
       <c r="B343" s="16"/>
-      <c r="L343" s="21"/>
+      <c r="L343" s="22"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="A344" s="16"/>
       <c r="B344" s="16"/>
-      <c r="L344" s="21"/>
+      <c r="L344" s="22"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="A345" s="16"/>
       <c r="B345" s="16"/>
-      <c r="L345" s="21"/>
+      <c r="L345" s="22"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="A346" s="16"/>
       <c r="B346" s="16"/>
-      <c r="L346" s="21"/>
+      <c r="L346" s="22"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
       <c r="A347" s="16"/>
       <c r="B347" s="16"/>
-      <c r="L347" s="21"/>
+      <c r="L347" s="22"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="A348" s="16"/>
       <c r="B348" s="16"/>
-      <c r="L348" s="21"/>
+      <c r="L348" s="22"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="A349" s="16"/>
       <c r="B349" s="16"/>
-      <c r="L349" s="21"/>
+      <c r="L349" s="22"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="A350" s="16"/>
       <c r="B350" s="16"/>
-      <c r="L350" s="21"/>
+      <c r="L350" s="22"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
       <c r="A351" s="16"/>
       <c r="B351" s="16"/>
-      <c r="L351" s="21"/>
+      <c r="L351" s="22"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="A352" s="16"/>
       <c r="B352" s="16"/>
-      <c r="L352" s="21"/>
+      <c r="L352" s="22"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="A353" s="16"/>
       <c r="B353" s="16"/>
-      <c r="L353" s="21"/>
+      <c r="L353" s="22"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="A354" s="16"/>
       <c r="B354" s="16"/>
-      <c r="L354" s="21"/>
+      <c r="L354" s="22"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
       <c r="A355" s="16"/>
       <c r="B355" s="16"/>
-      <c r="L355" s="21"/>
+      <c r="L355" s="22"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="A356" s="16"/>
       <c r="B356" s="16"/>
-      <c r="L356" s="21"/>
+      <c r="L356" s="22"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="A357" s="16"/>
       <c r="B357" s="16"/>
-      <c r="L357" s="21"/>
+      <c r="L357" s="22"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="A358" s="16"/>
       <c r="B358" s="16"/>
-      <c r="L358" s="21"/>
+      <c r="L358" s="22"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="A359" s="16"/>
       <c r="B359" s="16"/>
-      <c r="L359" s="21"/>
+      <c r="L359" s="22"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="A360" s="16"/>
       <c r="B360" s="16"/>
-      <c r="L360" s="21"/>
+      <c r="L360" s="22"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="A361" s="16"/>
       <c r="B361" s="16"/>
-      <c r="L361" s="21"/>
+      <c r="L361" s="22"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="A362" s="16"/>
       <c r="B362" s="16"/>
-      <c r="L362" s="21"/>
+      <c r="L362" s="22"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
       <c r="A363" s="16"/>
       <c r="B363" s="16"/>
-      <c r="L363" s="21"/>
+      <c r="L363" s="22"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="A364" s="16"/>
       <c r="B364" s="16"/>
-      <c r="L364" s="21"/>
+      <c r="L364" s="22"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="A365" s="16"/>
       <c r="B365" s="16"/>
-      <c r="L365" s="21"/>
+      <c r="L365" s="22"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="A366" s="16"/>
       <c r="B366" s="16"/>
-      <c r="L366" s="21"/>
+      <c r="L366" s="22"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="A367" s="16"/>
       <c r="B367" s="16"/>
-      <c r="L367" s="21"/>
+      <c r="L367" s="22"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="A368" s="16"/>
       <c r="B368" s="16"/>
-      <c r="L368" s="21"/>
+      <c r="L368" s="22"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="A369" s="16"/>
       <c r="B369" s="16"/>
-      <c r="L369" s="21"/>
+      <c r="L369" s="22"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="A370" s="16"/>
       <c r="B370" s="16"/>
-      <c r="L370" s="21"/>
+      <c r="L370" s="22"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
       <c r="A371" s="16"/>
       <c r="B371" s="16"/>
-      <c r="L371" s="21"/>
+      <c r="L371" s="22"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="A372" s="16"/>
       <c r="B372" s="16"/>
-      <c r="L372" s="21"/>
+      <c r="L372" s="22"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="A373" s="16"/>
       <c r="B373" s="16"/>
-      <c r="L373" s="21"/>
+      <c r="L373" s="22"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="A374" s="16"/>
       <c r="B374" s="16"/>
-      <c r="L374" s="21"/>
+      <c r="L374" s="22"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="A375" s="16"/>
       <c r="B375" s="16"/>
-      <c r="L375" s="21"/>
+      <c r="L375" s="22"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="A376" s="16"/>
       <c r="B376" s="16"/>
-      <c r="L376" s="21"/>
+      <c r="L376" s="22"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="A377" s="16"/>
       <c r="B377" s="16"/>
-      <c r="L377" s="21"/>
+      <c r="L377" s="22"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="A378" s="16"/>
       <c r="B378" s="16"/>
-      <c r="L378" s="21"/>
+      <c r="L378" s="22"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="A379" s="16"/>
       <c r="B379" s="16"/>
-      <c r="L379" s="21"/>
+      <c r="L379" s="22"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="A380" s="16"/>
       <c r="B380" s="16"/>
-      <c r="L380" s="21"/>
+      <c r="L380" s="22"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="A381" s="16"/>
       <c r="B381" s="16"/>
-      <c r="L381" s="21"/>
+      <c r="L381" s="22"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="A382" s="16"/>
       <c r="B382" s="16"/>
-      <c r="L382" s="21"/>
+      <c r="L382" s="22"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
       <c r="A383" s="16"/>
       <c r="B383" s="16"/>
-      <c r="L383" s="21"/>
+      <c r="L383" s="22"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="A384" s="16"/>
       <c r="B384" s="16"/>
-      <c r="L384" s="21"/>
+      <c r="L384" s="22"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="A385" s="16"/>
       <c r="B385" s="16"/>
-      <c r="L385" s="21"/>
+      <c r="L385" s="22"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="A386" s="16"/>
       <c r="B386" s="16"/>
-      <c r="L386" s="21"/>
+      <c r="L386" s="22"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
       <c r="A387" s="16"/>
       <c r="B387" s="16"/>
-      <c r="L387" s="21"/>
+      <c r="L387" s="22"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
       <c r="A388" s="16"/>
       <c r="B388" s="16"/>
-      <c r="L388" s="21"/>
+      <c r="L388" s="22"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
       <c r="A389" s="16"/>
       <c r="B389" s="16"/>
-      <c r="L389" s="21"/>
+      <c r="L389" s="22"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
       <c r="A390" s="16"/>
       <c r="B390" s="16"/>
-      <c r="L390" s="21"/>
+      <c r="L390" s="22"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
       <c r="A391" s="16"/>
       <c r="B391" s="16"/>
-      <c r="L391" s="21"/>
+      <c r="L391" s="22"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
       <c r="A392" s="16"/>
       <c r="B392" s="16"/>
-      <c r="L392" s="21"/>
+      <c r="L392" s="22"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
       <c r="A393" s="16"/>
       <c r="B393" s="16"/>
-      <c r="L393" s="21"/>
+      <c r="L393" s="22"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
       <c r="A394" s="16"/>
       <c r="B394" s="16"/>
-      <c r="L394" s="21"/>
+      <c r="L394" s="22"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
       <c r="A395" s="16"/>
       <c r="B395" s="16"/>
-      <c r="L395" s="21"/>
+      <c r="L395" s="22"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
       <c r="A396" s="16"/>
       <c r="B396" s="16"/>
-      <c r="L396" s="21"/>
+      <c r="L396" s="22"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
       <c r="A397" s="16"/>
       <c r="B397" s="16"/>
-      <c r="L397" s="21"/>
+      <c r="L397" s="22"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
       <c r="A398" s="16"/>
       <c r="B398" s="16"/>
-      <c r="L398" s="21"/>
+      <c r="L398" s="22"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
       <c r="A399" s="16"/>
       <c r="B399" s="16"/>
-      <c r="L399" s="21"/>
+      <c r="L399" s="22"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
       <c r="A400" s="16"/>
       <c r="B400" s="16"/>
-      <c r="L400" s="21"/>
+      <c r="L400" s="22"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
       <c r="A401" s="16"/>
       <c r="B401" s="16"/>
-      <c r="L401" s="21"/>
+      <c r="L401" s="22"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
       <c r="A402" s="16"/>
       <c r="B402" s="16"/>
-      <c r="L402" s="21"/>
+      <c r="L402" s="22"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
       <c r="A403" s="16"/>
       <c r="B403" s="16"/>
-      <c r="L403" s="21"/>
+      <c r="L403" s="22"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
       <c r="A404" s="16"/>
       <c r="B404" s="16"/>
-      <c r="L404" s="21"/>
+      <c r="L404" s="22"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
       <c r="A405" s="16"/>
       <c r="B405" s="16"/>
-      <c r="L405" s="21"/>
+      <c r="L405" s="22"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
       <c r="A406" s="16"/>
       <c r="B406" s="16"/>
-      <c r="L406" s="21"/>
+      <c r="L406" s="22"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
       <c r="A407" s="16"/>
       <c r="B407" s="16"/>
-      <c r="L407" s="21"/>
+      <c r="L407" s="22"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="A408" s="16"/>
       <c r="B408" s="16"/>
-      <c r="L408" s="21"/>
+      <c r="L408" s="22"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
       <c r="A409" s="16"/>
       <c r="B409" s="16"/>
-      <c r="L409" s="21"/>
+      <c r="L409" s="22"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="A410" s="16"/>
       <c r="B410" s="16"/>
-      <c r="L410" s="21"/>
+      <c r="L410" s="22"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
       <c r="A411" s="16"/>
       <c r="B411" s="16"/>
-      <c r="L411" s="21"/>
+      <c r="L411" s="22"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
       <c r="A412" s="16"/>
       <c r="B412" s="16"/>
-      <c r="L412" s="21"/>
+      <c r="L412" s="22"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
       <c r="A413" s="16"/>
       <c r="B413" s="16"/>
-      <c r="L413" s="21"/>
+      <c r="L413" s="22"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
       <c r="A414" s="16"/>
       <c r="B414" s="16"/>
-      <c r="L414" s="21"/>
+      <c r="L414" s="22"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
       <c r="A415" s="16"/>
       <c r="B415" s="16"/>
-      <c r="L415" s="21"/>
+      <c r="L415" s="22"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="A416" s="16"/>
       <c r="B416" s="16"/>
-      <c r="L416" s="21"/>
+      <c r="L416" s="22"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
       <c r="A417" s="16"/>
       <c r="B417" s="16"/>
-      <c r="L417" s="21"/>
+      <c r="L417" s="22"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="A418" s="16"/>
       <c r="B418" s="16"/>
-      <c r="L418" s="21"/>
+      <c r="L418" s="22"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
       <c r="A419" s="16"/>
       <c r="B419" s="16"/>
-      <c r="L419" s="21"/>
+      <c r="L419" s="22"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
       <c r="A420" s="16"/>
       <c r="B420" s="16"/>
-      <c r="L420" s="21"/>
+      <c r="L420" s="22"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
       <c r="A421" s="16"/>
       <c r="B421" s="16"/>
-      <c r="L421" s="21"/>
+      <c r="L421" s="22"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
       <c r="A422" s="16"/>
       <c r="B422" s="16"/>
-      <c r="L422" s="21"/>
+      <c r="L422" s="22"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
       <c r="A423" s="16"/>
       <c r="B423" s="16"/>
-      <c r="L423" s="21"/>
+      <c r="L423" s="22"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
       <c r="A424" s="16"/>
       <c r="B424" s="16"/>
-      <c r="L424" s="21"/>
+      <c r="L424" s="22"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
       <c r="A425" s="16"/>
       <c r="B425" s="16"/>
-      <c r="L425" s="21"/>
+      <c r="L425" s="22"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
       <c r="A426" s="16"/>
       <c r="B426" s="16"/>
-      <c r="L426" s="21"/>
+      <c r="L426" s="22"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="A427" s="16"/>
       <c r="B427" s="16"/>
-      <c r="L427" s="21"/>
+      <c r="L427" s="22"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="A428" s="16"/>
       <c r="B428" s="16"/>
-      <c r="L428" s="21"/>
+      <c r="L428" s="22"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="A429" s="16"/>
       <c r="B429" s="16"/>
-      <c r="L429" s="21"/>
+      <c r="L429" s="22"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="A430" s="16"/>
       <c r="B430" s="16"/>
-      <c r="L430" s="21"/>
+      <c r="L430" s="22"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="A431" s="16"/>
       <c r="B431" s="16"/>
-      <c r="L431" s="21"/>
+      <c r="L431" s="22"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="A432" s="16"/>
       <c r="B432" s="16"/>
-      <c r="L432" s="21"/>
+      <c r="L432" s="22"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="A433" s="16"/>
       <c r="B433" s="16"/>
-      <c r="L433" s="21"/>
+      <c r="L433" s="22"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="A434" s="16"/>
       <c r="B434" s="16"/>
-      <c r="L434" s="21"/>
+      <c r="L434" s="22"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="A435" s="16"/>
       <c r="B435" s="16"/>
-      <c r="L435" s="21"/>
+      <c r="L435" s="22"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="A436" s="16"/>
       <c r="B436" s="16"/>
-      <c r="L436" s="21"/>
+      <c r="L436" s="22"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="A437" s="16"/>
       <c r="B437" s="16"/>
-      <c r="L437" s="21"/>
+      <c r="L437" s="22"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="A438" s="16"/>
       <c r="B438" s="16"/>
-      <c r="L438" s="21"/>
+      <c r="L438" s="22"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
       <c r="A439" s="16"/>
       <c r="B439" s="16"/>
-      <c r="L439" s="21"/>
+      <c r="L439" s="22"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="A440" s="16"/>
       <c r="B440" s="16"/>
-      <c r="L440" s="21"/>
+      <c r="L440" s="22"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="A441" s="16"/>
       <c r="B441" s="16"/>
-      <c r="L441" s="21"/>
+      <c r="L441" s="22"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="A442" s="16"/>
       <c r="B442" s="16"/>
-      <c r="L442" s="21"/>
+      <c r="L442" s="22"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
       <c r="A443" s="16"/>
       <c r="B443" s="16"/>
-      <c r="L443" s="21"/>
+      <c r="L443" s="22"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="A444" s="16"/>
       <c r="B444" s="16"/>
-      <c r="L444" s="21"/>
+      <c r="L444" s="22"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="A445" s="16"/>
       <c r="B445" s="16"/>
-      <c r="L445" s="21"/>
+      <c r="L445" s="22"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="A446" s="16"/>
       <c r="B446" s="16"/>
-      <c r="L446" s="21"/>
+      <c r="L446" s="22"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="A447" s="16"/>
       <c r="B447" s="16"/>
-      <c r="L447" s="21"/>
+      <c r="L447" s="22"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="A448" s="16"/>
       <c r="B448" s="16"/>
-      <c r="L448" s="21"/>
+      <c r="L448" s="22"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="A449" s="16"/>
       <c r="B449" s="16"/>
-      <c r="L449" s="21"/>
+      <c r="L449" s="22"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="A450" s="16"/>
       <c r="B450" s="16"/>
-      <c r="L450" s="21"/>
+      <c r="L450" s="22"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="A451" s="16"/>
       <c r="B451" s="16"/>
-      <c r="L451" s="21"/>
+      <c r="L451" s="22"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="A452" s="16"/>
       <c r="B452" s="16"/>
-      <c r="L452" s="21"/>
+      <c r="L452" s="22"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="A453" s="16"/>
       <c r="B453" s="16"/>
-      <c r="L453" s="21"/>
+      <c r="L453" s="22"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="A454" s="16"/>
       <c r="B454" s="16"/>
-      <c r="L454" s="21"/>
+      <c r="L454" s="22"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="A455" s="16"/>
       <c r="B455" s="16"/>
-      <c r="L455" s="21"/>
+      <c r="L455" s="22"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="A456" s="16"/>
       <c r="B456" s="16"/>
-      <c r="L456" s="21"/>
+      <c r="L456" s="22"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="A457" s="16"/>
       <c r="B457" s="16"/>
-      <c r="L457" s="21"/>
+      <c r="L457" s="22"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="A458" s="16"/>
       <c r="B458" s="16"/>
-      <c r="L458" s="21"/>
+      <c r="L458" s="22"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="A459" s="16"/>
       <c r="B459" s="16"/>
-      <c r="L459" s="21"/>
+      <c r="L459" s="22"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="A460" s="16"/>
       <c r="B460" s="16"/>
-      <c r="L460" s="21"/>
+      <c r="L460" s="22"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="A461" s="16"/>
       <c r="B461" s="16"/>
-      <c r="L461" s="21"/>
+      <c r="L461" s="22"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="A462" s="16"/>
       <c r="B462" s="16"/>
-      <c r="L462" s="21"/>
+      <c r="L462" s="22"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
       <c r="A463" s="16"/>
       <c r="B463" s="16"/>
-      <c r="L463" s="21"/>
+      <c r="L463" s="22"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="A464" s="16"/>
       <c r="B464" s="16"/>
-      <c r="L464" s="21"/>
+      <c r="L464" s="22"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="A465" s="16"/>
       <c r="B465" s="16"/>
-      <c r="L465" s="21"/>
+      <c r="L465" s="22"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="A466" s="16"/>
       <c r="B466" s="16"/>
-      <c r="L466" s="21"/>
+      <c r="L466" s="22"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="A467" s="16"/>
       <c r="B467" s="16"/>
-      <c r="L467" s="21"/>
+      <c r="L467" s="22"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="A468" s="16"/>
       <c r="B468" s="16"/>
-      <c r="L468" s="21"/>
+      <c r="L468" s="22"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="A469" s="16"/>
       <c r="B469" s="16"/>
-      <c r="L469" s="21"/>
+      <c r="L469" s="22"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="A470" s="16"/>
       <c r="B470" s="16"/>
-      <c r="L470" s="21"/>
+      <c r="L470" s="22"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
       <c r="A471" s="16"/>
       <c r="B471" s="16"/>
-      <c r="L471" s="21"/>
+      <c r="L471" s="22"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="A472" s="16"/>
       <c r="B472" s="16"/>
-      <c r="L472" s="21"/>
+      <c r="L472" s="22"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="A473" s="16"/>
       <c r="B473" s="16"/>
-      <c r="L473" s="21"/>
+      <c r="L473" s="22"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="A474" s="16"/>
       <c r="B474" s="16"/>
-      <c r="L474" s="21"/>
+      <c r="L474" s="22"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
       <c r="A475" s="16"/>
       <c r="B475" s="16"/>
-      <c r="L475" s="21"/>
+      <c r="L475" s="22"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="A476" s="16"/>
       <c r="B476" s="16"/>
-      <c r="L476" s="21"/>
+      <c r="L476" s="22"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="A477" s="16"/>
       <c r="B477" s="16"/>
-      <c r="L477" s="21"/>
+      <c r="L477" s="22"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="A478" s="16"/>
       <c r="B478" s="16"/>
-      <c r="L478" s="21"/>
+      <c r="L478" s="22"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
       <c r="A479" s="16"/>
       <c r="B479" s="16"/>
-      <c r="L479" s="21"/>
+      <c r="L479" s="22"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="A480" s="16"/>
       <c r="B480" s="16"/>
-      <c r="L480" s="21"/>
+      <c r="L480" s="22"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="A481" s="16"/>
       <c r="B481" s="16"/>
-      <c r="L481" s="21"/>
+      <c r="L481" s="22"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="A482" s="16"/>
       <c r="B482" s="16"/>
-      <c r="L482" s="21"/>
+      <c r="L482" s="22"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="16"/>
       <c r="B483" s="16"/>
-      <c r="L483" s="21"/>
+      <c r="L483" s="22"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="A484" s="16"/>
       <c r="B484" s="16"/>
-      <c r="L484" s="21"/>
+      <c r="L484" s="22"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="A485" s="16"/>
       <c r="B485" s="16"/>
-      <c r="L485" s="21"/>
+      <c r="L485" s="22"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="A486" s="16"/>
       <c r="B486" s="16"/>
-      <c r="L486" s="21"/>
+      <c r="L486" s="22"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
       <c r="A487" s="16"/>
       <c r="B487" s="16"/>
-      <c r="L487" s="21"/>
+      <c r="L487" s="22"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="A488" s="16"/>
       <c r="B488" s="16"/>
-      <c r="L488" s="21"/>
+      <c r="L488" s="22"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="A489" s="16"/>
       <c r="B489" s="16"/>
-      <c r="L489" s="21"/>
+      <c r="L489" s="22"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="A490" s="16"/>
       <c r="B490" s="16"/>
-      <c r="L490" s="21"/>
+      <c r="L490" s="22"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
       <c r="A491" s="16"/>
       <c r="B491" s="16"/>
-      <c r="L491" s="21"/>
+      <c r="L491" s="22"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="A492" s="16"/>
       <c r="B492" s="16"/>
-      <c r="L492" s="21"/>
+      <c r="L492" s="22"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="A493" s="16"/>
       <c r="B493" s="16"/>
-      <c r="L493" s="21"/>
+      <c r="L493" s="22"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="A494" s="16"/>
       <c r="B494" s="16"/>
-      <c r="L494" s="21"/>
+      <c r="L494" s="22"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="A495" s="16"/>
       <c r="B495" s="16"/>
-      <c r="L495" s="21"/>
+      <c r="L495" s="22"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
       <c r="A496" s="16"/>
       <c r="B496" s="16"/>
-      <c r="L496" s="21"/>
+      <c r="L496" s="22"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
       <c r="A497" s="16"/>
       <c r="B497" s="16"/>
-      <c r="L497" s="21"/>
+      <c r="L497" s="22"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="A498" s="16"/>
       <c r="B498" s="16"/>
-      <c r="L498" s="21"/>
+      <c r="L498" s="22"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="A499" s="16"/>
       <c r="B499" s="16"/>
-      <c r="L499" s="21"/>
+      <c r="L499" s="22"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="A500" s="16"/>
       <c r="B500" s="16"/>
-      <c r="L500" s="21"/>
+      <c r="L500" s="22"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="A501" s="16"/>
       <c r="B501" s="16"/>
-      <c r="L501" s="21"/>
+      <c r="L501" s="22"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="A502" s="16"/>
       <c r="B502" s="16"/>
-      <c r="L502" s="21"/>
+      <c r="L502" s="22"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
       <c r="A503" s="16"/>
       <c r="B503" s="16"/>
-      <c r="L503" s="21"/>
+      <c r="L503" s="22"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="A504" s="16"/>
       <c r="B504" s="16"/>
-      <c r="L504" s="21"/>
+      <c r="L504" s="22"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="A505" s="16"/>
       <c r="B505" s="16"/>
-      <c r="L505" s="21"/>
+      <c r="L505" s="22"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="A506" s="16"/>
       <c r="B506" s="16"/>
-      <c r="L506" s="21"/>
+      <c r="L506" s="22"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="A507" s="16"/>
       <c r="B507" s="16"/>
-      <c r="L507" s="21"/>
+      <c r="L507" s="22"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="A508" s="16"/>
       <c r="B508" s="16"/>
-      <c r="L508" s="21"/>
+      <c r="L508" s="22"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="A509" s="16"/>
       <c r="B509" s="16"/>
-      <c r="L509" s="21"/>
+      <c r="L509" s="22"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="A510" s="16"/>
       <c r="B510" s="16"/>
-      <c r="L510" s="21"/>
+      <c r="L510" s="22"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="A511" s="16"/>
       <c r="B511" s="16"/>
-      <c r="L511" s="21"/>
+      <c r="L511" s="22"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="A512" s="16"/>
       <c r="B512" s="16"/>
-      <c r="L512" s="21"/>
+      <c r="L512" s="22"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="A513" s="16"/>
       <c r="B513" s="16"/>
-      <c r="L513" s="21"/>
+      <c r="L513" s="22"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="A514" s="16"/>
       <c r="B514" s="16"/>
-      <c r="L514" s="21"/>
+      <c r="L514" s="22"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="A515" s="16"/>
       <c r="B515" s="16"/>
-      <c r="L515" s="21"/>
+      <c r="L515" s="22"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="A516" s="16"/>
       <c r="B516" s="16"/>
-      <c r="L516" s="21"/>
+      <c r="L516" s="22"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="A517" s="16"/>
       <c r="B517" s="16"/>
-      <c r="L517" s="21"/>
+      <c r="L517" s="22"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="A518" s="16"/>
       <c r="B518" s="16"/>
-      <c r="L518" s="21"/>
+      <c r="L518" s="22"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="A519" s="16"/>
       <c r="B519" s="16"/>
-      <c r="L519" s="21"/>
+      <c r="L519" s="22"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="A520" s="16"/>
       <c r="B520" s="16"/>
-      <c r="L520" s="21"/>
+      <c r="L520" s="22"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="A521" s="16"/>
       <c r="B521" s="16"/>
-      <c r="L521" s="21"/>
+      <c r="L521" s="22"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="A522" s="16"/>
       <c r="B522" s="16"/>
-      <c r="L522" s="21"/>
+      <c r="L522" s="22"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="A523" s="16"/>
       <c r="B523" s="16"/>
-      <c r="L523" s="21"/>
+      <c r="L523" s="22"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
       <c r="A524" s="16"/>
       <c r="B524" s="16"/>
-      <c r="L524" s="21"/>
+      <c r="L524" s="22"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
       <c r="A525" s="16"/>
       <c r="B525" s="16"/>
-      <c r="L525" s="21"/>
+      <c r="L525" s="22"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="A526" s="16"/>
       <c r="B526" s="16"/>
-      <c r="L526" s="21"/>
+      <c r="L526" s="22"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="A527" s="16"/>
       <c r="B527" s="16"/>
-      <c r="L527" s="21"/>
+      <c r="L527" s="22"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
       <c r="A528" s="16"/>
       <c r="B528" s="16"/>
-      <c r="L528" s="21"/>
+      <c r="L528" s="22"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
       <c r="A529" s="16"/>
       <c r="B529" s="16"/>
-      <c r="L529" s="21"/>
+      <c r="L529" s="22"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="A530" s="16"/>
       <c r="B530" s="16"/>
-      <c r="L530" s="21"/>
+      <c r="L530" s="22"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="A531" s="16"/>
       <c r="B531" s="16"/>
-      <c r="L531" s="21"/>
+      <c r="L531" s="22"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
       <c r="A532" s="16"/>
       <c r="B532" s="16"/>
-      <c r="L532" s="21"/>
+      <c r="L532" s="22"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
       <c r="A533" s="16"/>
       <c r="B533" s="16"/>
-      <c r="L533" s="21"/>
+      <c r="L533" s="22"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
       <c r="A534" s="16"/>
       <c r="B534" s="16"/>
-      <c r="L534" s="21"/>
+      <c r="L534" s="22"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="A535" s="16"/>
       <c r="B535" s="16"/>
-      <c r="L535" s="21"/>
+      <c r="L535" s="22"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="A536" s="16"/>
       <c r="B536" s="16"/>
-      <c r="L536" s="21"/>
+      <c r="L536" s="22"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
       <c r="A537" s="16"/>
       <c r="B537" s="16"/>
-      <c r="L537" s="21"/>
+      <c r="L537" s="22"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
       <c r="A538" s="16"/>
       <c r="B538" s="16"/>
-      <c r="L538" s="21"/>
+      <c r="L538" s="22"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
       <c r="A539" s="16"/>
       <c r="B539" s="16"/>
-      <c r="L539" s="21"/>
+      <c r="L539" s="22"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
       <c r="A540" s="16"/>
       <c r="B540" s="16"/>
-      <c r="L540" s="21"/>
+      <c r="L540" s="22"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
       <c r="A541" s="16"/>
       <c r="B541" s="16"/>
-      <c r="L541" s="21"/>
+      <c r="L541" s="22"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
       <c r="A542" s="16"/>
       <c r="B542" s="16"/>
-      <c r="L542" s="21"/>
+      <c r="L542" s="22"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
       <c r="A543" s="16"/>
       <c r="B543" s="16"/>
-      <c r="L543" s="21"/>
+      <c r="L543" s="22"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="A544" s="16"/>
       <c r="B544" s="16"/>
-      <c r="L544" s="21"/>
+      <c r="L544" s="22"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="A545" s="16"/>
       <c r="B545" s="16"/>
-      <c r="L545" s="21"/>
+      <c r="L545" s="22"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="A546" s="16"/>
       <c r="B546" s="16"/>
-      <c r="L546" s="21"/>
+      <c r="L546" s="22"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="A547" s="16"/>
       <c r="B547" s="16"/>
-      <c r="L547" s="21"/>
+      <c r="L547" s="22"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="A548" s="16"/>
       <c r="B548" s="16"/>
-      <c r="L548" s="21"/>
+      <c r="L548" s="22"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="A549" s="16"/>
       <c r="B549" s="16"/>
-      <c r="L549" s="21"/>
+      <c r="L549" s="22"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="A550" s="16"/>
       <c r="B550" s="16"/>
-      <c r="L550" s="21"/>
+      <c r="L550" s="22"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="A551" s="16"/>
       <c r="B551" s="16"/>
-      <c r="L551" s="21"/>
+      <c r="L551" s="22"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="A552" s="16"/>
       <c r="B552" s="16"/>
-      <c r="L552" s="21"/>
+      <c r="L552" s="22"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="A553" s="16"/>
       <c r="B553" s="16"/>
-      <c r="L553" s="21"/>
+      <c r="L553" s="22"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="A554" s="16"/>
       <c r="B554" s="16"/>
-      <c r="L554" s="21"/>
+      <c r="L554" s="22"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="A555" s="16"/>
       <c r="B555" s="16"/>
-      <c r="L555" s="21"/>
+      <c r="L555" s="22"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="A556" s="16"/>
       <c r="B556" s="16"/>
-      <c r="L556" s="21"/>
+      <c r="L556" s="22"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="A557" s="16"/>
       <c r="B557" s="16"/>
-      <c r="L557" s="21"/>
+      <c r="L557" s="22"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="A558" s="16"/>
       <c r="B558" s="16"/>
-      <c r="L558" s="21"/>
+      <c r="L558" s="22"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="A559" s="16"/>
       <c r="B559" s="16"/>
-      <c r="L559" s="21"/>
+      <c r="L559" s="22"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="A560" s="16"/>
       <c r="B560" s="16"/>
-      <c r="L560" s="21"/>
+      <c r="L560" s="22"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="A561" s="16"/>
       <c r="B561" s="16"/>
-      <c r="L561" s="21"/>
+      <c r="L561" s="22"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="A562" s="16"/>
       <c r="B562" s="16"/>
-      <c r="L562" s="21"/>
+      <c r="L562" s="22"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
       <c r="A563" s="16"/>
       <c r="B563" s="16"/>
-      <c r="L563" s="21"/>
+      <c r="L563" s="22"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
       <c r="A564" s="16"/>
       <c r="B564" s="16"/>
-      <c r="L564" s="21"/>
+      <c r="L564" s="22"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
       <c r="A565" s="16"/>
       <c r="B565" s="16"/>
-      <c r="L565" s="21"/>
+      <c r="L565" s="22"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
       <c r="A566" s="16"/>
       <c r="B566" s="16"/>
-      <c r="L566" s="21"/>
+      <c r="L566" s="22"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
       <c r="A567" s="16"/>
       <c r="B567" s="16"/>
-      <c r="L567" s="21"/>
+      <c r="L567" s="22"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
       <c r="A568" s="16"/>
       <c r="B568" s="16"/>
-      <c r="L568" s="21"/>
+      <c r="L568" s="22"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
       <c r="A569" s="16"/>
       <c r="B569" s="16"/>
-      <c r="L569" s="21"/>
+      <c r="L569" s="22"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
       <c r="A570" s="16"/>
       <c r="B570" s="16"/>
-      <c r="L570" s="21"/>
+      <c r="L570" s="22"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
       <c r="A571" s="16"/>
       <c r="B571" s="16"/>
-      <c r="L571" s="21"/>
+      <c r="L571" s="22"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
       <c r="A572" s="16"/>
       <c r="B572" s="16"/>
-      <c r="L572" s="21"/>
+      <c r="L572" s="22"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
       <c r="A573" s="16"/>
       <c r="B573" s="16"/>
-      <c r="L573" s="21"/>
+      <c r="L573" s="22"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
       <c r="A574" s="16"/>
       <c r="B574" s="16"/>
-      <c r="L574" s="21"/>
+      <c r="L574" s="22"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
       <c r="A575" s="16"/>
       <c r="B575" s="16"/>
-      <c r="L575" s="21"/>
+      <c r="L575" s="22"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
       <c r="A576" s="16"/>
       <c r="B576" s="16"/>
-      <c r="L576" s="21"/>
+      <c r="L576" s="22"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
       <c r="A577" s="16"/>
       <c r="B577" s="16"/>
-      <c r="L577" s="21"/>
+      <c r="L577" s="22"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
       <c r="A578" s="16"/>
       <c r="B578" s="16"/>
-      <c r="L578" s="21"/>
+      <c r="L578" s="22"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
       <c r="A579" s="16"/>
       <c r="B579" s="16"/>
-      <c r="L579" s="21"/>
+      <c r="L579" s="22"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
       <c r="A580" s="16"/>
       <c r="B580" s="16"/>
-      <c r="L580" s="21"/>
+      <c r="L580" s="22"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
       <c r="A581" s="16"/>
       <c r="B581" s="16"/>
-      <c r="L581" s="21"/>
+      <c r="L581" s="22"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
       <c r="A582" s="16"/>
       <c r="B582" s="16"/>
-      <c r="L582" s="21"/>
+      <c r="L582" s="22"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
       <c r="A583" s="16"/>
       <c r="B583" s="16"/>
-      <c r="L583" s="21"/>
+      <c r="L583" s="22"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
       <c r="A584" s="16"/>
       <c r="B584" s="16"/>
-      <c r="L584" s="21"/>
+      <c r="L584" s="22"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
       <c r="A585" s="16"/>
       <c r="B585" s="16"/>
-      <c r="L585" s="21"/>
+      <c r="L585" s="22"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
       <c r="A586" s="16"/>
       <c r="B586" s="16"/>
-      <c r="L586" s="21"/>
+      <c r="L586" s="22"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="A587" s="16"/>
       <c r="B587" s="16"/>
-      <c r="L587" s="21"/>
+      <c r="L587" s="22"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="A588" s="16"/>
       <c r="B588" s="16"/>
-      <c r="L588" s="21"/>
+      <c r="L588" s="22"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="A589" s="16"/>
       <c r="B589" s="16"/>
-      <c r="L589" s="21"/>
+      <c r="L589" s="22"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="A590" s="16"/>
       <c r="B590" s="16"/>
-      <c r="L590" s="21"/>
+      <c r="L590" s="22"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="A591" s="16"/>
       <c r="B591" s="16"/>
-      <c r="L591" s="21"/>
+      <c r="L591" s="22"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
       <c r="A592" s="16"/>
       <c r="B592" s="16"/>
-      <c r="L592" s="21"/>
+      <c r="L592" s="22"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
       <c r="A593" s="16"/>
       <c r="B593" s="16"/>
-      <c r="L593" s="21"/>
+      <c r="L593" s="22"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="A594" s="16"/>
       <c r="B594" s="16"/>
-      <c r="L594" s="21"/>
+      <c r="L594" s="22"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="A595" s="16"/>
       <c r="B595" s="16"/>
-      <c r="L595" s="21"/>
+      <c r="L595" s="22"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="A596" s="16"/>
       <c r="B596" s="16"/>
-      <c r="L596" s="21"/>
+      <c r="L596" s="22"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="A597" s="16"/>
       <c r="B597" s="16"/>
-      <c r="L597" s="21"/>
+      <c r="L597" s="22"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="A598" s="16"/>
       <c r="B598" s="16"/>
-      <c r="L598" s="21"/>
+      <c r="L598" s="22"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="A599" s="16"/>
       <c r="B599" s="16"/>
-      <c r="L599" s="21"/>
+      <c r="L599" s="22"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
       <c r="A600" s="16"/>
       <c r="B600" s="16"/>
-      <c r="L600" s="21"/>
+      <c r="L600" s="22"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
       <c r="A601" s="16"/>
       <c r="B601" s="16"/>
-      <c r="L601" s="21"/>
+      <c r="L601" s="22"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
       <c r="A602" s="16"/>
       <c r="B602" s="16"/>
-      <c r="L602" s="21"/>
+      <c r="L602" s="22"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
       <c r="A603" s="16"/>
       <c r="B603" s="16"/>
-      <c r="L603" s="21"/>
+      <c r="L603" s="22"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="A604" s="16"/>
       <c r="B604" s="16"/>
-      <c r="L604" s="21"/>
+      <c r="L604" s="22"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="A605" s="16"/>
       <c r="B605" s="16"/>
-      <c r="L605" s="21"/>
+      <c r="L605" s="22"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="A606" s="16"/>
       <c r="B606" s="16"/>
-      <c r="L606" s="21"/>
+      <c r="L606" s="22"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="A607" s="16"/>
       <c r="B607" s="16"/>
-      <c r="L607" s="21"/>
+      <c r="L607" s="22"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
       <c r="A608" s="16"/>
       <c r="B608" s="16"/>
-      <c r="L608" s="21"/>
+      <c r="L608" s="22"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
       <c r="A609" s="16"/>
       <c r="B609" s="16"/>
-      <c r="L609" s="21"/>
+      <c r="L609" s="22"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
       <c r="A610" s="16"/>
       <c r="B610" s="16"/>
-      <c r="L610" s="21"/>
+      <c r="L610" s="22"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="A611" s="16"/>
       <c r="B611" s="16"/>
-      <c r="L611" s="21"/>
+      <c r="L611" s="22"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="A612" s="16"/>
       <c r="B612" s="16"/>
-      <c r="L612" s="21"/>
+      <c r="L612" s="22"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="A613" s="16"/>
       <c r="B613" s="16"/>
-      <c r="L613" s="21"/>
+      <c r="L613" s="22"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="A614" s="16"/>
       <c r="B614" s="16"/>
-      <c r="L614" s="21"/>
+      <c r="L614" s="22"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="A615" s="16"/>
       <c r="B615" s="16"/>
-      <c r="L615" s="21"/>
+      <c r="L615" s="22"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
       <c r="A616" s="16"/>
       <c r="B616" s="16"/>
-      <c r="L616" s="21"/>
+      <c r="L616" s="22"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
       <c r="A617" s="16"/>
       <c r="B617" s="16"/>
-      <c r="L617" s="21"/>
+      <c r="L617" s="22"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
       <c r="A618" s="16"/>
       <c r="B618" s="16"/>
-      <c r="L618" s="21"/>
+      <c r="L618" s="22"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="A619" s="16"/>
       <c r="B619" s="16"/>
-      <c r="L619" s="21"/>
+      <c r="L619" s="22"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="A620" s="16"/>
       <c r="B620" s="16"/>
-      <c r="L620" s="21"/>
+      <c r="L620" s="22"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="A621" s="16"/>
       <c r="B621" s="16"/>
-      <c r="L621" s="21"/>
+      <c r="L621" s="22"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="A622" s="16"/>
       <c r="B622" s="16"/>
-      <c r="L622" s="21"/>
+      <c r="L622" s="22"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
       <c r="A623" s="16"/>
       <c r="B623" s="16"/>
-      <c r="L623" s="21"/>
+      <c r="L623" s="22"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="A624" s="16"/>
       <c r="B624" s="16"/>
-      <c r="L624" s="21"/>
+      <c r="L624" s="22"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
       <c r="A625" s="16"/>
       <c r="B625" s="16"/>
-      <c r="L625" s="21"/>
+      <c r="L625" s="22"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="A626" s="16"/>
       <c r="B626" s="16"/>
-      <c r="L626" s="21"/>
+      <c r="L626" s="22"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="A627" s="16"/>
       <c r="B627" s="16"/>
-      <c r="L627" s="21"/>
+      <c r="L627" s="22"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="A628" s="16"/>
       <c r="B628" s="16"/>
-      <c r="L628" s="21"/>
+      <c r="L628" s="22"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="A629" s="16"/>
       <c r="B629" s="16"/>
-      <c r="L629" s="21"/>
+      <c r="L629" s="22"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="A630" s="16"/>
       <c r="B630" s="16"/>
-      <c r="L630" s="21"/>
+      <c r="L630" s="22"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="A631" s="16"/>
       <c r="B631" s="16"/>
-      <c r="L631" s="21"/>
+      <c r="L631" s="22"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
       <c r="A632" s="16"/>
       <c r="B632" s="16"/>
-      <c r="L632" s="21"/>
+      <c r="L632" s="22"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
       <c r="A633" s="16"/>
       <c r="B633" s="16"/>
-      <c r="L633" s="21"/>
+      <c r="L633" s="22"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
       <c r="A634" s="16"/>
       <c r="B634" s="16"/>
-      <c r="L634" s="21"/>
+      <c r="L634" s="22"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="A635" s="16"/>
       <c r="B635" s="16"/>
-      <c r="L635" s="21"/>
+      <c r="L635" s="22"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="A636" s="16"/>
       <c r="B636" s="16"/>
-      <c r="L636" s="21"/>
+      <c r="L636" s="22"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="A637" s="16"/>
       <c r="B637" s="16"/>
-      <c r="L637" s="21"/>
+      <c r="L637" s="22"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="A638" s="16"/>
       <c r="B638" s="16"/>
-      <c r="L638" s="21"/>
+      <c r="L638" s="22"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="A639" s="16"/>
       <c r="B639" s="16"/>
-      <c r="L639" s="21"/>
+      <c r="L639" s="22"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="A640" s="16"/>
       <c r="B640" s="16"/>
-      <c r="L640" s="21"/>
+      <c r="L640" s="22"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="A641" s="16"/>
       <c r="B641" s="16"/>
-      <c r="L641" s="21"/>
+      <c r="L641" s="22"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="A642" s="16"/>
       <c r="B642" s="16"/>
-      <c r="L642" s="21"/>
+      <c r="L642" s="22"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
       <c r="A643" s="16"/>
       <c r="B643" s="16"/>
-      <c r="L643" s="21"/>
+      <c r="L643" s="22"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
       <c r="A644" s="16"/>
       <c r="B644" s="16"/>
-      <c r="L644" s="21"/>
+      <c r="L644" s="22"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
       <c r="A645" s="16"/>
       <c r="B645" s="16"/>
-      <c r="L645" s="21"/>
+      <c r="L645" s="22"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
       <c r="A646" s="16"/>
       <c r="B646" s="16"/>
-      <c r="L646" s="21"/>
+      <c r="L646" s="22"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
       <c r="A647" s="16"/>
       <c r="B647" s="16"/>
-      <c r="L647" s="21"/>
+      <c r="L647" s="22"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
       <c r="A648" s="16"/>
       <c r="B648" s="16"/>
-      <c r="L648" s="21"/>
+      <c r="L648" s="22"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
       <c r="A649" s="16"/>
       <c r="B649" s="16"/>
-      <c r="L649" s="21"/>
+      <c r="L649" s="22"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
       <c r="A650" s="16"/>
       <c r="B650" s="16"/>
-      <c r="L650" s="21"/>
+      <c r="L650" s="22"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
       <c r="A651" s="16"/>
       <c r="B651" s="16"/>
-      <c r="L651" s="21"/>
+      <c r="L651" s="22"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
       <c r="A652" s="16"/>
       <c r="B652" s="16"/>
-      <c r="L652" s="21"/>
+      <c r="L652" s="22"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
       <c r="A653" s="16"/>
       <c r="B653" s="16"/>
-      <c r="L653" s="21"/>
+      <c r="L653" s="22"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
       <c r="A654" s="16"/>
       <c r="B654" s="16"/>
-      <c r="L654" s="21"/>
+      <c r="L654" s="22"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
       <c r="A655" s="16"/>
       <c r="B655" s="16"/>
-      <c r="L655" s="21"/>
+      <c r="L655" s="22"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
       <c r="A656" s="16"/>
       <c r="B656" s="16"/>
-      <c r="L656" s="21"/>
+      <c r="L656" s="22"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
       <c r="A657" s="16"/>
       <c r="B657" s="16"/>
-      <c r="L657" s="21"/>
+      <c r="L657" s="22"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
       <c r="A658" s="16"/>
       <c r="B658" s="16"/>
-      <c r="L658" s="21"/>
+      <c r="L658" s="22"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
       <c r="A659" s="16"/>
       <c r="B659" s="16"/>
-      <c r="L659" s="21"/>
+      <c r="L659" s="22"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
       <c r="A660" s="16"/>
       <c r="B660" s="16"/>
-      <c r="L660" s="21"/>
+      <c r="L660" s="22"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
       <c r="A661" s="16"/>
       <c r="B661" s="16"/>
-      <c r="L661" s="21"/>
+      <c r="L661" s="22"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
       <c r="A662" s="16"/>
       <c r="B662" s="16"/>
-      <c r="L662" s="21"/>
+      <c r="L662" s="22"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
       <c r="A663" s="16"/>
       <c r="B663" s="16"/>
-      <c r="L663" s="21"/>
+      <c r="L663" s="22"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
       <c r="A664" s="16"/>
       <c r="B664" s="16"/>
-      <c r="L664" s="21"/>
+      <c r="L664" s="22"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
       <c r="A665" s="16"/>
       <c r="B665" s="16"/>
-      <c r="L665" s="21"/>
+      <c r="L665" s="22"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
       <c r="A666" s="16"/>
       <c r="B666" s="16"/>
-      <c r="L666" s="21"/>
+      <c r="L666" s="22"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
       <c r="A667" s="16"/>
       <c r="B667" s="16"/>
-      <c r="L667" s="21"/>
+      <c r="L667" s="22"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
       <c r="A668" s="16"/>
       <c r="B668" s="16"/>
-      <c r="L668" s="21"/>
+      <c r="L668" s="22"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
       <c r="A669" s="16"/>
       <c r="B669" s="16"/>
-      <c r="L669" s="21"/>
+      <c r="L669" s="22"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
       <c r="A670" s="16"/>
       <c r="B670" s="16"/>
-      <c r="L670" s="21"/>
+      <c r="L670" s="22"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
       <c r="A671" s="16"/>
       <c r="B671" s="16"/>
-      <c r="L671" s="21"/>
+      <c r="L671" s="22"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
       <c r="A672" s="16"/>
       <c r="B672" s="16"/>
-      <c r="L672" s="21"/>
+      <c r="L672" s="22"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
       <c r="A673" s="16"/>
       <c r="B673" s="16"/>
-      <c r="L673" s="21"/>
+      <c r="L673" s="22"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
       <c r="A674" s="16"/>
       <c r="B674" s="16"/>
-      <c r="L674" s="21"/>
+      <c r="L674" s="22"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
       <c r="A675" s="16"/>
       <c r="B675" s="16"/>
-      <c r="L675" s="21"/>
+      <c r="L675" s="22"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
       <c r="A676" s="16"/>
       <c r="B676" s="16"/>
-      <c r="L676" s="21"/>
+      <c r="L676" s="22"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
       <c r="A677" s="16"/>
       <c r="B677" s="16"/>
-      <c r="L677" s="21"/>
+      <c r="L677" s="22"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
       <c r="A678" s="16"/>
       <c r="B678" s="16"/>
-      <c r="L678" s="21"/>
+      <c r="L678" s="22"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
       <c r="A679" s="16"/>
       <c r="B679" s="16"/>
-      <c r="L679" s="21"/>
+      <c r="L679" s="22"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
       <c r="A680" s="16"/>
       <c r="B680" s="16"/>
-      <c r="L680" s="21"/>
+      <c r="L680" s="22"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
       <c r="A681" s="16"/>
       <c r="B681" s="16"/>
-      <c r="L681" s="21"/>
+      <c r="L681" s="22"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
       <c r="A682" s="16"/>
       <c r="B682" s="16"/>
-      <c r="L682" s="21"/>
+      <c r="L682" s="22"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
       <c r="A683" s="16"/>
       <c r="B683" s="16"/>
-      <c r="L683" s="21"/>
+      <c r="L683" s="22"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
       <c r="A684" s="16"/>
       <c r="B684" s="16"/>
-      <c r="L684" s="21"/>
+      <c r="L684" s="22"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
       <c r="A685" s="16"/>
       <c r="B685" s="16"/>
-      <c r="L685" s="21"/>
+      <c r="L685" s="22"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
       <c r="A686" s="16"/>
       <c r="B686" s="16"/>
-      <c r="L686" s="21"/>
+      <c r="L686" s="22"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
       <c r="A687" s="16"/>
       <c r="B687" s="16"/>
-      <c r="L687" s="21"/>
+      <c r="L687" s="22"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
       <c r="A688" s="16"/>
       <c r="B688" s="16"/>
-      <c r="L688" s="21"/>
+      <c r="L688" s="22"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
       <c r="A689" s="16"/>
       <c r="B689" s="16"/>
-      <c r="L689" s="21"/>
+      <c r="L689" s="22"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
       <c r="A690" s="16"/>
       <c r="B690" s="16"/>
-      <c r="L690" s="21"/>
+      <c r="L690" s="22"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
       <c r="A691" s="16"/>
       <c r="B691" s="16"/>
-      <c r="L691" s="21"/>
+      <c r="L691" s="22"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
       <c r="A692" s="16"/>
       <c r="B692" s="16"/>
-      <c r="L692" s="21"/>
+      <c r="L692" s="22"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
       <c r="A693" s="16"/>
       <c r="B693" s="16"/>
-      <c r="L693" s="21"/>
+      <c r="L693" s="22"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
       <c r="A694" s="16"/>
       <c r="B694" s="16"/>
-      <c r="L694" s="21"/>
+      <c r="L694" s="22"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
       <c r="A695" s="16"/>
       <c r="B695" s="16"/>
-      <c r="L695" s="21"/>
+      <c r="L695" s="22"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
       <c r="A696" s="16"/>
       <c r="B696" s="16"/>
-      <c r="L696" s="21"/>
+      <c r="L696" s="22"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
       <c r="A697" s="16"/>
       <c r="B697" s="16"/>
-      <c r="L697" s="21"/>
+      <c r="L697" s="22"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
       <c r="A698" s="16"/>
       <c r="B698" s="16"/>
-      <c r="L698" s="21"/>
+      <c r="L698" s="22"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
       <c r="A699" s="16"/>
       <c r="B699" s="16"/>
-      <c r="L699" s="21"/>
+      <c r="L699" s="22"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
       <c r="A700" s="16"/>
       <c r="B700" s="16"/>
-      <c r="L700" s="21"/>
+      <c r="L700" s="22"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
       <c r="A701" s="16"/>
       <c r="B701" s="16"/>
-      <c r="L701" s="21"/>
+      <c r="L701" s="22"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
       <c r="A702" s="16"/>
       <c r="B702" s="16"/>
-      <c r="L702" s="21"/>
+      <c r="L702" s="22"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
       <c r="A703" s="16"/>
       <c r="B703" s="16"/>
-      <c r="L703" s="21"/>
+      <c r="L703" s="22"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
       <c r="A704" s="16"/>
       <c r="B704" s="16"/>
-      <c r="L704" s="21"/>
+      <c r="L704" s="22"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
       <c r="A705" s="16"/>
       <c r="B705" s="16"/>
-      <c r="L705" s="21"/>
+      <c r="L705" s="22"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
       <c r="A706" s="16"/>
       <c r="B706" s="16"/>
-      <c r="L706" s="21"/>
+      <c r="L706" s="22"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
       <c r="A707" s="16"/>
       <c r="B707" s="16"/>
-      <c r="L707" s="21"/>
+      <c r="L707" s="22"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
       <c r="A708" s="16"/>
       <c r="B708" s="16"/>
-      <c r="L708" s="21"/>
+      <c r="L708" s="22"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
       <c r="A709" s="16"/>
       <c r="B709" s="16"/>
-      <c r="L709" s="21"/>
+      <c r="L709" s="22"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
       <c r="A710" s="16"/>
       <c r="B710" s="16"/>
-      <c r="L710" s="21"/>
+      <c r="L710" s="22"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
       <c r="A711" s="16"/>
       <c r="B711" s="16"/>
-      <c r="L711" s="21"/>
+      <c r="L711" s="22"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
       <c r="A712" s="16"/>
       <c r="B712" s="16"/>
-      <c r="L712" s="21"/>
+      <c r="L712" s="22"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
       <c r="A713" s="16"/>
       <c r="B713" s="16"/>
-      <c r="L713" s="21"/>
+      <c r="L713" s="22"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
       <c r="A714" s="16"/>
       <c r="B714" s="16"/>
-      <c r="L714" s="21"/>
+      <c r="L714" s="22"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
       <c r="A715" s="16"/>
       <c r="B715" s="16"/>
-      <c r="L715" s="21"/>
+      <c r="L715" s="22"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
       <c r="A716" s="16"/>
       <c r="B716" s="16"/>
-      <c r="L716" s="21"/>
+      <c r="L716" s="22"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
       <c r="A717" s="16"/>
       <c r="B717" s="16"/>
-      <c r="L717" s="21"/>
+      <c r="L717" s="22"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
       <c r="A718" s="16"/>
       <c r="B718" s="16"/>
-      <c r="L718" s="21"/>
+      <c r="L718" s="22"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
       <c r="A719" s="16"/>
       <c r="B719" s="16"/>
-      <c r="L719" s="21"/>
+      <c r="L719" s="22"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
       <c r="A720" s="16"/>
       <c r="B720" s="16"/>
-      <c r="L720" s="21"/>
+      <c r="L720" s="22"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
       <c r="A721" s="16"/>
       <c r="B721" s="16"/>
-      <c r="L721" s="21"/>
+      <c r="L721" s="22"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
       <c r="A722" s="16"/>
       <c r="B722" s="16"/>
-      <c r="L722" s="21"/>
+      <c r="L722" s="22"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
       <c r="A723" s="16"/>
       <c r="B723" s="16"/>
-      <c r="L723" s="21"/>
+      <c r="L723" s="22"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
       <c r="A724" s="16"/>
       <c r="B724" s="16"/>
-      <c r="L724" s="21"/>
+      <c r="L724" s="22"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
       <c r="A725" s="16"/>
       <c r="B725" s="16"/>
-      <c r="L725" s="21"/>
+      <c r="L725" s="22"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
       <c r="A726" s="16"/>
       <c r="B726" s="16"/>
-      <c r="L726" s="21"/>
+      <c r="L726" s="22"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
       <c r="A727" s="16"/>
       <c r="B727" s="16"/>
-      <c r="L727" s="21"/>
+      <c r="L727" s="22"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
       <c r="A728" s="16"/>
       <c r="B728" s="16"/>
-      <c r="L728" s="21"/>
+      <c r="L728" s="22"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
       <c r="A729" s="16"/>
       <c r="B729" s="16"/>
-      <c r="L729" s="21"/>
+      <c r="L729" s="22"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
       <c r="A730" s="16"/>
       <c r="B730" s="16"/>
-      <c r="L730" s="21"/>
+      <c r="L730" s="22"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
       <c r="A731" s="16"/>
       <c r="B731" s="16"/>
-      <c r="L731" s="21"/>
+      <c r="L731" s="22"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
       <c r="A732" s="16"/>
       <c r="B732" s="16"/>
-      <c r="L732" s="21"/>
+      <c r="L732" s="22"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
       <c r="A733" s="16"/>
       <c r="B733" s="16"/>
-      <c r="L733" s="21"/>
+      <c r="L733" s="22"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
       <c r="A734" s="16"/>
       <c r="B734" s="16"/>
-      <c r="L734" s="21"/>
+      <c r="L734" s="22"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
       <c r="A735" s="16"/>
       <c r="B735" s="16"/>
-      <c r="L735" s="21"/>
+      <c r="L735" s="22"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
       <c r="A736" s="16"/>
       <c r="B736" s="16"/>
-      <c r="L736" s="21"/>
+      <c r="L736" s="22"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
       <c r="A737" s="16"/>
       <c r="B737" s="16"/>
-      <c r="L737" s="21"/>
+      <c r="L737" s="22"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
       <c r="A738" s="16"/>
       <c r="B738" s="16"/>
-      <c r="L738" s="21"/>
+      <c r="L738" s="22"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
       <c r="A739" s="16"/>
       <c r="B739" s="16"/>
-      <c r="L739" s="21"/>
+      <c r="L739" s="22"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
       <c r="A740" s="16"/>
       <c r="B740" s="16"/>
-      <c r="L740" s="21"/>
+      <c r="L740" s="22"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
       <c r="A741" s="16"/>
       <c r="B741" s="16"/>
-      <c r="L741" s="21"/>
+      <c r="L741" s="22"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
       <c r="A742" s="16"/>
       <c r="B742" s="16"/>
-      <c r="L742" s="21"/>
+      <c r="L742" s="22"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
       <c r="A743" s="16"/>
       <c r="B743" s="16"/>
-      <c r="L743" s="21"/>
+      <c r="L743" s="22"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
       <c r="A744" s="16"/>
       <c r="B744" s="16"/>
-      <c r="L744" s="21"/>
+      <c r="L744" s="22"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
       <c r="A745" s="16"/>
       <c r="B745" s="16"/>
-      <c r="L745" s="21"/>
+      <c r="L745" s="22"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
       <c r="A746" s="16"/>
       <c r="B746" s="16"/>
-      <c r="L746" s="21"/>
+      <c r="L746" s="22"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
       <c r="A747" s="16"/>
       <c r="B747" s="16"/>
-      <c r="L747" s="21"/>
+      <c r="L747" s="22"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
       <c r="A748" s="16"/>
       <c r="B748" s="16"/>
-      <c r="L748" s="21"/>
+      <c r="L748" s="22"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
       <c r="A749" s="16"/>
       <c r="B749" s="16"/>
-      <c r="L749" s="21"/>
+      <c r="L749" s="22"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
       <c r="A750" s="16"/>
       <c r="B750" s="16"/>
-      <c r="L750" s="21"/>
+      <c r="L750" s="22"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
       <c r="A751" s="16"/>
       <c r="B751" s="16"/>
-      <c r="L751" s="21"/>
+      <c r="L751" s="22"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
       <c r="A752" s="16"/>
       <c r="B752" s="16"/>
-      <c r="L752" s="21"/>
+      <c r="L752" s="22"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
       <c r="A753" s="16"/>
       <c r="B753" s="16"/>
-      <c r="L753" s="21"/>
+      <c r="L753" s="22"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
       <c r="A754" s="16"/>
       <c r="B754" s="16"/>
-      <c r="L754" s="21"/>
+      <c r="L754" s="22"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
       <c r="A755" s="16"/>
       <c r="B755" s="16"/>
-      <c r="L755" s="21"/>
+      <c r="L755" s="22"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
       <c r="A756" s="16"/>
       <c r="B756" s="16"/>
-      <c r="L756" s="21"/>
+      <c r="L756" s="22"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
       <c r="A757" s="16"/>
       <c r="B757" s="16"/>
-      <c r="L757" s="21"/>
+      <c r="L757" s="22"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
       <c r="A758" s="16"/>
       <c r="B758" s="16"/>
-      <c r="L758" s="21"/>
+      <c r="L758" s="22"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
       <c r="A759" s="16"/>
       <c r="B759" s="16"/>
-      <c r="L759" s="21"/>
+      <c r="L759" s="22"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
       <c r="A760" s="16"/>
       <c r="B760" s="16"/>
-      <c r="L760" s="21"/>
+      <c r="L760" s="22"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
       <c r="A761" s="16"/>
       <c r="B761" s="16"/>
-      <c r="L761" s="21"/>
+      <c r="L761" s="22"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
       <c r="A762" s="16"/>
       <c r="B762" s="16"/>
-      <c r="L762" s="21"/>
+      <c r="L762" s="22"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
       <c r="A763" s="16"/>
       <c r="B763" s="16"/>
-      <c r="L763" s="21"/>
+      <c r="L763" s="22"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
       <c r="A764" s="16"/>
       <c r="B764" s="16"/>
-      <c r="L764" s="21"/>
+      <c r="L764" s="22"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
       <c r="A765" s="16"/>
       <c r="B765" s="16"/>
-      <c r="L765" s="21"/>
+      <c r="L765" s="22"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
       <c r="A766" s="16"/>
       <c r="B766" s="16"/>
-      <c r="L766" s="21"/>
+      <c r="L766" s="22"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
       <c r="A767" s="16"/>
       <c r="B767" s="16"/>
-      <c r="L767" s="21"/>
+      <c r="L767" s="22"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
       <c r="A768" s="16"/>
       <c r="B768" s="16"/>
-      <c r="L768" s="21"/>
+      <c r="L768" s="22"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
       <c r="A769" s="16"/>
       <c r="B769" s="16"/>
-      <c r="L769" s="21"/>
+      <c r="L769" s="22"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
       <c r="A770" s="16"/>
       <c r="B770" s="16"/>
-      <c r="L770" s="21"/>
+      <c r="L770" s="22"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
       <c r="A771" s="16"/>
       <c r="B771" s="16"/>
-      <c r="L771" s="21"/>
+      <c r="L771" s="22"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
       <c r="A772" s="16"/>
       <c r="B772" s="16"/>
-      <c r="L772" s="21"/>
+      <c r="L772" s="22"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
       <c r="A773" s="16"/>
       <c r="B773" s="16"/>
-      <c r="L773" s="21"/>
+      <c r="L773" s="22"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
       <c r="A774" s="16"/>
       <c r="B774" s="16"/>
-      <c r="L774" s="21"/>
+      <c r="L774" s="22"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
       <c r="A775" s="16"/>
       <c r="B775" s="16"/>
-      <c r="L775" s="21"/>
+      <c r="L775" s="22"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
       <c r="A776" s="16"/>
       <c r="B776" s="16"/>
-      <c r="L776" s="21"/>
+      <c r="L776" s="22"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
       <c r="A777" s="16"/>
       <c r="B777" s="16"/>
-      <c r="L777" s="21"/>
+      <c r="L777" s="22"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
       <c r="A778" s="16"/>
       <c r="B778" s="16"/>
-      <c r="L778" s="21"/>
+      <c r="L778" s="22"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
       <c r="A779" s="16"/>
       <c r="B779" s="16"/>
-      <c r="L779" s="21"/>
+      <c r="L779" s="22"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
       <c r="A780" s="16"/>
       <c r="B780" s="16"/>
-      <c r="L780" s="21"/>
+      <c r="L780" s="22"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
       <c r="A781" s="16"/>
       <c r="B781" s="16"/>
-      <c r="L781" s="21"/>
+      <c r="L781" s="22"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
       <c r="A782" s="16"/>
       <c r="B782" s="16"/>
-      <c r="L782" s="21"/>
+      <c r="L782" s="22"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
       <c r="A783" s="16"/>
       <c r="B783" s="16"/>
-      <c r="L783" s="21"/>
+      <c r="L783" s="22"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
       <c r="A784" s="16"/>
       <c r="B784" s="16"/>
-      <c r="L784" s="21"/>
+      <c r="L784" s="22"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
       <c r="A785" s="16"/>
       <c r="B785" s="16"/>
-      <c r="L785" s="21"/>
+      <c r="L785" s="22"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
       <c r="A786" s="16"/>
       <c r="B786" s="16"/>
-      <c r="L786" s="21"/>
+      <c r="L786" s="22"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
       <c r="A787" s="16"/>
       <c r="B787" s="16"/>
-      <c r="L787" s="21"/>
+      <c r="L787" s="22"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
       <c r="A788" s="16"/>
       <c r="B788" s="16"/>
-      <c r="L788" s="21"/>
+      <c r="L788" s="22"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
       <c r="A789" s="16"/>
       <c r="B789" s="16"/>
-      <c r="L789" s="21"/>
+      <c r="L789" s="22"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
       <c r="A790" s="16"/>
       <c r="B790" s="16"/>
-      <c r="L790" s="21"/>
+      <c r="L790" s="22"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
       <c r="A791" s="16"/>
       <c r="B791" s="16"/>
-      <c r="L791" s="21"/>
+      <c r="L791" s="22"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
       <c r="A792" s="16"/>
       <c r="B792" s="16"/>
-      <c r="L792" s="21"/>
+      <c r="L792" s="22"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
       <c r="A793" s="16"/>
       <c r="B793" s="16"/>
-      <c r="L793" s="21"/>
+      <c r="L793" s="22"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
       <c r="A794" s="16"/>
       <c r="B794" s="16"/>
-      <c r="L794" s="21"/>
+      <c r="L794" s="22"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
       <c r="A795" s="16"/>
       <c r="B795" s="16"/>
-      <c r="L795" s="21"/>
+      <c r="L795" s="22"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
       <c r="A796" s="16"/>
       <c r="B796" s="16"/>
-      <c r="L796" s="21"/>
+      <c r="L796" s="22"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
       <c r="A797" s="16"/>
       <c r="B797" s="16"/>
-      <c r="L797" s="21"/>
+      <c r="L797" s="22"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
       <c r="A798" s="16"/>
       <c r="B798" s="16"/>
-      <c r="L798" s="21"/>
+      <c r="L798" s="22"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
       <c r="A799" s="16"/>
       <c r="B799" s="16"/>
-      <c r="L799" s="21"/>
+      <c r="L799" s="22"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
       <c r="A800" s="16"/>
       <c r="B800" s="16"/>
-      <c r="L800" s="21"/>
+      <c r="L800" s="22"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
       <c r="A801" s="16"/>
       <c r="B801" s="16"/>
-      <c r="L801" s="21"/>
+      <c r="L801" s="22"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
       <c r="A802" s="16"/>
       <c r="B802" s="16"/>
-      <c r="L802" s="21"/>
+      <c r="L802" s="22"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
       <c r="A803" s="16"/>
       <c r="B803" s="16"/>
-      <c r="L803" s="21"/>
+      <c r="L803" s="22"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
       <c r="A804" s="16"/>
       <c r="B804" s="16"/>
-      <c r="L804" s="21"/>
+      <c r="L804" s="22"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
       <c r="A805" s="16"/>
       <c r="B805" s="16"/>
-      <c r="L805" s="21"/>
+      <c r="L805" s="22"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
       <c r="A806" s="16"/>
       <c r="B806" s="16"/>
-      <c r="L806" s="21"/>
+      <c r="L806" s="22"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
       <c r="A807" s="16"/>
       <c r="B807" s="16"/>
-      <c r="L807" s="21"/>
+      <c r="L807" s="22"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
       <c r="A808" s="16"/>
       <c r="B808" s="16"/>
-      <c r="L808" s="21"/>
+      <c r="L808" s="22"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
       <c r="A809" s="16"/>
       <c r="B809" s="16"/>
-      <c r="L809" s="21"/>
+      <c r="L809" s="22"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
       <c r="A810" s="16"/>
       <c r="B810" s="16"/>
-      <c r="L810" s="21"/>
+      <c r="L810" s="22"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
       <c r="A811" s="16"/>
       <c r="B811" s="16"/>
-      <c r="L811" s="21"/>
+      <c r="L811" s="22"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
       <c r="A812" s="16"/>
       <c r="B812" s="16"/>
-      <c r="L812" s="21"/>
+      <c r="L812" s="22"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
       <c r="A813" s="16"/>
       <c r="B813" s="16"/>
-      <c r="L813" s="21"/>
+      <c r="L813" s="22"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
       <c r="A814" s="16"/>
       <c r="B814" s="16"/>
-      <c r="L814" s="21"/>
+      <c r="L814" s="22"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
       <c r="A815" s="16"/>
       <c r="B815" s="16"/>
-      <c r="L815" s="21"/>
+      <c r="L815" s="22"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
       <c r="A816" s="16"/>
       <c r="B816" s="16"/>
-      <c r="L816" s="21"/>
+      <c r="L816" s="22"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
       <c r="A817" s="16"/>
       <c r="B817" s="16"/>
-      <c r="L817" s="21"/>
+      <c r="L817" s="22"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
       <c r="A818" s="16"/>
       <c r="B818" s="16"/>
-      <c r="L818" s="21"/>
+      <c r="L818" s="22"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
       <c r="A819" s="16"/>
       <c r="B819" s="16"/>
-      <c r="L819" s="21"/>
+      <c r="L819" s="22"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
       <c r="A820" s="16"/>
       <c r="B820" s="16"/>
-      <c r="L820" s="21"/>
+      <c r="L820" s="22"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
       <c r="A821" s="16"/>
       <c r="B821" s="16"/>
-      <c r="L821" s="21"/>
+      <c r="L821" s="22"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
       <c r="A822" s="16"/>
       <c r="B822" s="16"/>
-      <c r="L822" s="21"/>
+      <c r="L822" s="22"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
       <c r="A823" s="16"/>
       <c r="B823" s="16"/>
-      <c r="L823" s="21"/>
+      <c r="L823" s="22"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
       <c r="A824" s="16"/>
       <c r="B824" s="16"/>
-      <c r="L824" s="21"/>
+      <c r="L824" s="22"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
       <c r="A825" s="16"/>
       <c r="B825" s="16"/>
-      <c r="L825" s="21"/>
+      <c r="L825" s="22"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
       <c r="A826" s="16"/>
       <c r="B826" s="16"/>
-      <c r="L826" s="21"/>
+      <c r="L826" s="22"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
       <c r="A827" s="16"/>
       <c r="B827" s="16"/>
-      <c r="L827" s="21"/>
+      <c r="L827" s="22"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
       <c r="A828" s="16"/>
       <c r="B828" s="16"/>
-      <c r="L828" s="21"/>
+      <c r="L828" s="22"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
       <c r="A829" s="16"/>
       <c r="B829" s="16"/>
-      <c r="L829" s="21"/>
+      <c r="L829" s="22"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
       <c r="A830" s="16"/>
       <c r="B830" s="16"/>
-      <c r="L830" s="21"/>
+      <c r="L830" s="22"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
       <c r="A831" s="16"/>
       <c r="B831" s="16"/>
-      <c r="L831" s="21"/>
+      <c r="L831" s="22"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
       <c r="A832" s="16"/>
       <c r="B832" s="16"/>
-      <c r="L832" s="21"/>
+      <c r="L832" s="22"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
       <c r="A833" s="16"/>
       <c r="B833" s="16"/>
-      <c r="L833" s="21"/>
+      <c r="L833" s="22"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
       <c r="A834" s="16"/>
       <c r="B834" s="16"/>
-      <c r="L834" s="21"/>
+      <c r="L834" s="22"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
       <c r="A835" s="16"/>
       <c r="B835" s="16"/>
-      <c r="L835" s="21"/>
+      <c r="L835" s="22"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
       <c r="A836" s="16"/>
       <c r="B836" s="16"/>
-      <c r="L836" s="21"/>
+      <c r="L836" s="22"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
       <c r="A837" s="16"/>
       <c r="B837" s="16"/>
-      <c r="L837" s="21"/>
+      <c r="L837" s="22"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
       <c r="A838" s="16"/>
       <c r="B838" s="16"/>
-      <c r="L838" s="21"/>
+      <c r="L838" s="22"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
       <c r="A839" s="16"/>
       <c r="B839" s="16"/>
-      <c r="L839" s="21"/>
+      <c r="L839" s="22"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
       <c r="A840" s="16"/>
       <c r="B840" s="16"/>
-      <c r="L840" s="21"/>
+      <c r="L840" s="22"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
       <c r="A841" s="16"/>
       <c r="B841" s="16"/>
-      <c r="L841" s="21"/>
+      <c r="L841" s="22"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
       <c r="A842" s="16"/>
       <c r="B842" s="16"/>
-      <c r="L842" s="21"/>
+      <c r="L842" s="22"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
       <c r="A843" s="16"/>
       <c r="B843" s="16"/>
-      <c r="L843" s="21"/>
+      <c r="L843" s="22"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
       <c r="A844" s="16"/>
       <c r="B844" s="16"/>
-      <c r="L844" s="21"/>
+      <c r="L844" s="22"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
       <c r="A845" s="16"/>
       <c r="B845" s="16"/>
-      <c r="L845" s="21"/>
+      <c r="L845" s="22"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
       <c r="A846" s="16"/>
       <c r="B846" s="16"/>
-      <c r="L846" s="21"/>
+      <c r="L846" s="22"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
       <c r="A847" s="16"/>
       <c r="B847" s="16"/>
-      <c r="L847" s="21"/>
+      <c r="L847" s="22"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
       <c r="A848" s="16"/>
       <c r="B848" s="16"/>
-      <c r="L848" s="21"/>
+      <c r="L848" s="22"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
       <c r="A849" s="16"/>
       <c r="B849" s="16"/>
-      <c r="L849" s="21"/>
+      <c r="L849" s="22"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
       <c r="A850" s="16"/>
       <c r="B850" s="16"/>
-      <c r="L850" s="21"/>
+      <c r="L850" s="22"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
       <c r="A851" s="16"/>
       <c r="B851" s="16"/>
-      <c r="L851" s="21"/>
+      <c r="L851" s="22"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
       <c r="A852" s="16"/>
       <c r="B852" s="16"/>
-      <c r="L852" s="21"/>
+      <c r="L852" s="22"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
       <c r="A853" s="16"/>
       <c r="B853" s="16"/>
-      <c r="L853" s="21"/>
+      <c r="L853" s="22"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
       <c r="A854" s="16"/>
       <c r="B854" s="16"/>
-      <c r="L854" s="21"/>
+      <c r="L854" s="22"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
       <c r="A855" s="16"/>
       <c r="B855" s="16"/>
-      <c r="L855" s="21"/>
+      <c r="L855" s="22"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
       <c r="A856" s="16"/>
       <c r="B856" s="16"/>
-      <c r="L856" s="21"/>
+      <c r="L856" s="22"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
       <c r="A857" s="16"/>
       <c r="B857" s="16"/>
-      <c r="L857" s="21"/>
+      <c r="L857" s="22"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
       <c r="A858" s="16"/>
       <c r="B858" s="16"/>
-      <c r="L858" s="21"/>
+      <c r="L858" s="22"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
       <c r="A859" s="16"/>
       <c r="B859" s="16"/>
-      <c r="L859" s="21"/>
+      <c r="L859" s="22"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
       <c r="A860" s="16"/>
       <c r="B860" s="16"/>
-      <c r="L860" s="21"/>
+      <c r="L860" s="22"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
       <c r="A861" s="16"/>
       <c r="B861" s="16"/>
-      <c r="L861" s="21"/>
+      <c r="L861" s="22"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
       <c r="A862" s="16"/>
       <c r="B862" s="16"/>
-      <c r="L862" s="21"/>
+      <c r="L862" s="22"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
       <c r="A863" s="16"/>
       <c r="B863" s="16"/>
-      <c r="L863" s="21"/>
+      <c r="L863" s="22"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
       <c r="A864" s="16"/>
       <c r="B864" s="16"/>
-      <c r="L864" s="21"/>
+      <c r="L864" s="22"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
       <c r="A865" s="16"/>
       <c r="B865" s="16"/>
-      <c r="L865" s="21"/>
+      <c r="L865" s="22"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
       <c r="A866" s="16"/>
       <c r="B866" s="16"/>
-      <c r="L866" s="21"/>
+      <c r="L866" s="22"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
       <c r="A867" s="16"/>
       <c r="B867" s="16"/>
-      <c r="L867" s="21"/>
+      <c r="L867" s="22"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
       <c r="A868" s="16"/>
       <c r="B868" s="16"/>
-      <c r="L868" s="21"/>
+      <c r="L868" s="22"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
       <c r="A869" s="16"/>
       <c r="B869" s="16"/>
-      <c r="L869" s="21"/>
+      <c r="L869" s="22"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
       <c r="A870" s="16"/>
       <c r="B870" s="16"/>
-      <c r="L870" s="21"/>
+      <c r="L870" s="22"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
       <c r="A871" s="16"/>
       <c r="B871" s="16"/>
-      <c r="L871" s="21"/>
+      <c r="L871" s="22"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
       <c r="A872" s="16"/>
       <c r="B872" s="16"/>
-      <c r="L872" s="21"/>
+      <c r="L872" s="22"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
       <c r="A873" s="16"/>
       <c r="B873" s="16"/>
-      <c r="L873" s="21"/>
+      <c r="L873" s="22"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
       <c r="A874" s="16"/>
       <c r="B874" s="16"/>
-      <c r="L874" s="21"/>
+      <c r="L874" s="22"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
       <c r="A875" s="16"/>
       <c r="B875" s="16"/>
-      <c r="L875" s="21"/>
+      <c r="L875" s="22"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
       <c r="A876" s="16"/>
       <c r="B876" s="16"/>
-      <c r="L876" s="21"/>
+      <c r="L876" s="22"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
       <c r="A877" s="16"/>
       <c r="B877" s="16"/>
-      <c r="L877" s="21"/>
+      <c r="L877" s="22"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
       <c r="A878" s="16"/>
       <c r="B878" s="16"/>
-      <c r="L878" s="21"/>
+      <c r="L878" s="22"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
       <c r="A879" s="16"/>
       <c r="B879" s="16"/>
-      <c r="L879" s="21"/>
+      <c r="L879" s="22"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
       <c r="A880" s="16"/>
       <c r="B880" s="16"/>
-      <c r="L880" s="21"/>
+      <c r="L880" s="22"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
       <c r="A881" s="16"/>
       <c r="B881" s="16"/>
-      <c r="L881" s="21"/>
+      <c r="L881" s="22"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
       <c r="A882" s="16"/>
       <c r="B882" s="16"/>
-      <c r="L882" s="21"/>
+      <c r="L882" s="22"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
       <c r="A883" s="16"/>
       <c r="B883" s="16"/>
-      <c r="L883" s="21"/>
+      <c r="L883" s="22"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
       <c r="A884" s="16"/>
       <c r="B884" s="16"/>
-      <c r="L884" s="21"/>
+      <c r="L884" s="22"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
       <c r="A885" s="16"/>
       <c r="B885" s="16"/>
-      <c r="L885" s="21"/>
+      <c r="L885" s="22"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
       <c r="A886" s="16"/>
       <c r="B886" s="16"/>
-      <c r="L886" s="21"/>
+      <c r="L886" s="22"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
       <c r="A887" s="16"/>
       <c r="B887" s="16"/>
-      <c r="L887" s="21"/>
+      <c r="L887" s="22"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
       <c r="A888" s="16"/>
       <c r="B888" s="16"/>
-      <c r="L888" s="21"/>
+      <c r="L888" s="22"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
       <c r="A889" s="16"/>
       <c r="B889" s="16"/>
-      <c r="L889" s="21"/>
+      <c r="L889" s="22"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
       <c r="A890" s="16"/>
       <c r="B890" s="16"/>
-      <c r="L890" s="21"/>
+      <c r="L890" s="22"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
       <c r="A891" s="16"/>
       <c r="B891" s="16"/>
-      <c r="L891" s="21"/>
+      <c r="L891" s="22"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
       <c r="A892" s="16"/>
       <c r="B892" s="16"/>
-      <c r="L892" s="21"/>
+      <c r="L892" s="22"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
       <c r="A893" s="16"/>
       <c r="B893" s="16"/>
-      <c r="L893" s="21"/>
+      <c r="L893" s="22"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
       <c r="A894" s="16"/>
       <c r="B894" s="16"/>
-      <c r="L894" s="21"/>
+      <c r="L894" s="22"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
       <c r="A895" s="16"/>
       <c r="B895" s="16"/>
-      <c r="L895" s="21"/>
+      <c r="L895" s="22"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
       <c r="A896" s="16"/>
       <c r="B896" s="16"/>
-      <c r="L896" s="21"/>
+      <c r="L896" s="22"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
       <c r="A897" s="16"/>
       <c r="B897" s="16"/>
-      <c r="L897" s="21"/>
+      <c r="L897" s="22"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
       <c r="A898" s="16"/>
       <c r="B898" s="16"/>
-      <c r="L898" s="21"/>
+      <c r="L898" s="22"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
       <c r="A899" s="16"/>
       <c r="B899" s="16"/>
-      <c r="L899" s="21"/>
+      <c r="L899" s="22"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
       <c r="A900" s="16"/>
       <c r="B900" s="16"/>
-      <c r="L900" s="21"/>
+      <c r="L900" s="22"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
       <c r="A901" s="16"/>
       <c r="B901" s="16"/>
-      <c r="L901" s="21"/>
+      <c r="L901" s="22"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
       <c r="A902" s="16"/>
       <c r="B902" s="16"/>
-      <c r="L902" s="21"/>
+      <c r="L902" s="22"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
       <c r="A903" s="16"/>
       <c r="B903" s="16"/>
-      <c r="L903" s="21"/>
+      <c r="L903" s="22"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
       <c r="A904" s="16"/>
       <c r="B904" s="16"/>
-      <c r="L904" s="21"/>
+      <c r="L904" s="22"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
       <c r="A905" s="16"/>
       <c r="B905" s="16"/>
-      <c r="L905" s="21"/>
+      <c r="L905" s="22"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
       <c r="A906" s="16"/>
       <c r="B906" s="16"/>
-      <c r="L906" s="21"/>
+      <c r="L906" s="22"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
       <c r="A907" s="16"/>
       <c r="B907" s="16"/>
-      <c r="L907" s="21"/>
+      <c r="L907" s="22"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
       <c r="A908" s="16"/>
       <c r="B908" s="16"/>
-      <c r="L908" s="21"/>
+      <c r="L908" s="22"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
       <c r="A909" s="16"/>
       <c r="B909" s="16"/>
-      <c r="L909" s="21"/>
+      <c r="L909" s="22"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
       <c r="A910" s="16"/>
       <c r="B910" s="16"/>
-      <c r="L910" s="21"/>
+      <c r="L910" s="22"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
       <c r="A911" s="16"/>
       <c r="B911" s="16"/>
-      <c r="L911" s="21"/>
+      <c r="L911" s="22"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
       <c r="A912" s="16"/>
       <c r="B912" s="16"/>
-      <c r="L912" s="21"/>
+      <c r="L912" s="22"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
       <c r="A913" s="16"/>
       <c r="B913" s="16"/>
-      <c r="L913" s="21"/>
+      <c r="L913" s="22"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
       <c r="A914" s="16"/>
       <c r="B914" s="16"/>
-      <c r="L914" s="21"/>
+      <c r="L914" s="22"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
       <c r="A915" s="16"/>
       <c r="B915" s="16"/>
-      <c r="L915" s="21"/>
+      <c r="L915" s="22"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
       <c r="A916" s="16"/>
       <c r="B916" s="16"/>
-      <c r="L916" s="21"/>
+      <c r="L916" s="22"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
       <c r="A917" s="16"/>
       <c r="B917" s="16"/>
-      <c r="L917" s="21"/>
+      <c r="L917" s="22"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
       <c r="A918" s="16"/>
       <c r="B918" s="16"/>
-      <c r="L918" s="21"/>
+      <c r="L918" s="22"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
       <c r="A919" s="16"/>
       <c r="B919" s="16"/>
-      <c r="L919" s="21"/>
+      <c r="L919" s="22"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
       <c r="A920" s="16"/>
       <c r="B920" s="16"/>
-      <c r="L920" s="21"/>
+      <c r="L920" s="22"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
       <c r="A921" s="16"/>
       <c r="B921" s="16"/>
-      <c r="L921" s="21"/>
+      <c r="L921" s="22"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
       <c r="A922" s="16"/>
       <c r="B922" s="16"/>
-      <c r="L922" s="21"/>
+      <c r="L922" s="22"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
       <c r="A923" s="16"/>
       <c r="B923" s="16"/>
-      <c r="L923" s="21"/>
+      <c r="L923" s="22"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
       <c r="A924" s="16"/>
       <c r="B924" s="16"/>
-      <c r="L924" s="21"/>
+      <c r="L924" s="22"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
       <c r="A925" s="16"/>
       <c r="B925" s="16"/>
-      <c r="L925" s="21"/>
+      <c r="L925" s="22"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
       <c r="A926" s="16"/>
       <c r="B926" s="16"/>
-      <c r="L926" s="21"/>
+      <c r="L926" s="22"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
       <c r="A927" s="16"/>
       <c r="B927" s="16"/>
-      <c r="L927" s="21"/>
+      <c r="L927" s="22"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
       <c r="A928" s="16"/>
       <c r="B928" s="16"/>
-      <c r="L928" s="21"/>
+      <c r="L928" s="22"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
       <c r="A929" s="16"/>
       <c r="B929" s="16"/>
-      <c r="L929" s="21"/>
+      <c r="L929" s="22"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
       <c r="A930" s="16"/>
       <c r="B930" s="16"/>
-      <c r="L930" s="21"/>
+      <c r="L930" s="22"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
       <c r="A931" s="16"/>
       <c r="B931" s="16"/>
-      <c r="L931" s="21"/>
+      <c r="L931" s="22"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
       <c r="A932" s="16"/>
       <c r="B932" s="16"/>
-      <c r="L932" s="21"/>
+      <c r="L932" s="22"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
       <c r="A933" s="16"/>
       <c r="B933" s="16"/>
-      <c r="L933" s="21"/>
+      <c r="L933" s="22"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
       <c r="A934" s="16"/>
       <c r="B934" s="16"/>
-      <c r="L934" s="21"/>
+      <c r="L934" s="22"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
       <c r="A935" s="16"/>
       <c r="B935" s="16"/>
-      <c r="L935" s="21"/>
+      <c r="L935" s="22"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
       <c r="A936" s="16"/>
       <c r="B936" s="16"/>
-      <c r="L936" s="21"/>
+      <c r="L936" s="22"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
       <c r="A937" s="16"/>
       <c r="B937" s="16"/>
-      <c r="L937" s="21"/>
+      <c r="L937" s="22"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
       <c r="A938" s="16"/>
       <c r="B938" s="16"/>
-      <c r="L938" s="21"/>
+      <c r="L938" s="22"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
       <c r="A939" s="16"/>
       <c r="B939" s="16"/>
-      <c r="L939" s="21"/>
+      <c r="L939" s="22"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
       <c r="A940" s="16"/>
       <c r="B940" s="16"/>
-      <c r="L940" s="21"/>
+      <c r="L940" s="22"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
       <c r="A941" s="16"/>
       <c r="B941" s="16"/>
-      <c r="L941" s="21"/>
+      <c r="L941" s="22"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
       <c r="A942" s="16"/>
       <c r="B942" s="16"/>
-      <c r="L942" s="21"/>
+      <c r="L942" s="22"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
       <c r="A943" s="16"/>
       <c r="B943" s="16"/>
-      <c r="L943" s="21"/>
+      <c r="L943" s="22"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
       <c r="A944" s="16"/>
       <c r="B944" s="16"/>
-      <c r="L944" s="21"/>
+      <c r="L944" s="22"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
       <c r="A945" s="16"/>
       <c r="B945" s="16"/>
-      <c r="L945" s="21"/>
+      <c r="L945" s="22"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
       <c r="A946" s="16"/>
       <c r="B946" s="16"/>
-      <c r="L946" s="21"/>
+      <c r="L946" s="22"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
       <c r="A947" s="16"/>
       <c r="B947" s="16"/>
-      <c r="L947" s="21"/>
+      <c r="L947" s="22"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
       <c r="A948" s="16"/>
       <c r="B948" s="16"/>
-      <c r="L948" s="21"/>
+      <c r="L948" s="22"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
       <c r="A949" s="16"/>
       <c r="B949" s="16"/>
-      <c r="L949" s="21"/>
+      <c r="L949" s="22"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
       <c r="A950" s="16"/>
       <c r="B950" s="16"/>
-      <c r="L950" s="21"/>
+      <c r="L950" s="22"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
       <c r="A951" s="16"/>
       <c r="B951" s="16"/>
-      <c r="L951" s="21"/>
+      <c r="L951" s="22"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
       <c r="A952" s="16"/>
       <c r="B952" s="16"/>
-      <c r="L952" s="21"/>
+      <c r="L952" s="22"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
       <c r="A953" s="16"/>
       <c r="B953" s="16"/>
-      <c r="L953" s="21"/>
+      <c r="L953" s="22"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
       <c r="A954" s="16"/>
       <c r="B954" s="16"/>
-      <c r="L954" s="21"/>
+      <c r="L954" s="22"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
       <c r="A955" s="16"/>
       <c r="B955" s="16"/>
-      <c r="L955" s="21"/>
+      <c r="L955" s="22"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
       <c r="A956" s="16"/>
       <c r="B956" s="16"/>
-      <c r="L956" s="21"/>
+      <c r="L956" s="22"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
       <c r="A957" s="16"/>
       <c r="B957" s="16"/>
-      <c r="L957" s="21"/>
+      <c r="L957" s="22"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
       <c r="A958" s="16"/>
       <c r="B958" s="16"/>
-      <c r="L958" s="21"/>
+      <c r="L958" s="22"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
       <c r="A959" s="16"/>
       <c r="B959" s="16"/>
-      <c r="L959" s="21"/>
+      <c r="L959" s="22"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
       <c r="A960" s="16"/>
       <c r="B960" s="16"/>
-      <c r="L960" s="21"/>
+      <c r="L960" s="22"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
       <c r="A961" s="16"/>
       <c r="B961" s="16"/>
-      <c r="L961" s="21"/>
+      <c r="L961" s="22"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
       <c r="A962" s="16"/>
       <c r="B962" s="16"/>
-      <c r="L962" s="21"/>
+      <c r="L962" s="22"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
       <c r="A963" s="16"/>
       <c r="B963" s="16"/>
-      <c r="L963" s="21"/>
+      <c r="L963" s="22"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
       <c r="A964" s="16"/>
       <c r="B964" s="16"/>
-      <c r="L964" s="21"/>
+      <c r="L964" s="22"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
       <c r="A965" s="16"/>
       <c r="B965" s="16"/>
-      <c r="L965" s="21"/>
+      <c r="L965" s="22"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
       <c r="A966" s="16"/>
       <c r="B966" s="16"/>
-      <c r="L966" s="21"/>
+      <c r="L966" s="22"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
       <c r="A967" s="16"/>
       <c r="B967" s="16"/>
-      <c r="L967" s="21"/>
+      <c r="L967" s="22"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
       <c r="A968" s="16"/>
       <c r="B968" s="16"/>
-      <c r="L968" s="21"/>
+      <c r="L968" s="22"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
       <c r="A969" s="16"/>
       <c r="B969" s="16"/>
-      <c r="L969" s="21"/>
+      <c r="L969" s="22"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
       <c r="A970" s="16"/>
       <c r="B970" s="16"/>
-      <c r="L970" s="21"/>
+      <c r="L970" s="22"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
       <c r="A971" s="16"/>
       <c r="B971" s="16"/>
-      <c r="L971" s="21"/>
+      <c r="L971" s="22"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
       <c r="A972" s="16"/>
       <c r="B972" s="16"/>
-      <c r="L972" s="21"/>
+      <c r="L972" s="22"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
       <c r="A973" s="16"/>
       <c r="B973" s="16"/>
-      <c r="L973" s="21"/>
+      <c r="L973" s="22"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
       <c r="A974" s="16"/>
       <c r="B974" s="16"/>
-      <c r="L974" s="21"/>
+      <c r="L974" s="22"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
       <c r="A975" s="16"/>
       <c r="B975" s="16"/>
-      <c r="L975" s="21"/>
+      <c r="L975" s="22"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
       <c r="A976" s="16"/>
       <c r="B976" s="16"/>
-      <c r="L976" s="21"/>
+      <c r="L976" s="22"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
       <c r="A977" s="16"/>
       <c r="B977" s="16"/>
-      <c r="L977" s="21"/>
+      <c r="L977" s="22"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
       <c r="A978" s="16"/>
       <c r="B978" s="16"/>
-      <c r="L978" s="21"/>
+      <c r="L978" s="22"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
       <c r="A979" s="16"/>
       <c r="B979" s="16"/>
-      <c r="L979" s="21"/>
+      <c r="L979" s="22"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
       <c r="A980" s="16"/>
       <c r="B980" s="16"/>
-      <c r="L980" s="21"/>
+      <c r="L980" s="22"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
       <c r="A981" s="16"/>
       <c r="B981" s="16"/>
-      <c r="L981" s="21"/>
+      <c r="L981" s="22"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
       <c r="A982" s="16"/>
       <c r="B982" s="16"/>
-      <c r="L982" s="21"/>
+      <c r="L982" s="22"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
       <c r="A983" s="16"/>
       <c r="B983" s="16"/>
-      <c r="L983" s="21"/>
+      <c r="L983" s="22"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
       <c r="A984" s="16"/>
       <c r="B984" s="16"/>
-      <c r="L984" s="21"/>
+      <c r="L984" s="22"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
       <c r="A985" s="16"/>
       <c r="B985" s="16"/>
-      <c r="L985" s="21"/>
+      <c r="L985" s="22"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
       <c r="A986" s="16"/>
       <c r="B986" s="16"/>
-      <c r="L986" s="21"/>
+      <c r="L986" s="22"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
       <c r="A987" s="16"/>
       <c r="B987" s="16"/>
-      <c r="L987" s="21"/>
+      <c r="L987" s="22"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
       <c r="A988" s="16"/>
       <c r="B988" s="16"/>
-      <c r="L988" s="21"/>
+      <c r="L988" s="22"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
       <c r="A989" s="16"/>
       <c r="B989" s="16"/>
-      <c r="L989" s="21"/>
+      <c r="L989" s="22"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
       <c r="A990" s="16"/>
       <c r="B990" s="16"/>
-      <c r="L990" s="21"/>
+      <c r="L990" s="22"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
       <c r="A991" s="16"/>
       <c r="B991" s="16"/>
-      <c r="L991" s="21"/>
+      <c r="L991" s="22"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
       <c r="A992" s="16"/>
       <c r="B992" s="16"/>
-      <c r="L992" s="21"/>
+      <c r="L992" s="22"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
       <c r="A993" s="16"/>
       <c r="B993" s="16"/>
-      <c r="L993" s="21"/>
+      <c r="L993" s="22"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
       <c r="A994" s="16"/>
       <c r="B994" s="16"/>
-      <c r="L994" s="21"/>
+      <c r="L994" s="22"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
       <c r="A995" s="16"/>
       <c r="B995" s="16"/>
-      <c r="L995" s="21"/>
+      <c r="L995" s="22"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
       <c r="A996" s="16"/>
       <c r="B996" s="16"/>
-      <c r="L996" s="21"/>
+      <c r="L996" s="22"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
       <c r="A997" s="16"/>
       <c r="B997" s="16"/>
-      <c r="L997" s="21"/>
+      <c r="L997" s="22"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
       <c r="A998" s="16"/>
       <c r="B998" s="16"/>
-      <c r="L998" s="21"/>
+      <c r="L998" s="22"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
       <c r="A999" s="16"/>
       <c r="B999" s="16"/>
-      <c r="L999" s="21"/>
+      <c r="L999" s="22"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
       <c r="A1000" s="16"/>
       <c r="B1000" s="16"/>
-      <c r="L1000" s="21"/>
+      <c r="L1000" s="22"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
       <c r="A1001" s="16"/>
       <c r="B1001" s="16"/>
-      <c r="L1001" s="21"/>
+      <c r="L1001" s="22"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
       <c r="A1002" s="16"/>
       <c r="B1002" s="16"/>
-      <c r="L1002" s="21"/>
+      <c r="L1002" s="22"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
       <c r="A1003" s="16"/>
       <c r="B1003" s="16"/>
-      <c r="L1003" s="21"/>
+      <c r="L1003" s="22"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
       <c r="A1004" s="16"/>
       <c r="B1004" s="16"/>
-      <c r="L1004" s="21"/>
+      <c r="L1004" s="22"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
       <c r="A1005" s="16"/>
       <c r="B1005" s="16"/>
-      <c r="L1005" s="21"/>
+      <c r="L1005" s="22"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
       <c r="A1006" s="16"/>
       <c r="B1006" s="16"/>
-      <c r="L1006" s="21"/>
+      <c r="L1006" s="22"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
       <c r="A1007" s="16"/>
       <c r="B1007" s="16"/>
-      <c r="L1007" s="21"/>
+      <c r="L1007" s="22"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
       <c r="A1008" s="16"/>
       <c r="B1008" s="16"/>
-      <c r="L1008" s="21"/>
+      <c r="L1008" s="22"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
       <c r="A1009" s="16"/>
       <c r="B1009" s="16"/>
-      <c r="L1009" s="21"/>
+      <c r="L1009" s="22"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
       <c r="A1010" s="16"/>
       <c r="B1010" s="16"/>
-      <c r="L1010" s="21"/>
+      <c r="L1010" s="22"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
       <c r="A1011" s="16"/>
       <c r="B1011" s="16"/>
-      <c r="L1011" s="21"/>
+      <c r="L1011" s="22"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
       <c r="A1012" s="16"/>
       <c r="B1012" s="16"/>
-      <c r="L1012" s="21"/>
+      <c r="L1012" s="22"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
       <c r="A1013" s="16"/>
       <c r="B1013" s="16"/>
-      <c r="L1013" s="21"/>
+      <c r="L1013" s="22"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
       <c r="A1014" s="16"/>
       <c r="B1014" s="16"/>
-      <c r="L1014" s="21"/>
+      <c r="L1014" s="22"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
       <c r="A1015" s="16"/>
       <c r="B1015" s="16"/>
-      <c r="L1015" s="21"/>
+      <c r="L1015" s="22"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
       <c r="A1016" s="16"/>
       <c r="B1016" s="16"/>
-      <c r="L1016" s="21"/>
+      <c r="L1016" s="22"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
       <c r="A1017" s="16"/>
       <c r="B1017" s="16"/>
-      <c r="L1017" s="21"/>
+      <c r="L1017" s="22"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
       <c r="A1018" s="16"/>
       <c r="B1018" s="16"/>
-      <c r="L1018" s="21"/>
+      <c r="L1018" s="22"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
       <c r="A1019" s="16"/>
       <c r="B1019" s="16"/>
-      <c r="L1019" s="21"/>
+      <c r="L1019" s="22"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
       <c r="A1020" s="16"/>
       <c r="B1020" s="16"/>
-      <c r="L1020" s="21"/>
+      <c r="L1020" s="22"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
       <c r="A1021" s="16"/>
       <c r="B1021" s="16"/>
-      <c r="L1021" s="21"/>
+      <c r="L1021" s="22"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
       <c r="A1022" s="16"/>
       <c r="B1022" s="16"/>
-      <c r="L1022" s="21"/>
+      <c r="L1022" s="22"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
       <c r="A1023" s="16"/>
       <c r="B1023" s="16"/>
-      <c r="L1023" s="21"/>
+      <c r="L1023" s="22"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
       <c r="A1024" s="16"/>
       <c r="B1024" s="16"/>
-      <c r="L1024" s="21"/>
+      <c r="L1024" s="22"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
       <c r="A1025" s="16"/>
       <c r="B1025" s="16"/>
-      <c r="L1025" s="21"/>
+      <c r="L1025" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7992,13 +7992,13 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>4</v>
@@ -8037,13 +8037,13 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>4</v>
@@ -8082,13 +8082,13 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>4</v>
@@ -8106,7 +8106,7 @@
         <v>339039.0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J7" s="13">
         <v>949835.78</v>
@@ -8127,13 +8127,13 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>4</v>
@@ -8151,7 +8151,7 @@
         <v>339039.0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J8" s="13">
         <v>524584.95</v>
@@ -8162,7 +8162,7 @@
       <c r="L8" s="14">
         <v>0.0</v>
       </c>
-      <c r="O8" s="27"/>
+      <c r="O8" s="21"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8173,13 +8173,13 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>4</v>
@@ -8197,7 +8197,7 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J9" s="13">
         <v>211614.23</v>
@@ -8218,13 +8218,13 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>4</v>
@@ -8263,13 +8263,13 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>4</v>
@@ -8308,13 +8308,13 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>4</v>
@@ -8332,7 +8332,7 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J12" s="13">
         <v>1600334.09</v>
@@ -8353,13 +8353,13 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>4</v>
@@ -8388,7 +8388,7 @@
       <c r="L13" s="13">
         <v>497601.53</v>
       </c>
-      <c r="M13" s="38"/>
+      <c r="M13" s="30"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8399,13 +8399,13 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>4</v>
@@ -8423,7 +8423,7 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J14" s="13">
         <v>968237.39</v>
@@ -8444,13 +8444,13 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>4</v>
@@ -8468,7 +8468,7 @@
         <v>339039.0</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="J15" s="13">
         <v>1011677.95</v>
@@ -8489,13 +8489,13 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>4</v>
@@ -8534,13 +8534,13 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>4</v>
@@ -8579,13 +8579,13 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>4</v>
@@ -8603,7 +8603,7 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J18" s="13">
         <v>63746.85</v>
@@ -8624,13 +8624,13 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>4</v>
@@ -8648,7 +8648,7 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="J19" s="13">
         <v>947931.1</v>
@@ -8669,13 +8669,13 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>4</v>
@@ -8714,13 +8714,13 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>4</v>
@@ -8759,18 +8759,18 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="41">
         <v>45953.0</v>
       </c>
       <c r="F22" s="8" t="s">
@@ -8804,18 +8804,18 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="47">
+      <c r="E23" s="41">
         <v>45953.0</v>
       </c>
       <c r="F23" s="8" t="s">
@@ -8828,7 +8828,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J23" s="13">
         <v>1000001.64</v>
@@ -8849,18 +8849,18 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E24" s="41">
         <v>45953.0</v>
       </c>
       <c r="F24" s="8" t="s">
@@ -8894,18 +8894,18 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="41">
         <v>45975.0</v>
       </c>
       <c r="F25" s="8" t="s">
@@ -8918,7 +8918,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="J25" s="13">
         <v>1157673.06</v>
@@ -8939,18 +8939,18 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="47">
+      <c r="E26" s="41">
         <v>45989.0</v>
       </c>
       <c r="F26" s="8" t="s">
@@ -8984,13 +8984,13 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>4</v>
@@ -9029,13 +9029,13 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>4</v>
@@ -9053,7 +9053,7 @@
         <v>339039.0</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J28" s="13">
         <v>1912292.52</v>
@@ -9074,13 +9074,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>4</v>
@@ -9100,13 +9100,13 @@
       <c r="I29" s="6">
         <v>2048.0</v>
       </c>
-      <c r="J29" s="51">
+      <c r="J29" s="50">
         <v>1496713.48</v>
       </c>
       <c r="K29" s="6">
         <v>0.0</v>
       </c>
-      <c r="L29" s="51">
+      <c r="L29" s="50">
         <v>1496713.48</v>
       </c>
       <c r="AB29" s="2"/>
@@ -9119,13 +9119,13 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>4</v>
@@ -9143,15 +9143,15 @@
         <v>339039.0</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="51">
+        <v>36</v>
+      </c>
+      <c r="J30" s="50">
         <v>624166.14</v>
       </c>
       <c r="K30" s="6">
         <v>0.0</v>
       </c>
-      <c r="L30" s="51">
+      <c r="L30" s="50">
         <v>624166.14</v>
       </c>
       <c r="AB30" s="2"/>
@@ -9164,13 +9164,13 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>4</v>
@@ -9188,15 +9188,15 @@
         <v>339039.0</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J31" s="51">
+        <v>110</v>
+      </c>
+      <c r="J31" s="50">
         <v>18462.36</v>
       </c>
       <c r="K31" s="6">
         <v>0.0</v>
       </c>
-      <c r="L31" s="51">
+      <c r="L31" s="50">
         <v>18462.36</v>
       </c>
       <c r="AB31" s="2"/>
@@ -9209,13 +9209,13 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>157</v>
+        <v>143</v>
+      </c>
+      <c r="C32" s="50" t="s">
+        <v>149</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>4</v>
@@ -9233,15 +9233,15 @@
         <v>339039.0</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="J32" s="51">
+        <v>110</v>
+      </c>
+      <c r="J32" s="50">
         <v>1530656.62</v>
       </c>
       <c r="K32" s="6">
         <v>0.0</v>
       </c>
-      <c r="L32" s="51">
+      <c r="L32" s="50">
         <v>1530656.62</v>
       </c>
       <c r="AB32" s="2"/>
@@ -9253,7 +9253,7 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="C33" s="51"/>
+      <c r="C33" s="50"/>
       <c r="AB33" s="2"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,12 +30,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="207">
   <si>
+    <t>Controle de pagamentos</t>
+  </si>
+  <si>
     <t>Saldo</t>
   </si>
   <si>
-    <t>Controle de pagamentos</t>
-  </si>
-  <si>
     <t>2025NE000005</t>
   </si>
   <si>
@@ -54,88 +54,100 @@
     <t>C25512</t>
   </si>
   <si>
+    <t>Número Contrato</t>
+  </si>
+  <si>
     <t>25E0385</t>
   </si>
   <si>
-    <t>Número Contrato</t>
-  </si>
-  <si>
     <t>UG Executora</t>
   </si>
   <si>
+    <t>UG Responsável</t>
+  </si>
+  <si>
+    <t>UG Fiscalizadora</t>
+  </si>
+  <si>
+    <t>Prazo Final de Execução</t>
+  </si>
+  <si>
+    <t>Prazo Final de Vigência</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ação</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>Moeda</t>
+  </si>
+  <si>
+    <t>Valor Total do Contrato</t>
+  </si>
+  <si>
+    <t>Valor a Empenhar</t>
+  </si>
+  <si>
+    <t>Valor Empenhado</t>
+  </si>
+  <si>
     <t>2025NE000369</t>
   </si>
   <si>
-    <t>UG Responsável</t>
+    <t>Valor Liquidado</t>
   </si>
   <si>
     <t>C25516</t>
   </si>
   <si>
-    <t>UG Fiscalizadora</t>
+    <t>Saldo (Valor a Faturar)</t>
   </si>
   <si>
     <t>25E0387</t>
   </si>
   <si>
-    <t>Prazo Final de Execução</t>
-  </si>
-  <si>
-    <t>Prazo Final de Vigência</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ação</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>Moeda</t>
-  </si>
-  <si>
-    <t>Valor Total do Contrato</t>
-  </si>
-  <si>
-    <t>Valor a Empenhar</t>
-  </si>
-  <si>
-    <t>Valor Empenhado</t>
-  </si>
-  <si>
-    <t>Valor Liquidado</t>
+    <t>Fornecedor</t>
+  </si>
+  <si>
+    <t>Tipo Despesa /Receita</t>
+  </si>
+  <si>
+    <t>Abrir</t>
+  </si>
+  <si>
+    <t>Editar</t>
+  </si>
+  <si>
+    <t>005/CELOG-PAMALS/2025</t>
   </si>
   <si>
     <t>2025NE000371</t>
   </si>
   <si>
-    <t>Saldo (Valor a Faturar)</t>
-  </si>
-  <si>
-    <t>Fornecedor</t>
+    <t>CELOG</t>
   </si>
   <si>
     <t>25E0389</t>
   </si>
   <si>
-    <t>Tipo Despesa /Receita</t>
-  </si>
-  <si>
-    <t>Abrir</t>
-  </si>
-  <si>
-    <t>Editar</t>
-  </si>
-  <si>
-    <t>005/CELOG-PAMALS/2025</t>
+    <t>PAMALS</t>
+  </si>
+  <si>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
   </si>
   <si>
     <t>2025NE000413</t>
   </si>
   <si>
-    <t>CELOG</t>
+    <t>67101.001510/2024-12</t>
   </si>
   <si>
     <t>C25501</t>
@@ -144,27 +156,18 @@
     <t>25E0403</t>
   </si>
   <si>
-    <t>PAMALS</t>
+    <t>R$</t>
   </si>
   <si>
     <t>20SP</t>
   </si>
   <si>
-    <t>Vigente</t>
-  </si>
-  <si>
-    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
-  </si>
-  <si>
-    <t>67101.001510/2024-12</t>
+    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
     <t>2025NE000414</t>
   </si>
   <si>
-    <t>R$</t>
-  </si>
-  <si>
     <t>C25525</t>
   </si>
   <si>
@@ -174,9 +177,6 @@
     <t>21EM</t>
   </si>
   <si>
-    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
-  </si>
-  <si>
     <t>2025NE000559</t>
   </si>
   <si>
@@ -189,18 +189,54 @@
     <t>20X7</t>
   </si>
   <si>
+    <t>Módulo</t>
+  </si>
+  <si>
     <t>2025NE000770</t>
   </si>
   <si>
     <t>25E0731</t>
   </si>
   <si>
+    <t>Referência</t>
+  </si>
+  <si>
+    <t>Nº recibo</t>
+  </si>
+  <si>
+    <t>Nº</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Empenho</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
     <t>2025NE000774</t>
   </si>
   <si>
+    <t>Valor das Nfs</t>
+  </si>
+  <si>
     <t>25E0737</t>
   </si>
   <si>
+    <t>Ordem de Pagamento</t>
+  </si>
+  <si>
+    <t>Faturado</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
     <t>2025NE000843</t>
   </si>
   <si>
@@ -219,13 +255,10 @@
     <t>25E0999</t>
   </si>
   <si>
-    <t>Módulo</t>
-  </si>
-  <si>
-    <t>Referência</t>
-  </si>
-  <si>
-    <t>Nº recibo</t>
+    <t>FEV/25</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>2025NE001200</t>
@@ -237,22 +270,7 @@
     <t>25E1128</t>
   </si>
   <si>
-    <t>Nº</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Empenho</t>
-  </si>
-  <si>
-    <t>Observações</t>
-  </si>
-  <si>
-    <t>Vencimento</t>
-  </si>
-  <si>
-    <t>Valor das Nfs</t>
+    <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
     <t>2025NE001598</t>
@@ -261,16 +279,10 @@
     <t>C25814</t>
   </si>
   <si>
-    <t>Ordem de Pagamento</t>
-  </si>
-  <si>
     <t>25E1446</t>
   </si>
   <si>
-    <t>Faturado</t>
-  </si>
-  <si>
-    <t>Pendente</t>
+    <t>2025NP001980</t>
   </si>
   <si>
     <t>2025NE001627</t>
@@ -288,15 +300,9 @@
     <t>25E1477</t>
   </si>
   <si>
-    <t>FEV/25</t>
-  </si>
-  <si>
     <t>2025NE001687</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>25E1535</t>
   </si>
   <si>
@@ -306,24 +312,27 @@
     <t>25E1536</t>
   </si>
   <si>
-    <t xml:space="preserve">2025NE000369 </t>
-  </si>
-  <si>
     <t>2025NE001689</t>
   </si>
   <si>
+    <t>MAR/25</t>
+  </si>
+  <si>
     <t>25E1537</t>
   </si>
   <si>
+    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
+  </si>
+  <si>
     <t>2025NE001690</t>
   </si>
   <si>
-    <t>2025NP001980</t>
-  </si>
-  <si>
     <t>25E1538</t>
   </si>
   <si>
+    <t>2025NP001979</t>
+  </si>
+  <si>
     <t>2025NE001823</t>
   </si>
   <si>
@@ -342,6 +351,9 @@
     <t>25E1667</t>
   </si>
   <si>
+    <t>ABR/25</t>
+  </si>
+  <si>
     <t>20YJ</t>
   </si>
   <si>
@@ -351,7 +363,7 @@
     <t>25E1669</t>
   </si>
   <si>
-    <t>MAR/25</t>
+    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
     <t>2025NE002200</t>
@@ -363,10 +375,7 @@
     <t>25E2021</t>
   </si>
   <si>
-    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
-  </si>
-  <si>
-    <t>2025NP001979</t>
+    <t>2025NP002341</t>
   </si>
   <si>
     <t>2025NE002237</t>
@@ -375,6 +384,9 @@
     <t>25E2058</t>
   </si>
   <si>
+    <t>MAI/25</t>
+  </si>
+  <si>
     <t>2026NE000330</t>
   </si>
   <si>
@@ -384,12 +396,6 @@
     <t>26E0320</t>
   </si>
   <si>
-    <t>ABR/25</t>
-  </si>
-  <si>
-    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
-  </si>
-  <si>
     <t>2026NE000388</t>
   </si>
   <si>
@@ -399,18 +405,15 @@
     <t>26E0375</t>
   </si>
   <si>
-    <t>2025NP002341</t>
-  </si>
-  <si>
     <t>2026NE000748</t>
   </si>
   <si>
-    <t>MAI/25</t>
-  </si>
-  <si>
     <t>C26312</t>
   </si>
   <si>
+    <t>2025NP002884</t>
+  </si>
+  <si>
     <t>26E0709</t>
   </si>
   <si>
@@ -429,25 +432,16 @@
     <t>C26326</t>
   </si>
   <si>
+    <t>JUN/25</t>
+  </si>
+  <si>
     <t>26E0777</t>
   </si>
   <si>
-    <t>2025NP002884</t>
-  </si>
-  <si>
     <t>2026NE000842</t>
   </si>
   <si>
     <t>26E0803</t>
-  </si>
-  <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
-    <t>26E0906</t>
-  </si>
-  <si>
-    <t>JUN/25</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -457,6 +451,12 @@
   </si>
   <si>
     <t>2025NP400522</t>
+  </si>
+  <si>
+    <t>2026NE000944</t>
+  </si>
+  <si>
+    <t>26E0906</t>
   </si>
   <si>
     <t>JUL/25</t>
@@ -664,8 +664,8 @@
     <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
-    <numFmt numFmtId="168" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="169" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
+    <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
+    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
     <numFmt numFmtId="171" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -701,15 +701,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -860,35 +860,35 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -913,31 +913,30 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -950,6 +949,7 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -962,17 +962,17 @@
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -987,19 +987,19 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1060,7 +1060,7 @@
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="9" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="5" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="167" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -1409,124 +1409,124 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="4"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="9"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" s="8"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="4"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="I4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="K4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="L4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="M4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="N4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="O4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="17" t="s">
+      <c r="P4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="17" t="s">
+      <c r="Q4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="R4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="R4" s="16" t="s">
+      <c r="S4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="T4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="U4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="T4" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" s="4"/>
+      <c r="V4" s="3"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="F5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>38</v>
-      </c>
       <c r="G5" s="19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1535,16 +1535,16 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L5" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="19" t="s">
         <v>42</v>
-      </c>
-      <c r="M5" s="19" t="s">
-        <v>44</v>
       </c>
       <c r="N5" s="21">
         <v>9.165159737E7</v>
@@ -1562,20 +1562,20 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="V5" s="3"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
-      <c r="L6" s="23"/>
-      <c r="V6" s="4"/>
+      <c r="L6" s="22"/>
+      <c r="V6" s="3"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
@@ -1589,62 +1589,62 @@
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
       <c r="P7" s="28"/>
-      <c r="V7" s="4"/>
+      <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
       <c r="C8" s="29" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D8" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>79</v>
+      <c r="L8" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>67</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="O8" s="29"/>
       <c r="P8" s="28"/>
-      <c r="V8" s="4"/>
+      <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="33">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="32">
         <v>1.0</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>86</v>
+      <c r="D9" s="33" t="s">
+        <v>75</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F9" s="36">
         <v>594.0</v>
@@ -1653,7 +1653,7 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="36" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I9" s="37"/>
       <c r="J9" s="37">
@@ -1663,26 +1663,26 @@
         <v>748504.24</v>
       </c>
       <c r="L9" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="40">
+        <v>84</v>
+      </c>
+      <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
-      <c r="N9" s="41"/>
+      <c r="N9" s="40"/>
       <c r="O9" s="26"/>
       <c r="P9" s="28"/>
-      <c r="V9" s="4"/>
+      <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="34" t="s">
-        <v>107</v>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="33" t="s">
+        <v>95</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F10" s="36">
         <v>620.0</v>
@@ -1691,7 +1691,7 @@
         <v>45775.0</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="I10" s="37"/>
       <c r="J10" s="37">
@@ -1701,26 +1701,26 @@
         <v>1110378.24</v>
       </c>
       <c r="L10" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="M10" s="40">
+        <v>100</v>
+      </c>
+      <c r="M10" s="39">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
       <c r="N10" s="43"/>
       <c r="O10" s="26"/>
       <c r="P10" s="28"/>
-      <c r="V10" s="4"/>
+      <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="34" t="s">
-        <v>118</v>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="33" t="s">
+        <v>107</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F11" s="36">
         <v>634.0</v>
@@ -1729,7 +1729,7 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="I11" s="37"/>
       <c r="J11" s="37">
@@ -1739,25 +1739,25 @@
         <v>974557.12</v>
       </c>
       <c r="L11" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="M11" s="40">
+        <v>115</v>
+      </c>
+      <c r="M11" s="39">
         <v>974557.12</v>
       </c>
       <c r="N11" s="43"/>
       <c r="O11" s="26"/>
       <c r="P11" s="28"/>
-      <c r="V11" s="4"/>
+      <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="34" t="s">
-        <v>125</v>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="33" t="s">
+        <v>118</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F12" s="35">
         <v>660.0</v>
@@ -1766,7 +1766,7 @@
         <v>45856.0</v>
       </c>
       <c r="H12" s="45" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37">
@@ -1776,25 +1776,25 @@
         <v>1402001.34</v>
       </c>
       <c r="L12" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="M12" s="40">
+        <v>127</v>
+      </c>
+      <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
       <c r="N12" s="48"/>
       <c r="O12" s="26"/>
       <c r="P12" s="28"/>
-      <c r="V12" s="4"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="42"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="49" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F13" s="36">
         <v>661.0</v>
@@ -1803,7 +1803,7 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I13" s="44"/>
       <c r="J13" s="44">
@@ -1813,25 +1813,25 @@
         <v>1223702.3</v>
       </c>
       <c r="L13" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="M13" s="40">
+        <v>139</v>
+      </c>
+      <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
       <c r="N13" s="48"/>
       <c r="O13" s="26"/>
       <c r="P13" s="50"/>
-      <c r="V13" s="4"/>
+      <c r="V13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="42"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="49" t="s">
         <v>142</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F14" s="35">
         <v>688.0</v>
@@ -1852,23 +1852,23 @@
       <c r="L14" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="M14" s="40">
+      <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
       <c r="N14" s="43"/>
       <c r="O14" s="26"/>
       <c r="P14" s="28"/>
-      <c r="V14" s="4"/>
+      <c r="V14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="42"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="49" t="s">
         <v>145</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F15" s="35">
         <v>696.0</v>
@@ -1877,7 +1877,7 @@
         <v>45923.0</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="I15" s="44"/>
       <c r="J15" s="44">
@@ -1889,22 +1889,22 @@
       <c r="L15" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="M15" s="40">
+      <c r="M15" s="39">
         <v>896744.06</v>
       </c>
       <c r="N15" s="48"/>
       <c r="O15" s="26"/>
-      <c r="V15" s="4"/>
+      <c r="V15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="42"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="49" t="s">
         <v>147</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F16" s="35">
         <v>704.0</v>
@@ -1925,17 +1925,17 @@
       <c r="L16" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="M16" s="40">
+      <c r="M16" s="39">
         <v>919329.06</v>
       </c>
       <c r="N16" s="43"/>
       <c r="O16" s="26"/>
-      <c r="V16" s="4"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="42"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
         <v>150</v>
       </c>
@@ -1959,22 +1959,22 @@
       <c r="L17" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="M17" s="40">
+      <c r="M17" s="39">
         <v>1157009.26</v>
       </c>
       <c r="N17" s="51"/>
       <c r="O17" s="26"/>
-      <c r="V17" s="4"/>
+      <c r="V17" s="3"/>
     </row>
     <row r="18">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="42"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="49" t="s">
         <v>153</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F18" s="35">
         <v>728.0</v>
@@ -1995,7 +1995,7 @@
       <c r="L18" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="M18" s="40">
+      <c r="M18" s="39">
         <v>1214597.952</v>
       </c>
       <c r="N18" s="51"/>
@@ -2007,14 +2007,14 @@
       <c r="V18" s="52"/>
     </row>
     <row r="19">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="42"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="49" t="s">
         <v>156</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F19" s="35">
         <v>278.0</v>
@@ -2035,7 +2035,7 @@
       <c r="L19" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="M19" s="40">
+      <c r="M19" s="39">
         <v>967082.09</v>
       </c>
       <c r="N19" s="51"/>
@@ -2047,9 +2047,9 @@
       <c r="V19" s="52"/>
     </row>
     <row r="20">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="42"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="49" t="s">
         <v>159</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>46078.0</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I20" s="44"/>
       <c r="J20" s="44">
@@ -2073,7 +2073,7 @@
       <c r="L20" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="M20" s="40">
+      <c r="M20" s="39">
         <v>719561.08</v>
       </c>
       <c r="N20" s="51"/>
@@ -2085,9 +2085,9 @@
       <c r="V20" s="52"/>
     </row>
     <row r="21">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="42"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="49" t="s">
         <v>161</v>
       </c>
@@ -2111,7 +2111,7 @@
       <c r="L21" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="M21" s="40">
+      <c r="M21" s="39">
         <v>885881.08</v>
       </c>
       <c r="N21" s="51"/>
@@ -2123,9 +2123,9 @@
       <c r="V21" s="52"/>
     </row>
     <row r="22">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="42"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="49" t="s">
         <v>164</v>
       </c>
@@ -2149,7 +2149,7 @@
       <c r="L22" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="M22" s="40" t="s">
+      <c r="M22" s="39" t="s">
         <v>166</v>
       </c>
       <c r="N22" s="51"/>
@@ -2161,9 +2161,9 @@
       <c r="V22" s="52"/>
     </row>
     <row r="23">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="42"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="41"/>
       <c r="D23" s="49" t="s">
         <v>168</v>
       </c>
@@ -2187,7 +2187,7 @@
       <c r="L23" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="M23" s="40">
+      <c r="M23" s="39">
         <v>1108954.4358333333</v>
       </c>
       <c r="N23" s="53"/>
@@ -2199,9 +2199,9 @@
       <c r="V23" s="52"/>
     </row>
     <row r="24">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="42"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="41"/>
       <c r="D24" s="49" t="s">
         <v>170</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="L24" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="M24" s="40">
+      <c r="M24" s="39">
         <v>218206.1</v>
       </c>
       <c r="N24" s="54"/>
@@ -2237,9 +2237,9 @@
       <c r="V24" s="52"/>
     </row>
     <row r="25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="42"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="49" t="s">
         <v>172</v>
       </c>
@@ -2263,7 +2263,7 @@
       <c r="L25" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="M25" s="40">
+      <c r="M25" s="39">
         <v>1549250.84</v>
       </c>
       <c r="N25" s="53"/>
@@ -2275,8 +2275,8 @@
       <c r="V25" s="52"/>
     </row>
     <row r="26">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="57"/>
       <c r="D26" s="49" t="s">
         <v>174</v>
@@ -2289,9 +2289,9 @@
       <c r="J26" s="56"/>
       <c r="K26" s="46"/>
       <c r="L26" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="M26" s="40" t="s">
+        <v>67</v>
+      </c>
+      <c r="M26" s="39" t="s">
         <v>175</v>
       </c>
       <c r="N26" s="53"/>
@@ -2303,37 +2303,37 @@
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
       <c r="C27" s="29" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>65</v>
+        <v>56</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>57</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G27" s="29"/>
       <c r="H27" s="29" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
       <c r="K27" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="L27" s="32" t="s">
-        <v>77</v>
+        <v>64</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="M27" s="59" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="O27" s="26"/>
       <c r="P27" s="28"/>
@@ -2351,9 +2351,9 @@
       <c r="AC27" s="28"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="33">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="32">
         <v>2.0</v>
       </c>
       <c r="D28" s="60" t="s">
@@ -2400,9 +2400,9 @@
       <c r="AC28" s="28"/>
     </row>
     <row r="29">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="42"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="41"/>
       <c r="D29" s="60" t="s">
         <v>178</v>
       </c>
@@ -2428,7 +2428,7 @@
       <c r="L29" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="M29" s="40">
+      <c r="M29" s="39">
         <v>112720.77</v>
       </c>
       <c r="N29" s="51"/>
@@ -2449,9 +2449,9 @@
       <c r="AC29" s="28"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="42"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="62" t="s">
         <v>181</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>45853.0</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I30" s="44"/>
       <c r="J30" s="44">
@@ -2477,7 +2477,7 @@
       <c r="L30" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="M30" s="40">
+      <c r="M30" s="39">
         <v>378307.61</v>
       </c>
       <c r="N30" s="51"/>
@@ -2498,9 +2498,9 @@
       <c r="AC30" s="28"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
-      <c r="A31" s="24"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="42"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="62" t="s">
         <v>184</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>45910.0</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I31" s="44"/>
       <c r="J31" s="44">
@@ -2526,7 +2526,7 @@
       <c r="L31" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="M31" s="40">
+      <c r="M31" s="39">
         <v>3315.04710000003</v>
       </c>
       <c r="N31" s="51"/>
@@ -2547,9 +2547,9 @@
       <c r="AC31" s="28"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="42"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="41"/>
       <c r="D32" s="62" t="s">
         <v>186</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>45904.0</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I32" s="67"/>
       <c r="J32" s="67">
@@ -2575,7 +2575,7 @@
       <c r="L32" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="M32" s="40">
+      <c r="M32" s="39">
         <v>198332.75</v>
       </c>
       <c r="N32" s="51"/>
@@ -2596,9 +2596,9 @@
       <c r="AC32" s="28"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="42"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="41"/>
       <c r="D33" s="62" t="s">
         <v>188</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>46008.0</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I33" s="67"/>
       <c r="J33" s="67">
@@ -2645,9 +2645,9 @@
       <c r="AC33" s="28"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="42"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="41"/>
       <c r="D34" s="62" t="s">
         <v>191</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>45930.0</v>
       </c>
       <c r="H34" s="35" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I34" s="67"/>
       <c r="J34" s="67">
@@ -2694,9 +2694,9 @@
       <c r="AC34" s="28"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="42"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="41"/>
       <c r="D35" s="62" t="s">
         <v>195</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>45968.0</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I35" s="67"/>
       <c r="J35" s="67">
@@ -2743,9 +2743,9 @@
       <c r="AC35" s="28"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="42"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="62" t="s">
         <v>198</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="66" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I36" s="71"/>
       <c r="J36" s="70">
@@ -2771,7 +2771,7 @@
       <c r="L36" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="M36" s="40">
+      <c r="M36" s="39">
         <v>11372.9</v>
       </c>
       <c r="N36" s="51"/>
@@ -2792,9 +2792,9 @@
       <c r="AC36" s="28"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="42"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="41"/>
       <c r="D37" s="62" t="s">
         <v>200</v>
       </c>
@@ -2808,7 +2808,7 @@
       <c r="J37" s="70"/>
       <c r="K37" s="46"/>
       <c r="L37" s="35"/>
-      <c r="M37" s="40"/>
+      <c r="M37" s="39"/>
       <c r="N37" s="51">
         <v>15854.78</v>
       </c>
@@ -2829,8 +2829,8 @@
       <c r="AC37" s="28"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="24"/>
-      <c r="B38" s="24"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
       <c r="C38" s="57"/>
       <c r="D38" s="62" t="s">
         <v>202</v>
@@ -2845,7 +2845,7 @@
       <c r="J38" s="70"/>
       <c r="K38" s="46"/>
       <c r="L38" s="35"/>
-      <c r="M38" s="40"/>
+      <c r="M38" s="39"/>
       <c r="N38" s="51" t="s">
         <v>203</v>
       </c>
@@ -2866,9 +2866,9 @@
       <c r="AC38" s="28"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="33">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="32">
         <v>3.0</v>
       </c>
       <c r="D39" s="62" t="s">
@@ -2882,7 +2882,7 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="66" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="I39" s="71"/>
       <c r="J39" s="70">
@@ -2917,7 +2917,7 @@
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
-      <c r="C40" s="42"/>
+      <c r="C40" s="41"/>
       <c r="D40" s="62" t="s">
         <v>206</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="66" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="I40" s="71"/>
       <c r="J40" s="70">
@@ -2939,53 +2939,53 @@
         <v>58868.35</v>
       </c>
       <c r="L40" s="35" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M40" s="73">
         <v>58868.35</v>
       </c>
       <c r="N40" s="51"/>
-      <c r="V40" s="4"/>
+      <c r="V40" s="3"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
-      <c r="C41" s="42"/>
+      <c r="C41" s="41"/>
       <c r="K41" s="74"/>
       <c r="M41" s="74"/>
-      <c r="V41" s="4"/>
+      <c r="V41" s="3"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
-      <c r="C42" s="42"/>
+      <c r="C42" s="41"/>
       <c r="K42" s="74"/>
       <c r="M42" s="74"/>
-      <c r="V42" s="4"/>
+      <c r="V42" s="3"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
-      <c r="C43" s="42"/>
-      <c r="V43" s="4"/>
+      <c r="C43" s="41"/>
+      <c r="V43" s="3"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
-      <c r="C44" s="42"/>
-      <c r="V44" s="4"/>
+      <c r="C44" s="41"/>
+      <c r="V44" s="3"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
-      <c r="C45" s="42"/>
-      <c r="V45" s="4"/>
+      <c r="C45" s="41"/>
+      <c r="V45" s="3"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
-      <c r="C46" s="42"/>
-      <c r="V46" s="4"/>
+      <c r="C46" s="41"/>
+      <c r="V46" s="3"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="15"/>
@@ -2993,7 +2993,7 @@
       <c r="C47" s="57"/>
       <c r="K47" s="74"/>
       <c r="M47" s="74"/>
-      <c r="V47" s="4"/>
+      <c r="V47" s="3"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="15"/>
@@ -3017,7 +3017,7 @@
       <c r="S48" s="75"/>
       <c r="T48" s="75"/>
       <c r="U48" s="75"/>
-      <c r="V48" s="4"/>
+      <c r="V48" s="3"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="15"/>
@@ -3234,4622 +3234,4622 @@
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
-      <c r="L102" s="23"/>
+      <c r="L102" s="22"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
-      <c r="L103" s="23"/>
+      <c r="L103" s="22"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
-      <c r="L104" s="23"/>
+      <c r="L104" s="22"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
-      <c r="L105" s="23"/>
+      <c r="L105" s="22"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
-      <c r="L106" s="23"/>
+      <c r="L106" s="22"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
-      <c r="L107" s="23"/>
+      <c r="L107" s="22"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
-      <c r="L108" s="23"/>
+      <c r="L108" s="22"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
-      <c r="L109" s="23"/>
+      <c r="L109" s="22"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
-      <c r="L110" s="23"/>
+      <c r="L110" s="22"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
-      <c r="L111" s="23"/>
+      <c r="L111" s="22"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
-      <c r="L112" s="23"/>
+      <c r="L112" s="22"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
-      <c r="L113" s="23"/>
+      <c r="L113" s="22"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
-      <c r="L114" s="23"/>
+      <c r="L114" s="22"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
-      <c r="L115" s="23"/>
+      <c r="L115" s="22"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
-      <c r="L116" s="23"/>
+      <c r="L116" s="22"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
-      <c r="L117" s="23"/>
+      <c r="L117" s="22"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
-      <c r="L118" s="23"/>
+      <c r="L118" s="22"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
-      <c r="L119" s="23"/>
+      <c r="L119" s="22"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
-      <c r="L120" s="23"/>
+      <c r="L120" s="22"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
-      <c r="L121" s="23"/>
+      <c r="L121" s="22"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
-      <c r="L122" s="23"/>
+      <c r="L122" s="22"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
-      <c r="L123" s="23"/>
+      <c r="L123" s="22"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
-      <c r="L124" s="23"/>
+      <c r="L124" s="22"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
-      <c r="L125" s="23"/>
+      <c r="L125" s="22"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
-      <c r="L126" s="23"/>
+      <c r="L126" s="22"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
-      <c r="L127" s="23"/>
+      <c r="L127" s="22"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
-      <c r="L128" s="23"/>
+      <c r="L128" s="22"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
-      <c r="L129" s="23"/>
+      <c r="L129" s="22"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
-      <c r="L130" s="23"/>
+      <c r="L130" s="22"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
-      <c r="L131" s="23"/>
+      <c r="L131" s="22"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
-      <c r="L132" s="23"/>
+      <c r="L132" s="22"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
-      <c r="L133" s="23"/>
+      <c r="L133" s="22"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
-      <c r="L134" s="23"/>
+      <c r="L134" s="22"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
-      <c r="L135" s="23"/>
+      <c r="L135" s="22"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
-      <c r="L136" s="23"/>
+      <c r="L136" s="22"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
-      <c r="L137" s="23"/>
+      <c r="L137" s="22"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
-      <c r="L138" s="23"/>
+      <c r="L138" s="22"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
-      <c r="L139" s="23"/>
+      <c r="L139" s="22"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
-      <c r="L140" s="23"/>
+      <c r="L140" s="22"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
-      <c r="L141" s="23"/>
+      <c r="L141" s="22"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
-      <c r="L142" s="23"/>
+      <c r="L142" s="22"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
-      <c r="L143" s="23"/>
+      <c r="L143" s="22"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
-      <c r="L144" s="23"/>
+      <c r="L144" s="22"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
-      <c r="L145" s="23"/>
+      <c r="L145" s="22"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
-      <c r="L146" s="23"/>
+      <c r="L146" s="22"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
-      <c r="L147" s="23"/>
+      <c r="L147" s="22"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="15"/>
       <c r="B148" s="15"/>
-      <c r="L148" s="23"/>
+      <c r="L148" s="22"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="15"/>
       <c r="B149" s="15"/>
-      <c r="L149" s="23"/>
+      <c r="L149" s="22"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="15"/>
       <c r="B150" s="15"/>
-      <c r="L150" s="23"/>
+      <c r="L150" s="22"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="15"/>
       <c r="B151" s="15"/>
-      <c r="L151" s="23"/>
+      <c r="L151" s="22"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="15"/>
       <c r="B152" s="15"/>
-      <c r="L152" s="23"/>
+      <c r="L152" s="22"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="15"/>
       <c r="B153" s="15"/>
-      <c r="L153" s="23"/>
+      <c r="L153" s="22"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="15"/>
       <c r="B154" s="15"/>
-      <c r="L154" s="23"/>
+      <c r="L154" s="22"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="15"/>
       <c r="B155" s="15"/>
-      <c r="L155" s="23"/>
+      <c r="L155" s="22"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="15"/>
       <c r="B156" s="15"/>
-      <c r="L156" s="23"/>
+      <c r="L156" s="22"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="15"/>
       <c r="B157" s="15"/>
-      <c r="L157" s="23"/>
+      <c r="L157" s="22"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="15"/>
       <c r="B158" s="15"/>
-      <c r="L158" s="23"/>
+      <c r="L158" s="22"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="15"/>
       <c r="B159" s="15"/>
-      <c r="L159" s="23"/>
+      <c r="L159" s="22"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="15"/>
       <c r="B160" s="15"/>
-      <c r="L160" s="23"/>
+      <c r="L160" s="22"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="15"/>
       <c r="B161" s="15"/>
-      <c r="L161" s="23"/>
+      <c r="L161" s="22"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="15"/>
       <c r="B162" s="15"/>
-      <c r="L162" s="23"/>
+      <c r="L162" s="22"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="15"/>
       <c r="B163" s="15"/>
-      <c r="L163" s="23"/>
+      <c r="L163" s="22"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="15"/>
       <c r="B164" s="15"/>
-      <c r="L164" s="23"/>
+      <c r="L164" s="22"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="15"/>
       <c r="B165" s="15"/>
-      <c r="L165" s="23"/>
+      <c r="L165" s="22"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="15"/>
       <c r="B166" s="15"/>
-      <c r="L166" s="23"/>
+      <c r="L166" s="22"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="15"/>
       <c r="B167" s="15"/>
-      <c r="L167" s="23"/>
+      <c r="L167" s="22"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="15"/>
       <c r="B168" s="15"/>
-      <c r="L168" s="23"/>
+      <c r="L168" s="22"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="15"/>
       <c r="B169" s="15"/>
-      <c r="L169" s="23"/>
+      <c r="L169" s="22"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="15"/>
       <c r="B170" s="15"/>
-      <c r="L170" s="23"/>
+      <c r="L170" s="22"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="15"/>
       <c r="B171" s="15"/>
-      <c r="L171" s="23"/>
+      <c r="L171" s="22"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="15"/>
       <c r="B172" s="15"/>
-      <c r="L172" s="23"/>
+      <c r="L172" s="22"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="15"/>
       <c r="B173" s="15"/>
-      <c r="L173" s="23"/>
+      <c r="L173" s="22"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="15"/>
       <c r="B174" s="15"/>
-      <c r="L174" s="23"/>
+      <c r="L174" s="22"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="15"/>
       <c r="B175" s="15"/>
-      <c r="L175" s="23"/>
+      <c r="L175" s="22"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="15"/>
       <c r="B176" s="15"/>
-      <c r="L176" s="23"/>
+      <c r="L176" s="22"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="15"/>
       <c r="B177" s="15"/>
-      <c r="L177" s="23"/>
+      <c r="L177" s="22"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="15"/>
       <c r="B178" s="15"/>
-      <c r="L178" s="23"/>
+      <c r="L178" s="22"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="15"/>
       <c r="B179" s="15"/>
-      <c r="L179" s="23"/>
+      <c r="L179" s="22"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="15"/>
       <c r="B180" s="15"/>
-      <c r="L180" s="23"/>
+      <c r="L180" s="22"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="15"/>
       <c r="B181" s="15"/>
-      <c r="L181" s="23"/>
+      <c r="L181" s="22"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="15"/>
       <c r="B182" s="15"/>
-      <c r="L182" s="23"/>
+      <c r="L182" s="22"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="15"/>
       <c r="B183" s="15"/>
-      <c r="L183" s="23"/>
+      <c r="L183" s="22"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="15"/>
       <c r="B184" s="15"/>
-      <c r="L184" s="23"/>
+      <c r="L184" s="22"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="15"/>
       <c r="B185" s="15"/>
-      <c r="L185" s="23"/>
+      <c r="L185" s="22"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="15"/>
       <c r="B186" s="15"/>
-      <c r="L186" s="23"/>
+      <c r="L186" s="22"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="15"/>
       <c r="B187" s="15"/>
-      <c r="L187" s="23"/>
+      <c r="L187" s="22"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="15"/>
       <c r="B188" s="15"/>
-      <c r="L188" s="23"/>
+      <c r="L188" s="22"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="15"/>
       <c r="B189" s="15"/>
-      <c r="L189" s="23"/>
+      <c r="L189" s="22"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="15"/>
       <c r="B190" s="15"/>
-      <c r="L190" s="23"/>
+      <c r="L190" s="22"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="15"/>
       <c r="B191" s="15"/>
-      <c r="L191" s="23"/>
+      <c r="L191" s="22"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="15"/>
       <c r="B192" s="15"/>
-      <c r="L192" s="23"/>
+      <c r="L192" s="22"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="15"/>
       <c r="B193" s="15"/>
-      <c r="L193" s="23"/>
+      <c r="L193" s="22"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="15"/>
       <c r="B194" s="15"/>
-      <c r="L194" s="23"/>
+      <c r="L194" s="22"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="15"/>
       <c r="B195" s="15"/>
-      <c r="L195" s="23"/>
+      <c r="L195" s="22"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="15"/>
       <c r="B196" s="15"/>
-      <c r="L196" s="23"/>
+      <c r="L196" s="22"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="15"/>
       <c r="B197" s="15"/>
-      <c r="L197" s="23"/>
+      <c r="L197" s="22"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="15"/>
       <c r="B198" s="15"/>
-      <c r="L198" s="23"/>
+      <c r="L198" s="22"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="15"/>
       <c r="B199" s="15"/>
-      <c r="L199" s="23"/>
+      <c r="L199" s="22"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="15"/>
       <c r="B200" s="15"/>
-      <c r="L200" s="23"/>
+      <c r="L200" s="22"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="15"/>
       <c r="B201" s="15"/>
-      <c r="L201" s="23"/>
+      <c r="L201" s="22"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="15"/>
       <c r="B202" s="15"/>
-      <c r="L202" s="23"/>
+      <c r="L202" s="22"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="15"/>
       <c r="B203" s="15"/>
-      <c r="L203" s="23"/>
+      <c r="L203" s="22"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="15"/>
       <c r="B204" s="15"/>
-      <c r="L204" s="23"/>
+      <c r="L204" s="22"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="15"/>
       <c r="B205" s="15"/>
-      <c r="L205" s="23"/>
+      <c r="L205" s="22"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="15"/>
       <c r="B206" s="15"/>
-      <c r="L206" s="23"/>
+      <c r="L206" s="22"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="15"/>
       <c r="B207" s="15"/>
-      <c r="L207" s="23"/>
+      <c r="L207" s="22"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="15"/>
       <c r="B208" s="15"/>
-      <c r="L208" s="23"/>
+      <c r="L208" s="22"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="15"/>
       <c r="B209" s="15"/>
-      <c r="L209" s="23"/>
+      <c r="L209" s="22"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="15"/>
       <c r="B210" s="15"/>
-      <c r="L210" s="23"/>
+      <c r="L210" s="22"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="15"/>
       <c r="B211" s="15"/>
-      <c r="L211" s="23"/>
+      <c r="L211" s="22"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="15"/>
       <c r="B212" s="15"/>
-      <c r="L212" s="23"/>
+      <c r="L212" s="22"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="15"/>
       <c r="B213" s="15"/>
-      <c r="L213" s="23"/>
+      <c r="L213" s="22"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="15"/>
       <c r="B214" s="15"/>
-      <c r="L214" s="23"/>
+      <c r="L214" s="22"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="15"/>
       <c r="B215" s="15"/>
-      <c r="L215" s="23"/>
+      <c r="L215" s="22"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="15"/>
       <c r="B216" s="15"/>
-      <c r="L216" s="23"/>
+      <c r="L216" s="22"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="15"/>
       <c r="B217" s="15"/>
-      <c r="L217" s="23"/>
+      <c r="L217" s="22"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="15"/>
       <c r="B218" s="15"/>
-      <c r="L218" s="23"/>
+      <c r="L218" s="22"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="15"/>
       <c r="B219" s="15"/>
-      <c r="L219" s="23"/>
+      <c r="L219" s="22"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="15"/>
       <c r="B220" s="15"/>
-      <c r="L220" s="23"/>
+      <c r="L220" s="22"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="15"/>
       <c r="B221" s="15"/>
-      <c r="L221" s="23"/>
+      <c r="L221" s="22"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="15"/>
       <c r="B222" s="15"/>
-      <c r="L222" s="23"/>
+      <c r="L222" s="22"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="15"/>
       <c r="B223" s="15"/>
-      <c r="L223" s="23"/>
+      <c r="L223" s="22"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="15"/>
       <c r="B224" s="15"/>
-      <c r="L224" s="23"/>
+      <c r="L224" s="22"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="15"/>
       <c r="B225" s="15"/>
-      <c r="L225" s="23"/>
+      <c r="L225" s="22"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="15"/>
       <c r="B226" s="15"/>
-      <c r="L226" s="23"/>
+      <c r="L226" s="22"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
       <c r="A227" s="15"/>
       <c r="B227" s="15"/>
-      <c r="L227" s="23"/>
+      <c r="L227" s="22"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="15"/>
       <c r="B228" s="15"/>
-      <c r="L228" s="23"/>
+      <c r="L228" s="22"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="A229" s="15"/>
       <c r="B229" s="15"/>
-      <c r="L229" s="23"/>
+      <c r="L229" s="22"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="15"/>
       <c r="B230" s="15"/>
-      <c r="L230" s="23"/>
+      <c r="L230" s="22"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="15"/>
       <c r="B231" s="15"/>
-      <c r="L231" s="23"/>
+      <c r="L231" s="22"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="15"/>
       <c r="B232" s="15"/>
-      <c r="L232" s="23"/>
+      <c r="L232" s="22"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="15"/>
       <c r="B233" s="15"/>
-      <c r="L233" s="23"/>
+      <c r="L233" s="22"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="15"/>
       <c r="B234" s="15"/>
-      <c r="L234" s="23"/>
+      <c r="L234" s="22"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
       <c r="A235" s="15"/>
       <c r="B235" s="15"/>
-      <c r="L235" s="23"/>
+      <c r="L235" s="22"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
       <c r="A236" s="15"/>
       <c r="B236" s="15"/>
-      <c r="L236" s="23"/>
+      <c r="L236" s="22"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
       <c r="A237" s="15"/>
       <c r="B237" s="15"/>
-      <c r="L237" s="23"/>
+      <c r="L237" s="22"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="A238" s="15"/>
       <c r="B238" s="15"/>
-      <c r="L238" s="23"/>
+      <c r="L238" s="22"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
       <c r="A239" s="15"/>
       <c r="B239" s="15"/>
-      <c r="L239" s="23"/>
+      <c r="L239" s="22"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
       <c r="A240" s="15"/>
       <c r="B240" s="15"/>
-      <c r="L240" s="23"/>
+      <c r="L240" s="22"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
       <c r="A241" s="15"/>
       <c r="B241" s="15"/>
-      <c r="L241" s="23"/>
+      <c r="L241" s="22"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="A242" s="15"/>
       <c r="B242" s="15"/>
-      <c r="L242" s="23"/>
+      <c r="L242" s="22"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
       <c r="A243" s="15"/>
       <c r="B243" s="15"/>
-      <c r="L243" s="23"/>
+      <c r="L243" s="22"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
       <c r="A244" s="15"/>
       <c r="B244" s="15"/>
-      <c r="L244" s="23"/>
+      <c r="L244" s="22"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="A245" s="15"/>
       <c r="B245" s="15"/>
-      <c r="L245" s="23"/>
+      <c r="L245" s="22"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="A246" s="15"/>
       <c r="B246" s="15"/>
-      <c r="L246" s="23"/>
+      <c r="L246" s="22"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
       <c r="A247" s="15"/>
       <c r="B247" s="15"/>
-      <c r="L247" s="23"/>
+      <c r="L247" s="22"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
       <c r="A248" s="15"/>
       <c r="B248" s="15"/>
-      <c r="L248" s="23"/>
+      <c r="L248" s="22"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
       <c r="A249" s="15"/>
       <c r="B249" s="15"/>
-      <c r="L249" s="23"/>
+      <c r="L249" s="22"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="A250" s="15"/>
       <c r="B250" s="15"/>
-      <c r="L250" s="23"/>
+      <c r="L250" s="22"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
       <c r="A251" s="15"/>
       <c r="B251" s="15"/>
-      <c r="L251" s="23"/>
+      <c r="L251" s="22"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
       <c r="A252" s="15"/>
       <c r="B252" s="15"/>
-      <c r="L252" s="23"/>
+      <c r="L252" s="22"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
       <c r="A253" s="15"/>
       <c r="B253" s="15"/>
-      <c r="L253" s="23"/>
+      <c r="L253" s="22"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="A254" s="15"/>
       <c r="B254" s="15"/>
-      <c r="L254" s="23"/>
+      <c r="L254" s="22"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
       <c r="A255" s="15"/>
       <c r="B255" s="15"/>
-      <c r="L255" s="23"/>
+      <c r="L255" s="22"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
       <c r="A256" s="15"/>
       <c r="B256" s="15"/>
-      <c r="L256" s="23"/>
+      <c r="L256" s="22"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="A257" s="15"/>
       <c r="B257" s="15"/>
-      <c r="L257" s="23"/>
+      <c r="L257" s="22"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="A258" s="15"/>
       <c r="B258" s="15"/>
-      <c r="L258" s="23"/>
+      <c r="L258" s="22"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
       <c r="A259" s="15"/>
       <c r="B259" s="15"/>
-      <c r="L259" s="23"/>
+      <c r="L259" s="22"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
       <c r="A260" s="15"/>
       <c r="B260" s="15"/>
-      <c r="L260" s="23"/>
+      <c r="L260" s="22"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="A261" s="15"/>
       <c r="B261" s="15"/>
-      <c r="L261" s="23"/>
+      <c r="L261" s="22"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="A262" s="15"/>
       <c r="B262" s="15"/>
-      <c r="L262" s="23"/>
+      <c r="L262" s="22"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
       <c r="A263" s="15"/>
       <c r="B263" s="15"/>
-      <c r="L263" s="23"/>
+      <c r="L263" s="22"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
       <c r="A264" s="15"/>
       <c r="B264" s="15"/>
-      <c r="L264" s="23"/>
+      <c r="L264" s="22"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="A265" s="15"/>
       <c r="B265" s="15"/>
-      <c r="L265" s="23"/>
+      <c r="L265" s="22"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="A266" s="15"/>
       <c r="B266" s="15"/>
-      <c r="L266" s="23"/>
+      <c r="L266" s="22"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
       <c r="A267" s="15"/>
       <c r="B267" s="15"/>
-      <c r="L267" s="23"/>
+      <c r="L267" s="22"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
       <c r="A268" s="15"/>
       <c r="B268" s="15"/>
-      <c r="L268" s="23"/>
+      <c r="L268" s="22"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="A269" s="15"/>
       <c r="B269" s="15"/>
-      <c r="L269" s="23"/>
+      <c r="L269" s="22"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="A270" s="15"/>
       <c r="B270" s="15"/>
-      <c r="L270" s="23"/>
+      <c r="L270" s="22"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
       <c r="A271" s="15"/>
       <c r="B271" s="15"/>
-      <c r="L271" s="23"/>
+      <c r="L271" s="22"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
       <c r="A272" s="15"/>
       <c r="B272" s="15"/>
-      <c r="L272" s="23"/>
+      <c r="L272" s="22"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="A273" s="15"/>
       <c r="B273" s="15"/>
-      <c r="L273" s="23"/>
+      <c r="L273" s="22"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="A274" s="15"/>
       <c r="B274" s="15"/>
-      <c r="L274" s="23"/>
+      <c r="L274" s="22"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
       <c r="A275" s="15"/>
       <c r="B275" s="15"/>
-      <c r="L275" s="23"/>
+      <c r="L275" s="22"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
       <c r="A276" s="15"/>
       <c r="B276" s="15"/>
-      <c r="L276" s="23"/>
+      <c r="L276" s="22"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
       <c r="A277" s="15"/>
       <c r="B277" s="15"/>
-      <c r="L277" s="23"/>
+      <c r="L277" s="22"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="A278" s="15"/>
       <c r="B278" s="15"/>
-      <c r="L278" s="23"/>
+      <c r="L278" s="22"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
       <c r="A279" s="15"/>
       <c r="B279" s="15"/>
-      <c r="L279" s="23"/>
+      <c r="L279" s="22"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
       <c r="A280" s="15"/>
       <c r="B280" s="15"/>
-      <c r="L280" s="23"/>
+      <c r="L280" s="22"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
       <c r="A281" s="15"/>
       <c r="B281" s="15"/>
-      <c r="L281" s="23"/>
+      <c r="L281" s="22"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="A282" s="15"/>
       <c r="B282" s="15"/>
-      <c r="L282" s="23"/>
+      <c r="L282" s="22"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
       <c r="A283" s="15"/>
       <c r="B283" s="15"/>
-      <c r="L283" s="23"/>
+      <c r="L283" s="22"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
       <c r="A284" s="15"/>
       <c r="B284" s="15"/>
-      <c r="L284" s="23"/>
+      <c r="L284" s="22"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
       <c r="A285" s="15"/>
       <c r="B285" s="15"/>
-      <c r="L285" s="23"/>
+      <c r="L285" s="22"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="A286" s="15"/>
       <c r="B286" s="15"/>
-      <c r="L286" s="23"/>
+      <c r="L286" s="22"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
       <c r="A287" s="15"/>
       <c r="B287" s="15"/>
-      <c r="L287" s="23"/>
+      <c r="L287" s="22"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
       <c r="A288" s="15"/>
       <c r="B288" s="15"/>
-      <c r="L288" s="23"/>
+      <c r="L288" s="22"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="A289" s="15"/>
       <c r="B289" s="15"/>
-      <c r="L289" s="23"/>
+      <c r="L289" s="22"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="A290" s="15"/>
       <c r="B290" s="15"/>
-      <c r="L290" s="23"/>
+      <c r="L290" s="22"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
       <c r="A291" s="15"/>
       <c r="B291" s="15"/>
-      <c r="L291" s="23"/>
+      <c r="L291" s="22"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
       <c r="A292" s="15"/>
       <c r="B292" s="15"/>
-      <c r="L292" s="23"/>
+      <c r="L292" s="22"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
       <c r="A293" s="15"/>
       <c r="B293" s="15"/>
-      <c r="L293" s="23"/>
+      <c r="L293" s="22"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
       <c r="A294" s="15"/>
       <c r="B294" s="15"/>
-      <c r="L294" s="23"/>
+      <c r="L294" s="22"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
       <c r="A295" s="15"/>
       <c r="B295" s="15"/>
-      <c r="L295" s="23"/>
+      <c r="L295" s="22"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
       <c r="A296" s="15"/>
       <c r="B296" s="15"/>
-      <c r="L296" s="23"/>
+      <c r="L296" s="22"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
       <c r="A297" s="15"/>
       <c r="B297" s="15"/>
-      <c r="L297" s="23"/>
+      <c r="L297" s="22"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="A298" s="15"/>
       <c r="B298" s="15"/>
-      <c r="L298" s="23"/>
+      <c r="L298" s="22"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
       <c r="A299" s="15"/>
       <c r="B299" s="15"/>
-      <c r="L299" s="23"/>
+      <c r="L299" s="22"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
       <c r="A300" s="15"/>
       <c r="B300" s="15"/>
-      <c r="L300" s="23"/>
+      <c r="L300" s="22"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
       <c r="A301" s="15"/>
       <c r="B301" s="15"/>
-      <c r="L301" s="23"/>
+      <c r="L301" s="22"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="A302" s="15"/>
       <c r="B302" s="15"/>
-      <c r="L302" s="23"/>
+      <c r="L302" s="22"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
       <c r="A303" s="15"/>
       <c r="B303" s="15"/>
-      <c r="L303" s="23"/>
+      <c r="L303" s="22"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
       <c r="A304" s="15"/>
       <c r="B304" s="15"/>
-      <c r="L304" s="23"/>
+      <c r="L304" s="22"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
       <c r="A305" s="15"/>
       <c r="B305" s="15"/>
-      <c r="L305" s="23"/>
+      <c r="L305" s="22"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="A306" s="15"/>
       <c r="B306" s="15"/>
-      <c r="L306" s="23"/>
+      <c r="L306" s="22"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
       <c r="A307" s="15"/>
       <c r="B307" s="15"/>
-      <c r="L307" s="23"/>
+      <c r="L307" s="22"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
       <c r="A308" s="15"/>
       <c r="B308" s="15"/>
-      <c r="L308" s="23"/>
+      <c r="L308" s="22"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
       <c r="A309" s="15"/>
       <c r="B309" s="15"/>
-      <c r="L309" s="23"/>
+      <c r="L309" s="22"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="A310" s="15"/>
       <c r="B310" s="15"/>
-      <c r="L310" s="23"/>
+      <c r="L310" s="22"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
       <c r="A311" s="15"/>
       <c r="B311" s="15"/>
-      <c r="L311" s="23"/>
+      <c r="L311" s="22"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
       <c r="A312" s="15"/>
       <c r="B312" s="15"/>
-      <c r="L312" s="23"/>
+      <c r="L312" s="22"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
       <c r="A313" s="15"/>
       <c r="B313" s="15"/>
-      <c r="L313" s="23"/>
+      <c r="L313" s="22"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="A314" s="15"/>
       <c r="B314" s="15"/>
-      <c r="L314" s="23"/>
+      <c r="L314" s="22"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
       <c r="A315" s="15"/>
       <c r="B315" s="15"/>
-      <c r="L315" s="23"/>
+      <c r="L315" s="22"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="A316" s="15"/>
       <c r="B316" s="15"/>
-      <c r="L316" s="23"/>
+      <c r="L316" s="22"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="A317" s="15"/>
       <c r="B317" s="15"/>
-      <c r="L317" s="23"/>
+      <c r="L317" s="22"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="A318" s="15"/>
       <c r="B318" s="15"/>
-      <c r="L318" s="23"/>
+      <c r="L318" s="22"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
       <c r="A319" s="15"/>
       <c r="B319" s="15"/>
-      <c r="L319" s="23"/>
+      <c r="L319" s="22"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="A320" s="15"/>
       <c r="B320" s="15"/>
-      <c r="L320" s="23"/>
+      <c r="L320" s="22"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="A321" s="15"/>
       <c r="B321" s="15"/>
-      <c r="L321" s="23"/>
+      <c r="L321" s="22"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="A322" s="15"/>
       <c r="B322" s="15"/>
-      <c r="L322" s="23"/>
+      <c r="L322" s="22"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
       <c r="A323" s="15"/>
       <c r="B323" s="15"/>
-      <c r="L323" s="23"/>
+      <c r="L323" s="22"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="A324" s="15"/>
       <c r="B324" s="15"/>
-      <c r="L324" s="23"/>
+      <c r="L324" s="22"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="A325" s="15"/>
       <c r="B325" s="15"/>
-      <c r="L325" s="23"/>
+      <c r="L325" s="22"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="A326" s="15"/>
       <c r="B326" s="15"/>
-      <c r="L326" s="23"/>
+      <c r="L326" s="22"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
       <c r="A327" s="15"/>
       <c r="B327" s="15"/>
-      <c r="L327" s="23"/>
+      <c r="L327" s="22"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="A328" s="15"/>
       <c r="B328" s="15"/>
-      <c r="L328" s="23"/>
+      <c r="L328" s="22"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="A329" s="15"/>
       <c r="B329" s="15"/>
-      <c r="L329" s="23"/>
+      <c r="L329" s="22"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="A330" s="15"/>
       <c r="B330" s="15"/>
-      <c r="L330" s="23"/>
+      <c r="L330" s="22"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
       <c r="A331" s="15"/>
       <c r="B331" s="15"/>
-      <c r="L331" s="23"/>
+      <c r="L331" s="22"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="A332" s="15"/>
       <c r="B332" s="15"/>
-      <c r="L332" s="23"/>
+      <c r="L332" s="22"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="A333" s="15"/>
       <c r="B333" s="15"/>
-      <c r="L333" s="23"/>
+      <c r="L333" s="22"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="A334" s="15"/>
       <c r="B334" s="15"/>
-      <c r="L334" s="23"/>
+      <c r="L334" s="22"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
       <c r="A335" s="15"/>
       <c r="B335" s="15"/>
-      <c r="L335" s="23"/>
+      <c r="L335" s="22"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="A336" s="15"/>
       <c r="B336" s="15"/>
-      <c r="L336" s="23"/>
+      <c r="L336" s="22"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="A337" s="15"/>
       <c r="B337" s="15"/>
-      <c r="L337" s="23"/>
+      <c r="L337" s="22"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="A338" s="15"/>
       <c r="B338" s="15"/>
-      <c r="L338" s="23"/>
+      <c r="L338" s="22"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
       <c r="A339" s="15"/>
       <c r="B339" s="15"/>
-      <c r="L339" s="23"/>
+      <c r="L339" s="22"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="A340" s="15"/>
       <c r="B340" s="15"/>
-      <c r="L340" s="23"/>
+      <c r="L340" s="22"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="A341" s="15"/>
       <c r="B341" s="15"/>
-      <c r="L341" s="23"/>
+      <c r="L341" s="22"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="A342" s="15"/>
       <c r="B342" s="15"/>
-      <c r="L342" s="23"/>
+      <c r="L342" s="22"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
       <c r="A343" s="15"/>
       <c r="B343" s="15"/>
-      <c r="L343" s="23"/>
+      <c r="L343" s="22"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="A344" s="15"/>
       <c r="B344" s="15"/>
-      <c r="L344" s="23"/>
+      <c r="L344" s="22"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="A345" s="15"/>
       <c r="B345" s="15"/>
-      <c r="L345" s="23"/>
+      <c r="L345" s="22"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="A346" s="15"/>
       <c r="B346" s="15"/>
-      <c r="L346" s="23"/>
+      <c r="L346" s="22"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
       <c r="A347" s="15"/>
       <c r="B347" s="15"/>
-      <c r="L347" s="23"/>
+      <c r="L347" s="22"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="A348" s="15"/>
       <c r="B348" s="15"/>
-      <c r="L348" s="23"/>
+      <c r="L348" s="22"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="A349" s="15"/>
       <c r="B349" s="15"/>
-      <c r="L349" s="23"/>
+      <c r="L349" s="22"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="A350" s="15"/>
       <c r="B350" s="15"/>
-      <c r="L350" s="23"/>
+      <c r="L350" s="22"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
       <c r="A351" s="15"/>
       <c r="B351" s="15"/>
-      <c r="L351" s="23"/>
+      <c r="L351" s="22"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="A352" s="15"/>
       <c r="B352" s="15"/>
-      <c r="L352" s="23"/>
+      <c r="L352" s="22"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="A353" s="15"/>
       <c r="B353" s="15"/>
-      <c r="L353" s="23"/>
+      <c r="L353" s="22"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="A354" s="15"/>
       <c r="B354" s="15"/>
-      <c r="L354" s="23"/>
+      <c r="L354" s="22"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
       <c r="A355" s="15"/>
       <c r="B355" s="15"/>
-      <c r="L355" s="23"/>
+      <c r="L355" s="22"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="A356" s="15"/>
       <c r="B356" s="15"/>
-      <c r="L356" s="23"/>
+      <c r="L356" s="22"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="A357" s="15"/>
       <c r="B357" s="15"/>
-      <c r="L357" s="23"/>
+      <c r="L357" s="22"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="A358" s="15"/>
       <c r="B358" s="15"/>
-      <c r="L358" s="23"/>
+      <c r="L358" s="22"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="A359" s="15"/>
       <c r="B359" s="15"/>
-      <c r="L359" s="23"/>
+      <c r="L359" s="22"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="A360" s="15"/>
       <c r="B360" s="15"/>
-      <c r="L360" s="23"/>
+      <c r="L360" s="22"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="A361" s="15"/>
       <c r="B361" s="15"/>
-      <c r="L361" s="23"/>
+      <c r="L361" s="22"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="A362" s="15"/>
       <c r="B362" s="15"/>
-      <c r="L362" s="23"/>
+      <c r="L362" s="22"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
       <c r="A363" s="15"/>
       <c r="B363" s="15"/>
-      <c r="L363" s="23"/>
+      <c r="L363" s="22"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="A364" s="15"/>
       <c r="B364" s="15"/>
-      <c r="L364" s="23"/>
+      <c r="L364" s="22"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="A365" s="15"/>
       <c r="B365" s="15"/>
-      <c r="L365" s="23"/>
+      <c r="L365" s="22"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="A366" s="15"/>
       <c r="B366" s="15"/>
-      <c r="L366" s="23"/>
+      <c r="L366" s="22"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="A367" s="15"/>
       <c r="B367" s="15"/>
-      <c r="L367" s="23"/>
+      <c r="L367" s="22"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="A368" s="15"/>
       <c r="B368" s="15"/>
-      <c r="L368" s="23"/>
+      <c r="L368" s="22"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="A369" s="15"/>
       <c r="B369" s="15"/>
-      <c r="L369" s="23"/>
+      <c r="L369" s="22"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="A370" s="15"/>
       <c r="B370" s="15"/>
-      <c r="L370" s="23"/>
+      <c r="L370" s="22"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
       <c r="A371" s="15"/>
       <c r="B371" s="15"/>
-      <c r="L371" s="23"/>
+      <c r="L371" s="22"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="A372" s="15"/>
       <c r="B372" s="15"/>
-      <c r="L372" s="23"/>
+      <c r="L372" s="22"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="A373" s="15"/>
       <c r="B373" s="15"/>
-      <c r="L373" s="23"/>
+      <c r="L373" s="22"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="A374" s="15"/>
       <c r="B374" s="15"/>
-      <c r="L374" s="23"/>
+      <c r="L374" s="22"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="A375" s="15"/>
       <c r="B375" s="15"/>
-      <c r="L375" s="23"/>
+      <c r="L375" s="22"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="A376" s="15"/>
       <c r="B376" s="15"/>
-      <c r="L376" s="23"/>
+      <c r="L376" s="22"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="A377" s="15"/>
       <c r="B377" s="15"/>
-      <c r="L377" s="23"/>
+      <c r="L377" s="22"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="A378" s="15"/>
       <c r="B378" s="15"/>
-      <c r="L378" s="23"/>
+      <c r="L378" s="22"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="A379" s="15"/>
       <c r="B379" s="15"/>
-      <c r="L379" s="23"/>
+      <c r="L379" s="22"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="A380" s="15"/>
       <c r="B380" s="15"/>
-      <c r="L380" s="23"/>
+      <c r="L380" s="22"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="A381" s="15"/>
       <c r="B381" s="15"/>
-      <c r="L381" s="23"/>
+      <c r="L381" s="22"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="A382" s="15"/>
       <c r="B382" s="15"/>
-      <c r="L382" s="23"/>
+      <c r="L382" s="22"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
       <c r="A383" s="15"/>
       <c r="B383" s="15"/>
-      <c r="L383" s="23"/>
+      <c r="L383" s="22"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="A384" s="15"/>
       <c r="B384" s="15"/>
-      <c r="L384" s="23"/>
+      <c r="L384" s="22"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="A385" s="15"/>
       <c r="B385" s="15"/>
-      <c r="L385" s="23"/>
+      <c r="L385" s="22"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="A386" s="15"/>
       <c r="B386" s="15"/>
-      <c r="L386" s="23"/>
+      <c r="L386" s="22"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
       <c r="A387" s="15"/>
       <c r="B387" s="15"/>
-      <c r="L387" s="23"/>
+      <c r="L387" s="22"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
       <c r="A388" s="15"/>
       <c r="B388" s="15"/>
-      <c r="L388" s="23"/>
+      <c r="L388" s="22"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
       <c r="A389" s="15"/>
       <c r="B389" s="15"/>
-      <c r="L389" s="23"/>
+      <c r="L389" s="22"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
       <c r="A390" s="15"/>
       <c r="B390" s="15"/>
-      <c r="L390" s="23"/>
+      <c r="L390" s="22"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
       <c r="A391" s="15"/>
       <c r="B391" s="15"/>
-      <c r="L391" s="23"/>
+      <c r="L391" s="22"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
       <c r="A392" s="15"/>
       <c r="B392" s="15"/>
-      <c r="L392" s="23"/>
+      <c r="L392" s="22"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
       <c r="A393" s="15"/>
       <c r="B393" s="15"/>
-      <c r="L393" s="23"/>
+      <c r="L393" s="22"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
       <c r="A394" s="15"/>
       <c r="B394" s="15"/>
-      <c r="L394" s="23"/>
+      <c r="L394" s="22"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
       <c r="A395" s="15"/>
       <c r="B395" s="15"/>
-      <c r="L395" s="23"/>
+      <c r="L395" s="22"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
       <c r="A396" s="15"/>
       <c r="B396" s="15"/>
-      <c r="L396" s="23"/>
+      <c r="L396" s="22"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
       <c r="A397" s="15"/>
       <c r="B397" s="15"/>
-      <c r="L397" s="23"/>
+      <c r="L397" s="22"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
       <c r="A398" s="15"/>
       <c r="B398" s="15"/>
-      <c r="L398" s="23"/>
+      <c r="L398" s="22"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
       <c r="A399" s="15"/>
       <c r="B399" s="15"/>
-      <c r="L399" s="23"/>
+      <c r="L399" s="22"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
       <c r="A400" s="15"/>
       <c r="B400" s="15"/>
-      <c r="L400" s="23"/>
+      <c r="L400" s="22"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
       <c r="A401" s="15"/>
       <c r="B401" s="15"/>
-      <c r="L401" s="23"/>
+      <c r="L401" s="22"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
       <c r="A402" s="15"/>
       <c r="B402" s="15"/>
-      <c r="L402" s="23"/>
+      <c r="L402" s="22"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
       <c r="A403" s="15"/>
       <c r="B403" s="15"/>
-      <c r="L403" s="23"/>
+      <c r="L403" s="22"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
       <c r="A404" s="15"/>
       <c r="B404" s="15"/>
-      <c r="L404" s="23"/>
+      <c r="L404" s="22"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
       <c r="A405" s="15"/>
       <c r="B405" s="15"/>
-      <c r="L405" s="23"/>
+      <c r="L405" s="22"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
       <c r="A406" s="15"/>
       <c r="B406" s="15"/>
-      <c r="L406" s="23"/>
+      <c r="L406" s="22"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
       <c r="A407" s="15"/>
       <c r="B407" s="15"/>
-      <c r="L407" s="23"/>
+      <c r="L407" s="22"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="A408" s="15"/>
       <c r="B408" s="15"/>
-      <c r="L408" s="23"/>
+      <c r="L408" s="22"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
       <c r="A409" s="15"/>
       <c r="B409" s="15"/>
-      <c r="L409" s="23"/>
+      <c r="L409" s="22"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="A410" s="15"/>
       <c r="B410" s="15"/>
-      <c r="L410" s="23"/>
+      <c r="L410" s="22"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
       <c r="A411" s="15"/>
       <c r="B411" s="15"/>
-      <c r="L411" s="23"/>
+      <c r="L411" s="22"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
       <c r="A412" s="15"/>
       <c r="B412" s="15"/>
-      <c r="L412" s="23"/>
+      <c r="L412" s="22"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
       <c r="A413" s="15"/>
       <c r="B413" s="15"/>
-      <c r="L413" s="23"/>
+      <c r="L413" s="22"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
       <c r="A414" s="15"/>
       <c r="B414" s="15"/>
-      <c r="L414" s="23"/>
+      <c r="L414" s="22"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
       <c r="A415" s="15"/>
       <c r="B415" s="15"/>
-      <c r="L415" s="23"/>
+      <c r="L415" s="22"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="A416" s="15"/>
       <c r="B416" s="15"/>
-      <c r="L416" s="23"/>
+      <c r="L416" s="22"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
       <c r="A417" s="15"/>
       <c r="B417" s="15"/>
-      <c r="L417" s="23"/>
+      <c r="L417" s="22"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="A418" s="15"/>
       <c r="B418" s="15"/>
-      <c r="L418" s="23"/>
+      <c r="L418" s="22"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
       <c r="A419" s="15"/>
       <c r="B419" s="15"/>
-      <c r="L419" s="23"/>
+      <c r="L419" s="22"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
       <c r="A420" s="15"/>
       <c r="B420" s="15"/>
-      <c r="L420" s="23"/>
+      <c r="L420" s="22"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
       <c r="A421" s="15"/>
       <c r="B421" s="15"/>
-      <c r="L421" s="23"/>
+      <c r="L421" s="22"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
       <c r="A422" s="15"/>
       <c r="B422" s="15"/>
-      <c r="L422" s="23"/>
+      <c r="L422" s="22"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
       <c r="A423" s="15"/>
       <c r="B423" s="15"/>
-      <c r="L423" s="23"/>
+      <c r="L423" s="22"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
       <c r="A424" s="15"/>
       <c r="B424" s="15"/>
-      <c r="L424" s="23"/>
+      <c r="L424" s="22"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
       <c r="A425" s="15"/>
       <c r="B425" s="15"/>
-      <c r="L425" s="23"/>
+      <c r="L425" s="22"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
       <c r="A426" s="15"/>
       <c r="B426" s="15"/>
-      <c r="L426" s="23"/>
+      <c r="L426" s="22"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="A427" s="15"/>
       <c r="B427" s="15"/>
-      <c r="L427" s="23"/>
+      <c r="L427" s="22"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="A428" s="15"/>
       <c r="B428" s="15"/>
-      <c r="L428" s="23"/>
+      <c r="L428" s="22"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="A429" s="15"/>
       <c r="B429" s="15"/>
-      <c r="L429" s="23"/>
+      <c r="L429" s="22"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="A430" s="15"/>
       <c r="B430" s="15"/>
-      <c r="L430" s="23"/>
+      <c r="L430" s="22"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="A431" s="15"/>
       <c r="B431" s="15"/>
-      <c r="L431" s="23"/>
+      <c r="L431" s="22"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="A432" s="15"/>
       <c r="B432" s="15"/>
-      <c r="L432" s="23"/>
+      <c r="L432" s="22"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="A433" s="15"/>
       <c r="B433" s="15"/>
-      <c r="L433" s="23"/>
+      <c r="L433" s="22"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="A434" s="15"/>
       <c r="B434" s="15"/>
-      <c r="L434" s="23"/>
+      <c r="L434" s="22"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="A435" s="15"/>
       <c r="B435" s="15"/>
-      <c r="L435" s="23"/>
+      <c r="L435" s="22"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="A436" s="15"/>
       <c r="B436" s="15"/>
-      <c r="L436" s="23"/>
+      <c r="L436" s="22"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="A437" s="15"/>
       <c r="B437" s="15"/>
-      <c r="L437" s="23"/>
+      <c r="L437" s="22"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="A438" s="15"/>
       <c r="B438" s="15"/>
-      <c r="L438" s="23"/>
+      <c r="L438" s="22"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
       <c r="A439" s="15"/>
       <c r="B439" s="15"/>
-      <c r="L439" s="23"/>
+      <c r="L439" s="22"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="A440" s="15"/>
       <c r="B440" s="15"/>
-      <c r="L440" s="23"/>
+      <c r="L440" s="22"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="A441" s="15"/>
       <c r="B441" s="15"/>
-      <c r="L441" s="23"/>
+      <c r="L441" s="22"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="A442" s="15"/>
       <c r="B442" s="15"/>
-      <c r="L442" s="23"/>
+      <c r="L442" s="22"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
       <c r="A443" s="15"/>
       <c r="B443" s="15"/>
-      <c r="L443" s="23"/>
+      <c r="L443" s="22"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="A444" s="15"/>
       <c r="B444" s="15"/>
-      <c r="L444" s="23"/>
+      <c r="L444" s="22"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="A445" s="15"/>
       <c r="B445" s="15"/>
-      <c r="L445" s="23"/>
+      <c r="L445" s="22"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="A446" s="15"/>
       <c r="B446" s="15"/>
-      <c r="L446" s="23"/>
+      <c r="L446" s="22"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="A447" s="15"/>
       <c r="B447" s="15"/>
-      <c r="L447" s="23"/>
+      <c r="L447" s="22"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="A448" s="15"/>
       <c r="B448" s="15"/>
-      <c r="L448" s="23"/>
+      <c r="L448" s="22"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="A449" s="15"/>
       <c r="B449" s="15"/>
-      <c r="L449" s="23"/>
+      <c r="L449" s="22"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="A450" s="15"/>
       <c r="B450" s="15"/>
-      <c r="L450" s="23"/>
+      <c r="L450" s="22"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="A451" s="15"/>
       <c r="B451" s="15"/>
-      <c r="L451" s="23"/>
+      <c r="L451" s="22"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="A452" s="15"/>
       <c r="B452" s="15"/>
-      <c r="L452" s="23"/>
+      <c r="L452" s="22"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="A453" s="15"/>
       <c r="B453" s="15"/>
-      <c r="L453" s="23"/>
+      <c r="L453" s="22"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="A454" s="15"/>
       <c r="B454" s="15"/>
-      <c r="L454" s="23"/>
+      <c r="L454" s="22"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="A455" s="15"/>
       <c r="B455" s="15"/>
-      <c r="L455" s="23"/>
+      <c r="L455" s="22"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="A456" s="15"/>
       <c r="B456" s="15"/>
-      <c r="L456" s="23"/>
+      <c r="L456" s="22"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="A457" s="15"/>
       <c r="B457" s="15"/>
-      <c r="L457" s="23"/>
+      <c r="L457" s="22"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="A458" s="15"/>
       <c r="B458" s="15"/>
-      <c r="L458" s="23"/>
+      <c r="L458" s="22"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="A459" s="15"/>
       <c r="B459" s="15"/>
-      <c r="L459" s="23"/>
+      <c r="L459" s="22"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="A460" s="15"/>
       <c r="B460" s="15"/>
-      <c r="L460" s="23"/>
+      <c r="L460" s="22"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="A461" s="15"/>
       <c r="B461" s="15"/>
-      <c r="L461" s="23"/>
+      <c r="L461" s="22"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="A462" s="15"/>
       <c r="B462" s="15"/>
-      <c r="L462" s="23"/>
+      <c r="L462" s="22"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
       <c r="A463" s="15"/>
       <c r="B463" s="15"/>
-      <c r="L463" s="23"/>
+      <c r="L463" s="22"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="A464" s="15"/>
       <c r="B464" s="15"/>
-      <c r="L464" s="23"/>
+      <c r="L464" s="22"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="A465" s="15"/>
       <c r="B465" s="15"/>
-      <c r="L465" s="23"/>
+      <c r="L465" s="22"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="A466" s="15"/>
       <c r="B466" s="15"/>
-      <c r="L466" s="23"/>
+      <c r="L466" s="22"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="A467" s="15"/>
       <c r="B467" s="15"/>
-      <c r="L467" s="23"/>
+      <c r="L467" s="22"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="A468" s="15"/>
       <c r="B468" s="15"/>
-      <c r="L468" s="23"/>
+      <c r="L468" s="22"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="A469" s="15"/>
       <c r="B469" s="15"/>
-      <c r="L469" s="23"/>
+      <c r="L469" s="22"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="A470" s="15"/>
       <c r="B470" s="15"/>
-      <c r="L470" s="23"/>
+      <c r="L470" s="22"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
       <c r="A471" s="15"/>
       <c r="B471" s="15"/>
-      <c r="L471" s="23"/>
+      <c r="L471" s="22"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="A472" s="15"/>
       <c r="B472" s="15"/>
-      <c r="L472" s="23"/>
+      <c r="L472" s="22"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="A473" s="15"/>
       <c r="B473" s="15"/>
-      <c r="L473" s="23"/>
+      <c r="L473" s="22"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="A474" s="15"/>
       <c r="B474" s="15"/>
-      <c r="L474" s="23"/>
+      <c r="L474" s="22"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
       <c r="A475" s="15"/>
       <c r="B475" s="15"/>
-      <c r="L475" s="23"/>
+      <c r="L475" s="22"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="A476" s="15"/>
       <c r="B476" s="15"/>
-      <c r="L476" s="23"/>
+      <c r="L476" s="22"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="A477" s="15"/>
       <c r="B477" s="15"/>
-      <c r="L477" s="23"/>
+      <c r="L477" s="22"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="A478" s="15"/>
       <c r="B478" s="15"/>
-      <c r="L478" s="23"/>
+      <c r="L478" s="22"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
       <c r="A479" s="15"/>
       <c r="B479" s="15"/>
-      <c r="L479" s="23"/>
+      <c r="L479" s="22"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="A480" s="15"/>
       <c r="B480" s="15"/>
-      <c r="L480" s="23"/>
+      <c r="L480" s="22"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="A481" s="15"/>
       <c r="B481" s="15"/>
-      <c r="L481" s="23"/>
+      <c r="L481" s="22"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="A482" s="15"/>
       <c r="B482" s="15"/>
-      <c r="L482" s="23"/>
+      <c r="L482" s="22"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="15"/>
       <c r="B483" s="15"/>
-      <c r="L483" s="23"/>
+      <c r="L483" s="22"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="A484" s="15"/>
       <c r="B484" s="15"/>
-      <c r="L484" s="23"/>
+      <c r="L484" s="22"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="A485" s="15"/>
       <c r="B485" s="15"/>
-      <c r="L485" s="23"/>
+      <c r="L485" s="22"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="A486" s="15"/>
       <c r="B486" s="15"/>
-      <c r="L486" s="23"/>
+      <c r="L486" s="22"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
       <c r="A487" s="15"/>
       <c r="B487" s="15"/>
-      <c r="L487" s="23"/>
+      <c r="L487" s="22"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="A488" s="15"/>
       <c r="B488" s="15"/>
-      <c r="L488" s="23"/>
+      <c r="L488" s="22"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="A489" s="15"/>
       <c r="B489" s="15"/>
-      <c r="L489" s="23"/>
+      <c r="L489" s="22"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="A490" s="15"/>
       <c r="B490" s="15"/>
-      <c r="L490" s="23"/>
+      <c r="L490" s="22"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
       <c r="A491" s="15"/>
       <c r="B491" s="15"/>
-      <c r="L491" s="23"/>
+      <c r="L491" s="22"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="A492" s="15"/>
       <c r="B492" s="15"/>
-      <c r="L492" s="23"/>
+      <c r="L492" s="22"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="A493" s="15"/>
       <c r="B493" s="15"/>
-      <c r="L493" s="23"/>
+      <c r="L493" s="22"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="A494" s="15"/>
       <c r="B494" s="15"/>
-      <c r="L494" s="23"/>
+      <c r="L494" s="22"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="A495" s="15"/>
       <c r="B495" s="15"/>
-      <c r="L495" s="23"/>
+      <c r="L495" s="22"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
       <c r="A496" s="15"/>
       <c r="B496" s="15"/>
-      <c r="L496" s="23"/>
+      <c r="L496" s="22"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
       <c r="A497" s="15"/>
       <c r="B497" s="15"/>
-      <c r="L497" s="23"/>
+      <c r="L497" s="22"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="A498" s="15"/>
       <c r="B498" s="15"/>
-      <c r="L498" s="23"/>
+      <c r="L498" s="22"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="A499" s="15"/>
       <c r="B499" s="15"/>
-      <c r="L499" s="23"/>
+      <c r="L499" s="22"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="A500" s="15"/>
       <c r="B500" s="15"/>
-      <c r="L500" s="23"/>
+      <c r="L500" s="22"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="A501" s="15"/>
       <c r="B501" s="15"/>
-      <c r="L501" s="23"/>
+      <c r="L501" s="22"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="A502" s="15"/>
       <c r="B502" s="15"/>
-      <c r="L502" s="23"/>
+      <c r="L502" s="22"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
       <c r="A503" s="15"/>
       <c r="B503" s="15"/>
-      <c r="L503" s="23"/>
+      <c r="L503" s="22"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="A504" s="15"/>
       <c r="B504" s="15"/>
-      <c r="L504" s="23"/>
+      <c r="L504" s="22"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="A505" s="15"/>
       <c r="B505" s="15"/>
-      <c r="L505" s="23"/>
+      <c r="L505" s="22"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="A506" s="15"/>
       <c r="B506" s="15"/>
-      <c r="L506" s="23"/>
+      <c r="L506" s="22"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="A507" s="15"/>
       <c r="B507" s="15"/>
-      <c r="L507" s="23"/>
+      <c r="L507" s="22"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="A508" s="15"/>
       <c r="B508" s="15"/>
-      <c r="L508" s="23"/>
+      <c r="L508" s="22"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="A509" s="15"/>
       <c r="B509" s="15"/>
-      <c r="L509" s="23"/>
+      <c r="L509" s="22"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="A510" s="15"/>
       <c r="B510" s="15"/>
-      <c r="L510" s="23"/>
+      <c r="L510" s="22"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="A511" s="15"/>
       <c r="B511" s="15"/>
-      <c r="L511" s="23"/>
+      <c r="L511" s="22"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="A512" s="15"/>
       <c r="B512" s="15"/>
-      <c r="L512" s="23"/>
+      <c r="L512" s="22"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="A513" s="15"/>
       <c r="B513" s="15"/>
-      <c r="L513" s="23"/>
+      <c r="L513" s="22"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="A514" s="15"/>
       <c r="B514" s="15"/>
-      <c r="L514" s="23"/>
+      <c r="L514" s="22"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="A515" s="15"/>
       <c r="B515" s="15"/>
-      <c r="L515" s="23"/>
+      <c r="L515" s="22"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="A516" s="15"/>
       <c r="B516" s="15"/>
-      <c r="L516" s="23"/>
+      <c r="L516" s="22"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="A517" s="15"/>
       <c r="B517" s="15"/>
-      <c r="L517" s="23"/>
+      <c r="L517" s="22"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="A518" s="15"/>
       <c r="B518" s="15"/>
-      <c r="L518" s="23"/>
+      <c r="L518" s="22"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="A519" s="15"/>
       <c r="B519" s="15"/>
-      <c r="L519" s="23"/>
+      <c r="L519" s="22"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="A520" s="15"/>
       <c r="B520" s="15"/>
-      <c r="L520" s="23"/>
+      <c r="L520" s="22"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="A521" s="15"/>
       <c r="B521" s="15"/>
-      <c r="L521" s="23"/>
+      <c r="L521" s="22"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="A522" s="15"/>
       <c r="B522" s="15"/>
-      <c r="L522" s="23"/>
+      <c r="L522" s="22"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="A523" s="15"/>
       <c r="B523" s="15"/>
-      <c r="L523" s="23"/>
+      <c r="L523" s="22"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
       <c r="A524" s="15"/>
       <c r="B524" s="15"/>
-      <c r="L524" s="23"/>
+      <c r="L524" s="22"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
       <c r="A525" s="15"/>
       <c r="B525" s="15"/>
-      <c r="L525" s="23"/>
+      <c r="L525" s="22"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="A526" s="15"/>
       <c r="B526" s="15"/>
-      <c r="L526" s="23"/>
+      <c r="L526" s="22"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="A527" s="15"/>
       <c r="B527" s="15"/>
-      <c r="L527" s="23"/>
+      <c r="L527" s="22"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
       <c r="A528" s="15"/>
       <c r="B528" s="15"/>
-      <c r="L528" s="23"/>
+      <c r="L528" s="22"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
       <c r="A529" s="15"/>
       <c r="B529" s="15"/>
-      <c r="L529" s="23"/>
+      <c r="L529" s="22"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="A530" s="15"/>
       <c r="B530" s="15"/>
-      <c r="L530" s="23"/>
+      <c r="L530" s="22"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="A531" s="15"/>
       <c r="B531" s="15"/>
-      <c r="L531" s="23"/>
+      <c r="L531" s="22"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
       <c r="A532" s="15"/>
       <c r="B532" s="15"/>
-      <c r="L532" s="23"/>
+      <c r="L532" s="22"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
       <c r="A533" s="15"/>
       <c r="B533" s="15"/>
-      <c r="L533" s="23"/>
+      <c r="L533" s="22"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
       <c r="A534" s="15"/>
       <c r="B534" s="15"/>
-      <c r="L534" s="23"/>
+      <c r="L534" s="22"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="A535" s="15"/>
       <c r="B535" s="15"/>
-      <c r="L535" s="23"/>
+      <c r="L535" s="22"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="A536" s="15"/>
       <c r="B536" s="15"/>
-      <c r="L536" s="23"/>
+      <c r="L536" s="22"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
       <c r="A537" s="15"/>
       <c r="B537" s="15"/>
-      <c r="L537" s="23"/>
+      <c r="L537" s="22"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
       <c r="A538" s="15"/>
       <c r="B538" s="15"/>
-      <c r="L538" s="23"/>
+      <c r="L538" s="22"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
       <c r="A539" s="15"/>
       <c r="B539" s="15"/>
-      <c r="L539" s="23"/>
+      <c r="L539" s="22"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
       <c r="A540" s="15"/>
       <c r="B540" s="15"/>
-      <c r="L540" s="23"/>
+      <c r="L540" s="22"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
       <c r="A541" s="15"/>
       <c r="B541" s="15"/>
-      <c r="L541" s="23"/>
+      <c r="L541" s="22"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
       <c r="A542" s="15"/>
       <c r="B542" s="15"/>
-      <c r="L542" s="23"/>
+      <c r="L542" s="22"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
       <c r="A543" s="15"/>
       <c r="B543" s="15"/>
-      <c r="L543" s="23"/>
+      <c r="L543" s="22"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="A544" s="15"/>
       <c r="B544" s="15"/>
-      <c r="L544" s="23"/>
+      <c r="L544" s="22"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="A545" s="15"/>
       <c r="B545" s="15"/>
-      <c r="L545" s="23"/>
+      <c r="L545" s="22"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="A546" s="15"/>
       <c r="B546" s="15"/>
-      <c r="L546" s="23"/>
+      <c r="L546" s="22"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="A547" s="15"/>
       <c r="B547" s="15"/>
-      <c r="L547" s="23"/>
+      <c r="L547" s="22"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="A548" s="15"/>
       <c r="B548" s="15"/>
-      <c r="L548" s="23"/>
+      <c r="L548" s="22"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="A549" s="15"/>
       <c r="B549" s="15"/>
-      <c r="L549" s="23"/>
+      <c r="L549" s="22"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="A550" s="15"/>
       <c r="B550" s="15"/>
-      <c r="L550" s="23"/>
+      <c r="L550" s="22"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="A551" s="15"/>
       <c r="B551" s="15"/>
-      <c r="L551" s="23"/>
+      <c r="L551" s="22"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="A552" s="15"/>
       <c r="B552" s="15"/>
-      <c r="L552" s="23"/>
+      <c r="L552" s="22"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="A553" s="15"/>
       <c r="B553" s="15"/>
-      <c r="L553" s="23"/>
+      <c r="L553" s="22"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="A554" s="15"/>
       <c r="B554" s="15"/>
-      <c r="L554" s="23"/>
+      <c r="L554" s="22"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="A555" s="15"/>
       <c r="B555" s="15"/>
-      <c r="L555" s="23"/>
+      <c r="L555" s="22"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="A556" s="15"/>
       <c r="B556" s="15"/>
-      <c r="L556" s="23"/>
+      <c r="L556" s="22"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="A557" s="15"/>
       <c r="B557" s="15"/>
-      <c r="L557" s="23"/>
+      <c r="L557" s="22"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="A558" s="15"/>
       <c r="B558" s="15"/>
-      <c r="L558" s="23"/>
+      <c r="L558" s="22"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="A559" s="15"/>
       <c r="B559" s="15"/>
-      <c r="L559" s="23"/>
+      <c r="L559" s="22"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="A560" s="15"/>
       <c r="B560" s="15"/>
-      <c r="L560" s="23"/>
+      <c r="L560" s="22"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="A561" s="15"/>
       <c r="B561" s="15"/>
-      <c r="L561" s="23"/>
+      <c r="L561" s="22"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="A562" s="15"/>
       <c r="B562" s="15"/>
-      <c r="L562" s="23"/>
+      <c r="L562" s="22"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
       <c r="A563" s="15"/>
       <c r="B563" s="15"/>
-      <c r="L563" s="23"/>
+      <c r="L563" s="22"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
       <c r="A564" s="15"/>
       <c r="B564" s="15"/>
-      <c r="L564" s="23"/>
+      <c r="L564" s="22"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
       <c r="A565" s="15"/>
       <c r="B565" s="15"/>
-      <c r="L565" s="23"/>
+      <c r="L565" s="22"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
       <c r="A566" s="15"/>
       <c r="B566" s="15"/>
-      <c r="L566" s="23"/>
+      <c r="L566" s="22"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
       <c r="A567" s="15"/>
       <c r="B567" s="15"/>
-      <c r="L567" s="23"/>
+      <c r="L567" s="22"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
       <c r="A568" s="15"/>
       <c r="B568" s="15"/>
-      <c r="L568" s="23"/>
+      <c r="L568" s="22"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
       <c r="A569" s="15"/>
       <c r="B569" s="15"/>
-      <c r="L569" s="23"/>
+      <c r="L569" s="22"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
       <c r="A570" s="15"/>
       <c r="B570" s="15"/>
-      <c r="L570" s="23"/>
+      <c r="L570" s="22"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
       <c r="A571" s="15"/>
       <c r="B571" s="15"/>
-      <c r="L571" s="23"/>
+      <c r="L571" s="22"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
       <c r="A572" s="15"/>
       <c r="B572" s="15"/>
-      <c r="L572" s="23"/>
+      <c r="L572" s="22"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
       <c r="A573" s="15"/>
       <c r="B573" s="15"/>
-      <c r="L573" s="23"/>
+      <c r="L573" s="22"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
       <c r="A574" s="15"/>
       <c r="B574" s="15"/>
-      <c r="L574" s="23"/>
+      <c r="L574" s="22"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
       <c r="A575" s="15"/>
       <c r="B575" s="15"/>
-      <c r="L575" s="23"/>
+      <c r="L575" s="22"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
       <c r="A576" s="15"/>
       <c r="B576" s="15"/>
-      <c r="L576" s="23"/>
+      <c r="L576" s="22"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
       <c r="A577" s="15"/>
       <c r="B577" s="15"/>
-      <c r="L577" s="23"/>
+      <c r="L577" s="22"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
       <c r="A578" s="15"/>
       <c r="B578" s="15"/>
-      <c r="L578" s="23"/>
+      <c r="L578" s="22"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
       <c r="A579" s="15"/>
       <c r="B579" s="15"/>
-      <c r="L579" s="23"/>
+      <c r="L579" s="22"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
       <c r="A580" s="15"/>
       <c r="B580" s="15"/>
-      <c r="L580" s="23"/>
+      <c r="L580" s="22"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
       <c r="A581" s="15"/>
       <c r="B581" s="15"/>
-      <c r="L581" s="23"/>
+      <c r="L581" s="22"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
       <c r="A582" s="15"/>
       <c r="B582" s="15"/>
-      <c r="L582" s="23"/>
+      <c r="L582" s="22"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
       <c r="A583" s="15"/>
       <c r="B583" s="15"/>
-      <c r="L583" s="23"/>
+      <c r="L583" s="22"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
       <c r="A584" s="15"/>
       <c r="B584" s="15"/>
-      <c r="L584" s="23"/>
+      <c r="L584" s="22"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
       <c r="A585" s="15"/>
       <c r="B585" s="15"/>
-      <c r="L585" s="23"/>
+      <c r="L585" s="22"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
       <c r="A586" s="15"/>
       <c r="B586" s="15"/>
-      <c r="L586" s="23"/>
+      <c r="L586" s="22"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="A587" s="15"/>
       <c r="B587" s="15"/>
-      <c r="L587" s="23"/>
+      <c r="L587" s="22"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="A588" s="15"/>
       <c r="B588" s="15"/>
-      <c r="L588" s="23"/>
+      <c r="L588" s="22"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="A589" s="15"/>
       <c r="B589" s="15"/>
-      <c r="L589" s="23"/>
+      <c r="L589" s="22"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="A590" s="15"/>
       <c r="B590" s="15"/>
-      <c r="L590" s="23"/>
+      <c r="L590" s="22"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="A591" s="15"/>
       <c r="B591" s="15"/>
-      <c r="L591" s="23"/>
+      <c r="L591" s="22"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
       <c r="A592" s="15"/>
       <c r="B592" s="15"/>
-      <c r="L592" s="23"/>
+      <c r="L592" s="22"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
       <c r="A593" s="15"/>
       <c r="B593" s="15"/>
-      <c r="L593" s="23"/>
+      <c r="L593" s="22"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="A594" s="15"/>
       <c r="B594" s="15"/>
-      <c r="L594" s="23"/>
+      <c r="L594" s="22"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="A595" s="15"/>
       <c r="B595" s="15"/>
-      <c r="L595" s="23"/>
+      <c r="L595" s="22"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="A596" s="15"/>
       <c r="B596" s="15"/>
-      <c r="L596" s="23"/>
+      <c r="L596" s="22"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="A597" s="15"/>
       <c r="B597" s="15"/>
-      <c r="L597" s="23"/>
+      <c r="L597" s="22"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="A598" s="15"/>
       <c r="B598" s="15"/>
-      <c r="L598" s="23"/>
+      <c r="L598" s="22"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="A599" s="15"/>
       <c r="B599" s="15"/>
-      <c r="L599" s="23"/>
+      <c r="L599" s="22"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
       <c r="A600" s="15"/>
       <c r="B600" s="15"/>
-      <c r="L600" s="23"/>
+      <c r="L600" s="22"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
       <c r="A601" s="15"/>
       <c r="B601" s="15"/>
-      <c r="L601" s="23"/>
+      <c r="L601" s="22"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
       <c r="A602" s="15"/>
       <c r="B602" s="15"/>
-      <c r="L602" s="23"/>
+      <c r="L602" s="22"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
       <c r="A603" s="15"/>
       <c r="B603" s="15"/>
-      <c r="L603" s="23"/>
+      <c r="L603" s="22"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="A604" s="15"/>
       <c r="B604" s="15"/>
-      <c r="L604" s="23"/>
+      <c r="L604" s="22"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="A605" s="15"/>
       <c r="B605" s="15"/>
-      <c r="L605" s="23"/>
+      <c r="L605" s="22"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="A606" s="15"/>
       <c r="B606" s="15"/>
-      <c r="L606" s="23"/>
+      <c r="L606" s="22"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="A607" s="15"/>
       <c r="B607" s="15"/>
-      <c r="L607" s="23"/>
+      <c r="L607" s="22"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
       <c r="A608" s="15"/>
       <c r="B608" s="15"/>
-      <c r="L608" s="23"/>
+      <c r="L608" s="22"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
       <c r="A609" s="15"/>
       <c r="B609" s="15"/>
-      <c r="L609" s="23"/>
+      <c r="L609" s="22"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
       <c r="A610" s="15"/>
       <c r="B610" s="15"/>
-      <c r="L610" s="23"/>
+      <c r="L610" s="22"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="A611" s="15"/>
       <c r="B611" s="15"/>
-      <c r="L611" s="23"/>
+      <c r="L611" s="22"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="A612" s="15"/>
       <c r="B612" s="15"/>
-      <c r="L612" s="23"/>
+      <c r="L612" s="22"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="A613" s="15"/>
       <c r="B613" s="15"/>
-      <c r="L613" s="23"/>
+      <c r="L613" s="22"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="A614" s="15"/>
       <c r="B614" s="15"/>
-      <c r="L614" s="23"/>
+      <c r="L614" s="22"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="A615" s="15"/>
       <c r="B615" s="15"/>
-      <c r="L615" s="23"/>
+      <c r="L615" s="22"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
       <c r="A616" s="15"/>
       <c r="B616" s="15"/>
-      <c r="L616" s="23"/>
+      <c r="L616" s="22"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
       <c r="A617" s="15"/>
       <c r="B617" s="15"/>
-      <c r="L617" s="23"/>
+      <c r="L617" s="22"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
       <c r="A618" s="15"/>
       <c r="B618" s="15"/>
-      <c r="L618" s="23"/>
+      <c r="L618" s="22"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="A619" s="15"/>
       <c r="B619" s="15"/>
-      <c r="L619" s="23"/>
+      <c r="L619" s="22"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="A620" s="15"/>
       <c r="B620" s="15"/>
-      <c r="L620" s="23"/>
+      <c r="L620" s="22"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="A621" s="15"/>
       <c r="B621" s="15"/>
-      <c r="L621" s="23"/>
+      <c r="L621" s="22"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="A622" s="15"/>
       <c r="B622" s="15"/>
-      <c r="L622" s="23"/>
+      <c r="L622" s="22"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
       <c r="A623" s="15"/>
       <c r="B623" s="15"/>
-      <c r="L623" s="23"/>
+      <c r="L623" s="22"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="A624" s="15"/>
       <c r="B624" s="15"/>
-      <c r="L624" s="23"/>
+      <c r="L624" s="22"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
       <c r="A625" s="15"/>
       <c r="B625" s="15"/>
-      <c r="L625" s="23"/>
+      <c r="L625" s="22"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="A626" s="15"/>
       <c r="B626" s="15"/>
-      <c r="L626" s="23"/>
+      <c r="L626" s="22"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="A627" s="15"/>
       <c r="B627" s="15"/>
-      <c r="L627" s="23"/>
+      <c r="L627" s="22"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="A628" s="15"/>
       <c r="B628" s="15"/>
-      <c r="L628" s="23"/>
+      <c r="L628" s="22"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="A629" s="15"/>
       <c r="B629" s="15"/>
-      <c r="L629" s="23"/>
+      <c r="L629" s="22"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="A630" s="15"/>
       <c r="B630" s="15"/>
-      <c r="L630" s="23"/>
+      <c r="L630" s="22"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="A631" s="15"/>
       <c r="B631" s="15"/>
-      <c r="L631" s="23"/>
+      <c r="L631" s="22"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
       <c r="A632" s="15"/>
       <c r="B632" s="15"/>
-      <c r="L632" s="23"/>
+      <c r="L632" s="22"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
       <c r="A633" s="15"/>
       <c r="B633" s="15"/>
-      <c r="L633" s="23"/>
+      <c r="L633" s="22"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
       <c r="A634" s="15"/>
       <c r="B634" s="15"/>
-      <c r="L634" s="23"/>
+      <c r="L634" s="22"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="A635" s="15"/>
       <c r="B635" s="15"/>
-      <c r="L635" s="23"/>
+      <c r="L635" s="22"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="A636" s="15"/>
       <c r="B636" s="15"/>
-      <c r="L636" s="23"/>
+      <c r="L636" s="22"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="A637" s="15"/>
       <c r="B637" s="15"/>
-      <c r="L637" s="23"/>
+      <c r="L637" s="22"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="A638" s="15"/>
       <c r="B638" s="15"/>
-      <c r="L638" s="23"/>
+      <c r="L638" s="22"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="A639" s="15"/>
       <c r="B639" s="15"/>
-      <c r="L639" s="23"/>
+      <c r="L639" s="22"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="A640" s="15"/>
       <c r="B640" s="15"/>
-      <c r="L640" s="23"/>
+      <c r="L640" s="22"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="A641" s="15"/>
       <c r="B641" s="15"/>
-      <c r="L641" s="23"/>
+      <c r="L641" s="22"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="A642" s="15"/>
       <c r="B642" s="15"/>
-      <c r="L642" s="23"/>
+      <c r="L642" s="22"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
       <c r="A643" s="15"/>
       <c r="B643" s="15"/>
-      <c r="L643" s="23"/>
+      <c r="L643" s="22"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
       <c r="A644" s="15"/>
       <c r="B644" s="15"/>
-      <c r="L644" s="23"/>
+      <c r="L644" s="22"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
       <c r="A645" s="15"/>
       <c r="B645" s="15"/>
-      <c r="L645" s="23"/>
+      <c r="L645" s="22"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
       <c r="A646" s="15"/>
       <c r="B646" s="15"/>
-      <c r="L646" s="23"/>
+      <c r="L646" s="22"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
       <c r="A647" s="15"/>
       <c r="B647" s="15"/>
-      <c r="L647" s="23"/>
+      <c r="L647" s="22"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
       <c r="A648" s="15"/>
       <c r="B648" s="15"/>
-      <c r="L648" s="23"/>
+      <c r="L648" s="22"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
       <c r="A649" s="15"/>
       <c r="B649" s="15"/>
-      <c r="L649" s="23"/>
+      <c r="L649" s="22"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
       <c r="A650" s="15"/>
       <c r="B650" s="15"/>
-      <c r="L650" s="23"/>
+      <c r="L650" s="22"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
       <c r="A651" s="15"/>
       <c r="B651" s="15"/>
-      <c r="L651" s="23"/>
+      <c r="L651" s="22"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
       <c r="A652" s="15"/>
       <c r="B652" s="15"/>
-      <c r="L652" s="23"/>
+      <c r="L652" s="22"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
       <c r="A653" s="15"/>
       <c r="B653" s="15"/>
-      <c r="L653" s="23"/>
+      <c r="L653" s="22"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
       <c r="A654" s="15"/>
       <c r="B654" s="15"/>
-      <c r="L654" s="23"/>
+      <c r="L654" s="22"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
       <c r="A655" s="15"/>
       <c r="B655" s="15"/>
-      <c r="L655" s="23"/>
+      <c r="L655" s="22"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
       <c r="A656" s="15"/>
       <c r="B656" s="15"/>
-      <c r="L656" s="23"/>
+      <c r="L656" s="22"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
       <c r="A657" s="15"/>
       <c r="B657" s="15"/>
-      <c r="L657" s="23"/>
+      <c r="L657" s="22"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
       <c r="A658" s="15"/>
       <c r="B658" s="15"/>
-      <c r="L658" s="23"/>
+      <c r="L658" s="22"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
       <c r="A659" s="15"/>
       <c r="B659" s="15"/>
-      <c r="L659" s="23"/>
+      <c r="L659" s="22"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
       <c r="A660" s="15"/>
       <c r="B660" s="15"/>
-      <c r="L660" s="23"/>
+      <c r="L660" s="22"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
       <c r="A661" s="15"/>
       <c r="B661" s="15"/>
-      <c r="L661" s="23"/>
+      <c r="L661" s="22"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
       <c r="A662" s="15"/>
       <c r="B662" s="15"/>
-      <c r="L662" s="23"/>
+      <c r="L662" s="22"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
       <c r="A663" s="15"/>
       <c r="B663" s="15"/>
-      <c r="L663" s="23"/>
+      <c r="L663" s="22"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
       <c r="A664" s="15"/>
       <c r="B664" s="15"/>
-      <c r="L664" s="23"/>
+      <c r="L664" s="22"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
       <c r="A665" s="15"/>
       <c r="B665" s="15"/>
-      <c r="L665" s="23"/>
+      <c r="L665" s="22"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
       <c r="A666" s="15"/>
       <c r="B666" s="15"/>
-      <c r="L666" s="23"/>
+      <c r="L666" s="22"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
       <c r="A667" s="15"/>
       <c r="B667" s="15"/>
-      <c r="L667" s="23"/>
+      <c r="L667" s="22"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
       <c r="A668" s="15"/>
       <c r="B668" s="15"/>
-      <c r="L668" s="23"/>
+      <c r="L668" s="22"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
       <c r="A669" s="15"/>
       <c r="B669" s="15"/>
-      <c r="L669" s="23"/>
+      <c r="L669" s="22"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
       <c r="A670" s="15"/>
       <c r="B670" s="15"/>
-      <c r="L670" s="23"/>
+      <c r="L670" s="22"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
       <c r="A671" s="15"/>
       <c r="B671" s="15"/>
-      <c r="L671" s="23"/>
+      <c r="L671" s="22"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
       <c r="A672" s="15"/>
       <c r="B672" s="15"/>
-      <c r="L672" s="23"/>
+      <c r="L672" s="22"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
       <c r="A673" s="15"/>
       <c r="B673" s="15"/>
-      <c r="L673" s="23"/>
+      <c r="L673" s="22"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
       <c r="A674" s="15"/>
       <c r="B674" s="15"/>
-      <c r="L674" s="23"/>
+      <c r="L674" s="22"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
       <c r="A675" s="15"/>
       <c r="B675" s="15"/>
-      <c r="L675" s="23"/>
+      <c r="L675" s="22"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
       <c r="A676" s="15"/>
       <c r="B676" s="15"/>
-      <c r="L676" s="23"/>
+      <c r="L676" s="22"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
       <c r="A677" s="15"/>
       <c r="B677" s="15"/>
-      <c r="L677" s="23"/>
+      <c r="L677" s="22"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
       <c r="A678" s="15"/>
       <c r="B678" s="15"/>
-      <c r="L678" s="23"/>
+      <c r="L678" s="22"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
       <c r="A679" s="15"/>
       <c r="B679" s="15"/>
-      <c r="L679" s="23"/>
+      <c r="L679" s="22"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
       <c r="A680" s="15"/>
       <c r="B680" s="15"/>
-      <c r="L680" s="23"/>
+      <c r="L680" s="22"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
       <c r="A681" s="15"/>
       <c r="B681" s="15"/>
-      <c r="L681" s="23"/>
+      <c r="L681" s="22"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
       <c r="A682" s="15"/>
       <c r="B682" s="15"/>
-      <c r="L682" s="23"/>
+      <c r="L682" s="22"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
       <c r="A683" s="15"/>
       <c r="B683" s="15"/>
-      <c r="L683" s="23"/>
+      <c r="L683" s="22"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
       <c r="A684" s="15"/>
       <c r="B684" s="15"/>
-      <c r="L684" s="23"/>
+      <c r="L684" s="22"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
       <c r="A685" s="15"/>
       <c r="B685" s="15"/>
-      <c r="L685" s="23"/>
+      <c r="L685" s="22"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
       <c r="A686" s="15"/>
       <c r="B686" s="15"/>
-      <c r="L686" s="23"/>
+      <c r="L686" s="22"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
       <c r="A687" s="15"/>
       <c r="B687" s="15"/>
-      <c r="L687" s="23"/>
+      <c r="L687" s="22"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
       <c r="A688" s="15"/>
       <c r="B688" s="15"/>
-      <c r="L688" s="23"/>
+      <c r="L688" s="22"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
       <c r="A689" s="15"/>
       <c r="B689" s="15"/>
-      <c r="L689" s="23"/>
+      <c r="L689" s="22"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
       <c r="A690" s="15"/>
       <c r="B690" s="15"/>
-      <c r="L690" s="23"/>
+      <c r="L690" s="22"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
       <c r="A691" s="15"/>
       <c r="B691" s="15"/>
-      <c r="L691" s="23"/>
+      <c r="L691" s="22"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
       <c r="A692" s="15"/>
       <c r="B692" s="15"/>
-      <c r="L692" s="23"/>
+      <c r="L692" s="22"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
       <c r="A693" s="15"/>
       <c r="B693" s="15"/>
-      <c r="L693" s="23"/>
+      <c r="L693" s="22"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
       <c r="A694" s="15"/>
       <c r="B694" s="15"/>
-      <c r="L694" s="23"/>
+      <c r="L694" s="22"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
       <c r="A695" s="15"/>
       <c r="B695" s="15"/>
-      <c r="L695" s="23"/>
+      <c r="L695" s="22"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
       <c r="A696" s="15"/>
       <c r="B696" s="15"/>
-      <c r="L696" s="23"/>
+      <c r="L696" s="22"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
       <c r="A697" s="15"/>
       <c r="B697" s="15"/>
-      <c r="L697" s="23"/>
+      <c r="L697" s="22"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
       <c r="A698" s="15"/>
       <c r="B698" s="15"/>
-      <c r="L698" s="23"/>
+      <c r="L698" s="22"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
       <c r="A699" s="15"/>
       <c r="B699" s="15"/>
-      <c r="L699" s="23"/>
+      <c r="L699" s="22"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
       <c r="A700" s="15"/>
       <c r="B700" s="15"/>
-      <c r="L700" s="23"/>
+      <c r="L700" s="22"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
       <c r="A701" s="15"/>
       <c r="B701" s="15"/>
-      <c r="L701" s="23"/>
+      <c r="L701" s="22"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
       <c r="A702" s="15"/>
       <c r="B702" s="15"/>
-      <c r="L702" s="23"/>
+      <c r="L702" s="22"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
       <c r="A703" s="15"/>
       <c r="B703" s="15"/>
-      <c r="L703" s="23"/>
+      <c r="L703" s="22"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
       <c r="A704" s="15"/>
       <c r="B704" s="15"/>
-      <c r="L704" s="23"/>
+      <c r="L704" s="22"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
       <c r="A705" s="15"/>
       <c r="B705" s="15"/>
-      <c r="L705" s="23"/>
+      <c r="L705" s="22"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
       <c r="A706" s="15"/>
       <c r="B706" s="15"/>
-      <c r="L706" s="23"/>
+      <c r="L706" s="22"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
       <c r="A707" s="15"/>
       <c r="B707" s="15"/>
-      <c r="L707" s="23"/>
+      <c r="L707" s="22"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
       <c r="A708" s="15"/>
       <c r="B708" s="15"/>
-      <c r="L708" s="23"/>
+      <c r="L708" s="22"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
       <c r="A709" s="15"/>
       <c r="B709" s="15"/>
-      <c r="L709" s="23"/>
+      <c r="L709" s="22"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
       <c r="A710" s="15"/>
       <c r="B710" s="15"/>
-      <c r="L710" s="23"/>
+      <c r="L710" s="22"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
       <c r="A711" s="15"/>
       <c r="B711" s="15"/>
-      <c r="L711" s="23"/>
+      <c r="L711" s="22"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
       <c r="A712" s="15"/>
       <c r="B712" s="15"/>
-      <c r="L712" s="23"/>
+      <c r="L712" s="22"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
       <c r="A713" s="15"/>
       <c r="B713" s="15"/>
-      <c r="L713" s="23"/>
+      <c r="L713" s="22"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
       <c r="A714" s="15"/>
       <c r="B714" s="15"/>
-      <c r="L714" s="23"/>
+      <c r="L714" s="22"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
       <c r="A715" s="15"/>
       <c r="B715" s="15"/>
-      <c r="L715" s="23"/>
+      <c r="L715" s="22"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
       <c r="A716" s="15"/>
       <c r="B716" s="15"/>
-      <c r="L716" s="23"/>
+      <c r="L716" s="22"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
       <c r="A717" s="15"/>
       <c r="B717" s="15"/>
-      <c r="L717" s="23"/>
+      <c r="L717" s="22"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
       <c r="A718" s="15"/>
       <c r="B718" s="15"/>
-      <c r="L718" s="23"/>
+      <c r="L718" s="22"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
       <c r="A719" s="15"/>
       <c r="B719" s="15"/>
-      <c r="L719" s="23"/>
+      <c r="L719" s="22"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
       <c r="A720" s="15"/>
       <c r="B720" s="15"/>
-      <c r="L720" s="23"/>
+      <c r="L720" s="22"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
       <c r="A721" s="15"/>
       <c r="B721" s="15"/>
-      <c r="L721" s="23"/>
+      <c r="L721" s="22"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
       <c r="A722" s="15"/>
       <c r="B722" s="15"/>
-      <c r="L722" s="23"/>
+      <c r="L722" s="22"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
       <c r="A723" s="15"/>
       <c r="B723" s="15"/>
-      <c r="L723" s="23"/>
+      <c r="L723" s="22"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
       <c r="A724" s="15"/>
       <c r="B724" s="15"/>
-      <c r="L724" s="23"/>
+      <c r="L724" s="22"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
       <c r="A725" s="15"/>
       <c r="B725" s="15"/>
-      <c r="L725" s="23"/>
+      <c r="L725" s="22"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
       <c r="A726" s="15"/>
       <c r="B726" s="15"/>
-      <c r="L726" s="23"/>
+      <c r="L726" s="22"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
       <c r="A727" s="15"/>
       <c r="B727" s="15"/>
-      <c r="L727" s="23"/>
+      <c r="L727" s="22"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
       <c r="A728" s="15"/>
       <c r="B728" s="15"/>
-      <c r="L728" s="23"/>
+      <c r="L728" s="22"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
       <c r="A729" s="15"/>
       <c r="B729" s="15"/>
-      <c r="L729" s="23"/>
+      <c r="L729" s="22"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
       <c r="A730" s="15"/>
       <c r="B730" s="15"/>
-      <c r="L730" s="23"/>
+      <c r="L730" s="22"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
       <c r="A731" s="15"/>
       <c r="B731" s="15"/>
-      <c r="L731" s="23"/>
+      <c r="L731" s="22"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
       <c r="A732" s="15"/>
       <c r="B732" s="15"/>
-      <c r="L732" s="23"/>
+      <c r="L732" s="22"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
       <c r="A733" s="15"/>
       <c r="B733" s="15"/>
-      <c r="L733" s="23"/>
+      <c r="L733" s="22"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
       <c r="A734" s="15"/>
       <c r="B734" s="15"/>
-      <c r="L734" s="23"/>
+      <c r="L734" s="22"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
       <c r="A735" s="15"/>
       <c r="B735" s="15"/>
-      <c r="L735" s="23"/>
+      <c r="L735" s="22"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
       <c r="A736" s="15"/>
       <c r="B736" s="15"/>
-      <c r="L736" s="23"/>
+      <c r="L736" s="22"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
       <c r="A737" s="15"/>
       <c r="B737" s="15"/>
-      <c r="L737" s="23"/>
+      <c r="L737" s="22"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
       <c r="A738" s="15"/>
       <c r="B738" s="15"/>
-      <c r="L738" s="23"/>
+      <c r="L738" s="22"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
       <c r="A739" s="15"/>
       <c r="B739" s="15"/>
-      <c r="L739" s="23"/>
+      <c r="L739" s="22"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
       <c r="A740" s="15"/>
       <c r="B740" s="15"/>
-      <c r="L740" s="23"/>
+      <c r="L740" s="22"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
       <c r="A741" s="15"/>
       <c r="B741" s="15"/>
-      <c r="L741" s="23"/>
+      <c r="L741" s="22"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
       <c r="A742" s="15"/>
       <c r="B742" s="15"/>
-      <c r="L742" s="23"/>
+      <c r="L742" s="22"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
       <c r="A743" s="15"/>
       <c r="B743" s="15"/>
-      <c r="L743" s="23"/>
+      <c r="L743" s="22"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
       <c r="A744" s="15"/>
       <c r="B744" s="15"/>
-      <c r="L744" s="23"/>
+      <c r="L744" s="22"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
       <c r="A745" s="15"/>
       <c r="B745" s="15"/>
-      <c r="L745" s="23"/>
+      <c r="L745" s="22"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
       <c r="A746" s="15"/>
       <c r="B746" s="15"/>
-      <c r="L746" s="23"/>
+      <c r="L746" s="22"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
       <c r="A747" s="15"/>
       <c r="B747" s="15"/>
-      <c r="L747" s="23"/>
+      <c r="L747" s="22"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
       <c r="A748" s="15"/>
       <c r="B748" s="15"/>
-      <c r="L748" s="23"/>
+      <c r="L748" s="22"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
       <c r="A749" s="15"/>
       <c r="B749" s="15"/>
-      <c r="L749" s="23"/>
+      <c r="L749" s="22"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
       <c r="A750" s="15"/>
       <c r="B750" s="15"/>
-      <c r="L750" s="23"/>
+      <c r="L750" s="22"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
       <c r="A751" s="15"/>
       <c r="B751" s="15"/>
-      <c r="L751" s="23"/>
+      <c r="L751" s="22"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
       <c r="A752" s="15"/>
       <c r="B752" s="15"/>
-      <c r="L752" s="23"/>
+      <c r="L752" s="22"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
       <c r="A753" s="15"/>
       <c r="B753" s="15"/>
-      <c r="L753" s="23"/>
+      <c r="L753" s="22"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
       <c r="A754" s="15"/>
       <c r="B754" s="15"/>
-      <c r="L754" s="23"/>
+      <c r="L754" s="22"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
       <c r="A755" s="15"/>
       <c r="B755" s="15"/>
-      <c r="L755" s="23"/>
+      <c r="L755" s="22"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
       <c r="A756" s="15"/>
       <c r="B756" s="15"/>
-      <c r="L756" s="23"/>
+      <c r="L756" s="22"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
       <c r="A757" s="15"/>
       <c r="B757" s="15"/>
-      <c r="L757" s="23"/>
+      <c r="L757" s="22"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
       <c r="A758" s="15"/>
       <c r="B758" s="15"/>
-      <c r="L758" s="23"/>
+      <c r="L758" s="22"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
       <c r="A759" s="15"/>
       <c r="B759" s="15"/>
-      <c r="L759" s="23"/>
+      <c r="L759" s="22"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
       <c r="A760" s="15"/>
       <c r="B760" s="15"/>
-      <c r="L760" s="23"/>
+      <c r="L760" s="22"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
       <c r="A761" s="15"/>
       <c r="B761" s="15"/>
-      <c r="L761" s="23"/>
+      <c r="L761" s="22"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
       <c r="A762" s="15"/>
       <c r="B762" s="15"/>
-      <c r="L762" s="23"/>
+      <c r="L762" s="22"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
       <c r="A763" s="15"/>
       <c r="B763" s="15"/>
-      <c r="L763" s="23"/>
+      <c r="L763" s="22"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
       <c r="A764" s="15"/>
       <c r="B764" s="15"/>
-      <c r="L764" s="23"/>
+      <c r="L764" s="22"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
       <c r="A765" s="15"/>
       <c r="B765" s="15"/>
-      <c r="L765" s="23"/>
+      <c r="L765" s="22"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
       <c r="A766" s="15"/>
       <c r="B766" s="15"/>
-      <c r="L766" s="23"/>
+      <c r="L766" s="22"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
       <c r="A767" s="15"/>
       <c r="B767" s="15"/>
-      <c r="L767" s="23"/>
+      <c r="L767" s="22"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
       <c r="A768" s="15"/>
       <c r="B768" s="15"/>
-      <c r="L768" s="23"/>
+      <c r="L768" s="22"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
       <c r="A769" s="15"/>
       <c r="B769" s="15"/>
-      <c r="L769" s="23"/>
+      <c r="L769" s="22"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
       <c r="A770" s="15"/>
       <c r="B770" s="15"/>
-      <c r="L770" s="23"/>
+      <c r="L770" s="22"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
       <c r="A771" s="15"/>
       <c r="B771" s="15"/>
-      <c r="L771" s="23"/>
+      <c r="L771" s="22"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
       <c r="A772" s="15"/>
       <c r="B772" s="15"/>
-      <c r="L772" s="23"/>
+      <c r="L772" s="22"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
       <c r="A773" s="15"/>
       <c r="B773" s="15"/>
-      <c r="L773" s="23"/>
+      <c r="L773" s="22"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
       <c r="A774" s="15"/>
       <c r="B774" s="15"/>
-      <c r="L774" s="23"/>
+      <c r="L774" s="22"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
       <c r="A775" s="15"/>
       <c r="B775" s="15"/>
-      <c r="L775" s="23"/>
+      <c r="L775" s="22"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
       <c r="A776" s="15"/>
       <c r="B776" s="15"/>
-      <c r="L776" s="23"/>
+      <c r="L776" s="22"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
       <c r="A777" s="15"/>
       <c r="B777" s="15"/>
-      <c r="L777" s="23"/>
+      <c r="L777" s="22"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
       <c r="A778" s="15"/>
       <c r="B778" s="15"/>
-      <c r="L778" s="23"/>
+      <c r="L778" s="22"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
       <c r="A779" s="15"/>
       <c r="B779" s="15"/>
-      <c r="L779" s="23"/>
+      <c r="L779" s="22"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
       <c r="A780" s="15"/>
       <c r="B780" s="15"/>
-      <c r="L780" s="23"/>
+      <c r="L780" s="22"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
       <c r="A781" s="15"/>
       <c r="B781" s="15"/>
-      <c r="L781" s="23"/>
+      <c r="L781" s="22"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
       <c r="A782" s="15"/>
       <c r="B782" s="15"/>
-      <c r="L782" s="23"/>
+      <c r="L782" s="22"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
       <c r="A783" s="15"/>
       <c r="B783" s="15"/>
-      <c r="L783" s="23"/>
+      <c r="L783" s="22"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
       <c r="A784" s="15"/>
       <c r="B784" s="15"/>
-      <c r="L784" s="23"/>
+      <c r="L784" s="22"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
       <c r="A785" s="15"/>
       <c r="B785" s="15"/>
-      <c r="L785" s="23"/>
+      <c r="L785" s="22"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
       <c r="A786" s="15"/>
       <c r="B786" s="15"/>
-      <c r="L786" s="23"/>
+      <c r="L786" s="22"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
       <c r="A787" s="15"/>
       <c r="B787" s="15"/>
-      <c r="L787" s="23"/>
+      <c r="L787" s="22"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
       <c r="A788" s="15"/>
       <c r="B788" s="15"/>
-      <c r="L788" s="23"/>
+      <c r="L788" s="22"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
       <c r="A789" s="15"/>
       <c r="B789" s="15"/>
-      <c r="L789" s="23"/>
+      <c r="L789" s="22"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
       <c r="A790" s="15"/>
       <c r="B790" s="15"/>
-      <c r="L790" s="23"/>
+      <c r="L790" s="22"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
       <c r="A791" s="15"/>
       <c r="B791" s="15"/>
-      <c r="L791" s="23"/>
+      <c r="L791" s="22"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
       <c r="A792" s="15"/>
       <c r="B792" s="15"/>
-      <c r="L792" s="23"/>
+      <c r="L792" s="22"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
       <c r="A793" s="15"/>
       <c r="B793" s="15"/>
-      <c r="L793" s="23"/>
+      <c r="L793" s="22"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
       <c r="A794" s="15"/>
       <c r="B794" s="15"/>
-      <c r="L794" s="23"/>
+      <c r="L794" s="22"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
       <c r="A795" s="15"/>
       <c r="B795" s="15"/>
-      <c r="L795" s="23"/>
+      <c r="L795" s="22"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
       <c r="A796" s="15"/>
       <c r="B796" s="15"/>
-      <c r="L796" s="23"/>
+      <c r="L796" s="22"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
       <c r="A797" s="15"/>
       <c r="B797" s="15"/>
-      <c r="L797" s="23"/>
+      <c r="L797" s="22"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
       <c r="A798" s="15"/>
       <c r="B798" s="15"/>
-      <c r="L798" s="23"/>
+      <c r="L798" s="22"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
       <c r="A799" s="15"/>
       <c r="B799" s="15"/>
-      <c r="L799" s="23"/>
+      <c r="L799" s="22"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
       <c r="A800" s="15"/>
       <c r="B800" s="15"/>
-      <c r="L800" s="23"/>
+      <c r="L800" s="22"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
       <c r="A801" s="15"/>
       <c r="B801" s="15"/>
-      <c r="L801" s="23"/>
+      <c r="L801" s="22"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
       <c r="A802" s="15"/>
       <c r="B802" s="15"/>
-      <c r="L802" s="23"/>
+      <c r="L802" s="22"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
       <c r="A803" s="15"/>
       <c r="B803" s="15"/>
-      <c r="L803" s="23"/>
+      <c r="L803" s="22"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
       <c r="A804" s="15"/>
       <c r="B804" s="15"/>
-      <c r="L804" s="23"/>
+      <c r="L804" s="22"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
       <c r="A805" s="15"/>
       <c r="B805" s="15"/>
-      <c r="L805" s="23"/>
+      <c r="L805" s="22"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
       <c r="A806" s="15"/>
       <c r="B806" s="15"/>
-      <c r="L806" s="23"/>
+      <c r="L806" s="22"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
       <c r="A807" s="15"/>
       <c r="B807" s="15"/>
-      <c r="L807" s="23"/>
+      <c r="L807" s="22"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
       <c r="A808" s="15"/>
       <c r="B808" s="15"/>
-      <c r="L808" s="23"/>
+      <c r="L808" s="22"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
       <c r="A809" s="15"/>
       <c r="B809" s="15"/>
-      <c r="L809" s="23"/>
+      <c r="L809" s="22"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
       <c r="A810" s="15"/>
       <c r="B810" s="15"/>
-      <c r="L810" s="23"/>
+      <c r="L810" s="22"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
       <c r="A811" s="15"/>
       <c r="B811" s="15"/>
-      <c r="L811" s="23"/>
+      <c r="L811" s="22"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
       <c r="A812" s="15"/>
       <c r="B812" s="15"/>
-      <c r="L812" s="23"/>
+      <c r="L812" s="22"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
       <c r="A813" s="15"/>
       <c r="B813" s="15"/>
-      <c r="L813" s="23"/>
+      <c r="L813" s="22"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
       <c r="A814" s="15"/>
       <c r="B814" s="15"/>
-      <c r="L814" s="23"/>
+      <c r="L814" s="22"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
       <c r="A815" s="15"/>
       <c r="B815" s="15"/>
-      <c r="L815" s="23"/>
+      <c r="L815" s="22"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
       <c r="A816" s="15"/>
       <c r="B816" s="15"/>
-      <c r="L816" s="23"/>
+      <c r="L816" s="22"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
       <c r="A817" s="15"/>
       <c r="B817" s="15"/>
-      <c r="L817" s="23"/>
+      <c r="L817" s="22"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
       <c r="A818" s="15"/>
       <c r="B818" s="15"/>
-      <c r="L818" s="23"/>
+      <c r="L818" s="22"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
       <c r="A819" s="15"/>
       <c r="B819" s="15"/>
-      <c r="L819" s="23"/>
+      <c r="L819" s="22"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
       <c r="A820" s="15"/>
       <c r="B820" s="15"/>
-      <c r="L820" s="23"/>
+      <c r="L820" s="22"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
       <c r="A821" s="15"/>
       <c r="B821" s="15"/>
-      <c r="L821" s="23"/>
+      <c r="L821" s="22"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
       <c r="A822" s="15"/>
       <c r="B822" s="15"/>
-      <c r="L822" s="23"/>
+      <c r="L822" s="22"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
       <c r="A823" s="15"/>
       <c r="B823" s="15"/>
-      <c r="L823" s="23"/>
+      <c r="L823" s="22"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
       <c r="A824" s="15"/>
       <c r="B824" s="15"/>
-      <c r="L824" s="23"/>
+      <c r="L824" s="22"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
       <c r="A825" s="15"/>
       <c r="B825" s="15"/>
-      <c r="L825" s="23"/>
+      <c r="L825" s="22"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
       <c r="A826" s="15"/>
       <c r="B826" s="15"/>
-      <c r="L826" s="23"/>
+      <c r="L826" s="22"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
       <c r="A827" s="15"/>
       <c r="B827" s="15"/>
-      <c r="L827" s="23"/>
+      <c r="L827" s="22"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
       <c r="A828" s="15"/>
       <c r="B828" s="15"/>
-      <c r="L828" s="23"/>
+      <c r="L828" s="22"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
       <c r="A829" s="15"/>
       <c r="B829" s="15"/>
-      <c r="L829" s="23"/>
+      <c r="L829" s="22"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
       <c r="A830" s="15"/>
       <c r="B830" s="15"/>
-      <c r="L830" s="23"/>
+      <c r="L830" s="22"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
       <c r="A831" s="15"/>
       <c r="B831" s="15"/>
-      <c r="L831" s="23"/>
+      <c r="L831" s="22"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
       <c r="A832" s="15"/>
       <c r="B832" s="15"/>
-      <c r="L832" s="23"/>
+      <c r="L832" s="22"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
       <c r="A833" s="15"/>
       <c r="B833" s="15"/>
-      <c r="L833" s="23"/>
+      <c r="L833" s="22"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
       <c r="A834" s="15"/>
       <c r="B834" s="15"/>
-      <c r="L834" s="23"/>
+      <c r="L834" s="22"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
       <c r="A835" s="15"/>
       <c r="B835" s="15"/>
-      <c r="L835" s="23"/>
+      <c r="L835" s="22"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
       <c r="A836" s="15"/>
       <c r="B836" s="15"/>
-      <c r="L836" s="23"/>
+      <c r="L836" s="22"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
       <c r="A837" s="15"/>
       <c r="B837" s="15"/>
-      <c r="L837" s="23"/>
+      <c r="L837" s="22"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
       <c r="A838" s="15"/>
       <c r="B838" s="15"/>
-      <c r="L838" s="23"/>
+      <c r="L838" s="22"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
       <c r="A839" s="15"/>
       <c r="B839" s="15"/>
-      <c r="L839" s="23"/>
+      <c r="L839" s="22"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
       <c r="A840" s="15"/>
       <c r="B840" s="15"/>
-      <c r="L840" s="23"/>
+      <c r="L840" s="22"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
       <c r="A841" s="15"/>
       <c r="B841" s="15"/>
-      <c r="L841" s="23"/>
+      <c r="L841" s="22"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
       <c r="A842" s="15"/>
       <c r="B842" s="15"/>
-      <c r="L842" s="23"/>
+      <c r="L842" s="22"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
       <c r="A843" s="15"/>
       <c r="B843" s="15"/>
-      <c r="L843" s="23"/>
+      <c r="L843" s="22"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
       <c r="A844" s="15"/>
       <c r="B844" s="15"/>
-      <c r="L844" s="23"/>
+      <c r="L844" s="22"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
       <c r="A845" s="15"/>
       <c r="B845" s="15"/>
-      <c r="L845" s="23"/>
+      <c r="L845" s="22"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
       <c r="A846" s="15"/>
       <c r="B846" s="15"/>
-      <c r="L846" s="23"/>
+      <c r="L846" s="22"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
       <c r="A847" s="15"/>
       <c r="B847" s="15"/>
-      <c r="L847" s="23"/>
+      <c r="L847" s="22"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
       <c r="A848" s="15"/>
       <c r="B848" s="15"/>
-      <c r="L848" s="23"/>
+      <c r="L848" s="22"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
       <c r="A849" s="15"/>
       <c r="B849" s="15"/>
-      <c r="L849" s="23"/>
+      <c r="L849" s="22"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
       <c r="A850" s="15"/>
       <c r="B850" s="15"/>
-      <c r="L850" s="23"/>
+      <c r="L850" s="22"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
       <c r="A851" s="15"/>
       <c r="B851" s="15"/>
-      <c r="L851" s="23"/>
+      <c r="L851" s="22"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
       <c r="A852" s="15"/>
       <c r="B852" s="15"/>
-      <c r="L852" s="23"/>
+      <c r="L852" s="22"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
       <c r="A853" s="15"/>
       <c r="B853" s="15"/>
-      <c r="L853" s="23"/>
+      <c r="L853" s="22"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
       <c r="A854" s="15"/>
       <c r="B854" s="15"/>
-      <c r="L854" s="23"/>
+      <c r="L854" s="22"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
       <c r="A855" s="15"/>
       <c r="B855" s="15"/>
-      <c r="L855" s="23"/>
+      <c r="L855" s="22"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
       <c r="A856" s="15"/>
       <c r="B856" s="15"/>
-      <c r="L856" s="23"/>
+      <c r="L856" s="22"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
       <c r="A857" s="15"/>
       <c r="B857" s="15"/>
-      <c r="L857" s="23"/>
+      <c r="L857" s="22"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
       <c r="A858" s="15"/>
       <c r="B858" s="15"/>
-      <c r="L858" s="23"/>
+      <c r="L858" s="22"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
       <c r="A859" s="15"/>
       <c r="B859" s="15"/>
-      <c r="L859" s="23"/>
+      <c r="L859" s="22"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
       <c r="A860" s="15"/>
       <c r="B860" s="15"/>
-      <c r="L860" s="23"/>
+      <c r="L860" s="22"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
       <c r="A861" s="15"/>
       <c r="B861" s="15"/>
-      <c r="L861" s="23"/>
+      <c r="L861" s="22"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
       <c r="A862" s="15"/>
       <c r="B862" s="15"/>
-      <c r="L862" s="23"/>
+      <c r="L862" s="22"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
       <c r="A863" s="15"/>
       <c r="B863" s="15"/>
-      <c r="L863" s="23"/>
+      <c r="L863" s="22"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
       <c r="A864" s="15"/>
       <c r="B864" s="15"/>
-      <c r="L864" s="23"/>
+      <c r="L864" s="22"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
       <c r="A865" s="15"/>
       <c r="B865" s="15"/>
-      <c r="L865" s="23"/>
+      <c r="L865" s="22"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
       <c r="A866" s="15"/>
       <c r="B866" s="15"/>
-      <c r="L866" s="23"/>
+      <c r="L866" s="22"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
       <c r="A867" s="15"/>
       <c r="B867" s="15"/>
-      <c r="L867" s="23"/>
+      <c r="L867" s="22"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
       <c r="A868" s="15"/>
       <c r="B868" s="15"/>
-      <c r="L868" s="23"/>
+      <c r="L868" s="22"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
       <c r="A869" s="15"/>
       <c r="B869" s="15"/>
-      <c r="L869" s="23"/>
+      <c r="L869" s="22"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
       <c r="A870" s="15"/>
       <c r="B870" s="15"/>
-      <c r="L870" s="23"/>
+      <c r="L870" s="22"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
       <c r="A871" s="15"/>
       <c r="B871" s="15"/>
-      <c r="L871" s="23"/>
+      <c r="L871" s="22"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
       <c r="A872" s="15"/>
       <c r="B872" s="15"/>
-      <c r="L872" s="23"/>
+      <c r="L872" s="22"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
       <c r="A873" s="15"/>
       <c r="B873" s="15"/>
-      <c r="L873" s="23"/>
+      <c r="L873" s="22"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
       <c r="A874" s="15"/>
       <c r="B874" s="15"/>
-      <c r="L874" s="23"/>
+      <c r="L874" s="22"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
       <c r="A875" s="15"/>
       <c r="B875" s="15"/>
-      <c r="L875" s="23"/>
+      <c r="L875" s="22"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
       <c r="A876" s="15"/>
       <c r="B876" s="15"/>
-      <c r="L876" s="23"/>
+      <c r="L876" s="22"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
       <c r="A877" s="15"/>
       <c r="B877" s="15"/>
-      <c r="L877" s="23"/>
+      <c r="L877" s="22"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
       <c r="A878" s="15"/>
       <c r="B878" s="15"/>
-      <c r="L878" s="23"/>
+      <c r="L878" s="22"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
       <c r="A879" s="15"/>
       <c r="B879" s="15"/>
-      <c r="L879" s="23"/>
+      <c r="L879" s="22"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
       <c r="A880" s="15"/>
       <c r="B880" s="15"/>
-      <c r="L880" s="23"/>
+      <c r="L880" s="22"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
       <c r="A881" s="15"/>
       <c r="B881" s="15"/>
-      <c r="L881" s="23"/>
+      <c r="L881" s="22"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
       <c r="A882" s="15"/>
       <c r="B882" s="15"/>
-      <c r="L882" s="23"/>
+      <c r="L882" s="22"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
       <c r="A883" s="15"/>
       <c r="B883" s="15"/>
-      <c r="L883" s="23"/>
+      <c r="L883" s="22"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
       <c r="A884" s="15"/>
       <c r="B884" s="15"/>
-      <c r="L884" s="23"/>
+      <c r="L884" s="22"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
       <c r="A885" s="15"/>
       <c r="B885" s="15"/>
-      <c r="L885" s="23"/>
+      <c r="L885" s="22"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
       <c r="A886" s="15"/>
       <c r="B886" s="15"/>
-      <c r="L886" s="23"/>
+      <c r="L886" s="22"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
       <c r="A887" s="15"/>
       <c r="B887" s="15"/>
-      <c r="L887" s="23"/>
+      <c r="L887" s="22"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
       <c r="A888" s="15"/>
       <c r="B888" s="15"/>
-      <c r="L888" s="23"/>
+      <c r="L888" s="22"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
       <c r="A889" s="15"/>
       <c r="B889" s="15"/>
-      <c r="L889" s="23"/>
+      <c r="L889" s="22"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
       <c r="A890" s="15"/>
       <c r="B890" s="15"/>
-      <c r="L890" s="23"/>
+      <c r="L890" s="22"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
       <c r="A891" s="15"/>
       <c r="B891" s="15"/>
-      <c r="L891" s="23"/>
+      <c r="L891" s="22"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
       <c r="A892" s="15"/>
       <c r="B892" s="15"/>
-      <c r="L892" s="23"/>
+      <c r="L892" s="22"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
       <c r="A893" s="15"/>
       <c r="B893" s="15"/>
-      <c r="L893" s="23"/>
+      <c r="L893" s="22"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
       <c r="A894" s="15"/>
       <c r="B894" s="15"/>
-      <c r="L894" s="23"/>
+      <c r="L894" s="22"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
       <c r="A895" s="15"/>
       <c r="B895" s="15"/>
-      <c r="L895" s="23"/>
+      <c r="L895" s="22"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
       <c r="A896" s="15"/>
       <c r="B896" s="15"/>
-      <c r="L896" s="23"/>
+      <c r="L896" s="22"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
       <c r="A897" s="15"/>
       <c r="B897" s="15"/>
-      <c r="L897" s="23"/>
+      <c r="L897" s="22"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
       <c r="A898" s="15"/>
       <c r="B898" s="15"/>
-      <c r="L898" s="23"/>
+      <c r="L898" s="22"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
       <c r="A899" s="15"/>
       <c r="B899" s="15"/>
-      <c r="L899" s="23"/>
+      <c r="L899" s="22"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
       <c r="A900" s="15"/>
       <c r="B900" s="15"/>
-      <c r="L900" s="23"/>
+      <c r="L900" s="22"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
       <c r="A901" s="15"/>
       <c r="B901" s="15"/>
-      <c r="L901" s="23"/>
+      <c r="L901" s="22"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
       <c r="A902" s="15"/>
       <c r="B902" s="15"/>
-      <c r="L902" s="23"/>
+      <c r="L902" s="22"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
       <c r="A903" s="15"/>
       <c r="B903" s="15"/>
-      <c r="L903" s="23"/>
+      <c r="L903" s="22"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
       <c r="A904" s="15"/>
       <c r="B904" s="15"/>
-      <c r="L904" s="23"/>
+      <c r="L904" s="22"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
       <c r="A905" s="15"/>
       <c r="B905" s="15"/>
-      <c r="L905" s="23"/>
+      <c r="L905" s="22"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
       <c r="A906" s="15"/>
       <c r="B906" s="15"/>
-      <c r="L906" s="23"/>
+      <c r="L906" s="22"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
       <c r="A907" s="15"/>
       <c r="B907" s="15"/>
-      <c r="L907" s="23"/>
+      <c r="L907" s="22"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
       <c r="A908" s="15"/>
       <c r="B908" s="15"/>
-      <c r="L908" s="23"/>
+      <c r="L908" s="22"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
       <c r="A909" s="15"/>
       <c r="B909" s="15"/>
-      <c r="L909" s="23"/>
+      <c r="L909" s="22"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
       <c r="A910" s="15"/>
       <c r="B910" s="15"/>
-      <c r="L910" s="23"/>
+      <c r="L910" s="22"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
       <c r="A911" s="15"/>
       <c r="B911" s="15"/>
-      <c r="L911" s="23"/>
+      <c r="L911" s="22"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
       <c r="A912" s="15"/>
       <c r="B912" s="15"/>
-      <c r="L912" s="23"/>
+      <c r="L912" s="22"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
       <c r="A913" s="15"/>
       <c r="B913" s="15"/>
-      <c r="L913" s="23"/>
+      <c r="L913" s="22"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
       <c r="A914" s="15"/>
       <c r="B914" s="15"/>
-      <c r="L914" s="23"/>
+      <c r="L914" s="22"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
       <c r="A915" s="15"/>
       <c r="B915" s="15"/>
-      <c r="L915" s="23"/>
+      <c r="L915" s="22"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
       <c r="A916" s="15"/>
       <c r="B916" s="15"/>
-      <c r="L916" s="23"/>
+      <c r="L916" s="22"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
       <c r="A917" s="15"/>
       <c r="B917" s="15"/>
-      <c r="L917" s="23"/>
+      <c r="L917" s="22"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
       <c r="A918" s="15"/>
       <c r="B918" s="15"/>
-      <c r="L918" s="23"/>
+      <c r="L918" s="22"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
       <c r="A919" s="15"/>
       <c r="B919" s="15"/>
-      <c r="L919" s="23"/>
+      <c r="L919" s="22"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
       <c r="A920" s="15"/>
       <c r="B920" s="15"/>
-      <c r="L920" s="23"/>
+      <c r="L920" s="22"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
       <c r="A921" s="15"/>
       <c r="B921" s="15"/>
-      <c r="L921" s="23"/>
+      <c r="L921" s="22"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
       <c r="A922" s="15"/>
       <c r="B922" s="15"/>
-      <c r="L922" s="23"/>
+      <c r="L922" s="22"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
       <c r="A923" s="15"/>
       <c r="B923" s="15"/>
-      <c r="L923" s="23"/>
+      <c r="L923" s="22"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
       <c r="A924" s="15"/>
       <c r="B924" s="15"/>
-      <c r="L924" s="23"/>
+      <c r="L924" s="22"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
       <c r="A925" s="15"/>
       <c r="B925" s="15"/>
-      <c r="L925" s="23"/>
+      <c r="L925" s="22"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
       <c r="A926" s="15"/>
       <c r="B926" s="15"/>
-      <c r="L926" s="23"/>
+      <c r="L926" s="22"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
       <c r="A927" s="15"/>
       <c r="B927" s="15"/>
-      <c r="L927" s="23"/>
+      <c r="L927" s="22"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
       <c r="A928" s="15"/>
       <c r="B928" s="15"/>
-      <c r="L928" s="23"/>
+      <c r="L928" s="22"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
       <c r="A929" s="15"/>
       <c r="B929" s="15"/>
-      <c r="L929" s="23"/>
+      <c r="L929" s="22"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
       <c r="A930" s="15"/>
       <c r="B930" s="15"/>
-      <c r="L930" s="23"/>
+      <c r="L930" s="22"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
       <c r="A931" s="15"/>
       <c r="B931" s="15"/>
-      <c r="L931" s="23"/>
+      <c r="L931" s="22"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
       <c r="A932" s="15"/>
       <c r="B932" s="15"/>
-      <c r="L932" s="23"/>
+      <c r="L932" s="22"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
       <c r="A933" s="15"/>
       <c r="B933" s="15"/>
-      <c r="L933" s="23"/>
+      <c r="L933" s="22"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
       <c r="A934" s="15"/>
       <c r="B934" s="15"/>
-      <c r="L934" s="23"/>
+      <c r="L934" s="22"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
       <c r="A935" s="15"/>
       <c r="B935" s="15"/>
-      <c r="L935" s="23"/>
+      <c r="L935" s="22"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
       <c r="A936" s="15"/>
       <c r="B936" s="15"/>
-      <c r="L936" s="23"/>
+      <c r="L936" s="22"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
       <c r="A937" s="15"/>
       <c r="B937" s="15"/>
-      <c r="L937" s="23"/>
+      <c r="L937" s="22"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
       <c r="A938" s="15"/>
       <c r="B938" s="15"/>
-      <c r="L938" s="23"/>
+      <c r="L938" s="22"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
       <c r="A939" s="15"/>
       <c r="B939" s="15"/>
-      <c r="L939" s="23"/>
+      <c r="L939" s="22"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
       <c r="A940" s="15"/>
       <c r="B940" s="15"/>
-      <c r="L940" s="23"/>
+      <c r="L940" s="22"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
       <c r="A941" s="15"/>
       <c r="B941" s="15"/>
-      <c r="L941" s="23"/>
+      <c r="L941" s="22"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
       <c r="A942" s="15"/>
       <c r="B942" s="15"/>
-      <c r="L942" s="23"/>
+      <c r="L942" s="22"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
       <c r="A943" s="15"/>
       <c r="B943" s="15"/>
-      <c r="L943" s="23"/>
+      <c r="L943" s="22"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
       <c r="A944" s="15"/>
       <c r="B944" s="15"/>
-      <c r="L944" s="23"/>
+      <c r="L944" s="22"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
       <c r="A945" s="15"/>
       <c r="B945" s="15"/>
-      <c r="L945" s="23"/>
+      <c r="L945" s="22"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
       <c r="A946" s="15"/>
       <c r="B946" s="15"/>
-      <c r="L946" s="23"/>
+      <c r="L946" s="22"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
       <c r="A947" s="15"/>
       <c r="B947" s="15"/>
-      <c r="L947" s="23"/>
+      <c r="L947" s="22"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
       <c r="A948" s="15"/>
       <c r="B948" s="15"/>
-      <c r="L948" s="23"/>
+      <c r="L948" s="22"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
       <c r="A949" s="15"/>
       <c r="B949" s="15"/>
-      <c r="L949" s="23"/>
+      <c r="L949" s="22"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
       <c r="A950" s="15"/>
       <c r="B950" s="15"/>
-      <c r="L950" s="23"/>
+      <c r="L950" s="22"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
       <c r="A951" s="15"/>
       <c r="B951" s="15"/>
-      <c r="L951" s="23"/>
+      <c r="L951" s="22"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
       <c r="A952" s="15"/>
       <c r="B952" s="15"/>
-      <c r="L952" s="23"/>
+      <c r="L952" s="22"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
       <c r="A953" s="15"/>
       <c r="B953" s="15"/>
-      <c r="L953" s="23"/>
+      <c r="L953" s="22"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
       <c r="A954" s="15"/>
       <c r="B954" s="15"/>
-      <c r="L954" s="23"/>
+      <c r="L954" s="22"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
       <c r="A955" s="15"/>
       <c r="B955" s="15"/>
-      <c r="L955" s="23"/>
+      <c r="L955" s="22"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
       <c r="A956" s="15"/>
       <c r="B956" s="15"/>
-      <c r="L956" s="23"/>
+      <c r="L956" s="22"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
       <c r="A957" s="15"/>
       <c r="B957" s="15"/>
-      <c r="L957" s="23"/>
+      <c r="L957" s="22"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
       <c r="A958" s="15"/>
       <c r="B958" s="15"/>
-      <c r="L958" s="23"/>
+      <c r="L958" s="22"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
       <c r="A959" s="15"/>
       <c r="B959" s="15"/>
-      <c r="L959" s="23"/>
+      <c r="L959" s="22"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
       <c r="A960" s="15"/>
       <c r="B960" s="15"/>
-      <c r="L960" s="23"/>
+      <c r="L960" s="22"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
       <c r="A961" s="15"/>
       <c r="B961" s="15"/>
-      <c r="L961" s="23"/>
+      <c r="L961" s="22"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
       <c r="A962" s="15"/>
       <c r="B962" s="15"/>
-      <c r="L962" s="23"/>
+      <c r="L962" s="22"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
       <c r="A963" s="15"/>
       <c r="B963" s="15"/>
-      <c r="L963" s="23"/>
+      <c r="L963" s="22"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
       <c r="A964" s="15"/>
       <c r="B964" s="15"/>
-      <c r="L964" s="23"/>
+      <c r="L964" s="22"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
       <c r="A965" s="15"/>
       <c r="B965" s="15"/>
-      <c r="L965" s="23"/>
+      <c r="L965" s="22"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
       <c r="A966" s="15"/>
       <c r="B966" s="15"/>
-      <c r="L966" s="23"/>
+      <c r="L966" s="22"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
       <c r="A967" s="15"/>
       <c r="B967" s="15"/>
-      <c r="L967" s="23"/>
+      <c r="L967" s="22"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
       <c r="A968" s="15"/>
       <c r="B968" s="15"/>
-      <c r="L968" s="23"/>
+      <c r="L968" s="22"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
       <c r="A969" s="15"/>
       <c r="B969" s="15"/>
-      <c r="L969" s="23"/>
+      <c r="L969" s="22"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
       <c r="A970" s="15"/>
       <c r="B970" s="15"/>
-      <c r="L970" s="23"/>
+      <c r="L970" s="22"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
       <c r="A971" s="15"/>
       <c r="B971" s="15"/>
-      <c r="L971" s="23"/>
+      <c r="L971" s="22"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
       <c r="A972" s="15"/>
       <c r="B972" s="15"/>
-      <c r="L972" s="23"/>
+      <c r="L972" s="22"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
       <c r="A973" s="15"/>
       <c r="B973" s="15"/>
-      <c r="L973" s="23"/>
+      <c r="L973" s="22"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
       <c r="A974" s="15"/>
       <c r="B974" s="15"/>
-      <c r="L974" s="23"/>
+      <c r="L974" s="22"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
       <c r="A975" s="15"/>
       <c r="B975" s="15"/>
-      <c r="L975" s="23"/>
+      <c r="L975" s="22"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
       <c r="A976" s="15"/>
       <c r="B976" s="15"/>
-      <c r="L976" s="23"/>
+      <c r="L976" s="22"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
       <c r="A977" s="15"/>
       <c r="B977" s="15"/>
-      <c r="L977" s="23"/>
+      <c r="L977" s="22"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
       <c r="A978" s="15"/>
       <c r="B978" s="15"/>
-      <c r="L978" s="23"/>
+      <c r="L978" s="22"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
       <c r="A979" s="15"/>
       <c r="B979" s="15"/>
-      <c r="L979" s="23"/>
+      <c r="L979" s="22"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
       <c r="A980" s="15"/>
       <c r="B980" s="15"/>
-      <c r="L980" s="23"/>
+      <c r="L980" s="22"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
       <c r="A981" s="15"/>
       <c r="B981" s="15"/>
-      <c r="L981" s="23"/>
+      <c r="L981" s="22"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
       <c r="A982" s="15"/>
       <c r="B982" s="15"/>
-      <c r="L982" s="23"/>
+      <c r="L982" s="22"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
       <c r="A983" s="15"/>
       <c r="B983" s="15"/>
-      <c r="L983" s="23"/>
+      <c r="L983" s="22"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
       <c r="A984" s="15"/>
       <c r="B984" s="15"/>
-      <c r="L984" s="23"/>
+      <c r="L984" s="22"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
       <c r="A985" s="15"/>
       <c r="B985" s="15"/>
-      <c r="L985" s="23"/>
+      <c r="L985" s="22"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
       <c r="A986" s="15"/>
       <c r="B986" s="15"/>
-      <c r="L986" s="23"/>
+      <c r="L986" s="22"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
       <c r="A987" s="15"/>
       <c r="B987" s="15"/>
-      <c r="L987" s="23"/>
+      <c r="L987" s="22"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
       <c r="A988" s="15"/>
       <c r="B988" s="15"/>
-      <c r="L988" s="23"/>
+      <c r="L988" s="22"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
       <c r="A989" s="15"/>
       <c r="B989" s="15"/>
-      <c r="L989" s="23"/>
+      <c r="L989" s="22"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
       <c r="A990" s="15"/>
       <c r="B990" s="15"/>
-      <c r="L990" s="23"/>
+      <c r="L990" s="22"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
       <c r="A991" s="15"/>
       <c r="B991" s="15"/>
-      <c r="L991" s="23"/>
+      <c r="L991" s="22"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
       <c r="A992" s="15"/>
       <c r="B992" s="15"/>
-      <c r="L992" s="23"/>
+      <c r="L992" s="22"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
       <c r="A993" s="15"/>
       <c r="B993" s="15"/>
-      <c r="L993" s="23"/>
+      <c r="L993" s="22"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
       <c r="A994" s="15"/>
       <c r="B994" s="15"/>
-      <c r="L994" s="23"/>
+      <c r="L994" s="22"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
       <c r="A995" s="15"/>
       <c r="B995" s="15"/>
-      <c r="L995" s="23"/>
+      <c r="L995" s="22"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
       <c r="A996" s="15"/>
       <c r="B996" s="15"/>
-      <c r="L996" s="23"/>
+      <c r="L996" s="22"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
       <c r="A997" s="15"/>
       <c r="B997" s="15"/>
-      <c r="L997" s="23"/>
+      <c r="L997" s="22"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
       <c r="A998" s="15"/>
       <c r="B998" s="15"/>
-      <c r="L998" s="23"/>
+      <c r="L998" s="22"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
       <c r="A999" s="15"/>
       <c r="B999" s="15"/>
-      <c r="L999" s="23"/>
+      <c r="L999" s="22"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
       <c r="A1000" s="15"/>
       <c r="B1000" s="15"/>
-      <c r="L1000" s="23"/>
+      <c r="L1000" s="22"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
       <c r="A1001" s="15"/>
       <c r="B1001" s="15"/>
-      <c r="L1001" s="23"/>
+      <c r="L1001" s="22"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
       <c r="A1002" s="15"/>
       <c r="B1002" s="15"/>
-      <c r="L1002" s="23"/>
+      <c r="L1002" s="22"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
       <c r="A1003" s="15"/>
       <c r="B1003" s="15"/>
-      <c r="L1003" s="23"/>
+      <c r="L1003" s="22"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
       <c r="A1004" s="15"/>
       <c r="B1004" s="15"/>
-      <c r="L1004" s="23"/>
+      <c r="L1004" s="22"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
       <c r="A1005" s="15"/>
       <c r="B1005" s="15"/>
-      <c r="L1005" s="23"/>
+      <c r="L1005" s="22"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
       <c r="A1006" s="15"/>
       <c r="B1006" s="15"/>
-      <c r="L1006" s="23"/>
+      <c r="L1006" s="22"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
       <c r="A1007" s="15"/>
       <c r="B1007" s="15"/>
-      <c r="L1007" s="23"/>
+      <c r="L1007" s="22"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
       <c r="A1008" s="15"/>
       <c r="B1008" s="15"/>
-      <c r="L1008" s="23"/>
+      <c r="L1008" s="22"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
       <c r="A1009" s="15"/>
       <c r="B1009" s="15"/>
-      <c r="L1009" s="23"/>
+      <c r="L1009" s="22"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
       <c r="A1010" s="15"/>
       <c r="B1010" s="15"/>
-      <c r="L1010" s="23"/>
+      <c r="L1010" s="22"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
       <c r="A1011" s="15"/>
       <c r="B1011" s="15"/>
-      <c r="L1011" s="23"/>
+      <c r="L1011" s="22"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
       <c r="A1012" s="15"/>
       <c r="B1012" s="15"/>
-      <c r="L1012" s="23"/>
+      <c r="L1012" s="22"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
       <c r="A1013" s="15"/>
       <c r="B1013" s="15"/>
-      <c r="L1013" s="23"/>
+      <c r="L1013" s="22"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
       <c r="A1014" s="15"/>
       <c r="B1014" s="15"/>
-      <c r="L1014" s="23"/>
+      <c r="L1014" s="22"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
       <c r="A1015" s="15"/>
       <c r="B1015" s="15"/>
-      <c r="L1015" s="23"/>
+      <c r="L1015" s="22"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
       <c r="A1016" s="15"/>
       <c r="B1016" s="15"/>
-      <c r="L1016" s="23"/>
+      <c r="L1016" s="22"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
       <c r="A1017" s="15"/>
       <c r="B1017" s="15"/>
-      <c r="L1017" s="23"/>
+      <c r="L1017" s="22"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
       <c r="A1018" s="15"/>
       <c r="B1018" s="15"/>
-      <c r="L1018" s="23"/>
+      <c r="L1018" s="22"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
       <c r="A1019" s="15"/>
       <c r="B1019" s="15"/>
-      <c r="L1019" s="23"/>
+      <c r="L1019" s="22"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
       <c r="A1020" s="15"/>
       <c r="B1020" s="15"/>
-      <c r="L1020" s="23"/>
+      <c r="L1020" s="22"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
       <c r="A1021" s="15"/>
       <c r="B1021" s="15"/>
-      <c r="L1021" s="23"/>
+      <c r="L1021" s="22"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
       <c r="A1022" s="15"/>
       <c r="B1022" s="15"/>
-      <c r="L1022" s="23"/>
+      <c r="L1022" s="22"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
       <c r="A1023" s="15"/>
       <c r="B1023" s="15"/>
-      <c r="L1023" s="23"/>
+      <c r="L1023" s="22"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
       <c r="A1024" s="15"/>
       <c r="B1024" s="15"/>
-      <c r="L1024" s="23"/>
+      <c r="L1024" s="22"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
       <c r="A1025" s="15"/>
       <c r="B1025" s="15"/>
-      <c r="L1025" s="23"/>
+      <c r="L1025" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7898,11 +7898,11 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>0</v>
+      <c r="L2" s="7" t="s">
+        <v>1</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -7913,31 +7913,31 @@
       <c r="AH2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="11">
         <v>2.5E32</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>45686.0</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="10">
         <v>12.0</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="10">
         <v>2048.0</v>
       </c>
       <c r="J3" s="14">
@@ -7946,7 +7946,7 @@
       <c r="K3" s="14">
         <v>1000.0</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="10">
         <v>0.0</v>
       </c>
       <c r="AB3" s="2"/>
@@ -7958,31 +7958,31 @@
       <c r="AH3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>45762.0</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="10">
         <v>12.0</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="10">
         <v>2048.0</v>
       </c>
       <c r="J4" s="14">
@@ -7991,7 +7991,7 @@
       <c r="K4" s="14">
         <v>52250.04</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="10">
         <v>0.0</v>
       </c>
       <c r="AB4" s="2"/>
@@ -8003,31 +8003,31 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="A5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>45762.0</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="10">
         <v>12.0</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="10">
         <v>2048.0</v>
       </c>
       <c r="J5" s="14">
@@ -8036,7 +8036,7 @@
       <c r="K5" s="14">
         <v>881914.18</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="10">
         <v>0.0</v>
       </c>
       <c r="AB5" s="2"/>
@@ -8048,31 +8048,31 @@
       <c r="AH5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="A6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>45762.0</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="10">
         <v>12.0</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="10">
         <v>2048.0</v>
       </c>
       <c r="J6" s="14">
@@ -8081,7 +8081,7 @@
       <c r="K6" s="14">
         <v>750000.0</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="10">
         <v>0.0</v>
       </c>
       <c r="AB6" s="2"/>
@@ -8093,32 +8093,32 @@
       <c r="AH6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="A7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>45763.0</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="10">
         <v>12.0</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>39</v>
+      <c r="I7" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="J7" s="14">
         <v>949835.78</v>
@@ -8126,7 +8126,7 @@
       <c r="K7" s="14">
         <v>949835.78</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="10">
         <v>0.0</v>
       </c>
       <c r="AB7" s="2"/>
@@ -8138,32 +8138,32 @@
       <c r="AH7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>45763.0</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="10">
         <v>12.0</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>47</v>
+      <c r="I8" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J8" s="14">
         <v>524584.95</v>
@@ -8171,10 +8171,10 @@
       <c r="K8" s="14">
         <v>524584.95</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="10">
         <v>0.0</v>
       </c>
-      <c r="O8" s="22"/>
+      <c r="O8" s="25"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8184,31 +8184,31 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>45792.0</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="10">
         <v>12.0</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="10" t="s">
         <v>52</v>
       </c>
       <c r="J9" s="14">
@@ -8217,7 +8217,7 @@
       <c r="K9" s="14">
         <v>211614.23</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="10">
         <v>0.0</v>
       </c>
       <c r="AB9" s="2"/>
@@ -8229,31 +8229,31 @@
       <c r="AH9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>45825.0</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="10">
         <v>12.0</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="10">
         <v>2048.0</v>
       </c>
       <c r="J10" s="14">
@@ -8274,31 +8274,31 @@
       <c r="AH10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="A11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>45825.0</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="10">
         <v>12.0</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="10">
         <v>2048.0</v>
       </c>
       <c r="J11" s="14">
@@ -8307,7 +8307,7 @@
       <c r="K11" s="14">
         <v>618154.38</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="10">
         <v>0.01</v>
       </c>
       <c r="AB11" s="2"/>
@@ -8319,32 +8319,32 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="A12" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="13">
         <v>45832.0</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="10">
         <v>12.0</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I12" s="8" t="s">
-        <v>60</v>
+      <c r="I12" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8352,7 +8352,7 @@
       <c r="K12" s="14">
         <v>1600334.09</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="10">
         <v>0.0</v>
       </c>
       <c r="AB12" s="2"/>
@@ -8364,31 +8364,31 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="C13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <v>45863.0</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="10">
         <v>12.0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="10">
         <v>2048.0</v>
       </c>
       <c r="J13" s="14">
@@ -8400,7 +8400,7 @@
       <c r="L13" s="14">
         <v>0.0</v>
       </c>
-      <c r="M13" s="30"/>
+      <c r="M13" s="34"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8410,31 +8410,31 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="8" t="s">
+      <c r="A14" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <v>45887.0</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="10">
         <v>12.0</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="10" t="s">
         <v>52</v>
       </c>
       <c r="J14" s="14">
@@ -8443,7 +8443,7 @@
       <c r="K14" s="14">
         <v>968237.39</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="10">
         <v>0.0</v>
       </c>
       <c r="AB14" s="2"/>
@@ -8455,32 +8455,32 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="A15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <v>45924.0</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="10">
         <v>12.0</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>39</v>
+      <c r="I15" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="J15" s="14">
         <v>1011677.95</v>
@@ -8488,7 +8488,7 @@
       <c r="K15" s="14">
         <v>1011677.95</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="10">
         <v>0.0</v>
       </c>
       <c r="AB15" s="2"/>
@@ -8500,31 +8500,31 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="C16" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <v>45929.0</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="10">
         <v>12.0</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="10">
         <v>2048.0</v>
       </c>
       <c r="J16" s="14">
@@ -8545,37 +8545,37 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="A17" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <v>45930.0</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="10">
         <v>12.0</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="10">
         <v>2048.0</v>
       </c>
       <c r="J17" s="14">
         <v>34065.36</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="10">
         <v>0.0</v>
       </c>
       <c r="L17" s="14">
@@ -8590,31 +8590,31 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="A18" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="10">
         <v>12.0</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="10" t="s">
         <v>52</v>
       </c>
       <c r="J18" s="14">
@@ -8623,7 +8623,7 @@
       <c r="K18" s="14">
         <v>63746.85</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="10">
         <v>0.0</v>
       </c>
       <c r="AB18" s="2"/>
@@ -8635,32 +8635,32 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="A19" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="10">
         <v>12.0</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>60</v>
+      <c r="I19" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8668,7 +8668,7 @@
       <c r="K19" s="14">
         <v>947931.1</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="10">
         <v>0.0</v>
       </c>
       <c r="AB19" s="2"/>
@@ -8680,31 +8680,31 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="C20" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="10">
         <v>12.0</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="10">
         <v>2048.0</v>
       </c>
       <c r="J20" s="14">
@@ -8713,7 +8713,7 @@
       <c r="K20" s="14">
         <v>259790.57</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="10">
         <v>0.0</v>
       </c>
       <c r="AB20" s="2"/>
@@ -8725,31 +8725,31 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="A21" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="10">
         <v>12.0</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="10">
         <v>2048.0</v>
       </c>
       <c r="J21" s="14">
@@ -8758,7 +8758,7 @@
       <c r="K21" s="14">
         <v>170479.3</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="10">
         <v>0.0</v>
       </c>
       <c r="AB21" s="2"/>
@@ -8770,31 +8770,31 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="A22" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="42">
         <v>45953.0</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="10">
         <v>12.0</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="10">
         <v>2000.0</v>
       </c>
       <c r="J22" s="14">
@@ -8815,32 +8815,32 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="A23" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="42">
         <v>45953.0</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="10">
         <v>12.0</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>104</v>
+      <c r="I23" s="10" t="s">
+        <v>108</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -8848,7 +8848,7 @@
       <c r="K23" s="14">
         <v>1000001.64</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="10">
         <v>0.0</v>
       </c>
       <c r="AB23" s="2"/>
@@ -8860,31 +8860,31 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="A24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="42">
         <v>45953.0</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="10">
         <v>12.0</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="10">
         <v>2048.0</v>
       </c>
       <c r="J24" s="14">
@@ -8893,7 +8893,7 @@
       <c r="K24" s="14">
         <v>68405.66</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="10">
         <v>0.0</v>
       </c>
       <c r="AB24" s="2"/>
@@ -8905,32 +8905,32 @@
       <c r="AH24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="42">
+        <v>45975.0</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="10">
+        <v>12.0</v>
+      </c>
+      <c r="H25" s="10">
+        <v>339039.0</v>
+      </c>
+      <c r="I25" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="39">
-        <v>45975.0</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="H25" s="8">
-        <v>339039.0</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -8938,7 +8938,7 @@
       <c r="K25" s="14">
         <v>1157673.06</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="10">
         <v>0.0</v>
       </c>
       <c r="AB25" s="2"/>
@@ -8950,31 +8950,31 @@
       <c r="AH25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="A26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="42">
         <v>45989.0</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="10">
         <v>12.0</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="10">
         <v>2048.0</v>
       </c>
       <c r="J26" s="14">
@@ -8983,7 +8983,7 @@
       <c r="K26" s="14">
         <v>34065.36</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="10">
         <v>0.0</v>
       </c>
       <c r="AB26" s="2"/>
@@ -8995,31 +8995,31 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="A27" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="13">
         <v>46104.0</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="10">
         <v>12.0</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="10">
         <v>2048.0</v>
       </c>
       <c r="J27" s="14">
@@ -9040,37 +9040,37 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="A28" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="B28" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="13">
         <v>46120.0</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="10">
         <v>12.0</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>47</v>
+      <c r="I28" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J28" s="14">
         <v>1912292.52</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="10">
         <v>0.0</v>
       </c>
       <c r="L28" s="14">
@@ -9085,37 +9085,37 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="8" t="s">
+      <c r="A29" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="C29" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="13">
         <v>46196.0</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="10">
         <v>12.0</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="10">
         <v>2048.0</v>
       </c>
       <c r="J29" s="14">
         <v>1496713.48</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="10">
         <v>0.0</v>
       </c>
       <c r="L29" s="14">
@@ -9130,37 +9130,37 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="A30" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="B30" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="C30" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="13">
         <v>46205.0</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="10">
         <v>12.0</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>39</v>
+      <c r="I30" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="J30" s="14">
         <v>624166.14</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="10">
         <v>0.0</v>
       </c>
       <c r="L30" s="14">
@@ -9175,37 +9175,37 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="B31" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="C31" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="13">
         <v>46205.0</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="10">
         <v>12.0</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>104</v>
+      <c r="I31" s="10" t="s">
+        <v>108</v>
       </c>
       <c r="J31" s="14">
         <v>18462.36</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="10">
         <v>0.0</v>
       </c>
       <c r="L31" s="14">
@@ -9220,37 +9220,37 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>132</v>
+      <c r="A32" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="13">
         <v>46213.0</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="10">
         <v>12.0</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>104</v>
+      <c r="I32" s="10" t="s">
+        <v>108</v>
       </c>
       <c r="J32" s="14">
         <v>1530656.62</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="10">
         <v>0.0</v>
       </c>
       <c r="L32" s="14">
@@ -9265,37 +9265,37 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B33" s="8" t="s">
+      <c r="A33" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="10" t="s">
         <v>126</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D33" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="13">
         <v>46227.0</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="10">
         <v>12.0</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="10">
         <v>2048.0</v>
       </c>
       <c r="J33" s="14">
         <v>173846.38</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="10">
         <v>0.0</v>
       </c>
       <c r="L33" s="14">

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,12 +30,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="207">
   <si>
+    <t>Saldo</t>
+  </si>
+  <si>
     <t>Controle de pagamentos</t>
   </si>
   <si>
-    <t>Saldo</t>
-  </si>
-  <si>
     <t>2025NE000005</t>
   </si>
   <si>
@@ -54,18 +54,33 @@
     <t>C25512</t>
   </si>
   <si>
+    <t>25E0385</t>
+  </si>
+  <si>
+    <t>2025NE000369</t>
+  </si>
+  <si>
+    <t>C25516</t>
+  </si>
+  <si>
+    <t>25E0387</t>
+  </si>
+  <si>
     <t>Número Contrato</t>
   </si>
   <si>
-    <t>25E0385</t>
-  </si>
-  <si>
     <t>UG Executora</t>
   </si>
   <si>
+    <t>2025NE000371</t>
+  </si>
+  <si>
     <t>UG Responsável</t>
   </si>
   <si>
+    <t>25E0389</t>
+  </si>
+  <si>
     <t>UG Fiscalizadora</t>
   </si>
   <si>
@@ -84,9 +99,18 @@
     <t>PAG</t>
   </si>
   <si>
+    <t>2025NE000413</t>
+  </si>
+  <si>
     <t>Moeda</t>
   </si>
   <si>
+    <t>C25501</t>
+  </si>
+  <si>
+    <t>25E0403</t>
+  </si>
+  <si>
     <t>Valor Total do Contrato</t>
   </si>
   <si>
@@ -96,24 +120,18 @@
     <t>Valor Empenhado</t>
   </si>
   <si>
-    <t>2025NE000369</t>
-  </si>
-  <si>
     <t>Valor Liquidado</t>
   </si>
   <si>
-    <t>C25516</t>
-  </si>
-  <si>
     <t>Saldo (Valor a Faturar)</t>
   </si>
   <si>
-    <t>25E0387</t>
-  </si>
-  <si>
     <t>Fornecedor</t>
   </si>
   <si>
+    <t>20SP</t>
+  </si>
+  <si>
     <t>Tipo Despesa /Receita</t>
   </si>
   <si>
@@ -126,57 +144,39 @@
     <t>005/CELOG-PAMALS/2025</t>
   </si>
   <si>
-    <t>2025NE000371</t>
-  </si>
-  <si>
     <t>CELOG</t>
   </si>
   <si>
-    <t>25E0389</t>
-  </si>
-  <si>
     <t>PAMALS</t>
   </si>
   <si>
+    <t>2025NE000414</t>
+  </si>
+  <si>
+    <t>C25525</t>
+  </si>
+  <si>
+    <t>25E0431</t>
+  </si>
+  <si>
+    <t>21EM</t>
+  </si>
+  <si>
     <t>Vigente</t>
   </si>
   <si>
     <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
   </si>
   <si>
-    <t>2025NE000413</t>
-  </si>
-  <si>
     <t>67101.001510/2024-12</t>
   </si>
   <si>
-    <t>C25501</t>
-  </si>
-  <si>
-    <t>25E0403</t>
-  </si>
-  <si>
     <t>R$</t>
   </si>
   <si>
-    <t>20SP</t>
-  </si>
-  <si>
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
-    <t>2025NE000414</t>
-  </si>
-  <si>
-    <t>C25525</t>
-  </si>
-  <si>
-    <t>25E0431</t>
-  </si>
-  <si>
-    <t>21EM</t>
-  </si>
-  <si>
     <t>2025NE000559</t>
   </si>
   <si>
@@ -189,21 +189,45 @@
     <t>20X7</t>
   </si>
   <si>
+    <t>2025NE000770</t>
+  </si>
+  <si>
+    <t>25E0731</t>
+  </si>
+  <si>
+    <t>2025NE000774</t>
+  </si>
+  <si>
+    <t>25E0737</t>
+  </si>
+  <si>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
+    <t>25E0787</t>
+  </si>
+  <si>
     <t>Módulo</t>
   </si>
   <si>
-    <t>2025NE000770</t>
-  </si>
-  <si>
-    <t>25E0731</t>
+    <t>219C</t>
   </si>
   <si>
     <t>Referência</t>
   </si>
   <si>
+    <t>2025NE001065</t>
+  </si>
+  <si>
     <t>Nº recibo</t>
   </si>
   <si>
+    <t>25E0999</t>
+  </si>
+  <si>
     <t>Nº</t>
   </si>
   <si>
@@ -219,40 +243,34 @@
     <t>Vencimento</t>
   </si>
   <si>
-    <t>2025NE000774</t>
-  </si>
-  <si>
     <t>Valor das Nfs</t>
   </si>
   <si>
-    <t>25E0737</t>
-  </si>
-  <si>
     <t>Ordem de Pagamento</t>
   </si>
   <si>
+    <t>2025NE001200</t>
+  </si>
+  <si>
+    <t>C25590</t>
+  </si>
+  <si>
     <t>Faturado</t>
   </si>
   <si>
+    <t>25E1128</t>
+  </si>
+  <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>2025NE000843</t>
-  </si>
-  <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
-  </si>
-  <si>
-    <t>219C</t>
-  </si>
-  <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
   </si>
   <si>
     <t>FEV/25</t>
@@ -261,36 +279,18 @@
     <t>-</t>
   </si>
   <si>
-    <t>2025NE001200</t>
-  </si>
-  <si>
-    <t>C25590</t>
-  </si>
-  <si>
-    <t>25E1128</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>25E1446</t>
+    <t>2025NE001627</t>
+  </si>
+  <si>
+    <t>25E1475</t>
   </si>
   <si>
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>2025NE001627</t>
-  </si>
-  <si>
-    <t>25E1475</t>
-  </si>
-  <si>
     <t>2025NE001629</t>
   </si>
   <si>
@@ -312,25 +312,28 @@
     <t>25E1536</t>
   </si>
   <si>
+    <t>MAR/25</t>
+  </si>
+  <si>
     <t>2025NE001689</t>
   </si>
   <si>
-    <t>MAR/25</t>
-  </si>
-  <si>
     <t>25E1537</t>
   </si>
   <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
   </si>
   <si>
+    <t>2025NP001979</t>
+  </si>
+  <si>
     <t>2025NE001690</t>
   </si>
   <si>
     <t>25E1538</t>
   </si>
   <si>
-    <t>2025NP001979</t>
+    <t>ABR/25</t>
   </si>
   <si>
     <t>2025NE001823</t>
@@ -342,6 +345,9 @@
     <t>25E1666</t>
   </si>
   <si>
+    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
+  </si>
+  <si>
     <t>2025NE001828</t>
   </si>
   <si>
@@ -351,21 +357,21 @@
     <t>25E1667</t>
   </si>
   <si>
-    <t>ABR/25</t>
+    <t>2025NP002341</t>
   </si>
   <si>
     <t>20YJ</t>
   </si>
   <si>
+    <t>MAI/25</t>
+  </si>
+  <si>
     <t>2025NE001830</t>
   </si>
   <si>
     <t>25E1669</t>
   </si>
   <si>
-    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
-  </si>
-  <si>
     <t>2025NE002200</t>
   </si>
   <si>
@@ -375,7 +381,7 @@
     <t>25E2021</t>
   </si>
   <si>
-    <t>2025NP002341</t>
+    <t>2025NP002884</t>
   </si>
   <si>
     <t>2025NE002237</t>
@@ -384,7 +390,7 @@
     <t>25E2058</t>
   </si>
   <si>
-    <t>MAI/25</t>
+    <t>JUN/25</t>
   </si>
   <si>
     <t>2026NE000330</t>
@@ -394,54 +400,6 @@
   </si>
   <si>
     <t>26E0320</t>
-  </si>
-  <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>2025NP002884</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>JUN/25</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -453,25 +411,67 @@
     <t>2025NP400522</t>
   </si>
   <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
+    <t>JUL/25</t>
+  </si>
+  <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
+    <t>2025NE000843, 2025NE001200</t>
+  </si>
+  <si>
+    <t>2025NP003724</t>
+  </si>
+  <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
+  </si>
+  <si>
+    <t>AGO/25</t>
+  </si>
+  <si>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
+  </si>
+  <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>2025NP004558</t>
+  </si>
+  <si>
+    <t>26E0803</t>
+  </si>
+  <si>
     <t>2026NE000944</t>
   </si>
   <si>
     <t>26E0906</t>
-  </si>
-  <si>
-    <t>JUL/25</t>
-  </si>
-  <si>
-    <t>2025NE000843, 2025NE001200</t>
-  </si>
-  <si>
-    <t>2025NP003724</t>
-  </si>
-  <si>
-    <t>AGO/25</t>
-  </si>
-  <si>
-    <t>2025NP004558</t>
   </si>
   <si>
     <t>SET/25</t>
@@ -701,15 +701,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Century Gothic"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -861,37 +861,37 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -913,25 +913,25 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -940,6 +940,7 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -949,7 +950,6 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -969,11 +969,11 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -993,13 +993,13 @@
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1412,103 +1412,103 @@
       <c r="V1" s="3"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
+      <c r="A2" s="5"/>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="9"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
       <c r="V3" s="3"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S4" s="16" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="V4" s="3"/>
     </row>
@@ -1517,16 +1517,16 @@
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1535,16 +1535,16 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="N5" s="21">
         <v>9.165159737E7</v>
@@ -1562,20 +1562,20 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="V5" s="3"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
-      <c r="L6" s="22"/>
+      <c r="L6" s="23"/>
       <c r="V6" s="3"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
@@ -1592,59 +1592,59 @@
       <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="29" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>66</v>
+        <v>71</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>72</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="O8" s="29"/>
       <c r="P8" s="28"/>
       <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="32">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="33">
         <v>1.0</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>75</v>
+      <c r="D9" s="34" t="s">
+        <v>81</v>
       </c>
       <c r="E9" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F9" s="36">
         <v>594.0</v>
@@ -1653,7 +1653,7 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="36" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I9" s="37"/>
       <c r="J9" s="37">
@@ -1663,7 +1663,7 @@
         <v>748504.24</v>
       </c>
       <c r="L9" s="36" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
@@ -1675,14 +1675,14 @@
       <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
       <c r="C10" s="41"/>
-      <c r="D10" s="33" t="s">
-        <v>95</v>
+      <c r="D10" s="34" t="s">
+        <v>94</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F10" s="36">
         <v>620.0</v>
@@ -1701,26 +1701,26 @@
         <v>1110378.24</v>
       </c>
       <c r="L10" s="36" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M10" s="39">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
-      <c r="N10" s="43"/>
+      <c r="N10" s="42"/>
       <c r="O10" s="26"/>
       <c r="P10" s="28"/>
       <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
       <c r="C11" s="41"/>
-      <c r="D11" s="33" t="s">
-        <v>107</v>
+      <c r="D11" s="34" t="s">
+        <v>101</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F11" s="36">
         <v>634.0</v>
@@ -1729,7 +1729,7 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I11" s="37"/>
       <c r="J11" s="37">
@@ -1739,25 +1739,25 @@
         <v>974557.12</v>
       </c>
       <c r="L11" s="35" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="M11" s="39">
         <v>974557.12</v>
       </c>
-      <c r="N11" s="43"/>
+      <c r="N11" s="42"/>
       <c r="O11" s="26"/>
       <c r="P11" s="28"/>
       <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
       <c r="C12" s="41"/>
-      <c r="D12" s="33" t="s">
-        <v>118</v>
+      <c r="D12" s="34" t="s">
+        <v>111</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F12" s="35">
         <v>660.0</v>
@@ -1766,7 +1766,7 @@
         <v>45856.0</v>
       </c>
       <c r="H12" s="45" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="I12" s="37"/>
       <c r="J12" s="37">
@@ -1776,7 +1776,7 @@
         <v>1402001.34</v>
       </c>
       <c r="L12" s="47" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="M12" s="39">
         <v>1402001.34</v>
@@ -1787,14 +1787,14 @@
       <c r="V12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="41"/>
       <c r="D13" s="49" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F13" s="36">
         <v>661.0</v>
@@ -1803,7 +1803,7 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="I13" s="44"/>
       <c r="J13" s="44">
@@ -1813,7 +1813,7 @@
         <v>1223702.3</v>
       </c>
       <c r="L13" s="35" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="M13" s="39">
         <v>1223702.3</v>
@@ -1824,14 +1824,14 @@
       <c r="V13" s="3"/>
     </row>
     <row r="14">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="41"/>
       <c r="D14" s="49" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F14" s="35">
         <v>688.0</v>
@@ -1840,7 +1840,7 @@
         <v>45901.0</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I14" s="44"/>
       <c r="J14" s="44">
@@ -1850,25 +1850,25 @@
         <v>1011677.95</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
-      <c r="N14" s="43"/>
+      <c r="N14" s="42"/>
       <c r="O14" s="26"/>
       <c r="P14" s="28"/>
       <c r="V14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="41"/>
       <c r="D15" s="49" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F15" s="35">
         <v>696.0</v>
@@ -1877,7 +1877,7 @@
         <v>45923.0</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I15" s="44"/>
       <c r="J15" s="44">
@@ -1887,7 +1887,7 @@
         <v>896744.06</v>
       </c>
       <c r="L15" s="35" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M15" s="39">
         <v>896744.06</v>
@@ -1897,14 +1897,14 @@
       <c r="V15" s="3"/>
     </row>
     <row r="16">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="41"/>
       <c r="D16" s="49" t="s">
         <v>147</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F16" s="35">
         <v>704.0</v>
@@ -1928,13 +1928,13 @@
       <c r="M16" s="39">
         <v>919329.06</v>
       </c>
-      <c r="N16" s="43"/>
+      <c r="N16" s="42"/>
       <c r="O16" s="26"/>
       <c r="V16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
         <v>150</v>
@@ -1967,14 +1967,14 @@
       <c r="V17" s="3"/>
     </row>
     <row r="18">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
       <c r="C18" s="41"/>
       <c r="D18" s="49" t="s">
         <v>153</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F18" s="35">
         <v>728.0</v>
@@ -2007,14 +2007,14 @@
       <c r="V18" s="52"/>
     </row>
     <row r="19">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="41"/>
       <c r="D19" s="49" t="s">
         <v>156</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F19" s="35">
         <v>278.0</v>
@@ -2047,8 +2047,8 @@
       <c r="V19" s="52"/>
     </row>
     <row r="20">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="41"/>
       <c r="D20" s="49" t="s">
         <v>159</v>
@@ -2061,7 +2061,7 @@
         <v>46078.0</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I20" s="44"/>
       <c r="J20" s="44">
@@ -2085,8 +2085,8 @@
       <c r="V20" s="52"/>
     </row>
     <row r="21">
-      <c r="A21" s="23"/>
-      <c r="B21" s="23"/>
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="41"/>
       <c r="D21" s="49" t="s">
         <v>161</v>
@@ -2123,8 +2123,8 @@
       <c r="V21" s="52"/>
     </row>
     <row r="22">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
       <c r="C22" s="41"/>
       <c r="D22" s="49" t="s">
         <v>164</v>
@@ -2161,8 +2161,8 @@
       <c r="V22" s="52"/>
     </row>
     <row r="23">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
       <c r="C23" s="41"/>
       <c r="D23" s="49" t="s">
         <v>168</v>
@@ -2199,8 +2199,8 @@
       <c r="V23" s="52"/>
     </row>
     <row r="24">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
       <c r="C24" s="41"/>
       <c r="D24" s="49" t="s">
         <v>170</v>
@@ -2237,8 +2237,8 @@
       <c r="V24" s="52"/>
     </row>
     <row r="25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="23"/>
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="41"/>
       <c r="D25" s="49" t="s">
         <v>172</v>
@@ -2275,8 +2275,8 @@
       <c r="V25" s="52"/>
     </row>
     <row r="26">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
       <c r="C26" s="57"/>
       <c r="D26" s="49" t="s">
         <v>174</v>
@@ -2289,7 +2289,7 @@
       <c r="J26" s="56"/>
       <c r="K26" s="46"/>
       <c r="L26" s="35" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M26" s="39" t="s">
         <v>175</v>
@@ -2303,37 +2303,37 @@
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
       <c r="C27" s="29" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G27" s="29"/>
       <c r="H27" s="29" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
       <c r="K27" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="L27" s="31" t="s">
-        <v>66</v>
+        <v>71</v>
+      </c>
+      <c r="L27" s="32" t="s">
+        <v>72</v>
       </c>
       <c r="M27" s="59" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="O27" s="26"/>
       <c r="P27" s="28"/>
@@ -2351,9 +2351,9 @@
       <c r="AC27" s="28"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="32">
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="33">
         <v>2.0</v>
       </c>
       <c r="D28" s="60" t="s">
@@ -2400,8 +2400,8 @@
       <c r="AC28" s="28"/>
     </row>
     <row r="29">
-      <c r="A29" s="23"/>
-      <c r="B29" s="23"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
       <c r="C29" s="41"/>
       <c r="D29" s="60" t="s">
         <v>178</v>
@@ -2449,8 +2449,8 @@
       <c r="AC29" s="28"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
       <c r="C30" s="41"/>
       <c r="D30" s="62" t="s">
         <v>181</v>
@@ -2465,7 +2465,7 @@
         <v>45853.0</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I30" s="44"/>
       <c r="J30" s="44">
@@ -2498,8 +2498,8 @@
       <c r="AC30" s="28"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
       <c r="C31" s="41"/>
       <c r="D31" s="62" t="s">
         <v>184</v>
@@ -2514,7 +2514,7 @@
         <v>45910.0</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I31" s="44"/>
       <c r="J31" s="44">
@@ -2547,8 +2547,8 @@
       <c r="AC31" s="28"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
       <c r="C32" s="41"/>
       <c r="D32" s="62" t="s">
         <v>186</v>
@@ -2563,7 +2563,7 @@
         <v>45904.0</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="I32" s="67"/>
       <c r="J32" s="67">
@@ -2596,8 +2596,8 @@
       <c r="AC32" s="28"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
       <c r="C33" s="41"/>
       <c r="D33" s="62" t="s">
         <v>188</v>
@@ -2612,7 +2612,7 @@
         <v>46008.0</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="67"/>
       <c r="J33" s="67">
@@ -2645,8 +2645,8 @@
       <c r="AC33" s="28"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
       <c r="C34" s="41"/>
       <c r="D34" s="62" t="s">
         <v>191</v>
@@ -2694,8 +2694,8 @@
       <c r="AC34" s="28"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
       <c r="C35" s="41"/>
       <c r="D35" s="62" t="s">
         <v>195</v>
@@ -2710,7 +2710,7 @@
         <v>45968.0</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I35" s="67"/>
       <c r="J35" s="67">
@@ -2743,8 +2743,8 @@
       <c r="AC35" s="28"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
+      <c r="A36" s="24"/>
+      <c r="B36" s="24"/>
       <c r="C36" s="41"/>
       <c r="D36" s="62" t="s">
         <v>198</v>
@@ -2759,7 +2759,7 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I36" s="71"/>
       <c r="J36" s="70">
@@ -2792,8 +2792,8 @@
       <c r="AC36" s="28"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
       <c r="C37" s="41"/>
       <c r="D37" s="62" t="s">
         <v>200</v>
@@ -2829,8 +2829,8 @@
       <c r="AC37" s="28"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="57"/>
       <c r="D38" s="62" t="s">
         <v>202</v>
@@ -2866,9 +2866,9 @@
       <c r="AC38" s="28"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="32">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="33">
         <v>3.0</v>
       </c>
       <c r="D39" s="62" t="s">
@@ -2882,7 +2882,7 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I39" s="71"/>
       <c r="J39" s="70">
@@ -2929,7 +2929,7 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="66" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I40" s="71"/>
       <c r="J40" s="70">
@@ -2939,7 +2939,7 @@
         <v>58868.35</v>
       </c>
       <c r="L40" s="35" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M40" s="73">
         <v>58868.35</v>
@@ -3234,4622 +3234,4622 @@
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
-      <c r="L102" s="22"/>
+      <c r="L102" s="23"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
-      <c r="L103" s="22"/>
+      <c r="L103" s="23"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
-      <c r="L104" s="22"/>
+      <c r="L104" s="23"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
-      <c r="L105" s="22"/>
+      <c r="L105" s="23"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
-      <c r="L106" s="22"/>
+      <c r="L106" s="23"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
-      <c r="L107" s="22"/>
+      <c r="L107" s="23"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
-      <c r="L108" s="22"/>
+      <c r="L108" s="23"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
-      <c r="L109" s="22"/>
+      <c r="L109" s="23"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
-      <c r="L110" s="22"/>
+      <c r="L110" s="23"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
-      <c r="L111" s="22"/>
+      <c r="L111" s="23"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
-      <c r="L112" s="22"/>
+      <c r="L112" s="23"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
-      <c r="L113" s="22"/>
+      <c r="L113" s="23"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
-      <c r="L114" s="22"/>
+      <c r="L114" s="23"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
-      <c r="L115" s="22"/>
+      <c r="L115" s="23"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
-      <c r="L116" s="22"/>
+      <c r="L116" s="23"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
-      <c r="L117" s="22"/>
+      <c r="L117" s="23"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
-      <c r="L118" s="22"/>
+      <c r="L118" s="23"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
-      <c r="L119" s="22"/>
+      <c r="L119" s="23"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
-      <c r="L120" s="22"/>
+      <c r="L120" s="23"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
-      <c r="L121" s="22"/>
+      <c r="L121" s="23"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
-      <c r="L122" s="22"/>
+      <c r="L122" s="23"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
-      <c r="L123" s="22"/>
+      <c r="L123" s="23"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
-      <c r="L124" s="22"/>
+      <c r="L124" s="23"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
-      <c r="L125" s="22"/>
+      <c r="L125" s="23"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
-      <c r="L126" s="22"/>
+      <c r="L126" s="23"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
-      <c r="L127" s="22"/>
+      <c r="L127" s="23"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
-      <c r="L128" s="22"/>
+      <c r="L128" s="23"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
-      <c r="L129" s="22"/>
+      <c r="L129" s="23"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
-      <c r="L130" s="22"/>
+      <c r="L130" s="23"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
-      <c r="L131" s="22"/>
+      <c r="L131" s="23"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
-      <c r="L132" s="22"/>
+      <c r="L132" s="23"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
-      <c r="L133" s="22"/>
+      <c r="L133" s="23"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
-      <c r="L134" s="22"/>
+      <c r="L134" s="23"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
-      <c r="L135" s="22"/>
+      <c r="L135" s="23"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
-      <c r="L136" s="22"/>
+      <c r="L136" s="23"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
-      <c r="L137" s="22"/>
+      <c r="L137" s="23"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
-      <c r="L138" s="22"/>
+      <c r="L138" s="23"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
-      <c r="L139" s="22"/>
+      <c r="L139" s="23"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
-      <c r="L140" s="22"/>
+      <c r="L140" s="23"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
-      <c r="L141" s="22"/>
+      <c r="L141" s="23"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
-      <c r="L142" s="22"/>
+      <c r="L142" s="23"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
-      <c r="L143" s="22"/>
+      <c r="L143" s="23"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
-      <c r="L144" s="22"/>
+      <c r="L144" s="23"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
-      <c r="L145" s="22"/>
+      <c r="L145" s="23"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
-      <c r="L146" s="22"/>
+      <c r="L146" s="23"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
-      <c r="L147" s="22"/>
+      <c r="L147" s="23"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="15"/>
       <c r="B148" s="15"/>
-      <c r="L148" s="22"/>
+      <c r="L148" s="23"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="15"/>
       <c r="B149" s="15"/>
-      <c r="L149" s="22"/>
+      <c r="L149" s="23"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="15"/>
       <c r="B150" s="15"/>
-      <c r="L150" s="22"/>
+      <c r="L150" s="23"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="15"/>
       <c r="B151" s="15"/>
-      <c r="L151" s="22"/>
+      <c r="L151" s="23"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="15"/>
       <c r="B152" s="15"/>
-      <c r="L152" s="22"/>
+      <c r="L152" s="23"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="15"/>
       <c r="B153" s="15"/>
-      <c r="L153" s="22"/>
+      <c r="L153" s="23"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="15"/>
       <c r="B154" s="15"/>
-      <c r="L154" s="22"/>
+      <c r="L154" s="23"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="15"/>
       <c r="B155" s="15"/>
-      <c r="L155" s="22"/>
+      <c r="L155" s="23"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="15"/>
       <c r="B156" s="15"/>
-      <c r="L156" s="22"/>
+      <c r="L156" s="23"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="15"/>
       <c r="B157" s="15"/>
-      <c r="L157" s="22"/>
+      <c r="L157" s="23"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="15"/>
       <c r="B158" s="15"/>
-      <c r="L158" s="22"/>
+      <c r="L158" s="23"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="15"/>
       <c r="B159" s="15"/>
-      <c r="L159" s="22"/>
+      <c r="L159" s="23"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="15"/>
       <c r="B160" s="15"/>
-      <c r="L160" s="22"/>
+      <c r="L160" s="23"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="15"/>
       <c r="B161" s="15"/>
-      <c r="L161" s="22"/>
+      <c r="L161" s="23"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="15"/>
       <c r="B162" s="15"/>
-      <c r="L162" s="22"/>
+      <c r="L162" s="23"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="15"/>
       <c r="B163" s="15"/>
-      <c r="L163" s="22"/>
+      <c r="L163" s="23"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="15"/>
       <c r="B164" s="15"/>
-      <c r="L164" s="22"/>
+      <c r="L164" s="23"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="15"/>
       <c r="B165" s="15"/>
-      <c r="L165" s="22"/>
+      <c r="L165" s="23"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="15"/>
       <c r="B166" s="15"/>
-      <c r="L166" s="22"/>
+      <c r="L166" s="23"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="15"/>
       <c r="B167" s="15"/>
-      <c r="L167" s="22"/>
+      <c r="L167" s="23"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="15"/>
       <c r="B168" s="15"/>
-      <c r="L168" s="22"/>
+      <c r="L168" s="23"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="15"/>
       <c r="B169" s="15"/>
-      <c r="L169" s="22"/>
+      <c r="L169" s="23"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="15"/>
       <c r="B170" s="15"/>
-      <c r="L170" s="22"/>
+      <c r="L170" s="23"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="15"/>
       <c r="B171" s="15"/>
-      <c r="L171" s="22"/>
+      <c r="L171" s="23"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="15"/>
       <c r="B172" s="15"/>
-      <c r="L172" s="22"/>
+      <c r="L172" s="23"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="15"/>
       <c r="B173" s="15"/>
-      <c r="L173" s="22"/>
+      <c r="L173" s="23"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="15"/>
       <c r="B174" s="15"/>
-      <c r="L174" s="22"/>
+      <c r="L174" s="23"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="15"/>
       <c r="B175" s="15"/>
-      <c r="L175" s="22"/>
+      <c r="L175" s="23"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="15"/>
       <c r="B176" s="15"/>
-      <c r="L176" s="22"/>
+      <c r="L176" s="23"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="15"/>
       <c r="B177" s="15"/>
-      <c r="L177" s="22"/>
+      <c r="L177" s="23"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="15"/>
       <c r="B178" s="15"/>
-      <c r="L178" s="22"/>
+      <c r="L178" s="23"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="15"/>
       <c r="B179" s="15"/>
-      <c r="L179" s="22"/>
+      <c r="L179" s="23"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="15"/>
       <c r="B180" s="15"/>
-      <c r="L180" s="22"/>
+      <c r="L180" s="23"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="15"/>
       <c r="B181" s="15"/>
-      <c r="L181" s="22"/>
+      <c r="L181" s="23"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="15"/>
       <c r="B182" s="15"/>
-      <c r="L182" s="22"/>
+      <c r="L182" s="23"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="15"/>
       <c r="B183" s="15"/>
-      <c r="L183" s="22"/>
+      <c r="L183" s="23"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="15"/>
       <c r="B184" s="15"/>
-      <c r="L184" s="22"/>
+      <c r="L184" s="23"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="15"/>
       <c r="B185" s="15"/>
-      <c r="L185" s="22"/>
+      <c r="L185" s="23"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="15"/>
       <c r="B186" s="15"/>
-      <c r="L186" s="22"/>
+      <c r="L186" s="23"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="15"/>
       <c r="B187" s="15"/>
-      <c r="L187" s="22"/>
+      <c r="L187" s="23"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="15"/>
       <c r="B188" s="15"/>
-      <c r="L188" s="22"/>
+      <c r="L188" s="23"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="15"/>
       <c r="B189" s="15"/>
-      <c r="L189" s="22"/>
+      <c r="L189" s="23"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="15"/>
       <c r="B190" s="15"/>
-      <c r="L190" s="22"/>
+      <c r="L190" s="23"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="15"/>
       <c r="B191" s="15"/>
-      <c r="L191" s="22"/>
+      <c r="L191" s="23"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="15"/>
       <c r="B192" s="15"/>
-      <c r="L192" s="22"/>
+      <c r="L192" s="23"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="15"/>
       <c r="B193" s="15"/>
-      <c r="L193" s="22"/>
+      <c r="L193" s="23"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="15"/>
       <c r="B194" s="15"/>
-      <c r="L194" s="22"/>
+      <c r="L194" s="23"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="15"/>
       <c r="B195" s="15"/>
-      <c r="L195" s="22"/>
+      <c r="L195" s="23"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="15"/>
       <c r="B196" s="15"/>
-      <c r="L196" s="22"/>
+      <c r="L196" s="23"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="15"/>
       <c r="B197" s="15"/>
-      <c r="L197" s="22"/>
+      <c r="L197" s="23"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="15"/>
       <c r="B198" s="15"/>
-      <c r="L198" s="22"/>
+      <c r="L198" s="23"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="15"/>
       <c r="B199" s="15"/>
-      <c r="L199" s="22"/>
+      <c r="L199" s="23"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="15"/>
       <c r="B200" s="15"/>
-      <c r="L200" s="22"/>
+      <c r="L200" s="23"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="15"/>
       <c r="B201" s="15"/>
-      <c r="L201" s="22"/>
+      <c r="L201" s="23"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="15"/>
       <c r="B202" s="15"/>
-      <c r="L202" s="22"/>
+      <c r="L202" s="23"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="15"/>
       <c r="B203" s="15"/>
-      <c r="L203" s="22"/>
+      <c r="L203" s="23"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="15"/>
       <c r="B204" s="15"/>
-      <c r="L204" s="22"/>
+      <c r="L204" s="23"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="15"/>
       <c r="B205" s="15"/>
-      <c r="L205" s="22"/>
+      <c r="L205" s="23"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="15"/>
       <c r="B206" s="15"/>
-      <c r="L206" s="22"/>
+      <c r="L206" s="23"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="15"/>
       <c r="B207" s="15"/>
-      <c r="L207" s="22"/>
+      <c r="L207" s="23"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="15"/>
       <c r="B208" s="15"/>
-      <c r="L208" s="22"/>
+      <c r="L208" s="23"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="15"/>
       <c r="B209" s="15"/>
-      <c r="L209" s="22"/>
+      <c r="L209" s="23"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="15"/>
       <c r="B210" s="15"/>
-      <c r="L210" s="22"/>
+      <c r="L210" s="23"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="15"/>
       <c r="B211" s="15"/>
-      <c r="L211" s="22"/>
+      <c r="L211" s="23"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="15"/>
       <c r="B212" s="15"/>
-      <c r="L212" s="22"/>
+      <c r="L212" s="23"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="15"/>
       <c r="B213" s="15"/>
-      <c r="L213" s="22"/>
+      <c r="L213" s="23"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="15"/>
       <c r="B214" s="15"/>
-      <c r="L214" s="22"/>
+      <c r="L214" s="23"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="15"/>
       <c r="B215" s="15"/>
-      <c r="L215" s="22"/>
+      <c r="L215" s="23"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="15"/>
       <c r="B216" s="15"/>
-      <c r="L216" s="22"/>
+      <c r="L216" s="23"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="15"/>
       <c r="B217" s="15"/>
-      <c r="L217" s="22"/>
+      <c r="L217" s="23"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="15"/>
       <c r="B218" s="15"/>
-      <c r="L218" s="22"/>
+      <c r="L218" s="23"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="15"/>
       <c r="B219" s="15"/>
-      <c r="L219" s="22"/>
+      <c r="L219" s="23"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="15"/>
       <c r="B220" s="15"/>
-      <c r="L220" s="22"/>
+      <c r="L220" s="23"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="15"/>
       <c r="B221" s="15"/>
-      <c r="L221" s="22"/>
+      <c r="L221" s="23"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="15"/>
       <c r="B222" s="15"/>
-      <c r="L222" s="22"/>
+      <c r="L222" s="23"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="15"/>
       <c r="B223" s="15"/>
-      <c r="L223" s="22"/>
+      <c r="L223" s="23"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="15"/>
       <c r="B224" s="15"/>
-      <c r="L224" s="22"/>
+      <c r="L224" s="23"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="15"/>
       <c r="B225" s="15"/>
-      <c r="L225" s="22"/>
+      <c r="L225" s="23"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="15"/>
       <c r="B226" s="15"/>
-      <c r="L226" s="22"/>
+      <c r="L226" s="23"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
       <c r="A227" s="15"/>
       <c r="B227" s="15"/>
-      <c r="L227" s="22"/>
+      <c r="L227" s="23"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="15"/>
       <c r="B228" s="15"/>
-      <c r="L228" s="22"/>
+      <c r="L228" s="23"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="A229" s="15"/>
       <c r="B229" s="15"/>
-      <c r="L229" s="22"/>
+      <c r="L229" s="23"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="15"/>
       <c r="B230" s="15"/>
-      <c r="L230" s="22"/>
+      <c r="L230" s="23"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="15"/>
       <c r="B231" s="15"/>
-      <c r="L231" s="22"/>
+      <c r="L231" s="23"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="15"/>
       <c r="B232" s="15"/>
-      <c r="L232" s="22"/>
+      <c r="L232" s="23"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="15"/>
       <c r="B233" s="15"/>
-      <c r="L233" s="22"/>
+      <c r="L233" s="23"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="15"/>
       <c r="B234" s="15"/>
-      <c r="L234" s="22"/>
+      <c r="L234" s="23"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
       <c r="A235" s="15"/>
       <c r="B235" s="15"/>
-      <c r="L235" s="22"/>
+      <c r="L235" s="23"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
       <c r="A236" s="15"/>
       <c r="B236" s="15"/>
-      <c r="L236" s="22"/>
+      <c r="L236" s="23"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
       <c r="A237" s="15"/>
       <c r="B237" s="15"/>
-      <c r="L237" s="22"/>
+      <c r="L237" s="23"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="A238" s="15"/>
       <c r="B238" s="15"/>
-      <c r="L238" s="22"/>
+      <c r="L238" s="23"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
       <c r="A239" s="15"/>
       <c r="B239" s="15"/>
-      <c r="L239" s="22"/>
+      <c r="L239" s="23"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
       <c r="A240" s="15"/>
       <c r="B240" s="15"/>
-      <c r="L240" s="22"/>
+      <c r="L240" s="23"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
       <c r="A241" s="15"/>
       <c r="B241" s="15"/>
-      <c r="L241" s="22"/>
+      <c r="L241" s="23"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="A242" s="15"/>
       <c r="B242" s="15"/>
-      <c r="L242" s="22"/>
+      <c r="L242" s="23"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
       <c r="A243" s="15"/>
       <c r="B243" s="15"/>
-      <c r="L243" s="22"/>
+      <c r="L243" s="23"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
       <c r="A244" s="15"/>
       <c r="B244" s="15"/>
-      <c r="L244" s="22"/>
+      <c r="L244" s="23"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="A245" s="15"/>
       <c r="B245" s="15"/>
-      <c r="L245" s="22"/>
+      <c r="L245" s="23"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="A246" s="15"/>
       <c r="B246" s="15"/>
-      <c r="L246" s="22"/>
+      <c r="L246" s="23"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
       <c r="A247" s="15"/>
       <c r="B247" s="15"/>
-      <c r="L247" s="22"/>
+      <c r="L247" s="23"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
       <c r="A248" s="15"/>
       <c r="B248" s="15"/>
-      <c r="L248" s="22"/>
+      <c r="L248" s="23"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
       <c r="A249" s="15"/>
       <c r="B249" s="15"/>
-      <c r="L249" s="22"/>
+      <c r="L249" s="23"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="A250" s="15"/>
       <c r="B250" s="15"/>
-      <c r="L250" s="22"/>
+      <c r="L250" s="23"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
       <c r="A251" s="15"/>
       <c r="B251" s="15"/>
-      <c r="L251" s="22"/>
+      <c r="L251" s="23"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
       <c r="A252" s="15"/>
       <c r="B252" s="15"/>
-      <c r="L252" s="22"/>
+      <c r="L252" s="23"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
       <c r="A253" s="15"/>
       <c r="B253" s="15"/>
-      <c r="L253" s="22"/>
+      <c r="L253" s="23"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="A254" s="15"/>
       <c r="B254" s="15"/>
-      <c r="L254" s="22"/>
+      <c r="L254" s="23"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
       <c r="A255" s="15"/>
       <c r="B255" s="15"/>
-      <c r="L255" s="22"/>
+      <c r="L255" s="23"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
       <c r="A256" s="15"/>
       <c r="B256" s="15"/>
-      <c r="L256" s="22"/>
+      <c r="L256" s="23"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="A257" s="15"/>
       <c r="B257" s="15"/>
-      <c r="L257" s="22"/>
+      <c r="L257" s="23"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="A258" s="15"/>
       <c r="B258" s="15"/>
-      <c r="L258" s="22"/>
+      <c r="L258" s="23"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
       <c r="A259" s="15"/>
       <c r="B259" s="15"/>
-      <c r="L259" s="22"/>
+      <c r="L259" s="23"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
       <c r="A260" s="15"/>
       <c r="B260" s="15"/>
-      <c r="L260" s="22"/>
+      <c r="L260" s="23"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="A261" s="15"/>
       <c r="B261" s="15"/>
-      <c r="L261" s="22"/>
+      <c r="L261" s="23"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="A262" s="15"/>
       <c r="B262" s="15"/>
-      <c r="L262" s="22"/>
+      <c r="L262" s="23"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
       <c r="A263" s="15"/>
       <c r="B263" s="15"/>
-      <c r="L263" s="22"/>
+      <c r="L263" s="23"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
       <c r="A264" s="15"/>
       <c r="B264" s="15"/>
-      <c r="L264" s="22"/>
+      <c r="L264" s="23"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="A265" s="15"/>
       <c r="B265" s="15"/>
-      <c r="L265" s="22"/>
+      <c r="L265" s="23"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="A266" s="15"/>
       <c r="B266" s="15"/>
-      <c r="L266" s="22"/>
+      <c r="L266" s="23"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
       <c r="A267" s="15"/>
       <c r="B267" s="15"/>
-      <c r="L267" s="22"/>
+      <c r="L267" s="23"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
       <c r="A268" s="15"/>
       <c r="B268" s="15"/>
-      <c r="L268" s="22"/>
+      <c r="L268" s="23"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="A269" s="15"/>
       <c r="B269" s="15"/>
-      <c r="L269" s="22"/>
+      <c r="L269" s="23"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="A270" s="15"/>
       <c r="B270" s="15"/>
-      <c r="L270" s="22"/>
+      <c r="L270" s="23"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
       <c r="A271" s="15"/>
       <c r="B271" s="15"/>
-      <c r="L271" s="22"/>
+      <c r="L271" s="23"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
       <c r="A272" s="15"/>
       <c r="B272" s="15"/>
-      <c r="L272" s="22"/>
+      <c r="L272" s="23"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="A273" s="15"/>
       <c r="B273" s="15"/>
-      <c r="L273" s="22"/>
+      <c r="L273" s="23"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="A274" s="15"/>
       <c r="B274" s="15"/>
-      <c r="L274" s="22"/>
+      <c r="L274" s="23"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
       <c r="A275" s="15"/>
       <c r="B275" s="15"/>
-      <c r="L275" s="22"/>
+      <c r="L275" s="23"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
       <c r="A276" s="15"/>
       <c r="B276" s="15"/>
-      <c r="L276" s="22"/>
+      <c r="L276" s="23"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
       <c r="A277" s="15"/>
       <c r="B277" s="15"/>
-      <c r="L277" s="22"/>
+      <c r="L277" s="23"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="A278" s="15"/>
       <c r="B278" s="15"/>
-      <c r="L278" s="22"/>
+      <c r="L278" s="23"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
       <c r="A279" s="15"/>
       <c r="B279" s="15"/>
-      <c r="L279" s="22"/>
+      <c r="L279" s="23"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
       <c r="A280" s="15"/>
       <c r="B280" s="15"/>
-      <c r="L280" s="22"/>
+      <c r="L280" s="23"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
       <c r="A281" s="15"/>
       <c r="B281" s="15"/>
-      <c r="L281" s="22"/>
+      <c r="L281" s="23"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="A282" s="15"/>
       <c r="B282" s="15"/>
-      <c r="L282" s="22"/>
+      <c r="L282" s="23"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
       <c r="A283" s="15"/>
       <c r="B283" s="15"/>
-      <c r="L283" s="22"/>
+      <c r="L283" s="23"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
       <c r="A284" s="15"/>
       <c r="B284" s="15"/>
-      <c r="L284" s="22"/>
+      <c r="L284" s="23"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
       <c r="A285" s="15"/>
       <c r="B285" s="15"/>
-      <c r="L285" s="22"/>
+      <c r="L285" s="23"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="A286" s="15"/>
       <c r="B286" s="15"/>
-      <c r="L286" s="22"/>
+      <c r="L286" s="23"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
       <c r="A287" s="15"/>
       <c r="B287" s="15"/>
-      <c r="L287" s="22"/>
+      <c r="L287" s="23"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
       <c r="A288" s="15"/>
       <c r="B288" s="15"/>
-      <c r="L288" s="22"/>
+      <c r="L288" s="23"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="A289" s="15"/>
       <c r="B289" s="15"/>
-      <c r="L289" s="22"/>
+      <c r="L289" s="23"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="A290" s="15"/>
       <c r="B290" s="15"/>
-      <c r="L290" s="22"/>
+      <c r="L290" s="23"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
       <c r="A291" s="15"/>
       <c r="B291" s="15"/>
-      <c r="L291" s="22"/>
+      <c r="L291" s="23"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
       <c r="A292" s="15"/>
       <c r="B292" s="15"/>
-      <c r="L292" s="22"/>
+      <c r="L292" s="23"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
       <c r="A293" s="15"/>
       <c r="B293" s="15"/>
-      <c r="L293" s="22"/>
+      <c r="L293" s="23"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
       <c r="A294" s="15"/>
       <c r="B294" s="15"/>
-      <c r="L294" s="22"/>
+      <c r="L294" s="23"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
       <c r="A295" s="15"/>
       <c r="B295" s="15"/>
-      <c r="L295" s="22"/>
+      <c r="L295" s="23"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
       <c r="A296" s="15"/>
       <c r="B296" s="15"/>
-      <c r="L296" s="22"/>
+      <c r="L296" s="23"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
       <c r="A297" s="15"/>
       <c r="B297" s="15"/>
-      <c r="L297" s="22"/>
+      <c r="L297" s="23"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="A298" s="15"/>
       <c r="B298" s="15"/>
-      <c r="L298" s="22"/>
+      <c r="L298" s="23"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
       <c r="A299" s="15"/>
       <c r="B299" s="15"/>
-      <c r="L299" s="22"/>
+      <c r="L299" s="23"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
       <c r="A300" s="15"/>
       <c r="B300" s="15"/>
-      <c r="L300" s="22"/>
+      <c r="L300" s="23"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
       <c r="A301" s="15"/>
       <c r="B301" s="15"/>
-      <c r="L301" s="22"/>
+      <c r="L301" s="23"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="A302" s="15"/>
       <c r="B302" s="15"/>
-      <c r="L302" s="22"/>
+      <c r="L302" s="23"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
       <c r="A303" s="15"/>
       <c r="B303" s="15"/>
-      <c r="L303" s="22"/>
+      <c r="L303" s="23"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
       <c r="A304" s="15"/>
       <c r="B304" s="15"/>
-      <c r="L304" s="22"/>
+      <c r="L304" s="23"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
       <c r="A305" s="15"/>
       <c r="B305" s="15"/>
-      <c r="L305" s="22"/>
+      <c r="L305" s="23"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="A306" s="15"/>
       <c r="B306" s="15"/>
-      <c r="L306" s="22"/>
+      <c r="L306" s="23"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
       <c r="A307" s="15"/>
       <c r="B307" s="15"/>
-      <c r="L307" s="22"/>
+      <c r="L307" s="23"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
       <c r="A308" s="15"/>
       <c r="B308" s="15"/>
-      <c r="L308" s="22"/>
+      <c r="L308" s="23"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
       <c r="A309" s="15"/>
       <c r="B309" s="15"/>
-      <c r="L309" s="22"/>
+      <c r="L309" s="23"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="A310" s="15"/>
       <c r="B310" s="15"/>
-      <c r="L310" s="22"/>
+      <c r="L310" s="23"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
       <c r="A311" s="15"/>
       <c r="B311" s="15"/>
-      <c r="L311" s="22"/>
+      <c r="L311" s="23"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
       <c r="A312" s="15"/>
       <c r="B312" s="15"/>
-      <c r="L312" s="22"/>
+      <c r="L312" s="23"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
       <c r="A313" s="15"/>
       <c r="B313" s="15"/>
-      <c r="L313" s="22"/>
+      <c r="L313" s="23"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="A314" s="15"/>
       <c r="B314" s="15"/>
-      <c r="L314" s="22"/>
+      <c r="L314" s="23"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
       <c r="A315" s="15"/>
       <c r="B315" s="15"/>
-      <c r="L315" s="22"/>
+      <c r="L315" s="23"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="A316" s="15"/>
       <c r="B316" s="15"/>
-      <c r="L316" s="22"/>
+      <c r="L316" s="23"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="A317" s="15"/>
       <c r="B317" s="15"/>
-      <c r="L317" s="22"/>
+      <c r="L317" s="23"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="A318" s="15"/>
       <c r="B318" s="15"/>
-      <c r="L318" s="22"/>
+      <c r="L318" s="23"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
       <c r="A319" s="15"/>
       <c r="B319" s="15"/>
-      <c r="L319" s="22"/>
+      <c r="L319" s="23"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="A320" s="15"/>
       <c r="B320" s="15"/>
-      <c r="L320" s="22"/>
+      <c r="L320" s="23"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="A321" s="15"/>
       <c r="B321" s="15"/>
-      <c r="L321" s="22"/>
+      <c r="L321" s="23"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="A322" s="15"/>
       <c r="B322" s="15"/>
-      <c r="L322" s="22"/>
+      <c r="L322" s="23"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
       <c r="A323" s="15"/>
       <c r="B323" s="15"/>
-      <c r="L323" s="22"/>
+      <c r="L323" s="23"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="A324" s="15"/>
       <c r="B324" s="15"/>
-      <c r="L324" s="22"/>
+      <c r="L324" s="23"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="A325" s="15"/>
       <c r="B325" s="15"/>
-      <c r="L325" s="22"/>
+      <c r="L325" s="23"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="A326" s="15"/>
       <c r="B326" s="15"/>
-      <c r="L326" s="22"/>
+      <c r="L326" s="23"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
       <c r="A327" s="15"/>
       <c r="B327" s="15"/>
-      <c r="L327" s="22"/>
+      <c r="L327" s="23"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="A328" s="15"/>
       <c r="B328" s="15"/>
-      <c r="L328" s="22"/>
+      <c r="L328" s="23"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="A329" s="15"/>
       <c r="B329" s="15"/>
-      <c r="L329" s="22"/>
+      <c r="L329" s="23"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="A330" s="15"/>
       <c r="B330" s="15"/>
-      <c r="L330" s="22"/>
+      <c r="L330" s="23"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
       <c r="A331" s="15"/>
       <c r="B331" s="15"/>
-      <c r="L331" s="22"/>
+      <c r="L331" s="23"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="A332" s="15"/>
       <c r="B332" s="15"/>
-      <c r="L332" s="22"/>
+      <c r="L332" s="23"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="A333" s="15"/>
       <c r="B333" s="15"/>
-      <c r="L333" s="22"/>
+      <c r="L333" s="23"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="A334" s="15"/>
       <c r="B334" s="15"/>
-      <c r="L334" s="22"/>
+      <c r="L334" s="23"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
       <c r="A335" s="15"/>
       <c r="B335" s="15"/>
-      <c r="L335" s="22"/>
+      <c r="L335" s="23"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="A336" s="15"/>
       <c r="B336" s="15"/>
-      <c r="L336" s="22"/>
+      <c r="L336" s="23"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="A337" s="15"/>
       <c r="B337" s="15"/>
-      <c r="L337" s="22"/>
+      <c r="L337" s="23"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="A338" s="15"/>
       <c r="B338" s="15"/>
-      <c r="L338" s="22"/>
+      <c r="L338" s="23"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
       <c r="A339" s="15"/>
       <c r="B339" s="15"/>
-      <c r="L339" s="22"/>
+      <c r="L339" s="23"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="A340" s="15"/>
       <c r="B340" s="15"/>
-      <c r="L340" s="22"/>
+      <c r="L340" s="23"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="A341" s="15"/>
       <c r="B341" s="15"/>
-      <c r="L341" s="22"/>
+      <c r="L341" s="23"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="A342" s="15"/>
       <c r="B342" s="15"/>
-      <c r="L342" s="22"/>
+      <c r="L342" s="23"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
       <c r="A343" s="15"/>
       <c r="B343" s="15"/>
-      <c r="L343" s="22"/>
+      <c r="L343" s="23"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="A344" s="15"/>
       <c r="B344" s="15"/>
-      <c r="L344" s="22"/>
+      <c r="L344" s="23"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="A345" s="15"/>
       <c r="B345" s="15"/>
-      <c r="L345" s="22"/>
+      <c r="L345" s="23"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="A346" s="15"/>
       <c r="B346" s="15"/>
-      <c r="L346" s="22"/>
+      <c r="L346" s="23"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
       <c r="A347" s="15"/>
       <c r="B347" s="15"/>
-      <c r="L347" s="22"/>
+      <c r="L347" s="23"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="A348" s="15"/>
       <c r="B348" s="15"/>
-      <c r="L348" s="22"/>
+      <c r="L348" s="23"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="A349" s="15"/>
       <c r="B349" s="15"/>
-      <c r="L349" s="22"/>
+      <c r="L349" s="23"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="A350" s="15"/>
       <c r="B350" s="15"/>
-      <c r="L350" s="22"/>
+      <c r="L350" s="23"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
       <c r="A351" s="15"/>
       <c r="B351" s="15"/>
-      <c r="L351" s="22"/>
+      <c r="L351" s="23"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="A352" s="15"/>
       <c r="B352" s="15"/>
-      <c r="L352" s="22"/>
+      <c r="L352" s="23"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="A353" s="15"/>
       <c r="B353" s="15"/>
-      <c r="L353" s="22"/>
+      <c r="L353" s="23"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="A354" s="15"/>
       <c r="B354" s="15"/>
-      <c r="L354" s="22"/>
+      <c r="L354" s="23"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
       <c r="A355" s="15"/>
       <c r="B355" s="15"/>
-      <c r="L355" s="22"/>
+      <c r="L355" s="23"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="A356" s="15"/>
       <c r="B356" s="15"/>
-      <c r="L356" s="22"/>
+      <c r="L356" s="23"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="A357" s="15"/>
       <c r="B357" s="15"/>
-      <c r="L357" s="22"/>
+      <c r="L357" s="23"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="A358" s="15"/>
       <c r="B358" s="15"/>
-      <c r="L358" s="22"/>
+      <c r="L358" s="23"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="A359" s="15"/>
       <c r="B359" s="15"/>
-      <c r="L359" s="22"/>
+      <c r="L359" s="23"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="A360" s="15"/>
       <c r="B360" s="15"/>
-      <c r="L360" s="22"/>
+      <c r="L360" s="23"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="A361" s="15"/>
       <c r="B361" s="15"/>
-      <c r="L361" s="22"/>
+      <c r="L361" s="23"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="A362" s="15"/>
       <c r="B362" s="15"/>
-      <c r="L362" s="22"/>
+      <c r="L362" s="23"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
       <c r="A363" s="15"/>
       <c r="B363" s="15"/>
-      <c r="L363" s="22"/>
+      <c r="L363" s="23"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="A364" s="15"/>
       <c r="B364" s="15"/>
-      <c r="L364" s="22"/>
+      <c r="L364" s="23"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="A365" s="15"/>
       <c r="B365" s="15"/>
-      <c r="L365" s="22"/>
+      <c r="L365" s="23"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="A366" s="15"/>
       <c r="B366" s="15"/>
-      <c r="L366" s="22"/>
+      <c r="L366" s="23"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="A367" s="15"/>
       <c r="B367" s="15"/>
-      <c r="L367" s="22"/>
+      <c r="L367" s="23"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="A368" s="15"/>
       <c r="B368" s="15"/>
-      <c r="L368" s="22"/>
+      <c r="L368" s="23"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="A369" s="15"/>
       <c r="B369" s="15"/>
-      <c r="L369" s="22"/>
+      <c r="L369" s="23"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="A370" s="15"/>
       <c r="B370" s="15"/>
-      <c r="L370" s="22"/>
+      <c r="L370" s="23"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
       <c r="A371" s="15"/>
       <c r="B371" s="15"/>
-      <c r="L371" s="22"/>
+      <c r="L371" s="23"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="A372" s="15"/>
       <c r="B372" s="15"/>
-      <c r="L372" s="22"/>
+      <c r="L372" s="23"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="A373" s="15"/>
       <c r="B373" s="15"/>
-      <c r="L373" s="22"/>
+      <c r="L373" s="23"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="A374" s="15"/>
       <c r="B374" s="15"/>
-      <c r="L374" s="22"/>
+      <c r="L374" s="23"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="A375" s="15"/>
       <c r="B375" s="15"/>
-      <c r="L375" s="22"/>
+      <c r="L375" s="23"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="A376" s="15"/>
       <c r="B376" s="15"/>
-      <c r="L376" s="22"/>
+      <c r="L376" s="23"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="A377" s="15"/>
       <c r="B377" s="15"/>
-      <c r="L377" s="22"/>
+      <c r="L377" s="23"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="A378" s="15"/>
       <c r="B378" s="15"/>
-      <c r="L378" s="22"/>
+      <c r="L378" s="23"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="A379" s="15"/>
       <c r="B379" s="15"/>
-      <c r="L379" s="22"/>
+      <c r="L379" s="23"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="A380" s="15"/>
       <c r="B380" s="15"/>
-      <c r="L380" s="22"/>
+      <c r="L380" s="23"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="A381" s="15"/>
       <c r="B381" s="15"/>
-      <c r="L381" s="22"/>
+      <c r="L381" s="23"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="A382" s="15"/>
       <c r="B382" s="15"/>
-      <c r="L382" s="22"/>
+      <c r="L382" s="23"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
       <c r="A383" s="15"/>
       <c r="B383" s="15"/>
-      <c r="L383" s="22"/>
+      <c r="L383" s="23"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="A384" s="15"/>
       <c r="B384" s="15"/>
-      <c r="L384" s="22"/>
+      <c r="L384" s="23"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="A385" s="15"/>
       <c r="B385" s="15"/>
-      <c r="L385" s="22"/>
+      <c r="L385" s="23"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="A386" s="15"/>
       <c r="B386" s="15"/>
-      <c r="L386" s="22"/>
+      <c r="L386" s="23"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
       <c r="A387" s="15"/>
       <c r="B387" s="15"/>
-      <c r="L387" s="22"/>
+      <c r="L387" s="23"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
       <c r="A388" s="15"/>
       <c r="B388" s="15"/>
-      <c r="L388" s="22"/>
+      <c r="L388" s="23"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
       <c r="A389" s="15"/>
       <c r="B389" s="15"/>
-      <c r="L389" s="22"/>
+      <c r="L389" s="23"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
       <c r="A390" s="15"/>
       <c r="B390" s="15"/>
-      <c r="L390" s="22"/>
+      <c r="L390" s="23"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
       <c r="A391" s="15"/>
       <c r="B391" s="15"/>
-      <c r="L391" s="22"/>
+      <c r="L391" s="23"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
       <c r="A392" s="15"/>
       <c r="B392" s="15"/>
-      <c r="L392" s="22"/>
+      <c r="L392" s="23"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
       <c r="A393" s="15"/>
       <c r="B393" s="15"/>
-      <c r="L393" s="22"/>
+      <c r="L393" s="23"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
       <c r="A394" s="15"/>
       <c r="B394" s="15"/>
-      <c r="L394" s="22"/>
+      <c r="L394" s="23"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
       <c r="A395" s="15"/>
       <c r="B395" s="15"/>
-      <c r="L395" s="22"/>
+      <c r="L395" s="23"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
       <c r="A396" s="15"/>
       <c r="B396" s="15"/>
-      <c r="L396" s="22"/>
+      <c r="L396" s="23"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
       <c r="A397" s="15"/>
       <c r="B397" s="15"/>
-      <c r="L397" s="22"/>
+      <c r="L397" s="23"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
       <c r="A398" s="15"/>
       <c r="B398" s="15"/>
-      <c r="L398" s="22"/>
+      <c r="L398" s="23"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
       <c r="A399" s="15"/>
       <c r="B399" s="15"/>
-      <c r="L399" s="22"/>
+      <c r="L399" s="23"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
       <c r="A400" s="15"/>
       <c r="B400" s="15"/>
-      <c r="L400" s="22"/>
+      <c r="L400" s="23"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
       <c r="A401" s="15"/>
       <c r="B401" s="15"/>
-      <c r="L401" s="22"/>
+      <c r="L401" s="23"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
       <c r="A402" s="15"/>
       <c r="B402" s="15"/>
-      <c r="L402" s="22"/>
+      <c r="L402" s="23"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
       <c r="A403" s="15"/>
       <c r="B403" s="15"/>
-      <c r="L403" s="22"/>
+      <c r="L403" s="23"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
       <c r="A404" s="15"/>
       <c r="B404" s="15"/>
-      <c r="L404" s="22"/>
+      <c r="L404" s="23"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
       <c r="A405" s="15"/>
       <c r="B405" s="15"/>
-      <c r="L405" s="22"/>
+      <c r="L405" s="23"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
       <c r="A406" s="15"/>
       <c r="B406" s="15"/>
-      <c r="L406" s="22"/>
+      <c r="L406" s="23"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
       <c r="A407" s="15"/>
       <c r="B407" s="15"/>
-      <c r="L407" s="22"/>
+      <c r="L407" s="23"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="A408" s="15"/>
       <c r="B408" s="15"/>
-      <c r="L408" s="22"/>
+      <c r="L408" s="23"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
       <c r="A409" s="15"/>
       <c r="B409" s="15"/>
-      <c r="L409" s="22"/>
+      <c r="L409" s="23"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="A410" s="15"/>
       <c r="B410" s="15"/>
-      <c r="L410" s="22"/>
+      <c r="L410" s="23"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
       <c r="A411" s="15"/>
       <c r="B411" s="15"/>
-      <c r="L411" s="22"/>
+      <c r="L411" s="23"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
       <c r="A412" s="15"/>
       <c r="B412" s="15"/>
-      <c r="L412" s="22"/>
+      <c r="L412" s="23"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
       <c r="A413" s="15"/>
       <c r="B413" s="15"/>
-      <c r="L413" s="22"/>
+      <c r="L413" s="23"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
       <c r="A414" s="15"/>
       <c r="B414" s="15"/>
-      <c r="L414" s="22"/>
+      <c r="L414" s="23"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
       <c r="A415" s="15"/>
       <c r="B415" s="15"/>
-      <c r="L415" s="22"/>
+      <c r="L415" s="23"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="A416" s="15"/>
       <c r="B416" s="15"/>
-      <c r="L416" s="22"/>
+      <c r="L416" s="23"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
       <c r="A417" s="15"/>
       <c r="B417" s="15"/>
-      <c r="L417" s="22"/>
+      <c r="L417" s="23"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="A418" s="15"/>
       <c r="B418" s="15"/>
-      <c r="L418" s="22"/>
+      <c r="L418" s="23"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
       <c r="A419" s="15"/>
       <c r="B419" s="15"/>
-      <c r="L419" s="22"/>
+      <c r="L419" s="23"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
       <c r="A420" s="15"/>
       <c r="B420" s="15"/>
-      <c r="L420" s="22"/>
+      <c r="L420" s="23"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
       <c r="A421" s="15"/>
       <c r="B421" s="15"/>
-      <c r="L421" s="22"/>
+      <c r="L421" s="23"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
       <c r="A422" s="15"/>
       <c r="B422" s="15"/>
-      <c r="L422" s="22"/>
+      <c r="L422" s="23"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
       <c r="A423" s="15"/>
       <c r="B423" s="15"/>
-      <c r="L423" s="22"/>
+      <c r="L423" s="23"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
       <c r="A424" s="15"/>
       <c r="B424" s="15"/>
-      <c r="L424" s="22"/>
+      <c r="L424" s="23"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
       <c r="A425" s="15"/>
       <c r="B425" s="15"/>
-      <c r="L425" s="22"/>
+      <c r="L425" s="23"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
       <c r="A426" s="15"/>
       <c r="B426" s="15"/>
-      <c r="L426" s="22"/>
+      <c r="L426" s="23"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="A427" s="15"/>
       <c r="B427" s="15"/>
-      <c r="L427" s="22"/>
+      <c r="L427" s="23"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="A428" s="15"/>
       <c r="B428" s="15"/>
-      <c r="L428" s="22"/>
+      <c r="L428" s="23"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="A429" s="15"/>
       <c r="B429" s="15"/>
-      <c r="L429" s="22"/>
+      <c r="L429" s="23"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="A430" s="15"/>
       <c r="B430" s="15"/>
-      <c r="L430" s="22"/>
+      <c r="L430" s="23"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="A431" s="15"/>
       <c r="B431" s="15"/>
-      <c r="L431" s="22"/>
+      <c r="L431" s="23"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="A432" s="15"/>
       <c r="B432" s="15"/>
-      <c r="L432" s="22"/>
+      <c r="L432" s="23"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="A433" s="15"/>
       <c r="B433" s="15"/>
-      <c r="L433" s="22"/>
+      <c r="L433" s="23"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="A434" s="15"/>
       <c r="B434" s="15"/>
-      <c r="L434" s="22"/>
+      <c r="L434" s="23"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="A435" s="15"/>
       <c r="B435" s="15"/>
-      <c r="L435" s="22"/>
+      <c r="L435" s="23"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="A436" s="15"/>
       <c r="B436" s="15"/>
-      <c r="L436" s="22"/>
+      <c r="L436" s="23"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="A437" s="15"/>
       <c r="B437" s="15"/>
-      <c r="L437" s="22"/>
+      <c r="L437" s="23"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="A438" s="15"/>
       <c r="B438" s="15"/>
-      <c r="L438" s="22"/>
+      <c r="L438" s="23"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
       <c r="A439" s="15"/>
       <c r="B439" s="15"/>
-      <c r="L439" s="22"/>
+      <c r="L439" s="23"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="A440" s="15"/>
       <c r="B440" s="15"/>
-      <c r="L440" s="22"/>
+      <c r="L440" s="23"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="A441" s="15"/>
       <c r="B441" s="15"/>
-      <c r="L441" s="22"/>
+      <c r="L441" s="23"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="A442" s="15"/>
       <c r="B442" s="15"/>
-      <c r="L442" s="22"/>
+      <c r="L442" s="23"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
       <c r="A443" s="15"/>
       <c r="B443" s="15"/>
-      <c r="L443" s="22"/>
+      <c r="L443" s="23"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="A444" s="15"/>
       <c r="B444" s="15"/>
-      <c r="L444" s="22"/>
+      <c r="L444" s="23"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="A445" s="15"/>
       <c r="B445" s="15"/>
-      <c r="L445" s="22"/>
+      <c r="L445" s="23"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="A446" s="15"/>
       <c r="B446" s="15"/>
-      <c r="L446" s="22"/>
+      <c r="L446" s="23"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="A447" s="15"/>
       <c r="B447" s="15"/>
-      <c r="L447" s="22"/>
+      <c r="L447" s="23"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="A448" s="15"/>
       <c r="B448" s="15"/>
-      <c r="L448" s="22"/>
+      <c r="L448" s="23"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="A449" s="15"/>
       <c r="B449" s="15"/>
-      <c r="L449" s="22"/>
+      <c r="L449" s="23"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="A450" s="15"/>
       <c r="B450" s="15"/>
-      <c r="L450" s="22"/>
+      <c r="L450" s="23"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="A451" s="15"/>
       <c r="B451" s="15"/>
-      <c r="L451" s="22"/>
+      <c r="L451" s="23"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="A452" s="15"/>
       <c r="B452" s="15"/>
-      <c r="L452" s="22"/>
+      <c r="L452" s="23"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="A453" s="15"/>
       <c r="B453" s="15"/>
-      <c r="L453" s="22"/>
+      <c r="L453" s="23"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="A454" s="15"/>
       <c r="B454" s="15"/>
-      <c r="L454" s="22"/>
+      <c r="L454" s="23"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="A455" s="15"/>
       <c r="B455" s="15"/>
-      <c r="L455" s="22"/>
+      <c r="L455" s="23"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="A456" s="15"/>
       <c r="B456" s="15"/>
-      <c r="L456" s="22"/>
+      <c r="L456" s="23"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="A457" s="15"/>
       <c r="B457" s="15"/>
-      <c r="L457" s="22"/>
+      <c r="L457" s="23"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="A458" s="15"/>
       <c r="B458" s="15"/>
-      <c r="L458" s="22"/>
+      <c r="L458" s="23"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="A459" s="15"/>
       <c r="B459" s="15"/>
-      <c r="L459" s="22"/>
+      <c r="L459" s="23"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="A460" s="15"/>
       <c r="B460" s="15"/>
-      <c r="L460" s="22"/>
+      <c r="L460" s="23"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="A461" s="15"/>
       <c r="B461" s="15"/>
-      <c r="L461" s="22"/>
+      <c r="L461" s="23"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="A462" s="15"/>
       <c r="B462" s="15"/>
-      <c r="L462" s="22"/>
+      <c r="L462" s="23"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
       <c r="A463" s="15"/>
       <c r="B463" s="15"/>
-      <c r="L463" s="22"/>
+      <c r="L463" s="23"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="A464" s="15"/>
       <c r="B464" s="15"/>
-      <c r="L464" s="22"/>
+      <c r="L464" s="23"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="A465" s="15"/>
       <c r="B465" s="15"/>
-      <c r="L465" s="22"/>
+      <c r="L465" s="23"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="A466" s="15"/>
       <c r="B466" s="15"/>
-      <c r="L466" s="22"/>
+      <c r="L466" s="23"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="A467" s="15"/>
       <c r="B467" s="15"/>
-      <c r="L467" s="22"/>
+      <c r="L467" s="23"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="A468" s="15"/>
       <c r="B468" s="15"/>
-      <c r="L468" s="22"/>
+      <c r="L468" s="23"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="A469" s="15"/>
       <c r="B469" s="15"/>
-      <c r="L469" s="22"/>
+      <c r="L469" s="23"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="A470" s="15"/>
       <c r="B470" s="15"/>
-      <c r="L470" s="22"/>
+      <c r="L470" s="23"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
       <c r="A471" s="15"/>
       <c r="B471" s="15"/>
-      <c r="L471" s="22"/>
+      <c r="L471" s="23"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="A472" s="15"/>
       <c r="B472" s="15"/>
-      <c r="L472" s="22"/>
+      <c r="L472" s="23"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="A473" s="15"/>
       <c r="B473" s="15"/>
-      <c r="L473" s="22"/>
+      <c r="L473" s="23"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="A474" s="15"/>
       <c r="B474" s="15"/>
-      <c r="L474" s="22"/>
+      <c r="L474" s="23"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
       <c r="A475" s="15"/>
       <c r="B475" s="15"/>
-      <c r="L475" s="22"/>
+      <c r="L475" s="23"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="A476" s="15"/>
       <c r="B476" s="15"/>
-      <c r="L476" s="22"/>
+      <c r="L476" s="23"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="A477" s="15"/>
       <c r="B477" s="15"/>
-      <c r="L477" s="22"/>
+      <c r="L477" s="23"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="A478" s="15"/>
       <c r="B478" s="15"/>
-      <c r="L478" s="22"/>
+      <c r="L478" s="23"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
       <c r="A479" s="15"/>
       <c r="B479" s="15"/>
-      <c r="L479" s="22"/>
+      <c r="L479" s="23"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="A480" s="15"/>
       <c r="B480" s="15"/>
-      <c r="L480" s="22"/>
+      <c r="L480" s="23"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="A481" s="15"/>
       <c r="B481" s="15"/>
-      <c r="L481" s="22"/>
+      <c r="L481" s="23"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="A482" s="15"/>
       <c r="B482" s="15"/>
-      <c r="L482" s="22"/>
+      <c r="L482" s="23"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="15"/>
       <c r="B483" s="15"/>
-      <c r="L483" s="22"/>
+      <c r="L483" s="23"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="A484" s="15"/>
       <c r="B484" s="15"/>
-      <c r="L484" s="22"/>
+      <c r="L484" s="23"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="A485" s="15"/>
       <c r="B485" s="15"/>
-      <c r="L485" s="22"/>
+      <c r="L485" s="23"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="A486" s="15"/>
       <c r="B486" s="15"/>
-      <c r="L486" s="22"/>
+      <c r="L486" s="23"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
       <c r="A487" s="15"/>
       <c r="B487" s="15"/>
-      <c r="L487" s="22"/>
+      <c r="L487" s="23"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="A488" s="15"/>
       <c r="B488" s="15"/>
-      <c r="L488" s="22"/>
+      <c r="L488" s="23"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="A489" s="15"/>
       <c r="B489" s="15"/>
-      <c r="L489" s="22"/>
+      <c r="L489" s="23"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="A490" s="15"/>
       <c r="B490" s="15"/>
-      <c r="L490" s="22"/>
+      <c r="L490" s="23"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
       <c r="A491" s="15"/>
       <c r="B491" s="15"/>
-      <c r="L491" s="22"/>
+      <c r="L491" s="23"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="A492" s="15"/>
       <c r="B492" s="15"/>
-      <c r="L492" s="22"/>
+      <c r="L492" s="23"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="A493" s="15"/>
       <c r="B493" s="15"/>
-      <c r="L493" s="22"/>
+      <c r="L493" s="23"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="A494" s="15"/>
       <c r="B494" s="15"/>
-      <c r="L494" s="22"/>
+      <c r="L494" s="23"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="A495" s="15"/>
       <c r="B495" s="15"/>
-      <c r="L495" s="22"/>
+      <c r="L495" s="23"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
       <c r="A496" s="15"/>
       <c r="B496" s="15"/>
-      <c r="L496" s="22"/>
+      <c r="L496" s="23"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
       <c r="A497" s="15"/>
       <c r="B497" s="15"/>
-      <c r="L497" s="22"/>
+      <c r="L497" s="23"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="A498" s="15"/>
       <c r="B498" s="15"/>
-      <c r="L498" s="22"/>
+      <c r="L498" s="23"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="A499" s="15"/>
       <c r="B499" s="15"/>
-      <c r="L499" s="22"/>
+      <c r="L499" s="23"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="A500" s="15"/>
       <c r="B500" s="15"/>
-      <c r="L500" s="22"/>
+      <c r="L500" s="23"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="A501" s="15"/>
       <c r="B501" s="15"/>
-      <c r="L501" s="22"/>
+      <c r="L501" s="23"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="A502" s="15"/>
       <c r="B502" s="15"/>
-      <c r="L502" s="22"/>
+      <c r="L502" s="23"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
       <c r="A503" s="15"/>
       <c r="B503" s="15"/>
-      <c r="L503" s="22"/>
+      <c r="L503" s="23"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="A504" s="15"/>
       <c r="B504" s="15"/>
-      <c r="L504" s="22"/>
+      <c r="L504" s="23"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="A505" s="15"/>
       <c r="B505" s="15"/>
-      <c r="L505" s="22"/>
+      <c r="L505" s="23"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="A506" s="15"/>
       <c r="B506" s="15"/>
-      <c r="L506" s="22"/>
+      <c r="L506" s="23"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="A507" s="15"/>
       <c r="B507" s="15"/>
-      <c r="L507" s="22"/>
+      <c r="L507" s="23"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="A508" s="15"/>
       <c r="B508" s="15"/>
-      <c r="L508" s="22"/>
+      <c r="L508" s="23"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="A509" s="15"/>
       <c r="B509" s="15"/>
-      <c r="L509" s="22"/>
+      <c r="L509" s="23"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="A510" s="15"/>
       <c r="B510" s="15"/>
-      <c r="L510" s="22"/>
+      <c r="L510" s="23"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="A511" s="15"/>
       <c r="B511" s="15"/>
-      <c r="L511" s="22"/>
+      <c r="L511" s="23"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="A512" s="15"/>
       <c r="B512" s="15"/>
-      <c r="L512" s="22"/>
+      <c r="L512" s="23"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="A513" s="15"/>
       <c r="B513" s="15"/>
-      <c r="L513" s="22"/>
+      <c r="L513" s="23"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="A514" s="15"/>
       <c r="B514" s="15"/>
-      <c r="L514" s="22"/>
+      <c r="L514" s="23"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="A515" s="15"/>
       <c r="B515" s="15"/>
-      <c r="L515" s="22"/>
+      <c r="L515" s="23"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="A516" s="15"/>
       <c r="B516" s="15"/>
-      <c r="L516" s="22"/>
+      <c r="L516" s="23"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="A517" s="15"/>
       <c r="B517" s="15"/>
-      <c r="L517" s="22"/>
+      <c r="L517" s="23"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="A518" s="15"/>
       <c r="B518" s="15"/>
-      <c r="L518" s="22"/>
+      <c r="L518" s="23"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="A519" s="15"/>
       <c r="B519" s="15"/>
-      <c r="L519" s="22"/>
+      <c r="L519" s="23"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="A520" s="15"/>
       <c r="B520" s="15"/>
-      <c r="L520" s="22"/>
+      <c r="L520" s="23"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="A521" s="15"/>
       <c r="B521" s="15"/>
-      <c r="L521" s="22"/>
+      <c r="L521" s="23"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="A522" s="15"/>
       <c r="B522" s="15"/>
-      <c r="L522" s="22"/>
+      <c r="L522" s="23"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="A523" s="15"/>
       <c r="B523" s="15"/>
-      <c r="L523" s="22"/>
+      <c r="L523" s="23"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
       <c r="A524" s="15"/>
       <c r="B524" s="15"/>
-      <c r="L524" s="22"/>
+      <c r="L524" s="23"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
       <c r="A525" s="15"/>
       <c r="B525" s="15"/>
-      <c r="L525" s="22"/>
+      <c r="L525" s="23"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="A526" s="15"/>
       <c r="B526" s="15"/>
-      <c r="L526" s="22"/>
+      <c r="L526" s="23"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="A527" s="15"/>
       <c r="B527" s="15"/>
-      <c r="L527" s="22"/>
+      <c r="L527" s="23"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
       <c r="A528" s="15"/>
       <c r="B528" s="15"/>
-      <c r="L528" s="22"/>
+      <c r="L528" s="23"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
       <c r="A529" s="15"/>
       <c r="B529" s="15"/>
-      <c r="L529" s="22"/>
+      <c r="L529" s="23"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="A530" s="15"/>
       <c r="B530" s="15"/>
-      <c r="L530" s="22"/>
+      <c r="L530" s="23"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="A531" s="15"/>
       <c r="B531" s="15"/>
-      <c r="L531" s="22"/>
+      <c r="L531" s="23"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
       <c r="A532" s="15"/>
       <c r="B532" s="15"/>
-      <c r="L532" s="22"/>
+      <c r="L532" s="23"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
       <c r="A533" s="15"/>
       <c r="B533" s="15"/>
-      <c r="L533" s="22"/>
+      <c r="L533" s="23"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
       <c r="A534" s="15"/>
       <c r="B534" s="15"/>
-      <c r="L534" s="22"/>
+      <c r="L534" s="23"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="A535" s="15"/>
       <c r="B535" s="15"/>
-      <c r="L535" s="22"/>
+      <c r="L535" s="23"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="A536" s="15"/>
       <c r="B536" s="15"/>
-      <c r="L536" s="22"/>
+      <c r="L536" s="23"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
       <c r="A537" s="15"/>
       <c r="B537" s="15"/>
-      <c r="L537" s="22"/>
+      <c r="L537" s="23"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
       <c r="A538" s="15"/>
       <c r="B538" s="15"/>
-      <c r="L538" s="22"/>
+      <c r="L538" s="23"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
       <c r="A539" s="15"/>
       <c r="B539" s="15"/>
-      <c r="L539" s="22"/>
+      <c r="L539" s="23"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
       <c r="A540" s="15"/>
       <c r="B540" s="15"/>
-      <c r="L540" s="22"/>
+      <c r="L540" s="23"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
       <c r="A541" s="15"/>
       <c r="B541" s="15"/>
-      <c r="L541" s="22"/>
+      <c r="L541" s="23"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
       <c r="A542" s="15"/>
       <c r="B542" s="15"/>
-      <c r="L542" s="22"/>
+      <c r="L542" s="23"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
       <c r="A543" s="15"/>
       <c r="B543" s="15"/>
-      <c r="L543" s="22"/>
+      <c r="L543" s="23"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="A544" s="15"/>
       <c r="B544" s="15"/>
-      <c r="L544" s="22"/>
+      <c r="L544" s="23"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="A545" s="15"/>
       <c r="B545" s="15"/>
-      <c r="L545" s="22"/>
+      <c r="L545" s="23"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="A546" s="15"/>
       <c r="B546" s="15"/>
-      <c r="L546" s="22"/>
+      <c r="L546" s="23"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="A547" s="15"/>
       <c r="B547" s="15"/>
-      <c r="L547" s="22"/>
+      <c r="L547" s="23"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="A548" s="15"/>
       <c r="B548" s="15"/>
-      <c r="L548" s="22"/>
+      <c r="L548" s="23"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="A549" s="15"/>
       <c r="B549" s="15"/>
-      <c r="L549" s="22"/>
+      <c r="L549" s="23"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="A550" s="15"/>
       <c r="B550" s="15"/>
-      <c r="L550" s="22"/>
+      <c r="L550" s="23"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="A551" s="15"/>
       <c r="B551" s="15"/>
-      <c r="L551" s="22"/>
+      <c r="L551" s="23"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="A552" s="15"/>
       <c r="B552" s="15"/>
-      <c r="L552" s="22"/>
+      <c r="L552" s="23"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="A553" s="15"/>
       <c r="B553" s="15"/>
-      <c r="L553" s="22"/>
+      <c r="L553" s="23"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="A554" s="15"/>
       <c r="B554" s="15"/>
-      <c r="L554" s="22"/>
+      <c r="L554" s="23"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="A555" s="15"/>
       <c r="B555" s="15"/>
-      <c r="L555" s="22"/>
+      <c r="L555" s="23"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="A556" s="15"/>
       <c r="B556" s="15"/>
-      <c r="L556" s="22"/>
+      <c r="L556" s="23"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="A557" s="15"/>
       <c r="B557" s="15"/>
-      <c r="L557" s="22"/>
+      <c r="L557" s="23"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="A558" s="15"/>
       <c r="B558" s="15"/>
-      <c r="L558" s="22"/>
+      <c r="L558" s="23"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="A559" s="15"/>
       <c r="B559" s="15"/>
-      <c r="L559" s="22"/>
+      <c r="L559" s="23"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="A560" s="15"/>
       <c r="B560" s="15"/>
-      <c r="L560" s="22"/>
+      <c r="L560" s="23"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="A561" s="15"/>
       <c r="B561" s="15"/>
-      <c r="L561" s="22"/>
+      <c r="L561" s="23"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="A562" s="15"/>
       <c r="B562" s="15"/>
-      <c r="L562" s="22"/>
+      <c r="L562" s="23"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
       <c r="A563" s="15"/>
       <c r="B563" s="15"/>
-      <c r="L563" s="22"/>
+      <c r="L563" s="23"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
       <c r="A564" s="15"/>
       <c r="B564" s="15"/>
-      <c r="L564" s="22"/>
+      <c r="L564" s="23"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
       <c r="A565" s="15"/>
       <c r="B565" s="15"/>
-      <c r="L565" s="22"/>
+      <c r="L565" s="23"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
       <c r="A566" s="15"/>
       <c r="B566" s="15"/>
-      <c r="L566" s="22"/>
+      <c r="L566" s="23"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
       <c r="A567" s="15"/>
       <c r="B567" s="15"/>
-      <c r="L567" s="22"/>
+      <c r="L567" s="23"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
       <c r="A568" s="15"/>
       <c r="B568" s="15"/>
-      <c r="L568" s="22"/>
+      <c r="L568" s="23"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
       <c r="A569" s="15"/>
       <c r="B569" s="15"/>
-      <c r="L569" s="22"/>
+      <c r="L569" s="23"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
       <c r="A570" s="15"/>
       <c r="B570" s="15"/>
-      <c r="L570" s="22"/>
+      <c r="L570" s="23"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
       <c r="A571" s="15"/>
       <c r="B571" s="15"/>
-      <c r="L571" s="22"/>
+      <c r="L571" s="23"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
       <c r="A572" s="15"/>
       <c r="B572" s="15"/>
-      <c r="L572" s="22"/>
+      <c r="L572" s="23"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
       <c r="A573" s="15"/>
       <c r="B573" s="15"/>
-      <c r="L573" s="22"/>
+      <c r="L573" s="23"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
       <c r="A574" s="15"/>
       <c r="B574" s="15"/>
-      <c r="L574" s="22"/>
+      <c r="L574" s="23"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
       <c r="A575" s="15"/>
       <c r="B575" s="15"/>
-      <c r="L575" s="22"/>
+      <c r="L575" s="23"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
       <c r="A576" s="15"/>
       <c r="B576" s="15"/>
-      <c r="L576" s="22"/>
+      <c r="L576" s="23"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
       <c r="A577" s="15"/>
       <c r="B577" s="15"/>
-      <c r="L577" s="22"/>
+      <c r="L577" s="23"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
       <c r="A578" s="15"/>
       <c r="B578" s="15"/>
-      <c r="L578" s="22"/>
+      <c r="L578" s="23"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
       <c r="A579" s="15"/>
       <c r="B579" s="15"/>
-      <c r="L579" s="22"/>
+      <c r="L579" s="23"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
       <c r="A580" s="15"/>
       <c r="B580" s="15"/>
-      <c r="L580" s="22"/>
+      <c r="L580" s="23"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
       <c r="A581" s="15"/>
       <c r="B581" s="15"/>
-      <c r="L581" s="22"/>
+      <c r="L581" s="23"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
       <c r="A582" s="15"/>
       <c r="B582" s="15"/>
-      <c r="L582" s="22"/>
+      <c r="L582" s="23"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
       <c r="A583" s="15"/>
       <c r="B583" s="15"/>
-      <c r="L583" s="22"/>
+      <c r="L583" s="23"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
       <c r="A584" s="15"/>
       <c r="B584" s="15"/>
-      <c r="L584" s="22"/>
+      <c r="L584" s="23"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
       <c r="A585" s="15"/>
       <c r="B585" s="15"/>
-      <c r="L585" s="22"/>
+      <c r="L585" s="23"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
       <c r="A586" s="15"/>
       <c r="B586" s="15"/>
-      <c r="L586" s="22"/>
+      <c r="L586" s="23"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="A587" s="15"/>
       <c r="B587" s="15"/>
-      <c r="L587" s="22"/>
+      <c r="L587" s="23"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="A588" s="15"/>
       <c r="B588" s="15"/>
-      <c r="L588" s="22"/>
+      <c r="L588" s="23"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="A589" s="15"/>
       <c r="B589" s="15"/>
-      <c r="L589" s="22"/>
+      <c r="L589" s="23"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="A590" s="15"/>
       <c r="B590" s="15"/>
-      <c r="L590" s="22"/>
+      <c r="L590" s="23"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="A591" s="15"/>
       <c r="B591" s="15"/>
-      <c r="L591" s="22"/>
+      <c r="L591" s="23"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
       <c r="A592" s="15"/>
       <c r="B592" s="15"/>
-      <c r="L592" s="22"/>
+      <c r="L592" s="23"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
       <c r="A593" s="15"/>
       <c r="B593" s="15"/>
-      <c r="L593" s="22"/>
+      <c r="L593" s="23"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="A594" s="15"/>
       <c r="B594" s="15"/>
-      <c r="L594" s="22"/>
+      <c r="L594" s="23"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="A595" s="15"/>
       <c r="B595" s="15"/>
-      <c r="L595" s="22"/>
+      <c r="L595" s="23"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="A596" s="15"/>
       <c r="B596" s="15"/>
-      <c r="L596" s="22"/>
+      <c r="L596" s="23"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="A597" s="15"/>
       <c r="B597" s="15"/>
-      <c r="L597" s="22"/>
+      <c r="L597" s="23"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="A598" s="15"/>
       <c r="B598" s="15"/>
-      <c r="L598" s="22"/>
+      <c r="L598" s="23"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="A599" s="15"/>
       <c r="B599" s="15"/>
-      <c r="L599" s="22"/>
+      <c r="L599" s="23"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
       <c r="A600" s="15"/>
       <c r="B600" s="15"/>
-      <c r="L600" s="22"/>
+      <c r="L600" s="23"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
       <c r="A601" s="15"/>
       <c r="B601" s="15"/>
-      <c r="L601" s="22"/>
+      <c r="L601" s="23"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
       <c r="A602" s="15"/>
       <c r="B602" s="15"/>
-      <c r="L602" s="22"/>
+      <c r="L602" s="23"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
       <c r="A603" s="15"/>
       <c r="B603" s="15"/>
-      <c r="L603" s="22"/>
+      <c r="L603" s="23"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="A604" s="15"/>
       <c r="B604" s="15"/>
-      <c r="L604" s="22"/>
+      <c r="L604" s="23"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="A605" s="15"/>
       <c r="B605" s="15"/>
-      <c r="L605" s="22"/>
+      <c r="L605" s="23"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="A606" s="15"/>
       <c r="B606" s="15"/>
-      <c r="L606" s="22"/>
+      <c r="L606" s="23"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="A607" s="15"/>
       <c r="B607" s="15"/>
-      <c r="L607" s="22"/>
+      <c r="L607" s="23"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
       <c r="A608" s="15"/>
       <c r="B608" s="15"/>
-      <c r="L608" s="22"/>
+      <c r="L608" s="23"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
       <c r="A609" s="15"/>
       <c r="B609" s="15"/>
-      <c r="L609" s="22"/>
+      <c r="L609" s="23"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
       <c r="A610" s="15"/>
       <c r="B610" s="15"/>
-      <c r="L610" s="22"/>
+      <c r="L610" s="23"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="A611" s="15"/>
       <c r="B611" s="15"/>
-      <c r="L611" s="22"/>
+      <c r="L611" s="23"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="A612" s="15"/>
       <c r="B612" s="15"/>
-      <c r="L612" s="22"/>
+      <c r="L612" s="23"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="A613" s="15"/>
       <c r="B613" s="15"/>
-      <c r="L613" s="22"/>
+      <c r="L613" s="23"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="A614" s="15"/>
       <c r="B614" s="15"/>
-      <c r="L614" s="22"/>
+      <c r="L614" s="23"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="A615" s="15"/>
       <c r="B615" s="15"/>
-      <c r="L615" s="22"/>
+      <c r="L615" s="23"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
       <c r="A616" s="15"/>
       <c r="B616" s="15"/>
-      <c r="L616" s="22"/>
+      <c r="L616" s="23"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
       <c r="A617" s="15"/>
       <c r="B617" s="15"/>
-      <c r="L617" s="22"/>
+      <c r="L617" s="23"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
       <c r="A618" s="15"/>
       <c r="B618" s="15"/>
-      <c r="L618" s="22"/>
+      <c r="L618" s="23"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="A619" s="15"/>
       <c r="B619" s="15"/>
-      <c r="L619" s="22"/>
+      <c r="L619" s="23"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="A620" s="15"/>
       <c r="B620" s="15"/>
-      <c r="L620" s="22"/>
+      <c r="L620" s="23"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="A621" s="15"/>
       <c r="B621" s="15"/>
-      <c r="L621" s="22"/>
+      <c r="L621" s="23"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="A622" s="15"/>
       <c r="B622" s="15"/>
-      <c r="L622" s="22"/>
+      <c r="L622" s="23"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
       <c r="A623" s="15"/>
       <c r="B623" s="15"/>
-      <c r="L623" s="22"/>
+      <c r="L623" s="23"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="A624" s="15"/>
       <c r="B624" s="15"/>
-      <c r="L624" s="22"/>
+      <c r="L624" s="23"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
       <c r="A625" s="15"/>
       <c r="B625" s="15"/>
-      <c r="L625" s="22"/>
+      <c r="L625" s="23"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="A626" s="15"/>
       <c r="B626" s="15"/>
-      <c r="L626" s="22"/>
+      <c r="L626" s="23"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="A627" s="15"/>
       <c r="B627" s="15"/>
-      <c r="L627" s="22"/>
+      <c r="L627" s="23"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="A628" s="15"/>
       <c r="B628" s="15"/>
-      <c r="L628" s="22"/>
+      <c r="L628" s="23"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="A629" s="15"/>
       <c r="B629" s="15"/>
-      <c r="L629" s="22"/>
+      <c r="L629" s="23"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="A630" s="15"/>
       <c r="B630" s="15"/>
-      <c r="L630" s="22"/>
+      <c r="L630" s="23"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="A631" s="15"/>
       <c r="B631" s="15"/>
-      <c r="L631" s="22"/>
+      <c r="L631" s="23"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
       <c r="A632" s="15"/>
       <c r="B632" s="15"/>
-      <c r="L632" s="22"/>
+      <c r="L632" s="23"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
       <c r="A633" s="15"/>
       <c r="B633" s="15"/>
-      <c r="L633" s="22"/>
+      <c r="L633" s="23"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
       <c r="A634" s="15"/>
       <c r="B634" s="15"/>
-      <c r="L634" s="22"/>
+      <c r="L634" s="23"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="A635" s="15"/>
       <c r="B635" s="15"/>
-      <c r="L635" s="22"/>
+      <c r="L635" s="23"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="A636" s="15"/>
       <c r="B636" s="15"/>
-      <c r="L636" s="22"/>
+      <c r="L636" s="23"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="A637" s="15"/>
       <c r="B637" s="15"/>
-      <c r="L637" s="22"/>
+      <c r="L637" s="23"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="A638" s="15"/>
       <c r="B638" s="15"/>
-      <c r="L638" s="22"/>
+      <c r="L638" s="23"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="A639" s="15"/>
       <c r="B639" s="15"/>
-      <c r="L639" s="22"/>
+      <c r="L639" s="23"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="A640" s="15"/>
       <c r="B640" s="15"/>
-      <c r="L640" s="22"/>
+      <c r="L640" s="23"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="A641" s="15"/>
       <c r="B641" s="15"/>
-      <c r="L641" s="22"/>
+      <c r="L641" s="23"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="A642" s="15"/>
       <c r="B642" s="15"/>
-      <c r="L642" s="22"/>
+      <c r="L642" s="23"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
       <c r="A643" s="15"/>
       <c r="B643" s="15"/>
-      <c r="L643" s="22"/>
+      <c r="L643" s="23"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
       <c r="A644" s="15"/>
       <c r="B644" s="15"/>
-      <c r="L644" s="22"/>
+      <c r="L644" s="23"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
       <c r="A645" s="15"/>
       <c r="B645" s="15"/>
-      <c r="L645" s="22"/>
+      <c r="L645" s="23"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
       <c r="A646" s="15"/>
       <c r="B646" s="15"/>
-      <c r="L646" s="22"/>
+      <c r="L646" s="23"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
       <c r="A647" s="15"/>
       <c r="B647" s="15"/>
-      <c r="L647" s="22"/>
+      <c r="L647" s="23"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
       <c r="A648" s="15"/>
       <c r="B648" s="15"/>
-      <c r="L648" s="22"/>
+      <c r="L648" s="23"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
       <c r="A649" s="15"/>
       <c r="B649" s="15"/>
-      <c r="L649" s="22"/>
+      <c r="L649" s="23"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
       <c r="A650" s="15"/>
       <c r="B650" s="15"/>
-      <c r="L650" s="22"/>
+      <c r="L650" s="23"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
       <c r="A651" s="15"/>
       <c r="B651" s="15"/>
-      <c r="L651" s="22"/>
+      <c r="L651" s="23"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
       <c r="A652" s="15"/>
       <c r="B652" s="15"/>
-      <c r="L652" s="22"/>
+      <c r="L652" s="23"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
       <c r="A653" s="15"/>
       <c r="B653" s="15"/>
-      <c r="L653" s="22"/>
+      <c r="L653" s="23"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
       <c r="A654" s="15"/>
       <c r="B654" s="15"/>
-      <c r="L654" s="22"/>
+      <c r="L654" s="23"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
       <c r="A655" s="15"/>
       <c r="B655" s="15"/>
-      <c r="L655" s="22"/>
+      <c r="L655" s="23"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
       <c r="A656" s="15"/>
       <c r="B656" s="15"/>
-      <c r="L656" s="22"/>
+      <c r="L656" s="23"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
       <c r="A657" s="15"/>
       <c r="B657" s="15"/>
-      <c r="L657" s="22"/>
+      <c r="L657" s="23"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
       <c r="A658" s="15"/>
       <c r="B658" s="15"/>
-      <c r="L658" s="22"/>
+      <c r="L658" s="23"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
       <c r="A659" s="15"/>
       <c r="B659" s="15"/>
-      <c r="L659" s="22"/>
+      <c r="L659" s="23"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
       <c r="A660" s="15"/>
       <c r="B660" s="15"/>
-      <c r="L660" s="22"/>
+      <c r="L660" s="23"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
       <c r="A661" s="15"/>
       <c r="B661" s="15"/>
-      <c r="L661" s="22"/>
+      <c r="L661" s="23"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
       <c r="A662" s="15"/>
       <c r="B662" s="15"/>
-      <c r="L662" s="22"/>
+      <c r="L662" s="23"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
       <c r="A663" s="15"/>
       <c r="B663" s="15"/>
-      <c r="L663" s="22"/>
+      <c r="L663" s="23"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
       <c r="A664" s="15"/>
       <c r="B664" s="15"/>
-      <c r="L664" s="22"/>
+      <c r="L664" s="23"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
       <c r="A665" s="15"/>
       <c r="B665" s="15"/>
-      <c r="L665" s="22"/>
+      <c r="L665" s="23"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
       <c r="A666" s="15"/>
       <c r="B666" s="15"/>
-      <c r="L666" s="22"/>
+      <c r="L666" s="23"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
       <c r="A667" s="15"/>
       <c r="B667" s="15"/>
-      <c r="L667" s="22"/>
+      <c r="L667" s="23"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
       <c r="A668" s="15"/>
       <c r="B668" s="15"/>
-      <c r="L668" s="22"/>
+      <c r="L668" s="23"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
       <c r="A669" s="15"/>
       <c r="B669" s="15"/>
-      <c r="L669" s="22"/>
+      <c r="L669" s="23"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
       <c r="A670" s="15"/>
       <c r="B670" s="15"/>
-      <c r="L670" s="22"/>
+      <c r="L670" s="23"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
       <c r="A671" s="15"/>
       <c r="B671" s="15"/>
-      <c r="L671" s="22"/>
+      <c r="L671" s="23"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
       <c r="A672" s="15"/>
       <c r="B672" s="15"/>
-      <c r="L672" s="22"/>
+      <c r="L672" s="23"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
       <c r="A673" s="15"/>
       <c r="B673" s="15"/>
-      <c r="L673" s="22"/>
+      <c r="L673" s="23"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
       <c r="A674" s="15"/>
       <c r="B674" s="15"/>
-      <c r="L674" s="22"/>
+      <c r="L674" s="23"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
       <c r="A675" s="15"/>
       <c r="B675" s="15"/>
-      <c r="L675" s="22"/>
+      <c r="L675" s="23"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
       <c r="A676" s="15"/>
       <c r="B676" s="15"/>
-      <c r="L676" s="22"/>
+      <c r="L676" s="23"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
       <c r="A677" s="15"/>
       <c r="B677" s="15"/>
-      <c r="L677" s="22"/>
+      <c r="L677" s="23"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
       <c r="A678" s="15"/>
       <c r="B678" s="15"/>
-      <c r="L678" s="22"/>
+      <c r="L678" s="23"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
       <c r="A679" s="15"/>
       <c r="B679" s="15"/>
-      <c r="L679" s="22"/>
+      <c r="L679" s="23"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
       <c r="A680" s="15"/>
       <c r="B680" s="15"/>
-      <c r="L680" s="22"/>
+      <c r="L680" s="23"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
       <c r="A681" s="15"/>
       <c r="B681" s="15"/>
-      <c r="L681" s="22"/>
+      <c r="L681" s="23"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
       <c r="A682" s="15"/>
       <c r="B682" s="15"/>
-      <c r="L682" s="22"/>
+      <c r="L682" s="23"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
       <c r="A683" s="15"/>
       <c r="B683" s="15"/>
-      <c r="L683" s="22"/>
+      <c r="L683" s="23"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
       <c r="A684" s="15"/>
       <c r="B684" s="15"/>
-      <c r="L684" s="22"/>
+      <c r="L684" s="23"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
       <c r="A685" s="15"/>
       <c r="B685" s="15"/>
-      <c r="L685" s="22"/>
+      <c r="L685" s="23"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
       <c r="A686" s="15"/>
       <c r="B686" s="15"/>
-      <c r="L686" s="22"/>
+      <c r="L686" s="23"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
       <c r="A687" s="15"/>
       <c r="B687" s="15"/>
-      <c r="L687" s="22"/>
+      <c r="L687" s="23"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
       <c r="A688" s="15"/>
       <c r="B688" s="15"/>
-      <c r="L688" s="22"/>
+      <c r="L688" s="23"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
       <c r="A689" s="15"/>
       <c r="B689" s="15"/>
-      <c r="L689" s="22"/>
+      <c r="L689" s="23"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
       <c r="A690" s="15"/>
       <c r="B690" s="15"/>
-      <c r="L690" s="22"/>
+      <c r="L690" s="23"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
       <c r="A691" s="15"/>
       <c r="B691" s="15"/>
-      <c r="L691" s="22"/>
+      <c r="L691" s="23"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
       <c r="A692" s="15"/>
       <c r="B692" s="15"/>
-      <c r="L692" s="22"/>
+      <c r="L692" s="23"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
       <c r="A693" s="15"/>
       <c r="B693" s="15"/>
-      <c r="L693" s="22"/>
+      <c r="L693" s="23"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
       <c r="A694" s="15"/>
       <c r="B694" s="15"/>
-      <c r="L694" s="22"/>
+      <c r="L694" s="23"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
       <c r="A695" s="15"/>
       <c r="B695" s="15"/>
-      <c r="L695" s="22"/>
+      <c r="L695" s="23"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
       <c r="A696" s="15"/>
       <c r="B696" s="15"/>
-      <c r="L696" s="22"/>
+      <c r="L696" s="23"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
       <c r="A697" s="15"/>
       <c r="B697" s="15"/>
-      <c r="L697" s="22"/>
+      <c r="L697" s="23"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
       <c r="A698" s="15"/>
       <c r="B698" s="15"/>
-      <c r="L698" s="22"/>
+      <c r="L698" s="23"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
       <c r="A699" s="15"/>
       <c r="B699" s="15"/>
-      <c r="L699" s="22"/>
+      <c r="L699" s="23"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
       <c r="A700" s="15"/>
       <c r="B700" s="15"/>
-      <c r="L700" s="22"/>
+      <c r="L700" s="23"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
       <c r="A701" s="15"/>
       <c r="B701" s="15"/>
-      <c r="L701" s="22"/>
+      <c r="L701" s="23"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
       <c r="A702" s="15"/>
       <c r="B702" s="15"/>
-      <c r="L702" s="22"/>
+      <c r="L702" s="23"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
       <c r="A703" s="15"/>
       <c r="B703" s="15"/>
-      <c r="L703" s="22"/>
+      <c r="L703" s="23"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
       <c r="A704" s="15"/>
       <c r="B704" s="15"/>
-      <c r="L704" s="22"/>
+      <c r="L704" s="23"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
       <c r="A705" s="15"/>
       <c r="B705" s="15"/>
-      <c r="L705" s="22"/>
+      <c r="L705" s="23"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
       <c r="A706" s="15"/>
       <c r="B706" s="15"/>
-      <c r="L706" s="22"/>
+      <c r="L706" s="23"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
       <c r="A707" s="15"/>
       <c r="B707" s="15"/>
-      <c r="L707" s="22"/>
+      <c r="L707" s="23"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
       <c r="A708" s="15"/>
       <c r="B708" s="15"/>
-      <c r="L708" s="22"/>
+      <c r="L708" s="23"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
       <c r="A709" s="15"/>
       <c r="B709" s="15"/>
-      <c r="L709" s="22"/>
+      <c r="L709" s="23"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
       <c r="A710" s="15"/>
       <c r="B710" s="15"/>
-      <c r="L710" s="22"/>
+      <c r="L710" s="23"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
       <c r="A711" s="15"/>
       <c r="B711" s="15"/>
-      <c r="L711" s="22"/>
+      <c r="L711" s="23"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
       <c r="A712" s="15"/>
       <c r="B712" s="15"/>
-      <c r="L712" s="22"/>
+      <c r="L712" s="23"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
       <c r="A713" s="15"/>
       <c r="B713" s="15"/>
-      <c r="L713" s="22"/>
+      <c r="L713" s="23"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
       <c r="A714" s="15"/>
       <c r="B714" s="15"/>
-      <c r="L714" s="22"/>
+      <c r="L714" s="23"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
       <c r="A715" s="15"/>
       <c r="B715" s="15"/>
-      <c r="L715" s="22"/>
+      <c r="L715" s="23"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
       <c r="A716" s="15"/>
       <c r="B716" s="15"/>
-      <c r="L716" s="22"/>
+      <c r="L716" s="23"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
       <c r="A717" s="15"/>
       <c r="B717" s="15"/>
-      <c r="L717" s="22"/>
+      <c r="L717" s="23"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
       <c r="A718" s="15"/>
       <c r="B718" s="15"/>
-      <c r="L718" s="22"/>
+      <c r="L718" s="23"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
       <c r="A719" s="15"/>
       <c r="B719" s="15"/>
-      <c r="L719" s="22"/>
+      <c r="L719" s="23"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
       <c r="A720" s="15"/>
       <c r="B720" s="15"/>
-      <c r="L720" s="22"/>
+      <c r="L720" s="23"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
       <c r="A721" s="15"/>
       <c r="B721" s="15"/>
-      <c r="L721" s="22"/>
+      <c r="L721" s="23"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
       <c r="A722" s="15"/>
       <c r="B722" s="15"/>
-      <c r="L722" s="22"/>
+      <c r="L722" s="23"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
       <c r="A723" s="15"/>
       <c r="B723" s="15"/>
-      <c r="L723" s="22"/>
+      <c r="L723" s="23"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
       <c r="A724" s="15"/>
       <c r="B724" s="15"/>
-      <c r="L724" s="22"/>
+      <c r="L724" s="23"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
       <c r="A725" s="15"/>
       <c r="B725" s="15"/>
-      <c r="L725" s="22"/>
+      <c r="L725" s="23"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
       <c r="A726" s="15"/>
       <c r="B726" s="15"/>
-      <c r="L726" s="22"/>
+      <c r="L726" s="23"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
       <c r="A727" s="15"/>
       <c r="B727" s="15"/>
-      <c r="L727" s="22"/>
+      <c r="L727" s="23"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
       <c r="A728" s="15"/>
       <c r="B728" s="15"/>
-      <c r="L728" s="22"/>
+      <c r="L728" s="23"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
       <c r="A729" s="15"/>
       <c r="B729" s="15"/>
-      <c r="L729" s="22"/>
+      <c r="L729" s="23"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
       <c r="A730" s="15"/>
       <c r="B730" s="15"/>
-      <c r="L730" s="22"/>
+      <c r="L730" s="23"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
       <c r="A731" s="15"/>
       <c r="B731" s="15"/>
-      <c r="L731" s="22"/>
+      <c r="L731" s="23"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
       <c r="A732" s="15"/>
       <c r="B732" s="15"/>
-      <c r="L732" s="22"/>
+      <c r="L732" s="23"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
       <c r="A733" s="15"/>
       <c r="B733" s="15"/>
-      <c r="L733" s="22"/>
+      <c r="L733" s="23"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
       <c r="A734" s="15"/>
       <c r="B734" s="15"/>
-      <c r="L734" s="22"/>
+      <c r="L734" s="23"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
       <c r="A735" s="15"/>
       <c r="B735" s="15"/>
-      <c r="L735" s="22"/>
+      <c r="L735" s="23"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
       <c r="A736" s="15"/>
       <c r="B736" s="15"/>
-      <c r="L736" s="22"/>
+      <c r="L736" s="23"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
       <c r="A737" s="15"/>
       <c r="B737" s="15"/>
-      <c r="L737" s="22"/>
+      <c r="L737" s="23"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
       <c r="A738" s="15"/>
       <c r="B738" s="15"/>
-      <c r="L738" s="22"/>
+      <c r="L738" s="23"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
       <c r="A739" s="15"/>
       <c r="B739" s="15"/>
-      <c r="L739" s="22"/>
+      <c r="L739" s="23"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
       <c r="A740" s="15"/>
       <c r="B740" s="15"/>
-      <c r="L740" s="22"/>
+      <c r="L740" s="23"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
       <c r="A741" s="15"/>
       <c r="B741" s="15"/>
-      <c r="L741" s="22"/>
+      <c r="L741" s="23"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
       <c r="A742" s="15"/>
       <c r="B742" s="15"/>
-      <c r="L742" s="22"/>
+      <c r="L742" s="23"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
       <c r="A743" s="15"/>
       <c r="B743" s="15"/>
-      <c r="L743" s="22"/>
+      <c r="L743" s="23"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
       <c r="A744" s="15"/>
       <c r="B744" s="15"/>
-      <c r="L744" s="22"/>
+      <c r="L744" s="23"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
       <c r="A745" s="15"/>
       <c r="B745" s="15"/>
-      <c r="L745" s="22"/>
+      <c r="L745" s="23"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
       <c r="A746" s="15"/>
       <c r="B746" s="15"/>
-      <c r="L746" s="22"/>
+      <c r="L746" s="23"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
       <c r="A747" s="15"/>
       <c r="B747" s="15"/>
-      <c r="L747" s="22"/>
+      <c r="L747" s="23"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
       <c r="A748" s="15"/>
       <c r="B748" s="15"/>
-      <c r="L748" s="22"/>
+      <c r="L748" s="23"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
       <c r="A749" s="15"/>
       <c r="B749" s="15"/>
-      <c r="L749" s="22"/>
+      <c r="L749" s="23"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
       <c r="A750" s="15"/>
       <c r="B750" s="15"/>
-      <c r="L750" s="22"/>
+      <c r="L750" s="23"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
       <c r="A751" s="15"/>
       <c r="B751" s="15"/>
-      <c r="L751" s="22"/>
+      <c r="L751" s="23"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
       <c r="A752" s="15"/>
       <c r="B752" s="15"/>
-      <c r="L752" s="22"/>
+      <c r="L752" s="23"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
       <c r="A753" s="15"/>
       <c r="B753" s="15"/>
-      <c r="L753" s="22"/>
+      <c r="L753" s="23"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
       <c r="A754" s="15"/>
       <c r="B754" s="15"/>
-      <c r="L754" s="22"/>
+      <c r="L754" s="23"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
       <c r="A755" s="15"/>
       <c r="B755" s="15"/>
-      <c r="L755" s="22"/>
+      <c r="L755" s="23"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
       <c r="A756" s="15"/>
       <c r="B756" s="15"/>
-      <c r="L756" s="22"/>
+      <c r="L756" s="23"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
       <c r="A757" s="15"/>
       <c r="B757" s="15"/>
-      <c r="L757" s="22"/>
+      <c r="L757" s="23"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
       <c r="A758" s="15"/>
       <c r="B758" s="15"/>
-      <c r="L758" s="22"/>
+      <c r="L758" s="23"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
       <c r="A759" s="15"/>
       <c r="B759" s="15"/>
-      <c r="L759" s="22"/>
+      <c r="L759" s="23"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
       <c r="A760" s="15"/>
       <c r="B760" s="15"/>
-      <c r="L760" s="22"/>
+      <c r="L760" s="23"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
       <c r="A761" s="15"/>
       <c r="B761" s="15"/>
-      <c r="L761" s="22"/>
+      <c r="L761" s="23"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
       <c r="A762" s="15"/>
       <c r="B762" s="15"/>
-      <c r="L762" s="22"/>
+      <c r="L762" s="23"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
       <c r="A763" s="15"/>
       <c r="B763" s="15"/>
-      <c r="L763" s="22"/>
+      <c r="L763" s="23"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
       <c r="A764" s="15"/>
       <c r="B764" s="15"/>
-      <c r="L764" s="22"/>
+      <c r="L764" s="23"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
       <c r="A765" s="15"/>
       <c r="B765" s="15"/>
-      <c r="L765" s="22"/>
+      <c r="L765" s="23"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
       <c r="A766" s="15"/>
       <c r="B766" s="15"/>
-      <c r="L766" s="22"/>
+      <c r="L766" s="23"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
       <c r="A767" s="15"/>
       <c r="B767" s="15"/>
-      <c r="L767" s="22"/>
+      <c r="L767" s="23"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
       <c r="A768" s="15"/>
       <c r="B768" s="15"/>
-      <c r="L768" s="22"/>
+      <c r="L768" s="23"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
       <c r="A769" s="15"/>
       <c r="B769" s="15"/>
-      <c r="L769" s="22"/>
+      <c r="L769" s="23"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
       <c r="A770" s="15"/>
       <c r="B770" s="15"/>
-      <c r="L770" s="22"/>
+      <c r="L770" s="23"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
       <c r="A771" s="15"/>
       <c r="B771" s="15"/>
-      <c r="L771" s="22"/>
+      <c r="L771" s="23"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
       <c r="A772" s="15"/>
       <c r="B772" s="15"/>
-      <c r="L772" s="22"/>
+      <c r="L772" s="23"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
       <c r="A773" s="15"/>
       <c r="B773" s="15"/>
-      <c r="L773" s="22"/>
+      <c r="L773" s="23"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
       <c r="A774" s="15"/>
       <c r="B774" s="15"/>
-      <c r="L774" s="22"/>
+      <c r="L774" s="23"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
       <c r="A775" s="15"/>
       <c r="B775" s="15"/>
-      <c r="L775" s="22"/>
+      <c r="L775" s="23"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
       <c r="A776" s="15"/>
       <c r="B776" s="15"/>
-      <c r="L776" s="22"/>
+      <c r="L776" s="23"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
       <c r="A777" s="15"/>
       <c r="B777" s="15"/>
-      <c r="L777" s="22"/>
+      <c r="L777" s="23"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
       <c r="A778" s="15"/>
       <c r="B778" s="15"/>
-      <c r="L778" s="22"/>
+      <c r="L778" s="23"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
       <c r="A779" s="15"/>
       <c r="B779" s="15"/>
-      <c r="L779" s="22"/>
+      <c r="L779" s="23"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
       <c r="A780" s="15"/>
       <c r="B780" s="15"/>
-      <c r="L780" s="22"/>
+      <c r="L780" s="23"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
       <c r="A781" s="15"/>
       <c r="B781" s="15"/>
-      <c r="L781" s="22"/>
+      <c r="L781" s="23"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
       <c r="A782" s="15"/>
       <c r="B782" s="15"/>
-      <c r="L782" s="22"/>
+      <c r="L782" s="23"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
       <c r="A783" s="15"/>
       <c r="B783" s="15"/>
-      <c r="L783" s="22"/>
+      <c r="L783" s="23"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
       <c r="A784" s="15"/>
       <c r="B784" s="15"/>
-      <c r="L784" s="22"/>
+      <c r="L784" s="23"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
       <c r="A785" s="15"/>
       <c r="B785" s="15"/>
-      <c r="L785" s="22"/>
+      <c r="L785" s="23"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
       <c r="A786" s="15"/>
       <c r="B786" s="15"/>
-      <c r="L786" s="22"/>
+      <c r="L786" s="23"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
       <c r="A787" s="15"/>
       <c r="B787" s="15"/>
-      <c r="L787" s="22"/>
+      <c r="L787" s="23"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
       <c r="A788" s="15"/>
       <c r="B788" s="15"/>
-      <c r="L788" s="22"/>
+      <c r="L788" s="23"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
       <c r="A789" s="15"/>
       <c r="B789" s="15"/>
-      <c r="L789" s="22"/>
+      <c r="L789" s="23"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
       <c r="A790" s="15"/>
       <c r="B790" s="15"/>
-      <c r="L790" s="22"/>
+      <c r="L790" s="23"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
       <c r="A791" s="15"/>
       <c r="B791" s="15"/>
-      <c r="L791" s="22"/>
+      <c r="L791" s="23"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
       <c r="A792" s="15"/>
       <c r="B792" s="15"/>
-      <c r="L792" s="22"/>
+      <c r="L792" s="23"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
       <c r="A793" s="15"/>
       <c r="B793" s="15"/>
-      <c r="L793" s="22"/>
+      <c r="L793" s="23"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
       <c r="A794" s="15"/>
       <c r="B794" s="15"/>
-      <c r="L794" s="22"/>
+      <c r="L794" s="23"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
       <c r="A795" s="15"/>
       <c r="B795" s="15"/>
-      <c r="L795" s="22"/>
+      <c r="L795" s="23"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
       <c r="A796" s="15"/>
       <c r="B796" s="15"/>
-      <c r="L796" s="22"/>
+      <c r="L796" s="23"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
       <c r="A797" s="15"/>
       <c r="B797" s="15"/>
-      <c r="L797" s="22"/>
+      <c r="L797" s="23"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
       <c r="A798" s="15"/>
       <c r="B798" s="15"/>
-      <c r="L798" s="22"/>
+      <c r="L798" s="23"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
       <c r="A799" s="15"/>
       <c r="B799" s="15"/>
-      <c r="L799" s="22"/>
+      <c r="L799" s="23"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
       <c r="A800" s="15"/>
       <c r="B800" s="15"/>
-      <c r="L800" s="22"/>
+      <c r="L800" s="23"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
       <c r="A801" s="15"/>
       <c r="B801" s="15"/>
-      <c r="L801" s="22"/>
+      <c r="L801" s="23"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
       <c r="A802" s="15"/>
       <c r="B802" s="15"/>
-      <c r="L802" s="22"/>
+      <c r="L802" s="23"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
       <c r="A803" s="15"/>
       <c r="B803" s="15"/>
-      <c r="L803" s="22"/>
+      <c r="L803" s="23"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
       <c r="A804" s="15"/>
       <c r="B804" s="15"/>
-      <c r="L804" s="22"/>
+      <c r="L804" s="23"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
       <c r="A805" s="15"/>
       <c r="B805" s="15"/>
-      <c r="L805" s="22"/>
+      <c r="L805" s="23"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
       <c r="A806" s="15"/>
       <c r="B806" s="15"/>
-      <c r="L806" s="22"/>
+      <c r="L806" s="23"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
       <c r="A807" s="15"/>
       <c r="B807" s="15"/>
-      <c r="L807" s="22"/>
+      <c r="L807" s="23"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
       <c r="A808" s="15"/>
       <c r="B808" s="15"/>
-      <c r="L808" s="22"/>
+      <c r="L808" s="23"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
       <c r="A809" s="15"/>
       <c r="B809" s="15"/>
-      <c r="L809" s="22"/>
+      <c r="L809" s="23"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
       <c r="A810" s="15"/>
       <c r="B810" s="15"/>
-      <c r="L810" s="22"/>
+      <c r="L810" s="23"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
       <c r="A811" s="15"/>
       <c r="B811" s="15"/>
-      <c r="L811" s="22"/>
+      <c r="L811" s="23"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
       <c r="A812" s="15"/>
       <c r="B812" s="15"/>
-      <c r="L812" s="22"/>
+      <c r="L812" s="23"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
       <c r="A813" s="15"/>
       <c r="B813" s="15"/>
-      <c r="L813" s="22"/>
+      <c r="L813" s="23"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
       <c r="A814" s="15"/>
       <c r="B814" s="15"/>
-      <c r="L814" s="22"/>
+      <c r="L814" s="23"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
       <c r="A815" s="15"/>
       <c r="B815" s="15"/>
-      <c r="L815" s="22"/>
+      <c r="L815" s="23"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
       <c r="A816" s="15"/>
       <c r="B816" s="15"/>
-      <c r="L816" s="22"/>
+      <c r="L816" s="23"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
       <c r="A817" s="15"/>
       <c r="B817" s="15"/>
-      <c r="L817" s="22"/>
+      <c r="L817" s="23"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
       <c r="A818" s="15"/>
       <c r="B818" s="15"/>
-      <c r="L818" s="22"/>
+      <c r="L818" s="23"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
       <c r="A819" s="15"/>
       <c r="B819" s="15"/>
-      <c r="L819" s="22"/>
+      <c r="L819" s="23"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
       <c r="A820" s="15"/>
       <c r="B820" s="15"/>
-      <c r="L820" s="22"/>
+      <c r="L820" s="23"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
       <c r="A821" s="15"/>
       <c r="B821" s="15"/>
-      <c r="L821" s="22"/>
+      <c r="L821" s="23"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
       <c r="A822" s="15"/>
       <c r="B822" s="15"/>
-      <c r="L822" s="22"/>
+      <c r="L822" s="23"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
       <c r="A823" s="15"/>
       <c r="B823" s="15"/>
-      <c r="L823" s="22"/>
+      <c r="L823" s="23"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
       <c r="A824" s="15"/>
       <c r="B824" s="15"/>
-      <c r="L824" s="22"/>
+      <c r="L824" s="23"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
       <c r="A825" s="15"/>
       <c r="B825" s="15"/>
-      <c r="L825" s="22"/>
+      <c r="L825" s="23"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
       <c r="A826" s="15"/>
       <c r="B826" s="15"/>
-      <c r="L826" s="22"/>
+      <c r="L826" s="23"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
       <c r="A827" s="15"/>
       <c r="B827" s="15"/>
-      <c r="L827" s="22"/>
+      <c r="L827" s="23"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
       <c r="A828" s="15"/>
       <c r="B828" s="15"/>
-      <c r="L828" s="22"/>
+      <c r="L828" s="23"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
       <c r="A829" s="15"/>
       <c r="B829" s="15"/>
-      <c r="L829" s="22"/>
+      <c r="L829" s="23"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
       <c r="A830" s="15"/>
       <c r="B830" s="15"/>
-      <c r="L830" s="22"/>
+      <c r="L830" s="23"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
       <c r="A831" s="15"/>
       <c r="B831" s="15"/>
-      <c r="L831" s="22"/>
+      <c r="L831" s="23"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
       <c r="A832" s="15"/>
       <c r="B832" s="15"/>
-      <c r="L832" s="22"/>
+      <c r="L832" s="23"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
       <c r="A833" s="15"/>
       <c r="B833" s="15"/>
-      <c r="L833" s="22"/>
+      <c r="L833" s="23"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
       <c r="A834" s="15"/>
       <c r="B834" s="15"/>
-      <c r="L834" s="22"/>
+      <c r="L834" s="23"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
       <c r="A835" s="15"/>
       <c r="B835" s="15"/>
-      <c r="L835" s="22"/>
+      <c r="L835" s="23"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
       <c r="A836" s="15"/>
       <c r="B836" s="15"/>
-      <c r="L836" s="22"/>
+      <c r="L836" s="23"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
       <c r="A837" s="15"/>
       <c r="B837" s="15"/>
-      <c r="L837" s="22"/>
+      <c r="L837" s="23"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
       <c r="A838" s="15"/>
       <c r="B838" s="15"/>
-      <c r="L838" s="22"/>
+      <c r="L838" s="23"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
       <c r="A839" s="15"/>
       <c r="B839" s="15"/>
-      <c r="L839" s="22"/>
+      <c r="L839" s="23"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
       <c r="A840" s="15"/>
       <c r="B840" s="15"/>
-      <c r="L840" s="22"/>
+      <c r="L840" s="23"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
       <c r="A841" s="15"/>
       <c r="B841" s="15"/>
-      <c r="L841" s="22"/>
+      <c r="L841" s="23"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
       <c r="A842" s="15"/>
       <c r="B842" s="15"/>
-      <c r="L842" s="22"/>
+      <c r="L842" s="23"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
       <c r="A843" s="15"/>
       <c r="B843" s="15"/>
-      <c r="L843" s="22"/>
+      <c r="L843" s="23"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
       <c r="A844" s="15"/>
       <c r="B844" s="15"/>
-      <c r="L844" s="22"/>
+      <c r="L844" s="23"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
       <c r="A845" s="15"/>
       <c r="B845" s="15"/>
-      <c r="L845" s="22"/>
+      <c r="L845" s="23"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
       <c r="A846" s="15"/>
       <c r="B846" s="15"/>
-      <c r="L846" s="22"/>
+      <c r="L846" s="23"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
       <c r="A847" s="15"/>
       <c r="B847" s="15"/>
-      <c r="L847" s="22"/>
+      <c r="L847" s="23"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
       <c r="A848" s="15"/>
       <c r="B848" s="15"/>
-      <c r="L848" s="22"/>
+      <c r="L848" s="23"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
       <c r="A849" s="15"/>
       <c r="B849" s="15"/>
-      <c r="L849" s="22"/>
+      <c r="L849" s="23"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
       <c r="A850" s="15"/>
       <c r="B850" s="15"/>
-      <c r="L850" s="22"/>
+      <c r="L850" s="23"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
       <c r="A851" s="15"/>
       <c r="B851" s="15"/>
-      <c r="L851" s="22"/>
+      <c r="L851" s="23"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
       <c r="A852" s="15"/>
       <c r="B852" s="15"/>
-      <c r="L852" s="22"/>
+      <c r="L852" s="23"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
       <c r="A853" s="15"/>
       <c r="B853" s="15"/>
-      <c r="L853" s="22"/>
+      <c r="L853" s="23"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
       <c r="A854" s="15"/>
       <c r="B854" s="15"/>
-      <c r="L854" s="22"/>
+      <c r="L854" s="23"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
       <c r="A855" s="15"/>
       <c r="B855" s="15"/>
-      <c r="L855" s="22"/>
+      <c r="L855" s="23"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
       <c r="A856" s="15"/>
       <c r="B856" s="15"/>
-      <c r="L856" s="22"/>
+      <c r="L856" s="23"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
       <c r="A857" s="15"/>
       <c r="B857" s="15"/>
-      <c r="L857" s="22"/>
+      <c r="L857" s="23"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
       <c r="A858" s="15"/>
       <c r="B858" s="15"/>
-      <c r="L858" s="22"/>
+      <c r="L858" s="23"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
       <c r="A859" s="15"/>
       <c r="B859" s="15"/>
-      <c r="L859" s="22"/>
+      <c r="L859" s="23"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
       <c r="A860" s="15"/>
       <c r="B860" s="15"/>
-      <c r="L860" s="22"/>
+      <c r="L860" s="23"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
       <c r="A861" s="15"/>
       <c r="B861" s="15"/>
-      <c r="L861" s="22"/>
+      <c r="L861" s="23"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
       <c r="A862" s="15"/>
       <c r="B862" s="15"/>
-      <c r="L862" s="22"/>
+      <c r="L862" s="23"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
       <c r="A863" s="15"/>
       <c r="B863" s="15"/>
-      <c r="L863" s="22"/>
+      <c r="L863" s="23"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
       <c r="A864" s="15"/>
       <c r="B864" s="15"/>
-      <c r="L864" s="22"/>
+      <c r="L864" s="23"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
       <c r="A865" s="15"/>
       <c r="B865" s="15"/>
-      <c r="L865" s="22"/>
+      <c r="L865" s="23"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
       <c r="A866" s="15"/>
       <c r="B866" s="15"/>
-      <c r="L866" s="22"/>
+      <c r="L866" s="23"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
       <c r="A867" s="15"/>
       <c r="B867" s="15"/>
-      <c r="L867" s="22"/>
+      <c r="L867" s="23"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
       <c r="A868" s="15"/>
       <c r="B868" s="15"/>
-      <c r="L868" s="22"/>
+      <c r="L868" s="23"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
       <c r="A869" s="15"/>
       <c r="B869" s="15"/>
-      <c r="L869" s="22"/>
+      <c r="L869" s="23"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
       <c r="A870" s="15"/>
       <c r="B870" s="15"/>
-      <c r="L870" s="22"/>
+      <c r="L870" s="23"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
       <c r="A871" s="15"/>
       <c r="B871" s="15"/>
-      <c r="L871" s="22"/>
+      <c r="L871" s="23"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
       <c r="A872" s="15"/>
       <c r="B872" s="15"/>
-      <c r="L872" s="22"/>
+      <c r="L872" s="23"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
       <c r="A873" s="15"/>
       <c r="B873" s="15"/>
-      <c r="L873" s="22"/>
+      <c r="L873" s="23"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
       <c r="A874" s="15"/>
       <c r="B874" s="15"/>
-      <c r="L874" s="22"/>
+      <c r="L874" s="23"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
       <c r="A875" s="15"/>
       <c r="B875" s="15"/>
-      <c r="L875" s="22"/>
+      <c r="L875" s="23"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
       <c r="A876" s="15"/>
       <c r="B876" s="15"/>
-      <c r="L876" s="22"/>
+      <c r="L876" s="23"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
       <c r="A877" s="15"/>
       <c r="B877" s="15"/>
-      <c r="L877" s="22"/>
+      <c r="L877" s="23"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
       <c r="A878" s="15"/>
       <c r="B878" s="15"/>
-      <c r="L878" s="22"/>
+      <c r="L878" s="23"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
       <c r="A879" s="15"/>
       <c r="B879" s="15"/>
-      <c r="L879" s="22"/>
+      <c r="L879" s="23"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
       <c r="A880" s="15"/>
       <c r="B880" s="15"/>
-      <c r="L880" s="22"/>
+      <c r="L880" s="23"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
       <c r="A881" s="15"/>
       <c r="B881" s="15"/>
-      <c r="L881" s="22"/>
+      <c r="L881" s="23"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
       <c r="A882" s="15"/>
       <c r="B882" s="15"/>
-      <c r="L882" s="22"/>
+      <c r="L882" s="23"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
       <c r="A883" s="15"/>
       <c r="B883" s="15"/>
-      <c r="L883" s="22"/>
+      <c r="L883" s="23"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
       <c r="A884" s="15"/>
       <c r="B884" s="15"/>
-      <c r="L884" s="22"/>
+      <c r="L884" s="23"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
       <c r="A885" s="15"/>
       <c r="B885" s="15"/>
-      <c r="L885" s="22"/>
+      <c r="L885" s="23"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
       <c r="A886" s="15"/>
       <c r="B886" s="15"/>
-      <c r="L886" s="22"/>
+      <c r="L886" s="23"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
       <c r="A887" s="15"/>
       <c r="B887" s="15"/>
-      <c r="L887" s="22"/>
+      <c r="L887" s="23"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
       <c r="A888" s="15"/>
       <c r="B888" s="15"/>
-      <c r="L888" s="22"/>
+      <c r="L888" s="23"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
       <c r="A889" s="15"/>
       <c r="B889" s="15"/>
-      <c r="L889" s="22"/>
+      <c r="L889" s="23"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
       <c r="A890" s="15"/>
       <c r="B890" s="15"/>
-      <c r="L890" s="22"/>
+      <c r="L890" s="23"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
       <c r="A891" s="15"/>
       <c r="B891" s="15"/>
-      <c r="L891" s="22"/>
+      <c r="L891" s="23"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
       <c r="A892" s="15"/>
       <c r="B892" s="15"/>
-      <c r="L892" s="22"/>
+      <c r="L892" s="23"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
       <c r="A893" s="15"/>
       <c r="B893" s="15"/>
-      <c r="L893" s="22"/>
+      <c r="L893" s="23"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
       <c r="A894" s="15"/>
       <c r="B894" s="15"/>
-      <c r="L894" s="22"/>
+      <c r="L894" s="23"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
       <c r="A895" s="15"/>
       <c r="B895" s="15"/>
-      <c r="L895" s="22"/>
+      <c r="L895" s="23"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
       <c r="A896" s="15"/>
       <c r="B896" s="15"/>
-      <c r="L896" s="22"/>
+      <c r="L896" s="23"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
       <c r="A897" s="15"/>
       <c r="B897" s="15"/>
-      <c r="L897" s="22"/>
+      <c r="L897" s="23"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
       <c r="A898" s="15"/>
       <c r="B898" s="15"/>
-      <c r="L898" s="22"/>
+      <c r="L898" s="23"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
       <c r="A899" s="15"/>
       <c r="B899" s="15"/>
-      <c r="L899" s="22"/>
+      <c r="L899" s="23"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
       <c r="A900" s="15"/>
       <c r="B900" s="15"/>
-      <c r="L900" s="22"/>
+      <c r="L900" s="23"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
       <c r="A901" s="15"/>
       <c r="B901" s="15"/>
-      <c r="L901" s="22"/>
+      <c r="L901" s="23"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
       <c r="A902" s="15"/>
       <c r="B902" s="15"/>
-      <c r="L902" s="22"/>
+      <c r="L902" s="23"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
       <c r="A903" s="15"/>
       <c r="B903" s="15"/>
-      <c r="L903" s="22"/>
+      <c r="L903" s="23"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
       <c r="A904" s="15"/>
       <c r="B904" s="15"/>
-      <c r="L904" s="22"/>
+      <c r="L904" s="23"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
       <c r="A905" s="15"/>
       <c r="B905" s="15"/>
-      <c r="L905" s="22"/>
+      <c r="L905" s="23"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
       <c r="A906" s="15"/>
       <c r="B906" s="15"/>
-      <c r="L906" s="22"/>
+      <c r="L906" s="23"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
       <c r="A907" s="15"/>
       <c r="B907" s="15"/>
-      <c r="L907" s="22"/>
+      <c r="L907" s="23"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
       <c r="A908" s="15"/>
       <c r="B908" s="15"/>
-      <c r="L908" s="22"/>
+      <c r="L908" s="23"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
       <c r="A909" s="15"/>
       <c r="B909" s="15"/>
-      <c r="L909" s="22"/>
+      <c r="L909" s="23"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
       <c r="A910" s="15"/>
       <c r="B910" s="15"/>
-      <c r="L910" s="22"/>
+      <c r="L910" s="23"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
       <c r="A911" s="15"/>
       <c r="B911" s="15"/>
-      <c r="L911" s="22"/>
+      <c r="L911" s="23"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
       <c r="A912" s="15"/>
       <c r="B912" s="15"/>
-      <c r="L912" s="22"/>
+      <c r="L912" s="23"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
       <c r="A913" s="15"/>
       <c r="B913" s="15"/>
-      <c r="L913" s="22"/>
+      <c r="L913" s="23"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
       <c r="A914" s="15"/>
       <c r="B914" s="15"/>
-      <c r="L914" s="22"/>
+      <c r="L914" s="23"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
       <c r="A915" s="15"/>
       <c r="B915" s="15"/>
-      <c r="L915" s="22"/>
+      <c r="L915" s="23"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
       <c r="A916" s="15"/>
       <c r="B916" s="15"/>
-      <c r="L916" s="22"/>
+      <c r="L916" s="23"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
       <c r="A917" s="15"/>
       <c r="B917" s="15"/>
-      <c r="L917" s="22"/>
+      <c r="L917" s="23"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
       <c r="A918" s="15"/>
       <c r="B918" s="15"/>
-      <c r="L918" s="22"/>
+      <c r="L918" s="23"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
       <c r="A919" s="15"/>
       <c r="B919" s="15"/>
-      <c r="L919" s="22"/>
+      <c r="L919" s="23"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
       <c r="A920" s="15"/>
       <c r="B920" s="15"/>
-      <c r="L920" s="22"/>
+      <c r="L920" s="23"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
       <c r="A921" s="15"/>
       <c r="B921" s="15"/>
-      <c r="L921" s="22"/>
+      <c r="L921" s="23"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
       <c r="A922" s="15"/>
       <c r="B922" s="15"/>
-      <c r="L922" s="22"/>
+      <c r="L922" s="23"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
       <c r="A923" s="15"/>
       <c r="B923" s="15"/>
-      <c r="L923" s="22"/>
+      <c r="L923" s="23"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
       <c r="A924" s="15"/>
       <c r="B924" s="15"/>
-      <c r="L924" s="22"/>
+      <c r="L924" s="23"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
       <c r="A925" s="15"/>
       <c r="B925" s="15"/>
-      <c r="L925" s="22"/>
+      <c r="L925" s="23"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
       <c r="A926" s="15"/>
       <c r="B926" s="15"/>
-      <c r="L926" s="22"/>
+      <c r="L926" s="23"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
       <c r="A927" s="15"/>
       <c r="B927" s="15"/>
-      <c r="L927" s="22"/>
+      <c r="L927" s="23"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
       <c r="A928" s="15"/>
       <c r="B928" s="15"/>
-      <c r="L928" s="22"/>
+      <c r="L928" s="23"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
       <c r="A929" s="15"/>
       <c r="B929" s="15"/>
-      <c r="L929" s="22"/>
+      <c r="L929" s="23"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
       <c r="A930" s="15"/>
       <c r="B930" s="15"/>
-      <c r="L930" s="22"/>
+      <c r="L930" s="23"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
       <c r="A931" s="15"/>
       <c r="B931" s="15"/>
-      <c r="L931" s="22"/>
+      <c r="L931" s="23"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
       <c r="A932" s="15"/>
       <c r="B932" s="15"/>
-      <c r="L932" s="22"/>
+      <c r="L932" s="23"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
       <c r="A933" s="15"/>
       <c r="B933" s="15"/>
-      <c r="L933" s="22"/>
+      <c r="L933" s="23"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
       <c r="A934" s="15"/>
       <c r="B934" s="15"/>
-      <c r="L934" s="22"/>
+      <c r="L934" s="23"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
       <c r="A935" s="15"/>
       <c r="B935" s="15"/>
-      <c r="L935" s="22"/>
+      <c r="L935" s="23"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
       <c r="A936" s="15"/>
       <c r="B936" s="15"/>
-      <c r="L936" s="22"/>
+      <c r="L936" s="23"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
       <c r="A937" s="15"/>
       <c r="B937" s="15"/>
-      <c r="L937" s="22"/>
+      <c r="L937" s="23"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
       <c r="A938" s="15"/>
       <c r="B938" s="15"/>
-      <c r="L938" s="22"/>
+      <c r="L938" s="23"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
       <c r="A939" s="15"/>
       <c r="B939" s="15"/>
-      <c r="L939" s="22"/>
+      <c r="L939" s="23"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
       <c r="A940" s="15"/>
       <c r="B940" s="15"/>
-      <c r="L940" s="22"/>
+      <c r="L940" s="23"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
       <c r="A941" s="15"/>
       <c r="B941" s="15"/>
-      <c r="L941" s="22"/>
+      <c r="L941" s="23"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
       <c r="A942" s="15"/>
       <c r="B942" s="15"/>
-      <c r="L942" s="22"/>
+      <c r="L942" s="23"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
       <c r="A943" s="15"/>
       <c r="B943" s="15"/>
-      <c r="L943" s="22"/>
+      <c r="L943" s="23"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
       <c r="A944" s="15"/>
       <c r="B944" s="15"/>
-      <c r="L944" s="22"/>
+      <c r="L944" s="23"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
       <c r="A945" s="15"/>
       <c r="B945" s="15"/>
-      <c r="L945" s="22"/>
+      <c r="L945" s="23"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
       <c r="A946" s="15"/>
       <c r="B946" s="15"/>
-      <c r="L946" s="22"/>
+      <c r="L946" s="23"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
       <c r="A947" s="15"/>
       <c r="B947" s="15"/>
-      <c r="L947" s="22"/>
+      <c r="L947" s="23"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
       <c r="A948" s="15"/>
       <c r="B948" s="15"/>
-      <c r="L948" s="22"/>
+      <c r="L948" s="23"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
       <c r="A949" s="15"/>
       <c r="B949" s="15"/>
-      <c r="L949" s="22"/>
+      <c r="L949" s="23"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
       <c r="A950" s="15"/>
       <c r="B950" s="15"/>
-      <c r="L950" s="22"/>
+      <c r="L950" s="23"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
       <c r="A951" s="15"/>
       <c r="B951" s="15"/>
-      <c r="L951" s="22"/>
+      <c r="L951" s="23"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
       <c r="A952" s="15"/>
       <c r="B952" s="15"/>
-      <c r="L952" s="22"/>
+      <c r="L952" s="23"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
       <c r="A953" s="15"/>
       <c r="B953" s="15"/>
-      <c r="L953" s="22"/>
+      <c r="L953" s="23"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
       <c r="A954" s="15"/>
       <c r="B954" s="15"/>
-      <c r="L954" s="22"/>
+      <c r="L954" s="23"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
       <c r="A955" s="15"/>
       <c r="B955" s="15"/>
-      <c r="L955" s="22"/>
+      <c r="L955" s="23"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
       <c r="A956" s="15"/>
       <c r="B956" s="15"/>
-      <c r="L956" s="22"/>
+      <c r="L956" s="23"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
       <c r="A957" s="15"/>
       <c r="B957" s="15"/>
-      <c r="L957" s="22"/>
+      <c r="L957" s="23"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
       <c r="A958" s="15"/>
       <c r="B958" s="15"/>
-      <c r="L958" s="22"/>
+      <c r="L958" s="23"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
       <c r="A959" s="15"/>
       <c r="B959" s="15"/>
-      <c r="L959" s="22"/>
+      <c r="L959" s="23"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
       <c r="A960" s="15"/>
       <c r="B960" s="15"/>
-      <c r="L960" s="22"/>
+      <c r="L960" s="23"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
       <c r="A961" s="15"/>
       <c r="B961" s="15"/>
-      <c r="L961" s="22"/>
+      <c r="L961" s="23"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
       <c r="A962" s="15"/>
       <c r="B962" s="15"/>
-      <c r="L962" s="22"/>
+      <c r="L962" s="23"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
       <c r="A963" s="15"/>
       <c r="B963" s="15"/>
-      <c r="L963" s="22"/>
+      <c r="L963" s="23"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
       <c r="A964" s="15"/>
       <c r="B964" s="15"/>
-      <c r="L964" s="22"/>
+      <c r="L964" s="23"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
       <c r="A965" s="15"/>
       <c r="B965" s="15"/>
-      <c r="L965" s="22"/>
+      <c r="L965" s="23"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
       <c r="A966" s="15"/>
       <c r="B966" s="15"/>
-      <c r="L966" s="22"/>
+      <c r="L966" s="23"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
       <c r="A967" s="15"/>
       <c r="B967" s="15"/>
-      <c r="L967" s="22"/>
+      <c r="L967" s="23"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
       <c r="A968" s="15"/>
       <c r="B968" s="15"/>
-      <c r="L968" s="22"/>
+      <c r="L968" s="23"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
       <c r="A969" s="15"/>
       <c r="B969" s="15"/>
-      <c r="L969" s="22"/>
+      <c r="L969" s="23"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
       <c r="A970" s="15"/>
       <c r="B970" s="15"/>
-      <c r="L970" s="22"/>
+      <c r="L970" s="23"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
       <c r="A971" s="15"/>
       <c r="B971" s="15"/>
-      <c r="L971" s="22"/>
+      <c r="L971" s="23"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
       <c r="A972" s="15"/>
       <c r="B972" s="15"/>
-      <c r="L972" s="22"/>
+      <c r="L972" s="23"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
       <c r="A973" s="15"/>
       <c r="B973" s="15"/>
-      <c r="L973" s="22"/>
+      <c r="L973" s="23"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
       <c r="A974" s="15"/>
       <c r="B974" s="15"/>
-      <c r="L974" s="22"/>
+      <c r="L974" s="23"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
       <c r="A975" s="15"/>
       <c r="B975" s="15"/>
-      <c r="L975" s="22"/>
+      <c r="L975" s="23"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
       <c r="A976" s="15"/>
       <c r="B976" s="15"/>
-      <c r="L976" s="22"/>
+      <c r="L976" s="23"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
       <c r="A977" s="15"/>
       <c r="B977" s="15"/>
-      <c r="L977" s="22"/>
+      <c r="L977" s="23"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
       <c r="A978" s="15"/>
       <c r="B978" s="15"/>
-      <c r="L978" s="22"/>
+      <c r="L978" s="23"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
       <c r="A979" s="15"/>
       <c r="B979" s="15"/>
-      <c r="L979" s="22"/>
+      <c r="L979" s="23"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
       <c r="A980" s="15"/>
       <c r="B980" s="15"/>
-      <c r="L980" s="22"/>
+      <c r="L980" s="23"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
       <c r="A981" s="15"/>
       <c r="B981" s="15"/>
-      <c r="L981" s="22"/>
+      <c r="L981" s="23"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
       <c r="A982" s="15"/>
       <c r="B982" s="15"/>
-      <c r="L982" s="22"/>
+      <c r="L982" s="23"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
       <c r="A983" s="15"/>
       <c r="B983" s="15"/>
-      <c r="L983" s="22"/>
+      <c r="L983" s="23"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
       <c r="A984" s="15"/>
       <c r="B984" s="15"/>
-      <c r="L984" s="22"/>
+      <c r="L984" s="23"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
       <c r="A985" s="15"/>
       <c r="B985" s="15"/>
-      <c r="L985" s="22"/>
+      <c r="L985" s="23"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
       <c r="A986" s="15"/>
       <c r="B986" s="15"/>
-      <c r="L986" s="22"/>
+      <c r="L986" s="23"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
       <c r="A987" s="15"/>
       <c r="B987" s="15"/>
-      <c r="L987" s="22"/>
+      <c r="L987" s="23"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
       <c r="A988" s="15"/>
       <c r="B988" s="15"/>
-      <c r="L988" s="22"/>
+      <c r="L988" s="23"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
       <c r="A989" s="15"/>
       <c r="B989" s="15"/>
-      <c r="L989" s="22"/>
+      <c r="L989" s="23"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
       <c r="A990" s="15"/>
       <c r="B990" s="15"/>
-      <c r="L990" s="22"/>
+      <c r="L990" s="23"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
       <c r="A991" s="15"/>
       <c r="B991" s="15"/>
-      <c r="L991" s="22"/>
+      <c r="L991" s="23"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
       <c r="A992" s="15"/>
       <c r="B992" s="15"/>
-      <c r="L992" s="22"/>
+      <c r="L992" s="23"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
       <c r="A993" s="15"/>
       <c r="B993" s="15"/>
-      <c r="L993" s="22"/>
+      <c r="L993" s="23"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
       <c r="A994" s="15"/>
       <c r="B994" s="15"/>
-      <c r="L994" s="22"/>
+      <c r="L994" s="23"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
       <c r="A995" s="15"/>
       <c r="B995" s="15"/>
-      <c r="L995" s="22"/>
+      <c r="L995" s="23"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
       <c r="A996" s="15"/>
       <c r="B996" s="15"/>
-      <c r="L996" s="22"/>
+      <c r="L996" s="23"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
       <c r="A997" s="15"/>
       <c r="B997" s="15"/>
-      <c r="L997" s="22"/>
+      <c r="L997" s="23"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
       <c r="A998" s="15"/>
       <c r="B998" s="15"/>
-      <c r="L998" s="22"/>
+      <c r="L998" s="23"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
       <c r="A999" s="15"/>
       <c r="B999" s="15"/>
-      <c r="L999" s="22"/>
+      <c r="L999" s="23"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
       <c r="A1000" s="15"/>
       <c r="B1000" s="15"/>
-      <c r="L1000" s="22"/>
+      <c r="L1000" s="23"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
       <c r="A1001" s="15"/>
       <c r="B1001" s="15"/>
-      <c r="L1001" s="22"/>
+      <c r="L1001" s="23"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
       <c r="A1002" s="15"/>
       <c r="B1002" s="15"/>
-      <c r="L1002" s="22"/>
+      <c r="L1002" s="23"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
       <c r="A1003" s="15"/>
       <c r="B1003" s="15"/>
-      <c r="L1003" s="22"/>
+      <c r="L1003" s="23"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
       <c r="A1004" s="15"/>
       <c r="B1004" s="15"/>
-      <c r="L1004" s="22"/>
+      <c r="L1004" s="23"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
       <c r="A1005" s="15"/>
       <c r="B1005" s="15"/>
-      <c r="L1005" s="22"/>
+      <c r="L1005" s="23"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
       <c r="A1006" s="15"/>
       <c r="B1006" s="15"/>
-      <c r="L1006" s="22"/>
+      <c r="L1006" s="23"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
       <c r="A1007" s="15"/>
       <c r="B1007" s="15"/>
-      <c r="L1007" s="22"/>
+      <c r="L1007" s="23"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
       <c r="A1008" s="15"/>
       <c r="B1008" s="15"/>
-      <c r="L1008" s="22"/>
+      <c r="L1008" s="23"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
       <c r="A1009" s="15"/>
       <c r="B1009" s="15"/>
-      <c r="L1009" s="22"/>
+      <c r="L1009" s="23"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
       <c r="A1010" s="15"/>
       <c r="B1010" s="15"/>
-      <c r="L1010" s="22"/>
+      <c r="L1010" s="23"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
       <c r="A1011" s="15"/>
       <c r="B1011" s="15"/>
-      <c r="L1011" s="22"/>
+      <c r="L1011" s="23"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
       <c r="A1012" s="15"/>
       <c r="B1012" s="15"/>
-      <c r="L1012" s="22"/>
+      <c r="L1012" s="23"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
       <c r="A1013" s="15"/>
       <c r="B1013" s="15"/>
-      <c r="L1013" s="22"/>
+      <c r="L1013" s="23"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
       <c r="A1014" s="15"/>
       <c r="B1014" s="15"/>
-      <c r="L1014" s="22"/>
+      <c r="L1014" s="23"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
       <c r="A1015" s="15"/>
       <c r="B1015" s="15"/>
-      <c r="L1015" s="22"/>
+      <c r="L1015" s="23"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
       <c r="A1016" s="15"/>
       <c r="B1016" s="15"/>
-      <c r="L1016" s="22"/>
+      <c r="L1016" s="23"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
       <c r="A1017" s="15"/>
       <c r="B1017" s="15"/>
-      <c r="L1017" s="22"/>
+      <c r="L1017" s="23"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
       <c r="A1018" s="15"/>
       <c r="B1018" s="15"/>
-      <c r="L1018" s="22"/>
+      <c r="L1018" s="23"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
       <c r="A1019" s="15"/>
       <c r="B1019" s="15"/>
-      <c r="L1019" s="22"/>
+      <c r="L1019" s="23"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
       <c r="A1020" s="15"/>
       <c r="B1020" s="15"/>
-      <c r="L1020" s="22"/>
+      <c r="L1020" s="23"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
       <c r="A1021" s="15"/>
       <c r="B1021" s="15"/>
-      <c r="L1021" s="22"/>
+      <c r="L1021" s="23"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
       <c r="A1022" s="15"/>
       <c r="B1022" s="15"/>
-      <c r="L1022" s="22"/>
+      <c r="L1022" s="23"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
       <c r="A1023" s="15"/>
       <c r="B1023" s="15"/>
-      <c r="L1023" s="22"/>
+      <c r="L1023" s="23"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
       <c r="A1024" s="15"/>
       <c r="B1024" s="15"/>
-      <c r="L1024" s="22"/>
+      <c r="L1024" s="23"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
       <c r="A1025" s="15"/>
       <c r="B1025" s="15"/>
-      <c r="L1025" s="22"/>
+      <c r="L1025" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7898,11 +7898,11 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="4">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>1</v>
+      <c r="L2" s="6" t="s">
+        <v>0</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -7913,40 +7913,40 @@
       <c r="AH2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>2.5E32</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>45686.0</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <v>12.0</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="13">
         <v>1000.0</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="13">
         <v>1000.0</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="8">
         <v>0.0</v>
       </c>
       <c r="AB3" s="2"/>
@@ -7958,40 +7958,40 @@
       <c r="AH3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <v>12.0</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>52250.04</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>52250.04</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="8">
         <v>0.0</v>
       </c>
       <c r="AB4" s="2"/>
@@ -8003,40 +8003,40 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="A5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>12.0</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>881914.18</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>881914.18</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="8">
         <v>0.0</v>
       </c>
       <c r="AB5" s="2"/>
@@ -8048,40 +8048,40 @@
       <c r="AH5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="A6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="8">
         <v>12.0</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>750000.0</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>750000.0</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="8">
         <v>0.0</v>
       </c>
       <c r="AB6" s="2"/>
@@ -8093,40 +8093,40 @@
       <c r="AH6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="A7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="12">
         <v>45763.0</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="8">
         <v>12.0</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="14">
+      <c r="I7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="13">
         <v>949835.78</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>949835.78</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="8">
         <v>0.0</v>
       </c>
       <c r="AB7" s="2"/>
@@ -8138,43 +8138,43 @@
       <c r="AH7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="A8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>45763.0</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="8">
         <v>12.0</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="14">
+      <c r="I8" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="13">
         <v>524584.95</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>524584.95</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="8">
         <v>0.0</v>
       </c>
-      <c r="O8" s="25"/>
+      <c r="O8" s="22"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8184,40 +8184,40 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <v>45792.0</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>12.0</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>211614.23</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>211614.23</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="8">
         <v>0.0</v>
       </c>
       <c r="AB9" s="2"/>
@@ -8229,40 +8229,40 @@
       <c r="AH9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>45825.0</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="8">
         <v>12.0</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="13">
         <v>2391157.42</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="13">
         <v>2391157.41</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="13">
         <v>0.01</v>
       </c>
       <c r="AB10" s="2"/>
@@ -8274,40 +8274,40 @@
       <c r="AH10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="A11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>45825.0</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="8">
         <v>12.0</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <v>618154.39</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="13">
         <v>618154.38</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="8">
         <v>0.01</v>
       </c>
       <c r="AB11" s="2"/>
@@ -8319,40 +8319,40 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="A12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>45832.0</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="8">
         <v>12.0</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J12" s="14">
+      <c r="I12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="13">
         <v>1600334.09</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="13">
         <v>1600334.09</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="8">
         <v>0.0</v>
       </c>
       <c r="AB12" s="2"/>
@@ -8364,43 +8364,43 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>45863.0</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>12.0</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <v>2364771.07</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="13">
         <v>2364771.07</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="13">
         <v>0.0</v>
       </c>
-      <c r="M13" s="34"/>
+      <c r="M13" s="31"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8410,40 +8410,40 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="A14" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>45887.0</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="8">
         <v>12.0</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="13">
         <v>968237.39</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>968237.39</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="8">
         <v>0.0</v>
       </c>
       <c r="AB14" s="2"/>
@@ -8455,40 +8455,40 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="A15" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>45924.0</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="8">
         <v>12.0</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="14">
+      <c r="I15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="13">
         <v>1011677.95</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="13">
         <v>1011677.95</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="8">
         <v>0.0</v>
       </c>
       <c r="AB15" s="2"/>
@@ -8500,40 +8500,40 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>45929.0</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="8">
         <v>12.0</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>1580293.02</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>1580293.02</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="13">
         <v>0.0</v>
       </c>
       <c r="AB16" s="2"/>
@@ -8545,40 +8545,40 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <v>45930.0</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="8">
         <v>12.0</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="13">
         <v>34065.36</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="8">
         <v>0.0</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="13">
         <v>34065.36</v>
       </c>
       <c r="AB17" s="2"/>
@@ -8590,40 +8590,40 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="8">
         <v>12.0</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="13">
         <v>63746.85</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="13">
         <v>63746.85</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="8">
         <v>0.0</v>
       </c>
       <c r="AB18" s="2"/>
@@ -8635,40 +8635,40 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="8">
         <v>12.0</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="14">
+      <c r="I19" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" s="13">
         <v>947931.1</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="13">
         <v>947931.1</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="8">
         <v>0.0</v>
       </c>
       <c r="AB19" s="2"/>
@@ -8680,40 +8680,40 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="10" t="s">
+      <c r="A20" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="8">
         <v>12.0</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="13">
         <v>259790.57</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>259790.57</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="8">
         <v>0.0</v>
       </c>
       <c r="AB20" s="2"/>
@@ -8725,40 +8725,40 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="A21" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="B21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="8">
         <v>12.0</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="13">
         <v>170479.3</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="13">
         <v>170479.3</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="8">
         <v>0.0</v>
       </c>
       <c r="AB21" s="2"/>
@@ -8770,40 +8770,40 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="C22" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="8">
         <v>12.0</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="8">
         <v>2000.0</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="13">
         <v>1500000.0</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="13">
         <v>1500000.0</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="13">
         <v>0.0</v>
       </c>
       <c r="AB22" s="2"/>
@@ -8815,40 +8815,40 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="A23" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="B23" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="8">
         <v>12.0</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="J23" s="14">
+      <c r="I23" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J23" s="13">
         <v>1000001.64</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="13">
         <v>1000001.64</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="8">
         <v>0.0</v>
       </c>
       <c r="AB23" s="2"/>
@@ -8860,40 +8860,40 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="A24" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="8">
         <v>12.0</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="13">
         <v>68405.66</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="13">
         <v>68405.66</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="8">
         <v>0.0</v>
       </c>
       <c r="AB24" s="2"/>
@@ -8905,40 +8905,40 @@
       <c r="AH24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="A25" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="B25" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E25" s="43">
         <v>45975.0</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="8">
         <v>12.0</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="J25" s="14">
+      <c r="I25" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="13">
         <v>1157673.06</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="13">
         <v>1157673.06</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="8">
         <v>0.0</v>
       </c>
       <c r="AB25" s="2"/>
@@ -8950,40 +8950,40 @@
       <c r="AH25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="10" t="s">
+      <c r="A26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="42">
+      <c r="E26" s="43">
         <v>45989.0</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="8">
         <v>12.0</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="13">
         <v>34065.36</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="13">
         <v>34065.36</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="8">
         <v>0.0</v>
       </c>
       <c r="AB26" s="2"/>
@@ -8995,40 +8995,40 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="A27" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="B27" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <v>46104.0</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="8">
         <v>12.0</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="13">
         <v>1770880.5</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="13">
         <v>843261.89</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="13">
         <v>927618.61</v>
       </c>
       <c r="AB27" s="2"/>
@@ -9040,40 +9040,40 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="A28" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="12">
         <v>46120.0</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="8">
         <v>12.0</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I28" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="J28" s="14">
+      <c r="I28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" s="13">
         <v>1912292.52</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="8">
         <v>0.0</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="13">
         <v>1912292.52</v>
       </c>
       <c r="AB28" s="2"/>
@@ -9085,40 +9085,40 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="A29" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <v>46196.0</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="8">
         <v>12.0</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="13">
         <v>1496713.48</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="8">
         <v>0.0</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="13">
         <v>1496713.48</v>
       </c>
       <c r="AB29" s="2"/>
@@ -9130,40 +9130,40 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="A30" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="12">
         <v>46205.0</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="8">
         <v>12.0</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J30" s="14">
+      <c r="I30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="13">
         <v>624166.14</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="8">
         <v>0.0</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="13">
         <v>624166.14</v>
       </c>
       <c r="AB30" s="2"/>
@@ -9175,40 +9175,40 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="A31" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <v>46205.0</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="8">
         <v>12.0</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I31" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="J31" s="14">
+      <c r="I31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J31" s="13">
         <v>18462.36</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="8">
         <v>0.0</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="13">
         <v>18462.36</v>
       </c>
       <c r="AB31" s="2"/>
@@ -9220,40 +9220,40 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="A32" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="12">
         <v>46213.0</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="8">
         <v>12.0</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="J32" s="14">
+      <c r="I32" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J32" s="13">
         <v>1530656.62</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="8">
         <v>0.0</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L32" s="13">
         <v>1530656.62</v>
       </c>
       <c r="AB32" s="2"/>
@@ -9265,40 +9265,40 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="A33" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="12">
         <v>46227.0</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="8">
         <v>12.0</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="8">
         <v>339039.0</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="13">
         <v>173846.38</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="8">
         <v>0.0</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="13">
         <v>173846.38</v>
       </c>
       <c r="AB33" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -57,99 +57,114 @@
     <t>25E0385</t>
   </si>
   <si>
+    <t>Número Contrato</t>
+  </si>
+  <si>
+    <t>UG Executora</t>
+  </si>
+  <si>
+    <t>UG Responsável</t>
+  </si>
+  <si>
+    <t>UG Fiscalizadora</t>
+  </si>
+  <si>
     <t>2025NE000369</t>
   </si>
   <si>
+    <t>Prazo Final de Execução</t>
+  </si>
+  <si>
     <t>C25516</t>
   </si>
   <si>
+    <t>Prazo Final de Vigência</t>
+  </si>
+  <si>
     <t>25E0387</t>
   </si>
   <si>
-    <t>Número Contrato</t>
-  </si>
-  <si>
-    <t>UG Executora</t>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ação</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>Moeda</t>
+  </si>
+  <si>
+    <t>Valor Total do Contrato</t>
+  </si>
+  <si>
+    <t>Valor a Empenhar</t>
+  </si>
+  <si>
+    <t>Valor Empenhado</t>
+  </si>
+  <si>
+    <t>Valor Liquidado</t>
+  </si>
+  <si>
+    <t>Saldo (Valor a Faturar)</t>
+  </si>
+  <si>
+    <t>Fornecedor</t>
+  </si>
+  <si>
+    <t>Tipo Despesa /Receita</t>
+  </si>
+  <si>
+    <t>Abrir</t>
+  </si>
+  <si>
+    <t>Editar</t>
   </si>
   <si>
     <t>2025NE000371</t>
   </si>
   <si>
-    <t>UG Responsável</t>
+    <t>005/CELOG-PAMALS/2025</t>
   </si>
   <si>
     <t>25E0389</t>
   </si>
   <si>
-    <t>UG Fiscalizadora</t>
-  </si>
-  <si>
-    <t>Prazo Final de Execução</t>
-  </si>
-  <si>
-    <t>Prazo Final de Vigência</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ação</t>
-  </si>
-  <si>
-    <t>PAG</t>
+    <t>CELOG</t>
+  </si>
+  <si>
+    <t>PAMALS</t>
+  </si>
+  <si>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
+  </si>
+  <si>
+    <t>67101.001510/2024-12</t>
+  </si>
+  <si>
+    <t>R$</t>
+  </si>
+  <si>
+    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
     <t>2025NE000413</t>
   </si>
   <si>
-    <t>Moeda</t>
-  </si>
-  <si>
     <t>C25501</t>
   </si>
   <si>
     <t>25E0403</t>
   </si>
   <si>
-    <t>Valor Total do Contrato</t>
-  </si>
-  <si>
-    <t>Valor a Empenhar</t>
-  </si>
-  <si>
-    <t>Valor Empenhado</t>
-  </si>
-  <si>
-    <t>Valor Liquidado</t>
-  </si>
-  <si>
-    <t>Saldo (Valor a Faturar)</t>
-  </si>
-  <si>
-    <t>Fornecedor</t>
-  </si>
-  <si>
     <t>20SP</t>
   </si>
   <si>
-    <t>Tipo Despesa /Receita</t>
-  </si>
-  <si>
-    <t>Abrir</t>
-  </si>
-  <si>
-    <t>Editar</t>
-  </si>
-  <si>
-    <t>005/CELOG-PAMALS/2025</t>
-  </si>
-  <si>
-    <t>CELOG</t>
-  </si>
-  <si>
-    <t>PAMALS</t>
-  </si>
-  <si>
     <t>2025NE000414</t>
   </si>
   <si>
@@ -162,19 +177,10 @@
     <t>21EM</t>
   </si>
   <si>
-    <t>Vigente</t>
-  </si>
-  <si>
-    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
-  </si>
-  <si>
-    <t>67101.001510/2024-12</t>
-  </si>
-  <si>
-    <t>R$</t>
-  </si>
-  <si>
-    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>Referência</t>
   </si>
   <si>
     <t>2025NE000559</t>
@@ -186,18 +192,48 @@
     <t>25E0524</t>
   </si>
   <si>
+    <t>Nº recibo</t>
+  </si>
+  <si>
     <t>20X7</t>
   </si>
   <si>
+    <t>Nº</t>
+  </si>
+  <si>
     <t>2025NE000770</t>
   </si>
   <si>
+    <t>Data</t>
+  </si>
+  <si>
     <t>25E0731</t>
   </si>
   <si>
+    <t>Empenho</t>
+  </si>
+  <si>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>Valor das Nfs</t>
+  </si>
+  <si>
+    <t>Ordem de Pagamento</t>
+  </si>
+  <si>
+    <t>Faturado</t>
+  </si>
+  <si>
     <t>2025NE000774</t>
   </si>
   <si>
+    <t>Pendente</t>
+  </si>
+  <si>
     <t>25E0737</t>
   </si>
   <si>
@@ -210,43 +246,25 @@
     <t>25E0787</t>
   </si>
   <si>
-    <t>Módulo</t>
+    <t>FEV/25</t>
   </si>
   <si>
     <t>219C</t>
   </si>
   <si>
-    <t>Referência</t>
+    <t>-</t>
   </si>
   <si>
     <t>2025NE001065</t>
   </si>
   <si>
-    <t>Nº recibo</t>
-  </si>
-  <si>
     <t>25E0999</t>
   </si>
   <si>
-    <t>Nº</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Empenho</t>
-  </si>
-  <si>
-    <t>Observações</t>
-  </si>
-  <si>
-    <t>Vencimento</t>
-  </si>
-  <si>
-    <t>Valor das Nfs</t>
-  </si>
-  <si>
-    <t>Ordem de Pagamento</t>
+    <t xml:space="preserve">2025NE000369 </t>
+  </si>
+  <si>
+    <t>2025NP001980</t>
   </si>
   <si>
     <t>2025NE001200</t>
@@ -255,15 +273,9 @@
     <t>C25590</t>
   </si>
   <si>
-    <t>Faturado</t>
-  </si>
-  <si>
     <t>25E1128</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
     <t>2025NE001598</t>
   </si>
   <si>
@@ -273,24 +285,15 @@
     <t>25E1446</t>
   </si>
   <si>
-    <t>FEV/25</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025NE000369 </t>
-  </si>
-  <si>
     <t>2025NE001627</t>
   </si>
   <si>
+    <t>MAR/25</t>
+  </si>
+  <si>
     <t>25E1475</t>
   </si>
   <si>
-    <t>2025NP001980</t>
-  </si>
-  <si>
     <t>2025NE001629</t>
   </si>
   <si>
@@ -312,94 +315,139 @@
     <t>25E1536</t>
   </si>
   <si>
-    <t>MAR/25</t>
-  </si>
-  <si>
     <t>2025NE001689</t>
   </si>
   <si>
     <t>25E1537</t>
   </si>
   <si>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
+  </si>
+  <si>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
+  </si>
+  <si>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
+  </si>
+  <si>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
+  </si>
+  <si>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
+  </si>
+  <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
   </si>
   <si>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
+  </si>
+  <si>
     <t>2025NP001979</t>
   </si>
   <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
+  </si>
+  <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
+  </si>
+  <si>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
+  </si>
+  <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
+  </si>
+  <si>
+    <t>2026NE000944</t>
+  </si>
+  <si>
+    <t>26E0906</t>
   </si>
   <si>
     <t>ABR/25</t>
   </si>
   <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
-  </si>
-  <si>
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
     <t>2025NP002341</t>
   </si>
   <si>
-    <t>20YJ</t>
-  </si>
-  <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
-  </si>
-  <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
-  </si>
-  <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
-  </si>
-  <si>
     <t>JUN/25</t>
-  </si>
-  <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -411,67 +459,19 @@
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
     <t>JUL/25</t>
   </si>
   <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
     <t>AGO/25</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
     <t>2025NP004558</t>
-  </si>
-  <si>
-    <t>26E0803</t>
-  </si>
-  <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
-    <t>26E0906</t>
   </si>
   <si>
     <t>SET/25</t>
@@ -701,12 +701,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -716,6 +710,12 @@
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -860,15 +860,15 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -879,19 +879,19 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -913,41 +913,40 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -959,21 +958,22 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -990,16 +990,16 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1015,19 +1015,19 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1409,124 +1409,124 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="3"/>
+      <c r="V1" s="4"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="5"/>
+      <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="V2" s="9"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
+      <c r="AA2" s="10"/>
+      <c r="AB2" s="10"/>
+      <c r="AC2" s="10"/>
+      <c r="AD2" s="10"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="3"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="4"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="G4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="J4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="K4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="L4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="M4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="N4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="P4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="S4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="T4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="U4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" s="3"/>
+      <c r="V4" s="4"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1535,16 +1535,16 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N5" s="21">
         <v>9.165159737E7</v>
@@ -1562,248 +1562,248 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="V5" s="3"/>
+        <v>40</v>
+      </c>
+      <c r="V5" s="4"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
-      <c r="L6" s="23"/>
-      <c r="V6" s="3"/>
+      <c r="L6" s="22"/>
+      <c r="V6" s="4"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="28"/>
-      <c r="V7" s="3"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="27"/>
+      <c r="V7" s="4"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="24"/>
-      <c r="B8" s="24"/>
-      <c r="C8" s="29" t="s">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="I8" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="K8" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="29" t="s">
+      <c r="M8" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>71</v>
-      </c>
-      <c r="L8" s="32" t="s">
+      <c r="O8" s="28"/>
+      <c r="P8" s="27"/>
+      <c r="V8" s="4"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="32">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="M8" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="29" t="s">
+      <c r="E9" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="35">
+        <v>594.0</v>
+      </c>
+      <c r="G9" s="36">
+        <v>45740.0</v>
+      </c>
+      <c r="H9" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="28"/>
-      <c r="V8" s="3"/>
-    </row>
-    <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="33">
-        <v>1.0</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="36">
-        <v>594.0</v>
-      </c>
-      <c r="G9" s="37">
-        <v>45740.0</v>
-      </c>
-      <c r="H9" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37">
+      <c r="I9" s="36"/>
+      <c r="J9" s="36">
         <v>45778.0</v>
       </c>
       <c r="K9" s="38">
         <v>748504.24</v>
       </c>
-      <c r="L9" s="36" t="s">
-        <v>86</v>
+      <c r="L9" s="35" t="s">
+        <v>78</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
       <c r="N9" s="40"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="28"/>
-      <c r="V9" s="3"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="27"/>
+      <c r="V9" s="4"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="41"/>
-      <c r="D10" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F10" s="36">
+      <c r="D10" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="35">
         <v>620.0</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="36">
         <v>45775.0</v>
       </c>
-      <c r="H10" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37">
+      <c r="H10" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36">
         <v>45806.0</v>
       </c>
       <c r="K10" s="38">
         <v>1110378.24</v>
       </c>
-      <c r="L10" s="36" t="s">
-        <v>98</v>
+      <c r="L10" s="35" t="s">
+        <v>114</v>
       </c>
       <c r="M10" s="39">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
-      <c r="N10" s="42"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="28"/>
-      <c r="V10" s="3"/>
+      <c r="N10" s="43"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="27"/>
+      <c r="V10" s="4"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="41"/>
-      <c r="D11" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="36">
+      <c r="D11" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="35">
         <v>634.0</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <v>45799.0</v>
       </c>
-      <c r="H11" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37">
+      <c r="H11" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36">
         <v>45844.0</v>
       </c>
       <c r="K11" s="38">
         <v>974557.12</v>
       </c>
-      <c r="L11" s="35" t="s">
-        <v>109</v>
+      <c r="L11" s="34" t="s">
+        <v>136</v>
       </c>
       <c r="M11" s="39">
         <v>974557.12</v>
       </c>
-      <c r="N11" s="42"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="28"/>
-      <c r="V11" s="3"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="27"/>
+      <c r="V11" s="4"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
       <c r="C12" s="41"/>
-      <c r="D12" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="35">
+      <c r="D12" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="34">
         <v>660.0</v>
       </c>
       <c r="G12" s="44">
         <v>45856.0</v>
       </c>
       <c r="H12" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37">
+        <v>69</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36">
         <v>45891.0</v>
       </c>
       <c r="K12" s="46">
         <v>1402001.34</v>
       </c>
       <c r="L12" s="47" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
       <c r="N12" s="48"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="28"/>
-      <c r="V12" s="3"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="27"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
+      <c r="A13" s="23"/>
+      <c r="B13" s="23"/>
       <c r="C13" s="41"/>
       <c r="D13" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="36">
+        <v>139</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" s="35">
         <v>661.0</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <v>45856.0</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>124</v>
+      <c r="H13" s="35" t="s">
+        <v>140</v>
       </c>
       <c r="I13" s="44"/>
       <c r="J13" s="44">
@@ -1812,35 +1812,35 @@
       <c r="K13" s="46">
         <v>1223702.3</v>
       </c>
-      <c r="L13" s="35" t="s">
-        <v>125</v>
+      <c r="L13" s="34" t="s">
+        <v>141</v>
       </c>
       <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
       <c r="N13" s="48"/>
-      <c r="O13" s="26"/>
+      <c r="O13" s="25"/>
       <c r="P13" s="50"/>
-      <c r="V13" s="3"/>
+      <c r="V13" s="4"/>
     </row>
     <row r="14">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
       <c r="C14" s="41"/>
       <c r="D14" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="35">
+        <v>142</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="34">
         <v>688.0</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="36">
         <v>45901.0</v>
       </c>
-      <c r="H14" s="35" t="s">
-        <v>133</v>
+      <c r="H14" s="34" t="s">
+        <v>143</v>
       </c>
       <c r="I14" s="44"/>
       <c r="J14" s="44">
@@ -1849,35 +1849,35 @@
       <c r="K14" s="46">
         <v>1011677.95</v>
       </c>
-      <c r="L14" s="35" t="s">
-        <v>134</v>
+      <c r="L14" s="34" t="s">
+        <v>144</v>
       </c>
       <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
-      <c r="N14" s="42"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="28"/>
-      <c r="V14" s="3"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="27"/>
+      <c r="V14" s="4"/>
     </row>
     <row r="15">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="41"/>
       <c r="D15" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" s="35">
+        <v>145</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="34">
         <v>696.0</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="36">
         <v>45923.0</v>
       </c>
-      <c r="H15" s="35" t="s">
-        <v>73</v>
+      <c r="H15" s="34" t="s">
+        <v>79</v>
       </c>
       <c r="I15" s="44"/>
       <c r="J15" s="44">
@@ -1886,33 +1886,33 @@
       <c r="K15" s="46">
         <v>896744.06</v>
       </c>
-      <c r="L15" s="35" t="s">
-        <v>143</v>
+      <c r="L15" s="34" t="s">
+        <v>146</v>
       </c>
       <c r="M15" s="39">
         <v>896744.06</v>
       </c>
       <c r="N15" s="48"/>
-      <c r="O15" s="26"/>
-      <c r="V15" s="3"/>
+      <c r="O15" s="25"/>
+      <c r="V15" s="4"/>
     </row>
     <row r="16">
-      <c r="A16" s="24"/>
-      <c r="B16" s="24"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="41"/>
       <c r="D16" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="E16" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="35">
+      <c r="E16" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="34">
         <v>704.0</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="36">
         <v>45957.0</v>
       </c>
-      <c r="H16" s="35" t="s">
+      <c r="H16" s="34" t="s">
         <v>148</v>
       </c>
       <c r="I16" s="44"/>
@@ -1922,107 +1922,107 @@
       <c r="K16" s="46">
         <v>919329.06</v>
       </c>
-      <c r="L16" s="35" t="s">
+      <c r="L16" s="34" t="s">
         <v>149</v>
       </c>
       <c r="M16" s="39">
         <v>919329.06</v>
       </c>
-      <c r="N16" s="42"/>
-      <c r="O16" s="26"/>
-      <c r="V16" s="3"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="25"/>
+      <c r="V16" s="4"/>
     </row>
     <row r="17">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="41"/>
       <c r="D17" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35">
+      <c r="E17" s="34"/>
+      <c r="F17" s="34">
         <v>705.0</v>
       </c>
       <c r="G17" s="44">
         <v>45972.0</v>
       </c>
-      <c r="H17" s="35" t="s">
+      <c r="H17" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="I17" s="35"/>
+      <c r="I17" s="34"/>
       <c r="J17" s="44">
         <v>46016.0</v>
       </c>
       <c r="K17" s="46">
         <v>1157009.26</v>
       </c>
-      <c r="L17" s="35" t="s">
+      <c r="L17" s="34" t="s">
         <v>152</v>
       </c>
       <c r="M17" s="39">
         <v>1157009.26</v>
       </c>
       <c r="N17" s="51"/>
-      <c r="O17" s="26"/>
-      <c r="V17" s="3"/>
+      <c r="O17" s="25"/>
+      <c r="V17" s="4"/>
     </row>
     <row r="18">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="41"/>
       <c r="D18" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="E18" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="35">
+      <c r="E18" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="34">
         <v>728.0</v>
       </c>
       <c r="G18" s="44">
         <v>46008.0</v>
       </c>
-      <c r="H18" s="35" t="s">
+      <c r="H18" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="I18" s="35"/>
+      <c r="I18" s="34"/>
       <c r="J18" s="44">
         <v>46040.0</v>
       </c>
       <c r="K18" s="46">
         <v>1214597.952</v>
       </c>
-      <c r="L18" s="35" t="s">
+      <c r="L18" s="34" t="s">
         <v>155</v>
       </c>
       <c r="M18" s="39">
         <v>1214597.952</v>
       </c>
       <c r="N18" s="51"/>
-      <c r="O18" s="26"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
+      <c r="O18" s="25"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
       <c r="V18" s="52"/>
     </row>
     <row r="19">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
+      <c r="A19" s="23"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="41"/>
       <c r="D19" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="E19" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" s="35">
+      <c r="E19" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="34">
         <v>278.0</v>
       </c>
       <c r="G19" s="44">
         <v>46042.0</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="34" t="s">
         <v>157</v>
       </c>
       <c r="I19" s="44"/>
@@ -2032,36 +2032,36 @@
       <c r="K19" s="46">
         <v>967082.09</v>
       </c>
-      <c r="L19" s="35" t="s">
+      <c r="L19" s="34" t="s">
         <v>158</v>
       </c>
       <c r="M19" s="39">
         <v>967082.09</v>
       </c>
       <c r="N19" s="51"/>
-      <c r="O19" s="26"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
+      <c r="O19" s="25"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
       <c r="V19" s="52"/>
     </row>
     <row r="20">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
       <c r="C20" s="41"/>
       <c r="D20" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35">
+      <c r="E20" s="34"/>
+      <c r="F20" s="34">
         <v>10.0</v>
       </c>
       <c r="G20" s="44">
         <v>46078.0</v>
       </c>
-      <c r="H20" s="35" t="s">
-        <v>102</v>
+      <c r="H20" s="34" t="s">
+        <v>99</v>
       </c>
       <c r="I20" s="44"/>
       <c r="J20" s="44">
@@ -2070,35 +2070,35 @@
       <c r="K20" s="46">
         <v>719561.08</v>
       </c>
-      <c r="L20" s="35" t="s">
+      <c r="L20" s="34" t="s">
         <v>160</v>
       </c>
       <c r="M20" s="39">
         <v>719561.08</v>
       </c>
       <c r="N20" s="51"/>
-      <c r="O20" s="26"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
+      <c r="O20" s="25"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
       <c r="V20" s="52"/>
     </row>
     <row r="21">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="41"/>
       <c r="D21" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35">
+      <c r="E21" s="34"/>
+      <c r="F21" s="34">
         <v>15.0</v>
       </c>
       <c r="G21" s="44">
         <v>46094.0</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="34" t="s">
         <v>162</v>
       </c>
       <c r="I21" s="44"/>
@@ -2108,35 +2108,35 @@
       <c r="K21" s="46">
         <v>885881.08</v>
       </c>
-      <c r="L21" s="35" t="s">
+      <c r="L21" s="34" t="s">
         <v>163</v>
       </c>
       <c r="M21" s="39">
         <v>885881.08</v>
       </c>
       <c r="N21" s="51"/>
-      <c r="O21" s="26"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="28"/>
+      <c r="O21" s="25"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
       <c r="V21" s="52"/>
     </row>
     <row r="22">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
       <c r="C22" s="41"/>
       <c r="D22" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35">
+      <c r="E22" s="34"/>
+      <c r="F22" s="34">
         <v>28.0</v>
       </c>
       <c r="G22" s="44">
         <v>46128.0</v>
       </c>
-      <c r="H22" s="35" t="s">
+      <c r="H22" s="34" t="s">
         <v>165</v>
       </c>
       <c r="I22" s="44"/>
@@ -2146,35 +2146,35 @@
       <c r="K22" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="35" t="s">
+      <c r="L22" s="34" t="s">
         <v>167</v>
       </c>
       <c r="M22" s="39" t="s">
         <v>166</v>
       </c>
       <c r="N22" s="51"/>
-      <c r="O22" s="26"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
+      <c r="O22" s="25"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
       <c r="V22" s="52"/>
     </row>
     <row r="23">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
       <c r="C23" s="41"/>
       <c r="D23" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35">
+      <c r="E23" s="34"/>
+      <c r="F23" s="34">
         <v>33.0</v>
       </c>
       <c r="G23" s="44">
         <v>46156.0</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H23" s="34" t="s">
         <v>169</v>
       </c>
       <c r="I23" s="44"/>
@@ -2184,35 +2184,35 @@
       <c r="K23" s="46">
         <v>1108954.4358333333</v>
       </c>
-      <c r="L23" s="35" t="s">
+      <c r="L23" s="34" t="s">
         <v>163</v>
       </c>
       <c r="M23" s="39">
         <v>1108954.4358333333</v>
       </c>
       <c r="N23" s="53"/>
-      <c r="O23" s="26"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
+      <c r="O23" s="25"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
       <c r="V23" s="52"/>
     </row>
     <row r="24">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
       <c r="C24" s="41"/>
       <c r="D24" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35">
+      <c r="E24" s="34"/>
+      <c r="F24" s="34">
         <v>29.0</v>
       </c>
       <c r="G24" s="44">
         <v>46149.0</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="34" t="s">
         <v>169</v>
       </c>
       <c r="I24" s="44"/>
@@ -2222,28 +2222,28 @@
       <c r="K24" s="46">
         <v>218206.1</v>
       </c>
-      <c r="L24" s="35" t="s">
+      <c r="L24" s="34" t="s">
         <v>171</v>
       </c>
       <c r="M24" s="39">
         <v>218206.1</v>
       </c>
       <c r="N24" s="54"/>
-      <c r="O24" s="26"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
+      <c r="O24" s="25"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
       <c r="V24" s="52"/>
     </row>
     <row r="25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="41"/>
       <c r="D25" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="35"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="55">
         <v>40.0</v>
       </c>
@@ -2260,148 +2260,148 @@
       <c r="K25" s="46">
         <v>1549250.84</v>
       </c>
-      <c r="L25" s="35" t="s">
+      <c r="L25" s="34" t="s">
         <v>173</v>
       </c>
       <c r="M25" s="39">
         <v>1549250.84</v>
       </c>
       <c r="N25" s="53"/>
-      <c r="O25" s="26"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
+      <c r="O25" s="25"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
       <c r="V25" s="52"/>
     </row>
     <row r="26">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
       <c r="C26" s="57"/>
       <c r="D26" s="49" t="s">
         <v>174</v>
       </c>
-      <c r="E26" s="35"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="55"/>
       <c r="G26" s="44"/>
       <c r="H26" s="55"/>
       <c r="I26" s="44"/>
       <c r="J26" s="56"/>
       <c r="K26" s="46"/>
-      <c r="L26" s="35" t="s">
-        <v>75</v>
+      <c r="L26" s="34" t="s">
+        <v>65</v>
       </c>
       <c r="M26" s="39" t="s">
         <v>175</v>
       </c>
       <c r="N26" s="53"/>
-      <c r="O26" s="26"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
+      <c r="O26" s="25"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="29" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="30" t="s">
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="L27" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="L27" s="32" t="s">
-        <v>72</v>
-      </c>
       <c r="M27" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="N27" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="O27" s="26"/>
-      <c r="P27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
+        <v>65</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="O27" s="25"/>
+      <c r="P27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
       <c r="V27" s="52"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="28"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="28"/>
-      <c r="AB27" s="28"/>
-      <c r="AC27" s="28"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="33">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="32">
         <v>2.0</v>
       </c>
       <c r="D28" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36">
+      <c r="E28" s="35"/>
+      <c r="F28" s="35">
         <v>402.0</v>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="36">
         <v>45791.0</v>
       </c>
-      <c r="H28" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37">
+      <c r="H28" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36">
         <v>45834.0</v>
       </c>
       <c r="K28" s="38">
         <v>188246.17</v>
       </c>
-      <c r="L28" s="35" t="s">
+      <c r="L28" s="34" t="s">
         <v>177</v>
       </c>
       <c r="M28" s="61">
         <v>188246.17</v>
       </c>
       <c r="N28" s="51"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
       <c r="V28" s="52"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="28"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="28"/>
-      <c r="AC28" s="28"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
     </row>
     <row r="29">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
       <c r="C29" s="41"/>
       <c r="D29" s="60" t="s">
         <v>178</v>
@@ -2409,13 +2409,13 @@
       <c r="E29" s="55">
         <v>46.0</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="35">
         <v>447.0</v>
       </c>
-      <c r="G29" s="37">
+      <c r="G29" s="36">
         <v>45814.0</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H29" s="34" t="s">
         <v>179</v>
       </c>
       <c r="I29" s="44"/>
@@ -2425,32 +2425,32 @@
       <c r="K29" s="38">
         <v>112720.77</v>
       </c>
-      <c r="L29" s="35" t="s">
+      <c r="L29" s="34" t="s">
         <v>180</v>
       </c>
       <c r="M29" s="39">
         <v>112720.77</v>
       </c>
       <c r="N29" s="51"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
       <c r="V29" s="52"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="24"/>
-      <c r="B30" s="24"/>
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
       <c r="C30" s="41"/>
       <c r="D30" s="62" t="s">
         <v>181</v>
@@ -2458,14 +2458,14 @@
       <c r="E30" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="35">
         <v>529.0</v>
       </c>
       <c r="G30" s="64">
         <v>45853.0</v>
       </c>
-      <c r="H30" s="35" t="s">
-        <v>53</v>
+      <c r="H30" s="34" t="s">
+        <v>57</v>
       </c>
       <c r="I30" s="44"/>
       <c r="J30" s="44">
@@ -2474,32 +2474,32 @@
       <c r="K30" s="46">
         <v>378307.61</v>
       </c>
-      <c r="L30" s="35" t="s">
+      <c r="L30" s="34" t="s">
         <v>183</v>
       </c>
       <c r="M30" s="39">
         <v>378307.61</v>
       </c>
       <c r="N30" s="51"/>
-      <c r="O30" s="26"/>
+      <c r="O30" s="25"/>
       <c r="P30" s="65"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="28"/>
-      <c r="U30" s="28"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
       <c r="V30" s="52"/>
-      <c r="W30" s="28"/>
-      <c r="X30" s="28"/>
-      <c r="Y30" s="28"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="28"/>
-      <c r="AB30" s="28"/>
-      <c r="AC30" s="28"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="27"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="27"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
-      <c r="A31" s="24"/>
-      <c r="B31" s="24"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
       <c r="C31" s="41"/>
       <c r="D31" s="62" t="s">
         <v>184</v>
@@ -2507,14 +2507,14 @@
       <c r="E31" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="34">
         <v>691.0</v>
       </c>
       <c r="G31" s="64">
         <v>45910.0</v>
       </c>
-      <c r="H31" s="35" t="s">
-        <v>53</v>
+      <c r="H31" s="34" t="s">
+        <v>57</v>
       </c>
       <c r="I31" s="44"/>
       <c r="J31" s="44">
@@ -2523,32 +2523,32 @@
       <c r="K31" s="38">
         <v>3315.0471000000252</v>
       </c>
-      <c r="L31" s="35" t="s">
+      <c r="L31" s="34" t="s">
         <v>185</v>
       </c>
       <c r="M31" s="39">
         <v>3315.04710000003</v>
       </c>
       <c r="N31" s="51"/>
-      <c r="O31" s="26"/>
+      <c r="O31" s="25"/>
       <c r="P31" s="65"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
       <c r="V31" s="52"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="28"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="28"/>
-      <c r="AC31" s="28"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="27"/>
+      <c r="AB31" s="27"/>
+      <c r="AC31" s="27"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
       <c r="C32" s="41"/>
       <c r="D32" s="62" t="s">
         <v>186</v>
@@ -2556,14 +2556,14 @@
       <c r="E32" s="66">
         <v>135.0</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="34">
         <v>677.0</v>
       </c>
       <c r="G32" s="64">
         <v>45904.0</v>
       </c>
-      <c r="H32" s="35" t="s">
-        <v>57</v>
+      <c r="H32" s="34" t="s">
+        <v>69</v>
       </c>
       <c r="I32" s="67"/>
       <c r="J32" s="67">
@@ -2572,32 +2572,32 @@
       <c r="K32" s="46">
         <v>198332.75</v>
       </c>
-      <c r="L32" s="35" t="s">
+      <c r="L32" s="34" t="s">
         <v>187</v>
       </c>
       <c r="M32" s="39">
         <v>198332.75</v>
       </c>
       <c r="N32" s="51"/>
-      <c r="O32" s="26"/>
+      <c r="O32" s="25"/>
       <c r="P32" s="65"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
       <c r="V32" s="52"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="27"/>
+      <c r="AB32" s="27"/>
+      <c r="AC32" s="27"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
       <c r="C33" s="41"/>
       <c r="D33" s="62" t="s">
         <v>188</v>
@@ -2605,14 +2605,14 @@
       <c r="E33" s="66">
         <v>40.0</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="34">
         <v>278.0</v>
       </c>
       <c r="G33" s="64">
         <v>46008.0</v>
       </c>
-      <c r="H33" s="35" t="s">
-        <v>114</v>
+      <c r="H33" s="34" t="s">
+        <v>108</v>
       </c>
       <c r="I33" s="67"/>
       <c r="J33" s="67">
@@ -2628,25 +2628,25 @@
         <v>190</v>
       </c>
       <c r="N33" s="51"/>
-      <c r="O33" s="26"/>
+      <c r="O33" s="25"/>
       <c r="P33" s="65"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="27"/>
       <c r="V33" s="52"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="28"/>
-      <c r="Y33" s="28"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="28"/>
-      <c r="AB33" s="28"/>
-      <c r="AC33" s="28"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27"/>
+      <c r="Y33" s="27"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="27"/>
+      <c r="AB33" s="27"/>
+      <c r="AC33" s="27"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
       <c r="C34" s="41"/>
       <c r="D34" s="62" t="s">
         <v>191</v>
@@ -2654,14 +2654,14 @@
       <c r="E34" s="66" t="s">
         <v>192</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="34">
         <v>748.0</v>
       </c>
       <c r="G34" s="64">
         <v>45930.0</v>
       </c>
-      <c r="H34" s="35" t="s">
-        <v>90</v>
+      <c r="H34" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="I34" s="67"/>
       <c r="J34" s="67">
@@ -2670,32 +2670,32 @@
       <c r="K34" s="46">
         <v>38718.58</v>
       </c>
-      <c r="L34" s="35" t="s">
+      <c r="L34" s="34" t="s">
         <v>193</v>
       </c>
       <c r="M34" s="61" t="s">
         <v>194</v>
       </c>
       <c r="N34" s="51"/>
-      <c r="O34" s="26"/>
+      <c r="O34" s="25"/>
       <c r="P34" s="65"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="27"/>
       <c r="V34" s="52"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="28"/>
-      <c r="Y34" s="28"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="28"/>
-      <c r="AB34" s="28"/>
-      <c r="AC34" s="28"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="27"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="27"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
       <c r="C35" s="41"/>
       <c r="D35" s="62" t="s">
         <v>195</v>
@@ -2703,14 +2703,14 @@
       <c r="E35" s="66">
         <v>154.0</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="34">
         <v>822.0</v>
       </c>
       <c r="G35" s="64">
         <v>45968.0</v>
       </c>
-      <c r="H35" s="35" t="s">
-        <v>106</v>
+      <c r="H35" s="34" t="s">
+        <v>102</v>
       </c>
       <c r="I35" s="67"/>
       <c r="J35" s="67">
@@ -2719,32 +2719,32 @@
       <c r="K35" s="46">
         <v>133124.11</v>
       </c>
-      <c r="L35" s="35" t="s">
+      <c r="L35" s="34" t="s">
         <v>196</v>
       </c>
       <c r="M35" s="61" t="s">
         <v>197</v>
       </c>
       <c r="N35" s="51"/>
-      <c r="O35" s="26"/>
+      <c r="O35" s="25"/>
       <c r="P35" s="65"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="27"/>
       <c r="V35" s="52"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="28"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="27"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="27"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
       <c r="C36" s="41"/>
       <c r="D36" s="62" t="s">
         <v>198</v>
@@ -2759,7 +2759,7 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="66" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I36" s="71"/>
       <c r="J36" s="70">
@@ -2768,32 +2768,32 @@
       <c r="K36" s="46">
         <v>11372.9</v>
       </c>
-      <c r="L36" s="35" t="s">
+      <c r="L36" s="34" t="s">
         <v>199</v>
       </c>
       <c r="M36" s="39">
         <v>11372.9</v>
       </c>
       <c r="N36" s="51"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="27"/>
       <c r="V36" s="52"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
-      <c r="AC36" s="28"/>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
+      <c r="Z36" s="27"/>
+      <c r="AA36" s="27"/>
+      <c r="AB36" s="27"/>
+      <c r="AC36" s="27"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
       <c r="C37" s="41"/>
       <c r="D37" s="62" t="s">
         <v>200</v>
@@ -2807,30 +2807,30 @@
       </c>
       <c r="J37" s="70"/>
       <c r="K37" s="46"/>
-      <c r="L37" s="35"/>
+      <c r="L37" s="34"/>
       <c r="M37" s="39"/>
       <c r="N37" s="51">
         <v>15854.78</v>
       </c>
-      <c r="O37" s="26"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
       <c r="V37" s="52"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="24"/>
-      <c r="B38" s="24"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
       <c r="C38" s="57"/>
       <c r="D38" s="62" t="s">
         <v>202</v>
@@ -2844,31 +2844,31 @@
       </c>
       <c r="J38" s="70"/>
       <c r="K38" s="46"/>
-      <c r="L38" s="35"/>
+      <c r="L38" s="34"/>
       <c r="M38" s="39"/>
       <c r="N38" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="O38" s="26"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
       <c r="V38" s="52"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
-      <c r="Y38" s="28"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
-      <c r="AB38" s="28"/>
-      <c r="AC38" s="28"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27"/>
+      <c r="Y38" s="27"/>
+      <c r="Z38" s="27"/>
+      <c r="AA38" s="27"/>
+      <c r="AB38" s="27"/>
+      <c r="AC38" s="27"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="33">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="32">
         <v>3.0</v>
       </c>
       <c r="D39" s="62" t="s">
@@ -2882,7 +2882,7 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="66" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I39" s="71"/>
       <c r="J39" s="70">
@@ -2898,21 +2898,21 @@
         <v>27801.11</v>
       </c>
       <c r="N39" s="51"/>
-      <c r="O39" s="26"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27"/>
       <c r="V39" s="52"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
+      <c r="W39" s="27"/>
+      <c r="X39" s="27"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="27"/>
+      <c r="AA39" s="27"/>
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="27"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="15"/>
@@ -2929,7 +2929,7 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="66" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="I40" s="71"/>
       <c r="J40" s="70">
@@ -2938,14 +2938,14 @@
       <c r="K40" s="46">
         <v>58868.35</v>
       </c>
-      <c r="L40" s="35" t="s">
-        <v>75</v>
+      <c r="L40" s="34" t="s">
+        <v>65</v>
       </c>
       <c r="M40" s="73">
         <v>58868.35</v>
       </c>
       <c r="N40" s="51"/>
-      <c r="V40" s="3"/>
+      <c r="V40" s="4"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="15"/>
@@ -2953,7 +2953,7 @@
       <c r="C41" s="41"/>
       <c r="K41" s="74"/>
       <c r="M41" s="74"/>
-      <c r="V41" s="3"/>
+      <c r="V41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="15"/>
@@ -2961,31 +2961,31 @@
       <c r="C42" s="41"/>
       <c r="K42" s="74"/>
       <c r="M42" s="74"/>
-      <c r="V42" s="3"/>
+      <c r="V42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
       <c r="C43" s="41"/>
-      <c r="V43" s="3"/>
+      <c r="V43" s="4"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
       <c r="C44" s="41"/>
-      <c r="V44" s="3"/>
+      <c r="V44" s="4"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
       <c r="C45" s="41"/>
-      <c r="V45" s="3"/>
+      <c r="V45" s="4"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
       <c r="C46" s="41"/>
-      <c r="V46" s="3"/>
+      <c r="V46" s="4"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="15"/>
@@ -2993,7 +2993,7 @@
       <c r="C47" s="57"/>
       <c r="K47" s="74"/>
       <c r="M47" s="74"/>
-      <c r="V47" s="3"/>
+      <c r="V47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="15"/>
@@ -3017,7 +3017,7 @@
       <c r="S48" s="75"/>
       <c r="T48" s="75"/>
       <c r="U48" s="75"/>
-      <c r="V48" s="3"/>
+      <c r="V48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="15"/>
@@ -3234,4622 +3234,4622 @@
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="15"/>
       <c r="B102" s="15"/>
-      <c r="L102" s="23"/>
+      <c r="L102" s="22"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="15"/>
       <c r="B103" s="15"/>
-      <c r="L103" s="23"/>
+      <c r="L103" s="22"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="15"/>
       <c r="B104" s="15"/>
-      <c r="L104" s="23"/>
+      <c r="L104" s="22"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="15"/>
       <c r="B105" s="15"/>
-      <c r="L105" s="23"/>
+      <c r="L105" s="22"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
-      <c r="L106" s="23"/>
+      <c r="L106" s="22"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
-      <c r="L107" s="23"/>
+      <c r="L107" s="22"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="15"/>
       <c r="B108" s="15"/>
-      <c r="L108" s="23"/>
+      <c r="L108" s="22"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="15"/>
       <c r="B109" s="15"/>
-      <c r="L109" s="23"/>
+      <c r="L109" s="22"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="15"/>
       <c r="B110" s="15"/>
-      <c r="L110" s="23"/>
+      <c r="L110" s="22"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="15"/>
       <c r="B111" s="15"/>
-      <c r="L111" s="23"/>
+      <c r="L111" s="22"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="15"/>
       <c r="B112" s="15"/>
-      <c r="L112" s="23"/>
+      <c r="L112" s="22"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
-      <c r="L113" s="23"/>
+      <c r="L113" s="22"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="15"/>
       <c r="B114" s="15"/>
-      <c r="L114" s="23"/>
+      <c r="L114" s="22"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="15"/>
       <c r="B115" s="15"/>
-      <c r="L115" s="23"/>
+      <c r="L115" s="22"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
-      <c r="L116" s="23"/>
+      <c r="L116" s="22"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="15"/>
       <c r="B117" s="15"/>
-      <c r="L117" s="23"/>
+      <c r="L117" s="22"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="15"/>
       <c r="B118" s="15"/>
-      <c r="L118" s="23"/>
+      <c r="L118" s="22"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="15"/>
       <c r="B119" s="15"/>
-      <c r="L119" s="23"/>
+      <c r="L119" s="22"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="15"/>
       <c r="B120" s="15"/>
-      <c r="L120" s="23"/>
+      <c r="L120" s="22"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="15"/>
       <c r="B121" s="15"/>
-      <c r="L121" s="23"/>
+      <c r="L121" s="22"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
-      <c r="L122" s="23"/>
+      <c r="L122" s="22"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="15"/>
       <c r="B123" s="15"/>
-      <c r="L123" s="23"/>
+      <c r="L123" s="22"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="15"/>
       <c r="B124" s="15"/>
-      <c r="L124" s="23"/>
+      <c r="L124" s="22"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="15"/>
       <c r="B125" s="15"/>
-      <c r="L125" s="23"/>
+      <c r="L125" s="22"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="15"/>
       <c r="B126" s="15"/>
-      <c r="L126" s="23"/>
+      <c r="L126" s="22"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="15"/>
       <c r="B127" s="15"/>
-      <c r="L127" s="23"/>
+      <c r="L127" s="22"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="15"/>
       <c r="B128" s="15"/>
-      <c r="L128" s="23"/>
+      <c r="L128" s="22"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="15"/>
       <c r="B129" s="15"/>
-      <c r="L129" s="23"/>
+      <c r="L129" s="22"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="15"/>
       <c r="B130" s="15"/>
-      <c r="L130" s="23"/>
+      <c r="L130" s="22"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="15"/>
       <c r="B131" s="15"/>
-      <c r="L131" s="23"/>
+      <c r="L131" s="22"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="15"/>
       <c r="B132" s="15"/>
-      <c r="L132" s="23"/>
+      <c r="L132" s="22"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="15"/>
       <c r="B133" s="15"/>
-      <c r="L133" s="23"/>
+      <c r="L133" s="22"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
-      <c r="L134" s="23"/>
+      <c r="L134" s="22"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="15"/>
       <c r="B135" s="15"/>
-      <c r="L135" s="23"/>
+      <c r="L135" s="22"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
-      <c r="L136" s="23"/>
+      <c r="L136" s="22"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="15"/>
       <c r="B137" s="15"/>
-      <c r="L137" s="23"/>
+      <c r="L137" s="22"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="15"/>
       <c r="B138" s="15"/>
-      <c r="L138" s="23"/>
+      <c r="L138" s="22"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="15"/>
       <c r="B139" s="15"/>
-      <c r="L139" s="23"/>
+      <c r="L139" s="22"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
-      <c r="L140" s="23"/>
+      <c r="L140" s="22"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="15"/>
       <c r="B141" s="15"/>
-      <c r="L141" s="23"/>
+      <c r="L141" s="22"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="15"/>
       <c r="B142" s="15"/>
-      <c r="L142" s="23"/>
+      <c r="L142" s="22"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="15"/>
       <c r="B143" s="15"/>
-      <c r="L143" s="23"/>
+      <c r="L143" s="22"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="15"/>
       <c r="B144" s="15"/>
-      <c r="L144" s="23"/>
+      <c r="L144" s="22"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="15"/>
       <c r="B145" s="15"/>
-      <c r="L145" s="23"/>
+      <c r="L145" s="22"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
-      <c r="L146" s="23"/>
+      <c r="L146" s="22"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="15"/>
       <c r="B147" s="15"/>
-      <c r="L147" s="23"/>
+      <c r="L147" s="22"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="15"/>
       <c r="B148" s="15"/>
-      <c r="L148" s="23"/>
+      <c r="L148" s="22"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="15"/>
       <c r="B149" s="15"/>
-      <c r="L149" s="23"/>
+      <c r="L149" s="22"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="15"/>
       <c r="B150" s="15"/>
-      <c r="L150" s="23"/>
+      <c r="L150" s="22"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="15"/>
       <c r="B151" s="15"/>
-      <c r="L151" s="23"/>
+      <c r="L151" s="22"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="15"/>
       <c r="B152" s="15"/>
-      <c r="L152" s="23"/>
+      <c r="L152" s="22"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="15"/>
       <c r="B153" s="15"/>
-      <c r="L153" s="23"/>
+      <c r="L153" s="22"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="15"/>
       <c r="B154" s="15"/>
-      <c r="L154" s="23"/>
+      <c r="L154" s="22"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="15"/>
       <c r="B155" s="15"/>
-      <c r="L155" s="23"/>
+      <c r="L155" s="22"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="15"/>
       <c r="B156" s="15"/>
-      <c r="L156" s="23"/>
+      <c r="L156" s="22"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="15"/>
       <c r="B157" s="15"/>
-      <c r="L157" s="23"/>
+      <c r="L157" s="22"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="15"/>
       <c r="B158" s="15"/>
-      <c r="L158" s="23"/>
+      <c r="L158" s="22"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="15"/>
       <c r="B159" s="15"/>
-      <c r="L159" s="23"/>
+      <c r="L159" s="22"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="15"/>
       <c r="B160" s="15"/>
-      <c r="L160" s="23"/>
+      <c r="L160" s="22"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="15"/>
       <c r="B161" s="15"/>
-      <c r="L161" s="23"/>
+      <c r="L161" s="22"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="15"/>
       <c r="B162" s="15"/>
-      <c r="L162" s="23"/>
+      <c r="L162" s="22"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="15"/>
       <c r="B163" s="15"/>
-      <c r="L163" s="23"/>
+      <c r="L163" s="22"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="15"/>
       <c r="B164" s="15"/>
-      <c r="L164" s="23"/>
+      <c r="L164" s="22"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="15"/>
       <c r="B165" s="15"/>
-      <c r="L165" s="23"/>
+      <c r="L165" s="22"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="15"/>
       <c r="B166" s="15"/>
-      <c r="L166" s="23"/>
+      <c r="L166" s="22"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="15"/>
       <c r="B167" s="15"/>
-      <c r="L167" s="23"/>
+      <c r="L167" s="22"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="15"/>
       <c r="B168" s="15"/>
-      <c r="L168" s="23"/>
+      <c r="L168" s="22"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="15"/>
       <c r="B169" s="15"/>
-      <c r="L169" s="23"/>
+      <c r="L169" s="22"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="15"/>
       <c r="B170" s="15"/>
-      <c r="L170" s="23"/>
+      <c r="L170" s="22"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="15"/>
       <c r="B171" s="15"/>
-      <c r="L171" s="23"/>
+      <c r="L171" s="22"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="15"/>
       <c r="B172" s="15"/>
-      <c r="L172" s="23"/>
+      <c r="L172" s="22"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="15"/>
       <c r="B173" s="15"/>
-      <c r="L173" s="23"/>
+      <c r="L173" s="22"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="15"/>
       <c r="B174" s="15"/>
-      <c r="L174" s="23"/>
+      <c r="L174" s="22"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="15"/>
       <c r="B175" s="15"/>
-      <c r="L175" s="23"/>
+      <c r="L175" s="22"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="15"/>
       <c r="B176" s="15"/>
-      <c r="L176" s="23"/>
+      <c r="L176" s="22"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="15"/>
       <c r="B177" s="15"/>
-      <c r="L177" s="23"/>
+      <c r="L177" s="22"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="15"/>
       <c r="B178" s="15"/>
-      <c r="L178" s="23"/>
+      <c r="L178" s="22"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="15"/>
       <c r="B179" s="15"/>
-      <c r="L179" s="23"/>
+      <c r="L179" s="22"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="15"/>
       <c r="B180" s="15"/>
-      <c r="L180" s="23"/>
+      <c r="L180" s="22"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="15"/>
       <c r="B181" s="15"/>
-      <c r="L181" s="23"/>
+      <c r="L181" s="22"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="15"/>
       <c r="B182" s="15"/>
-      <c r="L182" s="23"/>
+      <c r="L182" s="22"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="15"/>
       <c r="B183" s="15"/>
-      <c r="L183" s="23"/>
+      <c r="L183" s="22"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="15"/>
       <c r="B184" s="15"/>
-      <c r="L184" s="23"/>
+      <c r="L184" s="22"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="15"/>
       <c r="B185" s="15"/>
-      <c r="L185" s="23"/>
+      <c r="L185" s="22"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="15"/>
       <c r="B186" s="15"/>
-      <c r="L186" s="23"/>
+      <c r="L186" s="22"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="15"/>
       <c r="B187" s="15"/>
-      <c r="L187" s="23"/>
+      <c r="L187" s="22"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="15"/>
       <c r="B188" s="15"/>
-      <c r="L188" s="23"/>
+      <c r="L188" s="22"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="15"/>
       <c r="B189" s="15"/>
-      <c r="L189" s="23"/>
+      <c r="L189" s="22"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="15"/>
       <c r="B190" s="15"/>
-      <c r="L190" s="23"/>
+      <c r="L190" s="22"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="15"/>
       <c r="B191" s="15"/>
-      <c r="L191" s="23"/>
+      <c r="L191" s="22"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="15"/>
       <c r="B192" s="15"/>
-      <c r="L192" s="23"/>
+      <c r="L192" s="22"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="15"/>
       <c r="B193" s="15"/>
-      <c r="L193" s="23"/>
+      <c r="L193" s="22"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="15"/>
       <c r="B194" s="15"/>
-      <c r="L194" s="23"/>
+      <c r="L194" s="22"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="15"/>
       <c r="B195" s="15"/>
-      <c r="L195" s="23"/>
+      <c r="L195" s="22"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="15"/>
       <c r="B196" s="15"/>
-      <c r="L196" s="23"/>
+      <c r="L196" s="22"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="15"/>
       <c r="B197" s="15"/>
-      <c r="L197" s="23"/>
+      <c r="L197" s="22"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="15"/>
       <c r="B198" s="15"/>
-      <c r="L198" s="23"/>
+      <c r="L198" s="22"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="15"/>
       <c r="B199" s="15"/>
-      <c r="L199" s="23"/>
+      <c r="L199" s="22"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="15"/>
       <c r="B200" s="15"/>
-      <c r="L200" s="23"/>
+      <c r="L200" s="22"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="15"/>
       <c r="B201" s="15"/>
-      <c r="L201" s="23"/>
+      <c r="L201" s="22"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="15"/>
       <c r="B202" s="15"/>
-      <c r="L202" s="23"/>
+      <c r="L202" s="22"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="15"/>
       <c r="B203" s="15"/>
-      <c r="L203" s="23"/>
+      <c r="L203" s="22"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="15"/>
       <c r="B204" s="15"/>
-      <c r="L204" s="23"/>
+      <c r="L204" s="22"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="15"/>
       <c r="B205" s="15"/>
-      <c r="L205" s="23"/>
+      <c r="L205" s="22"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="15"/>
       <c r="B206" s="15"/>
-      <c r="L206" s="23"/>
+      <c r="L206" s="22"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="15"/>
       <c r="B207" s="15"/>
-      <c r="L207" s="23"/>
+      <c r="L207" s="22"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="15"/>
       <c r="B208" s="15"/>
-      <c r="L208" s="23"/>
+      <c r="L208" s="22"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="15"/>
       <c r="B209" s="15"/>
-      <c r="L209" s="23"/>
+      <c r="L209" s="22"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="15"/>
       <c r="B210" s="15"/>
-      <c r="L210" s="23"/>
+      <c r="L210" s="22"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="15"/>
       <c r="B211" s="15"/>
-      <c r="L211" s="23"/>
+      <c r="L211" s="22"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="15"/>
       <c r="B212" s="15"/>
-      <c r="L212" s="23"/>
+      <c r="L212" s="22"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="15"/>
       <c r="B213" s="15"/>
-      <c r="L213" s="23"/>
+      <c r="L213" s="22"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="15"/>
       <c r="B214" s="15"/>
-      <c r="L214" s="23"/>
+      <c r="L214" s="22"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="15"/>
       <c r="B215" s="15"/>
-      <c r="L215" s="23"/>
+      <c r="L215" s="22"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="15"/>
       <c r="B216" s="15"/>
-      <c r="L216" s="23"/>
+      <c r="L216" s="22"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="15"/>
       <c r="B217" s="15"/>
-      <c r="L217" s="23"/>
+      <c r="L217" s="22"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="15"/>
       <c r="B218" s="15"/>
-      <c r="L218" s="23"/>
+      <c r="L218" s="22"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="15"/>
       <c r="B219" s="15"/>
-      <c r="L219" s="23"/>
+      <c r="L219" s="22"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="15"/>
       <c r="B220" s="15"/>
-      <c r="L220" s="23"/>
+      <c r="L220" s="22"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="15"/>
       <c r="B221" s="15"/>
-      <c r="L221" s="23"/>
+      <c r="L221" s="22"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="15"/>
       <c r="B222" s="15"/>
-      <c r="L222" s="23"/>
+      <c r="L222" s="22"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="15"/>
       <c r="B223" s="15"/>
-      <c r="L223" s="23"/>
+      <c r="L223" s="22"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="15"/>
       <c r="B224" s="15"/>
-      <c r="L224" s="23"/>
+      <c r="L224" s="22"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="15"/>
       <c r="B225" s="15"/>
-      <c r="L225" s="23"/>
+      <c r="L225" s="22"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="15"/>
       <c r="B226" s="15"/>
-      <c r="L226" s="23"/>
+      <c r="L226" s="22"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
       <c r="A227" s="15"/>
       <c r="B227" s="15"/>
-      <c r="L227" s="23"/>
+      <c r="L227" s="22"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="15"/>
       <c r="B228" s="15"/>
-      <c r="L228" s="23"/>
+      <c r="L228" s="22"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="A229" s="15"/>
       <c r="B229" s="15"/>
-      <c r="L229" s="23"/>
+      <c r="L229" s="22"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="15"/>
       <c r="B230" s="15"/>
-      <c r="L230" s="23"/>
+      <c r="L230" s="22"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="15"/>
       <c r="B231" s="15"/>
-      <c r="L231" s="23"/>
+      <c r="L231" s="22"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="15"/>
       <c r="B232" s="15"/>
-      <c r="L232" s="23"/>
+      <c r="L232" s="22"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="15"/>
       <c r="B233" s="15"/>
-      <c r="L233" s="23"/>
+      <c r="L233" s="22"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="15"/>
       <c r="B234" s="15"/>
-      <c r="L234" s="23"/>
+      <c r="L234" s="22"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
       <c r="A235" s="15"/>
       <c r="B235" s="15"/>
-      <c r="L235" s="23"/>
+      <c r="L235" s="22"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
       <c r="A236" s="15"/>
       <c r="B236" s="15"/>
-      <c r="L236" s="23"/>
+      <c r="L236" s="22"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
       <c r="A237" s="15"/>
       <c r="B237" s="15"/>
-      <c r="L237" s="23"/>
+      <c r="L237" s="22"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="A238" s="15"/>
       <c r="B238" s="15"/>
-      <c r="L238" s="23"/>
+      <c r="L238" s="22"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
       <c r="A239" s="15"/>
       <c r="B239" s="15"/>
-      <c r="L239" s="23"/>
+      <c r="L239" s="22"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
       <c r="A240" s="15"/>
       <c r="B240" s="15"/>
-      <c r="L240" s="23"/>
+      <c r="L240" s="22"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
       <c r="A241" s="15"/>
       <c r="B241" s="15"/>
-      <c r="L241" s="23"/>
+      <c r="L241" s="22"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="A242" s="15"/>
       <c r="B242" s="15"/>
-      <c r="L242" s="23"/>
+      <c r="L242" s="22"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
       <c r="A243" s="15"/>
       <c r="B243" s="15"/>
-      <c r="L243" s="23"/>
+      <c r="L243" s="22"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
       <c r="A244" s="15"/>
       <c r="B244" s="15"/>
-      <c r="L244" s="23"/>
+      <c r="L244" s="22"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="A245" s="15"/>
       <c r="B245" s="15"/>
-      <c r="L245" s="23"/>
+      <c r="L245" s="22"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="A246" s="15"/>
       <c r="B246" s="15"/>
-      <c r="L246" s="23"/>
+      <c r="L246" s="22"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
       <c r="A247" s="15"/>
       <c r="B247" s="15"/>
-      <c r="L247" s="23"/>
+      <c r="L247" s="22"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
       <c r="A248" s="15"/>
       <c r="B248" s="15"/>
-      <c r="L248" s="23"/>
+      <c r="L248" s="22"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
       <c r="A249" s="15"/>
       <c r="B249" s="15"/>
-      <c r="L249" s="23"/>
+      <c r="L249" s="22"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="A250" s="15"/>
       <c r="B250" s="15"/>
-      <c r="L250" s="23"/>
+      <c r="L250" s="22"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
       <c r="A251" s="15"/>
       <c r="B251" s="15"/>
-      <c r="L251" s="23"/>
+      <c r="L251" s="22"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
       <c r="A252" s="15"/>
       <c r="B252" s="15"/>
-      <c r="L252" s="23"/>
+      <c r="L252" s="22"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
       <c r="A253" s="15"/>
       <c r="B253" s="15"/>
-      <c r="L253" s="23"/>
+      <c r="L253" s="22"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="A254" s="15"/>
       <c r="B254" s="15"/>
-      <c r="L254" s="23"/>
+      <c r="L254" s="22"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
       <c r="A255" s="15"/>
       <c r="B255" s="15"/>
-      <c r="L255" s="23"/>
+      <c r="L255" s="22"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
       <c r="A256" s="15"/>
       <c r="B256" s="15"/>
-      <c r="L256" s="23"/>
+      <c r="L256" s="22"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="A257" s="15"/>
       <c r="B257" s="15"/>
-      <c r="L257" s="23"/>
+      <c r="L257" s="22"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="A258" s="15"/>
       <c r="B258" s="15"/>
-      <c r="L258" s="23"/>
+      <c r="L258" s="22"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
       <c r="A259" s="15"/>
       <c r="B259" s="15"/>
-      <c r="L259" s="23"/>
+      <c r="L259" s="22"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
       <c r="A260" s="15"/>
       <c r="B260" s="15"/>
-      <c r="L260" s="23"/>
+      <c r="L260" s="22"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="A261" s="15"/>
       <c r="B261" s="15"/>
-      <c r="L261" s="23"/>
+      <c r="L261" s="22"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="A262" s="15"/>
       <c r="B262" s="15"/>
-      <c r="L262" s="23"/>
+      <c r="L262" s="22"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
       <c r="A263" s="15"/>
       <c r="B263" s="15"/>
-      <c r="L263" s="23"/>
+      <c r="L263" s="22"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
       <c r="A264" s="15"/>
       <c r="B264" s="15"/>
-      <c r="L264" s="23"/>
+      <c r="L264" s="22"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="A265" s="15"/>
       <c r="B265" s="15"/>
-      <c r="L265" s="23"/>
+      <c r="L265" s="22"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="A266" s="15"/>
       <c r="B266" s="15"/>
-      <c r="L266" s="23"/>
+      <c r="L266" s="22"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
       <c r="A267" s="15"/>
       <c r="B267" s="15"/>
-      <c r="L267" s="23"/>
+      <c r="L267" s="22"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
       <c r="A268" s="15"/>
       <c r="B268" s="15"/>
-      <c r="L268" s="23"/>
+      <c r="L268" s="22"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="A269" s="15"/>
       <c r="B269" s="15"/>
-      <c r="L269" s="23"/>
+      <c r="L269" s="22"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="A270" s="15"/>
       <c r="B270" s="15"/>
-      <c r="L270" s="23"/>
+      <c r="L270" s="22"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
       <c r="A271" s="15"/>
       <c r="B271" s="15"/>
-      <c r="L271" s="23"/>
+      <c r="L271" s="22"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
       <c r="A272" s="15"/>
       <c r="B272" s="15"/>
-      <c r="L272" s="23"/>
+      <c r="L272" s="22"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="A273" s="15"/>
       <c r="B273" s="15"/>
-      <c r="L273" s="23"/>
+      <c r="L273" s="22"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="A274" s="15"/>
       <c r="B274" s="15"/>
-      <c r="L274" s="23"/>
+      <c r="L274" s="22"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
       <c r="A275" s="15"/>
       <c r="B275" s="15"/>
-      <c r="L275" s="23"/>
+      <c r="L275" s="22"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
       <c r="A276" s="15"/>
       <c r="B276" s="15"/>
-      <c r="L276" s="23"/>
+      <c r="L276" s="22"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
       <c r="A277" s="15"/>
       <c r="B277" s="15"/>
-      <c r="L277" s="23"/>
+      <c r="L277" s="22"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="A278" s="15"/>
       <c r="B278" s="15"/>
-      <c r="L278" s="23"/>
+      <c r="L278" s="22"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
       <c r="A279" s="15"/>
       <c r="B279" s="15"/>
-      <c r="L279" s="23"/>
+      <c r="L279" s="22"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
       <c r="A280" s="15"/>
       <c r="B280" s="15"/>
-      <c r="L280" s="23"/>
+      <c r="L280" s="22"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
       <c r="A281" s="15"/>
       <c r="B281" s="15"/>
-      <c r="L281" s="23"/>
+      <c r="L281" s="22"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="A282" s="15"/>
       <c r="B282" s="15"/>
-      <c r="L282" s="23"/>
+      <c r="L282" s="22"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
       <c r="A283" s="15"/>
       <c r="B283" s="15"/>
-      <c r="L283" s="23"/>
+      <c r="L283" s="22"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
       <c r="A284" s="15"/>
       <c r="B284" s="15"/>
-      <c r="L284" s="23"/>
+      <c r="L284" s="22"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
       <c r="A285" s="15"/>
       <c r="B285" s="15"/>
-      <c r="L285" s="23"/>
+      <c r="L285" s="22"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="A286" s="15"/>
       <c r="B286" s="15"/>
-      <c r="L286" s="23"/>
+      <c r="L286" s="22"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
       <c r="A287" s="15"/>
       <c r="B287" s="15"/>
-      <c r="L287" s="23"/>
+      <c r="L287" s="22"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
       <c r="A288" s="15"/>
       <c r="B288" s="15"/>
-      <c r="L288" s="23"/>
+      <c r="L288" s="22"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="A289" s="15"/>
       <c r="B289" s="15"/>
-      <c r="L289" s="23"/>
+      <c r="L289" s="22"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="A290" s="15"/>
       <c r="B290" s="15"/>
-      <c r="L290" s="23"/>
+      <c r="L290" s="22"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
       <c r="A291" s="15"/>
       <c r="B291" s="15"/>
-      <c r="L291" s="23"/>
+      <c r="L291" s="22"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
       <c r="A292" s="15"/>
       <c r="B292" s="15"/>
-      <c r="L292" s="23"/>
+      <c r="L292" s="22"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
       <c r="A293" s="15"/>
       <c r="B293" s="15"/>
-      <c r="L293" s="23"/>
+      <c r="L293" s="22"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
       <c r="A294" s="15"/>
       <c r="B294" s="15"/>
-      <c r="L294" s="23"/>
+      <c r="L294" s="22"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
       <c r="A295" s="15"/>
       <c r="B295" s="15"/>
-      <c r="L295" s="23"/>
+      <c r="L295" s="22"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
       <c r="A296" s="15"/>
       <c r="B296" s="15"/>
-      <c r="L296" s="23"/>
+      <c r="L296" s="22"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
       <c r="A297" s="15"/>
       <c r="B297" s="15"/>
-      <c r="L297" s="23"/>
+      <c r="L297" s="22"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="A298" s="15"/>
       <c r="B298" s="15"/>
-      <c r="L298" s="23"/>
+      <c r="L298" s="22"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
       <c r="A299" s="15"/>
       <c r="B299" s="15"/>
-      <c r="L299" s="23"/>
+      <c r="L299" s="22"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
       <c r="A300" s="15"/>
       <c r="B300" s="15"/>
-      <c r="L300" s="23"/>
+      <c r="L300" s="22"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
       <c r="A301" s="15"/>
       <c r="B301" s="15"/>
-      <c r="L301" s="23"/>
+      <c r="L301" s="22"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="A302" s="15"/>
       <c r="B302" s="15"/>
-      <c r="L302" s="23"/>
+      <c r="L302" s="22"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
       <c r="A303" s="15"/>
       <c r="B303" s="15"/>
-      <c r="L303" s="23"/>
+      <c r="L303" s="22"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
       <c r="A304" s="15"/>
       <c r="B304" s="15"/>
-      <c r="L304" s="23"/>
+      <c r="L304" s="22"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
       <c r="A305" s="15"/>
       <c r="B305" s="15"/>
-      <c r="L305" s="23"/>
+      <c r="L305" s="22"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="A306" s="15"/>
       <c r="B306" s="15"/>
-      <c r="L306" s="23"/>
+      <c r="L306" s="22"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
       <c r="A307" s="15"/>
       <c r="B307" s="15"/>
-      <c r="L307" s="23"/>
+      <c r="L307" s="22"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
       <c r="A308" s="15"/>
       <c r="B308" s="15"/>
-      <c r="L308" s="23"/>
+      <c r="L308" s="22"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
       <c r="A309" s="15"/>
       <c r="B309" s="15"/>
-      <c r="L309" s="23"/>
+      <c r="L309" s="22"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="A310" s="15"/>
       <c r="B310" s="15"/>
-      <c r="L310" s="23"/>
+      <c r="L310" s="22"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
       <c r="A311" s="15"/>
       <c r="B311" s="15"/>
-      <c r="L311" s="23"/>
+      <c r="L311" s="22"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
       <c r="A312" s="15"/>
       <c r="B312" s="15"/>
-      <c r="L312" s="23"/>
+      <c r="L312" s="22"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
       <c r="A313" s="15"/>
       <c r="B313" s="15"/>
-      <c r="L313" s="23"/>
+      <c r="L313" s="22"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="A314" s="15"/>
       <c r="B314" s="15"/>
-      <c r="L314" s="23"/>
+      <c r="L314" s="22"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
       <c r="A315" s="15"/>
       <c r="B315" s="15"/>
-      <c r="L315" s="23"/>
+      <c r="L315" s="22"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="A316" s="15"/>
       <c r="B316" s="15"/>
-      <c r="L316" s="23"/>
+      <c r="L316" s="22"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="A317" s="15"/>
       <c r="B317" s="15"/>
-      <c r="L317" s="23"/>
+      <c r="L317" s="22"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="A318" s="15"/>
       <c r="B318" s="15"/>
-      <c r="L318" s="23"/>
+      <c r="L318" s="22"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
       <c r="A319" s="15"/>
       <c r="B319" s="15"/>
-      <c r="L319" s="23"/>
+      <c r="L319" s="22"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="A320" s="15"/>
       <c r="B320" s="15"/>
-      <c r="L320" s="23"/>
+      <c r="L320" s="22"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="A321" s="15"/>
       <c r="B321" s="15"/>
-      <c r="L321" s="23"/>
+      <c r="L321" s="22"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="A322" s="15"/>
       <c r="B322" s="15"/>
-      <c r="L322" s="23"/>
+      <c r="L322" s="22"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
       <c r="A323" s="15"/>
       <c r="B323" s="15"/>
-      <c r="L323" s="23"/>
+      <c r="L323" s="22"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="A324" s="15"/>
       <c r="B324" s="15"/>
-      <c r="L324" s="23"/>
+      <c r="L324" s="22"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="A325" s="15"/>
       <c r="B325" s="15"/>
-      <c r="L325" s="23"/>
+      <c r="L325" s="22"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="A326" s="15"/>
       <c r="B326" s="15"/>
-      <c r="L326" s="23"/>
+      <c r="L326" s="22"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
       <c r="A327" s="15"/>
       <c r="B327" s="15"/>
-      <c r="L327" s="23"/>
+      <c r="L327" s="22"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="A328" s="15"/>
       <c r="B328" s="15"/>
-      <c r="L328" s="23"/>
+      <c r="L328" s="22"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="A329" s="15"/>
       <c r="B329" s="15"/>
-      <c r="L329" s="23"/>
+      <c r="L329" s="22"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="A330" s="15"/>
       <c r="B330" s="15"/>
-      <c r="L330" s="23"/>
+      <c r="L330" s="22"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
       <c r="A331" s="15"/>
       <c r="B331" s="15"/>
-      <c r="L331" s="23"/>
+      <c r="L331" s="22"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="A332" s="15"/>
       <c r="B332" s="15"/>
-      <c r="L332" s="23"/>
+      <c r="L332" s="22"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="A333" s="15"/>
       <c r="B333" s="15"/>
-      <c r="L333" s="23"/>
+      <c r="L333" s="22"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="A334" s="15"/>
       <c r="B334" s="15"/>
-      <c r="L334" s="23"/>
+      <c r="L334" s="22"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
       <c r="A335" s="15"/>
       <c r="B335" s="15"/>
-      <c r="L335" s="23"/>
+      <c r="L335" s="22"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="A336" s="15"/>
       <c r="B336" s="15"/>
-      <c r="L336" s="23"/>
+      <c r="L336" s="22"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="A337" s="15"/>
       <c r="B337" s="15"/>
-      <c r="L337" s="23"/>
+      <c r="L337" s="22"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="A338" s="15"/>
       <c r="B338" s="15"/>
-      <c r="L338" s="23"/>
+      <c r="L338" s="22"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
       <c r="A339" s="15"/>
       <c r="B339" s="15"/>
-      <c r="L339" s="23"/>
+      <c r="L339" s="22"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="A340" s="15"/>
       <c r="B340" s="15"/>
-      <c r="L340" s="23"/>
+      <c r="L340" s="22"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="A341" s="15"/>
       <c r="B341" s="15"/>
-      <c r="L341" s="23"/>
+      <c r="L341" s="22"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="A342" s="15"/>
       <c r="B342" s="15"/>
-      <c r="L342" s="23"/>
+      <c r="L342" s="22"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
       <c r="A343" s="15"/>
       <c r="B343" s="15"/>
-      <c r="L343" s="23"/>
+      <c r="L343" s="22"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="A344" s="15"/>
       <c r="B344" s="15"/>
-      <c r="L344" s="23"/>
+      <c r="L344" s="22"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="A345" s="15"/>
       <c r="B345" s="15"/>
-      <c r="L345" s="23"/>
+      <c r="L345" s="22"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="A346" s="15"/>
       <c r="B346" s="15"/>
-      <c r="L346" s="23"/>
+      <c r="L346" s="22"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
       <c r="A347" s="15"/>
       <c r="B347" s="15"/>
-      <c r="L347" s="23"/>
+      <c r="L347" s="22"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="A348" s="15"/>
       <c r="B348" s="15"/>
-      <c r="L348" s="23"/>
+      <c r="L348" s="22"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="A349" s="15"/>
       <c r="B349" s="15"/>
-      <c r="L349" s="23"/>
+      <c r="L349" s="22"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="A350" s="15"/>
       <c r="B350" s="15"/>
-      <c r="L350" s="23"/>
+      <c r="L350" s="22"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
       <c r="A351" s="15"/>
       <c r="B351" s="15"/>
-      <c r="L351" s="23"/>
+      <c r="L351" s="22"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="A352" s="15"/>
       <c r="B352" s="15"/>
-      <c r="L352" s="23"/>
+      <c r="L352" s="22"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="A353" s="15"/>
       <c r="B353" s="15"/>
-      <c r="L353" s="23"/>
+      <c r="L353" s="22"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="A354" s="15"/>
       <c r="B354" s="15"/>
-      <c r="L354" s="23"/>
+      <c r="L354" s="22"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
       <c r="A355" s="15"/>
       <c r="B355" s="15"/>
-      <c r="L355" s="23"/>
+      <c r="L355" s="22"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="A356" s="15"/>
       <c r="B356" s="15"/>
-      <c r="L356" s="23"/>
+      <c r="L356" s="22"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="A357" s="15"/>
       <c r="B357" s="15"/>
-      <c r="L357" s="23"/>
+      <c r="L357" s="22"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="A358" s="15"/>
       <c r="B358" s="15"/>
-      <c r="L358" s="23"/>
+      <c r="L358" s="22"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="A359" s="15"/>
       <c r="B359" s="15"/>
-      <c r="L359" s="23"/>
+      <c r="L359" s="22"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="A360" s="15"/>
       <c r="B360" s="15"/>
-      <c r="L360" s="23"/>
+      <c r="L360" s="22"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="A361" s="15"/>
       <c r="B361" s="15"/>
-      <c r="L361" s="23"/>
+      <c r="L361" s="22"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="A362" s="15"/>
       <c r="B362" s="15"/>
-      <c r="L362" s="23"/>
+      <c r="L362" s="22"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
       <c r="A363" s="15"/>
       <c r="B363" s="15"/>
-      <c r="L363" s="23"/>
+      <c r="L363" s="22"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="A364" s="15"/>
       <c r="B364" s="15"/>
-      <c r="L364" s="23"/>
+      <c r="L364" s="22"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="A365" s="15"/>
       <c r="B365" s="15"/>
-      <c r="L365" s="23"/>
+      <c r="L365" s="22"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="A366" s="15"/>
       <c r="B366" s="15"/>
-      <c r="L366" s="23"/>
+      <c r="L366" s="22"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="A367" s="15"/>
       <c r="B367" s="15"/>
-      <c r="L367" s="23"/>
+      <c r="L367" s="22"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="A368" s="15"/>
       <c r="B368" s="15"/>
-      <c r="L368" s="23"/>
+      <c r="L368" s="22"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="A369" s="15"/>
       <c r="B369" s="15"/>
-      <c r="L369" s="23"/>
+      <c r="L369" s="22"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="A370" s="15"/>
       <c r="B370" s="15"/>
-      <c r="L370" s="23"/>
+      <c r="L370" s="22"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
       <c r="A371" s="15"/>
       <c r="B371" s="15"/>
-      <c r="L371" s="23"/>
+      <c r="L371" s="22"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="A372" s="15"/>
       <c r="B372" s="15"/>
-      <c r="L372" s="23"/>
+      <c r="L372" s="22"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="A373" s="15"/>
       <c r="B373" s="15"/>
-      <c r="L373" s="23"/>
+      <c r="L373" s="22"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="A374" s="15"/>
       <c r="B374" s="15"/>
-      <c r="L374" s="23"/>
+      <c r="L374" s="22"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="A375" s="15"/>
       <c r="B375" s="15"/>
-      <c r="L375" s="23"/>
+      <c r="L375" s="22"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="A376" s="15"/>
       <c r="B376" s="15"/>
-      <c r="L376" s="23"/>
+      <c r="L376" s="22"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="A377" s="15"/>
       <c r="B377" s="15"/>
-      <c r="L377" s="23"/>
+      <c r="L377" s="22"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="A378" s="15"/>
       <c r="B378" s="15"/>
-      <c r="L378" s="23"/>
+      <c r="L378" s="22"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="A379" s="15"/>
       <c r="B379" s="15"/>
-      <c r="L379" s="23"/>
+      <c r="L379" s="22"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="A380" s="15"/>
       <c r="B380" s="15"/>
-      <c r="L380" s="23"/>
+      <c r="L380" s="22"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="A381" s="15"/>
       <c r="B381" s="15"/>
-      <c r="L381" s="23"/>
+      <c r="L381" s="22"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="A382" s="15"/>
       <c r="B382" s="15"/>
-      <c r="L382" s="23"/>
+      <c r="L382" s="22"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
       <c r="A383" s="15"/>
       <c r="B383" s="15"/>
-      <c r="L383" s="23"/>
+      <c r="L383" s="22"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="A384" s="15"/>
       <c r="B384" s="15"/>
-      <c r="L384" s="23"/>
+      <c r="L384" s="22"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="A385" s="15"/>
       <c r="B385" s="15"/>
-      <c r="L385" s="23"/>
+      <c r="L385" s="22"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="A386" s="15"/>
       <c r="B386" s="15"/>
-      <c r="L386" s="23"/>
+      <c r="L386" s="22"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
       <c r="A387" s="15"/>
       <c r="B387" s="15"/>
-      <c r="L387" s="23"/>
+      <c r="L387" s="22"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
       <c r="A388" s="15"/>
       <c r="B388" s="15"/>
-      <c r="L388" s="23"/>
+      <c r="L388" s="22"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
       <c r="A389" s="15"/>
       <c r="B389" s="15"/>
-      <c r="L389" s="23"/>
+      <c r="L389" s="22"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
       <c r="A390" s="15"/>
       <c r="B390" s="15"/>
-      <c r="L390" s="23"/>
+      <c r="L390" s="22"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
       <c r="A391" s="15"/>
       <c r="B391" s="15"/>
-      <c r="L391" s="23"/>
+      <c r="L391" s="22"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
       <c r="A392" s="15"/>
       <c r="B392" s="15"/>
-      <c r="L392" s="23"/>
+      <c r="L392" s="22"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
       <c r="A393" s="15"/>
       <c r="B393" s="15"/>
-      <c r="L393" s="23"/>
+      <c r="L393" s="22"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
       <c r="A394" s="15"/>
       <c r="B394" s="15"/>
-      <c r="L394" s="23"/>
+      <c r="L394" s="22"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
       <c r="A395" s="15"/>
       <c r="B395" s="15"/>
-      <c r="L395" s="23"/>
+      <c r="L395" s="22"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
       <c r="A396" s="15"/>
       <c r="B396" s="15"/>
-      <c r="L396" s="23"/>
+      <c r="L396" s="22"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
       <c r="A397" s="15"/>
       <c r="B397" s="15"/>
-      <c r="L397" s="23"/>
+      <c r="L397" s="22"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
       <c r="A398" s="15"/>
       <c r="B398" s="15"/>
-      <c r="L398" s="23"/>
+      <c r="L398" s="22"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
       <c r="A399" s="15"/>
       <c r="B399" s="15"/>
-      <c r="L399" s="23"/>
+      <c r="L399" s="22"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
       <c r="A400" s="15"/>
       <c r="B400" s="15"/>
-      <c r="L400" s="23"/>
+      <c r="L400" s="22"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
       <c r="A401" s="15"/>
       <c r="B401" s="15"/>
-      <c r="L401" s="23"/>
+      <c r="L401" s="22"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
       <c r="A402" s="15"/>
       <c r="B402" s="15"/>
-      <c r="L402" s="23"/>
+      <c r="L402" s="22"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
       <c r="A403" s="15"/>
       <c r="B403" s="15"/>
-      <c r="L403" s="23"/>
+      <c r="L403" s="22"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
       <c r="A404" s="15"/>
       <c r="B404" s="15"/>
-      <c r="L404" s="23"/>
+      <c r="L404" s="22"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
       <c r="A405" s="15"/>
       <c r="B405" s="15"/>
-      <c r="L405" s="23"/>
+      <c r="L405" s="22"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
       <c r="A406" s="15"/>
       <c r="B406" s="15"/>
-      <c r="L406" s="23"/>
+      <c r="L406" s="22"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
       <c r="A407" s="15"/>
       <c r="B407" s="15"/>
-      <c r="L407" s="23"/>
+      <c r="L407" s="22"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="A408" s="15"/>
       <c r="B408" s="15"/>
-      <c r="L408" s="23"/>
+      <c r="L408" s="22"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
       <c r="A409" s="15"/>
       <c r="B409" s="15"/>
-      <c r="L409" s="23"/>
+      <c r="L409" s="22"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="A410" s="15"/>
       <c r="B410" s="15"/>
-      <c r="L410" s="23"/>
+      <c r="L410" s="22"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
       <c r="A411" s="15"/>
       <c r="B411" s="15"/>
-      <c r="L411" s="23"/>
+      <c r="L411" s="22"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
       <c r="A412" s="15"/>
       <c r="B412" s="15"/>
-      <c r="L412" s="23"/>
+      <c r="L412" s="22"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
       <c r="A413" s="15"/>
       <c r="B413" s="15"/>
-      <c r="L413" s="23"/>
+      <c r="L413" s="22"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
       <c r="A414" s="15"/>
       <c r="B414" s="15"/>
-      <c r="L414" s="23"/>
+      <c r="L414" s="22"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
       <c r="A415" s="15"/>
       <c r="B415" s="15"/>
-      <c r="L415" s="23"/>
+      <c r="L415" s="22"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="A416" s="15"/>
       <c r="B416" s="15"/>
-      <c r="L416" s="23"/>
+      <c r="L416" s="22"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
       <c r="A417" s="15"/>
       <c r="B417" s="15"/>
-      <c r="L417" s="23"/>
+      <c r="L417" s="22"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="A418" s="15"/>
       <c r="B418" s="15"/>
-      <c r="L418" s="23"/>
+      <c r="L418" s="22"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
       <c r="A419" s="15"/>
       <c r="B419" s="15"/>
-      <c r="L419" s="23"/>
+      <c r="L419" s="22"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
       <c r="A420" s="15"/>
       <c r="B420" s="15"/>
-      <c r="L420" s="23"/>
+      <c r="L420" s="22"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
       <c r="A421" s="15"/>
       <c r="B421" s="15"/>
-      <c r="L421" s="23"/>
+      <c r="L421" s="22"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
       <c r="A422" s="15"/>
       <c r="B422" s="15"/>
-      <c r="L422" s="23"/>
+      <c r="L422" s="22"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
       <c r="A423" s="15"/>
       <c r="B423" s="15"/>
-      <c r="L423" s="23"/>
+      <c r="L423" s="22"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
       <c r="A424" s="15"/>
       <c r="B424" s="15"/>
-      <c r="L424" s="23"/>
+      <c r="L424" s="22"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
       <c r="A425" s="15"/>
       <c r="B425" s="15"/>
-      <c r="L425" s="23"/>
+      <c r="L425" s="22"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
       <c r="A426" s="15"/>
       <c r="B426" s="15"/>
-      <c r="L426" s="23"/>
+      <c r="L426" s="22"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="A427" s="15"/>
       <c r="B427" s="15"/>
-      <c r="L427" s="23"/>
+      <c r="L427" s="22"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="A428" s="15"/>
       <c r="B428" s="15"/>
-      <c r="L428" s="23"/>
+      <c r="L428" s="22"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="A429" s="15"/>
       <c r="B429" s="15"/>
-      <c r="L429" s="23"/>
+      <c r="L429" s="22"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="A430" s="15"/>
       <c r="B430" s="15"/>
-      <c r="L430" s="23"/>
+      <c r="L430" s="22"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="A431" s="15"/>
       <c r="B431" s="15"/>
-      <c r="L431" s="23"/>
+      <c r="L431" s="22"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="A432" s="15"/>
       <c r="B432" s="15"/>
-      <c r="L432" s="23"/>
+      <c r="L432" s="22"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="A433" s="15"/>
       <c r="B433" s="15"/>
-      <c r="L433" s="23"/>
+      <c r="L433" s="22"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="A434" s="15"/>
       <c r="B434" s="15"/>
-      <c r="L434" s="23"/>
+      <c r="L434" s="22"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="A435" s="15"/>
       <c r="B435" s="15"/>
-      <c r="L435" s="23"/>
+      <c r="L435" s="22"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="A436" s="15"/>
       <c r="B436" s="15"/>
-      <c r="L436" s="23"/>
+      <c r="L436" s="22"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="A437" s="15"/>
       <c r="B437" s="15"/>
-      <c r="L437" s="23"/>
+      <c r="L437" s="22"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="A438" s="15"/>
       <c r="B438" s="15"/>
-      <c r="L438" s="23"/>
+      <c r="L438" s="22"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
       <c r="A439" s="15"/>
       <c r="B439" s="15"/>
-      <c r="L439" s="23"/>
+      <c r="L439" s="22"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="A440" s="15"/>
       <c r="B440" s="15"/>
-      <c r="L440" s="23"/>
+      <c r="L440" s="22"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="A441" s="15"/>
       <c r="B441" s="15"/>
-      <c r="L441" s="23"/>
+      <c r="L441" s="22"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="A442" s="15"/>
       <c r="B442" s="15"/>
-      <c r="L442" s="23"/>
+      <c r="L442" s="22"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
       <c r="A443" s="15"/>
       <c r="B443" s="15"/>
-      <c r="L443" s="23"/>
+      <c r="L443" s="22"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="A444" s="15"/>
       <c r="B444" s="15"/>
-      <c r="L444" s="23"/>
+      <c r="L444" s="22"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="A445" s="15"/>
       <c r="B445" s="15"/>
-      <c r="L445" s="23"/>
+      <c r="L445" s="22"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="A446" s="15"/>
       <c r="B446" s="15"/>
-      <c r="L446" s="23"/>
+      <c r="L446" s="22"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="A447" s="15"/>
       <c r="B447" s="15"/>
-      <c r="L447" s="23"/>
+      <c r="L447" s="22"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="A448" s="15"/>
       <c r="B448" s="15"/>
-      <c r="L448" s="23"/>
+      <c r="L448" s="22"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="A449" s="15"/>
       <c r="B449" s="15"/>
-      <c r="L449" s="23"/>
+      <c r="L449" s="22"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="A450" s="15"/>
       <c r="B450" s="15"/>
-      <c r="L450" s="23"/>
+      <c r="L450" s="22"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="A451" s="15"/>
       <c r="B451" s="15"/>
-      <c r="L451" s="23"/>
+      <c r="L451" s="22"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="A452" s="15"/>
       <c r="B452" s="15"/>
-      <c r="L452" s="23"/>
+      <c r="L452" s="22"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="A453" s="15"/>
       <c r="B453" s="15"/>
-      <c r="L453" s="23"/>
+      <c r="L453" s="22"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="A454" s="15"/>
       <c r="B454" s="15"/>
-      <c r="L454" s="23"/>
+      <c r="L454" s="22"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="A455" s="15"/>
       <c r="B455" s="15"/>
-      <c r="L455" s="23"/>
+      <c r="L455" s="22"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="A456" s="15"/>
       <c r="B456" s="15"/>
-      <c r="L456" s="23"/>
+      <c r="L456" s="22"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="A457" s="15"/>
       <c r="B457" s="15"/>
-      <c r="L457" s="23"/>
+      <c r="L457" s="22"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="A458" s="15"/>
       <c r="B458" s="15"/>
-      <c r="L458" s="23"/>
+      <c r="L458" s="22"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="A459" s="15"/>
       <c r="B459" s="15"/>
-      <c r="L459" s="23"/>
+      <c r="L459" s="22"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="A460" s="15"/>
       <c r="B460" s="15"/>
-      <c r="L460" s="23"/>
+      <c r="L460" s="22"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="A461" s="15"/>
       <c r="B461" s="15"/>
-      <c r="L461" s="23"/>
+      <c r="L461" s="22"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="A462" s="15"/>
       <c r="B462" s="15"/>
-      <c r="L462" s="23"/>
+      <c r="L462" s="22"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
       <c r="A463" s="15"/>
       <c r="B463" s="15"/>
-      <c r="L463" s="23"/>
+      <c r="L463" s="22"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="A464" s="15"/>
       <c r="B464" s="15"/>
-      <c r="L464" s="23"/>
+      <c r="L464" s="22"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="A465" s="15"/>
       <c r="B465" s="15"/>
-      <c r="L465" s="23"/>
+      <c r="L465" s="22"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="A466" s="15"/>
       <c r="B466" s="15"/>
-      <c r="L466" s="23"/>
+      <c r="L466" s="22"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="A467" s="15"/>
       <c r="B467" s="15"/>
-      <c r="L467" s="23"/>
+      <c r="L467" s="22"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="A468" s="15"/>
       <c r="B468" s="15"/>
-      <c r="L468" s="23"/>
+      <c r="L468" s="22"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="A469" s="15"/>
       <c r="B469" s="15"/>
-      <c r="L469" s="23"/>
+      <c r="L469" s="22"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="A470" s="15"/>
       <c r="B470" s="15"/>
-      <c r="L470" s="23"/>
+      <c r="L470" s="22"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
       <c r="A471" s="15"/>
       <c r="B471" s="15"/>
-      <c r="L471" s="23"/>
+      <c r="L471" s="22"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="A472" s="15"/>
       <c r="B472" s="15"/>
-      <c r="L472" s="23"/>
+      <c r="L472" s="22"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="A473" s="15"/>
       <c r="B473" s="15"/>
-      <c r="L473" s="23"/>
+      <c r="L473" s="22"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="A474" s="15"/>
       <c r="B474" s="15"/>
-      <c r="L474" s="23"/>
+      <c r="L474" s="22"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
       <c r="A475" s="15"/>
       <c r="B475" s="15"/>
-      <c r="L475" s="23"/>
+      <c r="L475" s="22"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="A476" s="15"/>
       <c r="B476" s="15"/>
-      <c r="L476" s="23"/>
+      <c r="L476" s="22"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="A477" s="15"/>
       <c r="B477" s="15"/>
-      <c r="L477" s="23"/>
+      <c r="L477" s="22"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="A478" s="15"/>
       <c r="B478" s="15"/>
-      <c r="L478" s="23"/>
+      <c r="L478" s="22"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
       <c r="A479" s="15"/>
       <c r="B479" s="15"/>
-      <c r="L479" s="23"/>
+      <c r="L479" s="22"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="A480" s="15"/>
       <c r="B480" s="15"/>
-      <c r="L480" s="23"/>
+      <c r="L480" s="22"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="A481" s="15"/>
       <c r="B481" s="15"/>
-      <c r="L481" s="23"/>
+      <c r="L481" s="22"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="A482" s="15"/>
       <c r="B482" s="15"/>
-      <c r="L482" s="23"/>
+      <c r="L482" s="22"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="15"/>
       <c r="B483" s="15"/>
-      <c r="L483" s="23"/>
+      <c r="L483" s="22"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="A484" s="15"/>
       <c r="B484" s="15"/>
-      <c r="L484" s="23"/>
+      <c r="L484" s="22"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="A485" s="15"/>
       <c r="B485" s="15"/>
-      <c r="L485" s="23"/>
+      <c r="L485" s="22"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="A486" s="15"/>
       <c r="B486" s="15"/>
-      <c r="L486" s="23"/>
+      <c r="L486" s="22"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
       <c r="A487" s="15"/>
       <c r="B487" s="15"/>
-      <c r="L487" s="23"/>
+      <c r="L487" s="22"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="A488" s="15"/>
       <c r="B488" s="15"/>
-      <c r="L488" s="23"/>
+      <c r="L488" s="22"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="A489" s="15"/>
       <c r="B489" s="15"/>
-      <c r="L489" s="23"/>
+      <c r="L489" s="22"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="A490" s="15"/>
       <c r="B490" s="15"/>
-      <c r="L490" s="23"/>
+      <c r="L490" s="22"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
       <c r="A491" s="15"/>
       <c r="B491" s="15"/>
-      <c r="L491" s="23"/>
+      <c r="L491" s="22"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="A492" s="15"/>
       <c r="B492" s="15"/>
-      <c r="L492" s="23"/>
+      <c r="L492" s="22"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="A493" s="15"/>
       <c r="B493" s="15"/>
-      <c r="L493" s="23"/>
+      <c r="L493" s="22"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="A494" s="15"/>
       <c r="B494" s="15"/>
-      <c r="L494" s="23"/>
+      <c r="L494" s="22"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="A495" s="15"/>
       <c r="B495" s="15"/>
-      <c r="L495" s="23"/>
+      <c r="L495" s="22"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
       <c r="A496" s="15"/>
       <c r="B496" s="15"/>
-      <c r="L496" s="23"/>
+      <c r="L496" s="22"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
       <c r="A497" s="15"/>
       <c r="B497" s="15"/>
-      <c r="L497" s="23"/>
+      <c r="L497" s="22"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="A498" s="15"/>
       <c r="B498" s="15"/>
-      <c r="L498" s="23"/>
+      <c r="L498" s="22"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="A499" s="15"/>
       <c r="B499" s="15"/>
-      <c r="L499" s="23"/>
+      <c r="L499" s="22"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="A500" s="15"/>
       <c r="B500" s="15"/>
-      <c r="L500" s="23"/>
+      <c r="L500" s="22"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="A501" s="15"/>
       <c r="B501" s="15"/>
-      <c r="L501" s="23"/>
+      <c r="L501" s="22"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="A502" s="15"/>
       <c r="B502" s="15"/>
-      <c r="L502" s="23"/>
+      <c r="L502" s="22"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
       <c r="A503" s="15"/>
       <c r="B503" s="15"/>
-      <c r="L503" s="23"/>
+      <c r="L503" s="22"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="A504" s="15"/>
       <c r="B504" s="15"/>
-      <c r="L504" s="23"/>
+      <c r="L504" s="22"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="A505" s="15"/>
       <c r="B505" s="15"/>
-      <c r="L505" s="23"/>
+      <c r="L505" s="22"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="A506" s="15"/>
       <c r="B506" s="15"/>
-      <c r="L506" s="23"/>
+      <c r="L506" s="22"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="A507" s="15"/>
       <c r="B507" s="15"/>
-      <c r="L507" s="23"/>
+      <c r="L507" s="22"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="A508" s="15"/>
       <c r="B508" s="15"/>
-      <c r="L508" s="23"/>
+      <c r="L508" s="22"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="A509" s="15"/>
       <c r="B509" s="15"/>
-      <c r="L509" s="23"/>
+      <c r="L509" s="22"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="A510" s="15"/>
       <c r="B510" s="15"/>
-      <c r="L510" s="23"/>
+      <c r="L510" s="22"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="A511" s="15"/>
       <c r="B511" s="15"/>
-      <c r="L511" s="23"/>
+      <c r="L511" s="22"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="A512" s="15"/>
       <c r="B512" s="15"/>
-      <c r="L512" s="23"/>
+      <c r="L512" s="22"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="A513" s="15"/>
       <c r="B513" s="15"/>
-      <c r="L513" s="23"/>
+      <c r="L513" s="22"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="A514" s="15"/>
       <c r="B514" s="15"/>
-      <c r="L514" s="23"/>
+      <c r="L514" s="22"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="A515" s="15"/>
       <c r="B515" s="15"/>
-      <c r="L515" s="23"/>
+      <c r="L515" s="22"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="A516" s="15"/>
       <c r="B516" s="15"/>
-      <c r="L516" s="23"/>
+      <c r="L516" s="22"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="A517" s="15"/>
       <c r="B517" s="15"/>
-      <c r="L517" s="23"/>
+      <c r="L517" s="22"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="A518" s="15"/>
       <c r="B518" s="15"/>
-      <c r="L518" s="23"/>
+      <c r="L518" s="22"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="A519" s="15"/>
       <c r="B519" s="15"/>
-      <c r="L519" s="23"/>
+      <c r="L519" s="22"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="A520" s="15"/>
       <c r="B520" s="15"/>
-      <c r="L520" s="23"/>
+      <c r="L520" s="22"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="A521" s="15"/>
       <c r="B521" s="15"/>
-      <c r="L521" s="23"/>
+      <c r="L521" s="22"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="A522" s="15"/>
       <c r="B522" s="15"/>
-      <c r="L522" s="23"/>
+      <c r="L522" s="22"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="A523" s="15"/>
       <c r="B523" s="15"/>
-      <c r="L523" s="23"/>
+      <c r="L523" s="22"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
       <c r="A524" s="15"/>
       <c r="B524" s="15"/>
-      <c r="L524" s="23"/>
+      <c r="L524" s="22"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
       <c r="A525" s="15"/>
       <c r="B525" s="15"/>
-      <c r="L525" s="23"/>
+      <c r="L525" s="22"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="A526" s="15"/>
       <c r="B526" s="15"/>
-      <c r="L526" s="23"/>
+      <c r="L526" s="22"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="A527" s="15"/>
       <c r="B527" s="15"/>
-      <c r="L527" s="23"/>
+      <c r="L527" s="22"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
       <c r="A528" s="15"/>
       <c r="B528" s="15"/>
-      <c r="L528" s="23"/>
+      <c r="L528" s="22"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
       <c r="A529" s="15"/>
       <c r="B529" s="15"/>
-      <c r="L529" s="23"/>
+      <c r="L529" s="22"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="A530" s="15"/>
       <c r="B530" s="15"/>
-      <c r="L530" s="23"/>
+      <c r="L530" s="22"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="A531" s="15"/>
       <c r="B531" s="15"/>
-      <c r="L531" s="23"/>
+      <c r="L531" s="22"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
       <c r="A532" s="15"/>
       <c r="B532" s="15"/>
-      <c r="L532" s="23"/>
+      <c r="L532" s="22"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
       <c r="A533" s="15"/>
       <c r="B533" s="15"/>
-      <c r="L533" s="23"/>
+      <c r="L533" s="22"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
       <c r="A534" s="15"/>
       <c r="B534" s="15"/>
-      <c r="L534" s="23"/>
+      <c r="L534" s="22"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="A535" s="15"/>
       <c r="B535" s="15"/>
-      <c r="L535" s="23"/>
+      <c r="L535" s="22"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="A536" s="15"/>
       <c r="B536" s="15"/>
-      <c r="L536" s="23"/>
+      <c r="L536" s="22"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
       <c r="A537" s="15"/>
       <c r="B537" s="15"/>
-      <c r="L537" s="23"/>
+      <c r="L537" s="22"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
       <c r="A538" s="15"/>
       <c r="B538" s="15"/>
-      <c r="L538" s="23"/>
+      <c r="L538" s="22"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
       <c r="A539" s="15"/>
       <c r="B539" s="15"/>
-      <c r="L539" s="23"/>
+      <c r="L539" s="22"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
       <c r="A540" s="15"/>
       <c r="B540" s="15"/>
-      <c r="L540" s="23"/>
+      <c r="L540" s="22"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
       <c r="A541" s="15"/>
       <c r="B541" s="15"/>
-      <c r="L541" s="23"/>
+      <c r="L541" s="22"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
       <c r="A542" s="15"/>
       <c r="B542" s="15"/>
-      <c r="L542" s="23"/>
+      <c r="L542" s="22"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
       <c r="A543" s="15"/>
       <c r="B543" s="15"/>
-      <c r="L543" s="23"/>
+      <c r="L543" s="22"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="A544" s="15"/>
       <c r="B544" s="15"/>
-      <c r="L544" s="23"/>
+      <c r="L544" s="22"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="A545" s="15"/>
       <c r="B545" s="15"/>
-      <c r="L545" s="23"/>
+      <c r="L545" s="22"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="A546" s="15"/>
       <c r="B546" s="15"/>
-      <c r="L546" s="23"/>
+      <c r="L546" s="22"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="A547" s="15"/>
       <c r="B547" s="15"/>
-      <c r="L547" s="23"/>
+      <c r="L547" s="22"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="A548" s="15"/>
       <c r="B548" s="15"/>
-      <c r="L548" s="23"/>
+      <c r="L548" s="22"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="A549" s="15"/>
       <c r="B549" s="15"/>
-      <c r="L549" s="23"/>
+      <c r="L549" s="22"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="A550" s="15"/>
       <c r="B550" s="15"/>
-      <c r="L550" s="23"/>
+      <c r="L550" s="22"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="A551" s="15"/>
       <c r="B551" s="15"/>
-      <c r="L551" s="23"/>
+      <c r="L551" s="22"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="A552" s="15"/>
       <c r="B552" s="15"/>
-      <c r="L552" s="23"/>
+      <c r="L552" s="22"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="A553" s="15"/>
       <c r="B553" s="15"/>
-      <c r="L553" s="23"/>
+      <c r="L553" s="22"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="A554" s="15"/>
       <c r="B554" s="15"/>
-      <c r="L554" s="23"/>
+      <c r="L554" s="22"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="A555" s="15"/>
       <c r="B555" s="15"/>
-      <c r="L555" s="23"/>
+      <c r="L555" s="22"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="A556" s="15"/>
       <c r="B556" s="15"/>
-      <c r="L556" s="23"/>
+      <c r="L556" s="22"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="A557" s="15"/>
       <c r="B557" s="15"/>
-      <c r="L557" s="23"/>
+      <c r="L557" s="22"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="A558" s="15"/>
       <c r="B558" s="15"/>
-      <c r="L558" s="23"/>
+      <c r="L558" s="22"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="A559" s="15"/>
       <c r="B559" s="15"/>
-      <c r="L559" s="23"/>
+      <c r="L559" s="22"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="A560" s="15"/>
       <c r="B560" s="15"/>
-      <c r="L560" s="23"/>
+      <c r="L560" s="22"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="A561" s="15"/>
       <c r="B561" s="15"/>
-      <c r="L561" s="23"/>
+      <c r="L561" s="22"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="A562" s="15"/>
       <c r="B562" s="15"/>
-      <c r="L562" s="23"/>
+      <c r="L562" s="22"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
       <c r="A563" s="15"/>
       <c r="B563" s="15"/>
-      <c r="L563" s="23"/>
+      <c r="L563" s="22"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
       <c r="A564" s="15"/>
       <c r="B564" s="15"/>
-      <c r="L564" s="23"/>
+      <c r="L564" s="22"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
       <c r="A565" s="15"/>
       <c r="B565" s="15"/>
-      <c r="L565" s="23"/>
+      <c r="L565" s="22"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
       <c r="A566" s="15"/>
       <c r="B566" s="15"/>
-      <c r="L566" s="23"/>
+      <c r="L566" s="22"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
       <c r="A567" s="15"/>
       <c r="B567" s="15"/>
-      <c r="L567" s="23"/>
+      <c r="L567" s="22"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
       <c r="A568" s="15"/>
       <c r="B568" s="15"/>
-      <c r="L568" s="23"/>
+      <c r="L568" s="22"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
       <c r="A569" s="15"/>
       <c r="B569" s="15"/>
-      <c r="L569" s="23"/>
+      <c r="L569" s="22"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
       <c r="A570" s="15"/>
       <c r="B570" s="15"/>
-      <c r="L570" s="23"/>
+      <c r="L570" s="22"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
       <c r="A571" s="15"/>
       <c r="B571" s="15"/>
-      <c r="L571" s="23"/>
+      <c r="L571" s="22"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
       <c r="A572" s="15"/>
       <c r="B572" s="15"/>
-      <c r="L572" s="23"/>
+      <c r="L572" s="22"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
       <c r="A573" s="15"/>
       <c r="B573" s="15"/>
-      <c r="L573" s="23"/>
+      <c r="L573" s="22"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
       <c r="A574" s="15"/>
       <c r="B574" s="15"/>
-      <c r="L574" s="23"/>
+      <c r="L574" s="22"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
       <c r="A575" s="15"/>
       <c r="B575" s="15"/>
-      <c r="L575" s="23"/>
+      <c r="L575" s="22"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
       <c r="A576" s="15"/>
       <c r="B576" s="15"/>
-      <c r="L576" s="23"/>
+      <c r="L576" s="22"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
       <c r="A577" s="15"/>
       <c r="B577" s="15"/>
-      <c r="L577" s="23"/>
+      <c r="L577" s="22"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
       <c r="A578" s="15"/>
       <c r="B578" s="15"/>
-      <c r="L578" s="23"/>
+      <c r="L578" s="22"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
       <c r="A579" s="15"/>
       <c r="B579" s="15"/>
-      <c r="L579" s="23"/>
+      <c r="L579" s="22"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
       <c r="A580" s="15"/>
       <c r="B580" s="15"/>
-      <c r="L580" s="23"/>
+      <c r="L580" s="22"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
       <c r="A581" s="15"/>
       <c r="B581" s="15"/>
-      <c r="L581" s="23"/>
+      <c r="L581" s="22"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
       <c r="A582" s="15"/>
       <c r="B582" s="15"/>
-      <c r="L582" s="23"/>
+      <c r="L582" s="22"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
       <c r="A583" s="15"/>
       <c r="B583" s="15"/>
-      <c r="L583" s="23"/>
+      <c r="L583" s="22"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
       <c r="A584" s="15"/>
       <c r="B584" s="15"/>
-      <c r="L584" s="23"/>
+      <c r="L584" s="22"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
       <c r="A585" s="15"/>
       <c r="B585" s="15"/>
-      <c r="L585" s="23"/>
+      <c r="L585" s="22"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
       <c r="A586" s="15"/>
       <c r="B586" s="15"/>
-      <c r="L586" s="23"/>
+      <c r="L586" s="22"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="A587" s="15"/>
       <c r="B587" s="15"/>
-      <c r="L587" s="23"/>
+      <c r="L587" s="22"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="A588" s="15"/>
       <c r="B588" s="15"/>
-      <c r="L588" s="23"/>
+      <c r="L588" s="22"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="A589" s="15"/>
       <c r="B589" s="15"/>
-      <c r="L589" s="23"/>
+      <c r="L589" s="22"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="A590" s="15"/>
       <c r="B590" s="15"/>
-      <c r="L590" s="23"/>
+      <c r="L590" s="22"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="A591" s="15"/>
       <c r="B591" s="15"/>
-      <c r="L591" s="23"/>
+      <c r="L591" s="22"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
       <c r="A592" s="15"/>
       <c r="B592" s="15"/>
-      <c r="L592" s="23"/>
+      <c r="L592" s="22"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
       <c r="A593" s="15"/>
       <c r="B593" s="15"/>
-      <c r="L593" s="23"/>
+      <c r="L593" s="22"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="A594" s="15"/>
       <c r="B594" s="15"/>
-      <c r="L594" s="23"/>
+      <c r="L594" s="22"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="A595" s="15"/>
       <c r="B595" s="15"/>
-      <c r="L595" s="23"/>
+      <c r="L595" s="22"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="A596" s="15"/>
       <c r="B596" s="15"/>
-      <c r="L596" s="23"/>
+      <c r="L596" s="22"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="A597" s="15"/>
       <c r="B597" s="15"/>
-      <c r="L597" s="23"/>
+      <c r="L597" s="22"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="A598" s="15"/>
       <c r="B598" s="15"/>
-      <c r="L598" s="23"/>
+      <c r="L598" s="22"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="A599" s="15"/>
       <c r="B599" s="15"/>
-      <c r="L599" s="23"/>
+      <c r="L599" s="22"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
       <c r="A600" s="15"/>
       <c r="B600" s="15"/>
-      <c r="L600" s="23"/>
+      <c r="L600" s="22"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
       <c r="A601" s="15"/>
       <c r="B601" s="15"/>
-      <c r="L601" s="23"/>
+      <c r="L601" s="22"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
       <c r="A602" s="15"/>
       <c r="B602" s="15"/>
-      <c r="L602" s="23"/>
+      <c r="L602" s="22"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
       <c r="A603" s="15"/>
       <c r="B603" s="15"/>
-      <c r="L603" s="23"/>
+      <c r="L603" s="22"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="A604" s="15"/>
       <c r="B604" s="15"/>
-      <c r="L604" s="23"/>
+      <c r="L604" s="22"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="A605" s="15"/>
       <c r="B605" s="15"/>
-      <c r="L605" s="23"/>
+      <c r="L605" s="22"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="A606" s="15"/>
       <c r="B606" s="15"/>
-      <c r="L606" s="23"/>
+      <c r="L606" s="22"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="A607" s="15"/>
       <c r="B607" s="15"/>
-      <c r="L607" s="23"/>
+      <c r="L607" s="22"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
       <c r="A608" s="15"/>
       <c r="B608" s="15"/>
-      <c r="L608" s="23"/>
+      <c r="L608" s="22"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
       <c r="A609" s="15"/>
       <c r="B609" s="15"/>
-      <c r="L609" s="23"/>
+      <c r="L609" s="22"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
       <c r="A610" s="15"/>
       <c r="B610" s="15"/>
-      <c r="L610" s="23"/>
+      <c r="L610" s="22"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="A611" s="15"/>
       <c r="B611" s="15"/>
-      <c r="L611" s="23"/>
+      <c r="L611" s="22"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="A612" s="15"/>
       <c r="B612" s="15"/>
-      <c r="L612" s="23"/>
+      <c r="L612" s="22"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="A613" s="15"/>
       <c r="B613" s="15"/>
-      <c r="L613" s="23"/>
+      <c r="L613" s="22"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="A614" s="15"/>
       <c r="B614" s="15"/>
-      <c r="L614" s="23"/>
+      <c r="L614" s="22"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="A615" s="15"/>
       <c r="B615" s="15"/>
-      <c r="L615" s="23"/>
+      <c r="L615" s="22"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
       <c r="A616" s="15"/>
       <c r="B616" s="15"/>
-      <c r="L616" s="23"/>
+      <c r="L616" s="22"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
       <c r="A617" s="15"/>
       <c r="B617" s="15"/>
-      <c r="L617" s="23"/>
+      <c r="L617" s="22"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
       <c r="A618" s="15"/>
       <c r="B618" s="15"/>
-      <c r="L618" s="23"/>
+      <c r="L618" s="22"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="A619" s="15"/>
       <c r="B619" s="15"/>
-      <c r="L619" s="23"/>
+      <c r="L619" s="22"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="A620" s="15"/>
       <c r="B620" s="15"/>
-      <c r="L620" s="23"/>
+      <c r="L620" s="22"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="A621" s="15"/>
       <c r="B621" s="15"/>
-      <c r="L621" s="23"/>
+      <c r="L621" s="22"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="A622" s="15"/>
       <c r="B622" s="15"/>
-      <c r="L622" s="23"/>
+      <c r="L622" s="22"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
       <c r="A623" s="15"/>
       <c r="B623" s="15"/>
-      <c r="L623" s="23"/>
+      <c r="L623" s="22"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="A624" s="15"/>
       <c r="B624" s="15"/>
-      <c r="L624" s="23"/>
+      <c r="L624" s="22"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
       <c r="A625" s="15"/>
       <c r="B625" s="15"/>
-      <c r="L625" s="23"/>
+      <c r="L625" s="22"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="A626" s="15"/>
       <c r="B626" s="15"/>
-      <c r="L626" s="23"/>
+      <c r="L626" s="22"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="A627" s="15"/>
       <c r="B627" s="15"/>
-      <c r="L627" s="23"/>
+      <c r="L627" s="22"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="A628" s="15"/>
       <c r="B628" s="15"/>
-      <c r="L628" s="23"/>
+      <c r="L628" s="22"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="A629" s="15"/>
       <c r="B629" s="15"/>
-      <c r="L629" s="23"/>
+      <c r="L629" s="22"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="A630" s="15"/>
       <c r="B630" s="15"/>
-      <c r="L630" s="23"/>
+      <c r="L630" s="22"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="A631" s="15"/>
       <c r="B631" s="15"/>
-      <c r="L631" s="23"/>
+      <c r="L631" s="22"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
       <c r="A632" s="15"/>
       <c r="B632" s="15"/>
-      <c r="L632" s="23"/>
+      <c r="L632" s="22"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
       <c r="A633" s="15"/>
       <c r="B633" s="15"/>
-      <c r="L633" s="23"/>
+      <c r="L633" s="22"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
       <c r="A634" s="15"/>
       <c r="B634" s="15"/>
-      <c r="L634" s="23"/>
+      <c r="L634" s="22"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="A635" s="15"/>
       <c r="B635" s="15"/>
-      <c r="L635" s="23"/>
+      <c r="L635" s="22"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="A636" s="15"/>
       <c r="B636" s="15"/>
-      <c r="L636" s="23"/>
+      <c r="L636" s="22"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="A637" s="15"/>
       <c r="B637" s="15"/>
-      <c r="L637" s="23"/>
+      <c r="L637" s="22"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="A638" s="15"/>
       <c r="B638" s="15"/>
-      <c r="L638" s="23"/>
+      <c r="L638" s="22"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="A639" s="15"/>
       <c r="B639" s="15"/>
-      <c r="L639" s="23"/>
+      <c r="L639" s="22"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="A640" s="15"/>
       <c r="B640" s="15"/>
-      <c r="L640" s="23"/>
+      <c r="L640" s="22"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="A641" s="15"/>
       <c r="B641" s="15"/>
-      <c r="L641" s="23"/>
+      <c r="L641" s="22"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="A642" s="15"/>
       <c r="B642" s="15"/>
-      <c r="L642" s="23"/>
+      <c r="L642" s="22"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
       <c r="A643" s="15"/>
       <c r="B643" s="15"/>
-      <c r="L643" s="23"/>
+      <c r="L643" s="22"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
       <c r="A644" s="15"/>
       <c r="B644" s="15"/>
-      <c r="L644" s="23"/>
+      <c r="L644" s="22"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
       <c r="A645" s="15"/>
       <c r="B645" s="15"/>
-      <c r="L645" s="23"/>
+      <c r="L645" s="22"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
       <c r="A646" s="15"/>
       <c r="B646" s="15"/>
-      <c r="L646" s="23"/>
+      <c r="L646" s="22"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
       <c r="A647" s="15"/>
       <c r="B647" s="15"/>
-      <c r="L647" s="23"/>
+      <c r="L647" s="22"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
       <c r="A648" s="15"/>
       <c r="B648" s="15"/>
-      <c r="L648" s="23"/>
+      <c r="L648" s="22"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
       <c r="A649" s="15"/>
       <c r="B649" s="15"/>
-      <c r="L649" s="23"/>
+      <c r="L649" s="22"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
       <c r="A650" s="15"/>
       <c r="B650" s="15"/>
-      <c r="L650" s="23"/>
+      <c r="L650" s="22"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
       <c r="A651" s="15"/>
       <c r="B651" s="15"/>
-      <c r="L651" s="23"/>
+      <c r="L651" s="22"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
       <c r="A652" s="15"/>
       <c r="B652" s="15"/>
-      <c r="L652" s="23"/>
+      <c r="L652" s="22"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
       <c r="A653" s="15"/>
       <c r="B653" s="15"/>
-      <c r="L653" s="23"/>
+      <c r="L653" s="22"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
       <c r="A654" s="15"/>
       <c r="B654" s="15"/>
-      <c r="L654" s="23"/>
+      <c r="L654" s="22"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
       <c r="A655" s="15"/>
       <c r="B655" s="15"/>
-      <c r="L655" s="23"/>
+      <c r="L655" s="22"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
       <c r="A656" s="15"/>
       <c r="B656" s="15"/>
-      <c r="L656" s="23"/>
+      <c r="L656" s="22"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
       <c r="A657" s="15"/>
       <c r="B657" s="15"/>
-      <c r="L657" s="23"/>
+      <c r="L657" s="22"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
       <c r="A658" s="15"/>
       <c r="B658" s="15"/>
-      <c r="L658" s="23"/>
+      <c r="L658" s="22"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
       <c r="A659" s="15"/>
       <c r="B659" s="15"/>
-      <c r="L659" s="23"/>
+      <c r="L659" s="22"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
       <c r="A660" s="15"/>
       <c r="B660" s="15"/>
-      <c r="L660" s="23"/>
+      <c r="L660" s="22"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
       <c r="A661" s="15"/>
       <c r="B661" s="15"/>
-      <c r="L661" s="23"/>
+      <c r="L661" s="22"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
       <c r="A662" s="15"/>
       <c r="B662" s="15"/>
-      <c r="L662" s="23"/>
+      <c r="L662" s="22"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
       <c r="A663" s="15"/>
       <c r="B663" s="15"/>
-      <c r="L663" s="23"/>
+      <c r="L663" s="22"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
       <c r="A664" s="15"/>
       <c r="B664" s="15"/>
-      <c r="L664" s="23"/>
+      <c r="L664" s="22"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
       <c r="A665" s="15"/>
       <c r="B665" s="15"/>
-      <c r="L665" s="23"/>
+      <c r="L665" s="22"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
       <c r="A666" s="15"/>
       <c r="B666" s="15"/>
-      <c r="L666" s="23"/>
+      <c r="L666" s="22"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
       <c r="A667" s="15"/>
       <c r="B667" s="15"/>
-      <c r="L667" s="23"/>
+      <c r="L667" s="22"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
       <c r="A668" s="15"/>
       <c r="B668" s="15"/>
-      <c r="L668" s="23"/>
+      <c r="L668" s="22"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
       <c r="A669" s="15"/>
       <c r="B669" s="15"/>
-      <c r="L669" s="23"/>
+      <c r="L669" s="22"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
       <c r="A670" s="15"/>
       <c r="B670" s="15"/>
-      <c r="L670" s="23"/>
+      <c r="L670" s="22"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
       <c r="A671" s="15"/>
       <c r="B671" s="15"/>
-      <c r="L671" s="23"/>
+      <c r="L671" s="22"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
       <c r="A672" s="15"/>
       <c r="B672" s="15"/>
-      <c r="L672" s="23"/>
+      <c r="L672" s="22"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
       <c r="A673" s="15"/>
       <c r="B673" s="15"/>
-      <c r="L673" s="23"/>
+      <c r="L673" s="22"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
       <c r="A674" s="15"/>
       <c r="B674" s="15"/>
-      <c r="L674" s="23"/>
+      <c r="L674" s="22"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
       <c r="A675" s="15"/>
       <c r="B675" s="15"/>
-      <c r="L675" s="23"/>
+      <c r="L675" s="22"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
       <c r="A676" s="15"/>
       <c r="B676" s="15"/>
-      <c r="L676" s="23"/>
+      <c r="L676" s="22"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
       <c r="A677" s="15"/>
       <c r="B677" s="15"/>
-      <c r="L677" s="23"/>
+      <c r="L677" s="22"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
       <c r="A678" s="15"/>
       <c r="B678" s="15"/>
-      <c r="L678" s="23"/>
+      <c r="L678" s="22"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
       <c r="A679" s="15"/>
       <c r="B679" s="15"/>
-      <c r="L679" s="23"/>
+      <c r="L679" s="22"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
       <c r="A680" s="15"/>
       <c r="B680" s="15"/>
-      <c r="L680" s="23"/>
+      <c r="L680" s="22"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
       <c r="A681" s="15"/>
       <c r="B681" s="15"/>
-      <c r="L681" s="23"/>
+      <c r="L681" s="22"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
       <c r="A682" s="15"/>
       <c r="B682" s="15"/>
-      <c r="L682" s="23"/>
+      <c r="L682" s="22"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
       <c r="A683" s="15"/>
       <c r="B683" s="15"/>
-      <c r="L683" s="23"/>
+      <c r="L683" s="22"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
       <c r="A684" s="15"/>
       <c r="B684" s="15"/>
-      <c r="L684" s="23"/>
+      <c r="L684" s="22"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
       <c r="A685" s="15"/>
       <c r="B685" s="15"/>
-      <c r="L685" s="23"/>
+      <c r="L685" s="22"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
       <c r="A686" s="15"/>
       <c r="B686" s="15"/>
-      <c r="L686" s="23"/>
+      <c r="L686" s="22"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
       <c r="A687" s="15"/>
       <c r="B687" s="15"/>
-      <c r="L687" s="23"/>
+      <c r="L687" s="22"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
       <c r="A688" s="15"/>
       <c r="B688" s="15"/>
-      <c r="L688" s="23"/>
+      <c r="L688" s="22"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
       <c r="A689" s="15"/>
       <c r="B689" s="15"/>
-      <c r="L689" s="23"/>
+      <c r="L689" s="22"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
       <c r="A690" s="15"/>
       <c r="B690" s="15"/>
-      <c r="L690" s="23"/>
+      <c r="L690" s="22"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
       <c r="A691" s="15"/>
       <c r="B691" s="15"/>
-      <c r="L691" s="23"/>
+      <c r="L691" s="22"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
       <c r="A692" s="15"/>
       <c r="B692" s="15"/>
-      <c r="L692" s="23"/>
+      <c r="L692" s="22"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
       <c r="A693" s="15"/>
       <c r="B693" s="15"/>
-      <c r="L693" s="23"/>
+      <c r="L693" s="22"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
       <c r="A694" s="15"/>
       <c r="B694" s="15"/>
-      <c r="L694" s="23"/>
+      <c r="L694" s="22"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
       <c r="A695" s="15"/>
       <c r="B695" s="15"/>
-      <c r="L695" s="23"/>
+      <c r="L695" s="22"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
       <c r="A696" s="15"/>
       <c r="B696" s="15"/>
-      <c r="L696" s="23"/>
+      <c r="L696" s="22"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
       <c r="A697" s="15"/>
       <c r="B697" s="15"/>
-      <c r="L697" s="23"/>
+      <c r="L697" s="22"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
       <c r="A698" s="15"/>
       <c r="B698" s="15"/>
-      <c r="L698" s="23"/>
+      <c r="L698" s="22"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
       <c r="A699" s="15"/>
       <c r="B699" s="15"/>
-      <c r="L699" s="23"/>
+      <c r="L699" s="22"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
       <c r="A700" s="15"/>
       <c r="B700" s="15"/>
-      <c r="L700" s="23"/>
+      <c r="L700" s="22"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
       <c r="A701" s="15"/>
       <c r="B701" s="15"/>
-      <c r="L701" s="23"/>
+      <c r="L701" s="22"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
       <c r="A702" s="15"/>
       <c r="B702" s="15"/>
-      <c r="L702" s="23"/>
+      <c r="L702" s="22"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
       <c r="A703" s="15"/>
       <c r="B703" s="15"/>
-      <c r="L703" s="23"/>
+      <c r="L703" s="22"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
       <c r="A704" s="15"/>
       <c r="B704" s="15"/>
-      <c r="L704" s="23"/>
+      <c r="L704" s="22"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
       <c r="A705" s="15"/>
       <c r="B705" s="15"/>
-      <c r="L705" s="23"/>
+      <c r="L705" s="22"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
       <c r="A706" s="15"/>
       <c r="B706" s="15"/>
-      <c r="L706" s="23"/>
+      <c r="L706" s="22"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
       <c r="A707" s="15"/>
       <c r="B707" s="15"/>
-      <c r="L707" s="23"/>
+      <c r="L707" s="22"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
       <c r="A708" s="15"/>
       <c r="B708" s="15"/>
-      <c r="L708" s="23"/>
+      <c r="L708" s="22"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
       <c r="A709" s="15"/>
       <c r="B709" s="15"/>
-      <c r="L709" s="23"/>
+      <c r="L709" s="22"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
       <c r="A710" s="15"/>
       <c r="B710" s="15"/>
-      <c r="L710" s="23"/>
+      <c r="L710" s="22"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
       <c r="A711" s="15"/>
       <c r="B711" s="15"/>
-      <c r="L711" s="23"/>
+      <c r="L711" s="22"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
       <c r="A712" s="15"/>
       <c r="B712" s="15"/>
-      <c r="L712" s="23"/>
+      <c r="L712" s="22"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
       <c r="A713" s="15"/>
       <c r="B713" s="15"/>
-      <c r="L713" s="23"/>
+      <c r="L713" s="22"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
       <c r="A714" s="15"/>
       <c r="B714" s="15"/>
-      <c r="L714" s="23"/>
+      <c r="L714" s="22"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
       <c r="A715" s="15"/>
       <c r="B715" s="15"/>
-      <c r="L715" s="23"/>
+      <c r="L715" s="22"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
       <c r="A716" s="15"/>
       <c r="B716" s="15"/>
-      <c r="L716" s="23"/>
+      <c r="L716" s="22"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
       <c r="A717" s="15"/>
       <c r="B717" s="15"/>
-      <c r="L717" s="23"/>
+      <c r="L717" s="22"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
       <c r="A718" s="15"/>
       <c r="B718" s="15"/>
-      <c r="L718" s="23"/>
+      <c r="L718" s="22"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
       <c r="A719" s="15"/>
       <c r="B719" s="15"/>
-      <c r="L719" s="23"/>
+      <c r="L719" s="22"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
       <c r="A720" s="15"/>
       <c r="B720" s="15"/>
-      <c r="L720" s="23"/>
+      <c r="L720" s="22"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
       <c r="A721" s="15"/>
       <c r="B721" s="15"/>
-      <c r="L721" s="23"/>
+      <c r="L721" s="22"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
       <c r="A722" s="15"/>
       <c r="B722" s="15"/>
-      <c r="L722" s="23"/>
+      <c r="L722" s="22"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
       <c r="A723" s="15"/>
       <c r="B723" s="15"/>
-      <c r="L723" s="23"/>
+      <c r="L723" s="22"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
       <c r="A724" s="15"/>
       <c r="B724" s="15"/>
-      <c r="L724" s="23"/>
+      <c r="L724" s="22"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
       <c r="A725" s="15"/>
       <c r="B725" s="15"/>
-      <c r="L725" s="23"/>
+      <c r="L725" s="22"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
       <c r="A726" s="15"/>
       <c r="B726" s="15"/>
-      <c r="L726" s="23"/>
+      <c r="L726" s="22"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
       <c r="A727" s="15"/>
       <c r="B727" s="15"/>
-      <c r="L727" s="23"/>
+      <c r="L727" s="22"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
       <c r="A728" s="15"/>
       <c r="B728" s="15"/>
-      <c r="L728" s="23"/>
+      <c r="L728" s="22"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
       <c r="A729" s="15"/>
       <c r="B729" s="15"/>
-      <c r="L729" s="23"/>
+      <c r="L729" s="22"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
       <c r="A730" s="15"/>
       <c r="B730" s="15"/>
-      <c r="L730" s="23"/>
+      <c r="L730" s="22"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
       <c r="A731" s="15"/>
       <c r="B731" s="15"/>
-      <c r="L731" s="23"/>
+      <c r="L731" s="22"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
       <c r="A732" s="15"/>
       <c r="B732" s="15"/>
-      <c r="L732" s="23"/>
+      <c r="L732" s="22"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
       <c r="A733" s="15"/>
       <c r="B733" s="15"/>
-      <c r="L733" s="23"/>
+      <c r="L733" s="22"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
       <c r="A734" s="15"/>
       <c r="B734" s="15"/>
-      <c r="L734" s="23"/>
+      <c r="L734" s="22"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
       <c r="A735" s="15"/>
       <c r="B735" s="15"/>
-      <c r="L735" s="23"/>
+      <c r="L735" s="22"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
       <c r="A736" s="15"/>
       <c r="B736" s="15"/>
-      <c r="L736" s="23"/>
+      <c r="L736" s="22"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
       <c r="A737" s="15"/>
       <c r="B737" s="15"/>
-      <c r="L737" s="23"/>
+      <c r="L737" s="22"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
       <c r="A738" s="15"/>
       <c r="B738" s="15"/>
-      <c r="L738" s="23"/>
+      <c r="L738" s="22"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
       <c r="A739" s="15"/>
       <c r="B739" s="15"/>
-      <c r="L739" s="23"/>
+      <c r="L739" s="22"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
       <c r="A740" s="15"/>
       <c r="B740" s="15"/>
-      <c r="L740" s="23"/>
+      <c r="L740" s="22"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
       <c r="A741" s="15"/>
       <c r="B741" s="15"/>
-      <c r="L741" s="23"/>
+      <c r="L741" s="22"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
       <c r="A742" s="15"/>
       <c r="B742" s="15"/>
-      <c r="L742" s="23"/>
+      <c r="L742" s="22"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
       <c r="A743" s="15"/>
       <c r="B743" s="15"/>
-      <c r="L743" s="23"/>
+      <c r="L743" s="22"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
       <c r="A744" s="15"/>
       <c r="B744" s="15"/>
-      <c r="L744" s="23"/>
+      <c r="L744" s="22"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
       <c r="A745" s="15"/>
       <c r="B745" s="15"/>
-      <c r="L745" s="23"/>
+      <c r="L745" s="22"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
       <c r="A746" s="15"/>
       <c r="B746" s="15"/>
-      <c r="L746" s="23"/>
+      <c r="L746" s="22"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
       <c r="A747" s="15"/>
       <c r="B747" s="15"/>
-      <c r="L747" s="23"/>
+      <c r="L747" s="22"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
       <c r="A748" s="15"/>
       <c r="B748" s="15"/>
-      <c r="L748" s="23"/>
+      <c r="L748" s="22"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
       <c r="A749" s="15"/>
       <c r="B749" s="15"/>
-      <c r="L749" s="23"/>
+      <c r="L749" s="22"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
       <c r="A750" s="15"/>
       <c r="B750" s="15"/>
-      <c r="L750" s="23"/>
+      <c r="L750" s="22"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
       <c r="A751" s="15"/>
       <c r="B751" s="15"/>
-      <c r="L751" s="23"/>
+      <c r="L751" s="22"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
       <c r="A752" s="15"/>
       <c r="B752" s="15"/>
-      <c r="L752" s="23"/>
+      <c r="L752" s="22"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
       <c r="A753" s="15"/>
       <c r="B753" s="15"/>
-      <c r="L753" s="23"/>
+      <c r="L753" s="22"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
       <c r="A754" s="15"/>
       <c r="B754" s="15"/>
-      <c r="L754" s="23"/>
+      <c r="L754" s="22"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
       <c r="A755" s="15"/>
       <c r="B755" s="15"/>
-      <c r="L755" s="23"/>
+      <c r="L755" s="22"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
       <c r="A756" s="15"/>
       <c r="B756" s="15"/>
-      <c r="L756" s="23"/>
+      <c r="L756" s="22"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
       <c r="A757" s="15"/>
       <c r="B757" s="15"/>
-      <c r="L757" s="23"/>
+      <c r="L757" s="22"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
       <c r="A758" s="15"/>
       <c r="B758" s="15"/>
-      <c r="L758" s="23"/>
+      <c r="L758" s="22"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
       <c r="A759" s="15"/>
       <c r="B759" s="15"/>
-      <c r="L759" s="23"/>
+      <c r="L759" s="22"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
       <c r="A760" s="15"/>
       <c r="B760" s="15"/>
-      <c r="L760" s="23"/>
+      <c r="L760" s="22"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
       <c r="A761" s="15"/>
       <c r="B761" s="15"/>
-      <c r="L761" s="23"/>
+      <c r="L761" s="22"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
       <c r="A762" s="15"/>
       <c r="B762" s="15"/>
-      <c r="L762" s="23"/>
+      <c r="L762" s="22"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
       <c r="A763" s="15"/>
       <c r="B763" s="15"/>
-      <c r="L763" s="23"/>
+      <c r="L763" s="22"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
       <c r="A764" s="15"/>
       <c r="B764" s="15"/>
-      <c r="L764" s="23"/>
+      <c r="L764" s="22"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
       <c r="A765" s="15"/>
       <c r="B765" s="15"/>
-      <c r="L765" s="23"/>
+      <c r="L765" s="22"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
       <c r="A766" s="15"/>
       <c r="B766" s="15"/>
-      <c r="L766" s="23"/>
+      <c r="L766" s="22"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
       <c r="A767" s="15"/>
       <c r="B767" s="15"/>
-      <c r="L767" s="23"/>
+      <c r="L767" s="22"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
       <c r="A768" s="15"/>
       <c r="B768" s="15"/>
-      <c r="L768" s="23"/>
+      <c r="L768" s="22"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
       <c r="A769" s="15"/>
       <c r="B769" s="15"/>
-      <c r="L769" s="23"/>
+      <c r="L769" s="22"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
       <c r="A770" s="15"/>
       <c r="B770" s="15"/>
-      <c r="L770" s="23"/>
+      <c r="L770" s="22"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
       <c r="A771" s="15"/>
       <c r="B771" s="15"/>
-      <c r="L771" s="23"/>
+      <c r="L771" s="22"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
       <c r="A772" s="15"/>
       <c r="B772" s="15"/>
-      <c r="L772" s="23"/>
+      <c r="L772" s="22"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
       <c r="A773" s="15"/>
       <c r="B773" s="15"/>
-      <c r="L773" s="23"/>
+      <c r="L773" s="22"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
       <c r="A774" s="15"/>
       <c r="B774" s="15"/>
-      <c r="L774" s="23"/>
+      <c r="L774" s="22"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
       <c r="A775" s="15"/>
       <c r="B775" s="15"/>
-      <c r="L775" s="23"/>
+      <c r="L775" s="22"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
       <c r="A776" s="15"/>
       <c r="B776" s="15"/>
-      <c r="L776" s="23"/>
+      <c r="L776" s="22"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
       <c r="A777" s="15"/>
       <c r="B777" s="15"/>
-      <c r="L777" s="23"/>
+      <c r="L777" s="22"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
       <c r="A778" s="15"/>
       <c r="B778" s="15"/>
-      <c r="L778" s="23"/>
+      <c r="L778" s="22"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
       <c r="A779" s="15"/>
       <c r="B779" s="15"/>
-      <c r="L779" s="23"/>
+      <c r="L779" s="22"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
       <c r="A780" s="15"/>
       <c r="B780" s="15"/>
-      <c r="L780" s="23"/>
+      <c r="L780" s="22"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
       <c r="A781" s="15"/>
       <c r="B781" s="15"/>
-      <c r="L781" s="23"/>
+      <c r="L781" s="22"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
       <c r="A782" s="15"/>
       <c r="B782" s="15"/>
-      <c r="L782" s="23"/>
+      <c r="L782" s="22"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
       <c r="A783" s="15"/>
       <c r="B783" s="15"/>
-      <c r="L783" s="23"/>
+      <c r="L783" s="22"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
       <c r="A784" s="15"/>
       <c r="B784" s="15"/>
-      <c r="L784" s="23"/>
+      <c r="L784" s="22"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
       <c r="A785" s="15"/>
       <c r="B785" s="15"/>
-      <c r="L785" s="23"/>
+      <c r="L785" s="22"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
       <c r="A786" s="15"/>
       <c r="B786" s="15"/>
-      <c r="L786" s="23"/>
+      <c r="L786" s="22"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
       <c r="A787" s="15"/>
       <c r="B787" s="15"/>
-      <c r="L787" s="23"/>
+      <c r="L787" s="22"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
       <c r="A788" s="15"/>
       <c r="B788" s="15"/>
-      <c r="L788" s="23"/>
+      <c r="L788" s="22"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
       <c r="A789" s="15"/>
       <c r="B789" s="15"/>
-      <c r="L789" s="23"/>
+      <c r="L789" s="22"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
       <c r="A790" s="15"/>
       <c r="B790" s="15"/>
-      <c r="L790" s="23"/>
+      <c r="L790" s="22"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
       <c r="A791" s="15"/>
       <c r="B791" s="15"/>
-      <c r="L791" s="23"/>
+      <c r="L791" s="22"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
       <c r="A792" s="15"/>
       <c r="B792" s="15"/>
-      <c r="L792" s="23"/>
+      <c r="L792" s="22"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
       <c r="A793" s="15"/>
       <c r="B793" s="15"/>
-      <c r="L793" s="23"/>
+      <c r="L793" s="22"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
       <c r="A794" s="15"/>
       <c r="B794" s="15"/>
-      <c r="L794" s="23"/>
+      <c r="L794" s="22"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
       <c r="A795" s="15"/>
       <c r="B795" s="15"/>
-      <c r="L795" s="23"/>
+      <c r="L795" s="22"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
       <c r="A796" s="15"/>
       <c r="B796" s="15"/>
-      <c r="L796" s="23"/>
+      <c r="L796" s="22"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
       <c r="A797" s="15"/>
       <c r="B797" s="15"/>
-      <c r="L797" s="23"/>
+      <c r="L797" s="22"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
       <c r="A798" s="15"/>
       <c r="B798" s="15"/>
-      <c r="L798" s="23"/>
+      <c r="L798" s="22"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
       <c r="A799" s="15"/>
       <c r="B799" s="15"/>
-      <c r="L799" s="23"/>
+      <c r="L799" s="22"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
       <c r="A800" s="15"/>
       <c r="B800" s="15"/>
-      <c r="L800" s="23"/>
+      <c r="L800" s="22"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
       <c r="A801" s="15"/>
       <c r="B801" s="15"/>
-      <c r="L801" s="23"/>
+      <c r="L801" s="22"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
       <c r="A802" s="15"/>
       <c r="B802" s="15"/>
-      <c r="L802" s="23"/>
+      <c r="L802" s="22"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
       <c r="A803" s="15"/>
       <c r="B803" s="15"/>
-      <c r="L803" s="23"/>
+      <c r="L803" s="22"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
       <c r="A804" s="15"/>
       <c r="B804" s="15"/>
-      <c r="L804" s="23"/>
+      <c r="L804" s="22"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
       <c r="A805" s="15"/>
       <c r="B805" s="15"/>
-      <c r="L805" s="23"/>
+      <c r="L805" s="22"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
       <c r="A806" s="15"/>
       <c r="B806" s="15"/>
-      <c r="L806" s="23"/>
+      <c r="L806" s="22"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
       <c r="A807" s="15"/>
       <c r="B807" s="15"/>
-      <c r="L807" s="23"/>
+      <c r="L807" s="22"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
       <c r="A808" s="15"/>
       <c r="B808" s="15"/>
-      <c r="L808" s="23"/>
+      <c r="L808" s="22"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
       <c r="A809" s="15"/>
       <c r="B809" s="15"/>
-      <c r="L809" s="23"/>
+      <c r="L809" s="22"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
       <c r="A810" s="15"/>
       <c r="B810" s="15"/>
-      <c r="L810" s="23"/>
+      <c r="L810" s="22"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
       <c r="A811" s="15"/>
       <c r="B811" s="15"/>
-      <c r="L811" s="23"/>
+      <c r="L811" s="22"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
       <c r="A812" s="15"/>
       <c r="B812" s="15"/>
-      <c r="L812" s="23"/>
+      <c r="L812" s="22"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
       <c r="A813" s="15"/>
       <c r="B813" s="15"/>
-      <c r="L813" s="23"/>
+      <c r="L813" s="22"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
       <c r="A814" s="15"/>
       <c r="B814" s="15"/>
-      <c r="L814" s="23"/>
+      <c r="L814" s="22"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
       <c r="A815" s="15"/>
       <c r="B815" s="15"/>
-      <c r="L815" s="23"/>
+      <c r="L815" s="22"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
       <c r="A816" s="15"/>
       <c r="B816" s="15"/>
-      <c r="L816" s="23"/>
+      <c r="L816" s="22"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
       <c r="A817" s="15"/>
       <c r="B817" s="15"/>
-      <c r="L817" s="23"/>
+      <c r="L817" s="22"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
       <c r="A818" s="15"/>
       <c r="B818" s="15"/>
-      <c r="L818" s="23"/>
+      <c r="L818" s="22"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
       <c r="A819" s="15"/>
       <c r="B819" s="15"/>
-      <c r="L819" s="23"/>
+      <c r="L819" s="22"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
       <c r="A820" s="15"/>
       <c r="B820" s="15"/>
-      <c r="L820" s="23"/>
+      <c r="L820" s="22"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
       <c r="A821" s="15"/>
       <c r="B821" s="15"/>
-      <c r="L821" s="23"/>
+      <c r="L821" s="22"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
       <c r="A822" s="15"/>
       <c r="B822" s="15"/>
-      <c r="L822" s="23"/>
+      <c r="L822" s="22"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
       <c r="A823" s="15"/>
       <c r="B823" s="15"/>
-      <c r="L823" s="23"/>
+      <c r="L823" s="22"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
       <c r="A824" s="15"/>
       <c r="B824" s="15"/>
-      <c r="L824" s="23"/>
+      <c r="L824" s="22"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
       <c r="A825" s="15"/>
       <c r="B825" s="15"/>
-      <c r="L825" s="23"/>
+      <c r="L825" s="22"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
       <c r="A826" s="15"/>
       <c r="B826" s="15"/>
-      <c r="L826" s="23"/>
+      <c r="L826" s="22"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
       <c r="A827" s="15"/>
       <c r="B827" s="15"/>
-      <c r="L827" s="23"/>
+      <c r="L827" s="22"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
       <c r="A828" s="15"/>
       <c r="B828" s="15"/>
-      <c r="L828" s="23"/>
+      <c r="L828" s="22"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
       <c r="A829" s="15"/>
       <c r="B829" s="15"/>
-      <c r="L829" s="23"/>
+      <c r="L829" s="22"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
       <c r="A830" s="15"/>
       <c r="B830" s="15"/>
-      <c r="L830" s="23"/>
+      <c r="L830" s="22"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
       <c r="A831" s="15"/>
       <c r="B831" s="15"/>
-      <c r="L831" s="23"/>
+      <c r="L831" s="22"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
       <c r="A832" s="15"/>
       <c r="B832" s="15"/>
-      <c r="L832" s="23"/>
+      <c r="L832" s="22"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
       <c r="A833" s="15"/>
       <c r="B833" s="15"/>
-      <c r="L833" s="23"/>
+      <c r="L833" s="22"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
       <c r="A834" s="15"/>
       <c r="B834" s="15"/>
-      <c r="L834" s="23"/>
+      <c r="L834" s="22"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
       <c r="A835" s="15"/>
       <c r="B835" s="15"/>
-      <c r="L835" s="23"/>
+      <c r="L835" s="22"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
       <c r="A836" s="15"/>
       <c r="B836" s="15"/>
-      <c r="L836" s="23"/>
+      <c r="L836" s="22"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
       <c r="A837" s="15"/>
       <c r="B837" s="15"/>
-      <c r="L837" s="23"/>
+      <c r="L837" s="22"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
       <c r="A838" s="15"/>
       <c r="B838" s="15"/>
-      <c r="L838" s="23"/>
+      <c r="L838" s="22"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
       <c r="A839" s="15"/>
       <c r="B839" s="15"/>
-      <c r="L839" s="23"/>
+      <c r="L839" s="22"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
       <c r="A840" s="15"/>
       <c r="B840" s="15"/>
-      <c r="L840" s="23"/>
+      <c r="L840" s="22"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
       <c r="A841" s="15"/>
       <c r="B841" s="15"/>
-      <c r="L841" s="23"/>
+      <c r="L841" s="22"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
       <c r="A842" s="15"/>
       <c r="B842" s="15"/>
-      <c r="L842" s="23"/>
+      <c r="L842" s="22"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
       <c r="A843" s="15"/>
       <c r="B843" s="15"/>
-      <c r="L843" s="23"/>
+      <c r="L843" s="22"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
       <c r="A844" s="15"/>
       <c r="B844" s="15"/>
-      <c r="L844" s="23"/>
+      <c r="L844" s="22"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
       <c r="A845" s="15"/>
       <c r="B845" s="15"/>
-      <c r="L845" s="23"/>
+      <c r="L845" s="22"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
       <c r="A846" s="15"/>
       <c r="B846" s="15"/>
-      <c r="L846" s="23"/>
+      <c r="L846" s="22"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
       <c r="A847" s="15"/>
       <c r="B847" s="15"/>
-      <c r="L847" s="23"/>
+      <c r="L847" s="22"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
       <c r="A848" s="15"/>
       <c r="B848" s="15"/>
-      <c r="L848" s="23"/>
+      <c r="L848" s="22"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
       <c r="A849" s="15"/>
       <c r="B849" s="15"/>
-      <c r="L849" s="23"/>
+      <c r="L849" s="22"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
       <c r="A850" s="15"/>
       <c r="B850" s="15"/>
-      <c r="L850" s="23"/>
+      <c r="L850" s="22"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
       <c r="A851" s="15"/>
       <c r="B851" s="15"/>
-      <c r="L851" s="23"/>
+      <c r="L851" s="22"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
       <c r="A852" s="15"/>
       <c r="B852" s="15"/>
-      <c r="L852" s="23"/>
+      <c r="L852" s="22"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
       <c r="A853" s="15"/>
       <c r="B853" s="15"/>
-      <c r="L853" s="23"/>
+      <c r="L853" s="22"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
       <c r="A854" s="15"/>
       <c r="B854" s="15"/>
-      <c r="L854" s="23"/>
+      <c r="L854" s="22"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
       <c r="A855" s="15"/>
       <c r="B855" s="15"/>
-      <c r="L855" s="23"/>
+      <c r="L855" s="22"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
       <c r="A856" s="15"/>
       <c r="B856" s="15"/>
-      <c r="L856" s="23"/>
+      <c r="L856" s="22"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
       <c r="A857" s="15"/>
       <c r="B857" s="15"/>
-      <c r="L857" s="23"/>
+      <c r="L857" s="22"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
       <c r="A858" s="15"/>
       <c r="B858" s="15"/>
-      <c r="L858" s="23"/>
+      <c r="L858" s="22"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
       <c r="A859" s="15"/>
       <c r="B859" s="15"/>
-      <c r="L859" s="23"/>
+      <c r="L859" s="22"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
       <c r="A860" s="15"/>
       <c r="B860" s="15"/>
-      <c r="L860" s="23"/>
+      <c r="L860" s="22"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
       <c r="A861" s="15"/>
       <c r="B861" s="15"/>
-      <c r="L861" s="23"/>
+      <c r="L861" s="22"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
       <c r="A862" s="15"/>
       <c r="B862" s="15"/>
-      <c r="L862" s="23"/>
+      <c r="L862" s="22"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
       <c r="A863" s="15"/>
       <c r="B863" s="15"/>
-      <c r="L863" s="23"/>
+      <c r="L863" s="22"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
       <c r="A864" s="15"/>
       <c r="B864" s="15"/>
-      <c r="L864" s="23"/>
+      <c r="L864" s="22"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
       <c r="A865" s="15"/>
       <c r="B865" s="15"/>
-      <c r="L865" s="23"/>
+      <c r="L865" s="22"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
       <c r="A866" s="15"/>
       <c r="B866" s="15"/>
-      <c r="L866" s="23"/>
+      <c r="L866" s="22"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
       <c r="A867" s="15"/>
       <c r="B867" s="15"/>
-      <c r="L867" s="23"/>
+      <c r="L867" s="22"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
       <c r="A868" s="15"/>
       <c r="B868" s="15"/>
-      <c r="L868" s="23"/>
+      <c r="L868" s="22"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
       <c r="A869" s="15"/>
       <c r="B869" s="15"/>
-      <c r="L869" s="23"/>
+      <c r="L869" s="22"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
       <c r="A870" s="15"/>
       <c r="B870" s="15"/>
-      <c r="L870" s="23"/>
+      <c r="L870" s="22"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
       <c r="A871" s="15"/>
       <c r="B871" s="15"/>
-      <c r="L871" s="23"/>
+      <c r="L871" s="22"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
       <c r="A872" s="15"/>
       <c r="B872" s="15"/>
-      <c r="L872" s="23"/>
+      <c r="L872" s="22"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
       <c r="A873" s="15"/>
       <c r="B873" s="15"/>
-      <c r="L873" s="23"/>
+      <c r="L873" s="22"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
       <c r="A874" s="15"/>
       <c r="B874" s="15"/>
-      <c r="L874" s="23"/>
+      <c r="L874" s="22"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
       <c r="A875" s="15"/>
       <c r="B875" s="15"/>
-      <c r="L875" s="23"/>
+      <c r="L875" s="22"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
       <c r="A876" s="15"/>
       <c r="B876" s="15"/>
-      <c r="L876" s="23"/>
+      <c r="L876" s="22"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
       <c r="A877" s="15"/>
       <c r="B877" s="15"/>
-      <c r="L877" s="23"/>
+      <c r="L877" s="22"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
       <c r="A878" s="15"/>
       <c r="B878" s="15"/>
-      <c r="L878" s="23"/>
+      <c r="L878" s="22"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
       <c r="A879" s="15"/>
       <c r="B879" s="15"/>
-      <c r="L879" s="23"/>
+      <c r="L879" s="22"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
       <c r="A880" s="15"/>
       <c r="B880" s="15"/>
-      <c r="L880" s="23"/>
+      <c r="L880" s="22"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
       <c r="A881" s="15"/>
       <c r="B881" s="15"/>
-      <c r="L881" s="23"/>
+      <c r="L881" s="22"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
       <c r="A882" s="15"/>
       <c r="B882" s="15"/>
-      <c r="L882" s="23"/>
+      <c r="L882" s="22"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
       <c r="A883" s="15"/>
       <c r="B883" s="15"/>
-      <c r="L883" s="23"/>
+      <c r="L883" s="22"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
       <c r="A884" s="15"/>
       <c r="B884" s="15"/>
-      <c r="L884" s="23"/>
+      <c r="L884" s="22"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
       <c r="A885" s="15"/>
       <c r="B885" s="15"/>
-      <c r="L885" s="23"/>
+      <c r="L885" s="22"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
       <c r="A886" s="15"/>
       <c r="B886" s="15"/>
-      <c r="L886" s="23"/>
+      <c r="L886" s="22"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
       <c r="A887" s="15"/>
       <c r="B887" s="15"/>
-      <c r="L887" s="23"/>
+      <c r="L887" s="22"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
       <c r="A888" s="15"/>
       <c r="B888" s="15"/>
-      <c r="L888" s="23"/>
+      <c r="L888" s="22"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
       <c r="A889" s="15"/>
       <c r="B889" s="15"/>
-      <c r="L889" s="23"/>
+      <c r="L889" s="22"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
       <c r="A890" s="15"/>
       <c r="B890" s="15"/>
-      <c r="L890" s="23"/>
+      <c r="L890" s="22"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
       <c r="A891" s="15"/>
       <c r="B891" s="15"/>
-      <c r="L891" s="23"/>
+      <c r="L891" s="22"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
       <c r="A892" s="15"/>
       <c r="B892" s="15"/>
-      <c r="L892" s="23"/>
+      <c r="L892" s="22"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
       <c r="A893" s="15"/>
       <c r="B893" s="15"/>
-      <c r="L893" s="23"/>
+      <c r="L893" s="22"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
       <c r="A894" s="15"/>
       <c r="B894" s="15"/>
-      <c r="L894" s="23"/>
+      <c r="L894" s="22"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
       <c r="A895" s="15"/>
       <c r="B895" s="15"/>
-      <c r="L895" s="23"/>
+      <c r="L895" s="22"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
       <c r="A896" s="15"/>
       <c r="B896" s="15"/>
-      <c r="L896" s="23"/>
+      <c r="L896" s="22"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
       <c r="A897" s="15"/>
       <c r="B897" s="15"/>
-      <c r="L897" s="23"/>
+      <c r="L897" s="22"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
       <c r="A898" s="15"/>
       <c r="B898" s="15"/>
-      <c r="L898" s="23"/>
+      <c r="L898" s="22"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
       <c r="A899" s="15"/>
       <c r="B899" s="15"/>
-      <c r="L899" s="23"/>
+      <c r="L899" s="22"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
       <c r="A900" s="15"/>
       <c r="B900" s="15"/>
-      <c r="L900" s="23"/>
+      <c r="L900" s="22"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
       <c r="A901" s="15"/>
       <c r="B901" s="15"/>
-      <c r="L901" s="23"/>
+      <c r="L901" s="22"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
       <c r="A902" s="15"/>
       <c r="B902" s="15"/>
-      <c r="L902" s="23"/>
+      <c r="L902" s="22"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
       <c r="A903" s="15"/>
       <c r="B903" s="15"/>
-      <c r="L903" s="23"/>
+      <c r="L903" s="22"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
       <c r="A904" s="15"/>
       <c r="B904" s="15"/>
-      <c r="L904" s="23"/>
+      <c r="L904" s="22"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
       <c r="A905" s="15"/>
       <c r="B905" s="15"/>
-      <c r="L905" s="23"/>
+      <c r="L905" s="22"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
       <c r="A906" s="15"/>
       <c r="B906" s="15"/>
-      <c r="L906" s="23"/>
+      <c r="L906" s="22"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
       <c r="A907" s="15"/>
       <c r="B907" s="15"/>
-      <c r="L907" s="23"/>
+      <c r="L907" s="22"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
       <c r="A908" s="15"/>
       <c r="B908" s="15"/>
-      <c r="L908" s="23"/>
+      <c r="L908" s="22"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
       <c r="A909" s="15"/>
       <c r="B909" s="15"/>
-      <c r="L909" s="23"/>
+      <c r="L909" s="22"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
       <c r="A910" s="15"/>
       <c r="B910" s="15"/>
-      <c r="L910" s="23"/>
+      <c r="L910" s="22"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
       <c r="A911" s="15"/>
       <c r="B911" s="15"/>
-      <c r="L911" s="23"/>
+      <c r="L911" s="22"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
       <c r="A912" s="15"/>
       <c r="B912" s="15"/>
-      <c r="L912" s="23"/>
+      <c r="L912" s="22"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
       <c r="A913" s="15"/>
       <c r="B913" s="15"/>
-      <c r="L913" s="23"/>
+      <c r="L913" s="22"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
       <c r="A914" s="15"/>
       <c r="B914" s="15"/>
-      <c r="L914" s="23"/>
+      <c r="L914" s="22"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
       <c r="A915" s="15"/>
       <c r="B915" s="15"/>
-      <c r="L915" s="23"/>
+      <c r="L915" s="22"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
       <c r="A916" s="15"/>
       <c r="B916" s="15"/>
-      <c r="L916" s="23"/>
+      <c r="L916" s="22"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
       <c r="A917" s="15"/>
       <c r="B917" s="15"/>
-      <c r="L917" s="23"/>
+      <c r="L917" s="22"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
       <c r="A918" s="15"/>
       <c r="B918" s="15"/>
-      <c r="L918" s="23"/>
+      <c r="L918" s="22"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
       <c r="A919" s="15"/>
       <c r="B919" s="15"/>
-      <c r="L919" s="23"/>
+      <c r="L919" s="22"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
       <c r="A920" s="15"/>
       <c r="B920" s="15"/>
-      <c r="L920" s="23"/>
+      <c r="L920" s="22"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
       <c r="A921" s="15"/>
       <c r="B921" s="15"/>
-      <c r="L921" s="23"/>
+      <c r="L921" s="22"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
       <c r="A922" s="15"/>
       <c r="B922" s="15"/>
-      <c r="L922" s="23"/>
+      <c r="L922" s="22"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
       <c r="A923" s="15"/>
       <c r="B923" s="15"/>
-      <c r="L923" s="23"/>
+      <c r="L923" s="22"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
       <c r="A924" s="15"/>
       <c r="B924" s="15"/>
-      <c r="L924" s="23"/>
+      <c r="L924" s="22"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
       <c r="A925" s="15"/>
       <c r="B925" s="15"/>
-      <c r="L925" s="23"/>
+      <c r="L925" s="22"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
       <c r="A926" s="15"/>
       <c r="B926" s="15"/>
-      <c r="L926" s="23"/>
+      <c r="L926" s="22"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
       <c r="A927" s="15"/>
       <c r="B927" s="15"/>
-      <c r="L927" s="23"/>
+      <c r="L927" s="22"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
       <c r="A928" s="15"/>
       <c r="B928" s="15"/>
-      <c r="L928" s="23"/>
+      <c r="L928" s="22"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
       <c r="A929" s="15"/>
       <c r="B929" s="15"/>
-      <c r="L929" s="23"/>
+      <c r="L929" s="22"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
       <c r="A930" s="15"/>
       <c r="B930" s="15"/>
-      <c r="L930" s="23"/>
+      <c r="L930" s="22"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
       <c r="A931" s="15"/>
       <c r="B931" s="15"/>
-      <c r="L931" s="23"/>
+      <c r="L931" s="22"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
       <c r="A932" s="15"/>
       <c r="B932" s="15"/>
-      <c r="L932" s="23"/>
+      <c r="L932" s="22"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
       <c r="A933" s="15"/>
       <c r="B933" s="15"/>
-      <c r="L933" s="23"/>
+      <c r="L933" s="22"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
       <c r="A934" s="15"/>
       <c r="B934" s="15"/>
-      <c r="L934" s="23"/>
+      <c r="L934" s="22"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
       <c r="A935" s="15"/>
       <c r="B935" s="15"/>
-      <c r="L935" s="23"/>
+      <c r="L935" s="22"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
       <c r="A936" s="15"/>
       <c r="B936" s="15"/>
-      <c r="L936" s="23"/>
+      <c r="L936" s="22"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
       <c r="A937" s="15"/>
       <c r="B937" s="15"/>
-      <c r="L937" s="23"/>
+      <c r="L937" s="22"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
       <c r="A938" s="15"/>
       <c r="B938" s="15"/>
-      <c r="L938" s="23"/>
+      <c r="L938" s="22"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
       <c r="A939" s="15"/>
       <c r="B939" s="15"/>
-      <c r="L939" s="23"/>
+      <c r="L939" s="22"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
       <c r="A940" s="15"/>
       <c r="B940" s="15"/>
-      <c r="L940" s="23"/>
+      <c r="L940" s="22"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
       <c r="A941" s="15"/>
       <c r="B941" s="15"/>
-      <c r="L941" s="23"/>
+      <c r="L941" s="22"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
       <c r="A942" s="15"/>
       <c r="B942" s="15"/>
-      <c r="L942" s="23"/>
+      <c r="L942" s="22"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
       <c r="A943" s="15"/>
       <c r="B943" s="15"/>
-      <c r="L943" s="23"/>
+      <c r="L943" s="22"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
       <c r="A944" s="15"/>
       <c r="B944" s="15"/>
-      <c r="L944" s="23"/>
+      <c r="L944" s="22"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
       <c r="A945" s="15"/>
       <c r="B945" s="15"/>
-      <c r="L945" s="23"/>
+      <c r="L945" s="22"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
       <c r="A946" s="15"/>
       <c r="B946" s="15"/>
-      <c r="L946" s="23"/>
+      <c r="L946" s="22"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
       <c r="A947" s="15"/>
       <c r="B947" s="15"/>
-      <c r="L947" s="23"/>
+      <c r="L947" s="22"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
       <c r="A948" s="15"/>
       <c r="B948" s="15"/>
-      <c r="L948" s="23"/>
+      <c r="L948" s="22"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
       <c r="A949" s="15"/>
       <c r="B949" s="15"/>
-      <c r="L949" s="23"/>
+      <c r="L949" s="22"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
       <c r="A950" s="15"/>
       <c r="B950" s="15"/>
-      <c r="L950" s="23"/>
+      <c r="L950" s="22"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
       <c r="A951" s="15"/>
       <c r="B951" s="15"/>
-      <c r="L951" s="23"/>
+      <c r="L951" s="22"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
       <c r="A952" s="15"/>
       <c r="B952" s="15"/>
-      <c r="L952" s="23"/>
+      <c r="L952" s="22"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
       <c r="A953" s="15"/>
       <c r="B953" s="15"/>
-      <c r="L953" s="23"/>
+      <c r="L953" s="22"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
       <c r="A954" s="15"/>
       <c r="B954" s="15"/>
-      <c r="L954" s="23"/>
+      <c r="L954" s="22"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
       <c r="A955" s="15"/>
       <c r="B955" s="15"/>
-      <c r="L955" s="23"/>
+      <c r="L955" s="22"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
       <c r="A956" s="15"/>
       <c r="B956" s="15"/>
-      <c r="L956" s="23"/>
+      <c r="L956" s="22"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
       <c r="A957" s="15"/>
       <c r="B957" s="15"/>
-      <c r="L957" s="23"/>
+      <c r="L957" s="22"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
       <c r="A958" s="15"/>
       <c r="B958" s="15"/>
-      <c r="L958" s="23"/>
+      <c r="L958" s="22"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
       <c r="A959" s="15"/>
       <c r="B959" s="15"/>
-      <c r="L959" s="23"/>
+      <c r="L959" s="22"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
       <c r="A960" s="15"/>
       <c r="B960" s="15"/>
-      <c r="L960" s="23"/>
+      <c r="L960" s="22"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
       <c r="A961" s="15"/>
       <c r="B961" s="15"/>
-      <c r="L961" s="23"/>
+      <c r="L961" s="22"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
       <c r="A962" s="15"/>
       <c r="B962" s="15"/>
-      <c r="L962" s="23"/>
+      <c r="L962" s="22"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
       <c r="A963" s="15"/>
       <c r="B963" s="15"/>
-      <c r="L963" s="23"/>
+      <c r="L963" s="22"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
       <c r="A964" s="15"/>
       <c r="B964" s="15"/>
-      <c r="L964" s="23"/>
+      <c r="L964" s="22"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
       <c r="A965" s="15"/>
       <c r="B965" s="15"/>
-      <c r="L965" s="23"/>
+      <c r="L965" s="22"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
       <c r="A966" s="15"/>
       <c r="B966" s="15"/>
-      <c r="L966" s="23"/>
+      <c r="L966" s="22"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
       <c r="A967" s="15"/>
       <c r="B967" s="15"/>
-      <c r="L967" s="23"/>
+      <c r="L967" s="22"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
       <c r="A968" s="15"/>
       <c r="B968" s="15"/>
-      <c r="L968" s="23"/>
+      <c r="L968" s="22"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
       <c r="A969" s="15"/>
       <c r="B969" s="15"/>
-      <c r="L969" s="23"/>
+      <c r="L969" s="22"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
       <c r="A970" s="15"/>
       <c r="B970" s="15"/>
-      <c r="L970" s="23"/>
+      <c r="L970" s="22"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
       <c r="A971" s="15"/>
       <c r="B971" s="15"/>
-      <c r="L971" s="23"/>
+      <c r="L971" s="22"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
       <c r="A972" s="15"/>
       <c r="B972" s="15"/>
-      <c r="L972" s="23"/>
+      <c r="L972" s="22"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
       <c r="A973" s="15"/>
       <c r="B973" s="15"/>
-      <c r="L973" s="23"/>
+      <c r="L973" s="22"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
       <c r="A974" s="15"/>
       <c r="B974" s="15"/>
-      <c r="L974" s="23"/>
+      <c r="L974" s="22"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
       <c r="A975" s="15"/>
       <c r="B975" s="15"/>
-      <c r="L975" s="23"/>
+      <c r="L975" s="22"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
       <c r="A976" s="15"/>
       <c r="B976" s="15"/>
-      <c r="L976" s="23"/>
+      <c r="L976" s="22"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
       <c r="A977" s="15"/>
       <c r="B977" s="15"/>
-      <c r="L977" s="23"/>
+      <c r="L977" s="22"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
       <c r="A978" s="15"/>
       <c r="B978" s="15"/>
-      <c r="L978" s="23"/>
+      <c r="L978" s="22"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
       <c r="A979" s="15"/>
       <c r="B979" s="15"/>
-      <c r="L979" s="23"/>
+      <c r="L979" s="22"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
       <c r="A980" s="15"/>
       <c r="B980" s="15"/>
-      <c r="L980" s="23"/>
+      <c r="L980" s="22"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
       <c r="A981" s="15"/>
       <c r="B981" s="15"/>
-      <c r="L981" s="23"/>
+      <c r="L981" s="22"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
       <c r="A982" s="15"/>
       <c r="B982" s="15"/>
-      <c r="L982" s="23"/>
+      <c r="L982" s="22"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
       <c r="A983" s="15"/>
       <c r="B983" s="15"/>
-      <c r="L983" s="23"/>
+      <c r="L983" s="22"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
       <c r="A984" s="15"/>
       <c r="B984" s="15"/>
-      <c r="L984" s="23"/>
+      <c r="L984" s="22"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
       <c r="A985" s="15"/>
       <c r="B985" s="15"/>
-      <c r="L985" s="23"/>
+      <c r="L985" s="22"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
       <c r="A986" s="15"/>
       <c r="B986" s="15"/>
-      <c r="L986" s="23"/>
+      <c r="L986" s="22"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
       <c r="A987" s="15"/>
       <c r="B987" s="15"/>
-      <c r="L987" s="23"/>
+      <c r="L987" s="22"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
       <c r="A988" s="15"/>
       <c r="B988" s="15"/>
-      <c r="L988" s="23"/>
+      <c r="L988" s="22"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
       <c r="A989" s="15"/>
       <c r="B989" s="15"/>
-      <c r="L989" s="23"/>
+      <c r="L989" s="22"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
       <c r="A990" s="15"/>
       <c r="B990" s="15"/>
-      <c r="L990" s="23"/>
+      <c r="L990" s="22"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
       <c r="A991" s="15"/>
       <c r="B991" s="15"/>
-      <c r="L991" s="23"/>
+      <c r="L991" s="22"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
       <c r="A992" s="15"/>
       <c r="B992" s="15"/>
-      <c r="L992" s="23"/>
+      <c r="L992" s="22"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
       <c r="A993" s="15"/>
       <c r="B993" s="15"/>
-      <c r="L993" s="23"/>
+      <c r="L993" s="22"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
       <c r="A994" s="15"/>
       <c r="B994" s="15"/>
-      <c r="L994" s="23"/>
+      <c r="L994" s="22"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
       <c r="A995" s="15"/>
       <c r="B995" s="15"/>
-      <c r="L995" s="23"/>
+      <c r="L995" s="22"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
       <c r="A996" s="15"/>
       <c r="B996" s="15"/>
-      <c r="L996" s="23"/>
+      <c r="L996" s="22"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
       <c r="A997" s="15"/>
       <c r="B997" s="15"/>
-      <c r="L997" s="23"/>
+      <c r="L997" s="22"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
       <c r="A998" s="15"/>
       <c r="B998" s="15"/>
-      <c r="L998" s="23"/>
+      <c r="L998" s="22"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
       <c r="A999" s="15"/>
       <c r="B999" s="15"/>
-      <c r="L999" s="23"/>
+      <c r="L999" s="22"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
       <c r="A1000" s="15"/>
       <c r="B1000" s="15"/>
-      <c r="L1000" s="23"/>
+      <c r="L1000" s="22"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
       <c r="A1001" s="15"/>
       <c r="B1001" s="15"/>
-      <c r="L1001" s="23"/>
+      <c r="L1001" s="22"/>
     </row>
     <row r="1002" ht="12.75" customHeight="1">
       <c r="A1002" s="15"/>
       <c r="B1002" s="15"/>
-      <c r="L1002" s="23"/>
+      <c r="L1002" s="22"/>
     </row>
     <row r="1003" ht="12.75" customHeight="1">
       <c r="A1003" s="15"/>
       <c r="B1003" s="15"/>
-      <c r="L1003" s="23"/>
+      <c r="L1003" s="22"/>
     </row>
     <row r="1004" ht="12.75" customHeight="1">
       <c r="A1004" s="15"/>
       <c r="B1004" s="15"/>
-      <c r="L1004" s="23"/>
+      <c r="L1004" s="22"/>
     </row>
     <row r="1005" ht="12.75" customHeight="1">
       <c r="A1005" s="15"/>
       <c r="B1005" s="15"/>
-      <c r="L1005" s="23"/>
+      <c r="L1005" s="22"/>
     </row>
     <row r="1006" ht="12.75" customHeight="1">
       <c r="A1006" s="15"/>
       <c r="B1006" s="15"/>
-      <c r="L1006" s="23"/>
+      <c r="L1006" s="22"/>
     </row>
     <row r="1007" ht="12.75" customHeight="1">
       <c r="A1007" s="15"/>
       <c r="B1007" s="15"/>
-      <c r="L1007" s="23"/>
+      <c r="L1007" s="22"/>
     </row>
     <row r="1008" ht="12.75" customHeight="1">
       <c r="A1008" s="15"/>
       <c r="B1008" s="15"/>
-      <c r="L1008" s="23"/>
+      <c r="L1008" s="22"/>
     </row>
     <row r="1009" ht="12.75" customHeight="1">
       <c r="A1009" s="15"/>
       <c r="B1009" s="15"/>
-      <c r="L1009" s="23"/>
+      <c r="L1009" s="22"/>
     </row>
     <row r="1010" ht="12.75" customHeight="1">
       <c r="A1010" s="15"/>
       <c r="B1010" s="15"/>
-      <c r="L1010" s="23"/>
+      <c r="L1010" s="22"/>
     </row>
     <row r="1011" ht="12.75" customHeight="1">
       <c r="A1011" s="15"/>
       <c r="B1011" s="15"/>
-      <c r="L1011" s="23"/>
+      <c r="L1011" s="22"/>
     </row>
     <row r="1012" ht="12.75" customHeight="1">
       <c r="A1012" s="15"/>
       <c r="B1012" s="15"/>
-      <c r="L1012" s="23"/>
+      <c r="L1012" s="22"/>
     </row>
     <row r="1013" ht="12.75" customHeight="1">
       <c r="A1013" s="15"/>
       <c r="B1013" s="15"/>
-      <c r="L1013" s="23"/>
+      <c r="L1013" s="22"/>
     </row>
     <row r="1014" ht="12.75" customHeight="1">
       <c r="A1014" s="15"/>
       <c r="B1014" s="15"/>
-      <c r="L1014" s="23"/>
+      <c r="L1014" s="22"/>
     </row>
     <row r="1015" ht="12.75" customHeight="1">
       <c r="A1015" s="15"/>
       <c r="B1015" s="15"/>
-      <c r="L1015" s="23"/>
+      <c r="L1015" s="22"/>
     </row>
     <row r="1016" ht="12.75" customHeight="1">
       <c r="A1016" s="15"/>
       <c r="B1016" s="15"/>
-      <c r="L1016" s="23"/>
+      <c r="L1016" s="22"/>
     </row>
     <row r="1017" ht="12.75" customHeight="1">
       <c r="A1017" s="15"/>
       <c r="B1017" s="15"/>
-      <c r="L1017" s="23"/>
+      <c r="L1017" s="22"/>
     </row>
     <row r="1018" ht="12.75" customHeight="1">
       <c r="A1018" s="15"/>
       <c r="B1018" s="15"/>
-      <c r="L1018" s="23"/>
+      <c r="L1018" s="22"/>
     </row>
     <row r="1019" ht="12.75" customHeight="1">
       <c r="A1019" s="15"/>
       <c r="B1019" s="15"/>
-      <c r="L1019" s="23"/>
+      <c r="L1019" s="22"/>
     </row>
     <row r="1020" ht="12.75" customHeight="1">
       <c r="A1020" s="15"/>
       <c r="B1020" s="15"/>
-      <c r="L1020" s="23"/>
+      <c r="L1020" s="22"/>
     </row>
     <row r="1021" ht="12.75" customHeight="1">
       <c r="A1021" s="15"/>
       <c r="B1021" s="15"/>
-      <c r="L1021" s="23"/>
+      <c r="L1021" s="22"/>
     </row>
     <row r="1022" ht="12.75" customHeight="1">
       <c r="A1022" s="15"/>
       <c r="B1022" s="15"/>
-      <c r="L1022" s="23"/>
+      <c r="L1022" s="22"/>
     </row>
     <row r="1023" ht="12.75" customHeight="1">
       <c r="A1023" s="15"/>
       <c r="B1023" s="15"/>
-      <c r="L1023" s="23"/>
+      <c r="L1023" s="22"/>
     </row>
     <row r="1024" ht="12.75" customHeight="1">
       <c r="A1024" s="15"/>
       <c r="B1024" s="15"/>
-      <c r="L1024" s="23"/>
+      <c r="L1024" s="22"/>
     </row>
     <row r="1025" ht="12.75" customHeight="1">
       <c r="A1025" s="15"/>
       <c r="B1025" s="15"/>
-      <c r="L1025" s="23"/>
+      <c r="L1025" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -7898,10 +7898,10 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="AB2" s="2"/>
@@ -7919,7 +7919,7 @@
       <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="11">
         <v>2.5E32</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -7940,10 +7940,10 @@
       <c r="I3" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="14">
         <v>1000.0</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="14">
         <v>1000.0</v>
       </c>
       <c r="L3" s="8">
@@ -7985,10 +7985,10 @@
       <c r="I4" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="14">
         <v>52250.04</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="14">
         <v>52250.04</v>
       </c>
       <c r="L4" s="8">
@@ -8004,13 +8004,13 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>4</v>
@@ -8030,10 +8030,10 @@
       <c r="I5" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="14">
         <v>881914.18</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="14">
         <v>881914.18</v>
       </c>
       <c r="L5" s="8">
@@ -8049,13 +8049,13 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>4</v>
@@ -8075,10 +8075,10 @@
       <c r="I6" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <v>750000.0</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="14">
         <v>750000.0</v>
       </c>
       <c r="L6" s="8">
@@ -8094,13 +8094,13 @@
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>4</v>
@@ -8118,12 +8118,12 @@
         <v>339039.0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="13">
+        <v>44</v>
+      </c>
+      <c r="J7" s="14">
         <v>949835.78</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="14">
         <v>949835.78</v>
       </c>
       <c r="L7" s="8">
@@ -8139,13 +8139,13 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>4</v>
@@ -8163,18 +8163,18 @@
         <v>339039.0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="13">
+        <v>48</v>
+      </c>
+      <c r="J8" s="14">
         <v>524584.95</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="14">
         <v>524584.95</v>
       </c>
       <c r="L8" s="8">
         <v>0.0</v>
       </c>
-      <c r="O8" s="22"/>
+      <c r="O8" s="29"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8185,13 +8185,13 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>4</v>
@@ -8209,12 +8209,12 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="13">
+        <v>55</v>
+      </c>
+      <c r="J9" s="14">
         <v>211614.23</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="14">
         <v>211614.23</v>
       </c>
       <c r="L9" s="8">
@@ -8230,13 +8230,13 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>4</v>
@@ -8256,13 +8256,13 @@
       <c r="I10" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <v>2391157.42</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="14">
         <v>2391157.41</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="14">
         <v>0.01</v>
       </c>
       <c r="AB10" s="2"/>
@@ -8275,13 +8275,13 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>4</v>
@@ -8301,10 +8301,10 @@
       <c r="I11" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <v>618154.39</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="14">
         <v>618154.38</v>
       </c>
       <c r="L11" s="8">
@@ -8320,13 +8320,13 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>4</v>
@@ -8344,12 +8344,12 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12" s="13">
+        <v>73</v>
+      </c>
+      <c r="J12" s="14">
         <v>1600334.09</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="14">
         <v>1600334.09</v>
       </c>
       <c r="L12" s="8">
@@ -8365,13 +8365,13 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>4</v>
@@ -8391,16 +8391,16 @@
       <c r="I13" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <v>2364771.07</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="14">
         <v>2364771.07</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="14">
         <v>0.0</v>
       </c>
-      <c r="M13" s="31"/>
+      <c r="M13" s="37"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8411,13 +8411,13 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>4</v>
@@ -8435,12 +8435,12 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="13">
+        <v>55</v>
+      </c>
+      <c r="J14" s="14">
         <v>968237.39</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="14">
         <v>968237.39</v>
       </c>
       <c r="L14" s="8">
@@ -8456,13 +8456,13 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>4</v>
@@ -8480,12 +8480,12 @@
         <v>339039.0</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" s="13">
+        <v>44</v>
+      </c>
+      <c r="J15" s="14">
         <v>1011677.95</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="14">
         <v>1011677.95</v>
       </c>
       <c r="L15" s="8">
@@ -8501,13 +8501,13 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>4</v>
@@ -8527,13 +8527,13 @@
       <c r="I16" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="14">
         <v>1580293.02</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="14">
         <v>1580293.02</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="14">
         <v>0.0</v>
       </c>
       <c r="AB16" s="2"/>
@@ -8546,13 +8546,13 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>4</v>
@@ -8572,13 +8572,13 @@
       <c r="I17" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="14">
         <v>34065.36</v>
       </c>
       <c r="K17" s="8">
         <v>0.0</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="14">
         <v>34065.36</v>
       </c>
       <c r="AB17" s="2"/>
@@ -8591,13 +8591,13 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>4</v>
@@ -8615,12 +8615,12 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="13">
+        <v>55</v>
+      </c>
+      <c r="J18" s="14">
         <v>63746.85</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="14">
         <v>63746.85</v>
       </c>
       <c r="L18" s="8">
@@ -8636,13 +8636,13 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>4</v>
@@ -8660,12 +8660,12 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="13">
+        <v>73</v>
+      </c>
+      <c r="J19" s="14">
         <v>947931.1</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="14">
         <v>947931.1</v>
       </c>
       <c r="L19" s="8">
@@ -8707,10 +8707,10 @@
       <c r="I20" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="14">
         <v>259790.57</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="14">
         <v>259790.57</v>
       </c>
       <c r="L20" s="8">
@@ -8726,13 +8726,13 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>4</v>
@@ -8752,10 +8752,10 @@
       <c r="I21" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="14">
         <v>170479.3</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="14">
         <v>170479.3</v>
       </c>
       <c r="L21" s="8">
@@ -8771,18 +8771,18 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="42">
         <v>45953.0</v>
       </c>
       <c r="F22" s="8" t="s">
@@ -8797,13 +8797,13 @@
       <c r="I22" s="8">
         <v>2000.0</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="14">
         <v>1500000.0</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="14">
         <v>1500000.0</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="14">
         <v>0.0</v>
       </c>
       <c r="AB22" s="2"/>
@@ -8816,18 +8816,18 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="42">
         <v>45953.0</v>
       </c>
       <c r="F23" s="8" t="s">
@@ -8840,12 +8840,12 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" s="13">
+        <v>105</v>
+      </c>
+      <c r="J23" s="14">
         <v>1000001.64</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="14">
         <v>1000001.64</v>
       </c>
       <c r="L23" s="8">
@@ -8861,18 +8861,18 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="42">
         <v>45953.0</v>
       </c>
       <c r="F24" s="8" t="s">
@@ -8887,10 +8887,10 @@
       <c r="I24" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="14">
         <v>68405.66</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="14">
         <v>68405.66</v>
       </c>
       <c r="L24" s="8">
@@ -8906,18 +8906,18 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="42">
         <v>45975.0</v>
       </c>
       <c r="F25" s="8" t="s">
@@ -8930,12 +8930,12 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J25" s="13">
+        <v>105</v>
+      </c>
+      <c r="J25" s="14">
         <v>1157673.06</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="14">
         <v>1157673.06</v>
       </c>
       <c r="L25" s="8">
@@ -8951,18 +8951,18 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="42">
         <v>45989.0</v>
       </c>
       <c r="F26" s="8" t="s">
@@ -8977,10 +8977,10 @@
       <c r="I26" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="14">
         <v>34065.36</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="14">
         <v>34065.36</v>
       </c>
       <c r="L26" s="8">
@@ -8996,13 +8996,13 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>4</v>
@@ -9022,13 +9022,13 @@
       <c r="I27" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="14">
         <v>1770880.5</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="14">
         <v>843261.89</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="14">
         <v>927618.61</v>
       </c>
       <c r="AB27" s="2"/>
@@ -9041,13 +9041,13 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>4</v>
@@ -9065,15 +9065,15 @@
         <v>339039.0</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J28" s="13">
+        <v>48</v>
+      </c>
+      <c r="J28" s="14">
         <v>1912292.52</v>
       </c>
       <c r="K28" s="8">
         <v>0.0</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="14">
         <v>1912292.52</v>
       </c>
       <c r="AB28" s="2"/>
@@ -9086,13 +9086,13 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>4</v>
@@ -9112,13 +9112,13 @@
       <c r="I29" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="14">
         <v>1496713.48</v>
       </c>
       <c r="K29" s="8">
         <v>0.0</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="14">
         <v>1496713.48</v>
       </c>
       <c r="AB29" s="2"/>
@@ -9131,13 +9131,13 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>4</v>
@@ -9155,15 +9155,15 @@
         <v>339039.0</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="13">
+        <v>44</v>
+      </c>
+      <c r="J30" s="14">
         <v>624166.14</v>
       </c>
       <c r="K30" s="8">
         <v>0.0</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="14">
         <v>624166.14</v>
       </c>
       <c r="AB30" s="2"/>
@@ -9176,13 +9176,13 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>4</v>
@@ -9200,15 +9200,15 @@
         <v>339039.0</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J31" s="13">
+        <v>105</v>
+      </c>
+      <c r="J31" s="14">
         <v>18462.36</v>
       </c>
       <c r="K31" s="8">
         <v>0.0</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="14">
         <v>18462.36</v>
       </c>
       <c r="AB31" s="2"/>
@@ -9221,13 +9221,13 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>144</v>
+        <v>128</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>131</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>4</v>
@@ -9245,15 +9245,15 @@
         <v>339039.0</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="J32" s="13">
+        <v>105</v>
+      </c>
+      <c r="J32" s="14">
         <v>1530656.62</v>
       </c>
       <c r="K32" s="8">
         <v>0.0</v>
       </c>
-      <c r="L32" s="13">
+      <c r="L32" s="14">
         <v>1530656.62</v>
       </c>
       <c r="AB32" s="2"/>
@@ -9266,13 +9266,13 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>146</v>
+        <v>122</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>4</v>
@@ -9292,13 +9292,13 @@
       <c r="I33" s="8">
         <v>2048.0</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="14">
         <v>173846.38</v>
       </c>
       <c r="K33" s="8">
         <v>0.0</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="14">
         <v>173846.38</v>
       </c>
       <c r="AB33" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="209">
   <si>
     <t>Saldo</t>
   </si>
@@ -69,42 +69,42 @@
     <t>UG Fiscalizadora</t>
   </si>
   <si>
+    <t>Prazo Final de Execução</t>
+  </si>
+  <si>
+    <t>Prazo Final de Vigência</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ação</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>Moeda</t>
+  </si>
+  <si>
     <t>2025NE000369</t>
   </si>
   <si>
-    <t>Prazo Final de Execução</t>
+    <t>Valor Total do Contrato</t>
+  </si>
+  <si>
+    <t>Valor a Empenhar</t>
   </si>
   <si>
     <t>C25516</t>
   </si>
   <si>
-    <t>Prazo Final de Vigência</t>
+    <t>Valor Empenhado</t>
   </si>
   <si>
     <t>25E0387</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ação</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>Moeda</t>
-  </si>
-  <si>
-    <t>Valor Total do Contrato</t>
-  </si>
-  <si>
-    <t>Valor a Empenhar</t>
-  </si>
-  <si>
-    <t>Valor Empenhado</t>
-  </si>
-  <si>
     <t>Valor Liquidado</t>
   </si>
   <si>
@@ -123,30 +123,30 @@
     <t>Editar</t>
   </si>
   <si>
+    <t>005/CELOG-PAMALS/2025</t>
+  </si>
+  <si>
+    <t>CELOG</t>
+  </si>
+  <si>
+    <t>PAMALS</t>
+  </si>
+  <si>
     <t>2025NE000371</t>
   </si>
   <si>
-    <t>005/CELOG-PAMALS/2025</t>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
+  </si>
+  <si>
+    <t>67101.001510/2024-12</t>
   </si>
   <si>
     <t>25E0389</t>
   </si>
   <si>
-    <t>CELOG</t>
-  </si>
-  <si>
-    <t>PAMALS</t>
-  </si>
-  <si>
-    <t>Vigente</t>
-  </si>
-  <si>
-    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
-  </si>
-  <si>
-    <t>67101.001510/2024-12</t>
-  </si>
-  <si>
     <t>R$</t>
   </si>
   <si>
@@ -174,69 +174,78 @@
     <t>25E0431</t>
   </si>
   <si>
+    <t>Módulo</t>
+  </si>
+  <si>
     <t>21EM</t>
   </si>
   <si>
-    <t>Módulo</t>
-  </si>
-  <si>
     <t>Referência</t>
   </si>
   <si>
+    <t>Nº recibo</t>
+  </si>
+  <si>
+    <t>Nº</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Empenho</t>
+  </si>
+  <si>
     <t>2025NE000559</t>
   </si>
   <si>
     <t>C25545</t>
   </si>
   <si>
+    <t>Observações</t>
+  </si>
+  <si>
     <t>25E0524</t>
   </si>
   <si>
-    <t>Nº recibo</t>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>Valor das Nfs</t>
+  </si>
+  <si>
+    <t>Ordem de Pagamento</t>
   </si>
   <si>
     <t>20X7</t>
   </si>
   <si>
-    <t>Nº</t>
+    <t>Faturado</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
   <si>
     <t>2025NE000770</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
     <t>25E0731</t>
   </si>
   <si>
-    <t>Empenho</t>
-  </si>
-  <si>
-    <t>Observações</t>
-  </si>
-  <si>
-    <t>Vencimento</t>
-  </si>
-  <si>
-    <t>Valor das Nfs</t>
-  </si>
-  <si>
-    <t>Ordem de Pagamento</t>
-  </si>
-  <si>
-    <t>Faturado</t>
+    <t>FEV/25</t>
   </si>
   <si>
     <t>2025NE000774</t>
   </si>
   <si>
-    <t>Pendente</t>
+    <t>-</t>
   </si>
   <si>
     <t>25E0737</t>
   </si>
   <si>
+    <t xml:space="preserve">2025NE000369 </t>
+  </si>
+  <si>
     <t>2025NE000843</t>
   </si>
   <si>
@@ -246,13 +255,10 @@
     <t>25E0787</t>
   </si>
   <si>
-    <t>FEV/25</t>
-  </si>
-  <si>
     <t>219C</t>
   </si>
   <si>
-    <t>-</t>
+    <t>2025NP001980</t>
   </si>
   <si>
     <t>2025NE001065</t>
@@ -261,12 +267,6 @@
     <t>25E0999</t>
   </si>
   <si>
-    <t xml:space="preserve">2025NE000369 </t>
-  </si>
-  <si>
-    <t>2025NP001980</t>
-  </si>
-  <si>
     <t>2025NE001200</t>
   </si>
   <si>
@@ -276,6 +276,9 @@
     <t>25E1128</t>
   </si>
   <si>
+    <t>MAR/25</t>
+  </si>
+  <si>
     <t>2025NE001598</t>
   </si>
   <si>
@@ -285,15 +288,18 @@
     <t>25E1446</t>
   </si>
   <si>
+    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
+  </si>
+  <si>
     <t>2025NE001627</t>
   </si>
   <si>
-    <t>MAR/25</t>
-  </si>
-  <si>
     <t>25E1475</t>
   </si>
   <si>
+    <t>2025NP001979</t>
+  </si>
+  <si>
     <t>2025NE001629</t>
   </si>
   <si>
@@ -303,151 +309,46 @@
     <t>25E1477</t>
   </si>
   <si>
+    <t>ABR/25</t>
+  </si>
+  <si>
+    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
+  </si>
+  <si>
     <t>2025NE001687</t>
   </si>
   <si>
     <t>25E1535</t>
   </si>
   <si>
+    <t>2025NP002341</t>
+  </si>
+  <si>
+    <t>MAI/25</t>
+  </si>
+  <si>
     <t>2025NE001688</t>
   </si>
   <si>
     <t>25E1536</t>
   </si>
   <si>
+    <t>2025NP002884</t>
+  </si>
+  <si>
     <t>2025NE001689</t>
   </si>
   <si>
     <t>25E1537</t>
   </si>
   <si>
+    <t>JUN/25</t>
+  </si>
+  <si>
     <t>2025NE001690</t>
   </si>
   <si>
     <t>25E1538</t>
-  </si>
-  <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
-  </si>
-  <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
-    <t>20YJ</t>
-  </si>
-  <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
-  </si>
-  <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
-  </si>
-  <si>
-    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
-  </si>
-  <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
-  </si>
-  <si>
-    <t>2025NP001979</t>
-  </si>
-  <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
-  </si>
-  <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
-  </si>
-  <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
-    <t>26E0906</t>
-  </si>
-  <si>
-    <t>ABR/25</t>
-  </si>
-  <si>
-    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
-  </si>
-  <si>
-    <t>2025NP002341</t>
-  </si>
-  <si>
-    <t>MAI/25</t>
-  </si>
-  <si>
-    <t>2025NP002884</t>
-  </si>
-  <si>
-    <t>JUN/25</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -459,22 +360,64 @@
     <t>2025NP400522</t>
   </si>
   <si>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
+  </si>
+  <si>
     <t>JUL/25</t>
   </si>
   <si>
+    <t>2025NE001828</t>
+  </si>
+  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
+  </si>
+  <si>
     <t>2025NP003724</t>
   </si>
   <si>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
+  </si>
+  <si>
     <t>AGO/25</t>
   </si>
   <si>
     <t>2025NP004558</t>
   </si>
   <si>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
+  </si>
+  <si>
     <t>SET/25</t>
+  </si>
+  <si>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
   </si>
   <si>
     <t>2025NE001688 
@@ -484,15 +427,42 @@
     <t>2025NP004897</t>
   </si>
   <si>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
+  </si>
+  <si>
     <t>OUT/25</t>
   </si>
   <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
     <t>2025NP004932</t>
   </si>
   <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
     <t>NOV/25</t>
   </si>
   <si>
@@ -502,21 +472,51 @@
     <t>2026NP400440</t>
   </si>
   <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
+  </si>
+  <si>
     <t>DEZ/25</t>
   </si>
   <si>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
+  </si>
+  <si>
     <t>2025NE001065, 2025NE002200</t>
   </si>
   <si>
     <t>2026NP400412</t>
   </si>
   <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
+  </si>
+  <si>
     <t>JAN/26</t>
   </si>
   <si>
+    <t>2026NE000944</t>
+  </si>
+  <si>
     <t>2026NP401035</t>
   </si>
   <si>
+    <t>26E0906</t>
+  </si>
+  <si>
     <t>FEV/26</t>
   </si>
   <si>
@@ -559,7 +559,13 @@
     <t>JUNHO/26</t>
   </si>
   <si>
+    <t>2025NE001065, 2026NE000330</t>
+  </si>
+  <si>
     <t>R$ 1.340.865,98</t>
+  </si>
+  <si>
+    <t>2026NP402899</t>
   </si>
   <si>
     <t>Módulo II – Parcial Orçamento 10 (FAB 2728)</t>
@@ -665,8 +671,8 @@
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
+    <numFmt numFmtId="169" formatCode="MM/DD/YY"/>
+    <numFmt numFmtId="170" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="171" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12">
@@ -852,7 +858,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -879,11 +885,11 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -958,10 +964,10 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -969,16 +975,13 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -996,6 +999,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1007,12 +1013,6 @@
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1026,6 +1026,9 @@
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1417,14 +1420,14 @@
         <v>1</v>
       </c>
       <c r="V2" s="9"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="10"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
@@ -1466,31 +1469,31 @@
         <v>12</v>
       </c>
       <c r="G4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="I4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="K4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="16" t="s">
+      <c r="M4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="N4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N4" s="17" t="s">
+      <c r="O4" s="17" t="s">
         <v>23</v>
-      </c>
-      <c r="O4" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="P4" s="17" t="s">
         <v>25</v>
@@ -1517,16 +1520,16 @@
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>34</v>
-      </c>
       <c r="F5" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1535,13 +1538,13 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="L5" s="19" t="s">
         <v>37</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>38</v>
       </c>
       <c r="M5" s="19" t="s">
         <v>39</v>
@@ -1595,40 +1598,40 @@
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
       <c r="C8" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="28" t="s">
+      <c r="I8" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="L8" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" s="28" t="s">
+      <c r="M8" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="N8" s="28" t="s">
         <v>64</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="28" t="s">
-        <v>67</v>
       </c>
       <c r="O8" s="28"/>
       <c r="P8" s="27"/>
@@ -1641,10 +1644,10 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F9" s="35">
         <v>594.0</v>
@@ -1653,17 +1656,17 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I9" s="36"/>
       <c r="J9" s="36">
         <v>45778.0</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="37">
         <v>748504.24</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
@@ -1679,10 +1682,10 @@
       <c r="B10" s="23"/>
       <c r="C10" s="41"/>
       <c r="D10" s="33" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F10" s="35">
         <v>620.0</v>
@@ -1691,23 +1694,23 @@
         <v>45775.0</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="I10" s="36"/>
       <c r="J10" s="36">
         <v>45806.0</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="37">
         <v>1110378.24</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="M10" s="39">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
-      <c r="N10" s="43"/>
+      <c r="N10" s="42"/>
       <c r="O10" s="25"/>
       <c r="P10" s="27"/>
       <c r="V10" s="4"/>
@@ -1717,10 +1720,10 @@
       <c r="B11" s="23"/>
       <c r="C11" s="41"/>
       <c r="D11" s="33" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F11" s="35">
         <v>634.0</v>
@@ -1729,22 +1732,22 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36">
         <v>45844.0</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="37">
         <v>974557.12</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="M11" s="39">
         <v>974557.12</v>
       </c>
-      <c r="N11" s="43"/>
+      <c r="N11" s="42"/>
       <c r="O11" s="25"/>
       <c r="P11" s="27"/>
       <c r="V11" s="4"/>
@@ -1754,34 +1757,34 @@
       <c r="B12" s="23"/>
       <c r="C12" s="41"/>
       <c r="D12" s="33" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F12" s="34">
         <v>660.0</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="43">
         <v>45856.0</v>
       </c>
-      <c r="H12" s="45" t="s">
-        <v>69</v>
+      <c r="H12" s="44" t="s">
+        <v>72</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36">
         <v>45891.0</v>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="45">
         <v>1402001.34</v>
       </c>
-      <c r="L12" s="47" t="s">
-        <v>138</v>
+      <c r="L12" s="46" t="s">
+        <v>101</v>
       </c>
       <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
-      <c r="N12" s="48"/>
+      <c r="N12" s="47"/>
       <c r="O12" s="25"/>
       <c r="P12" s="27"/>
       <c r="V12" s="4"/>
@@ -1790,11 +1793,11 @@
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="41"/>
-      <c r="D13" s="49" t="s">
-        <v>139</v>
+      <c r="D13" s="48" t="s">
+        <v>104</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F13" s="35">
         <v>661.0</v>
@@ -1803,35 +1806,35 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44">
+        <v>107</v>
+      </c>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43">
         <v>45891.0</v>
       </c>
-      <c r="K13" s="46">
+      <c r="K13" s="45">
         <v>1223702.3</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
-      <c r="N13" s="48"/>
+      <c r="N13" s="47"/>
       <c r="O13" s="25"/>
-      <c r="P13" s="50"/>
+      <c r="P13" s="49"/>
       <c r="V13" s="4"/>
     </row>
     <row r="14">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="41"/>
-      <c r="D14" s="49" t="s">
-        <v>142</v>
+      <c r="D14" s="48" t="s">
+        <v>112</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F14" s="34">
         <v>688.0</v>
@@ -1840,22 +1843,22 @@
         <v>45901.0</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44">
+        <v>114</v>
+      </c>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="45">
         <v>1011677.95</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
-      <c r="N14" s="43"/>
+      <c r="N14" s="42"/>
       <c r="O14" s="25"/>
       <c r="P14" s="27"/>
       <c r="V14" s="4"/>
@@ -1864,11 +1867,11 @@
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="49" t="s">
-        <v>145</v>
+      <c r="D15" s="48" t="s">
+        <v>121</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F15" s="34">
         <v>696.0</v>
@@ -1879,20 +1882,20 @@
       <c r="H15" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44">
+      <c r="I15" s="43"/>
+      <c r="J15" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="45">
         <v>896744.06</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="M15" s="39">
         <v>896744.06</v>
       </c>
-      <c r="N15" s="48"/>
+      <c r="N15" s="47"/>
       <c r="O15" s="25"/>
       <c r="V15" s="4"/>
     </row>
@@ -1900,11 +1903,11 @@
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="41"/>
-      <c r="D16" s="49" t="s">
-        <v>147</v>
+      <c r="D16" s="48" t="s">
+        <v>126</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F16" s="34">
         <v>704.0</v>
@@ -1913,22 +1916,22 @@
         <v>45957.0</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44">
+        <v>129</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43">
         <v>46003.0</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="45">
         <v>919329.06</v>
       </c>
       <c r="L16" s="34" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="M16" s="39">
         <v>919329.06</v>
       </c>
-      <c r="N16" s="43"/>
+      <c r="N16" s="42"/>
       <c r="O16" s="25"/>
       <c r="V16" s="4"/>
     </row>
@@ -1936,28 +1939,28 @@
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
       <c r="C17" s="41"/>
-      <c r="D17" s="49" t="s">
-        <v>150</v>
+      <c r="D17" s="48" t="s">
+        <v>134</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="34">
         <v>705.0</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <v>45972.0</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="I17" s="34"/>
-      <c r="J17" s="44">
+      <c r="J17" s="43">
         <v>46016.0</v>
       </c>
-      <c r="K17" s="46">
+      <c r="K17" s="45">
         <v>1157009.26</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="M17" s="39">
         <v>1157009.26</v>
@@ -1970,30 +1973,30 @@
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
       <c r="C18" s="41"/>
-      <c r="D18" s="49" t="s">
-        <v>153</v>
+      <c r="D18" s="48" t="s">
+        <v>143</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F18" s="34">
         <v>728.0</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="43">
         <v>46008.0</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="I18" s="34"/>
-      <c r="J18" s="44">
+      <c r="J18" s="43">
         <v>46040.0</v>
       </c>
-      <c r="K18" s="46">
+      <c r="K18" s="45">
         <v>1214597.952</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="M18" s="39">
         <v>1214597.952</v>
@@ -2010,30 +2013,30 @@
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
       <c r="C19" s="41"/>
-      <c r="D19" s="49" t="s">
-        <v>156</v>
+      <c r="D19" s="48" t="s">
+        <v>149</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F19" s="34">
         <v>278.0</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="43">
         <v>46042.0</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44">
+        <v>153</v>
+      </c>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43">
         <v>46074.0</v>
       </c>
-      <c r="K19" s="46">
+      <c r="K19" s="45">
         <v>967082.09</v>
       </c>
       <c r="L19" s="34" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="M19" s="39">
         <v>967082.09</v>
@@ -2050,28 +2053,28 @@
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
       <c r="C20" s="41"/>
-      <c r="D20" s="49" t="s">
-        <v>159</v>
+      <c r="D20" s="48" t="s">
+        <v>157</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34">
         <v>10.0</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="43">
         <v>46078.0</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44">
+        <v>109</v>
+      </c>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43">
         <v>46106.0</v>
       </c>
-      <c r="K20" s="46">
+      <c r="K20" s="45">
         <v>719561.08</v>
       </c>
       <c r="L20" s="34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M20" s="39">
         <v>719561.08</v>
@@ -2088,24 +2091,24 @@
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
       <c r="C21" s="41"/>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="48" t="s">
         <v>161</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34">
         <v>15.0</v>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="43">
         <v>46094.0</v>
       </c>
       <c r="H21" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44">
+      <c r="I21" s="43"/>
+      <c r="J21" s="43">
         <v>46128.0</v>
       </c>
-      <c r="K21" s="46">
+      <c r="K21" s="45">
         <v>885881.08</v>
       </c>
       <c r="L21" s="34" t="s">
@@ -2126,24 +2129,24 @@
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
       <c r="C22" s="41"/>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="48" t="s">
         <v>164</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="34">
         <v>28.0</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="43">
         <v>46128.0</v>
       </c>
       <c r="H22" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44">
+      <c r="I22" s="43"/>
+      <c r="J22" s="43">
         <v>46164.0</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="45" t="s">
         <v>166</v>
       </c>
       <c r="L22" s="34" t="s">
@@ -2164,24 +2167,24 @@
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="41"/>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="48" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="34">
         <v>33.0</v>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="43">
         <v>46156.0</v>
       </c>
       <c r="H23" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44">
+      <c r="I23" s="43"/>
+      <c r="J23" s="43">
         <v>46191.0</v>
       </c>
-      <c r="K23" s="46">
+      <c r="K23" s="45">
         <v>1108954.4358333333</v>
       </c>
       <c r="L23" s="34" t="s">
@@ -2202,24 +2205,24 @@
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
       <c r="C24" s="41"/>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="48" t="s">
         <v>170</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="34">
         <v>29.0</v>
       </c>
-      <c r="G24" s="44">
+      <c r="G24" s="43">
         <v>46149.0</v>
       </c>
       <c r="H24" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44">
+      <c r="I24" s="43"/>
+      <c r="J24" s="43">
         <v>46185.0</v>
       </c>
-      <c r="K24" s="46">
+      <c r="K24" s="45">
         <v>218206.1</v>
       </c>
       <c r="L24" s="34" t="s">
@@ -2240,24 +2243,24 @@
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
       <c r="C25" s="41"/>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="48" t="s">
         <v>172</v>
       </c>
       <c r="E25" s="34"/>
-      <c r="F25" s="55">
+      <c r="F25" s="34">
         <v>40.0</v>
       </c>
-      <c r="G25" s="44">
+      <c r="G25" s="43">
         <v>46156.0</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="I25" s="44"/>
-      <c r="J25" s="56">
+      <c r="I25" s="43"/>
+      <c r="J25" s="43">
         <v>46191.0</v>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="45">
         <v>1549250.84</v>
       </c>
       <c r="L25" s="34" t="s">
@@ -2266,7 +2269,7 @@
       <c r="M25" s="39">
         <v>1549250.84</v>
       </c>
-      <c r="N25" s="53"/>
+      <c r="N25" s="54"/>
       <c r="O25" s="25"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
@@ -2277,24 +2280,34 @@
     <row r="26">
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="49" t="s">
+      <c r="C26" s="55"/>
+      <c r="D26" s="48" t="s">
         <v>174</v>
       </c>
       <c r="E26" s="34"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="46"/>
+      <c r="F26" s="34">
+        <v>48.0</v>
+      </c>
+      <c r="G26" s="43">
+        <v>46230.0</v>
+      </c>
+      <c r="H26" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43">
+        <v>46262.0</v>
+      </c>
+      <c r="K26" s="45" t="s">
+        <v>176</v>
+      </c>
       <c r="L26" s="34" t="s">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="M26" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="N26" s="53"/>
+        <v>176</v>
+      </c>
+      <c r="N26" s="54"/>
       <c r="O26" s="25"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
@@ -2306,34 +2319,34 @@
       <c r="A27" s="23"/>
       <c r="B27" s="23"/>
       <c r="C27" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27" s="28" t="s">
         <v>50</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G27" s="28"/>
       <c r="H27" s="28" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
-      <c r="K27" s="58" t="s">
+      <c r="K27" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="M27" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="L27" s="31" t="s">
+      <c r="N27" s="28" t="s">
         <v>64</v>
-      </c>
-      <c r="M27" s="59" t="s">
-        <v>65</v>
-      </c>
-      <c r="N27" s="28" t="s">
-        <v>67</v>
       </c>
       <c r="O27" s="25"/>
       <c r="P27" s="27"/>
@@ -2356,8 +2369,8 @@
       <c r="C28" s="32">
         <v>2.0</v>
       </c>
-      <c r="D28" s="60" t="s">
-        <v>176</v>
+      <c r="D28" s="58" t="s">
+        <v>178</v>
       </c>
       <c r="E28" s="35"/>
       <c r="F28" s="35">
@@ -2367,19 +2380,19 @@
         <v>45791.0</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I28" s="36"/>
       <c r="J28" s="36">
         <v>45834.0</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="37">
         <v>188246.17</v>
       </c>
       <c r="L28" s="34" t="s">
-        <v>177</v>
-      </c>
-      <c r="M28" s="61">
+        <v>179</v>
+      </c>
+      <c r="M28" s="59">
         <v>188246.17</v>
       </c>
       <c r="N28" s="51"/>
@@ -2403,10 +2416,10 @@
       <c r="A29" s="23"/>
       <c r="B29" s="23"/>
       <c r="C29" s="41"/>
-      <c r="D29" s="60" t="s">
-        <v>178</v>
-      </c>
-      <c r="E29" s="55">
+      <c r="D29" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="60">
         <v>46.0</v>
       </c>
       <c r="F29" s="35">
@@ -2416,17 +2429,17 @@
         <v>45814.0</v>
       </c>
       <c r="H29" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44">
+        <v>181</v>
+      </c>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43">
         <v>45955.0</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29" s="37">
         <v>112720.77</v>
       </c>
       <c r="L29" s="34" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M29" s="39">
         <v>112720.77</v>
@@ -2452,37 +2465,37 @@
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
       <c r="C30" s="41"/>
-      <c r="D30" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="E30" s="63" t="s">
-        <v>182</v>
+      <c r="D30" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="E30" s="62" t="s">
+        <v>184</v>
       </c>
       <c r="F30" s="35">
         <v>529.0</v>
       </c>
-      <c r="G30" s="64">
+      <c r="G30" s="63">
         <v>45853.0</v>
       </c>
       <c r="H30" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44">
+        <v>65</v>
+      </c>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43">
         <v>45939.0</v>
       </c>
-      <c r="K30" s="46">
+      <c r="K30" s="45">
         <v>378307.61</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M30" s="39">
         <v>378307.61</v>
       </c>
       <c r="N30" s="51"/>
       <c r="O30" s="25"/>
-      <c r="P30" s="65"/>
+      <c r="P30" s="64"/>
       <c r="Q30" s="27"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
@@ -2501,37 +2514,37 @@
       <c r="A31" s="23"/>
       <c r="B31" s="23"/>
       <c r="C31" s="41"/>
-      <c r="D31" s="62" t="s">
+      <c r="D31" s="61" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="62" t="s">
         <v>184</v>
-      </c>
-      <c r="E31" s="63" t="s">
-        <v>182</v>
       </c>
       <c r="F31" s="34">
         <v>691.0</v>
       </c>
-      <c r="G31" s="64">
+      <c r="G31" s="63">
         <v>45910.0</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44">
+        <v>65</v>
+      </c>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43">
         <v>45941.0</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31" s="37">
         <v>3315.0471000000252</v>
       </c>
       <c r="L31" s="34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M31" s="39">
         <v>3315.04710000003</v>
       </c>
       <c r="N31" s="51"/>
       <c r="O31" s="25"/>
-      <c r="P31" s="65"/>
+      <c r="P31" s="64"/>
       <c r="Q31" s="27"/>
       <c r="R31" s="27"/>
       <c r="S31" s="27"/>
@@ -2550,37 +2563,37 @@
       <c r="A32" s="23"/>
       <c r="B32" s="23"/>
       <c r="C32" s="41"/>
-      <c r="D32" s="62" t="s">
-        <v>186</v>
-      </c>
-      <c r="E32" s="66">
+      <c r="D32" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" s="65">
         <v>135.0</v>
       </c>
       <c r="F32" s="34">
         <v>677.0</v>
       </c>
-      <c r="G32" s="64">
+      <c r="G32" s="63">
         <v>45904.0</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>69</v>
-      </c>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67">
+        <v>72</v>
+      </c>
+      <c r="I32" s="66"/>
+      <c r="J32" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K32" s="46">
+      <c r="K32" s="45">
         <v>198332.75</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="M32" s="39">
         <v>198332.75</v>
       </c>
       <c r="N32" s="51"/>
       <c r="O32" s="25"/>
-      <c r="P32" s="65"/>
+      <c r="P32" s="64"/>
       <c r="Q32" s="27"/>
       <c r="R32" s="27"/>
       <c r="S32" s="27"/>
@@ -2599,37 +2612,37 @@
       <c r="A33" s="23"/>
       <c r="B33" s="23"/>
       <c r="C33" s="41"/>
-      <c r="D33" s="62" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="66">
+      <c r="D33" s="61" t="s">
+        <v>190</v>
+      </c>
+      <c r="E33" s="65">
         <v>40.0</v>
       </c>
       <c r="F33" s="34">
         <v>278.0</v>
       </c>
-      <c r="G33" s="64">
+      <c r="G33" s="63">
         <v>46008.0</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="I33" s="67"/>
-      <c r="J33" s="67">
+        <v>123</v>
+      </c>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66">
         <v>46066.0</v>
       </c>
-      <c r="K33" s="46">
+      <c r="K33" s="45">
         <v>1528.62</v>
       </c>
-      <c r="L33" s="68" t="s">
-        <v>189</v>
-      </c>
-      <c r="M33" s="69" t="s">
-        <v>190</v>
+      <c r="L33" s="67" t="s">
+        <v>191</v>
+      </c>
+      <c r="M33" s="68" t="s">
+        <v>192</v>
       </c>
       <c r="N33" s="51"/>
       <c r="O33" s="25"/>
-      <c r="P33" s="65"/>
+      <c r="P33" s="64"/>
       <c r="Q33" s="27"/>
       <c r="R33" s="27"/>
       <c r="S33" s="27"/>
@@ -2648,37 +2661,37 @@
       <c r="A34" s="23"/>
       <c r="B34" s="23"/>
       <c r="C34" s="41"/>
-      <c r="D34" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="E34" s="66" t="s">
-        <v>192</v>
+      <c r="D34" s="61" t="s">
+        <v>193</v>
+      </c>
+      <c r="E34" s="65" t="s">
+        <v>194</v>
       </c>
       <c r="F34" s="34">
         <v>748.0</v>
       </c>
-      <c r="G34" s="64">
+      <c r="G34" s="63">
         <v>45930.0</v>
       </c>
       <c r="H34" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="I34" s="67"/>
-      <c r="J34" s="67">
+        <v>95</v>
+      </c>
+      <c r="I34" s="66"/>
+      <c r="J34" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K34" s="46">
+      <c r="K34" s="45">
         <v>38718.58</v>
       </c>
       <c r="L34" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="M34" s="61" t="s">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="M34" s="59" t="s">
+        <v>196</v>
       </c>
       <c r="N34" s="51"/>
       <c r="O34" s="25"/>
-      <c r="P34" s="65"/>
+      <c r="P34" s="64"/>
       <c r="Q34" s="27"/>
       <c r="R34" s="27"/>
       <c r="S34" s="27"/>
@@ -2697,37 +2710,37 @@
       <c r="A35" s="23"/>
       <c r="B35" s="23"/>
       <c r="C35" s="41"/>
-      <c r="D35" s="62" t="s">
-        <v>195</v>
-      </c>
-      <c r="E35" s="66">
+      <c r="D35" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="E35" s="65">
         <v>154.0</v>
       </c>
       <c r="F35" s="34">
         <v>822.0</v>
       </c>
-      <c r="G35" s="64">
+      <c r="G35" s="63">
         <v>45968.0</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="I35" s="67"/>
-      <c r="J35" s="67">
+        <v>113</v>
+      </c>
+      <c r="I35" s="66"/>
+      <c r="J35" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K35" s="46">
+      <c r="K35" s="45">
         <v>133124.11</v>
       </c>
       <c r="L35" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="M35" s="61" t="s">
-        <v>197</v>
+        <v>198</v>
+      </c>
+      <c r="M35" s="59" t="s">
+        <v>199</v>
       </c>
       <c r="N35" s="51"/>
       <c r="O35" s="25"/>
-      <c r="P35" s="65"/>
+      <c r="P35" s="64"/>
       <c r="Q35" s="27"/>
       <c r="R35" s="27"/>
       <c r="S35" s="27"/>
@@ -2746,30 +2759,30 @@
       <c r="A36" s="23"/>
       <c r="B36" s="23"/>
       <c r="C36" s="41"/>
-      <c r="D36" s="62" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="66">
+      <c r="D36" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="E36" s="65">
         <v>252.0</v>
       </c>
-      <c r="F36" s="66">
+      <c r="F36" s="65">
         <v>360.0</v>
       </c>
-      <c r="G36" s="70">
+      <c r="G36" s="69">
         <v>46043.0</v>
       </c>
-      <c r="H36" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="I36" s="71"/>
-      <c r="J36" s="70">
+      <c r="H36" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="I36" s="70"/>
+      <c r="J36" s="69">
         <v>46075.0</v>
       </c>
-      <c r="K36" s="46">
+      <c r="K36" s="45">
         <v>11372.9</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M36" s="39">
         <v>11372.9</v>
@@ -2795,18 +2808,18 @@
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
       <c r="C37" s="41"/>
-      <c r="D37" s="62" t="s">
-        <v>200</v>
-      </c>
-      <c r="E37" s="66"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="66" t="s">
-        <v>201</v>
-      </c>
-      <c r="J37" s="70"/>
-      <c r="K37" s="46"/>
+      <c r="D37" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="J37" s="69"/>
+      <c r="K37" s="45"/>
       <c r="L37" s="34"/>
       <c r="M37" s="39"/>
       <c r="N37" s="51">
@@ -2831,23 +2844,23 @@
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="62" t="s">
-        <v>202</v>
-      </c>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66" t="s">
-        <v>201</v>
-      </c>
-      <c r="J38" s="70"/>
-      <c r="K38" s="46"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="61" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="J38" s="69"/>
+      <c r="K38" s="45"/>
       <c r="L38" s="34"/>
       <c r="M38" s="39"/>
       <c r="N38" s="51" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O38" s="25"/>
       <c r="P38" s="27"/>
@@ -2871,30 +2884,30 @@
       <c r="C39" s="32">
         <v>3.0</v>
       </c>
-      <c r="D39" s="62" t="s">
-        <v>204</v>
-      </c>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66">
+      <c r="D39" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65">
         <v>1465.0</v>
       </c>
-      <c r="G39" s="70">
+      <c r="G39" s="69">
         <v>46104.0</v>
       </c>
-      <c r="H39" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="I39" s="71"/>
-      <c r="J39" s="70">
+      <c r="H39" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="70"/>
+      <c r="J39" s="69">
         <v>46106.0</v>
       </c>
-      <c r="K39" s="46">
+      <c r="K39" s="45">
         <v>27801.11</v>
       </c>
-      <c r="L39" s="72" t="s">
-        <v>205</v>
-      </c>
-      <c r="M39" s="73">
+      <c r="L39" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="M39" s="72">
         <v>27801.11</v>
       </c>
       <c r="N39" s="51"/>
@@ -2918,30 +2931,30 @@
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
       <c r="C40" s="41"/>
-      <c r="D40" s="62" t="s">
-        <v>206</v>
-      </c>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66">
+      <c r="D40" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65">
         <v>1882.0</v>
       </c>
-      <c r="G40" s="70">
+      <c r="G40" s="69">
         <v>46199.0</v>
       </c>
-      <c r="H40" s="66" t="s">
-        <v>75</v>
-      </c>
-      <c r="I40" s="71"/>
-      <c r="J40" s="70">
+      <c r="H40" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" s="70"/>
+      <c r="J40" s="69">
         <v>46233.0</v>
       </c>
-      <c r="K40" s="46">
+      <c r="K40" s="45">
         <v>58868.35</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="M40" s="73">
+        <v>63</v>
+      </c>
+      <c r="M40" s="72">
         <v>58868.35</v>
       </c>
       <c r="N40" s="51"/>
@@ -2951,16 +2964,16 @@
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
       <c r="C41" s="41"/>
-      <c r="K41" s="74"/>
-      <c r="M41" s="74"/>
+      <c r="K41" s="73"/>
+      <c r="M41" s="73"/>
       <c r="V41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
       <c r="C42" s="41"/>
-      <c r="K42" s="74"/>
-      <c r="M42" s="74"/>
+      <c r="K42" s="73"/>
+      <c r="M42" s="73"/>
       <c r="V42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
@@ -2990,9 +3003,9 @@
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
-      <c r="C47" s="57"/>
-      <c r="K47" s="74"/>
-      <c r="M47" s="74"/>
+      <c r="C47" s="55"/>
+      <c r="K47" s="73"/>
+      <c r="M47" s="73"/>
       <c r="V47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
@@ -3011,12 +3024,12 @@
       <c r="M48" s="15"/>
       <c r="N48" s="15"/>
       <c r="O48" s="15"/>
-      <c r="P48" s="75"/>
-      <c r="Q48" s="75"/>
-      <c r="R48" s="75"/>
-      <c r="S48" s="75"/>
-      <c r="T48" s="75"/>
-      <c r="U48" s="75"/>
+      <c r="P48" s="74"/>
+      <c r="Q48" s="74"/>
+      <c r="R48" s="74"/>
+      <c r="S48" s="74"/>
+      <c r="T48" s="74"/>
+      <c r="U48" s="74"/>
       <c r="V48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
@@ -7919,7 +7932,7 @@
       <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>2.5E32</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -8004,13 +8017,13 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>4</v>
@@ -8049,13 +8062,13 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>4</v>
@@ -8163,7 +8176,7 @@
         <v>339039.0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" s="14">
         <v>524584.95</v>
@@ -8185,13 +8198,13 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>4</v>
@@ -8209,7 +8222,7 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J9" s="14">
         <v>211614.23</v>
@@ -8230,13 +8243,13 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>4</v>
@@ -8275,13 +8288,13 @@
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>4</v>
@@ -8320,13 +8333,13 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>4</v>
@@ -8344,7 +8357,7 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8365,13 +8378,13 @@
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>4</v>
@@ -8400,7 +8413,7 @@
       <c r="L13" s="14">
         <v>0.0</v>
       </c>
-      <c r="M13" s="37"/>
+      <c r="M13" s="38"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8435,7 +8448,7 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J14" s="14">
         <v>968237.39</v>
@@ -8456,13 +8469,13 @@
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>4</v>
@@ -8501,13 +8514,13 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>4</v>
@@ -8546,13 +8559,13 @@
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>4</v>
@@ -8591,13 +8604,13 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>80</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>4</v>
@@ -8615,7 +8628,7 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J18" s="14">
         <v>63746.85</v>
@@ -8636,13 +8649,13 @@
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>4</v>
@@ -8660,7 +8673,7 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8681,13 +8694,13 @@
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>4</v>
@@ -8726,13 +8739,13 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>4</v>
@@ -8771,18 +8784,18 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="50">
         <v>45953.0</v>
       </c>
       <c r="F22" s="8" t="s">
@@ -8816,18 +8829,18 @@
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="42">
+      <c r="E23" s="50">
         <v>45953.0</v>
       </c>
       <c r="F23" s="8" t="s">
@@ -8840,7 +8853,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -8861,18 +8874,18 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="42">
+      <c r="E24" s="50">
         <v>45953.0</v>
       </c>
       <c r="F24" s="8" t="s">
@@ -8906,18 +8919,18 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="42">
+      <c r="E25" s="50">
         <v>45975.0</v>
       </c>
       <c r="F25" s="8" t="s">
@@ -8930,7 +8943,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -8951,18 +8964,18 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="42">
+      <c r="E26" s="50">
         <v>45989.0</v>
       </c>
       <c r="F26" s="8" t="s">
@@ -8996,13 +9009,13 @@
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>4</v>
@@ -9041,13 +9054,13 @@
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>4</v>
@@ -9065,7 +9078,7 @@
         <v>339039.0</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J28" s="14">
         <v>1912292.52</v>
@@ -9086,13 +9099,13 @@
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>4</v>
@@ -9131,13 +9144,13 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>4</v>
@@ -9176,13 +9189,13 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>4</v>
@@ -9200,7 +9213,7 @@
         <v>339039.0</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J31" s="14">
         <v>18462.36</v>
@@ -9221,13 +9234,13 @@
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>4</v>
@@ -9245,7 +9258,7 @@
         <v>339039.0</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J32" s="14">
         <v>1530656.62</v>
@@ -9266,13 +9279,13 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>4</v>
@@ -17610,18 +17623,18 @@
       <c r="I955" s="2"/>
       <c r="J955" s="2"/>
       <c r="K955" s="2"/>
-      <c r="L955" s="76"/>
+      <c r="L955" s="75"/>
       <c r="M955" s="2"/>
       <c r="N955" s="2"/>
       <c r="O955" s="2"/>
       <c r="P955" s="2"/>
       <c r="Q955" s="2"/>
-      <c r="R955" s="77"/>
-      <c r="S955" s="77"/>
-      <c r="T955" s="77"/>
-      <c r="U955" s="77"/>
-      <c r="V955" s="77"/>
-      <c r="W955" s="76"/>
+      <c r="R955" s="76"/>
+      <c r="S955" s="76"/>
+      <c r="T955" s="76"/>
+      <c r="U955" s="76"/>
+      <c r="V955" s="76"/>
+      <c r="W955" s="75"/>
       <c r="X955" s="2"/>
       <c r="Y955" s="2"/>
       <c r="Z955" s="2"/>
@@ -17646,18 +17659,18 @@
       <c r="I956" s="2"/>
       <c r="J956" s="2"/>
       <c r="K956" s="2"/>
-      <c r="L956" s="76"/>
+      <c r="L956" s="75"/>
       <c r="M956" s="2"/>
       <c r="N956" s="2"/>
       <c r="O956" s="2"/>
       <c r="P956" s="2"/>
       <c r="Q956" s="2"/>
-      <c r="R956" s="77"/>
-      <c r="S956" s="77"/>
-      <c r="T956" s="77"/>
-      <c r="U956" s="77"/>
-      <c r="V956" s="77"/>
-      <c r="W956" s="76"/>
+      <c r="R956" s="76"/>
+      <c r="S956" s="76"/>
+      <c r="T956" s="76"/>
+      <c r="U956" s="76"/>
+      <c r="V956" s="76"/>
+      <c r="W956" s="75"/>
       <c r="X956" s="2"/>
       <c r="Y956" s="2"/>
       <c r="Z956" s="2"/>
@@ -17682,18 +17695,18 @@
       <c r="I957" s="2"/>
       <c r="J957" s="2"/>
       <c r="K957" s="2"/>
-      <c r="L957" s="76"/>
+      <c r="L957" s="75"/>
       <c r="M957" s="2"/>
       <c r="N957" s="2"/>
       <c r="O957" s="2"/>
       <c r="P957" s="2"/>
       <c r="Q957" s="2"/>
-      <c r="R957" s="77"/>
-      <c r="S957" s="77"/>
-      <c r="T957" s="77"/>
-      <c r="U957" s="77"/>
-      <c r="V957" s="77"/>
-      <c r="W957" s="76"/>
+      <c r="R957" s="76"/>
+      <c r="S957" s="76"/>
+      <c r="T957" s="76"/>
+      <c r="U957" s="76"/>
+      <c r="V957" s="76"/>
+      <c r="W957" s="75"/>
       <c r="X957" s="2"/>
       <c r="Y957" s="2"/>
       <c r="Z957" s="2"/>
@@ -17718,18 +17731,18 @@
       <c r="I958" s="2"/>
       <c r="J958" s="2"/>
       <c r="K958" s="2"/>
-      <c r="L958" s="76"/>
+      <c r="L958" s="75"/>
       <c r="M958" s="2"/>
       <c r="N958" s="2"/>
       <c r="O958" s="2"/>
       <c r="P958" s="2"/>
       <c r="Q958" s="2"/>
-      <c r="R958" s="77"/>
-      <c r="S958" s="77"/>
-      <c r="T958" s="77"/>
-      <c r="U958" s="77"/>
-      <c r="V958" s="77"/>
-      <c r="W958" s="76"/>
+      <c r="R958" s="76"/>
+      <c r="S958" s="76"/>
+      <c r="T958" s="76"/>
+      <c r="U958" s="76"/>
+      <c r="V958" s="76"/>
+      <c r="W958" s="75"/>
       <c r="X958" s="2"/>
       <c r="Y958" s="2"/>
       <c r="Z958" s="2"/>
@@ -17754,18 +17767,18 @@
       <c r="I959" s="2"/>
       <c r="J959" s="2"/>
       <c r="K959" s="2"/>
-      <c r="L959" s="76"/>
+      <c r="L959" s="75"/>
       <c r="M959" s="2"/>
       <c r="N959" s="2"/>
       <c r="O959" s="2"/>
       <c r="P959" s="2"/>
       <c r="Q959" s="2"/>
-      <c r="R959" s="77"/>
-      <c r="S959" s="77"/>
-      <c r="T959" s="77"/>
-      <c r="U959" s="77"/>
-      <c r="V959" s="77"/>
-      <c r="W959" s="76"/>
+      <c r="R959" s="76"/>
+      <c r="S959" s="76"/>
+      <c r="T959" s="76"/>
+      <c r="U959" s="76"/>
+      <c r="V959" s="76"/>
+      <c r="W959" s="75"/>
       <c r="X959" s="2"/>
       <c r="Y959" s="2"/>
       <c r="Z959" s="2"/>
@@ -17790,18 +17803,18 @@
       <c r="I960" s="2"/>
       <c r="J960" s="2"/>
       <c r="K960" s="2"/>
-      <c r="L960" s="76"/>
+      <c r="L960" s="75"/>
       <c r="M960" s="2"/>
       <c r="N960" s="2"/>
       <c r="O960" s="2"/>
       <c r="P960" s="2"/>
       <c r="Q960" s="2"/>
-      <c r="R960" s="77"/>
-      <c r="S960" s="77"/>
-      <c r="T960" s="77"/>
-      <c r="U960" s="77"/>
-      <c r="V960" s="77"/>
-      <c r="W960" s="76"/>
+      <c r="R960" s="76"/>
+      <c r="S960" s="76"/>
+      <c r="T960" s="76"/>
+      <c r="U960" s="76"/>
+      <c r="V960" s="76"/>
+      <c r="W960" s="75"/>
       <c r="X960" s="2"/>
       <c r="Y960" s="2"/>
       <c r="Z960" s="2"/>
@@ -17826,18 +17839,18 @@
       <c r="I961" s="2"/>
       <c r="J961" s="2"/>
       <c r="K961" s="2"/>
-      <c r="L961" s="76"/>
+      <c r="L961" s="75"/>
       <c r="M961" s="2"/>
       <c r="N961" s="2"/>
       <c r="O961" s="2"/>
       <c r="P961" s="2"/>
       <c r="Q961" s="2"/>
-      <c r="R961" s="77"/>
-      <c r="S961" s="77"/>
-      <c r="T961" s="77"/>
-      <c r="U961" s="77"/>
-      <c r="V961" s="77"/>
-      <c r="W961" s="76"/>
+      <c r="R961" s="76"/>
+      <c r="S961" s="76"/>
+      <c r="T961" s="76"/>
+      <c r="U961" s="76"/>
+      <c r="V961" s="76"/>
+      <c r="W961" s="75"/>
       <c r="X961" s="2"/>
       <c r="Y961" s="2"/>
       <c r="Z961" s="2"/>
@@ -17862,18 +17875,18 @@
       <c r="I962" s="2"/>
       <c r="J962" s="2"/>
       <c r="K962" s="2"/>
-      <c r="L962" s="76"/>
+      <c r="L962" s="75"/>
       <c r="M962" s="2"/>
       <c r="N962" s="2"/>
       <c r="O962" s="2"/>
       <c r="P962" s="2"/>
       <c r="Q962" s="2"/>
-      <c r="R962" s="77"/>
-      <c r="S962" s="77"/>
-      <c r="T962" s="77"/>
-      <c r="U962" s="77"/>
-      <c r="V962" s="77"/>
-      <c r="W962" s="76"/>
+      <c r="R962" s="76"/>
+      <c r="S962" s="76"/>
+      <c r="T962" s="76"/>
+      <c r="U962" s="76"/>
+      <c r="V962" s="76"/>
+      <c r="W962" s="75"/>
       <c r="X962" s="2"/>
       <c r="Y962" s="2"/>
       <c r="Z962" s="2"/>
@@ -17898,18 +17911,18 @@
       <c r="I963" s="2"/>
       <c r="J963" s="2"/>
       <c r="K963" s="2"/>
-      <c r="L963" s="76"/>
+      <c r="L963" s="75"/>
       <c r="M963" s="2"/>
       <c r="N963" s="2"/>
       <c r="O963" s="2"/>
       <c r="P963" s="2"/>
       <c r="Q963" s="2"/>
-      <c r="R963" s="77"/>
-      <c r="S963" s="77"/>
-      <c r="T963" s="77"/>
-      <c r="U963" s="77"/>
-      <c r="V963" s="77"/>
-      <c r="W963" s="76"/>
+      <c r="R963" s="76"/>
+      <c r="S963" s="76"/>
+      <c r="T963" s="76"/>
+      <c r="U963" s="76"/>
+      <c r="V963" s="76"/>
+      <c r="W963" s="75"/>
       <c r="X963" s="2"/>
       <c r="Y963" s="2"/>
       <c r="Z963" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,12 +30,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="209">
   <si>
+    <t>Controle de pagamentos</t>
+  </si>
+  <si>
     <t>Saldo</t>
   </si>
   <si>
-    <t>Controle de pagamentos</t>
-  </si>
-  <si>
     <t>2025NE000005</t>
   </si>
   <si>
@@ -81,13 +81,19 @@
     <t>Ação</t>
   </si>
   <si>
+    <t>2025NE000369</t>
+  </si>
+  <si>
     <t>PAG</t>
   </si>
   <si>
+    <t>C25516</t>
+  </si>
+  <si>
     <t>Moeda</t>
   </si>
   <si>
-    <t>2025NE000369</t>
+    <t>25E0387</t>
   </si>
   <si>
     <t>Valor Total do Contrato</t>
@@ -96,15 +102,9 @@
     <t>Valor a Empenhar</t>
   </si>
   <si>
-    <t>C25516</t>
-  </si>
-  <si>
     <t>Valor Empenhado</t>
   </si>
   <si>
-    <t>25E0387</t>
-  </si>
-  <si>
     <t>Valor Liquidado</t>
   </si>
   <si>
@@ -123,18 +123,21 @@
     <t>Editar</t>
   </si>
   <si>
+    <t>2025NE000371</t>
+  </si>
+  <si>
     <t>005/CELOG-PAMALS/2025</t>
   </si>
   <si>
+    <t>25E0389</t>
+  </si>
+  <si>
     <t>CELOG</t>
   </si>
   <si>
     <t>PAMALS</t>
   </si>
   <si>
-    <t>2025NE000371</t>
-  </si>
-  <si>
     <t>Vigente</t>
   </si>
   <si>
@@ -144,27 +147,24 @@
     <t>67101.001510/2024-12</t>
   </si>
   <si>
-    <t>25E0389</t>
-  </si>
-  <si>
     <t>R$</t>
   </si>
   <si>
+    <t>2025NE000413</t>
+  </si>
+  <si>
+    <t>C25501</t>
+  </si>
+  <si>
+    <t>25E0403</t>
+  </si>
+  <si>
+    <t>20SP</t>
+  </si>
+  <si>
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
-    <t>2025NE000413</t>
-  </si>
-  <si>
-    <t>C25501</t>
-  </si>
-  <si>
-    <t>25E0403</t>
-  </si>
-  <si>
-    <t>20SP</t>
-  </si>
-  <si>
     <t>2025NE000414</t>
   </si>
   <si>
@@ -174,10 +174,19 @@
     <t>25E0431</t>
   </si>
   <si>
+    <t>21EM</t>
+  </si>
+  <si>
     <t>Módulo</t>
   </si>
   <si>
-    <t>21EM</t>
+    <t>2025NE000559</t>
+  </si>
+  <si>
+    <t>C25545</t>
+  </si>
+  <si>
+    <t>25E0524</t>
   </si>
   <si>
     <t>Referência</t>
@@ -186,6 +195,9 @@
     <t>Nº recibo</t>
   </si>
   <si>
+    <t>20X7</t>
+  </si>
+  <si>
     <t>Nº</t>
   </si>
   <si>
@@ -195,16 +207,13 @@
     <t>Empenho</t>
   </si>
   <si>
-    <t>2025NE000559</t>
-  </si>
-  <si>
-    <t>C25545</t>
+    <t>2025NE000770</t>
   </si>
   <si>
     <t>Observações</t>
   </si>
   <si>
-    <t>25E0524</t>
+    <t>25E0731</t>
   </si>
   <si>
     <t>Vencimento</t>
@@ -216,57 +225,48 @@
     <t>Ordem de Pagamento</t>
   </si>
   <si>
-    <t>20X7</t>
-  </si>
-  <si>
     <t>Faturado</t>
   </si>
   <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>2025NE000770</t>
-  </si>
-  <si>
-    <t>25E0731</t>
+    <t>2025NE000774</t>
+  </si>
+  <si>
+    <t>25E0737</t>
   </si>
   <si>
     <t>FEV/25</t>
   </si>
   <si>
-    <t>2025NE000774</t>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
+    <t>25E0787</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>25E0737</t>
+    <t>219C</t>
   </si>
   <si>
     <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
-    <t>2025NE000843</t>
-  </si>
-  <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
-  </si>
-  <si>
-    <t>219C</t>
+    <t>2025NE001065</t>
+  </si>
+  <si>
+    <t>25E0999</t>
   </si>
   <si>
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
-  </si>
-  <si>
     <t>2025NE001200</t>
   </si>
   <si>
@@ -276,37 +276,43 @@
     <t>25E1128</t>
   </si>
   <si>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
+  </si>
+  <si>
+    <t>2025NE001627</t>
+  </si>
+  <si>
+    <t>25E1475</t>
+  </si>
+  <si>
     <t>MAR/25</t>
   </si>
   <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>25E1446</t>
-  </si>
-  <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
   </si>
   <si>
-    <t>2025NE001627</t>
-  </si>
-  <si>
-    <t>25E1475</t>
+    <t>2025NE001629</t>
+  </si>
+  <si>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
   </si>
   <si>
     <t>2025NP001979</t>
   </si>
   <si>
-    <t>2025NE001629</t>
-  </si>
-  <si>
-    <t>C25820</t>
-  </si>
-  <si>
-    <t>25E1477</t>
+    <t>2025NE001687</t>
+  </si>
+  <si>
+    <t>25E1535</t>
   </si>
   <si>
     <t>ABR/25</t>
@@ -315,40 +321,46 @@
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>2025NE001687</t>
-  </si>
-  <si>
-    <t>25E1535</t>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
   </si>
   <si>
     <t>2025NP002341</t>
   </si>
   <si>
+    <t>2025NE001689</t>
+  </si>
+  <si>
+    <t>25E1537</t>
+  </si>
+  <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>2025NE001688</t>
-  </si>
-  <si>
-    <t>25E1536</t>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
   </si>
   <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>2025NE001689</t>
-  </si>
-  <si>
-    <t>25E1537</t>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
   </si>
   <si>
     <t>JUN/25</t>
   </si>
   <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
+    <t>2025NE001828</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -357,164 +369,152 @@
 2025NE000774</t>
   </si>
   <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
+  </si>
+  <si>
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
   </si>
   <si>
     <t>JUL/25</t>
   </si>
   <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
-    <t>20YJ</t>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
   </si>
   <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
+    <t>25E2021</t>
   </si>
   <si>
     <t>AGO/25</t>
   </si>
   <si>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
+  </si>
+  <si>
     <t>2025NP004558</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
   </si>
   <si>
     <t>SET/25</t>
-  </si>
-  <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
   </si>
   <si>
     <t>2025NE001688 
 2025NE001828</t>
   </si>
   <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
     <t>2025NP004897</t>
   </si>
   <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
+    <t>26E0375</t>
   </si>
   <si>
     <t>OUT/25</t>
   </si>
   <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
     <t>2025NP004932</t>
   </si>
   <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
   </si>
   <si>
     <t>NOV/25</t>
   </si>
   <si>
+    <t>2026NE000817</t>
+  </si>
+  <si>
     <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
   </si>
   <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
+  </si>
+  <si>
     <t>2026NP400440</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
   </si>
   <si>
     <t>DEZ/25</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
+    <t>2026NE000944</t>
   </si>
   <si>
     <t>2025NE001065, 2025NE002200</t>
   </si>
   <si>
+    <t>26E0906</t>
+  </si>
+  <si>
     <t>2026NP400412</t>
   </si>
   <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
-  </si>
-  <si>
     <t>JAN/26</t>
   </si>
   <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
     <t>2026NP401035</t>
-  </si>
-  <si>
-    <t>26E0906</t>
   </si>
   <si>
     <t>FEV/26</t>
@@ -715,13 +715,13 @@
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Century Gothic"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -866,35 +866,35 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -931,28 +931,28 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -971,7 +971,7 @@
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="6" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -993,14 +993,14 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1015,13 +1015,13 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1030,7 +1030,7 @@
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1412,46 +1412,46 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="4"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V2" s="9"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" s="8"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="4"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="15"/>
@@ -1481,19 +1481,19 @@
         <v>16</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P4" s="17" t="s">
         <v>25</v>
@@ -1513,23 +1513,23 @@
       <c r="U4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="V4" s="4"/>
+      <c r="V4" s="3"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1538,13 +1538,13 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M5" s="19" t="s">
         <v>39</v>
@@ -1565,15 +1565,15 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" s="4"/>
+        <v>44</v>
+      </c>
+      <c r="V5" s="3"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="L6" s="22"/>
-      <c r="V6" s="4"/>
+      <c r="V6" s="3"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="23"/>
@@ -1587,55 +1587,55 @@
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
-      <c r="L7" s="26"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="27"/>
-      <c r="V7" s="4"/>
+      <c r="P7" s="28"/>
+      <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>50</v>
+      <c r="C8" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>53</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="28" t="s">
         <v>54</v>
       </c>
+      <c r="F8" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>58</v>
+      </c>
       <c r="I8" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="K8" s="28" t="s">
         <v>60</v>
       </c>
+      <c r="J8" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>63</v>
+      </c>
       <c r="L8" s="31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="O8" s="28"/>
-      <c r="P8" s="27"/>
-      <c r="V8" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="29"/>
+      <c r="P8" s="28"/>
+      <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="23"/>
@@ -1644,10 +1644,10 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F9" s="35">
         <v>594.0</v>
@@ -1656,7 +1656,7 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I9" s="36"/>
       <c r="J9" s="36">
@@ -1666,7 +1666,7 @@
         <v>748504.24</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
@@ -1674,18 +1674,18 @@
       </c>
       <c r="N9" s="40"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="27"/>
-      <c r="V9" s="4"/>
+      <c r="P9" s="28"/>
+      <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
       <c r="C10" s="41"/>
       <c r="D10" s="33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F10" s="35">
         <v>620.0</v>
@@ -1694,7 +1694,7 @@
         <v>45775.0</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I10" s="36"/>
       <c r="J10" s="36">
@@ -1704,7 +1704,7 @@
         <v>1110378.24</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M10" s="39">
         <f t="shared" si="1"/>
@@ -1712,18 +1712,18 @@
       </c>
       <c r="N10" s="42"/>
       <c r="O10" s="25"/>
-      <c r="P10" s="27"/>
-      <c r="V10" s="4"/>
+      <c r="P10" s="28"/>
+      <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="41"/>
       <c r="D11" s="33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F11" s="35">
         <v>634.0</v>
@@ -1732,7 +1732,7 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36">
@@ -1742,25 +1742,25 @@
         <v>974557.12</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M11" s="39">
         <v>974557.12</v>
       </c>
       <c r="N11" s="42"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="27"/>
-      <c r="V11" s="4"/>
+      <c r="P11" s="28"/>
+      <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="41"/>
       <c r="D12" s="33" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F12" s="34">
         <v>660.0</v>
@@ -1769,7 +1769,7 @@
         <v>45856.0</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36">
@@ -1779,25 +1779,25 @@
         <v>1402001.34</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
       <c r="N12" s="47"/>
       <c r="O12" s="25"/>
-      <c r="P12" s="27"/>
-      <c r="V12" s="4"/>
+      <c r="P12" s="28"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="41"/>
-      <c r="D13" s="48" t="s">
-        <v>104</v>
+      <c r="D13" s="49" t="s">
+        <v>109</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F13" s="35">
         <v>661.0</v>
@@ -1806,7 +1806,7 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I13" s="43"/>
       <c r="J13" s="43">
@@ -1816,25 +1816,25 @@
         <v>1223702.3</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
       <c r="N13" s="47"/>
       <c r="O13" s="25"/>
-      <c r="P13" s="49"/>
-      <c r="V13" s="4"/>
+      <c r="P13" s="50"/>
+      <c r="V13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="41"/>
-      <c r="D14" s="48" t="s">
-        <v>112</v>
+      <c r="D14" s="49" t="s">
+        <v>118</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F14" s="34">
         <v>688.0</v>
@@ -1843,7 +1843,7 @@
         <v>45901.0</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I14" s="43"/>
       <c r="J14" s="43">
@@ -1853,25 +1853,25 @@
         <v>1011677.95</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
       <c r="N14" s="42"/>
       <c r="O14" s="25"/>
-      <c r="P14" s="27"/>
-      <c r="V14" s="4"/>
+      <c r="P14" s="28"/>
+      <c r="V14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="48" t="s">
-        <v>121</v>
+      <c r="D15" s="49" t="s">
+        <v>124</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F15" s="34">
         <v>696.0</v>
@@ -1890,24 +1890,24 @@
         <v>896744.06</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M15" s="39">
         <v>896744.06</v>
       </c>
       <c r="N15" s="47"/>
       <c r="O15" s="25"/>
-      <c r="V15" s="4"/>
+      <c r="V15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="41"/>
-      <c r="D16" s="48" t="s">
-        <v>126</v>
+      <c r="D16" s="49" t="s">
+        <v>131</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F16" s="34">
         <v>704.0</v>
@@ -1916,7 +1916,7 @@
         <v>45957.0</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I16" s="43"/>
       <c r="J16" s="43">
@@ -1926,21 +1926,21 @@
         <v>919329.06</v>
       </c>
       <c r="L16" s="34" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M16" s="39">
         <v>919329.06</v>
       </c>
       <c r="N16" s="42"/>
       <c r="O16" s="25"/>
-      <c r="V16" s="4"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
       <c r="C17" s="41"/>
-      <c r="D17" s="48" t="s">
-        <v>134</v>
+      <c r="D17" s="49" t="s">
+        <v>137</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="34">
@@ -1950,7 +1950,7 @@
         <v>45972.0</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I17" s="34"/>
       <c r="J17" s="43">
@@ -1960,24 +1960,24 @@
         <v>1157009.26</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="M17" s="39">
         <v>1157009.26</v>
       </c>
       <c r="N17" s="51"/>
       <c r="O17" s="25"/>
-      <c r="V17" s="4"/>
+      <c r="V17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
       <c r="C18" s="41"/>
-      <c r="D18" s="48" t="s">
-        <v>143</v>
+      <c r="D18" s="49" t="s">
+        <v>146</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F18" s="34">
         <v>728.0</v>
@@ -1986,7 +1986,7 @@
         <v>46008.0</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I18" s="34"/>
       <c r="J18" s="43">
@@ -1996,28 +1996,28 @@
         <v>1214597.952</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M18" s="39">
         <v>1214597.952</v>
       </c>
       <c r="N18" s="51"/>
       <c r="O18" s="25"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="27"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
       <c r="V18" s="52"/>
     </row>
     <row r="19">
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
       <c r="C19" s="41"/>
-      <c r="D19" s="48" t="s">
-        <v>149</v>
+      <c r="D19" s="49" t="s">
+        <v>154</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F19" s="34">
         <v>278.0</v>
@@ -2026,7 +2026,7 @@
         <v>46042.0</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I19" s="43"/>
       <c r="J19" s="43">
@@ -2036,25 +2036,25 @@
         <v>967082.09</v>
       </c>
       <c r="L19" s="34" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="M19" s="39">
         <v>967082.09</v>
       </c>
       <c r="N19" s="51"/>
       <c r="O19" s="25"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
       <c r="V19" s="52"/>
     </row>
     <row r="20">
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
       <c r="C20" s="41"/>
-      <c r="D20" s="48" t="s">
-        <v>157</v>
+      <c r="D20" s="49" t="s">
+        <v>159</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34">
@@ -2064,7 +2064,7 @@
         <v>46078.0</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I20" s="43"/>
       <c r="J20" s="43">
@@ -2074,24 +2074,24 @@
         <v>719561.08</v>
       </c>
       <c r="L20" s="34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M20" s="39">
         <v>719561.08</v>
       </c>
       <c r="N20" s="51"/>
       <c r="O20" s="25"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
       <c r="V20" s="52"/>
     </row>
     <row r="21">
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
       <c r="C21" s="41"/>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="49" t="s">
         <v>161</v>
       </c>
       <c r="E21" s="34"/>
@@ -2119,17 +2119,17 @@
       </c>
       <c r="N21" s="51"/>
       <c r="O21" s="25"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
       <c r="V21" s="52"/>
     </row>
     <row r="22">
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
       <c r="C22" s="41"/>
-      <c r="D22" s="48" t="s">
+      <c r="D22" s="49" t="s">
         <v>164</v>
       </c>
       <c r="E22" s="34"/>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="N22" s="51"/>
       <c r="O22" s="25"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
       <c r="V22" s="52"/>
     </row>
     <row r="23">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="41"/>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="49" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="34"/>
@@ -2195,17 +2195,17 @@
       </c>
       <c r="N23" s="53"/>
       <c r="O23" s="25"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
       <c r="V23" s="52"/>
     </row>
     <row r="24">
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
       <c r="C24" s="41"/>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="49" t="s">
         <v>170</v>
       </c>
       <c r="E24" s="34"/>
@@ -2233,17 +2233,17 @@
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="25"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
       <c r="V24" s="52"/>
     </row>
     <row r="25">
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
       <c r="C25" s="41"/>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="49" t="s">
         <v>172</v>
       </c>
       <c r="E25" s="34"/>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="N25" s="54"/>
       <c r="O25" s="25"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
       <c r="V25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
       <c r="C26" s="55"/>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="49" t="s">
         <v>174</v>
       </c>
       <c r="E26" s="34"/>
@@ -2309,59 +2309,59 @@
       </c>
       <c r="N26" s="54"/>
       <c r="O26" s="25"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="23"/>
-      <c r="C27" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>50</v>
+      <c r="C27" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>53</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+      <c r="F27" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
       <c r="K27" s="56" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L27" s="31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="M27" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="N27" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="N27" s="29" t="s">
+        <v>66</v>
       </c>
       <c r="O27" s="25"/>
-      <c r="P27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
+      <c r="P27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
       <c r="V27" s="52"/>
-      <c r="W27" s="27"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-      <c r="AA27" s="27"/>
-      <c r="AB27" s="27"/>
-      <c r="AC27" s="27"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="23"/>
@@ -2380,7 +2380,7 @@
         <v>45791.0</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I28" s="36"/>
       <c r="J28" s="36">
@@ -2397,20 +2397,20 @@
       </c>
       <c r="N28" s="51"/>
       <c r="O28" s="25"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
       <c r="V28" s="52"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="27"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
     </row>
     <row r="29">
       <c r="A29" s="23"/>
@@ -2446,20 +2446,20 @@
       </c>
       <c r="N29" s="51"/>
       <c r="O29" s="25"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
       <c r="V29" s="52"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="27"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="23"/>
@@ -2478,7 +2478,7 @@
         <v>45853.0</v>
       </c>
       <c r="H30" s="34" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I30" s="43"/>
       <c r="J30" s="43">
@@ -2496,19 +2496,19 @@
       <c r="N30" s="51"/>
       <c r="O30" s="25"/>
       <c r="P30" s="64"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="27"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="28"/>
       <c r="V30" s="52"/>
-      <c r="W30" s="27"/>
-      <c r="X30" s="27"/>
-      <c r="Y30" s="27"/>
-      <c r="Z30" s="27"/>
-      <c r="AA30" s="27"/>
-      <c r="AB30" s="27"/>
-      <c r="AC30" s="27"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+      <c r="AC30" s="28"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
       <c r="A31" s="23"/>
@@ -2527,7 +2527,7 @@
         <v>45910.0</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I31" s="43"/>
       <c r="J31" s="43">
@@ -2545,19 +2545,19 @@
       <c r="N31" s="51"/>
       <c r="O31" s="25"/>
       <c r="P31" s="64"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="27"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
       <c r="V31" s="52"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="27"/>
-      <c r="Y31" s="27"/>
-      <c r="Z31" s="27"/>
-      <c r="AA31" s="27"/>
-      <c r="AB31" s="27"/>
-      <c r="AC31" s="27"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+      <c r="AC31" s="28"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="23"/>
@@ -2576,7 +2576,7 @@
         <v>45904.0</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
@@ -2594,19 +2594,19 @@
       <c r="N32" s="51"/>
       <c r="O32" s="25"/>
       <c r="P32" s="64"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
       <c r="V32" s="52"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
-      <c r="AC32" s="27"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="23"/>
@@ -2625,7 +2625,7 @@
         <v>46008.0</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
@@ -2643,19 +2643,19 @@
       <c r="N33" s="51"/>
       <c r="O33" s="25"/>
       <c r="P33" s="64"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="27"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
       <c r="V33" s="52"/>
-      <c r="W33" s="27"/>
-      <c r="X33" s="27"/>
-      <c r="Y33" s="27"/>
-      <c r="Z33" s="27"/>
-      <c r="AA33" s="27"/>
-      <c r="AB33" s="27"/>
-      <c r="AC33" s="27"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="28"/>
+      <c r="AA33" s="28"/>
+      <c r="AB33" s="28"/>
+      <c r="AC33" s="28"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="23"/>
@@ -2674,7 +2674,7 @@
         <v>45930.0</v>
       </c>
       <c r="H34" s="34" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
@@ -2692,19 +2692,19 @@
       <c r="N34" s="51"/>
       <c r="O34" s="25"/>
       <c r="P34" s="64"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="27"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
       <c r="V34" s="52"/>
-      <c r="W34" s="27"/>
-      <c r="X34" s="27"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="27"/>
-      <c r="AA34" s="27"/>
-      <c r="AB34" s="27"/>
-      <c r="AC34" s="27"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="28"/>
+      <c r="AA34" s="28"/>
+      <c r="AB34" s="28"/>
+      <c r="AC34" s="28"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="23"/>
@@ -2723,7 +2723,7 @@
         <v>45968.0</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
@@ -2741,19 +2741,19 @@
       <c r="N35" s="51"/>
       <c r="O35" s="25"/>
       <c r="P35" s="64"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="27"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
       <c r="V35" s="52"/>
-      <c r="W35" s="27"/>
-      <c r="X35" s="27"/>
-      <c r="Y35" s="27"/>
-      <c r="Z35" s="27"/>
-      <c r="AA35" s="27"/>
-      <c r="AB35" s="27"/>
-      <c r="AC35" s="27"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="23"/>
@@ -2772,7 +2772,7 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
@@ -2789,20 +2789,20 @@
       </c>
       <c r="N36" s="51"/>
       <c r="O36" s="25"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="27"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
       <c r="V36" s="52"/>
-      <c r="W36" s="27"/>
-      <c r="X36" s="27"/>
-      <c r="Y36" s="27"/>
-      <c r="Z36" s="27"/>
-      <c r="AA36" s="27"/>
-      <c r="AB36" s="27"/>
-      <c r="AC36" s="27"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="28"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
+      <c r="AC36" s="28"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="23"/>
@@ -2826,20 +2826,20 @@
         <v>15854.78</v>
       </c>
       <c r="O37" s="25"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
       <c r="V37" s="52"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="23"/>
@@ -2863,20 +2863,20 @@
         <v>205</v>
       </c>
       <c r="O38" s="25"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
       <c r="V38" s="52"/>
-      <c r="W38" s="27"/>
-      <c r="X38" s="27"/>
-      <c r="Y38" s="27"/>
-      <c r="Z38" s="27"/>
-      <c r="AA38" s="27"/>
-      <c r="AB38" s="27"/>
-      <c r="AC38" s="27"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="23"/>
@@ -2895,7 +2895,7 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
@@ -2912,20 +2912,20 @@
       </c>
       <c r="N39" s="51"/>
       <c r="O39" s="25"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
       <c r="V39" s="52"/>
-      <c r="W39" s="27"/>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
-      <c r="AA39" s="27"/>
-      <c r="AB39" s="27"/>
-      <c r="AC39" s="27"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="28"/>
+      <c r="AA39" s="28"/>
+      <c r="AB39" s="28"/>
+      <c r="AC39" s="28"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="15"/>
@@ -2942,7 +2942,7 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
@@ -2952,13 +2952,13 @@
         <v>58868.35</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
       </c>
       <c r="N40" s="51"/>
-      <c r="V40" s="4"/>
+      <c r="V40" s="3"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="15"/>
@@ -2966,7 +2966,7 @@
       <c r="C41" s="41"/>
       <c r="K41" s="73"/>
       <c r="M41" s="73"/>
-      <c r="V41" s="4"/>
+      <c r="V41" s="3"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="15"/>
@@ -2974,31 +2974,31 @@
       <c r="C42" s="41"/>
       <c r="K42" s="73"/>
       <c r="M42" s="73"/>
-      <c r="V42" s="4"/>
+      <c r="V42" s="3"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
       <c r="C43" s="41"/>
-      <c r="V43" s="4"/>
+      <c r="V43" s="3"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
       <c r="C44" s="41"/>
-      <c r="V44" s="4"/>
+      <c r="V44" s="3"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
       <c r="C45" s="41"/>
-      <c r="V45" s="4"/>
+      <c r="V45" s="3"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
       <c r="C46" s="41"/>
-      <c r="V46" s="4"/>
+      <c r="V46" s="3"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="15"/>
@@ -3006,7 +3006,7 @@
       <c r="C47" s="55"/>
       <c r="K47" s="73"/>
       <c r="M47" s="73"/>
-      <c r="V47" s="4"/>
+      <c r="V47" s="3"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="15"/>
@@ -3030,7 +3030,7 @@
       <c r="S48" s="74"/>
       <c r="T48" s="74"/>
       <c r="U48" s="74"/>
-      <c r="V48" s="4"/>
+      <c r="V48" s="3"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="15"/>
@@ -7911,11 +7911,11 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="3">
+      <c r="A2" s="5">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>0</v>
+      <c r="L2" s="7" t="s">
+        <v>1</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -7926,31 +7926,31 @@
       <c r="AH2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="11">
         <v>2.5E32</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="13">
         <v>45686.0</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="10">
         <v>12.0</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="10">
         <v>2048.0</v>
       </c>
       <c r="J3" s="14">
@@ -7959,7 +7959,7 @@
       <c r="K3" s="14">
         <v>1000.0</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="10">
         <v>0.0</v>
       </c>
       <c r="AB3" s="2"/>
@@ -7971,31 +7971,31 @@
       <c r="AH3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <v>45762.0</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="10">
         <v>12.0</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="10">
         <v>2048.0</v>
       </c>
       <c r="J4" s="14">
@@ -8004,7 +8004,7 @@
       <c r="K4" s="14">
         <v>52250.04</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="10">
         <v>0.0</v>
       </c>
       <c r="AB4" s="2"/>
@@ -8016,31 +8016,31 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <v>45762.0</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="10">
         <v>12.0</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="10">
         <v>2048.0</v>
       </c>
       <c r="J5" s="14">
@@ -8049,7 +8049,7 @@
       <c r="K5" s="14">
         <v>881914.18</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="10">
         <v>0.0</v>
       </c>
       <c r="AB5" s="2"/>
@@ -8061,31 +8061,31 @@
       <c r="AH5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="A6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>45762.0</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="10">
         <v>12.0</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="10">
         <v>2048.0</v>
       </c>
       <c r="J6" s="14">
@@ -8094,7 +8094,7 @@
       <c r="K6" s="14">
         <v>750000.0</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="10">
         <v>0.0</v>
       </c>
       <c r="AB6" s="2"/>
@@ -8106,32 +8106,32 @@
       <c r="AH6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="13">
+        <v>45763.0</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="10">
+        <v>12.0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>339039.0</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="12">
-        <v>45763.0</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>339039.0</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>44</v>
       </c>
       <c r="J7" s="14">
         <v>949835.78</v>
@@ -8139,7 +8139,7 @@
       <c r="K7" s="14">
         <v>949835.78</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="10">
         <v>0.0</v>
       </c>
       <c r="AB7" s="2"/>
@@ -8151,32 +8151,32 @@
       <c r="AH7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>45763.0</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="10">
         <v>12.0</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>49</v>
+      <c r="I8" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J8" s="14">
         <v>524584.95</v>
@@ -8184,10 +8184,10 @@
       <c r="K8" s="14">
         <v>524584.95</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="10">
         <v>0.0</v>
       </c>
-      <c r="O8" s="29"/>
+      <c r="O8" s="26"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8197,32 +8197,32 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="13">
+        <v>45792.0</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="10">
+        <v>12.0</v>
+      </c>
+      <c r="H9" s="10">
+        <v>339039.0</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="12">
-        <v>45792.0</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>339039.0</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="J9" s="14">
         <v>211614.23</v>
@@ -8230,7 +8230,7 @@
       <c r="K9" s="14">
         <v>211614.23</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="10">
         <v>0.0</v>
       </c>
       <c r="AB9" s="2"/>
@@ -8242,31 +8242,31 @@
       <c r="AH9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>45825.0</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="10">
         <v>12.0</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="10">
         <v>2048.0</v>
       </c>
       <c r="J10" s="14">
@@ -8287,31 +8287,31 @@
       <c r="AH10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>45825.0</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="10">
         <v>12.0</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="10">
         <v>2048.0</v>
       </c>
       <c r="J11" s="14">
@@ -8320,7 +8320,7 @@
       <c r="K11" s="14">
         <v>618154.38</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="10">
         <v>0.01</v>
       </c>
       <c r="AB11" s="2"/>
@@ -8332,32 +8332,32 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="13">
+        <v>45832.0</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="10">
+        <v>12.0</v>
+      </c>
+      <c r="H12" s="10">
+        <v>339039.0</v>
+      </c>
+      <c r="I12" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="12">
-        <v>45832.0</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="8">
-        <v>12.0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>339039.0</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8365,7 +8365,7 @@
       <c r="K12" s="14">
         <v>1600334.09</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="10">
         <v>0.0</v>
       </c>
       <c r="AB12" s="2"/>
@@ -8377,31 +8377,31 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <v>45863.0</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="10">
         <v>12.0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="10">
         <v>2048.0</v>
       </c>
       <c r="J13" s="14">
@@ -8423,32 +8423,32 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <v>45887.0</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="10">
         <v>12.0</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>62</v>
+      <c r="I14" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="J14" s="14">
         <v>968237.39</v>
@@ -8456,7 +8456,7 @@
       <c r="K14" s="14">
         <v>968237.39</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="10">
         <v>0.0</v>
       </c>
       <c r="AB14" s="2"/>
@@ -8468,32 +8468,32 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <v>45924.0</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="10">
         <v>12.0</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>44</v>
+      <c r="I15" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="J15" s="14">
         <v>1011677.95</v>
@@ -8501,7 +8501,7 @@
       <c r="K15" s="14">
         <v>1011677.95</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="10">
         <v>0.0</v>
       </c>
       <c r="AB15" s="2"/>
@@ -8513,31 +8513,31 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="C16" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <v>45929.0</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="10">
         <v>12.0</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="10">
         <v>2048.0</v>
       </c>
       <c r="J16" s="14">
@@ -8558,37 +8558,37 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <v>45930.0</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="10">
         <v>12.0</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="10">
         <v>2048.0</v>
       </c>
       <c r="J17" s="14">
         <v>34065.36</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="10">
         <v>0.0</v>
       </c>
       <c r="L17" s="14">
@@ -8603,32 +8603,32 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="8" t="s">
+      <c r="A18" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="C18" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="10">
         <v>12.0</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>62</v>
+      <c r="I18" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="J18" s="14">
         <v>63746.85</v>
@@ -8636,7 +8636,7 @@
       <c r="K18" s="14">
         <v>63746.85</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="10">
         <v>0.0</v>
       </c>
       <c r="AB18" s="2"/>
@@ -8648,32 +8648,32 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="8" t="s">
+      <c r="A19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="10">
         <v>12.0</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>75</v>
+      <c r="I19" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8681,7 +8681,7 @@
       <c r="K19" s="14">
         <v>947931.1</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="10">
         <v>0.0</v>
       </c>
       <c r="AB19" s="2"/>
@@ -8693,31 +8693,31 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="C20" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="10">
         <v>12.0</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="10">
         <v>2048.0</v>
       </c>
       <c r="J20" s="14">
@@ -8726,7 +8726,7 @@
       <c r="K20" s="14">
         <v>259790.57</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="10">
         <v>0.0</v>
       </c>
       <c r="AB20" s="2"/>
@@ -8738,31 +8738,31 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="A21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <v>45938.0</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="10">
         <v>12.0</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="10">
         <v>2048.0</v>
       </c>
       <c r="J21" s="14">
@@ -8771,7 +8771,7 @@
       <c r="K21" s="14">
         <v>170479.3</v>
       </c>
-      <c r="L21" s="8">
+      <c r="L21" s="10">
         <v>0.0</v>
       </c>
       <c r="AB21" s="2"/>
@@ -8783,31 +8783,31 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="A22" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="48">
         <v>45953.0</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="10">
         <v>12.0</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="10">
         <v>2000.0</v>
       </c>
       <c r="J22" s="14">
@@ -8828,32 +8828,32 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="48">
         <v>45953.0</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="10">
         <v>12.0</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>117</v>
+      <c r="I23" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -8861,7 +8861,7 @@
       <c r="K23" s="14">
         <v>1000001.64</v>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="10">
         <v>0.0</v>
       </c>
       <c r="AB23" s="2"/>
@@ -8873,31 +8873,31 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="8" t="s">
+      <c r="A24" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="48">
         <v>45953.0</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="10">
         <v>12.0</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="10">
         <v>2048.0</v>
       </c>
       <c r="J24" s="14">
@@ -8906,7 +8906,7 @@
       <c r="K24" s="14">
         <v>68405.66</v>
       </c>
-      <c r="L24" s="8">
+      <c r="L24" s="10">
         <v>0.0</v>
       </c>
       <c r="AB24" s="2"/>
@@ -8918,32 +8918,32 @@
       <c r="AH24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="48">
         <v>45975.0</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="10">
         <v>12.0</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>117</v>
+      <c r="I25" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -8951,7 +8951,7 @@
       <c r="K25" s="14">
         <v>1157673.06</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="10">
         <v>0.0</v>
       </c>
       <c r="AB25" s="2"/>
@@ -8963,31 +8963,31 @@
       <c r="AH25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="8" t="s">
+      <c r="A26" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="48">
         <v>45989.0</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="10">
         <v>12.0</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="10">
         <v>2048.0</v>
       </c>
       <c r="J26" s="14">
@@ -8996,7 +8996,7 @@
       <c r="K26" s="14">
         <v>34065.36</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="10">
         <v>0.0</v>
       </c>
       <c r="AB26" s="2"/>
@@ -9008,31 +9008,31 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="A27" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="13">
         <v>46104.0</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="10">
         <v>12.0</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="10">
         <v>2048.0</v>
       </c>
       <c r="J27" s="14">
@@ -9053,37 +9053,37 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="13">
         <v>46120.0</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="10">
         <v>12.0</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>49</v>
+      <c r="I28" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="J28" s="14">
         <v>1912292.52</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="10">
         <v>0.0</v>
       </c>
       <c r="L28" s="14">
@@ -9098,37 +9098,37 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="13">
         <v>46196.0</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="10">
         <v>12.0</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="10">
         <v>2048.0</v>
       </c>
       <c r="J29" s="14">
         <v>1496713.48</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="10">
         <v>0.0</v>
       </c>
       <c r="L29" s="14">
@@ -9143,37 +9143,37 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="A30" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="13">
         <v>46205.0</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="10">
         <v>12.0</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>44</v>
+      <c r="I30" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="J30" s="14">
         <v>624166.14</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="10">
         <v>0.0</v>
       </c>
       <c r="L30" s="14">
@@ -9188,37 +9188,37 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="13">
         <v>46205.0</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="10">
         <v>12.0</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>117</v>
+      <c r="I31" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="J31" s="14">
         <v>18462.36</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="10">
         <v>0.0</v>
       </c>
       <c r="L31" s="14">
@@ -9233,37 +9233,37 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>151</v>
+      <c r="A32" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>149</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="13">
         <v>46213.0</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="10">
         <v>12.0</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>117</v>
+      <c r="I32" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="J32" s="14">
         <v>1530656.62</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="10">
         <v>0.0</v>
       </c>
       <c r="L32" s="14">
@@ -9278,37 +9278,37 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>141</v>
+      <c r="A33" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="D33" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="13">
         <v>46227.0</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="10">
         <v>12.0</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I33" s="8">
+      <c r="I33" s="10">
         <v>2048.0</v>
       </c>
       <c r="J33" s="14">
         <v>173846.38</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K33" s="10">
         <v>0.0</v>
       </c>
       <c r="L33" s="14">

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -81,33 +81,33 @@
     <t>Ação</t>
   </si>
   <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>Moeda</t>
+  </si>
+  <si>
+    <t>Valor Total do Contrato</t>
+  </si>
+  <si>
+    <t>Valor a Empenhar</t>
+  </si>
+  <si>
     <t>2025NE000369</t>
   </si>
   <si>
-    <t>PAG</t>
+    <t>Valor Empenhado</t>
   </si>
   <si>
     <t>C25516</t>
   </si>
   <si>
-    <t>Moeda</t>
+    <t>Valor Liquidado</t>
   </si>
   <si>
     <t>25E0387</t>
   </si>
   <si>
-    <t>Valor Total do Contrato</t>
-  </si>
-  <si>
-    <t>Valor a Empenhar</t>
-  </si>
-  <si>
-    <t>Valor Empenhado</t>
-  </si>
-  <si>
-    <t>Valor Liquidado</t>
-  </si>
-  <si>
     <t>Saldo (Valor a Faturar)</t>
   </si>
   <si>
@@ -123,21 +123,21 @@
     <t>Editar</t>
   </si>
   <si>
+    <t>005/CELOG-PAMALS/2025</t>
+  </si>
+  <si>
+    <t>CELOG</t>
+  </si>
+  <si>
+    <t>PAMALS</t>
+  </si>
+  <si>
     <t>2025NE000371</t>
   </si>
   <si>
-    <t>005/CELOG-PAMALS/2025</t>
-  </si>
-  <si>
     <t>25E0389</t>
   </si>
   <si>
-    <t>CELOG</t>
-  </si>
-  <si>
-    <t>PAMALS</t>
-  </si>
-  <si>
     <t>Vigente</t>
   </si>
   <si>
@@ -150,6 +150,9 @@
     <t>R$</t>
   </si>
   <si>
+    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
+  </si>
+  <si>
     <t>2025NE000413</t>
   </si>
   <si>
@@ -162,9 +165,6 @@
     <t>20SP</t>
   </si>
   <si>
-    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
-  </si>
-  <si>
     <t>2025NE000414</t>
   </si>
   <si>
@@ -180,55 +180,61 @@
     <t>Módulo</t>
   </si>
   <si>
+    <t>Referência</t>
+  </si>
+  <si>
+    <t>Nº recibo</t>
+  </si>
+  <si>
+    <t>Nº</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
     <t>2025NE000559</t>
   </si>
   <si>
     <t>C25545</t>
   </si>
   <si>
+    <t>Empenho</t>
+  </si>
+  <si>
     <t>25E0524</t>
   </si>
   <si>
-    <t>Referência</t>
-  </si>
-  <si>
-    <t>Nº recibo</t>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>Valor das Nfs</t>
   </si>
   <si>
     <t>20X7</t>
   </si>
   <si>
-    <t>Nº</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Empenho</t>
+    <t>Ordem de Pagamento</t>
+  </si>
+  <si>
+    <t>Faturado</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
   <si>
     <t>2025NE000770</t>
   </si>
   <si>
-    <t>Observações</t>
-  </si>
-  <si>
     <t>25E0731</t>
   </si>
   <si>
-    <t>Vencimento</t>
-  </si>
-  <si>
-    <t>Valor das Nfs</t>
-  </si>
-  <si>
-    <t>Ordem de Pagamento</t>
-  </si>
-  <si>
-    <t>Faturado</t>
-  </si>
-  <si>
-    <t>Pendente</t>
+    <t>FEV/25</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>2025NE000774</t>
@@ -237,7 +243,10 @@
     <t>25E0737</t>
   </si>
   <si>
-    <t>FEV/25</t>
+    <t xml:space="preserve">2025NE000369 </t>
+  </si>
+  <si>
+    <t>2025NP001980</t>
   </si>
   <si>
     <t>2025NE000843</t>
@@ -249,22 +258,22 @@
     <t>25E0787</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>219C</t>
   </si>
   <si>
-    <t xml:space="preserve">2025NE000369 </t>
-  </si>
-  <si>
     <t>2025NE001065</t>
   </si>
   <si>
     <t>25E0999</t>
   </si>
   <si>
-    <t>2025NP001980</t>
+    <t>MAR/25</t>
+  </si>
+  <si>
+    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
+  </si>
+  <si>
+    <t>2025NP001979</t>
   </si>
   <si>
     <t>2025NE001200</t>
@@ -279,22 +288,28 @@
     <t>2025NE001598</t>
   </si>
   <si>
+    <t>ABR/25</t>
+  </si>
+  <si>
     <t>C25814</t>
   </si>
   <si>
     <t>25E1446</t>
   </si>
   <si>
+    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
+  </si>
+  <si>
+    <t>2025NP002341</t>
+  </si>
+  <si>
     <t>2025NE001627</t>
   </si>
   <si>
     <t>25E1475</t>
   </si>
   <si>
-    <t>MAR/25</t>
-  </si>
-  <si>
-    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
+    <t>MAI/25</t>
   </si>
   <si>
     <t>2025NE001629</t>
@@ -306,61 +321,16 @@
     <t>25E1477</t>
   </si>
   <si>
-    <t>2025NP001979</t>
+    <t>2025NP002884</t>
   </si>
   <si>
     <t>2025NE001687</t>
   </si>
   <si>
+    <t>JUN/25</t>
+  </si>
+  <si>
     <t>25E1535</t>
-  </si>
-  <si>
-    <t>ABR/25</t>
-  </si>
-  <si>
-    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
-  </si>
-  <si>
-    <t>2025NE001688</t>
-  </si>
-  <si>
-    <t>25E1536</t>
-  </si>
-  <si>
-    <t>2025NP002341</t>
-  </si>
-  <si>
-    <t>2025NE001689</t>
-  </si>
-  <si>
-    <t>25E1537</t>
-  </si>
-  <si>
-    <t>MAI/25</t>
-  </si>
-  <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
-  </si>
-  <si>
-    <t>2025NP002884</t>
-  </si>
-  <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
-  </si>
-  <si>
-    <t>JUN/25</t>
-  </si>
-  <si>
-    <t>2025NE001828</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -369,22 +339,13 @@
 2025NE000774</t>
   </si>
   <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
-    <t>20YJ</t>
-  </si>
-  <si>
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
   </si>
   <si>
     <t>JUL/25</t>
@@ -393,59 +354,125 @@
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
+    <t>2025NE001689</t>
   </si>
   <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>25E2021</t>
+    <t>25E1537</t>
   </si>
   <si>
     <t>AGO/25</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
   </si>
   <si>
     <t>2025NP004558</t>
   </si>
   <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
-  </si>
-  <si>
     <t>SET/25</t>
+  </si>
+  <si>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
   </si>
   <si>
     <t>2025NE001688 
 2025NE001828</t>
   </si>
   <si>
+    <t>2025NP004897</t>
+  </si>
+  <si>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>OUT/25</t>
+  </si>
+  <si>
+    <t>20YJ</t>
+  </si>
+  <si>
+    <t>2025NE001688, 2025NE001828, 2025NE002200</t>
+  </si>
+  <si>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>2025NP004932</t>
+  </si>
+  <si>
+    <t>25E1669</t>
+  </si>
+  <si>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
+  </si>
+  <si>
+    <t>NOV/25</t>
+  </si>
+  <si>
+    <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
+  </si>
+  <si>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
+  </si>
+  <si>
+    <t>2026NP400440</t>
+  </si>
+  <si>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
+  </si>
+  <si>
+    <t>DEZ/25</t>
+  </si>
+  <si>
+    <t>2025NE001065, 2025NE002200</t>
+  </si>
+  <si>
+    <t>2026NP400412</t>
+  </si>
+  <si>
     <t>2026NE000388</t>
   </si>
   <si>
     <t>C26193</t>
   </si>
   <si>
-    <t>2025NP004897</t>
-  </si>
-  <si>
     <t>26E0375</t>
   </si>
   <si>
-    <t>OUT/25</t>
+    <t>JAN/26</t>
   </si>
   <si>
     <t>2026NE000748</t>
@@ -457,10 +484,7 @@
     <t>26E0709</t>
   </si>
   <si>
-    <t>2025NE001688, 2025NE001828, 2025NE002200</t>
-  </si>
-  <si>
-    <t>2025NP004932</t>
+    <t>2026NP401035</t>
   </si>
   <si>
     <t>2026NE000816</t>
@@ -472,22 +496,25 @@
     <t>26E0776</t>
   </si>
   <si>
-    <t>NOV/25</t>
+    <t>FEV/26</t>
+  </si>
+  <si>
+    <t>2025NE001627, 2025NE001629, 2025NE001823</t>
   </si>
   <si>
     <t>2026NE000817</t>
   </si>
   <si>
-    <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
-  </si>
-  <si>
     <t>C26326</t>
   </si>
   <si>
     <t>26E0777</t>
   </si>
   <si>
-    <t>2026NP400440</t>
+    <t>2026NP402272</t>
+  </si>
+  <si>
+    <t>MAR/26</t>
   </si>
   <si>
     <t>2026NE000842</t>
@@ -496,46 +523,19 @@
     <t>26E0803</t>
   </si>
   <si>
-    <t>DEZ/25</t>
+    <t>2025NE000770, 2025NE001627</t>
+  </si>
+  <si>
+    <t>R$ 1.350.542,52</t>
+  </si>
+  <si>
+    <t>2026NP401762</t>
   </si>
   <si>
     <t>2026NE000944</t>
   </si>
   <si>
-    <t>2025NE001065, 2025NE002200</t>
-  </si>
-  <si>
     <t>26E0906</t>
-  </si>
-  <si>
-    <t>2026NP400412</t>
-  </si>
-  <si>
-    <t>JAN/26</t>
-  </si>
-  <si>
-    <t>2026NP401035</t>
-  </si>
-  <si>
-    <t>FEV/26</t>
-  </si>
-  <si>
-    <t>2025NE001627, 2025NE001629, 2025NE001823</t>
-  </si>
-  <si>
-    <t>2026NP402272</t>
-  </si>
-  <si>
-    <t>MAR/26</t>
-  </si>
-  <si>
-    <t>2025NE000770, 2025NE001627</t>
-  </si>
-  <si>
-    <t>R$ 1.350.542,52</t>
-  </si>
-  <si>
-    <t>2026NP401762</t>
   </si>
   <si>
     <t>ABR/26</t>
@@ -715,13 +715,13 @@
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Century Gothic"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -931,28 +931,28 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -967,14 +967,14 @@
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="6" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -993,14 +993,14 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1015,13 +1015,13 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1030,7 +1030,7 @@
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1481,22 +1481,22 @@
         <v>16</v>
       </c>
       <c r="K4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="16" t="s">
+      <c r="M4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="O4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="17" t="s">
+      <c r="P4" s="17" t="s">
         <v>24</v>
-      </c>
-      <c r="P4" s="17" t="s">
-        <v>25</v>
       </c>
       <c r="Q4" s="17" t="s">
         <v>26</v>
@@ -1520,16 +1520,16 @@
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>34</v>
-      </c>
       <c r="F5" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1565,7 +1565,7 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="V5" s="3"/>
     </row>
@@ -1587,54 +1587,54 @@
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
-      <c r="L7" s="27"/>
+      <c r="L7" s="26"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="28"/>
+      <c r="P7" s="27"/>
       <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="29" t="s">
+      <c r="H8" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="29" t="s">
+      <c r="I8" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="J8" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="K8" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="L8" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="M8" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="N8" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M8" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="O8" s="29"/>
-      <c r="P8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="27"/>
       <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
@@ -1644,10 +1644,10 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F9" s="35">
         <v>594.0</v>
@@ -1656,7 +1656,7 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I9" s="36"/>
       <c r="J9" s="36">
@@ -1666,26 +1666,26 @@
         <v>748504.24</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="M9" s="39">
+        <v>72</v>
+      </c>
+      <c r="M9" s="38">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
-      <c r="N9" s="40"/>
+      <c r="N9" s="39"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="28"/>
+      <c r="P9" s="27"/>
       <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="41"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="33" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F10" s="35">
         <v>620.0</v>
@@ -1694,7 +1694,7 @@
         <v>45775.0</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I10" s="36"/>
       <c r="J10" s="36">
@@ -1704,26 +1704,26 @@
         <v>1110378.24</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="M10" s="39">
+        <v>81</v>
+      </c>
+      <c r="M10" s="38">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
       <c r="N10" s="42"/>
       <c r="O10" s="25"/>
-      <c r="P10" s="28"/>
+      <c r="P10" s="27"/>
       <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="41"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="33" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F11" s="35">
         <v>634.0</v>
@@ -1732,7 +1732,7 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36">
@@ -1742,25 +1742,25 @@
         <v>974557.12</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="M11" s="39">
+        <v>90</v>
+      </c>
+      <c r="M11" s="38">
         <v>974557.12</v>
       </c>
       <c r="N11" s="42"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="28"/>
+      <c r="P11" s="27"/>
       <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="41"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="33" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F12" s="34">
         <v>660.0</v>
@@ -1769,7 +1769,7 @@
         <v>45856.0</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36">
@@ -1779,25 +1779,25 @@
         <v>1402001.34</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="M12" s="39">
+        <v>97</v>
+      </c>
+      <c r="M12" s="38">
         <v>1402001.34</v>
       </c>
       <c r="N12" s="47"/>
       <c r="O12" s="25"/>
-      <c r="P12" s="28"/>
+      <c r="P12" s="27"/>
       <c r="V12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="49" t="s">
-        <v>109</v>
+      <c r="C13" s="40"/>
+      <c r="D13" s="48" t="s">
+        <v>99</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F13" s="35">
         <v>661.0</v>
@@ -1806,7 +1806,7 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="I13" s="43"/>
       <c r="J13" s="43">
@@ -1816,25 +1816,25 @@
         <v>1223702.3</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="M13" s="39">
+        <v>102</v>
+      </c>
+      <c r="M13" s="38">
         <v>1223702.3</v>
       </c>
       <c r="N13" s="47"/>
       <c r="O13" s="25"/>
-      <c r="P13" s="50"/>
+      <c r="P13" s="49"/>
       <c r="V13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="49" t="s">
-        <v>118</v>
+      <c r="C14" s="40"/>
+      <c r="D14" s="48" t="s">
+        <v>105</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F14" s="34">
         <v>688.0</v>
@@ -1843,7 +1843,7 @@
         <v>45901.0</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="I14" s="43"/>
       <c r="J14" s="43">
@@ -1853,25 +1853,25 @@
         <v>1011677.95</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="M14" s="39">
+        <v>108</v>
+      </c>
+      <c r="M14" s="38">
         <v>1011677.95</v>
       </c>
       <c r="N14" s="42"/>
       <c r="O14" s="25"/>
-      <c r="P14" s="28"/>
+      <c r="P14" s="27"/>
       <c r="V14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="49" t="s">
-        <v>124</v>
+      <c r="C15" s="40"/>
+      <c r="D15" s="48" t="s">
+        <v>110</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F15" s="34">
         <v>696.0</v>
@@ -1880,7 +1880,7 @@
         <v>45923.0</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I15" s="43"/>
       <c r="J15" s="43">
@@ -1890,9 +1890,9 @@
         <v>896744.06</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="M15" s="39">
+        <v>113</v>
+      </c>
+      <c r="M15" s="38">
         <v>896744.06</v>
       </c>
       <c r="N15" s="47"/>
@@ -1902,12 +1902,12 @@
     <row r="16">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="49" t="s">
-        <v>131</v>
+      <c r="C16" s="40"/>
+      <c r="D16" s="48" t="s">
+        <v>114</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F16" s="34">
         <v>704.0</v>
@@ -1916,7 +1916,7 @@
         <v>45957.0</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I16" s="43"/>
       <c r="J16" s="43">
@@ -1926,9 +1926,9 @@
         <v>919329.06</v>
       </c>
       <c r="L16" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="M16" s="39">
+        <v>119</v>
+      </c>
+      <c r="M16" s="38">
         <v>919329.06</v>
       </c>
       <c r="N16" s="42"/>
@@ -1938,9 +1938,9 @@
     <row r="17">
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="49" t="s">
-        <v>137</v>
+      <c r="C17" s="40"/>
+      <c r="D17" s="48" t="s">
+        <v>123</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="34">
@@ -1950,7 +1950,7 @@
         <v>45972.0</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="I17" s="34"/>
       <c r="J17" s="43">
@@ -1960,9 +1960,9 @@
         <v>1157009.26</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="M17" s="39">
+        <v>127</v>
+      </c>
+      <c r="M17" s="38">
         <v>1157009.26</v>
       </c>
       <c r="N17" s="51"/>
@@ -1972,12 +1972,12 @@
     <row r="18">
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="49" t="s">
-        <v>146</v>
+      <c r="C18" s="40"/>
+      <c r="D18" s="48" t="s">
+        <v>132</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F18" s="34">
         <v>728.0</v>
@@ -1986,7 +1986,7 @@
         <v>46008.0</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="I18" s="34"/>
       <c r="J18" s="43">
@@ -1996,28 +1996,28 @@
         <v>1214597.952</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>151</v>
-      </c>
-      <c r="M18" s="39">
+        <v>136</v>
+      </c>
+      <c r="M18" s="38">
         <v>1214597.952</v>
       </c>
       <c r="N18" s="51"/>
       <c r="O18" s="25"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
       <c r="V18" s="52"/>
     </row>
     <row r="19">
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="49" t="s">
-        <v>154</v>
+      <c r="C19" s="40"/>
+      <c r="D19" s="48" t="s">
+        <v>140</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F19" s="34">
         <v>278.0</v>
@@ -2026,7 +2026,7 @@
         <v>46042.0</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="I19" s="43"/>
       <c r="J19" s="43">
@@ -2036,25 +2036,25 @@
         <v>967082.09</v>
       </c>
       <c r="L19" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="M19" s="39">
+        <v>142</v>
+      </c>
+      <c r="M19" s="38">
         <v>967082.09</v>
       </c>
       <c r="N19" s="51"/>
       <c r="O19" s="25"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
       <c r="V19" s="52"/>
     </row>
     <row r="20">
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="49" t="s">
-        <v>159</v>
+      <c r="C20" s="40"/>
+      <c r="D20" s="48" t="s">
+        <v>146</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34">
@@ -2064,7 +2064,7 @@
         <v>46078.0</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I20" s="43"/>
       <c r="J20" s="43">
@@ -2074,25 +2074,25 @@
         <v>719561.08</v>
       </c>
       <c r="L20" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="M20" s="39">
+        <v>150</v>
+      </c>
+      <c r="M20" s="38">
         <v>719561.08</v>
       </c>
       <c r="N20" s="51"/>
       <c r="O20" s="25"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
       <c r="V20" s="52"/>
     </row>
     <row r="21">
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="49" t="s">
-        <v>161</v>
+      <c r="C21" s="40"/>
+      <c r="D21" s="48" t="s">
+        <v>154</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34">
@@ -2102,7 +2102,7 @@
         <v>46094.0</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I21" s="43"/>
       <c r="J21" s="43">
@@ -2112,25 +2112,25 @@
         <v>885881.08</v>
       </c>
       <c r="L21" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="M21" s="39">
+        <v>159</v>
+      </c>
+      <c r="M21" s="38">
         <v>885881.08</v>
       </c>
       <c r="N21" s="51"/>
       <c r="O21" s="25"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="28"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
       <c r="V21" s="52"/>
     </row>
     <row r="22">
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="49" t="s">
-        <v>164</v>
+      <c r="C22" s="40"/>
+      <c r="D22" s="48" t="s">
+        <v>160</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="34">
@@ -2140,34 +2140,34 @@
         <v>46128.0</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I22" s="43"/>
       <c r="J22" s="43">
         <v>46164.0</v>
       </c>
       <c r="K22" s="45" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L22" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="M22" s="39" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+      <c r="M22" s="38" t="s">
+        <v>164</v>
       </c>
       <c r="N22" s="51"/>
       <c r="O22" s="25"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
       <c r="V22" s="52"/>
     </row>
     <row r="23">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="49" t="s">
+      <c r="C23" s="40"/>
+      <c r="D23" s="48" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="34"/>
@@ -2188,24 +2188,24 @@
         <v>1108954.4358333333</v>
       </c>
       <c r="L23" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="M23" s="39">
+        <v>159</v>
+      </c>
+      <c r="M23" s="38">
         <v>1108954.4358333333</v>
       </c>
       <c r="N23" s="53"/>
       <c r="O23" s="25"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
       <c r="V23" s="52"/>
     </row>
     <row r="24">
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="49" t="s">
+      <c r="C24" s="40"/>
+      <c r="D24" s="48" t="s">
         <v>170</v>
       </c>
       <c r="E24" s="34"/>
@@ -2228,22 +2228,22 @@
       <c r="L24" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="M24" s="39">
+      <c r="M24" s="38">
         <v>218206.1</v>
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="25"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
       <c r="V24" s="52"/>
     </row>
     <row r="25">
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="49" t="s">
+      <c r="C25" s="40"/>
+      <c r="D25" s="48" t="s">
         <v>172</v>
       </c>
       <c r="E25" s="34"/>
@@ -2266,22 +2266,22 @@
       <c r="L25" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="M25" s="39">
+      <c r="M25" s="38">
         <v>1549250.84</v>
       </c>
       <c r="N25" s="54"/>
       <c r="O25" s="25"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
       <c r="V25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
       <c r="C26" s="55"/>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="48" t="s">
         <v>174</v>
       </c>
       <c r="E26" s="34"/>
@@ -2304,64 +2304,64 @@
       <c r="L26" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="M26" s="39" t="s">
+      <c r="M26" s="38" t="s">
         <v>176</v>
       </c>
       <c r="N26" s="54"/>
       <c r="O26" s="25"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="23"/>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="29" t="s">
-        <v>53</v>
+      <c r="D27" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
       <c r="K27" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="M27" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="L27" s="31" t="s">
+      <c r="N27" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="M27" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="N27" s="29" t="s">
-        <v>66</v>
-      </c>
       <c r="O27" s="25"/>
-      <c r="P27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
+      <c r="P27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
       <c r="V27" s="52"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="28"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="28"/>
-      <c r="AB27" s="28"/>
-      <c r="AC27" s="28"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="23"/>
@@ -2380,7 +2380,7 @@
         <v>45791.0</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I28" s="36"/>
       <c r="J28" s="36">
@@ -2397,25 +2397,25 @@
       </c>
       <c r="N28" s="51"/>
       <c r="O28" s="25"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
       <c r="V28" s="52"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="28"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="28"/>
-      <c r="AC28" s="28"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
     </row>
     <row r="29">
       <c r="A29" s="23"/>
       <c r="B29" s="23"/>
-      <c r="C29" s="41"/>
+      <c r="C29" s="40"/>
       <c r="D29" s="58" t="s">
         <v>180</v>
       </c>
@@ -2441,30 +2441,30 @@
       <c r="L29" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="M29" s="39">
+      <c r="M29" s="38">
         <v>112720.77</v>
       </c>
       <c r="N29" s="51"/>
       <c r="O29" s="25"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
       <c r="V29" s="52"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
-      <c r="C30" s="41"/>
+      <c r="C30" s="40"/>
       <c r="D30" s="61" t="s">
         <v>183</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>45853.0</v>
       </c>
       <c r="H30" s="34" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I30" s="43"/>
       <c r="J30" s="43">
@@ -2490,30 +2490,30 @@
       <c r="L30" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="M30" s="39">
+      <c r="M30" s="38">
         <v>378307.61</v>
       </c>
       <c r="N30" s="51"/>
       <c r="O30" s="25"/>
       <c r="P30" s="64"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="28"/>
-      <c r="U30" s="28"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
       <c r="V30" s="52"/>
-      <c r="W30" s="28"/>
-      <c r="X30" s="28"/>
-      <c r="Y30" s="28"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="28"/>
-      <c r="AB30" s="28"/>
-      <c r="AC30" s="28"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="27"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="27"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
       <c r="A31" s="23"/>
       <c r="B31" s="23"/>
-      <c r="C31" s="41"/>
+      <c r="C31" s="40"/>
       <c r="D31" s="61" t="s">
         <v>186</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>45910.0</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I31" s="43"/>
       <c r="J31" s="43">
@@ -2539,30 +2539,30 @@
       <c r="L31" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="M31" s="39">
+      <c r="M31" s="38">
         <v>3315.04710000003</v>
       </c>
       <c r="N31" s="51"/>
       <c r="O31" s="25"/>
       <c r="P31" s="64"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
       <c r="V31" s="52"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="28"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="28"/>
-      <c r="AC31" s="28"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="27"/>
+      <c r="AB31" s="27"/>
+      <c r="AC31" s="27"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="23"/>
       <c r="B32" s="23"/>
-      <c r="C32" s="41"/>
+      <c r="C32" s="40"/>
       <c r="D32" s="61" t="s">
         <v>188</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>45904.0</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
@@ -2588,30 +2588,30 @@
       <c r="L32" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="M32" s="39">
+      <c r="M32" s="38">
         <v>198332.75</v>
       </c>
       <c r="N32" s="51"/>
       <c r="O32" s="25"/>
       <c r="P32" s="64"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
       <c r="V32" s="52"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="27"/>
+      <c r="AB32" s="27"/>
+      <c r="AC32" s="27"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="23"/>
       <c r="B33" s="23"/>
-      <c r="C33" s="41"/>
+      <c r="C33" s="40"/>
       <c r="D33" s="61" t="s">
         <v>190</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>46008.0</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
@@ -2643,24 +2643,24 @@
       <c r="N33" s="51"/>
       <c r="O33" s="25"/>
       <c r="P33" s="64"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="27"/>
       <c r="V33" s="52"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="28"/>
-      <c r="Y33" s="28"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="28"/>
-      <c r="AB33" s="28"/>
-      <c r="AC33" s="28"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27"/>
+      <c r="Y33" s="27"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="27"/>
+      <c r="AB33" s="27"/>
+      <c r="AC33" s="27"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="23"/>
-      <c r="C34" s="41"/>
+      <c r="C34" s="40"/>
       <c r="D34" s="61" t="s">
         <v>193</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>45930.0</v>
       </c>
       <c r="H34" s="34" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
@@ -2692,24 +2692,24 @@
       <c r="N34" s="51"/>
       <c r="O34" s="25"/>
       <c r="P34" s="64"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="27"/>
       <c r="V34" s="52"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="28"/>
-      <c r="Y34" s="28"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="28"/>
-      <c r="AB34" s="28"/>
-      <c r="AC34" s="28"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="27"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="27"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="23"/>
-      <c r="C35" s="41"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="61" t="s">
         <v>197</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>45968.0</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
@@ -2741,24 +2741,24 @@
       <c r="N35" s="51"/>
       <c r="O35" s="25"/>
       <c r="P35" s="64"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="27"/>
       <c r="V35" s="52"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="28"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="27"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="27"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="23"/>
-      <c r="C36" s="41"/>
+      <c r="C36" s="40"/>
       <c r="D36" s="61" t="s">
         <v>200</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
@@ -2784,30 +2784,30 @@
       <c r="L36" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="M36" s="39">
+      <c r="M36" s="38">
         <v>11372.9</v>
       </c>
       <c r="N36" s="51"/>
       <c r="O36" s="25"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="27"/>
       <c r="V36" s="52"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
-      <c r="AC36" s="28"/>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
+      <c r="Z36" s="27"/>
+      <c r="AA36" s="27"/>
+      <c r="AB36" s="27"/>
+      <c r="AC36" s="27"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
-      <c r="C37" s="41"/>
+      <c r="C37" s="40"/>
       <c r="D37" s="61" t="s">
         <v>202</v>
       </c>
@@ -2821,25 +2821,25 @@
       <c r="J37" s="69"/>
       <c r="K37" s="45"/>
       <c r="L37" s="34"/>
-      <c r="M37" s="39"/>
+      <c r="M37" s="38"/>
       <c r="N37" s="51">
         <v>15854.78</v>
       </c>
       <c r="O37" s="25"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
       <c r="V37" s="52"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="23"/>
@@ -2858,25 +2858,25 @@
       <c r="J38" s="69"/>
       <c r="K38" s="45"/>
       <c r="L38" s="34"/>
-      <c r="M38" s="39"/>
+      <c r="M38" s="38"/>
       <c r="N38" s="51" t="s">
         <v>205</v>
       </c>
       <c r="O38" s="25"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
       <c r="V38" s="52"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
-      <c r="Y38" s="28"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
-      <c r="AB38" s="28"/>
-      <c r="AC38" s="28"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27"/>
+      <c r="Y38" s="27"/>
+      <c r="Z38" s="27"/>
+      <c r="AA38" s="27"/>
+      <c r="AB38" s="27"/>
+      <c r="AC38" s="27"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="23"/>
@@ -2895,7 +2895,7 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
@@ -2912,25 +2912,25 @@
       </c>
       <c r="N39" s="51"/>
       <c r="O39" s="25"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27"/>
       <c r="V39" s="52"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
+      <c r="W39" s="27"/>
+      <c r="X39" s="27"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="27"/>
+      <c r="AA39" s="27"/>
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="27"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
-      <c r="C40" s="41"/>
+      <c r="C40" s="40"/>
       <c r="D40" s="61" t="s">
         <v>208</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
@@ -2952,7 +2952,7 @@
         <v>58868.35</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
@@ -2963,7 +2963,7 @@
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
-      <c r="C41" s="41"/>
+      <c r="C41" s="40"/>
       <c r="K41" s="73"/>
       <c r="M41" s="73"/>
       <c r="V41" s="3"/>
@@ -2971,7 +2971,7 @@
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
-      <c r="C42" s="41"/>
+      <c r="C42" s="40"/>
       <c r="K42" s="73"/>
       <c r="M42" s="73"/>
       <c r="V42" s="3"/>
@@ -2979,25 +2979,25 @@
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
-      <c r="C43" s="41"/>
+      <c r="C43" s="40"/>
       <c r="V43" s="3"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
-      <c r="C44" s="41"/>
+      <c r="C44" s="40"/>
       <c r="V44" s="3"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
-      <c r="C45" s="41"/>
+      <c r="C45" s="40"/>
       <c r="V45" s="3"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
-      <c r="C46" s="41"/>
+      <c r="C46" s="40"/>
       <c r="V46" s="3"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
@@ -8017,13 +8017,13 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>4</v>
@@ -8062,13 +8062,13 @@
     </row>
     <row r="6">
       <c r="A6" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>4</v>
@@ -8107,13 +8107,13 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>4</v>
@@ -8131,7 +8131,7 @@
         <v>339039.0</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" s="14">
         <v>949835.78</v>
@@ -8187,7 +8187,7 @@
       <c r="L8" s="10">
         <v>0.0</v>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="29"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8198,13 +8198,13 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>4</v>
@@ -8222,7 +8222,7 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J9" s="14">
         <v>211614.23</v>
@@ -8243,13 +8243,13 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>4</v>
@@ -8288,13 +8288,13 @@
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>4</v>
@@ -8333,13 +8333,13 @@
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>4</v>
@@ -8357,7 +8357,7 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8378,13 +8378,13 @@
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>4</v>
@@ -8413,7 +8413,7 @@
       <c r="L13" s="14">
         <v>0.0</v>
       </c>
-      <c r="M13" s="38"/>
+      <c r="M13" s="41"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8424,13 +8424,13 @@
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>4</v>
@@ -8448,7 +8448,7 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J14" s="14">
         <v>968237.39</v>
@@ -8469,13 +8469,13 @@
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>4</v>
@@ -8493,7 +8493,7 @@
         <v>339039.0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J15" s="14">
         <v>1011677.95</v>
@@ -8514,13 +8514,13 @@
     </row>
     <row r="16">
       <c r="A16" s="10" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>4</v>
@@ -8559,13 +8559,13 @@
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>4</v>
@@ -8604,13 +8604,13 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>4</v>
@@ -8628,7 +8628,7 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J18" s="14">
         <v>63746.85</v>
@@ -8649,13 +8649,13 @@
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>4</v>
@@ -8673,7 +8673,7 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8694,13 +8694,13 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>4</v>
@@ -8739,13 +8739,13 @@
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>4</v>
@@ -8784,18 +8784,18 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="50">
         <v>45953.0</v>
       </c>
       <c r="F22" s="10" t="s">
@@ -8829,18 +8829,18 @@
     </row>
     <row r="23">
       <c r="A23" s="10" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="48">
+      <c r="E23" s="50">
         <v>45953.0</v>
       </c>
       <c r="F23" s="10" t="s">
@@ -8853,7 +8853,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -8874,18 +8874,18 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="50">
         <v>45953.0</v>
       </c>
       <c r="F24" s="10" t="s">
@@ -8919,18 +8919,18 @@
     </row>
     <row r="25">
       <c r="A25" s="10" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="50">
         <v>45975.0</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -8943,7 +8943,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -8964,18 +8964,18 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="48">
+      <c r="E26" s="50">
         <v>45989.0</v>
       </c>
       <c r="F26" s="10" t="s">
@@ -9009,13 +9009,13 @@
     </row>
     <row r="27">
       <c r="A27" s="10" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>4</v>
@@ -9054,13 +9054,13 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>4</v>
@@ -9099,13 +9099,13 @@
     </row>
     <row r="29">
       <c r="A29" s="10" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>4</v>
@@ -9144,13 +9144,13 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>4</v>
@@ -9168,7 +9168,7 @@
         <v>339039.0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J30" s="14">
         <v>624166.14</v>
@@ -9189,13 +9189,13 @@
     </row>
     <row r="31">
       <c r="A31" s="10" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>4</v>
@@ -9213,7 +9213,7 @@
         <v>339039.0</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J31" s="14">
         <v>18462.36</v>
@@ -9234,13 +9234,13 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>4</v>
@@ -9258,7 +9258,7 @@
         <v>339039.0</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="J32" s="14">
         <v>1530656.62</v>
@@ -9279,13 +9279,13 @@
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>4</v>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,12 +30,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="209">
   <si>
+    <t>Saldo</t>
+  </si>
+  <si>
     <t>Controle de pagamentos</t>
   </si>
   <si>
-    <t>Saldo</t>
-  </si>
-  <si>
     <t>2025NE000005</t>
   </si>
   <si>
@@ -57,6 +57,15 @@
     <t>25E0385</t>
   </si>
   <si>
+    <t>2025NE000369</t>
+  </si>
+  <si>
+    <t>C25516</t>
+  </si>
+  <si>
+    <t>25E0387</t>
+  </si>
+  <si>
     <t>Número Contrato</t>
   </si>
   <si>
@@ -84,12 +93,18 @@
     <t>PAG</t>
   </si>
   <si>
+    <t>2025NE000371</t>
+  </si>
+  <si>
     <t>Moeda</t>
   </si>
   <si>
     <t>Valor Total do Contrato</t>
   </si>
   <si>
+    <t>25E0389</t>
+  </si>
+  <si>
     <t>Valor a Empenhar</t>
   </si>
   <si>
@@ -114,12 +129,21 @@
     <t>Editar</t>
   </si>
   <si>
+    <t>2025NE000413</t>
+  </si>
+  <si>
     <t>005/CELOG-PAMALS/2025</t>
   </si>
   <si>
+    <t>C25501</t>
+  </si>
+  <si>
     <t>CELOG</t>
   </si>
   <si>
+    <t>25E0403</t>
+  </si>
+  <si>
     <t>PAMALS</t>
   </si>
   <si>
@@ -129,6 +153,9 @@
     <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
   </si>
   <si>
+    <t>20SP</t>
+  </si>
+  <si>
     <t>67101.001510/2024-12</t>
   </si>
   <si>
@@ -138,19 +165,25 @@
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
-    <t>2025NE000369</t>
-  </si>
-  <si>
-    <t>C25516</t>
-  </si>
-  <si>
-    <t>25E0387</t>
-  </si>
-  <si>
-    <t>2025NE000371</t>
-  </si>
-  <si>
-    <t>25E0389</t>
+    <t>2025NE000414</t>
+  </si>
+  <si>
+    <t>C25525</t>
+  </si>
+  <si>
+    <t>25E0431</t>
+  </si>
+  <si>
+    <t>21EM</t>
+  </si>
+  <si>
+    <t>2025NE000559</t>
+  </si>
+  <si>
+    <t>C25545</t>
+  </si>
+  <si>
+    <t>25E0524</t>
   </si>
   <si>
     <t>Módulo</t>
@@ -159,33 +192,30 @@
     <t>Referência</t>
   </si>
   <si>
+    <t>20X7</t>
+  </si>
+  <si>
     <t>Nº recibo</t>
   </si>
   <si>
-    <t>2025NE000413</t>
-  </si>
-  <si>
-    <t>C25501</t>
-  </si>
-  <si>
     <t>Nº</t>
   </si>
   <si>
-    <t>25E0403</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
     <t>Empenho</t>
   </si>
   <si>
-    <t>20SP</t>
+    <t>2025NE000770</t>
   </si>
   <si>
     <t>Observações</t>
   </si>
   <si>
+    <t>25E0731</t>
+  </si>
+  <si>
     <t>Vencimento</t>
   </si>
   <si>
@@ -195,37 +225,34 @@
     <t>Ordem de Pagamento</t>
   </si>
   <si>
-    <t>2025NE000414</t>
-  </si>
-  <si>
     <t>Faturado</t>
   </si>
   <si>
-    <t>C25525</t>
-  </si>
-  <si>
-    <t>25E0431</t>
-  </si>
-  <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>21EM</t>
+    <t>2025NE000774</t>
+  </si>
+  <si>
+    <t>25E0737</t>
   </si>
   <si>
     <t>FEV/25</t>
   </si>
   <si>
-    <t>2025NE000559</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>C25545</t>
-  </si>
-  <si>
-    <t>25E0524</t>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
+    <t>25E0787</t>
+  </si>
+  <si>
+    <t>219C</t>
   </si>
   <si>
     <t xml:space="preserve">2025NE000369 </t>
@@ -234,103 +261,103 @@
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>20X7</t>
-  </si>
-  <si>
-    <t>2025NE000770</t>
-  </si>
-  <si>
-    <t>25E0731</t>
-  </si>
-  <si>
-    <t>2025NE000774</t>
-  </si>
-  <si>
-    <t>25E0737</t>
-  </si>
-  <si>
-    <t>2025NE000843</t>
-  </si>
-  <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
+    <t>2025NE001065</t>
+  </si>
+  <si>
+    <t>25E0999</t>
+  </si>
+  <si>
+    <t>2025NE001200</t>
+  </si>
+  <si>
+    <t>C25590</t>
+  </si>
+  <si>
+    <t>25E1128</t>
+  </si>
+  <si>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
   </si>
   <si>
     <t>MAR/25</t>
   </si>
   <si>
-    <t>219C</t>
+    <t>2025NE001627</t>
   </si>
   <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
   </si>
   <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
+    <t>25E1475</t>
   </si>
   <si>
     <t>2025NP001979</t>
   </si>
   <si>
+    <t>2025NE001629</t>
+  </si>
+  <si>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
+  </si>
+  <si>
     <t>ABR/25</t>
   </si>
   <si>
-    <t>2025NE001200</t>
-  </si>
-  <si>
-    <t>C25590</t>
-  </si>
-  <si>
-    <t>25E1128</t>
+    <t>2025NE001687</t>
   </si>
   <si>
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>25E1446</t>
+    <t>25E1535</t>
   </si>
   <si>
     <t>2025NP002341</t>
   </si>
   <si>
-    <t>2025NE001627</t>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
   </si>
   <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>25E1475</t>
-  </si>
-  <si>
-    <t>2025NE001629</t>
+    <t>2025NE001689</t>
+  </si>
+  <si>
+    <t>25E1537</t>
   </si>
   <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>C25820</t>
-  </si>
-  <si>
-    <t>25E1477</t>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
   </si>
   <si>
     <t>JUN/25</t>
   </si>
   <si>
-    <t>2025NE001687</t>
-  </si>
-  <si>
-    <t>25E1535</t>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -342,49 +369,73 @@
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2025NE001688</t>
-  </si>
-  <si>
-    <t>25E1536</t>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
   </si>
   <si>
     <t>JUL/25</t>
   </si>
   <si>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
+  </si>
+  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
-    <t>2025NE001689</t>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
   </si>
   <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>25E1537</t>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
   </si>
   <si>
     <t>AGO/25</t>
   </si>
   <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
   </si>
   <si>
     <t>2025NP004558</t>
   </si>
   <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
-  </si>
-  <si>
     <t>SET/25</t>
+  </si>
+  <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
   </si>
   <si>
     <t>2025NE001688 
@@ -394,43 +445,43 @@
     <t>2025NP004897</t>
   </si>
   <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
   </si>
   <si>
     <t>OUT/25</t>
   </si>
   <si>
-    <t>20YJ</t>
+    <t>26E0709</t>
   </si>
   <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
-  </si>
-  <si>
     <t>2025NP004932</t>
   </si>
   <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
+  </si>
+  <si>
     <t>NOV/25</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
   </si>
   <si>
     <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
@@ -439,78 +490,48 @@
     <t>2026NP400440</t>
   </si>
   <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
+  </si>
+  <si>
     <t>DEZ/25</t>
   </si>
   <si>
+    <t>2026NE000944</t>
+  </si>
+  <si>
     <t>2025NE001065, 2025NE002200</t>
   </si>
   <si>
+    <t>26E0906</t>
+  </si>
+  <si>
     <t>2026NP400412</t>
   </si>
   <si>
     <t>JAN/26</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
-  </si>
-  <si>
     <t>2026NP401035</t>
   </si>
   <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
-  </si>
-  <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
     <t>FEV/26</t>
   </si>
   <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
     <t>2025NE001627, 2025NE001629, 2025NE001823</t>
   </si>
   <si>
     <t>2026NP402272</t>
   </si>
   <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
     <t>MAR/26</t>
   </si>
   <si>
     <t>2025NE000770, 2025NE001627</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
     <t>R$ 1.350.542,52</t>
   </si>
   <si>
@@ -520,28 +541,7 @@
     <t>ABR/26</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
     <t>2025NE000770, 2025NE001065, 2025NE001627</t>
-  </si>
-  <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
-  </si>
-  <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
-    <t>26E0906</t>
   </si>
   <si>
     <t>REAJUSTE</t>
@@ -715,13 +715,13 @@
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Century Gothic"/>
     </font>
     <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Century Gothic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -866,15 +866,15 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -888,11 +888,11 @@
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -931,28 +931,28 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -967,17 +967,17 @@
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="6" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -993,14 +993,14 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1015,13 +1015,13 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1030,7 +1030,7 @@
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1412,22 +1412,22 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="3"/>
+      <c r="V1" s="5"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="5"/>
+      <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="10"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
@@ -1451,85 +1451,85 @@
       <c r="S3" s="14"/>
       <c r="T3" s="14"/>
       <c r="U3" s="14"/>
-      <c r="V3" s="3"/>
+      <c r="V3" s="5"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S4" s="16" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="V4" s="5"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1538,16 +1538,16 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="N5" s="21">
         <v>9.165159737E7</v>
@@ -1565,15 +1565,15 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="V5" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="V5" s="5"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="L6" s="22"/>
-      <c r="V6" s="3"/>
+      <c r="V6" s="5"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="23"/>
@@ -1587,55 +1587,55 @@
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
-      <c r="L7" s="26"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="27"/>
-      <c r="V7" s="3"/>
+      <c r="P7" s="28"/>
+      <c r="V7" s="5"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="28" t="s">
+      <c r="C8" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="D8" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="29" t="s">
+      <c r="E8" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="N8" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="O8" s="28"/>
-      <c r="P8" s="27"/>
-      <c r="V8" s="3"/>
+      <c r="G8" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="29"/>
+      <c r="P8" s="28"/>
+      <c r="V8" s="5"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="23"/>
@@ -1644,10 +1644,10 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F9" s="35">
         <v>594.0</v>
@@ -1656,7 +1656,7 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I9" s="36"/>
       <c r="J9" s="36">
@@ -1666,26 +1666,26 @@
         <v>748504.24</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" s="38">
+        <v>76</v>
+      </c>
+      <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
-      <c r="N9" s="39"/>
+      <c r="N9" s="40"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="27"/>
-      <c r="V9" s="3"/>
+      <c r="P9" s="28"/>
+      <c r="V9" s="5"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="40"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="33" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F10" s="35">
         <v>620.0</v>
@@ -1694,7 +1694,7 @@
         <v>45775.0</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I10" s="36"/>
       <c r="J10" s="36">
@@ -1704,26 +1704,26 @@
         <v>1110378.24</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="M10" s="38">
+        <v>89</v>
+      </c>
+      <c r="M10" s="39">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
-      <c r="N10" s="41"/>
+      <c r="N10" s="42"/>
       <c r="O10" s="25"/>
-      <c r="P10" s="27"/>
-      <c r="V10" s="3"/>
+      <c r="P10" s="28"/>
+      <c r="V10" s="5"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="40"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="33" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F11" s="35">
         <v>634.0</v>
@@ -1732,7 +1732,7 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36">
@@ -1742,25 +1742,25 @@
         <v>974557.12</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="M11" s="38">
+        <v>97</v>
+      </c>
+      <c r="M11" s="39">
         <v>974557.12</v>
       </c>
-      <c r="N11" s="41"/>
+      <c r="N11" s="42"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="27"/>
-      <c r="V11" s="3"/>
+      <c r="P11" s="28"/>
+      <c r="V11" s="5"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="40"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="33" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F12" s="34">
         <v>660.0</v>
@@ -1769,7 +1769,7 @@
         <v>45856.0</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36">
@@ -1779,25 +1779,25 @@
         <v>1402001.34</v>
       </c>
       <c r="L12" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="M12" s="38">
+        <v>103</v>
+      </c>
+      <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
       <c r="N12" s="47"/>
       <c r="O12" s="25"/>
-      <c r="P12" s="27"/>
-      <c r="V12" s="3"/>
+      <c r="P12" s="28"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="40"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="48" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F13" s="35">
         <v>661.0</v>
@@ -1806,7 +1806,7 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="I13" s="43"/>
       <c r="J13" s="43">
@@ -1816,25 +1816,25 @@
         <v>1223702.3</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="M13" s="38">
+        <v>111</v>
+      </c>
+      <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
       <c r="N13" s="47"/>
       <c r="O13" s="25"/>
-      <c r="P13" s="49"/>
-      <c r="V13" s="3"/>
+      <c r="P13" s="50"/>
+      <c r="V13" s="5"/>
     </row>
     <row r="14">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
-      <c r="C14" s="40"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="48" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F14" s="34">
         <v>688.0</v>
@@ -1843,7 +1843,7 @@
         <v>45901.0</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="I14" s="43"/>
       <c r="J14" s="43">
@@ -1853,25 +1853,25 @@
         <v>1011677.95</v>
       </c>
       <c r="L14" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="M14" s="38">
+        <v>123</v>
+      </c>
+      <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="42"/>
       <c r="O14" s="25"/>
-      <c r="P14" s="27"/>
-      <c r="V14" s="3"/>
+      <c r="P14" s="28"/>
+      <c r="V14" s="5"/>
     </row>
     <row r="15">
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
-      <c r="C15" s="40"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="48" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F15" s="34">
         <v>696.0</v>
@@ -1880,7 +1880,7 @@
         <v>45923.0</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="I15" s="43"/>
       <c r="J15" s="43">
@@ -1890,24 +1890,24 @@
         <v>896744.06</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="M15" s="38">
+        <v>130</v>
+      </c>
+      <c r="M15" s="39">
         <v>896744.06</v>
       </c>
       <c r="N15" s="47"/>
       <c r="O15" s="25"/>
-      <c r="V15" s="3"/>
+      <c r="V15" s="5"/>
     </row>
     <row r="16">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
-      <c r="C16" s="40"/>
+      <c r="C16" s="41"/>
       <c r="D16" s="48" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F16" s="34">
         <v>704.0</v>
@@ -1916,7 +1916,7 @@
         <v>45957.0</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="I16" s="43"/>
       <c r="J16" s="43">
@@ -1926,21 +1926,21 @@
         <v>919329.06</v>
       </c>
       <c r="L16" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="M16" s="38">
+        <v>136</v>
+      </c>
+      <c r="M16" s="39">
         <v>919329.06</v>
       </c>
-      <c r="N16" s="41"/>
+      <c r="N16" s="42"/>
       <c r="O16" s="25"/>
-      <c r="V16" s="3"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
-      <c r="C17" s="40"/>
+      <c r="C17" s="41"/>
       <c r="D17" s="48" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="34">
@@ -1950,7 +1950,7 @@
         <v>45972.0</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="I17" s="34"/>
       <c r="J17" s="43">
@@ -1960,24 +1960,24 @@
         <v>1157009.26</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="M17" s="38">
+        <v>142</v>
+      </c>
+      <c r="M17" s="39">
         <v>1157009.26</v>
       </c>
       <c r="N17" s="51"/>
       <c r="O17" s="25"/>
-      <c r="V17" s="3"/>
+      <c r="V17" s="5"/>
     </row>
     <row r="18">
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
-      <c r="C18" s="40"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="48" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F18" s="34">
         <v>728.0</v>
@@ -1986,7 +1986,7 @@
         <v>46008.0</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="I18" s="34"/>
       <c r="J18" s="43">
@@ -1996,28 +1996,28 @@
         <v>1214597.952</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="M18" s="38">
+        <v>151</v>
+      </c>
+      <c r="M18" s="39">
         <v>1214597.952</v>
       </c>
       <c r="N18" s="51"/>
       <c r="O18" s="25"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="27"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
       <c r="V18" s="52"/>
     </row>
     <row r="19">
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
-      <c r="C19" s="40"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="48" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F19" s="34">
         <v>278.0</v>
@@ -2026,7 +2026,7 @@
         <v>46042.0</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="I19" s="43"/>
       <c r="J19" s="43">
@@ -2036,25 +2036,25 @@
         <v>967082.09</v>
       </c>
       <c r="L19" s="34" t="s">
-        <v>137</v>
-      </c>
-      <c r="M19" s="38">
+        <v>158</v>
+      </c>
+      <c r="M19" s="39">
         <v>967082.09</v>
       </c>
       <c r="N19" s="51"/>
       <c r="O19" s="25"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
       <c r="V19" s="52"/>
     </row>
     <row r="20">
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
-      <c r="C20" s="40"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="48" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34">
@@ -2064,7 +2064,7 @@
         <v>46078.0</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I20" s="43"/>
       <c r="J20" s="43">
@@ -2074,25 +2074,25 @@
         <v>719561.08</v>
       </c>
       <c r="L20" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="M20" s="38">
+        <v>160</v>
+      </c>
+      <c r="M20" s="39">
         <v>719561.08</v>
       </c>
       <c r="N20" s="51"/>
       <c r="O20" s="25"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
       <c r="V20" s="52"/>
     </row>
     <row r="21">
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
-      <c r="C21" s="40"/>
+      <c r="C21" s="41"/>
       <c r="D21" s="48" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34">
@@ -2102,7 +2102,7 @@
         <v>46094.0</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="I21" s="43"/>
       <c r="J21" s="43">
@@ -2112,25 +2112,25 @@
         <v>885881.08</v>
       </c>
       <c r="L21" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="M21" s="38">
+        <v>163</v>
+      </c>
+      <c r="M21" s="39">
         <v>885881.08</v>
       </c>
       <c r="N21" s="51"/>
       <c r="O21" s="25"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
       <c r="V21" s="52"/>
     </row>
     <row r="22">
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
-      <c r="C22" s="40"/>
+      <c r="C22" s="41"/>
       <c r="D22" s="48" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="34">
@@ -2140,35 +2140,35 @@
         <v>46128.0</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I22" s="43"/>
       <c r="J22" s="43">
         <v>46164.0</v>
       </c>
       <c r="K22" s="45" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="L22" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="M22" s="38" t="s">
-        <v>159</v>
+        <v>167</v>
+      </c>
+      <c r="M22" s="39" t="s">
+        <v>166</v>
       </c>
       <c r="N22" s="51"/>
       <c r="O22" s="25"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
       <c r="V22" s="52"/>
     </row>
     <row r="23">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
-      <c r="C23" s="40"/>
+      <c r="C23" s="41"/>
       <c r="D23" s="48" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="34">
@@ -2178,7 +2178,7 @@
         <v>46156.0</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I23" s="43"/>
       <c r="J23" s="43">
@@ -2188,23 +2188,23 @@
         <v>1108954.4358333333</v>
       </c>
       <c r="L23" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="M23" s="38">
+        <v>163</v>
+      </c>
+      <c r="M23" s="39">
         <v>1108954.4358333333</v>
       </c>
       <c r="N23" s="53"/>
       <c r="O23" s="25"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
       <c r="V23" s="52"/>
     </row>
     <row r="24">
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
-      <c r="C24" s="40"/>
+      <c r="C24" s="41"/>
       <c r="D24" s="48" t="s">
         <v>170</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>46149.0</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I24" s="43"/>
       <c r="J24" s="43">
@@ -2228,21 +2228,21 @@
       <c r="L24" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="M24" s="38">
+      <c r="M24" s="39">
         <v>218206.1</v>
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="25"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
       <c r="V24" s="52"/>
     </row>
     <row r="25">
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
-      <c r="C25" s="40"/>
+      <c r="C25" s="41"/>
       <c r="D25" s="48" t="s">
         <v>172</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>46156.0</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I25" s="43"/>
       <c r="J25" s="43">
@@ -2266,15 +2266,15 @@
       <c r="L25" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="M25" s="38">
+      <c r="M25" s="39">
         <v>1549250.84</v>
       </c>
       <c r="N25" s="54"/>
       <c r="O25" s="25"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
       <c r="V25" s="52"/>
     </row>
     <row r="26">
@@ -2304,64 +2304,64 @@
       <c r="L26" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="M26" s="38" t="s">
+      <c r="M26" s="39" t="s">
         <v>176</v>
       </c>
       <c r="N26" s="54"/>
       <c r="O26" s="25"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="23"/>
-      <c r="C27" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+      <c r="C27" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
       <c r="K27" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="30" t="s">
-        <v>54</v>
+        <v>63</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>64</v>
       </c>
       <c r="M27" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="N27" s="28" t="s">
-        <v>59</v>
+        <v>65</v>
+      </c>
+      <c r="N27" s="29" t="s">
+        <v>66</v>
       </c>
       <c r="O27" s="25"/>
-      <c r="P27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
+      <c r="P27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
       <c r="V27" s="52"/>
-      <c r="W27" s="27"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
-      <c r="AA27" s="27"/>
-      <c r="AB27" s="27"/>
-      <c r="AC27" s="27"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="23"/>
@@ -2380,7 +2380,7 @@
         <v>45791.0</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I28" s="36"/>
       <c r="J28" s="36">
@@ -2397,25 +2397,25 @@
       </c>
       <c r="N28" s="51"/>
       <c r="O28" s="25"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
       <c r="V28" s="52"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="27"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
     </row>
     <row r="29">
       <c r="A29" s="23"/>
       <c r="B29" s="23"/>
-      <c r="C29" s="40"/>
+      <c r="C29" s="41"/>
       <c r="D29" s="58" t="s">
         <v>180</v>
       </c>
@@ -2441,30 +2441,30 @@
       <c r="L29" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="M29" s="38">
+      <c r="M29" s="39">
         <v>112720.77</v>
       </c>
       <c r="N29" s="51"/>
       <c r="O29" s="25"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
       <c r="V29" s="52"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="27"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
-      <c r="C30" s="40"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="61" t="s">
         <v>183</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>45853.0</v>
       </c>
       <c r="H30" s="34" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I30" s="43"/>
       <c r="J30" s="43">
@@ -2490,30 +2490,30 @@
       <c r="L30" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="39">
         <v>378307.61</v>
       </c>
       <c r="N30" s="51"/>
       <c r="O30" s="25"/>
       <c r="P30" s="64"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="27"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="28"/>
       <c r="V30" s="52"/>
-      <c r="W30" s="27"/>
-      <c r="X30" s="27"/>
-      <c r="Y30" s="27"/>
-      <c r="Z30" s="27"/>
-      <c r="AA30" s="27"/>
-      <c r="AB30" s="27"/>
-      <c r="AC30" s="27"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+      <c r="AC30" s="28"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
       <c r="A31" s="23"/>
       <c r="B31" s="23"/>
-      <c r="C31" s="40"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="61" t="s">
         <v>186</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>45910.0</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I31" s="43"/>
       <c r="J31" s="43">
@@ -2539,30 +2539,30 @@
       <c r="L31" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="M31" s="38">
+      <c r="M31" s="39">
         <v>3315.04710000003</v>
       </c>
       <c r="N31" s="51"/>
       <c r="O31" s="25"/>
       <c r="P31" s="64"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="27"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
       <c r="V31" s="52"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="27"/>
-      <c r="Y31" s="27"/>
-      <c r="Z31" s="27"/>
-      <c r="AA31" s="27"/>
-      <c r="AB31" s="27"/>
-      <c r="AC31" s="27"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+      <c r="AC31" s="28"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="23"/>
       <c r="B32" s="23"/>
-      <c r="C32" s="40"/>
+      <c r="C32" s="41"/>
       <c r="D32" s="61" t="s">
         <v>188</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>45904.0</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
@@ -2588,30 +2588,30 @@
       <c r="L32" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="M32" s="38">
+      <c r="M32" s="39">
         <v>198332.75</v>
       </c>
       <c r="N32" s="51"/>
       <c r="O32" s="25"/>
       <c r="P32" s="64"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
       <c r="V32" s="52"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
-      <c r="AC32" s="27"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="23"/>
       <c r="B33" s="23"/>
-      <c r="C33" s="40"/>
+      <c r="C33" s="41"/>
       <c r="D33" s="61" t="s">
         <v>190</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>46008.0</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
@@ -2643,24 +2643,24 @@
       <c r="N33" s="51"/>
       <c r="O33" s="25"/>
       <c r="P33" s="64"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="27"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
       <c r="V33" s="52"/>
-      <c r="W33" s="27"/>
-      <c r="X33" s="27"/>
-      <c r="Y33" s="27"/>
-      <c r="Z33" s="27"/>
-      <c r="AA33" s="27"/>
-      <c r="AB33" s="27"/>
-      <c r="AC33" s="27"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="28"/>
+      <c r="AA33" s="28"/>
+      <c r="AB33" s="28"/>
+      <c r="AC33" s="28"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="23"/>
-      <c r="C34" s="40"/>
+      <c r="C34" s="41"/>
       <c r="D34" s="61" t="s">
         <v>193</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>45930.0</v>
       </c>
       <c r="H34" s="34" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
@@ -2692,24 +2692,24 @@
       <c r="N34" s="51"/>
       <c r="O34" s="25"/>
       <c r="P34" s="64"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="27"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
       <c r="V34" s="52"/>
-      <c r="W34" s="27"/>
-      <c r="X34" s="27"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="27"/>
-      <c r="AA34" s="27"/>
-      <c r="AB34" s="27"/>
-      <c r="AC34" s="27"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="28"/>
+      <c r="AA34" s="28"/>
+      <c r="AB34" s="28"/>
+      <c r="AC34" s="28"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="23"/>
-      <c r="C35" s="40"/>
+      <c r="C35" s="41"/>
       <c r="D35" s="61" t="s">
         <v>197</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>45968.0</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
@@ -2741,24 +2741,24 @@
       <c r="N35" s="51"/>
       <c r="O35" s="25"/>
       <c r="P35" s="64"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="27"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
       <c r="V35" s="52"/>
-      <c r="W35" s="27"/>
-      <c r="X35" s="27"/>
-      <c r="Y35" s="27"/>
-      <c r="Z35" s="27"/>
-      <c r="AA35" s="27"/>
-      <c r="AB35" s="27"/>
-      <c r="AC35" s="27"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="23"/>
-      <c r="C36" s="40"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="61" t="s">
         <v>200</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
@@ -2784,30 +2784,30 @@
       <c r="L36" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="M36" s="38">
+      <c r="M36" s="39">
         <v>11372.9</v>
       </c>
       <c r="N36" s="51"/>
       <c r="O36" s="25"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="27"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
       <c r="V36" s="52"/>
-      <c r="W36" s="27"/>
-      <c r="X36" s="27"/>
-      <c r="Y36" s="27"/>
-      <c r="Z36" s="27"/>
-      <c r="AA36" s="27"/>
-      <c r="AB36" s="27"/>
-      <c r="AC36" s="27"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="28"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
+      <c r="AC36" s="28"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
-      <c r="C37" s="40"/>
+      <c r="C37" s="41"/>
       <c r="D37" s="61" t="s">
         <v>202</v>
       </c>
@@ -2821,25 +2821,25 @@
       <c r="J37" s="69"/>
       <c r="K37" s="45"/>
       <c r="L37" s="34"/>
-      <c r="M37" s="38"/>
+      <c r="M37" s="39"/>
       <c r="N37" s="51">
         <v>15854.78</v>
       </c>
       <c r="O37" s="25"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
       <c r="V37" s="52"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="23"/>
@@ -2858,25 +2858,25 @@
       <c r="J38" s="69"/>
       <c r="K38" s="45"/>
       <c r="L38" s="34"/>
-      <c r="M38" s="38"/>
+      <c r="M38" s="39"/>
       <c r="N38" s="51" t="s">
         <v>205</v>
       </c>
       <c r="O38" s="25"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
       <c r="V38" s="52"/>
-      <c r="W38" s="27"/>
-      <c r="X38" s="27"/>
-      <c r="Y38" s="27"/>
-      <c r="Z38" s="27"/>
-      <c r="AA38" s="27"/>
-      <c r="AB38" s="27"/>
-      <c r="AC38" s="27"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="23"/>
@@ -2895,7 +2895,7 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
@@ -2912,25 +2912,25 @@
       </c>
       <c r="N39" s="51"/>
       <c r="O39" s="25"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
       <c r="V39" s="52"/>
-      <c r="W39" s="27"/>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
-      <c r="AA39" s="27"/>
-      <c r="AB39" s="27"/>
-      <c r="AC39" s="27"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="28"/>
+      <c r="AA39" s="28"/>
+      <c r="AB39" s="28"/>
+      <c r="AC39" s="28"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
-      <c r="C40" s="40"/>
+      <c r="C40" s="41"/>
       <c r="D40" s="61" t="s">
         <v>208</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
@@ -2952,53 +2952,53 @@
         <v>58868.35</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
       </c>
       <c r="N40" s="51"/>
-      <c r="V40" s="3"/>
+      <c r="V40" s="5"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
-      <c r="C41" s="40"/>
+      <c r="C41" s="41"/>
       <c r="K41" s="73"/>
       <c r="M41" s="73"/>
-      <c r="V41" s="3"/>
+      <c r="V41" s="5"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
-      <c r="C42" s="40"/>
+      <c r="C42" s="41"/>
       <c r="K42" s="73"/>
       <c r="M42" s="73"/>
-      <c r="V42" s="3"/>
+      <c r="V42" s="5"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
-      <c r="C43" s="40"/>
-      <c r="V43" s="3"/>
+      <c r="C43" s="41"/>
+      <c r="V43" s="5"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
-      <c r="C44" s="40"/>
-      <c r="V44" s="3"/>
+      <c r="C44" s="41"/>
+      <c r="V44" s="5"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
-      <c r="C45" s="40"/>
-      <c r="V45" s="3"/>
+      <c r="C45" s="41"/>
+      <c r="V45" s="5"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
-      <c r="C46" s="40"/>
-      <c r="V46" s="3"/>
+      <c r="C46" s="41"/>
+      <c r="V46" s="5"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="15"/>
@@ -3006,7 +3006,7 @@
       <c r="C47" s="55"/>
       <c r="K47" s="73"/>
       <c r="M47" s="73"/>
-      <c r="V47" s="3"/>
+      <c r="V47" s="5"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="15"/>
@@ -3030,7 +3030,7 @@
       <c r="S48" s="74"/>
       <c r="T48" s="74"/>
       <c r="U48" s="74"/>
-      <c r="V48" s="3"/>
+      <c r="V48" s="5"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="15"/>
@@ -7911,11 +7911,11 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>1</v>
+      <c r="L2" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -7938,7 +7938,7 @@
       <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="12">
         <v>45686.0</v>
       </c>
       <c r="F3" s="7" t="s">
@@ -7983,7 +7983,7 @@
       <c r="D4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="12">
         <v>45762.0</v>
       </c>
       <c r="F4" s="7" t="s">
@@ -8017,18 +8017,18 @@
     </row>
     <row r="5">
       <c r="A5" s="7" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="12">
         <v>45762.0</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -8062,18 +8062,18 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <v>45762.0</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -8107,18 +8107,18 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="12">
         <v>45763.0</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -8131,7 +8131,7 @@
         <v>339039.0</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J7" s="13">
         <v>949835.78</v>
@@ -8152,18 +8152,18 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="12">
         <v>45763.0</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -8176,7 +8176,7 @@
         <v>339039.0</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J8" s="13">
         <v>524584.95</v>
@@ -8187,7 +8187,7 @@
       <c r="L8" s="7">
         <v>0.0</v>
       </c>
-      <c r="O8" s="31"/>
+      <c r="O8" s="26"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8198,18 +8198,18 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="12">
         <v>45792.0</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -8222,7 +8222,7 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="J9" s="13">
         <v>211614.23</v>
@@ -8243,18 +8243,18 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="12">
         <v>45825.0</v>
       </c>
       <c r="F10" s="7" t="s">
@@ -8288,18 +8288,18 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <v>45825.0</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -8333,18 +8333,18 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="12">
         <v>45832.0</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -8357,7 +8357,7 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J12" s="13">
         <v>1600334.09</v>
@@ -8378,18 +8378,18 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="12">
         <v>45863.0</v>
       </c>
       <c r="F13" s="7" t="s">
@@ -8413,7 +8413,7 @@
       <c r="L13" s="13">
         <v>0.0</v>
       </c>
-      <c r="M13" s="42"/>
+      <c r="M13" s="38"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8424,18 +8424,18 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="12">
         <v>45887.0</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -8448,7 +8448,7 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="J14" s="13">
         <v>968237.39</v>
@@ -8469,18 +8469,18 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="12">
         <v>45924.0</v>
       </c>
       <c r="F15" s="7" t="s">
@@ -8493,7 +8493,7 @@
         <v>339039.0</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J15" s="13">
         <v>1011677.95</v>
@@ -8514,18 +8514,18 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="12">
         <v>45929.0</v>
       </c>
       <c r="F16" s="7" t="s">
@@ -8559,18 +8559,18 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="12">
         <v>45930.0</v>
       </c>
       <c r="F17" s="7" t="s">
@@ -8604,18 +8604,18 @@
     </row>
     <row r="18">
       <c r="A18" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="12">
         <v>45938.0</v>
       </c>
       <c r="F18" s="7" t="s">
@@ -8628,7 +8628,7 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="J18" s="13">
         <v>63746.85</v>
@@ -8649,18 +8649,18 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="12">
         <v>45938.0</v>
       </c>
       <c r="F19" s="7" t="s">
@@ -8673,7 +8673,7 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J19" s="13">
         <v>947931.1</v>
@@ -8694,18 +8694,18 @@
     </row>
     <row r="20">
       <c r="A20" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="12">
         <v>45938.0</v>
       </c>
       <c r="F20" s="7" t="s">
@@ -8739,18 +8739,18 @@
     </row>
     <row r="21">
       <c r="A21" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="12">
         <v>45938.0</v>
       </c>
       <c r="F21" s="7" t="s">
@@ -8784,18 +8784,18 @@
     </row>
     <row r="22">
       <c r="A22" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="49">
         <v>45953.0</v>
       </c>
       <c r="F22" s="7" t="s">
@@ -8829,18 +8829,18 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="49">
         <v>45953.0</v>
       </c>
       <c r="F23" s="7" t="s">
@@ -8853,7 +8853,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="J23" s="13">
         <v>1000001.64</v>
@@ -8874,18 +8874,18 @@
     </row>
     <row r="24">
       <c r="A24" s="7" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="49">
         <v>45953.0</v>
       </c>
       <c r="F24" s="7" t="s">
@@ -8919,18 +8919,18 @@
     </row>
     <row r="25">
       <c r="A25" s="7" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="49">
         <v>45975.0</v>
       </c>
       <c r="F25" s="7" t="s">
@@ -8943,7 +8943,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="J25" s="13">
         <v>1157673.06</v>
@@ -8964,18 +8964,18 @@
     </row>
     <row r="26">
       <c r="A26" s="7" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="49">
         <v>45989.0</v>
       </c>
       <c r="F26" s="7" t="s">
@@ -9009,18 +9009,18 @@
     </row>
     <row r="27">
       <c r="A27" s="7" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="12">
         <v>46104.0</v>
       </c>
       <c r="F27" s="7" t="s">
@@ -9054,18 +9054,18 @@
     </row>
     <row r="28">
       <c r="A28" s="7" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="12">
         <v>46120.0</v>
       </c>
       <c r="F28" s="7" t="s">
@@ -9078,7 +9078,7 @@
         <v>339039.0</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J28" s="13">
         <v>1912292.52</v>
@@ -9099,18 +9099,18 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="12">
         <v>46196.0</v>
       </c>
       <c r="F29" s="7" t="s">
@@ -9144,18 +9144,18 @@
     </row>
     <row r="30">
       <c r="A30" s="7" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="12">
         <v>46205.0</v>
       </c>
       <c r="F30" s="7" t="s">
@@ -9168,7 +9168,7 @@
         <v>339039.0</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J30" s="13">
         <v>624166.14</v>
@@ -9189,18 +9189,18 @@
     </row>
     <row r="31">
       <c r="A31" s="7" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="12">
         <v>46205.0</v>
       </c>
       <c r="F31" s="7" t="s">
@@ -9213,7 +9213,7 @@
         <v>339039.0</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="J31" s="13">
         <v>18462.36</v>
@@ -9234,18 +9234,18 @@
     </row>
     <row r="32">
       <c r="A32" s="7" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="12">
         <v>46213.0</v>
       </c>
       <c r="F32" s="7" t="s">
@@ -9258,7 +9258,7 @@
         <v>339039.0</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="J32" s="13">
         <v>1530656.62</v>
@@ -9279,18 +9279,18 @@
     </row>
     <row r="33">
       <c r="A33" s="7" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="12">
         <v>46227.0</v>
       </c>
       <c r="F33" s="7" t="s">

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -57,30 +57,30 @@
     <t>25E0385</t>
   </si>
   <si>
+    <t>Número Contrato</t>
+  </si>
+  <si>
+    <t>UG Executora</t>
+  </si>
+  <si>
+    <t>UG Responsável</t>
+  </si>
+  <si>
     <t>2025NE000369</t>
   </si>
   <si>
+    <t>UG Fiscalizadora</t>
+  </si>
+  <si>
     <t>C25516</t>
   </si>
   <si>
+    <t>Prazo Final de Execução</t>
+  </si>
+  <si>
     <t>25E0387</t>
   </si>
   <si>
-    <t>Número Contrato</t>
-  </si>
-  <si>
-    <t>UG Executora</t>
-  </si>
-  <si>
-    <t>UG Responsável</t>
-  </si>
-  <si>
-    <t>UG Fiscalizadora</t>
-  </si>
-  <si>
-    <t>Prazo Final de Execução</t>
-  </si>
-  <si>
     <t>Prazo Final de Vigência</t>
   </si>
   <si>
@@ -93,75 +93,75 @@
     <t>PAG</t>
   </si>
   <si>
+    <t>Moeda</t>
+  </si>
+  <si>
+    <t>Valor Total do Contrato</t>
+  </si>
+  <si>
+    <t>Valor a Empenhar</t>
+  </si>
+  <si>
+    <t>Valor Empenhado</t>
+  </si>
+  <si>
+    <t>Valor Liquidado</t>
+  </si>
+  <si>
+    <t>Saldo (Valor a Faturar)</t>
+  </si>
+  <si>
+    <t>Fornecedor</t>
+  </si>
+  <si>
     <t>2025NE000371</t>
   </si>
   <si>
-    <t>Moeda</t>
-  </si>
-  <si>
-    <t>Valor Total do Contrato</t>
+    <t>Tipo Despesa /Receita</t>
+  </si>
+  <si>
+    <t>Abrir</t>
   </si>
   <si>
     <t>25E0389</t>
   </si>
   <si>
-    <t>Valor a Empenhar</t>
-  </si>
-  <si>
-    <t>Valor Empenhado</t>
-  </si>
-  <si>
-    <t>Valor Liquidado</t>
-  </si>
-  <si>
-    <t>Saldo (Valor a Faturar)</t>
-  </si>
-  <si>
-    <t>Fornecedor</t>
-  </si>
-  <si>
-    <t>Tipo Despesa /Receita</t>
-  </si>
-  <si>
-    <t>Abrir</t>
-  </si>
-  <si>
     <t>Editar</t>
   </si>
   <si>
+    <t>005/CELOG-PAMALS/2025</t>
+  </si>
+  <si>
+    <t>CELOG</t>
+  </si>
+  <si>
+    <t>PAMALS</t>
+  </si>
+  <si>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
+  </si>
+  <si>
+    <t>67101.001510/2024-12</t>
+  </si>
+  <si>
     <t>2025NE000413</t>
   </si>
   <si>
-    <t>005/CELOG-PAMALS/2025</t>
+    <t>R$</t>
   </si>
   <si>
     <t>C25501</t>
   </si>
   <si>
-    <t>CELOG</t>
-  </si>
-  <si>
     <t>25E0403</t>
   </si>
   <si>
-    <t>PAMALS</t>
-  </si>
-  <si>
-    <t>Vigente</t>
-  </si>
-  <si>
-    <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
-  </si>
-  <si>
     <t>20SP</t>
   </si>
   <si>
-    <t>67101.001510/2024-12</t>
-  </si>
-  <si>
-    <t>R$</t>
-  </si>
-  <si>
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
@@ -186,13 +186,19 @@
     <t>25E0524</t>
   </si>
   <si>
+    <t>20X7</t>
+  </si>
+  <si>
     <t>Módulo</t>
   </si>
   <si>
     <t>Referência</t>
   </si>
   <si>
-    <t>20X7</t>
+    <t>2025NE000770</t>
+  </si>
+  <si>
+    <t>25E0731</t>
   </si>
   <si>
     <t>Nº recibo</t>
@@ -207,13 +213,13 @@
     <t>Empenho</t>
   </si>
   <si>
-    <t>2025NE000770</t>
+    <t>2025NE000774</t>
   </si>
   <si>
     <t>Observações</t>
   </si>
   <si>
-    <t>25E0731</t>
+    <t>25E0737</t>
   </si>
   <si>
     <t>Vencimento</t>
@@ -228,136 +234,190 @@
     <t>Faturado</t>
   </si>
   <si>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
+  </si>
+  <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>2025NE000774</t>
-  </si>
-  <si>
-    <t>25E0737</t>
+    <t>25E0787</t>
+  </si>
+  <si>
+    <t>219C</t>
+  </si>
+  <si>
+    <t>2025NE001065</t>
+  </si>
+  <si>
+    <t>25E0999</t>
   </si>
   <si>
     <t>FEV/25</t>
   </si>
   <si>
+    <t>2025NE001200</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>2025NE000843</t>
-  </si>
-  <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
-  </si>
-  <si>
-    <t>219C</t>
+    <t>C25590</t>
+  </si>
+  <si>
+    <t>25E1128</t>
   </si>
   <si>
     <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
+  </si>
+  <si>
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
-  </si>
-  <si>
-    <t>2025NE001200</t>
-  </si>
-  <si>
-    <t>C25590</t>
-  </si>
-  <si>
-    <t>25E1128</t>
-  </si>
-  <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>25E1446</t>
+    <t>2025NE001627</t>
+  </si>
+  <si>
+    <t>25E1475</t>
+  </si>
+  <si>
+    <t>2025NE001629</t>
+  </si>
+  <si>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
+  </si>
+  <si>
+    <t>2025NE001687</t>
+  </si>
+  <si>
+    <t>25E1535</t>
+  </si>
+  <si>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
   </si>
   <si>
     <t>MAR/25</t>
   </si>
   <si>
-    <t>2025NE001627</t>
+    <t>2025NE001689</t>
+  </si>
+  <si>
+    <t>25E1537</t>
   </si>
   <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
   </si>
   <si>
-    <t>25E1475</t>
+    <t>2025NE001690</t>
   </si>
   <si>
     <t>2025NP001979</t>
   </si>
   <si>
-    <t>2025NE001629</t>
-  </si>
-  <si>
-    <t>C25820</t>
-  </si>
-  <si>
-    <t>25E1477</t>
+    <t>25E1538</t>
+  </si>
+  <si>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
   </si>
   <si>
     <t>ABR/25</t>
   </si>
   <si>
-    <t>2025NE001687</t>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
   </si>
   <si>
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>25E1535</t>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
   </si>
   <si>
     <t>2025NP002341</t>
   </si>
   <si>
-    <t>2025NE001688</t>
-  </si>
-  <si>
-    <t>25E1536</t>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
   </si>
   <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>2025NE001689</t>
-  </si>
-  <si>
-    <t>25E1537</t>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
+  </si>
+  <si>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
   </si>
   <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
   </si>
   <si>
     <t>JUN/25</t>
-  </si>
-  <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -366,76 +426,55 @@
 2025NE000774</t>
   </si>
   <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
+  </si>
+  <si>
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
-    <t>20YJ</t>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
   </si>
   <si>
     <t>JUL/25</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
-  </si>
-  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
-  </si>
-  <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
+    <t>2026NE000842</t>
+  </si>
+  <si>
+    <t>26E0803</t>
   </si>
   <si>
     <t>AGO/25</t>
   </si>
   <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
+    <t>2026NE000944</t>
+  </si>
+  <si>
+    <t>26E0906</t>
   </si>
   <si>
     <t>2025NP004558</t>
   </si>
   <si>
     <t>SET/25</t>
-  </si>
-  <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
   </si>
   <si>
     <t>2025NE001688 
@@ -445,67 +484,28 @@
     <t>2025NP004897</t>
   </si>
   <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
     <t>OUT/25</t>
   </si>
   <si>
-    <t>26E0709</t>
-  </si>
-  <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
     <t>2025NP004932</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
     <t>NOV/25</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
     <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
   </si>
   <si>
     <t>2026NP400440</t>
   </si>
   <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
-  </si>
-  <si>
     <t>DEZ/25</t>
   </si>
   <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
     <t>2025NE001065, 2025NE002200</t>
-  </si>
-  <si>
-    <t>26E0906</t>
   </si>
   <si>
     <t>2026NP400412</t>
@@ -671,8 +671,8 @@
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="MM/DD/YY"/>
-    <numFmt numFmtId="170" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
     <numFmt numFmtId="171" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12">
@@ -866,24 +866,18 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -891,13 +885,19 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -952,6 +952,7 @@
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -967,7 +968,6 @@
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -978,10 +978,13 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -995,9 +998,6 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1412,64 +1412,64 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="5"/>
+      <c r="V1" s="3"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="8" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="10"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="11"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="11"/>
-      <c r="AB2" s="11"/>
-      <c r="AC2" s="11"/>
-      <c r="AD2" s="11"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="14"/>
-      <c r="R3" s="14"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="5"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="3"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="16" t="s">
+      <c r="G4" s="17" t="s">
         <v>15</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>16</v>
       </c>
       <c r="H4" s="17" t="s">
         <v>17</v>
@@ -1484,52 +1484,52 @@
         <v>20</v>
       </c>
       <c r="L4" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="N4" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="O4" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="Q4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="R4" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="R4" s="16" t="s">
+      <c r="S4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="S4" s="16" t="s">
+      <c r="T4" s="16" t="s">
         <v>30</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>31</v>
       </c>
       <c r="U4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="V4" s="5"/>
+      <c r="V4" s="3"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>36</v>
-      </c>
       <c r="F5" s="19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1538,16 +1538,16 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K5" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="19" t="s">
         <v>40</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="19" t="s">
-        <v>43</v>
       </c>
       <c r="N5" s="21">
         <v>9.165159737E7</v>
@@ -1567,13 +1567,13 @@
       <c r="S5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="5"/>
+      <c r="V5" s="3"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="L6" s="22"/>
-      <c r="V6" s="5"/>
+      <c r="V6" s="3"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="23"/>
@@ -1592,50 +1592,50 @@
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
       <c r="P7" s="28"/>
-      <c r="V7" s="5"/>
+      <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
       <c r="C8" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J8" s="29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K8" s="29" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L8" s="31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O8" s="29"/>
       <c r="P8" s="28"/>
-      <c r="V8" s="5"/>
+      <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="23"/>
@@ -1643,30 +1643,30 @@
       <c r="C9" s="32">
         <v>1.0</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="35">
+      <c r="D9" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="36">
         <v>594.0</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="37">
         <v>45740.0</v>
       </c>
-      <c r="H9" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36">
+      <c r="H9" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37">
         <v>45778.0</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="38">
         <v>748504.24</v>
       </c>
-      <c r="L9" s="35" t="s">
-        <v>76</v>
+      <c r="L9" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
@@ -1675,36 +1675,36 @@
       <c r="N9" s="40"/>
       <c r="O9" s="25"/>
       <c r="P9" s="28"/>
-      <c r="V9" s="5"/>
+      <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
       <c r="C10" s="41"/>
-      <c r="D10" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="35">
+      <c r="D10" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="36">
         <v>620.0</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <v>45775.0</v>
       </c>
-      <c r="H10" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36">
+      <c r="H10" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37">
         <v>45806.0</v>
       </c>
-      <c r="K10" s="37">
+      <c r="K10" s="38">
         <v>1110378.24</v>
       </c>
-      <c r="L10" s="35" t="s">
-        <v>89</v>
+      <c r="L10" s="36" t="s">
+        <v>99</v>
       </c>
       <c r="M10" s="39">
         <f t="shared" si="1"/>
@@ -1713,36 +1713,36 @@
       <c r="N10" s="42"/>
       <c r="O10" s="25"/>
       <c r="P10" s="28"/>
-      <c r="V10" s="5"/>
+      <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="41"/>
-      <c r="D11" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="D11" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="36">
         <v>634.0</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <v>45799.0</v>
       </c>
-      <c r="H11" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36">
+      <c r="H11" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37">
         <v>45844.0</v>
       </c>
-      <c r="K11" s="37">
+      <c r="K11" s="38">
         <v>974557.12</v>
       </c>
-      <c r="L11" s="34" t="s">
-        <v>97</v>
+      <c r="L11" s="35" t="s">
+        <v>112</v>
       </c>
       <c r="M11" s="39">
         <v>974557.12</v>
@@ -1750,110 +1750,110 @@
       <c r="N11" s="42"/>
       <c r="O11" s="25"/>
       <c r="P11" s="28"/>
-      <c r="V11" s="5"/>
+      <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="41"/>
-      <c r="D12" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="34">
+      <c r="D12" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="35">
         <v>660.0</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <v>45856.0</v>
       </c>
-      <c r="H12" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36">
+      <c r="H12" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37">
         <v>45891.0</v>
       </c>
-      <c r="K12" s="45">
+      <c r="K12" s="46">
         <v>1402001.34</v>
       </c>
-      <c r="L12" s="46" t="s">
-        <v>103</v>
+      <c r="L12" s="47" t="s">
+        <v>122</v>
       </c>
       <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
-      <c r="N12" s="47"/>
+      <c r="N12" s="48"/>
       <c r="O12" s="25"/>
       <c r="P12" s="28"/>
-      <c r="V12" s="5"/>
+      <c r="V12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="41"/>
-      <c r="D13" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="35">
+      <c r="D13" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="36">
         <v>661.0</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <v>45856.0</v>
       </c>
-      <c r="H13" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43">
+      <c r="H13" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44">
         <v>45891.0</v>
       </c>
-      <c r="K13" s="45">
+      <c r="K13" s="46">
         <v>1223702.3</v>
       </c>
-      <c r="L13" s="34" t="s">
-        <v>111</v>
+      <c r="L13" s="35" t="s">
+        <v>134</v>
       </c>
       <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
-      <c r="N13" s="47"/>
+      <c r="N13" s="48"/>
       <c r="O13" s="25"/>
       <c r="P13" s="50"/>
-      <c r="V13" s="5"/>
+      <c r="V13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="41"/>
-      <c r="D14" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="34">
+      <c r="D14" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="35">
         <v>688.0</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="37">
         <v>45901.0</v>
       </c>
-      <c r="H14" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43">
+      <c r="H14" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44">
         <v>45938.0</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="46">
         <v>1011677.95</v>
       </c>
-      <c r="L14" s="34" t="s">
-        <v>123</v>
+      <c r="L14" s="35" t="s">
+        <v>140</v>
       </c>
       <c r="M14" s="39">
         <v>1011677.95</v>
@@ -1861,142 +1861,142 @@
       <c r="N14" s="42"/>
       <c r="O14" s="25"/>
       <c r="P14" s="28"/>
-      <c r="V14" s="5"/>
+      <c r="V14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="34">
+      <c r="D15" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="35">
         <v>696.0</v>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="37">
         <v>45923.0</v>
       </c>
-      <c r="H15" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43">
+      <c r="H15" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44">
         <v>45938.0</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="46">
         <v>896744.06</v>
       </c>
-      <c r="L15" s="34" t="s">
-        <v>130</v>
+      <c r="L15" s="35" t="s">
+        <v>146</v>
       </c>
       <c r="M15" s="39">
         <v>896744.06</v>
       </c>
-      <c r="N15" s="47"/>
+      <c r="N15" s="48"/>
       <c r="O15" s="25"/>
-      <c r="V15" s="5"/>
+      <c r="V15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="41"/>
-      <c r="D16" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="34">
+      <c r="D16" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" s="35">
         <v>704.0</v>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="37">
         <v>45957.0</v>
       </c>
-      <c r="H16" s="34" t="s">
-        <v>135</v>
-      </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43">
+      <c r="H16" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44">
         <v>46003.0</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="46">
         <v>919329.06</v>
       </c>
-      <c r="L16" s="34" t="s">
-        <v>136</v>
+      <c r="L16" s="35" t="s">
+        <v>149</v>
       </c>
       <c r="M16" s="39">
         <v>919329.06</v>
       </c>
       <c r="N16" s="42"/>
       <c r="O16" s="25"/>
-      <c r="V16" s="5"/>
+      <c r="V16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
       <c r="C17" s="41"/>
-      <c r="D17" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34">
+      <c r="D17" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35">
         <v>705.0</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="44">
         <v>45972.0</v>
       </c>
-      <c r="H17" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="I17" s="34"/>
-      <c r="J17" s="43">
+      <c r="H17" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="I17" s="35"/>
+      <c r="J17" s="44">
         <v>46016.0</v>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="46">
         <v>1157009.26</v>
       </c>
-      <c r="L17" s="34" t="s">
-        <v>142</v>
+      <c r="L17" s="35" t="s">
+        <v>152</v>
       </c>
       <c r="M17" s="39">
         <v>1157009.26</v>
       </c>
       <c r="N17" s="51"/>
       <c r="O17" s="25"/>
-      <c r="V17" s="5"/>
+      <c r="V17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
       <c r="C18" s="41"/>
-      <c r="D18" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="34">
+      <c r="D18" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="35">
         <v>728.0</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <v>46008.0</v>
       </c>
-      <c r="H18" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="I18" s="34"/>
-      <c r="J18" s="43">
+      <c r="H18" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="35"/>
+      <c r="J18" s="44">
         <v>46040.0</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="46">
         <v>1214597.952</v>
       </c>
-      <c r="L18" s="34" t="s">
-        <v>151</v>
+      <c r="L18" s="35" t="s">
+        <v>155</v>
       </c>
       <c r="M18" s="39">
         <v>1214597.952</v>
@@ -2013,29 +2013,29 @@
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
       <c r="C19" s="41"/>
-      <c r="D19" s="48" t="s">
-        <v>154</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="34">
+      <c r="D19" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="35">
         <v>278.0</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="44">
         <v>46042.0</v>
       </c>
-      <c r="H19" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43">
+      <c r="H19" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44">
         <v>46074.0</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="46">
         <v>967082.09</v>
       </c>
-      <c r="L19" s="34" t="s">
+      <c r="L19" s="35" t="s">
         <v>158</v>
       </c>
       <c r="M19" s="39">
@@ -2053,27 +2053,27 @@
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
       <c r="C20" s="41"/>
-      <c r="D20" s="48" t="s">
+      <c r="D20" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34">
+      <c r="E20" s="35"/>
+      <c r="F20" s="35">
         <v>10.0</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="44">
         <v>46078.0</v>
       </c>
-      <c r="H20" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43">
+      <c r="H20" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44">
         <v>46106.0</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="46">
         <v>719561.08</v>
       </c>
-      <c r="L20" s="34" t="s">
+      <c r="L20" s="35" t="s">
         <v>160</v>
       </c>
       <c r="M20" s="39">
@@ -2091,27 +2091,27 @@
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
       <c r="C21" s="41"/>
-      <c r="D21" s="48" t="s">
+      <c r="D21" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34">
+      <c r="E21" s="35"/>
+      <c r="F21" s="35">
         <v>15.0</v>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="44">
         <v>46094.0</v>
       </c>
-      <c r="H21" s="34" t="s">
+      <c r="H21" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43">
+      <c r="I21" s="44"/>
+      <c r="J21" s="44">
         <v>46128.0</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="46">
         <v>885881.08</v>
       </c>
-      <c r="L21" s="34" t="s">
+      <c r="L21" s="35" t="s">
         <v>163</v>
       </c>
       <c r="M21" s="39">
@@ -2129,27 +2129,27 @@
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
       <c r="C22" s="41"/>
-      <c r="D22" s="48" t="s">
+      <c r="D22" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34">
+      <c r="E22" s="35"/>
+      <c r="F22" s="35">
         <v>28.0</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <v>46128.0</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43">
+      <c r="I22" s="44"/>
+      <c r="J22" s="44">
         <v>46164.0</v>
       </c>
-      <c r="K22" s="45" t="s">
+      <c r="K22" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="34" t="s">
+      <c r="L22" s="35" t="s">
         <v>167</v>
       </c>
       <c r="M22" s="39" t="s">
@@ -2167,27 +2167,27 @@
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="41"/>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34">
+      <c r="E23" s="35"/>
+      <c r="F23" s="35">
         <v>33.0</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="44">
         <v>46156.0</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43">
+      <c r="I23" s="44"/>
+      <c r="J23" s="44">
         <v>46191.0</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="46">
         <v>1108954.4358333333</v>
       </c>
-      <c r="L23" s="34" t="s">
+      <c r="L23" s="35" t="s">
         <v>163</v>
       </c>
       <c r="M23" s="39">
@@ -2205,27 +2205,27 @@
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
       <c r="C24" s="41"/>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34">
+      <c r="E24" s="35"/>
+      <c r="F24" s="35">
         <v>29.0</v>
       </c>
-      <c r="G24" s="43">
+      <c r="G24" s="44">
         <v>46149.0</v>
       </c>
-      <c r="H24" s="34" t="s">
+      <c r="H24" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43">
+      <c r="I24" s="44"/>
+      <c r="J24" s="44">
         <v>46185.0</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="46">
         <v>218206.1</v>
       </c>
-      <c r="L24" s="34" t="s">
+      <c r="L24" s="35" t="s">
         <v>171</v>
       </c>
       <c r="M24" s="39">
@@ -2243,27 +2243,27 @@
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
       <c r="C25" s="41"/>
-      <c r="D25" s="48" t="s">
+      <c r="D25" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34">
+      <c r="E25" s="35"/>
+      <c r="F25" s="35">
         <v>40.0</v>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="44">
         <v>46156.0</v>
       </c>
-      <c r="H25" s="34" t="s">
+      <c r="H25" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43">
+      <c r="I25" s="44"/>
+      <c r="J25" s="44">
         <v>46191.0</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="46">
         <v>1549250.84</v>
       </c>
-      <c r="L25" s="34" t="s">
+      <c r="L25" s="35" t="s">
         <v>173</v>
       </c>
       <c r="M25" s="39">
@@ -2281,27 +2281,27 @@
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
       <c r="C26" s="55"/>
-      <c r="D26" s="48" t="s">
+      <c r="D26" s="49" t="s">
         <v>174</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34">
+      <c r="E26" s="35"/>
+      <c r="F26" s="35">
         <v>48.0</v>
       </c>
-      <c r="G26" s="43">
+      <c r="G26" s="44">
         <v>46230.0</v>
       </c>
-      <c r="H26" s="34" t="s">
+      <c r="H26" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43">
+      <c r="I26" s="44"/>
+      <c r="J26" s="44">
         <v>46262.0</v>
       </c>
-      <c r="K26" s="45" t="s">
+      <c r="K26" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="L26" s="34" t="s">
+      <c r="L26" s="35" t="s">
         <v>177</v>
       </c>
       <c r="M26" s="39" t="s">
@@ -2319,34 +2319,34 @@
       <c r="A27" s="23"/>
       <c r="B27" s="23"/>
       <c r="C27" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G27" s="29"/>
       <c r="H27" s="29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
       <c r="K27" s="56" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L27" s="31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M27" s="57" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="O27" s="25"/>
       <c r="P27" s="28"/>
@@ -2372,24 +2372,24 @@
       <c r="D28" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35">
+      <c r="E28" s="36"/>
+      <c r="F28" s="36">
         <v>402.0</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="37">
         <v>45791.0</v>
       </c>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36">
+      <c r="I28" s="37"/>
+      <c r="J28" s="37">
         <v>45834.0</v>
       </c>
-      <c r="K28" s="37">
+      <c r="K28" s="38">
         <v>188246.17</v>
       </c>
-      <c r="L28" s="34" t="s">
+      <c r="L28" s="35" t="s">
         <v>179</v>
       </c>
       <c r="M28" s="59">
@@ -2422,23 +2422,23 @@
       <c r="E29" s="60">
         <v>46.0</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="36">
         <v>447.0</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="37">
         <v>45814.0</v>
       </c>
-      <c r="H29" s="34" t="s">
+      <c r="H29" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43">
+      <c r="I29" s="44"/>
+      <c r="J29" s="44">
         <v>45955.0</v>
       </c>
-      <c r="K29" s="37">
+      <c r="K29" s="38">
         <v>112720.77</v>
       </c>
-      <c r="L29" s="34" t="s">
+      <c r="L29" s="35" t="s">
         <v>182</v>
       </c>
       <c r="M29" s="39">
@@ -2471,23 +2471,23 @@
       <c r="E30" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>529.0</v>
       </c>
       <c r="G30" s="63">
         <v>45853.0</v>
       </c>
-      <c r="H30" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43">
+      <c r="H30" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44">
         <v>45939.0</v>
       </c>
-      <c r="K30" s="45">
+      <c r="K30" s="46">
         <v>378307.61</v>
       </c>
-      <c r="L30" s="34" t="s">
+      <c r="L30" s="35" t="s">
         <v>185</v>
       </c>
       <c r="M30" s="39">
@@ -2520,23 +2520,23 @@
       <c r="E31" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <v>691.0</v>
       </c>
       <c r="G31" s="63">
         <v>45910.0</v>
       </c>
-      <c r="H31" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43">
+      <c r="H31" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44">
         <v>45941.0</v>
       </c>
-      <c r="K31" s="37">
+      <c r="K31" s="38">
         <v>3315.0471000000252</v>
       </c>
-      <c r="L31" s="34" t="s">
+      <c r="L31" s="35" t="s">
         <v>187</v>
       </c>
       <c r="M31" s="39">
@@ -2569,23 +2569,23 @@
       <c r="E32" s="65">
         <v>135.0</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="35">
         <v>677.0</v>
       </c>
       <c r="G32" s="63">
         <v>45904.0</v>
       </c>
-      <c r="H32" s="34" t="s">
-        <v>71</v>
+      <c r="H32" s="35" t="s">
+        <v>68</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K32" s="45">
+      <c r="K32" s="46">
         <v>198332.75</v>
       </c>
-      <c r="L32" s="34" t="s">
+      <c r="L32" s="35" t="s">
         <v>189</v>
       </c>
       <c r="M32" s="39">
@@ -2618,20 +2618,20 @@
       <c r="E33" s="65">
         <v>40.0</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>278.0</v>
       </c>
       <c r="G33" s="63">
         <v>46008.0</v>
       </c>
-      <c r="H33" s="34" t="s">
-        <v>120</v>
+      <c r="H33" s="35" t="s">
+        <v>113</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
         <v>46066.0</v>
       </c>
-      <c r="K33" s="45">
+      <c r="K33" s="46">
         <v>1528.62</v>
       </c>
       <c r="L33" s="67" t="s">
@@ -2667,23 +2667,23 @@
       <c r="E34" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>748.0</v>
       </c>
       <c r="G34" s="63">
         <v>45930.0</v>
       </c>
-      <c r="H34" s="34" t="s">
-        <v>94</v>
+      <c r="H34" s="35" t="s">
+        <v>90</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="46">
         <v>38718.58</v>
       </c>
-      <c r="L34" s="34" t="s">
+      <c r="L34" s="35" t="s">
         <v>195</v>
       </c>
       <c r="M34" s="59" t="s">
@@ -2716,23 +2716,23 @@
       <c r="E35" s="65">
         <v>154.0</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>822.0</v>
       </c>
       <c r="G35" s="63">
         <v>45968.0</v>
       </c>
-      <c r="H35" s="34" t="s">
-        <v>112</v>
+      <c r="H35" s="35" t="s">
+        <v>105</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K35" s="45">
+      <c r="K35" s="46">
         <v>133124.11</v>
       </c>
-      <c r="L35" s="34" t="s">
+      <c r="L35" s="35" t="s">
         <v>198</v>
       </c>
       <c r="M35" s="59" t="s">
@@ -2772,16 +2772,16 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
         <v>46075.0</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="46">
         <v>11372.9</v>
       </c>
-      <c r="L36" s="34" t="s">
+      <c r="L36" s="35" t="s">
         <v>201</v>
       </c>
       <c r="M36" s="39">
@@ -2819,8 +2819,8 @@
         <v>203</v>
       </c>
       <c r="J37" s="69"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="34"/>
+      <c r="K37" s="46"/>
+      <c r="L37" s="35"/>
       <c r="M37" s="39"/>
       <c r="N37" s="51">
         <v>15854.78</v>
@@ -2856,8 +2856,8 @@
         <v>203</v>
       </c>
       <c r="J38" s="69"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="34"/>
+      <c r="K38" s="46"/>
+      <c r="L38" s="35"/>
       <c r="M38" s="39"/>
       <c r="N38" s="51" t="s">
         <v>205</v>
@@ -2895,13 +2895,13 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
         <v>46106.0</v>
       </c>
-      <c r="K39" s="45">
+      <c r="K39" s="46">
         <v>27801.11</v>
       </c>
       <c r="L39" s="71" t="s">
@@ -2942,23 +2942,23 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
         <v>46233.0</v>
       </c>
-      <c r="K40" s="45">
+      <c r="K40" s="46">
         <v>58868.35</v>
       </c>
-      <c r="L40" s="34" t="s">
-        <v>65</v>
+      <c r="L40" s="35" t="s">
+        <v>67</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
       </c>
       <c r="N40" s="51"/>
-      <c r="V40" s="5"/>
+      <c r="V40" s="3"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="15"/>
@@ -2966,7 +2966,7 @@
       <c r="C41" s="41"/>
       <c r="K41" s="73"/>
       <c r="M41" s="73"/>
-      <c r="V41" s="5"/>
+      <c r="V41" s="3"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="15"/>
@@ -2974,31 +2974,31 @@
       <c r="C42" s="41"/>
       <c r="K42" s="73"/>
       <c r="M42" s="73"/>
-      <c r="V42" s="5"/>
+      <c r="V42" s="3"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
       <c r="C43" s="41"/>
-      <c r="V43" s="5"/>
+      <c r="V43" s="3"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
       <c r="C44" s="41"/>
-      <c r="V44" s="5"/>
+      <c r="V44" s="3"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
       <c r="C45" s="41"/>
-      <c r="V45" s="5"/>
+      <c r="V45" s="3"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
       <c r="C46" s="41"/>
-      <c r="V46" s="5"/>
+      <c r="V46" s="3"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="15"/>
@@ -3006,7 +3006,7 @@
       <c r="C47" s="55"/>
       <c r="K47" s="73"/>
       <c r="M47" s="73"/>
-      <c r="V47" s="5"/>
+      <c r="V47" s="3"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="15"/>
@@ -3030,7 +3030,7 @@
       <c r="S48" s="74"/>
       <c r="T48" s="74"/>
       <c r="U48" s="74"/>
-      <c r="V48" s="5"/>
+      <c r="V48" s="3"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="15"/>
@@ -7911,10 +7911,10 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="AB2" s="2"/>
@@ -7926,40 +7926,40 @@
       <c r="AH2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="11">
         <v>2.5E32</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="12">
         <v>45686.0</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="10">
         <v>12.0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="14">
         <v>1000.0</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="14">
         <v>1000.0</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="10">
         <v>0.0</v>
       </c>
       <c r="AB3" s="2"/>
@@ -7971,40 +7971,40 @@
       <c r="AH3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="10">
         <v>12.0</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="14">
         <v>52250.04</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="14">
         <v>52250.04</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="10">
         <v>0.0</v>
       </c>
       <c r="AB4" s="2"/>
@@ -8016,40 +8016,40 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="A5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="10">
         <v>12.0</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="14">
         <v>881914.18</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="14">
         <v>881914.18</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="10">
         <v>0.0</v>
       </c>
       <c r="AB5" s="2"/>
@@ -8061,40 +8061,40 @@
       <c r="AH5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="A6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="12">
         <v>45762.0</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="10">
         <v>12.0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <v>750000.0</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="14">
         <v>750000.0</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="10">
         <v>0.0</v>
       </c>
       <c r="AB6" s="2"/>
@@ -8106,40 +8106,40 @@
       <c r="AH6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="A7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="12">
         <v>45763.0</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="10">
         <v>12.0</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" s="13">
+      <c r="I7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="14">
         <v>949835.78</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="14">
         <v>949835.78</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="10">
         <v>0.0</v>
       </c>
       <c r="AB7" s="2"/>
@@ -8151,40 +8151,40 @@
       <c r="AH7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="12">
         <v>45763.0</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="10">
         <v>12.0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <v>524584.95</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="14">
         <v>524584.95</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="10">
         <v>0.0</v>
       </c>
       <c r="O8" s="26"/>
@@ -8197,40 +8197,40 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="12">
         <v>45792.0</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="10">
         <v>12.0</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="13">
+      <c r="I9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="14">
         <v>211614.23</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="14">
         <v>211614.23</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="10">
         <v>0.0</v>
       </c>
       <c r="AB9" s="2"/>
@@ -8242,40 +8242,40 @@
       <c r="AH9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="12">
         <v>45825.0</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="10">
         <v>12.0</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <v>2391157.42</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="14">
         <v>2391157.41</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="14">
         <v>0.01</v>
       </c>
       <c r="AB10" s="2"/>
@@ -8287,40 +8287,40 @@
       <c r="AH10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="7" t="s">
+      <c r="A11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="12">
         <v>45825.0</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="10">
         <v>12.0</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="14">
         <v>618154.39</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="14">
         <v>618154.38</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="10">
         <v>0.01</v>
       </c>
       <c r="AB11" s="2"/>
@@ -8332,40 +8332,40 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="12">
         <v>45832.0</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="10">
         <v>12.0</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="13">
+      <c r="I12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12" s="14">
         <v>1600334.09</v>
       </c>
-      <c r="K12" s="13">
+      <c r="K12" s="14">
         <v>1600334.09</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="10">
         <v>0.0</v>
       </c>
       <c r="AB12" s="2"/>
@@ -8377,43 +8377,43 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="A13" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="12">
         <v>45863.0</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="10">
         <v>12.0</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <v>2364771.07</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="14">
         <v>2364771.07</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="14">
         <v>0.0</v>
       </c>
-      <c r="M13" s="38"/>
+      <c r="M13" s="33"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8423,40 +8423,40 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="12">
         <v>45887.0</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="10">
         <v>12.0</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14" s="13">
+      <c r="I14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J14" s="14">
         <v>968237.39</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="14">
         <v>968237.39</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="10">
         <v>0.0</v>
       </c>
       <c r="AB14" s="2"/>
@@ -8468,40 +8468,40 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="12">
         <v>45924.0</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="10">
         <v>12.0</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J15" s="13">
+      <c r="I15" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="14">
         <v>1011677.95</v>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="14">
         <v>1011677.95</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="10">
         <v>0.0</v>
       </c>
       <c r="AB15" s="2"/>
@@ -8513,40 +8513,40 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="12">
         <v>45929.0</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="10">
         <v>12.0</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="14">
         <v>1580293.02</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="14">
         <v>1580293.02</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="14">
         <v>0.0</v>
       </c>
       <c r="AB16" s="2"/>
@@ -8558,40 +8558,40 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="A17" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E17" s="12">
         <v>45930.0</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="10">
         <v>12.0</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="14">
         <v>34065.36</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="10">
         <v>0.0</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L17" s="14">
         <v>34065.36</v>
       </c>
       <c r="AB17" s="2"/>
@@ -8603,40 +8603,40 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="A18" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E18" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="10">
         <v>12.0</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="J18" s="13">
+      <c r="I18" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="14">
         <v>63746.85</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="14">
         <v>63746.85</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="10">
         <v>0.0</v>
       </c>
       <c r="AB18" s="2"/>
@@ -8648,40 +8648,40 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="A19" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E19" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="10">
         <v>12.0</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" s="13">
+      <c r="I19" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="14">
         <v>947931.1</v>
       </c>
-      <c r="K19" s="13">
+      <c r="K19" s="14">
         <v>947931.1</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="10">
         <v>0.0</v>
       </c>
       <c r="AB19" s="2"/>
@@ -8693,40 +8693,40 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="A20" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E20" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="10">
         <v>12.0</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I20" s="7">
+      <c r="I20" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="14">
         <v>259790.57</v>
       </c>
-      <c r="K20" s="13">
+      <c r="K20" s="14">
         <v>259790.57</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="10">
         <v>0.0</v>
       </c>
       <c r="AB20" s="2"/>
@@ -8738,40 +8738,40 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="7" t="s">
+      <c r="A21" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E21" s="12">
         <v>45938.0</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="10">
         <v>12.0</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I21" s="7">
+      <c r="I21" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="14">
         <v>170479.3</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="14">
         <v>170479.3</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="10">
         <v>0.0</v>
       </c>
       <c r="AB21" s="2"/>
@@ -8783,40 +8783,40 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="7" t="s">
+      <c r="A22" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="10">
         <v>12.0</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="10">
         <v>2000.0</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="14">
         <v>1500000.0</v>
       </c>
-      <c r="K22" s="13">
+      <c r="K22" s="14">
         <v>1500000.0</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="14">
         <v>0.0</v>
       </c>
       <c r="AB22" s="2"/>
@@ -8828,40 +8828,40 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="A23" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="49">
+      <c r="E23" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="10">
         <v>12.0</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="13">
+      <c r="I23" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" s="14">
         <v>1000001.64</v>
       </c>
-      <c r="K23" s="13">
+      <c r="K23" s="14">
         <v>1000001.64</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="10">
         <v>0.0</v>
       </c>
       <c r="AB23" s="2"/>
@@ -8873,40 +8873,40 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="A24" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="10">
         <v>12.0</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I24" s="7">
+      <c r="I24" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="14">
         <v>68405.66</v>
       </c>
-      <c r="K24" s="13">
+      <c r="K24" s="14">
         <v>68405.66</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="10">
         <v>0.0</v>
       </c>
       <c r="AB24" s="2"/>
@@ -8918,40 +8918,40 @@
       <c r="AH24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="7" t="s">
+      <c r="A25" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="49">
+      <c r="E25" s="43">
         <v>45975.0</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="10">
         <v>12.0</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I25" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J25" s="13">
+      <c r="I25" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J25" s="14">
         <v>1157673.06</v>
       </c>
-      <c r="K25" s="13">
+      <c r="K25" s="14">
         <v>1157673.06</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="10">
         <v>0.0</v>
       </c>
       <c r="AB25" s="2"/>
@@ -8963,40 +8963,40 @@
       <c r="AH25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B26" s="7" t="s">
+      <c r="A26" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="7" t="s">
+      <c r="C26" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="49">
+      <c r="E26" s="43">
         <v>45989.0</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="10">
         <v>12.0</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I26" s="7">
+      <c r="I26" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="14">
         <v>34065.36</v>
       </c>
-      <c r="K26" s="13">
+      <c r="K26" s="14">
         <v>34065.36</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="10">
         <v>0.0</v>
       </c>
       <c r="AB26" s="2"/>
@@ -9008,40 +9008,40 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D27" s="7" t="s">
+      <c r="A27" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E27" s="12">
         <v>46104.0</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="10">
         <v>12.0</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="14">
         <v>1770880.5</v>
       </c>
-      <c r="K27" s="13">
+      <c r="K27" s="14">
         <v>843261.89</v>
       </c>
-      <c r="L27" s="13">
+      <c r="L27" s="14">
         <v>927618.61</v>
       </c>
       <c r="AB27" s="2"/>
@@ -9053,40 +9053,40 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="A28" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E28" s="12">
         <v>46120.0</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="10">
         <v>12.0</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="14">
         <v>1912292.52</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="10">
         <v>0.0</v>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="14">
         <v>1912292.52</v>
       </c>
       <c r="AB28" s="2"/>
@@ -9098,40 +9098,40 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" s="7" t="s">
+      <c r="A29" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="12">
         <v>46196.0</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="10">
         <v>12.0</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="14">
         <v>1496713.48</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="10">
         <v>0.0</v>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="14">
         <v>1496713.48</v>
       </c>
       <c r="AB29" s="2"/>
@@ -9143,40 +9143,40 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="A30" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E30" s="12">
         <v>46205.0</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="10">
         <v>12.0</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I30" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="13">
+      <c r="I30" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="14">
         <v>624166.14</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="10">
         <v>0.0</v>
       </c>
-      <c r="L30" s="13">
+      <c r="L30" s="14">
         <v>624166.14</v>
       </c>
       <c r="AB30" s="2"/>
@@ -9188,40 +9188,40 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="A31" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E31" s="12">
         <v>46205.0</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="10">
         <v>12.0</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I31" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J31" s="13">
+      <c r="I31" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J31" s="14">
         <v>18462.36</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="10">
         <v>0.0</v>
       </c>
-      <c r="L31" s="13">
+      <c r="L31" s="14">
         <v>18462.36</v>
       </c>
       <c r="AB31" s="2"/>
@@ -9233,40 +9233,40 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="A32" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E32" s="12">
         <v>46213.0</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="10">
         <v>12.0</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J32" s="13">
+      <c r="I32" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="J32" s="14">
         <v>1530656.62</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32" s="10">
         <v>0.0</v>
       </c>
-      <c r="L32" s="13">
+      <c r="L32" s="14">
         <v>1530656.62</v>
       </c>
       <c r="AB32" s="2"/>
@@ -9278,40 +9278,40 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="7" t="s">
+      <c r="A33" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E33" s="12">
         <v>46227.0</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="10">
         <v>12.0</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="10">
         <v>339039.0</v>
       </c>
-      <c r="I33" s="7">
+      <c r="I33" s="10">
         <v>2048.0</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="14">
         <v>173846.38</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33" s="10">
         <v>0.0</v>
       </c>
-      <c r="L33" s="13">
+      <c r="L33" s="14">
         <v>173846.38</v>
       </c>
       <c r="AB33" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,12 +30,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="209">
   <si>
+    <t>Controle de pagamentos</t>
+  </si>
+  <si>
     <t>Saldo</t>
   </si>
   <si>
-    <t>Controle de pagamentos</t>
-  </si>
-  <si>
     <t>2025NE000005</t>
   </si>
   <si>
@@ -66,39 +66,39 @@
     <t>UG Responsável</t>
   </si>
   <si>
+    <t>UG Fiscalizadora</t>
+  </si>
+  <si>
+    <t>Prazo Final de Execução</t>
+  </si>
+  <si>
+    <t>Prazo Final de Vigência</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ação</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
     <t>2025NE000369</t>
   </si>
   <si>
-    <t>UG Fiscalizadora</t>
+    <t>Moeda</t>
   </si>
   <si>
     <t>C25516</t>
   </si>
   <si>
-    <t>Prazo Final de Execução</t>
+    <t>Valor Total do Contrato</t>
   </si>
   <si>
     <t>25E0387</t>
   </si>
   <si>
-    <t>Prazo Final de Vigência</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Ação</t>
-  </si>
-  <si>
-    <t>PAG</t>
-  </si>
-  <si>
-    <t>Moeda</t>
-  </si>
-  <si>
-    <t>Valor Total do Contrato</t>
-  </si>
-  <si>
     <t>Valor a Empenhar</t>
   </si>
   <si>
@@ -114,27 +114,27 @@
     <t>Fornecedor</t>
   </si>
   <si>
+    <t>Tipo Despesa /Receita</t>
+  </si>
+  <si>
+    <t>Abrir</t>
+  </si>
+  <si>
+    <t>Editar</t>
+  </si>
+  <si>
     <t>2025NE000371</t>
   </si>
   <si>
-    <t>Tipo Despesa /Receita</t>
-  </si>
-  <si>
-    <t>Abrir</t>
+    <t>005/CELOG-PAMALS/2025</t>
+  </si>
+  <si>
+    <t>CELOG</t>
   </si>
   <si>
     <t>25E0389</t>
   </si>
   <si>
-    <t>Editar</t>
-  </si>
-  <si>
-    <t>005/CELOG-PAMALS/2025</t>
-  </si>
-  <si>
-    <t>CELOG</t>
-  </si>
-  <si>
     <t>PAMALS</t>
   </si>
   <si>
@@ -147,24 +147,24 @@
     <t>67101.001510/2024-12</t>
   </si>
   <si>
+    <t>R$</t>
+  </si>
+  <si>
     <t>2025NE000413</t>
   </si>
   <si>
-    <t>R$</t>
-  </si>
-  <si>
     <t>C25501</t>
   </si>
   <si>
+    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
+  </si>
+  <si>
     <t>25E0403</t>
   </si>
   <si>
     <t>20SP</t>
   </si>
   <si>
-    <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
-  </si>
-  <si>
     <t>2025NE000414</t>
   </si>
   <si>
@@ -177,6 +177,15 @@
     <t>21EM</t>
   </si>
   <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>Referência</t>
+  </si>
+  <si>
+    <t>Nº recibo</t>
+  </si>
+  <si>
     <t>2025NE000559</t>
   </si>
   <si>
@@ -186,52 +195,55 @@
     <t>25E0524</t>
   </si>
   <si>
+    <t>Nº</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Empenho</t>
+  </si>
+  <si>
     <t>20X7</t>
   </si>
   <si>
-    <t>Módulo</t>
-  </si>
-  <si>
-    <t>Referência</t>
+    <t>Observações</t>
+  </si>
+  <si>
+    <t>Vencimento</t>
+  </si>
+  <si>
+    <t>Valor das Nfs</t>
+  </si>
+  <si>
+    <t>Ordem de Pagamento</t>
+  </si>
+  <si>
+    <t>Faturado</t>
   </si>
   <si>
     <t>2025NE000770</t>
   </si>
   <si>
+    <t>Pendente</t>
+  </si>
+  <si>
     <t>25E0731</t>
   </si>
   <si>
-    <t>Nº recibo</t>
-  </si>
-  <si>
-    <t>Nº</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Empenho</t>
-  </si>
-  <si>
     <t>2025NE000774</t>
   </si>
   <si>
-    <t>Observações</t>
-  </si>
-  <si>
     <t>25E0737</t>
   </si>
   <si>
-    <t>Vencimento</t>
-  </si>
-  <si>
-    <t>Valor das Nfs</t>
-  </si>
-  <si>
-    <t>Ordem de Pagamento</t>
-  </si>
-  <si>
-    <t>Faturado</t>
+    <t>FEV/25</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
     <t>2025NE000843</t>
@@ -240,37 +252,31 @@
     <t>C25630</t>
   </si>
   <si>
-    <t>Pendente</t>
-  </si>
-  <si>
     <t>25E0787</t>
   </si>
   <si>
     <t>219C</t>
   </si>
   <si>
+    <t>2025NP001980</t>
+  </si>
+  <si>
     <t>2025NE001065</t>
   </si>
   <si>
     <t>25E0999</t>
   </si>
   <si>
-    <t>FEV/25</t>
-  </si>
-  <si>
     <t>2025NE001200</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>C25590</t>
   </si>
   <si>
     <t>25E1128</t>
   </si>
   <si>
-    <t xml:space="preserve">2025NE000369 </t>
+    <t>MAR/25</t>
   </si>
   <si>
     <t>2025NE001598</t>
@@ -282,7 +288,10 @@
     <t>25E1446</t>
   </si>
   <si>
-    <t>2025NP001980</t>
+    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
+  </si>
+  <si>
+    <t>2025NP001979</t>
   </si>
   <si>
     <t>2025NE001627</t>
@@ -300,121 +309,43 @@
     <t>25E1477</t>
   </si>
   <si>
+    <t>ABR/25</t>
+  </si>
+  <si>
+    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
+  </si>
+  <si>
     <t>2025NE001687</t>
   </si>
   <si>
+    <t>2025NP002341</t>
+  </si>
+  <si>
     <t>25E1535</t>
   </si>
   <si>
+    <t>MAI/25</t>
+  </si>
+  <si>
     <t>2025NE001688</t>
   </si>
   <si>
     <t>25E1536</t>
   </si>
   <si>
-    <t>MAR/25</t>
-  </si>
-  <si>
     <t>2025NE001689</t>
   </si>
   <si>
+    <t>2025NP002884</t>
+  </si>
+  <si>
     <t>25E1537</t>
   </si>
   <si>
-    <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
-  </si>
-  <si>
     <t>2025NE001690</t>
   </si>
   <si>
-    <t>2025NP001979</t>
-  </si>
-  <si>
     <t>25E1538</t>
-  </si>
-  <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
-    <t>25E1666</t>
-  </si>
-  <si>
-    <t>ABR/25</t>
-  </si>
-  <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
-    <t>20YJ</t>
-  </si>
-  <si>
-    <t>2025NE000413, 2025NE000414, 2025NE000559</t>
-  </si>
-  <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
-    <t>25E1669</t>
-  </si>
-  <si>
-    <t>2025NP002341</t>
-  </si>
-  <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
-  </si>
-  <si>
-    <t>MAI/25</t>
-  </si>
-  <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
-  </si>
-  <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
-  </si>
-  <si>
-    <t>2025NP002884</t>
-  </si>
-  <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
   </si>
   <si>
     <t>JUN/25</t>
@@ -426,52 +357,64 @@
 2025NE000774</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
   </si>
   <si>
     <t>2025NP400522</t>
   </si>
   <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
+    <t>25E1666</t>
   </si>
   <si>
     <t>JUL/25</t>
   </si>
   <si>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
+    <t>20YJ</t>
+  </si>
+  <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
-    <t>26E0803</t>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
   </si>
   <si>
     <t>AGO/25</t>
   </si>
   <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
-    <t>26E0906</t>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
   </si>
   <si>
     <t>2025NP004558</t>
+  </si>
+  <si>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
   </si>
   <si>
     <t>SET/25</t>
@@ -481,25 +424,82 @@
 2025NE001828</t>
   </si>
   <si>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
+  </si>
+  <si>
     <t>2025NP004897</t>
   </si>
   <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
+  </si>
+  <si>
     <t>OUT/25</t>
   </si>
   <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
     <t>2025NP004932</t>
   </si>
   <si>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
+  </si>
+  <si>
+    <t>2026NE000817</t>
+  </si>
+  <si>
     <t>NOV/25</t>
   </si>
   <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
+  </si>
+  <si>
     <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
   </si>
   <si>
+    <t>2026NE000842</t>
+  </si>
+  <si>
     <t>2026NP400440</t>
+  </si>
+  <si>
+    <t>26E0803</t>
+  </si>
+  <si>
+    <t>2026NE000944</t>
+  </si>
+  <si>
+    <t>26E0906</t>
   </si>
   <si>
     <t>DEZ/25</t>
@@ -671,8 +671,8 @@
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
+    <numFmt numFmtId="169" formatCode="MM/DD/YY"/>
+    <numFmt numFmtId="170" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="171" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="12">
@@ -867,11 +867,11 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -931,14 +931,14 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -952,7 +952,6 @@
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -968,6 +967,7 @@
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -978,13 +978,10 @@
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -998,6 +995,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -1415,9 +1415,9 @@
       <c r="V1" s="3"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="5"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="7" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" s="8"/>
       <c r="W2" s="9"/>
@@ -1466,28 +1466,28 @@
         <v>11</v>
       </c>
       <c r="F4" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="J4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="16" t="s">
+      <c r="L4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" s="16" t="s">
+      <c r="M4" s="17" t="s">
         <v>21</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>22</v>
       </c>
       <c r="N4" s="17" t="s">
         <v>23</v>
@@ -1505,13 +1505,13 @@
         <v>27</v>
       </c>
       <c r="S4" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="T4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="T4" s="16" t="s">
+      <c r="U4" s="16" t="s">
         <v>30</v>
-      </c>
-      <c r="U4" s="16" t="s">
-        <v>32</v>
       </c>
       <c r="V4" s="3"/>
     </row>
@@ -1520,10 +1520,10 @@
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>33</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>34</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>35</v>
@@ -1547,7 +1547,7 @@
         <v>38</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N5" s="21">
         <v>9.165159737E7</v>
@@ -1565,7 +1565,7 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="V5" s="3"/>
     </row>
@@ -1587,54 +1587,54 @@
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
-      <c r="L7" s="27"/>
+      <c r="L7" s="26"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="28"/>
+      <c r="P7" s="27"/>
       <c r="V7" s="3"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
       <c r="C8" s="29" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="29" t="s">
+      <c r="I8" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="J8" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="K8" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="K8" s="29" t="s">
+      <c r="M8" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="N8" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>70</v>
-      </c>
       <c r="O8" s="29"/>
-      <c r="P8" s="28"/>
+      <c r="P8" s="27"/>
       <c r="V8" s="3"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
@@ -1643,30 +1643,30 @@
       <c r="C9" s="32">
         <v>1.0</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F9" s="36">
+      <c r="D9" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="35">
         <v>594.0</v>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="36">
         <v>45740.0</v>
       </c>
-      <c r="H9" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37">
+      <c r="H9" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36">
         <v>45778.0</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="37">
         <v>748504.24</v>
       </c>
-      <c r="L9" s="36" t="s">
-        <v>84</v>
+      <c r="L9" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
@@ -1674,37 +1674,37 @@
       </c>
       <c r="N9" s="40"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="28"/>
+      <c r="P9" s="27"/>
       <c r="V9" s="3"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
       <c r="C10" s="41"/>
-      <c r="D10" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="36">
+      <c r="D10" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="35">
         <v>620.0</v>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="36">
         <v>45775.0</v>
       </c>
-      <c r="H10" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37">
+      <c r="H10" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36">
         <v>45806.0</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="37">
         <v>1110378.24</v>
       </c>
-      <c r="L10" s="36" t="s">
-        <v>99</v>
+      <c r="L10" s="35" t="s">
+        <v>87</v>
       </c>
       <c r="M10" s="39">
         <f t="shared" si="1"/>
@@ -1712,116 +1712,116 @@
       </c>
       <c r="N10" s="42"/>
       <c r="O10" s="25"/>
-      <c r="P10" s="28"/>
+      <c r="P10" s="27"/>
       <c r="V10" s="3"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="41"/>
-      <c r="D11" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" s="36">
+      <c r="D11" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="35">
         <v>634.0</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <v>45799.0</v>
       </c>
-      <c r="H11" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="I11" s="37"/>
-      <c r="J11" s="37">
+      <c r="H11" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36">
         <v>45844.0</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="37">
         <v>974557.12</v>
       </c>
-      <c r="L11" s="35" t="s">
-        <v>112</v>
+      <c r="L11" s="34" t="s">
+        <v>96</v>
       </c>
       <c r="M11" s="39">
         <v>974557.12</v>
       </c>
       <c r="N11" s="42"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="28"/>
+      <c r="P11" s="27"/>
       <c r="V11" s="3"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
       <c r="C12" s="41"/>
-      <c r="D12" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" s="35">
+      <c r="D12" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="34">
         <v>660.0</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="43">
         <v>45856.0</v>
       </c>
-      <c r="H12" s="45" t="s">
-        <v>68</v>
-      </c>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37">
+      <c r="H12" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36">
         <v>45891.0</v>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="45">
         <v>1402001.34</v>
       </c>
-      <c r="L12" s="47" t="s">
-        <v>122</v>
+      <c r="L12" s="46" t="s">
+        <v>102</v>
       </c>
       <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
-      <c r="N12" s="48"/>
+      <c r="N12" s="47"/>
       <c r="O12" s="25"/>
-      <c r="P12" s="28"/>
+      <c r="P12" s="27"/>
       <c r="V12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
       <c r="C13" s="41"/>
-      <c r="D13" s="49" t="s">
-        <v>129</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="36">
+      <c r="D13" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="35">
         <v>661.0</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <v>45856.0</v>
       </c>
-      <c r="H13" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44">
+      <c r="H13" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43">
         <v>45891.0</v>
       </c>
-      <c r="K13" s="46">
+      <c r="K13" s="45">
         <v>1223702.3</v>
       </c>
-      <c r="L13" s="35" t="s">
-        <v>134</v>
+      <c r="L13" s="34" t="s">
+        <v>110</v>
       </c>
       <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
-      <c r="N13" s="48"/>
+      <c r="N13" s="47"/>
       <c r="O13" s="25"/>
       <c r="P13" s="50"/>
       <c r="V13" s="3"/>
@@ -1830,72 +1830,72 @@
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
       <c r="C14" s="41"/>
-      <c r="D14" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F14" s="35">
+      <c r="D14" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="34">
         <v>688.0</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="36">
         <v>45901.0</v>
       </c>
-      <c r="H14" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44">
+      <c r="H14" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="45">
         <v>1011677.95</v>
       </c>
-      <c r="L14" s="35" t="s">
-        <v>140</v>
+      <c r="L14" s="34" t="s">
+        <v>118</v>
       </c>
       <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
       <c r="N14" s="42"/>
       <c r="O14" s="25"/>
-      <c r="P14" s="28"/>
+      <c r="P14" s="27"/>
       <c r="V14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
       <c r="C15" s="41"/>
-      <c r="D15" s="49" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="35">
+      <c r="D15" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="34">
         <v>696.0</v>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="36">
         <v>45923.0</v>
       </c>
-      <c r="H15" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44">
+      <c r="H15" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43">
         <v>45938.0</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="45">
         <v>896744.06</v>
       </c>
-      <c r="L15" s="35" t="s">
-        <v>146</v>
+      <c r="L15" s="34" t="s">
+        <v>125</v>
       </c>
       <c r="M15" s="39">
         <v>896744.06</v>
       </c>
-      <c r="N15" s="48"/>
+      <c r="N15" s="47"/>
       <c r="O15" s="25"/>
       <c r="V15" s="3"/>
     </row>
@@ -1903,30 +1903,30 @@
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="41"/>
-      <c r="D16" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F16" s="35">
+      <c r="D16" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="34">
         <v>704.0</v>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="36">
         <v>45957.0</v>
       </c>
-      <c r="H16" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44">
+      <c r="H16" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43">
         <v>46003.0</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="45">
         <v>919329.06</v>
       </c>
-      <c r="L16" s="35" t="s">
-        <v>149</v>
+      <c r="L16" s="34" t="s">
+        <v>133</v>
       </c>
       <c r="M16" s="39">
         <v>919329.06</v>
@@ -1939,28 +1939,28 @@
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
       <c r="C17" s="41"/>
-      <c r="D17" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35">
+      <c r="D17" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34">
         <v>705.0</v>
       </c>
-      <c r="G17" s="44">
+      <c r="G17" s="43">
         <v>45972.0</v>
       </c>
-      <c r="H17" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="I17" s="35"/>
-      <c r="J17" s="44">
+      <c r="H17" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="34"/>
+      <c r="J17" s="43">
         <v>46016.0</v>
       </c>
-      <c r="K17" s="46">
+      <c r="K17" s="45">
         <v>1157009.26</v>
       </c>
-      <c r="L17" s="35" t="s">
-        <v>152</v>
+      <c r="L17" s="34" t="s">
+        <v>142</v>
       </c>
       <c r="M17" s="39">
         <v>1157009.26</v>
@@ -1973,69 +1973,69 @@
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
       <c r="C18" s="41"/>
-      <c r="D18" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18" s="35">
+      <c r="D18" s="48" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="34">
         <v>728.0</v>
       </c>
-      <c r="G18" s="44">
+      <c r="G18" s="43">
         <v>46008.0</v>
       </c>
-      <c r="H18" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="I18" s="35"/>
-      <c r="J18" s="44">
+      <c r="H18" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="43">
         <v>46040.0</v>
       </c>
-      <c r="K18" s="46">
+      <c r="K18" s="45">
         <v>1214597.952</v>
       </c>
-      <c r="L18" s="35" t="s">
-        <v>155</v>
+      <c r="L18" s="34" t="s">
+        <v>152</v>
       </c>
       <c r="M18" s="39">
         <v>1214597.952</v>
       </c>
       <c r="N18" s="51"/>
       <c r="O18" s="25"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="28"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+      <c r="U18" s="27"/>
       <c r="V18" s="52"/>
     </row>
     <row r="19">
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
       <c r="C19" s="41"/>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="E19" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="35">
+      <c r="E19" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="34">
         <v>278.0</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="43">
         <v>46042.0</v>
       </c>
-      <c r="H19" s="35" t="s">
+      <c r="H19" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44">
+      <c r="I19" s="43"/>
+      <c r="J19" s="43">
         <v>46074.0</v>
       </c>
-      <c r="K19" s="46">
+      <c r="K19" s="45">
         <v>967082.09</v>
       </c>
-      <c r="L19" s="35" t="s">
+      <c r="L19" s="34" t="s">
         <v>158</v>
       </c>
       <c r="M19" s="39">
@@ -2043,37 +2043,37 @@
       </c>
       <c r="N19" s="51"/>
       <c r="O19" s="25"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+      <c r="U19" s="27"/>
       <c r="V19" s="52"/>
     </row>
     <row r="20">
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
       <c r="C20" s="41"/>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35">
+      <c r="E20" s="34"/>
+      <c r="F20" s="34">
         <v>10.0</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G20" s="43">
         <v>46078.0</v>
       </c>
-      <c r="H20" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44">
+      <c r="H20" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43">
         <v>46106.0</v>
       </c>
-      <c r="K20" s="46">
+      <c r="K20" s="45">
         <v>719561.08</v>
       </c>
-      <c r="L20" s="35" t="s">
+      <c r="L20" s="34" t="s">
         <v>160</v>
       </c>
       <c r="M20" s="39">
@@ -2081,37 +2081,37 @@
       </c>
       <c r="N20" s="51"/>
       <c r="O20" s="25"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
       <c r="V20" s="52"/>
     </row>
     <row r="21">
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
       <c r="C21" s="41"/>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35">
+      <c r="E21" s="34"/>
+      <c r="F21" s="34">
         <v>15.0</v>
       </c>
-      <c r="G21" s="44">
+      <c r="G21" s="43">
         <v>46094.0</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44">
+      <c r="I21" s="43"/>
+      <c r="J21" s="43">
         <v>46128.0</v>
       </c>
-      <c r="K21" s="46">
+      <c r="K21" s="45">
         <v>885881.08</v>
       </c>
-      <c r="L21" s="35" t="s">
+      <c r="L21" s="34" t="s">
         <v>163</v>
       </c>
       <c r="M21" s="39">
@@ -2119,37 +2119,37 @@
       </c>
       <c r="N21" s="51"/>
       <c r="O21" s="25"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="28"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+      <c r="U21" s="27"/>
       <c r="V21" s="52"/>
     </row>
     <row r="22">
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
       <c r="C22" s="41"/>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35">
+      <c r="E22" s="34"/>
+      <c r="F22" s="34">
         <v>28.0</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G22" s="43">
         <v>46128.0</v>
       </c>
-      <c r="H22" s="35" t="s">
+      <c r="H22" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44">
+      <c r="I22" s="43"/>
+      <c r="J22" s="43">
         <v>46164.0</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="35" t="s">
+      <c r="L22" s="34" t="s">
         <v>167</v>
       </c>
       <c r="M22" s="39" t="s">
@@ -2157,37 +2157,37 @@
       </c>
       <c r="N22" s="51"/>
       <c r="O22" s="25"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
       <c r="V22" s="52"/>
     </row>
     <row r="23">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="41"/>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35">
+      <c r="E23" s="34"/>
+      <c r="F23" s="34">
         <v>33.0</v>
       </c>
-      <c r="G23" s="44">
+      <c r="G23" s="43">
         <v>46156.0</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H23" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44">
+      <c r="I23" s="43"/>
+      <c r="J23" s="43">
         <v>46191.0</v>
       </c>
-      <c r="K23" s="46">
+      <c r="K23" s="45">
         <v>1108954.4358333333</v>
       </c>
-      <c r="L23" s="35" t="s">
+      <c r="L23" s="34" t="s">
         <v>163</v>
       </c>
       <c r="M23" s="39">
@@ -2195,37 +2195,37 @@
       </c>
       <c r="N23" s="53"/>
       <c r="O23" s="25"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
       <c r="V23" s="52"/>
     </row>
     <row r="24">
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
       <c r="C24" s="41"/>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="48" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35">
+      <c r="E24" s="34"/>
+      <c r="F24" s="34">
         <v>29.0</v>
       </c>
-      <c r="G24" s="44">
+      <c r="G24" s="43">
         <v>46149.0</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="I24" s="44"/>
-      <c r="J24" s="44">
+      <c r="I24" s="43"/>
+      <c r="J24" s="43">
         <v>46185.0</v>
       </c>
-      <c r="K24" s="46">
+      <c r="K24" s="45">
         <v>218206.1</v>
       </c>
-      <c r="L24" s="35" t="s">
+      <c r="L24" s="34" t="s">
         <v>171</v>
       </c>
       <c r="M24" s="39">
@@ -2233,37 +2233,37 @@
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="25"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
       <c r="V24" s="52"/>
     </row>
     <row r="25">
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
       <c r="C25" s="41"/>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35">
+      <c r="E25" s="34"/>
+      <c r="F25" s="34">
         <v>40.0</v>
       </c>
-      <c r="G25" s="44">
+      <c r="G25" s="43">
         <v>46156.0</v>
       </c>
-      <c r="H25" s="35" t="s">
+      <c r="H25" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44">
+      <c r="I25" s="43"/>
+      <c r="J25" s="43">
         <v>46191.0</v>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="45">
         <v>1549250.84</v>
       </c>
-      <c r="L25" s="35" t="s">
+      <c r="L25" s="34" t="s">
         <v>173</v>
       </c>
       <c r="M25" s="39">
@@ -2271,37 +2271,37 @@
       </c>
       <c r="N25" s="54"/>
       <c r="O25" s="25"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
       <c r="V25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
       <c r="C26" s="55"/>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35">
+      <c r="E26" s="34"/>
+      <c r="F26" s="34">
         <v>48.0</v>
       </c>
-      <c r="G26" s="44">
+      <c r="G26" s="43">
         <v>46230.0</v>
       </c>
-      <c r="H26" s="35" t="s">
+      <c r="H26" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44">
+      <c r="I26" s="43"/>
+      <c r="J26" s="43">
         <v>46262.0</v>
       </c>
-      <c r="K26" s="46" t="s">
+      <c r="K26" s="45" t="s">
         <v>176</v>
       </c>
-      <c r="L26" s="35" t="s">
+      <c r="L26" s="34" t="s">
         <v>177</v>
       </c>
       <c r="M26" s="39" t="s">
@@ -2309,59 +2309,59 @@
       </c>
       <c r="N26" s="54"/>
       <c r="O26" s="25"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
       <c r="V26" s="52"/>
     </row>
     <row r="27" ht="30.75" customHeight="1">
       <c r="A27" s="23"/>
       <c r="B27" s="23"/>
       <c r="C27" s="29" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F27" s="29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G27" s="29"/>
       <c r="H27" s="29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
       <c r="K27" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="M27" s="57" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="L27" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="M27" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="N27" s="29" t="s">
-        <v>70</v>
-      </c>
       <c r="O27" s="25"/>
-      <c r="P27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
+      <c r="P27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
       <c r="V27" s="52"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="28"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="28"/>
-      <c r="AB27" s="28"/>
-      <c r="AC27" s="28"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="23"/>
@@ -2372,24 +2372,24 @@
       <c r="D28" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36">
+      <c r="E28" s="35"/>
+      <c r="F28" s="35">
         <v>402.0</v>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="36">
         <v>45791.0</v>
       </c>
-      <c r="H28" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37">
+      <c r="H28" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36">
         <v>45834.0</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="37">
         <v>188246.17</v>
       </c>
-      <c r="L28" s="35" t="s">
+      <c r="L28" s="34" t="s">
         <v>179</v>
       </c>
       <c r="M28" s="59">
@@ -2397,20 +2397,20 @@
       </c>
       <c r="N28" s="51"/>
       <c r="O28" s="25"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="28"/>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
       <c r="V28" s="52"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="28"/>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="28"/>
-      <c r="AC28" s="28"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
     </row>
     <row r="29">
       <c r="A29" s="23"/>
@@ -2422,23 +2422,23 @@
       <c r="E29" s="60">
         <v>46.0</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="35">
         <v>447.0</v>
       </c>
-      <c r="G29" s="37">
+      <c r="G29" s="36">
         <v>45814.0</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H29" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44">
+      <c r="I29" s="43"/>
+      <c r="J29" s="43">
         <v>45955.0</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29" s="37">
         <v>112720.77</v>
       </c>
-      <c r="L29" s="35" t="s">
+      <c r="L29" s="34" t="s">
         <v>182</v>
       </c>
       <c r="M29" s="39">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="N29" s="51"/>
       <c r="O29" s="25"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
       <c r="V29" s="52"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="27"/>
+      <c r="AC29" s="27"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="23"/>
@@ -2471,23 +2471,23 @@
       <c r="E30" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="35">
         <v>529.0</v>
       </c>
       <c r="G30" s="63">
         <v>45853.0</v>
       </c>
-      <c r="H30" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44">
+      <c r="H30" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43">
         <v>45939.0</v>
       </c>
-      <c r="K30" s="46">
+      <c r="K30" s="45">
         <v>378307.61</v>
       </c>
-      <c r="L30" s="35" t="s">
+      <c r="L30" s="34" t="s">
         <v>185</v>
       </c>
       <c r="M30" s="39">
@@ -2496,19 +2496,19 @@
       <c r="N30" s="51"/>
       <c r="O30" s="25"/>
       <c r="P30" s="64"/>
-      <c r="Q30" s="28"/>
-      <c r="R30" s="28"/>
-      <c r="S30" s="28"/>
-      <c r="T30" s="28"/>
-      <c r="U30" s="28"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+      <c r="U30" s="27"/>
       <c r="V30" s="52"/>
-      <c r="W30" s="28"/>
-      <c r="X30" s="28"/>
-      <c r="Y30" s="28"/>
-      <c r="Z30" s="28"/>
-      <c r="AA30" s="28"/>
-      <c r="AB30" s="28"/>
-      <c r="AC30" s="28"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="27"/>
+      <c r="Z30" s="27"/>
+      <c r="AA30" s="27"/>
+      <c r="AB30" s="27"/>
+      <c r="AC30" s="27"/>
     </row>
     <row r="31" ht="60.0" customHeight="1">
       <c r="A31" s="23"/>
@@ -2520,23 +2520,23 @@
       <c r="E31" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="34">
         <v>691.0</v>
       </c>
       <c r="G31" s="63">
         <v>45910.0</v>
       </c>
-      <c r="H31" s="35" t="s">
-        <v>55</v>
-      </c>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44">
+      <c r="H31" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43">
         <v>45941.0</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31" s="37">
         <v>3315.0471000000252</v>
       </c>
-      <c r="L31" s="35" t="s">
+      <c r="L31" s="34" t="s">
         <v>187</v>
       </c>
       <c r="M31" s="39">
@@ -2545,19 +2545,19 @@
       <c r="N31" s="51"/>
       <c r="O31" s="25"/>
       <c r="P31" s="64"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-      <c r="U31" s="28"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+      <c r="U31" s="27"/>
       <c r="V31" s="52"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="28"/>
-      <c r="Y31" s="28"/>
-      <c r="Z31" s="28"/>
-      <c r="AA31" s="28"/>
-      <c r="AB31" s="28"/>
-      <c r="AC31" s="28"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="27"/>
+      <c r="AA31" s="27"/>
+      <c r="AB31" s="27"/>
+      <c r="AC31" s="27"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="23"/>
@@ -2569,23 +2569,23 @@
       <c r="E32" s="65">
         <v>135.0</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="34">
         <v>677.0</v>
       </c>
       <c r="G32" s="63">
         <v>45904.0</v>
       </c>
-      <c r="H32" s="35" t="s">
-        <v>68</v>
+      <c r="H32" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="I32" s="66"/>
       <c r="J32" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K32" s="46">
+      <c r="K32" s="45">
         <v>198332.75</v>
       </c>
-      <c r="L32" s="35" t="s">
+      <c r="L32" s="34" t="s">
         <v>189</v>
       </c>
       <c r="M32" s="39">
@@ -2594,19 +2594,19 @@
       <c r="N32" s="51"/>
       <c r="O32" s="25"/>
       <c r="P32" s="64"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
       <c r="V32" s="52"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="27"/>
+      <c r="AA32" s="27"/>
+      <c r="AB32" s="27"/>
+      <c r="AC32" s="27"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="23"/>
@@ -2618,20 +2618,20 @@
       <c r="E33" s="65">
         <v>40.0</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="34">
         <v>278.0</v>
       </c>
       <c r="G33" s="63">
         <v>46008.0</v>
       </c>
-      <c r="H33" s="35" t="s">
-        <v>113</v>
+      <c r="H33" s="34" t="s">
+        <v>122</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
         <v>46066.0</v>
       </c>
-      <c r="K33" s="46">
+      <c r="K33" s="45">
         <v>1528.62</v>
       </c>
       <c r="L33" s="67" t="s">
@@ -2643,19 +2643,19 @@
       <c r="N33" s="51"/>
       <c r="O33" s="25"/>
       <c r="P33" s="64"/>
-      <c r="Q33" s="28"/>
-      <c r="R33" s="28"/>
-      <c r="S33" s="28"/>
-      <c r="T33" s="28"/>
-      <c r="U33" s="28"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+      <c r="U33" s="27"/>
       <c r="V33" s="52"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="28"/>
-      <c r="Y33" s="28"/>
-      <c r="Z33" s="28"/>
-      <c r="AA33" s="28"/>
-      <c r="AB33" s="28"/>
-      <c r="AC33" s="28"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27"/>
+      <c r="Y33" s="27"/>
+      <c r="Z33" s="27"/>
+      <c r="AA33" s="27"/>
+      <c r="AB33" s="27"/>
+      <c r="AC33" s="27"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="23"/>
@@ -2667,23 +2667,23 @@
       <c r="E34" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="34">
         <v>748.0</v>
       </c>
       <c r="G34" s="63">
         <v>45930.0</v>
       </c>
-      <c r="H34" s="35" t="s">
-        <v>90</v>
+      <c r="H34" s="34" t="s">
+        <v>95</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K34" s="46">
+      <c r="K34" s="45">
         <v>38718.58</v>
       </c>
-      <c r="L34" s="35" t="s">
+      <c r="L34" s="34" t="s">
         <v>195</v>
       </c>
       <c r="M34" s="59" t="s">
@@ -2692,19 +2692,19 @@
       <c r="N34" s="51"/>
       <c r="O34" s="25"/>
       <c r="P34" s="64"/>
-      <c r="Q34" s="28"/>
-      <c r="R34" s="28"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="28"/>
-      <c r="U34" s="28"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+      <c r="U34" s="27"/>
       <c r="V34" s="52"/>
-      <c r="W34" s="28"/>
-      <c r="X34" s="28"/>
-      <c r="Y34" s="28"/>
-      <c r="Z34" s="28"/>
-      <c r="AA34" s="28"/>
-      <c r="AB34" s="28"/>
-      <c r="AC34" s="28"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="27"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="27"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="23"/>
@@ -2716,23 +2716,23 @@
       <c r="E35" s="65">
         <v>154.0</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="34">
         <v>822.0</v>
       </c>
       <c r="G35" s="63">
         <v>45968.0</v>
       </c>
-      <c r="H35" s="35" t="s">
-        <v>105</v>
+      <c r="H35" s="34" t="s">
+        <v>113</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K35" s="46">
+      <c r="K35" s="45">
         <v>133124.11</v>
       </c>
-      <c r="L35" s="35" t="s">
+      <c r="L35" s="34" t="s">
         <v>198</v>
       </c>
       <c r="M35" s="59" t="s">
@@ -2741,19 +2741,19 @@
       <c r="N35" s="51"/>
       <c r="O35" s="25"/>
       <c r="P35" s="64"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="27"/>
       <c r="V35" s="52"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="28"/>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="27"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="27"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="23"/>
@@ -2772,16 +2772,16 @@
         <v>46043.0</v>
       </c>
       <c r="H36" s="65" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I36" s="70"/>
       <c r="J36" s="69">
         <v>46075.0</v>
       </c>
-      <c r="K36" s="46">
+      <c r="K36" s="45">
         <v>11372.9</v>
       </c>
-      <c r="L36" s="35" t="s">
+      <c r="L36" s="34" t="s">
         <v>201</v>
       </c>
       <c r="M36" s="39">
@@ -2789,20 +2789,20 @@
       </c>
       <c r="N36" s="51"/>
       <c r="O36" s="25"/>
-      <c r="P36" s="28"/>
-      <c r="Q36" s="28"/>
-      <c r="R36" s="28"/>
-      <c r="S36" s="28"/>
-      <c r="T36" s="28"/>
-      <c r="U36" s="28"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+      <c r="U36" s="27"/>
       <c r="V36" s="52"/>
-      <c r="W36" s="28"/>
-      <c r="X36" s="28"/>
-      <c r="Y36" s="28"/>
-      <c r="Z36" s="28"/>
-      <c r="AA36" s="28"/>
-      <c r="AB36" s="28"/>
-      <c r="AC36" s="28"/>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
+      <c r="Z36" s="27"/>
+      <c r="AA36" s="27"/>
+      <c r="AB36" s="27"/>
+      <c r="AC36" s="27"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="23"/>
@@ -2819,27 +2819,27 @@
         <v>203</v>
       </c>
       <c r="J37" s="69"/>
-      <c r="K37" s="46"/>
-      <c r="L37" s="35"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="34"/>
       <c r="M37" s="39"/>
       <c r="N37" s="51">
         <v>15854.78</v>
       </c>
       <c r="O37" s="25"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
       <c r="V37" s="52"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="23"/>
@@ -2856,27 +2856,27 @@
         <v>203</v>
       </c>
       <c r="J38" s="69"/>
-      <c r="K38" s="46"/>
-      <c r="L38" s="35"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="34"/>
       <c r="M38" s="39"/>
       <c r="N38" s="51" t="s">
         <v>205</v>
       </c>
       <c r="O38" s="25"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+      <c r="U38" s="27"/>
       <c r="V38" s="52"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
-      <c r="Y38" s="28"/>
-      <c r="Z38" s="28"/>
-      <c r="AA38" s="28"/>
-      <c r="AB38" s="28"/>
-      <c r="AC38" s="28"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27"/>
+      <c r="Y38" s="27"/>
+      <c r="Z38" s="27"/>
+      <c r="AA38" s="27"/>
+      <c r="AB38" s="27"/>
+      <c r="AC38" s="27"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="23"/>
@@ -2895,13 +2895,13 @@
         <v>46104.0</v>
       </c>
       <c r="H39" s="65" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I39" s="70"/>
       <c r="J39" s="69">
         <v>46106.0</v>
       </c>
-      <c r="K39" s="46">
+      <c r="K39" s="45">
         <v>27801.11</v>
       </c>
       <c r="L39" s="71" t="s">
@@ -2912,20 +2912,20 @@
       </c>
       <c r="N39" s="51"/>
       <c r="O39" s="25"/>
-      <c r="P39" s="28"/>
-      <c r="Q39" s="28"/>
-      <c r="R39" s="28"/>
-      <c r="S39" s="28"/>
-      <c r="T39" s="28"/>
-      <c r="U39" s="28"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+      <c r="U39" s="27"/>
       <c r="V39" s="52"/>
-      <c r="W39" s="28"/>
-      <c r="X39" s="28"/>
-      <c r="Y39" s="28"/>
-      <c r="Z39" s="28"/>
-      <c r="AA39" s="28"/>
-      <c r="AB39" s="28"/>
-      <c r="AC39" s="28"/>
+      <c r="W39" s="27"/>
+      <c r="X39" s="27"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="27"/>
+      <c r="AA39" s="27"/>
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="27"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="15"/>
@@ -2942,17 +2942,17 @@
         <v>46199.0</v>
       </c>
       <c r="H40" s="65" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I40" s="70"/>
       <c r="J40" s="69">
         <v>46233.0</v>
       </c>
-      <c r="K40" s="46">
+      <c r="K40" s="45">
         <v>58868.35</v>
       </c>
-      <c r="L40" s="35" t="s">
-        <v>67</v>
+      <c r="L40" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="M40" s="72">
         <v>58868.35</v>
@@ -7911,11 +7911,11 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="4">
+      <c r="A2" s="5">
         <v>46212.0</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -8017,13 +8017,13 @@
     </row>
     <row r="5">
       <c r="A5" s="10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>4</v>
@@ -8062,13 +8062,13 @@
     </row>
     <row r="6">
       <c r="A6" s="10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>4</v>
@@ -8107,13 +8107,13 @@
     </row>
     <row r="7">
       <c r="A7" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>4</v>
@@ -8131,7 +8131,7 @@
         <v>339039.0</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" s="14">
         <v>949835.78</v>
@@ -8187,7 +8187,7 @@
       <c r="L8" s="10">
         <v>0.0</v>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="28"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8198,13 +8198,13 @@
     </row>
     <row r="9">
       <c r="A9" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>4</v>
@@ -8222,7 +8222,7 @@
         <v>339039.0</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J9" s="14">
         <v>211614.23</v>
@@ -8243,13 +8243,13 @@
     </row>
     <row r="10">
       <c r="A10" s="10" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>4</v>
@@ -8288,13 +8288,13 @@
     </row>
     <row r="11">
       <c r="A11" s="10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>4</v>
@@ -8333,13 +8333,13 @@
     </row>
     <row r="12">
       <c r="A12" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>4</v>
@@ -8357,7 +8357,7 @@
         <v>339039.0</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J12" s="14">
         <v>1600334.09</v>
@@ -8378,13 +8378,13 @@
     </row>
     <row r="13">
       <c r="A13" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>4</v>
@@ -8413,7 +8413,7 @@
       <c r="L13" s="14">
         <v>0.0</v>
       </c>
-      <c r="M13" s="33"/>
+      <c r="M13" s="38"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8424,13 +8424,13 @@
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>4</v>
@@ -8448,7 +8448,7 @@
         <v>339039.0</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J14" s="14">
         <v>968237.39</v>
@@ -8469,13 +8469,13 @@
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>4</v>
@@ -8493,7 +8493,7 @@
         <v>339039.0</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J15" s="14">
         <v>1011677.95</v>
@@ -8514,13 +8514,13 @@
     </row>
     <row r="16">
       <c r="A16" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>4</v>
@@ -8559,13 +8559,13 @@
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>4</v>
@@ -8604,13 +8604,13 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>4</v>
@@ -8628,7 +8628,7 @@
         <v>339039.0</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J18" s="14">
         <v>63746.85</v>
@@ -8649,13 +8649,13 @@
     </row>
     <row r="19">
       <c r="A19" s="10" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>4</v>
@@ -8673,7 +8673,7 @@
         <v>339039.0</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J19" s="14">
         <v>947931.1</v>
@@ -8694,13 +8694,13 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>4</v>
@@ -8739,13 +8739,13 @@
     </row>
     <row r="21">
       <c r="A21" s="10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>4</v>
@@ -8784,18 +8784,18 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="49">
         <v>45953.0</v>
       </c>
       <c r="F22" s="10" t="s">
@@ -8829,18 +8829,18 @@
     </row>
     <row r="23">
       <c r="A23" s="10" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="49">
         <v>45953.0</v>
       </c>
       <c r="F23" s="10" t="s">
@@ -8853,7 +8853,7 @@
         <v>339039.0</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J23" s="14">
         <v>1000001.64</v>
@@ -8874,18 +8874,18 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="49">
         <v>45953.0</v>
       </c>
       <c r="F24" s="10" t="s">
@@ -8919,18 +8919,18 @@
     </row>
     <row r="25">
       <c r="A25" s="10" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="49">
         <v>45975.0</v>
       </c>
       <c r="F25" s="10" t="s">
@@ -8943,7 +8943,7 @@
         <v>339039.0</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J25" s="14">
         <v>1157673.06</v>
@@ -8964,18 +8964,18 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="49">
         <v>45989.0</v>
       </c>
       <c r="F26" s="10" t="s">
@@ -9009,13 +9009,13 @@
     </row>
     <row r="27">
       <c r="A27" s="10" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>4</v>
@@ -9054,13 +9054,13 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>4</v>
@@ -9099,13 +9099,13 @@
     </row>
     <row r="29">
       <c r="A29" s="10" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>4</v>
@@ -9144,13 +9144,13 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>4</v>
@@ -9168,7 +9168,7 @@
         <v>339039.0</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J30" s="14">
         <v>624166.14</v>
@@ -9189,13 +9189,13 @@
     </row>
     <row r="31">
       <c r="A31" s="10" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>4</v>
@@ -9213,7 +9213,7 @@
         <v>339039.0</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J31" s="14">
         <v>18462.36</v>
@@ -9234,13 +9234,13 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>4</v>
@@ -9258,7 +9258,7 @@
         <v>339039.0</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J32" s="14">
         <v>1530656.62</v>
@@ -9279,13 +9279,13 @@
     </row>
     <row r="33">
       <c r="A33" s="10" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>4</v>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,15 +30,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="216">
   <si>
+    <t>Saldo</t>
+  </si>
+  <si>
+    <t>025NE000005</t>
+  </si>
+  <si>
     <t>Controle de pagamentos</t>
   </si>
   <si>
-    <t>Saldo</t>
-  </si>
-  <si>
-    <t>025NE000005</t>
-  </si>
-  <si>
     <t>C25375</t>
   </si>
   <si>
@@ -57,9 +57,18 @@
     <t>25E0385</t>
   </si>
   <si>
+    <t>2025NE000369</t>
+  </si>
+  <si>
     <t>Número Contrato</t>
   </si>
   <si>
+    <t>C25516</t>
+  </si>
+  <si>
+    <t>25E0387</t>
+  </si>
+  <si>
     <t>UG Executora</t>
   </si>
   <si>
@@ -93,12 +102,18 @@
     <t>Valor a Empenhar</t>
   </si>
   <si>
+    <t>2025NE000371</t>
+  </si>
+  <si>
     <t>Valor Empenhado</t>
   </si>
   <si>
     <t>Valor Liquidado</t>
   </si>
   <si>
+    <t>25E0389</t>
+  </si>
+  <si>
     <t>Saldo (Valor a Faturar)</t>
   </si>
   <si>
@@ -108,21 +123,12 @@
     <t>Tipo Despesa /Receita</t>
   </si>
   <si>
-    <t>2025NE000369</t>
-  </si>
-  <si>
     <t>Abrir</t>
   </si>
   <si>
-    <t>C25516</t>
-  </si>
-  <si>
     <t>Editar</t>
   </si>
   <si>
-    <t>25E0387</t>
-  </si>
-  <si>
     <t>005/CELOG-PAMALS/2025</t>
   </si>
   <si>
@@ -132,48 +138,72 @@
     <t>PAMALS</t>
   </si>
   <si>
+    <t>2025NE000413</t>
+  </si>
+  <si>
+    <t>C25501</t>
+  </si>
+  <si>
+    <t>25E0403</t>
+  </si>
+  <si>
     <t>Vigente</t>
   </si>
   <si>
     <t>2048 20YJ 21EM 219C 20SP 20X7 2000</t>
   </si>
   <si>
+    <t>20SP</t>
+  </si>
+  <si>
     <t>67101.001510/2024-12</t>
   </si>
   <si>
     <t>R$</t>
   </si>
   <si>
-    <t>2025NE000371</t>
-  </si>
-  <si>
-    <t>25E0389</t>
+    <t>2025NE000414</t>
   </si>
   <si>
     <t>VEE ONE-MANUTENCAO E SERVICOS TECNICOS LTDA</t>
   </si>
   <si>
-    <t>2025NE000413</t>
-  </si>
-  <si>
-    <t>C25501</t>
-  </si>
-  <si>
-    <t>25E0403</t>
+    <t>C25525</t>
+  </si>
+  <si>
+    <t>25E0431</t>
+  </si>
+  <si>
+    <t>21EM</t>
+  </si>
+  <si>
+    <t>2025NE000559</t>
+  </si>
+  <si>
+    <t>C25545</t>
+  </si>
+  <si>
+    <t>25E0524</t>
   </si>
   <si>
     <t>Módulo</t>
   </si>
   <si>
+    <t>20X7</t>
+  </si>
+  <si>
     <t>Referência</t>
   </si>
   <si>
-    <t>20SP</t>
-  </si>
-  <si>
     <t>Nº recibo</t>
   </si>
   <si>
+    <t>2025NE000770</t>
+  </si>
+  <si>
+    <t>25E0731</t>
+  </si>
+  <si>
     <t>Nº</t>
   </si>
   <si>
@@ -189,133 +219,196 @@
     <t>Vencimento</t>
   </si>
   <si>
+    <t>2025NE000774</t>
+  </si>
+  <si>
+    <t>25E0737</t>
+  </si>
+  <si>
     <t>Valor das Nfs</t>
   </si>
   <si>
     <t>Ordem de Pagamento</t>
   </si>
   <si>
-    <t>2025NE000414</t>
-  </si>
-  <si>
     <t>Faturado</t>
   </si>
   <si>
     <t>Pendente</t>
   </si>
   <si>
-    <t>C25525</t>
-  </si>
-  <si>
-    <t>25E0431</t>
-  </si>
-  <si>
-    <t>21EM</t>
+    <t>2025NE000843</t>
+  </si>
+  <si>
+    <t>C25630</t>
   </si>
   <si>
     <t>FEV/25</t>
   </si>
   <si>
+    <t>25E0787</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
+    <t>219C</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025NE000369 </t>
   </si>
   <si>
-    <t>2025NE000559</t>
-  </si>
-  <si>
-    <t>C25545</t>
-  </si>
-  <si>
-    <t>25E0524</t>
+    <t>2025NE001065</t>
+  </si>
+  <si>
+    <t>25E0999</t>
   </si>
   <si>
     <t>2025NP001980</t>
   </si>
   <si>
-    <t>20X7</t>
-  </si>
-  <si>
-    <t>2025NE000770</t>
-  </si>
-  <si>
-    <t>25E0731</t>
+    <t>2025NE001200</t>
+  </si>
+  <si>
+    <t>C25590</t>
+  </si>
+  <si>
+    <t>25E1128</t>
+  </si>
+  <si>
+    <t>2025NE001598</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>25E1446</t>
+  </si>
+  <si>
+    <t>2025NE001627</t>
+  </si>
+  <si>
+    <t>25E1475</t>
   </si>
   <si>
     <t>MAR/25</t>
   </si>
   <si>
-    <t>2025NE000774</t>
+    <t>2025NE001629</t>
+  </si>
+  <si>
+    <t>C25820</t>
+  </si>
+  <si>
+    <t>25E1477</t>
+  </si>
+  <si>
+    <t>2025NE001687</t>
+  </si>
+  <si>
+    <t>25E1535</t>
   </si>
   <si>
     <t>2025NE000367, 2025NE000369, 2025NE000371, 2025NE000413</t>
   </si>
   <si>
-    <t>25E0737</t>
+    <t>2025NE001688</t>
+  </si>
+  <si>
+    <t>25E1536</t>
   </si>
   <si>
     <t>2025NP001979</t>
   </si>
   <si>
-    <t>2025NE000843</t>
-  </si>
-  <si>
-    <t>C25630</t>
-  </si>
-  <si>
-    <t>25E0787</t>
-  </si>
-  <si>
-    <t>219C</t>
-  </si>
-  <si>
-    <t>2025NE001065</t>
-  </si>
-  <si>
-    <t>25E0999</t>
+    <t>2025NE001689</t>
+  </si>
+  <si>
+    <t>25E1537</t>
   </si>
   <si>
     <t>ABR/25</t>
   </si>
   <si>
+    <t>2025NE001690</t>
+  </si>
+  <si>
+    <t>25E1538</t>
+  </si>
+  <si>
     <t>2025NE000413, 2025NE000414, 2025NE000559</t>
   </si>
   <si>
-    <t>2025NE001200</t>
+    <t>2025NE001823</t>
+  </si>
+  <si>
+    <t>C25865</t>
+  </si>
+  <si>
+    <t>25E1666</t>
   </si>
   <si>
     <t>2025NP002341</t>
   </si>
   <si>
-    <t>C25590</t>
-  </si>
-  <si>
-    <t>25E1128</t>
+    <t>2025NE001828</t>
+  </si>
+  <si>
+    <t>C25869</t>
+  </si>
+  <si>
+    <t>25E1667</t>
+  </si>
+  <si>
+    <t>20YJ</t>
   </si>
   <si>
     <t>MAI/25</t>
   </si>
   <si>
-    <t>2025NE001598</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>25E1446</t>
+    <t>2025NE001830</t>
+  </si>
+  <si>
+    <t>25E1669</t>
+  </si>
+  <si>
+    <t>2025NE002200</t>
+  </si>
+  <si>
+    <t>C25863</t>
+  </si>
+  <si>
+    <t>25E2021</t>
   </si>
   <si>
     <t>2025NP002884</t>
   </si>
   <si>
-    <t>2025NE001627</t>
-  </si>
-  <si>
-    <t>25E1475</t>
+    <t>2025NE002237</t>
+  </si>
+  <si>
+    <t>25E2058</t>
+  </si>
+  <si>
+    <t>2026NE000330</t>
+  </si>
+  <si>
+    <t>C26163</t>
+  </si>
+  <si>
+    <t>26E0320</t>
   </si>
   <si>
     <t>JUN/25</t>
+  </si>
+  <si>
+    <t>2026NE000388</t>
+  </si>
+  <si>
+    <t>C26193</t>
+  </si>
+  <si>
+    <t>26E0375</t>
   </si>
   <si>
     <t>2025NE000005,
@@ -324,62 +417,80 @@
 2025NE000774</t>
   </si>
   <si>
-    <t>2025NE001629</t>
-  </si>
-  <si>
-    <t>C25820</t>
-  </si>
-  <si>
-    <t>25E1477</t>
-  </si>
-  <si>
     <t>2025NP400522</t>
   </si>
   <si>
+    <t>2026NE000748</t>
+  </si>
+  <si>
+    <t>C26312</t>
+  </si>
+  <si>
+    <t>26E0709</t>
+  </si>
+  <si>
     <t>JUL/25</t>
   </si>
   <si>
-    <t>2025NE001687</t>
+    <t>2026NE000816</t>
+  </si>
+  <si>
+    <t>C26324</t>
+  </si>
+  <si>
+    <t>26E0776</t>
   </si>
   <si>
     <t>2025NE000843, 2025NE001200</t>
   </si>
   <si>
-    <t>25E1535</t>
-  </si>
-  <si>
     <t>2025NP003724</t>
   </si>
   <si>
-    <t>2025NE001688</t>
+    <t>2026NE000817</t>
+  </si>
+  <si>
+    <t>C26326</t>
+  </si>
+  <si>
+    <t>26E0777</t>
+  </si>
+  <si>
+    <t>2026NE000842</t>
   </si>
   <si>
     <t>AGO/25</t>
   </si>
   <si>
-    <t>25E1536</t>
+    <t>26E0803</t>
+  </si>
+  <si>
+    <t>2026NE000944</t>
   </si>
   <si>
     <t>2025NP004558</t>
   </si>
   <si>
-    <t>2025NE001689</t>
-  </si>
-  <si>
-    <t>25E1537</t>
+    <t>26E0906</t>
+  </si>
+  <si>
+    <t>2026NE900959</t>
+  </si>
+  <si>
+    <t>C26363</t>
   </si>
   <si>
     <t>SET/25</t>
+  </si>
+  <si>
+    <t>26E0959</t>
   </si>
   <si>
     <t>2025NE001688 
 2025NE001828</t>
   </si>
   <si>
-    <t>2025NE001690</t>
-  </si>
-  <si>
-    <t>25E1538</t>
+    <t>20XV</t>
   </si>
   <si>
     <t>2025NP004897</t>
@@ -388,51 +499,24 @@
     <t>OUT/25</t>
   </si>
   <si>
-    <t>2025NE001823</t>
-  </si>
-  <si>
-    <t>C25865</t>
-  </si>
-  <si>
     <t>2025NE001688, 2025NE001828, 2025NE002200</t>
   </si>
   <si>
-    <t>25E1666</t>
-  </si>
-  <si>
     <t>2025NP004932</t>
   </si>
   <si>
-    <t>2025NE001828</t>
-  </si>
-  <si>
-    <t>C25869</t>
-  </si>
-  <si>
-    <t>25E1667</t>
-  </si>
-  <si>
     <t>NOV/25</t>
   </si>
   <si>
     <t>2025NE001687, 2025NE001689, 2025NE001690, 2025NE001823, 2025NE001830, 2025NE002237</t>
   </si>
   <si>
-    <t>20YJ</t>
-  </si>
-  <si>
     <t>2026NP400440</t>
   </si>
   <si>
-    <t>2025NE001830</t>
-  </si>
-  <si>
     <t>DEZ/25</t>
   </si>
   <si>
-    <t>25E1669</t>
-  </si>
-  <si>
     <t>2025NE001065, 2025NE002200</t>
   </si>
   <si>
@@ -442,15 +526,6 @@
     <t>JAN/26</t>
   </si>
   <si>
-    <t>2025NE002200</t>
-  </si>
-  <si>
-    <t>C25863</t>
-  </si>
-  <si>
-    <t>25E2021</t>
-  </si>
-  <si>
     <t>2026NP401035</t>
   </si>
   <si>
@@ -460,24 +535,9 @@
     <t>2025NE001627, 2025NE001629, 2025NE001823</t>
   </si>
   <si>
-    <t>2025NE002237</t>
-  </si>
-  <si>
-    <t>25E2058</t>
-  </si>
-  <si>
     <t>2026NP402272</t>
   </si>
   <si>
-    <t>2026NE000330</t>
-  </si>
-  <si>
-    <t>C26163</t>
-  </si>
-  <si>
-    <t>26E0320</t>
-  </si>
-  <si>
     <t>MAR/26</t>
   </si>
   <si>
@@ -487,91 +547,31 @@
     <t>R$ 1.350.542,52</t>
   </si>
   <si>
-    <t>2026NE000388</t>
-  </si>
-  <si>
     <t>2026NP401762</t>
   </si>
   <si>
-    <t>C26193</t>
-  </si>
-  <si>
-    <t>26E0375</t>
-  </si>
-  <si>
-    <t>2026NE000748</t>
-  </si>
-  <si>
-    <t>C26312</t>
-  </si>
-  <si>
-    <t>26E0709</t>
-  </si>
-  <si>
     <t>ABR/26</t>
   </si>
   <si>
     <t>2025NE000770, 2025NE001065, 2025NE001627</t>
   </si>
   <si>
-    <t>2026NE000816</t>
-  </si>
-  <si>
-    <t>C26324</t>
-  </si>
-  <si>
-    <t>26E0776</t>
-  </si>
-  <si>
-    <t>2026NE000817</t>
-  </si>
-  <si>
-    <t>C26326</t>
-  </si>
-  <si>
-    <t>26E0777</t>
-  </si>
-  <si>
     <t>REAJUSTE</t>
   </si>
   <si>
-    <t>2026NE000842</t>
-  </si>
-  <si>
     <t>2026NP402148</t>
   </si>
   <si>
-    <t>26E0803</t>
-  </si>
-  <si>
     <t>MAIO/26</t>
   </si>
   <si>
-    <t>2026NE000944</t>
-  </si>
-  <si>
-    <t>26E0906</t>
-  </si>
-  <si>
     <t>2026NP402373</t>
   </si>
   <si>
-    <t>2026NE900959</t>
-  </si>
-  <si>
     <t>JUNHO/26</t>
   </si>
   <si>
-    <t>C26363</t>
-  </si>
-  <si>
-    <t>26E0959</t>
-  </si>
-  <si>
     <t>2025NE001065, 2026NE000330</t>
-  </si>
-  <si>
-    <t>20XV</t>
   </si>
   <si>
     <t>R$ 1.340.865,98</t>
@@ -692,8 +692,8 @@
     <numFmt numFmtId="166" formatCode="dd/MM/yyyy"/>
     <numFmt numFmtId="167" formatCode="R$ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
-    <numFmt numFmtId="169" formatCode="MM/DD/YY"/>
-    <numFmt numFmtId="170" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="169" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="170" formatCode="MM/DD/YY"/>
     <numFmt numFmtId="171" formatCode="[$R$ -416]#,##0.00"/>
     <numFmt numFmtId="172" formatCode="_([$R$ -416]* #,##0.00_);_([$R$ -416]* \(#,##0.00\);_([$R$ -416]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -737,18 +737,18 @@
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Century Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Century Gothic"/>
     </font>
     <font>
       <b/>
@@ -888,24 +888,15 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -913,13 +904,22 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
@@ -953,76 +953,76 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="6" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="169" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="169" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="170" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="9" numFmtId="168" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1037,13 +1037,13 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1052,13 +1052,13 @@
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1067,10 +1067,10 @@
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="9" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -1440,124 +1440,124 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="3"/>
+      <c r="V1" s="5"/>
     </row>
     <row r="2" ht="59.25" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" s="11"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="3"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="5"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="15"/>
       <c r="B4" s="15"/>
       <c r="C4" s="16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R4" s="16" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S4" s="16" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="U4" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="V4" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="V4" s="5"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="15"/>
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5" s="20">
         <v>1564.0</v>
@@ -1566,16 +1566,16 @@
         <v>1564.0</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N5" s="21">
         <v>9.165159737E7</v>
@@ -1593,15 +1593,15 @@
         <v>1.085943044E7</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="V5" s="3"/>
+        <v>45</v>
+      </c>
+      <c r="V5" s="5"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="L6" s="22"/>
-      <c r="V6" s="3"/>
+      <c r="V6" s="5"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="23"/>
@@ -1615,67 +1615,67 @@
       <c r="I7" s="25"/>
       <c r="J7" s="25"/>
       <c r="K7" s="25"/>
-      <c r="L7" s="26"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
       <c r="O7" s="25"/>
-      <c r="P7" s="27"/>
-      <c r="V7" s="3"/>
+      <c r="P7" s="28"/>
+      <c r="V7" s="5"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="23"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="28" t="s">
+      <c r="C8" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="30" t="s">
+      <c r="D8" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="M8" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="N8" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="28"/>
-      <c r="P8" s="27"/>
-      <c r="V8" s="3"/>
+      <c r="E8" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="O8" s="29"/>
+      <c r="P8" s="28"/>
+      <c r="V8" s="5"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="23"/>
       <c r="B9" s="23"/>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <v>1.0</v>
       </c>
-      <c r="D9" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>62</v>
+      <c r="D9" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>73</v>
       </c>
       <c r="F9" s="35">
         <v>594.0</v>
@@ -1684,7 +1684,7 @@
         <v>45740.0</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="I9" s="36"/>
       <c r="J9" s="36">
@@ -1694,26 +1694,26 @@
         <v>748504.24</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="M9" s="38">
+        <v>78</v>
+      </c>
+      <c r="M9" s="39">
         <f t="shared" ref="M9:M10" si="1">K9</f>
         <v>748504.24</v>
       </c>
-      <c r="N9" s="39"/>
+      <c r="N9" s="40"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="27"/>
-      <c r="V9" s="3"/>
+      <c r="P9" s="28"/>
+      <c r="V9" s="5"/>
     </row>
     <row r="10" ht="51.0" customHeight="1">
       <c r="A10" s="23"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>62</v>
+      <c r="C10" s="41"/>
+      <c r="D10" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>73</v>
       </c>
       <c r="F10" s="35">
         <v>620.0</v>
@@ -1722,7 +1722,7 @@
         <v>45775.0</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I10" s="36"/>
       <c r="J10" s="36">
@@ -1732,26 +1732,26 @@
         <v>1110378.24</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="M10" s="38">
+        <v>96</v>
+      </c>
+      <c r="M10" s="39">
         <f t="shared" si="1"/>
         <v>1110378.24</v>
       </c>
-      <c r="N10" s="41"/>
+      <c r="N10" s="42"/>
       <c r="O10" s="25"/>
-      <c r="P10" s="27"/>
-      <c r="V10" s="3"/>
+      <c r="P10" s="28"/>
+      <c r="V10" s="5"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>62</v>
+      <c r="C11" s="41"/>
+      <c r="D11" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>73</v>
       </c>
       <c r="F11" s="35">
         <v>634.0</v>
@@ -1760,7 +1760,7 @@
         <v>45799.0</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="I11" s="36"/>
       <c r="J11" s="36">
@@ -1769,63 +1769,63 @@
       <c r="K11" s="37">
         <v>974557.12</v>
       </c>
-      <c r="L11" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="M11" s="38">
+      <c r="L11" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="M11" s="39">
         <v>974557.12</v>
       </c>
-      <c r="N11" s="41"/>
+      <c r="N11" s="42"/>
       <c r="O11" s="25"/>
-      <c r="P11" s="27"/>
-      <c r="V11" s="3"/>
+      <c r="P11" s="28"/>
+      <c r="V11" s="5"/>
     </row>
     <row r="12" ht="27.75" customHeight="1">
       <c r="A12" s="23"/>
       <c r="B12" s="23"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F12" s="33">
+      <c r="C12" s="41"/>
+      <c r="D12" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="34">
         <v>660.0</v>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="44">
         <v>45856.0</v>
       </c>
-      <c r="H12" s="44" t="s">
-        <v>76</v>
+      <c r="H12" s="45" t="s">
+        <v>69</v>
       </c>
       <c r="I12" s="36"/>
       <c r="J12" s="36">
         <v>45891.0</v>
       </c>
-      <c r="K12" s="45">
+      <c r="K12" s="46">
         <v>1402001.34</v>
       </c>
-      <c r="L12" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="M12" s="38">
+      <c r="L12" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="M12" s="39">
         <v>1402001.34</v>
       </c>
-      <c r="N12" s="47"/>
+      <c r="N12" s="48"/>
       <c r="O12" s="25"/>
-      <c r="P12" s="27"/>
-      <c r="V12" s="3"/>
+      <c r="P12" s="28"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="48" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>62</v>
+      <c r="C13" s="41"/>
+      <c r="D13" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>73</v>
       </c>
       <c r="F13" s="35">
         <v>661.0</v>
@@ -1834,591 +1834,591 @@
         <v>45856.0</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43">
+        <v>127</v>
+      </c>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44">
         <v>45891.0</v>
       </c>
-      <c r="K13" s="45">
+      <c r="K13" s="46">
         <v>1223702.3</v>
       </c>
-      <c r="L13" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="M13" s="38">
+      <c r="L13" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="M13" s="39">
         <v>1223702.3</v>
       </c>
-      <c r="N13" s="47"/>
+      <c r="N13" s="48"/>
       <c r="O13" s="25"/>
-      <c r="P13" s="49"/>
-      <c r="V13" s="3"/>
+      <c r="P13" s="50"/>
+      <c r="V13" s="5"/>
     </row>
     <row r="14">
       <c r="A14" s="23"/>
       <c r="B14" s="23"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="33">
+      <c r="C14" s="41"/>
+      <c r="D14" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="34">
         <v>688.0</v>
       </c>
       <c r="G14" s="36">
         <v>45901.0</v>
       </c>
-      <c r="H14" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43">
+      <c r="H14" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44">
         <v>45938.0</v>
       </c>
-      <c r="K14" s="45">
+      <c r="K14" s="46">
         <v>1011677.95</v>
       </c>
-      <c r="L14" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="M14" s="38">
+      <c r="L14" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="M14" s="39">
         <v>1011677.95</v>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="42"/>
       <c r="O14" s="25"/>
-      <c r="P14" s="27"/>
-      <c r="V14" s="3"/>
+      <c r="P14" s="28"/>
+      <c r="V14" s="5"/>
     </row>
     <row r="15">
       <c r="A15" s="23"/>
       <c r="B15" s="23"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="33">
+      <c r="C15" s="41"/>
+      <c r="D15" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="34">
         <v>696.0</v>
       </c>
       <c r="G15" s="36">
         <v>45923.0</v>
       </c>
-      <c r="H15" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43">
+      <c r="H15" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44">
         <v>45938.0</v>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="46">
         <v>896744.06</v>
       </c>
-      <c r="L15" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="M15" s="38">
+      <c r="L15" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="M15" s="39">
         <v>896744.06</v>
       </c>
-      <c r="N15" s="47"/>
+      <c r="N15" s="48"/>
       <c r="O15" s="25"/>
-      <c r="V15" s="3"/>
+      <c r="V15" s="5"/>
     </row>
     <row r="16">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="33">
+      <c r="C16" s="41"/>
+      <c r="D16" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="34">
         <v>704.0</v>
       </c>
       <c r="G16" s="36">
         <v>45957.0</v>
       </c>
-      <c r="H16" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43">
+      <c r="H16" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44">
         <v>46003.0</v>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="46">
         <v>919329.06</v>
       </c>
-      <c r="L16" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="M16" s="38">
+      <c r="L16" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="M16" s="39">
         <v>919329.06</v>
       </c>
-      <c r="N16" s="41"/>
+      <c r="N16" s="42"/>
       <c r="O16" s="25"/>
-      <c r="V16" s="3"/>
+      <c r="V16" s="5"/>
     </row>
     <row r="17">
       <c r="A17" s="23"/>
       <c r="B17" s="23"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33">
+      <c r="C17" s="41"/>
+      <c r="D17" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34">
         <v>705.0</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G17" s="44">
         <v>45972.0</v>
       </c>
-      <c r="H17" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="43">
+      <c r="H17" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="I17" s="34"/>
+      <c r="J17" s="44">
         <v>46016.0</v>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="46">
         <v>1157009.26</v>
       </c>
-      <c r="L17" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="M17" s="38">
+      <c r="L17" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="M17" s="39">
         <v>1157009.26</v>
       </c>
       <c r="N17" s="51"/>
       <c r="O17" s="25"/>
-      <c r="V17" s="3"/>
+      <c r="V17" s="5"/>
     </row>
     <row r="18">
       <c r="A18" s="23"/>
       <c r="B18" s="23"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="33">
+      <c r="C18" s="41"/>
+      <c r="D18" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="34">
         <v>728.0</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G18" s="44">
         <v>46008.0</v>
       </c>
-      <c r="H18" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="43">
+      <c r="H18" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="J18" s="44">
         <v>46040.0</v>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="46">
         <v>1214597.952</v>
       </c>
-      <c r="L18" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="M18" s="38">
+      <c r="L18" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="M18" s="39">
         <v>1214597.952</v>
       </c>
       <c r="N18" s="51"/>
       <c r="O18" s="25"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="27"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
       <c r="V18" s="52"/>
     </row>
     <row r="19">
       <c r="A19" s="23"/>
       <c r="B19" s="23"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="33">
+      <c r="C19" s="41"/>
+      <c r="D19" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="34">
         <v>278.0</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G19" s="44">
         <v>46042.0</v>
       </c>
-      <c r="H19" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43">
+      <c r="H19" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44">
         <v>46074.0</v>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="46">
         <v>967082.09</v>
       </c>
-      <c r="L19" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="M19" s="38">
+      <c r="L19" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="M19" s="39">
         <v>967082.09</v>
       </c>
       <c r="N19" s="51"/>
       <c r="O19" s="25"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
       <c r="V19" s="52"/>
     </row>
     <row r="20">
       <c r="A20" s="23"/>
       <c r="B20" s="23"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33">
+      <c r="C20" s="41"/>
+      <c r="D20" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34">
         <v>10.0</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G20" s="44">
         <v>46078.0</v>
       </c>
-      <c r="H20" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43">
+      <c r="H20" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44">
         <v>46106.0</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="46">
         <v>719561.08</v>
       </c>
-      <c r="L20" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="M20" s="38">
+      <c r="L20" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="M20" s="39">
         <v>719561.08</v>
       </c>
       <c r="N20" s="51"/>
       <c r="O20" s="25"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
       <c r="V20" s="52"/>
     </row>
     <row r="21">
       <c r="A21" s="23"/>
       <c r="B21" s="23"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33">
+      <c r="C21" s="41"/>
+      <c r="D21" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34">
         <v>15.0</v>
       </c>
-      <c r="G21" s="43">
+      <c r="G21" s="44">
         <v>46094.0</v>
       </c>
-      <c r="H21" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43">
+      <c r="H21" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44">
         <v>46128.0</v>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="46">
         <v>885881.08</v>
       </c>
-      <c r="L21" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="M21" s="38">
+      <c r="L21" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="M21" s="39">
         <v>885881.08</v>
       </c>
       <c r="N21" s="51"/>
       <c r="O21" s="25"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27"/>
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="28"/>
       <c r="V21" s="52"/>
     </row>
     <row r="22">
       <c r="A22" s="23"/>
       <c r="B22" s="23"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="48" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33">
+      <c r="C22" s="41"/>
+      <c r="D22" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34">
         <v>28.0</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="44">
         <v>46128.0</v>
       </c>
-      <c r="H22" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43">
+      <c r="H22" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44">
         <v>46164.0</v>
       </c>
-      <c r="K22" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="L22" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="M22" s="38" t="s">
-        <v>150</v>
+      <c r="K22" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="L22" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="M22" s="39" t="s">
+        <v>170</v>
       </c>
       <c r="N22" s="51"/>
       <c r="O22" s="25"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28"/>
       <c r="V22" s="52"/>
     </row>
     <row r="23">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33">
+      <c r="C23" s="41"/>
+      <c r="D23" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34">
         <v>33.0</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G23" s="44">
         <v>46156.0</v>
       </c>
-      <c r="H23" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43">
+      <c r="H23" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44">
         <v>46191.0</v>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="46">
         <v>1108954.4358333333</v>
       </c>
-      <c r="L23" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="M23" s="38">
+      <c r="L23" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="M23" s="39">
         <v>1108954.4358333333</v>
       </c>
       <c r="N23" s="53"/>
       <c r="O23" s="25"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
       <c r="V23" s="52"/>
     </row>
     <row r="24">
       <c r="A24" s="23"/>
       <c r="B24" s="23"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="48" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33">
+      <c r="C24" s="41"/>
+      <c r="D24" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34">
         <v>29.0</v>
       </c>
-      <c r="G24" s="43">
+      <c r="G24" s="44">
         <v>46149.0</v>
       </c>
-      <c r="H24" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43">
+      <c r="H24" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44">
         <v>46185.0</v>
       </c>
-      <c r="K24" s="45">
+      <c r="K24" s="46">
         <v>218206.1</v>
       </c>
-      <c r="L24" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="M24" s="38">
+      <c r="L24" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="M24" s="39">
         <v>218206.1</v>
       </c>
       <c r="N24" s="54"/>
       <c r="O24" s="25"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
       <c r="V24" s="52"/>
     </row>
     <row r="25">
       <c r="A25" s="23"/>
       <c r="B25" s="23"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33">
+      <c r="C25" s="41"/>
+      <c r="D25" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34">
         <v>40.0</v>
       </c>
-      <c r="G25" s="43">
+      <c r="G25" s="44">
         <v>46156.0</v>
       </c>
-      <c r="H25" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43">
+      <c r="H25" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44">
         <v>46191.0</v>
       </c>
-      <c r="K25" s="45">
+      <c r="K25" s="46">
         <v>1549250.84</v>
       </c>
-      <c r="L25" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="M25" s="38">
+      <c r="L25" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="M25" s="39">
         <v>1549250.84</v>
       </c>
       <c r="N25" s="54"/>
       <c r="O25" s="25"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
       <c r="V25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="23"/>
       <c r="B26" s="23"/>
       <c r="C26" s="55"/>
-      <c r="D26" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33">
+      <c r="D26" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34">
         <v>48.0</v>
       </c>
-      <c r="G26" s="43">
+      <c r="G26" s="44">
         <v>46230.0</v>
       </c>
-      <c r="H26" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43">
+      <c r="H26" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44">
         <v>46262.0</v>
       </c>
-      <c r="K26" s="45" t="s">
+      <c r="K26" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="L26" s="33" t="s">
+      <c r="L26" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M26" s="38" t="s">
+      <c r="M26" s="39" t="s">
         <v>180</v>
       </c>
       <c r="N26" s="54"/>
       <c r="O26" s="25"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
       <c r="V26" s="52"/>
     </row>
     <row r="27">
       <c r="A27" s="23"/>
       <c r="B27" s="23"/>
       <c r="C27" s="35"/>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="49" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="38"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="39"/>
       <c r="N27" s="54"/>
       <c r="O27" s="25"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
       <c r="V27" s="52"/>
     </row>
     <row r="28" ht="30.75" customHeight="1">
       <c r="A28" s="23"/>
       <c r="B28" s="23"/>
-      <c r="C28" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="C28" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
       <c r="K28" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="L28" s="30" t="s">
-        <v>54</v>
+        <v>65</v>
+      </c>
+      <c r="L28" s="31" t="s">
+        <v>66</v>
       </c>
       <c r="M28" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="N28" s="28" t="s">
-        <v>57</v>
+        <v>67</v>
+      </c>
+      <c r="N28" s="29" t="s">
+        <v>68</v>
       </c>
       <c r="O28" s="25"/>
-      <c r="P28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
+      <c r="P28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
       <c r="V28" s="52"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="27"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="23"/>
       <c r="B29" s="23"/>
-      <c r="C29" s="31">
+      <c r="C29" s="32">
         <v>2.0</v>
       </c>
       <c r="D29" s="58" t="s">
@@ -2432,7 +2432,7 @@
         <v>45791.0</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I29" s="36"/>
       <c r="J29" s="36">
@@ -2441,7 +2441,7 @@
       <c r="K29" s="37">
         <v>188246.17</v>
       </c>
-      <c r="L29" s="33" t="s">
+      <c r="L29" s="34" t="s">
         <v>184</v>
       </c>
       <c r="M29" s="59">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="N29" s="51"/>
       <c r="O29" s="25"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
       <c r="V29" s="52"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="27"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
     </row>
     <row r="30">
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
-      <c r="C30" s="40"/>
+      <c r="C30" s="41"/>
       <c r="D30" s="58" t="s">
         <v>185</v>
       </c>
@@ -2480,43 +2480,43 @@
       <c r="G30" s="36">
         <v>45814.0</v>
       </c>
-      <c r="H30" s="33" t="s">
+      <c r="H30" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43">
+      <c r="I30" s="44"/>
+      <c r="J30" s="44">
         <v>45955.0</v>
       </c>
       <c r="K30" s="37">
         <v>112720.77</v>
       </c>
-      <c r="L30" s="33" t="s">
+      <c r="L30" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="39">
         <v>112720.77</v>
       </c>
       <c r="N30" s="51"/>
       <c r="O30" s="25"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="27"/>
+      <c r="P30" s="28"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="28"/>
       <c r="V30" s="52"/>
-      <c r="W30" s="27"/>
-      <c r="X30" s="27"/>
-      <c r="Y30" s="27"/>
-      <c r="Z30" s="27"/>
-      <c r="AA30" s="27"/>
-      <c r="AB30" s="27"/>
-      <c r="AC30" s="27"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+      <c r="AC30" s="28"/>
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="23"/>
       <c r="B31" s="23"/>
-      <c r="C31" s="40"/>
+      <c r="C31" s="41"/>
       <c r="D31" s="61" t="s">
         <v>188</v>
       </c>
@@ -2529,161 +2529,161 @@
       <c r="G31" s="63">
         <v>45853.0</v>
       </c>
-      <c r="H31" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43">
+      <c r="H31" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44">
         <v>45939.0</v>
       </c>
-      <c r="K31" s="45">
+      <c r="K31" s="46">
         <v>378307.61</v>
       </c>
-      <c r="L31" s="33" t="s">
+      <c r="L31" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="M31" s="38">
+      <c r="M31" s="39">
         <v>378307.61</v>
       </c>
       <c r="N31" s="51"/>
       <c r="O31" s="25"/>
       <c r="P31" s="64"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="27"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="28"/>
       <c r="V31" s="52"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="27"/>
-      <c r="Y31" s="27"/>
-      <c r="Z31" s="27"/>
-      <c r="AA31" s="27"/>
-      <c r="AB31" s="27"/>
-      <c r="AC31" s="27"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+      <c r="AC31" s="28"/>
     </row>
     <row r="32" ht="60.0" customHeight="1">
       <c r="A32" s="23"/>
       <c r="B32" s="23"/>
-      <c r="C32" s="40"/>
+      <c r="C32" s="41"/>
       <c r="D32" s="61" t="s">
         <v>191</v>
       </c>
       <c r="E32" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="34">
         <v>691.0</v>
       </c>
       <c r="G32" s="63">
         <v>45910.0</v>
       </c>
-      <c r="H32" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43">
+      <c r="H32" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44">
         <v>45941.0</v>
       </c>
       <c r="K32" s="37">
         <v>3315.0471000000252</v>
       </c>
-      <c r="L32" s="33" t="s">
+      <c r="L32" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="M32" s="38">
+      <c r="M32" s="39">
         <v>3315.04710000003</v>
       </c>
       <c r="N32" s="51"/>
       <c r="O32" s="25"/>
       <c r="P32" s="64"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
       <c r="V32" s="52"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
-      <c r="AC32" s="27"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="23"/>
       <c r="B33" s="23"/>
-      <c r="C33" s="40"/>
+      <c r="C33" s="41"/>
       <c r="D33" s="61" t="s">
         <v>193</v>
       </c>
       <c r="E33" s="65">
         <v>135.0</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>677.0</v>
       </c>
       <c r="G33" s="63">
         <v>45904.0</v>
       </c>
-      <c r="H33" s="33" t="s">
-        <v>76</v>
+      <c r="H33" s="34" t="s">
+        <v>69</v>
       </c>
       <c r="I33" s="66"/>
       <c r="J33" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K33" s="45">
+      <c r="K33" s="46">
         <v>198332.75</v>
       </c>
-      <c r="L33" s="33" t="s">
+      <c r="L33" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="M33" s="38">
+      <c r="M33" s="39">
         <v>198332.75</v>
       </c>
       <c r="N33" s="51"/>
       <c r="O33" s="25"/>
       <c r="P33" s="64"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="27"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
       <c r="V33" s="52"/>
-      <c r="W33" s="27"/>
-      <c r="X33" s="27"/>
-      <c r="Y33" s="27"/>
-      <c r="Z33" s="27"/>
-      <c r="AA33" s="27"/>
-      <c r="AB33" s="27"/>
-      <c r="AC33" s="27"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28"/>
+      <c r="Y33" s="28"/>
+      <c r="Z33" s="28"/>
+      <c r="AA33" s="28"/>
+      <c r="AB33" s="28"/>
+      <c r="AC33" s="28"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="23"/>
       <c r="B34" s="23"/>
-      <c r="C34" s="40"/>
+      <c r="C34" s="41"/>
       <c r="D34" s="61" t="s">
         <v>195</v>
       </c>
       <c r="E34" s="65">
         <v>40.0</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>278.0</v>
       </c>
       <c r="G34" s="63">
         <v>46008.0</v>
       </c>
-      <c r="H34" s="33" t="s">
-        <v>136</v>
+      <c r="H34" s="34" t="s">
+        <v>114</v>
       </c>
       <c r="I34" s="66"/>
       <c r="J34" s="66">
         <v>46066.0</v>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="46">
         <v>1528.62</v>
       </c>
       <c r="L34" s="67" t="s">
@@ -2695,47 +2695,47 @@
       <c r="N34" s="51"/>
       <c r="O34" s="25"/>
       <c r="P34" s="64"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="27"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
       <c r="V34" s="52"/>
-      <c r="W34" s="27"/>
-      <c r="X34" s="27"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="27"/>
-      <c r="AA34" s="27"/>
-      <c r="AB34" s="27"/>
-      <c r="AC34" s="27"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28"/>
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="28"/>
+      <c r="AA34" s="28"/>
+      <c r="AB34" s="28"/>
+      <c r="AC34" s="28"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="23"/>
       <c r="B35" s="23"/>
-      <c r="C35" s="40"/>
+      <c r="C35" s="41"/>
       <c r="D35" s="61" t="s">
         <v>198</v>
       </c>
       <c r="E35" s="65" t="s">
         <v>199</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>748.0</v>
       </c>
       <c r="G35" s="63">
         <v>45930.0</v>
       </c>
-      <c r="H35" s="33" t="s">
-        <v>102</v>
+      <c r="H35" s="34" t="s">
+        <v>91</v>
       </c>
       <c r="I35" s="66"/>
       <c r="J35" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K35" s="45">
+      <c r="K35" s="46">
         <v>38718.58</v>
       </c>
-      <c r="L35" s="33" t="s">
+      <c r="L35" s="34" t="s">
         <v>200</v>
       </c>
       <c r="M35" s="59" t="s">
@@ -2744,47 +2744,47 @@
       <c r="N35" s="51"/>
       <c r="O35" s="25"/>
       <c r="P35" s="64"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="27"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
       <c r="V35" s="52"/>
-      <c r="W35" s="27"/>
-      <c r="X35" s="27"/>
-      <c r="Y35" s="27"/>
-      <c r="Z35" s="27"/>
-      <c r="AA35" s="27"/>
-      <c r="AB35" s="27"/>
-      <c r="AC35" s="27"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="23"/>
       <c r="B36" s="23"/>
-      <c r="C36" s="40"/>
+      <c r="C36" s="41"/>
       <c r="D36" s="61" t="s">
         <v>202</v>
       </c>
       <c r="E36" s="65">
         <v>154.0</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="34">
         <v>822.0</v>
       </c>
       <c r="G36" s="63">
         <v>45968.0</v>
       </c>
-      <c r="H36" s="33" t="s">
-        <v>123</v>
+      <c r="H36" s="34" t="s">
+        <v>107</v>
       </c>
       <c r="I36" s="66"/>
       <c r="J36" s="66">
         <v>45935.0</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="46">
         <v>133124.11</v>
       </c>
-      <c r="L36" s="33" t="s">
+      <c r="L36" s="34" t="s">
         <v>203</v>
       </c>
       <c r="M36" s="59" t="s">
@@ -2793,24 +2793,24 @@
       <c r="N36" s="51"/>
       <c r="O36" s="25"/>
       <c r="P36" s="64"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="27"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="S36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
       <c r="V36" s="52"/>
-      <c r="W36" s="27"/>
-      <c r="X36" s="27"/>
-      <c r="Y36" s="27"/>
-      <c r="Z36" s="27"/>
-      <c r="AA36" s="27"/>
-      <c r="AB36" s="27"/>
-      <c r="AC36" s="27"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="28"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
+      <c r="AC36" s="28"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
-      <c r="C37" s="40"/>
+      <c r="C37" s="41"/>
       <c r="D37" s="61" t="s">
         <v>205</v>
       </c>
@@ -2824,42 +2824,42 @@
         <v>46043.0</v>
       </c>
       <c r="H37" s="65" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="I37" s="70"/>
       <c r="J37" s="69">
         <v>46075.0</v>
       </c>
-      <c r="K37" s="45">
+      <c r="K37" s="46">
         <v>11372.9</v>
       </c>
-      <c r="L37" s="33" t="s">
+      <c r="L37" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="M37" s="38">
+      <c r="M37" s="39">
         <v>11372.9</v>
       </c>
       <c r="N37" s="51"/>
       <c r="O37" s="25"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
       <c r="V37" s="52"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
-      <c r="C38" s="40"/>
+      <c r="C38" s="41"/>
       <c r="D38" s="61" t="s">
         <v>207</v>
       </c>
@@ -2871,27 +2871,27 @@
         <v>208</v>
       </c>
       <c r="J38" s="69"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="38"/>
+      <c r="K38" s="46"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="39"/>
       <c r="N38" s="51">
         <v>15854.78</v>
       </c>
       <c r="O38" s="25"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="S38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
       <c r="V38" s="52"/>
-      <c r="W38" s="27"/>
-      <c r="X38" s="27"/>
-      <c r="Y38" s="27"/>
-      <c r="Z38" s="27"/>
-      <c r="AA38" s="27"/>
-      <c r="AB38" s="27"/>
-      <c r="AC38" s="27"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="23"/>
@@ -2908,27 +2908,27 @@
         <v>208</v>
       </c>
       <c r="J39" s="69"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="38"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="39"/>
       <c r="N39" s="71">
         <v>42229.72325</v>
       </c>
       <c r="O39" s="25"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
       <c r="V39" s="52"/>
-      <c r="W39" s="27"/>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
-      <c r="AA39" s="27"/>
-      <c r="AB39" s="27"/>
-      <c r="AC39" s="27"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="28"/>
+      <c r="AA39" s="28"/>
+      <c r="AB39" s="28"/>
+      <c r="AC39" s="28"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="23"/>
@@ -2945,27 +2945,27 @@
         <v>208</v>
       </c>
       <c r="J40" s="69"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="46"/>
-      <c r="M40" s="38"/>
+      <c r="K40" s="46"/>
+      <c r="L40" s="47"/>
+      <c r="M40" s="39"/>
       <c r="N40" s="72">
         <v>48857.395500000006</v>
       </c>
       <c r="O40" s="25"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
       <c r="V40" s="52"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="27"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
+      <c r="AC40" s="28"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="23"/>
@@ -2982,30 +2982,30 @@
         <v>212</v>
       </c>
       <c r="J41" s="69"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="46"/>
-      <c r="M41" s="38"/>
+      <c r="K41" s="46"/>
+      <c r="L41" s="47"/>
+      <c r="M41" s="39"/>
       <c r="N41" s="72"/>
       <c r="O41" s="25"/>
-      <c r="P41" s="27"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="27"/>
-      <c r="S41" s="27"/>
-      <c r="T41" s="27"/>
-      <c r="U41" s="27"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28"/>
       <c r="V41" s="52"/>
-      <c r="W41" s="27"/>
-      <c r="X41" s="27"/>
-      <c r="Y41" s="27"/>
-      <c r="Z41" s="27"/>
-      <c r="AA41" s="27"/>
-      <c r="AB41" s="27"/>
-      <c r="AC41" s="27"/>
+      <c r="W41" s="28"/>
+      <c r="X41" s="28"/>
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="28"/>
+      <c r="AA41" s="28"/>
+      <c r="AB41" s="28"/>
+      <c r="AC41" s="28"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="23"/>
       <c r="B42" s="23"/>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>3.0</v>
       </c>
       <c r="D42" s="61" t="s">
@@ -3019,13 +3019,13 @@
         <v>46104.0</v>
       </c>
       <c r="H42" s="65" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="I42" s="70"/>
       <c r="J42" s="69">
         <v>46106.0</v>
       </c>
-      <c r="K42" s="45">
+      <c r="K42" s="46">
         <v>27801.11</v>
       </c>
       <c r="L42" s="73" t="s">
@@ -3036,25 +3036,25 @@
       </c>
       <c r="N42" s="51"/>
       <c r="O42" s="25"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
-      <c r="T42" s="27"/>
-      <c r="U42" s="27"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="28"/>
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
       <c r="V42" s="52"/>
-      <c r="W42" s="27"/>
-      <c r="X42" s="27"/>
-      <c r="Y42" s="27"/>
-      <c r="Z42" s="27"/>
-      <c r="AA42" s="27"/>
-      <c r="AB42" s="27"/>
-      <c r="AC42" s="27"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28"/>
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
+      <c r="AC42" s="28"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
-      <c r="C43" s="40"/>
+      <c r="C43" s="41"/>
       <c r="D43" s="61" t="s">
         <v>215</v>
       </c>
@@ -3066,63 +3066,63 @@
         <v>46199.0</v>
       </c>
       <c r="H43" s="65" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I43" s="70"/>
       <c r="J43" s="69">
         <v>46233.0</v>
       </c>
-      <c r="K43" s="45">
+      <c r="K43" s="46">
         <v>58868.35</v>
       </c>
-      <c r="L43" s="33" t="s">
-        <v>56</v>
+      <c r="L43" s="34" t="s">
+        <v>67</v>
       </c>
       <c r="M43" s="74">
         <v>58868.35</v>
       </c>
       <c r="N43" s="51"/>
-      <c r="V43" s="3"/>
+      <c r="V43" s="5"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
-      <c r="C44" s="40"/>
+      <c r="C44" s="41"/>
       <c r="K44" s="75"/>
       <c r="M44" s="75"/>
-      <c r="V44" s="3"/>
+      <c r="V44" s="5"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
-      <c r="C45" s="40"/>
+      <c r="C45" s="41"/>
       <c r="K45" s="75"/>
       <c r="M45" s="75"/>
-      <c r="V45" s="3"/>
+      <c r="V45" s="5"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
-      <c r="C46" s="40"/>
-      <c r="V46" s="3"/>
+      <c r="C46" s="41"/>
+      <c r="V46" s="5"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
-      <c r="C47" s="40"/>
-      <c r="V47" s="3"/>
+      <c r="C47" s="41"/>
+      <c r="V47" s="5"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="15"/>
       <c r="B48" s="15"/>
-      <c r="C48" s="40"/>
-      <c r="V48" s="3"/>
+      <c r="C48" s="41"/>
+      <c r="V48" s="5"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="15"/>
       <c r="B49" s="15"/>
-      <c r="C49" s="40"/>
-      <c r="V49" s="3"/>
+      <c r="C49" s="41"/>
+      <c r="V49" s="5"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="15"/>
@@ -3130,7 +3130,7 @@
       <c r="C50" s="55"/>
       <c r="K50" s="75"/>
       <c r="M50" s="75"/>
-      <c r="V50" s="3"/>
+      <c r="V50" s="5"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="15"/>
@@ -3154,7 +3154,7 @@
       <c r="S51" s="76"/>
       <c r="T51" s="76"/>
       <c r="U51" s="76"/>
-      <c r="V51" s="3"/>
+      <c r="V51" s="5"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="15"/>
@@ -8035,11 +8035,11 @@
       <c r="AH1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="3">
         <v>46212.0</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>1</v>
+      <c r="L2" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -8050,40 +8050,40 @@
       <c r="AH2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>2.5E32</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="9">
         <v>45686.0</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="7">
         <v>12.0</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="12">
         <v>1000.0</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="12">
         <v>1000.0</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="7">
         <v>0.0</v>
       </c>
       <c r="AB3" s="2"/>
@@ -8095,40 +8095,40 @@
       <c r="AH3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="9">
         <v>45762.0</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="7">
         <v>12.0</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="12">
         <v>52250.04</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="12">
         <v>52250.04</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="7">
         <v>0.0</v>
       </c>
       <c r="AB4" s="2"/>
@@ -8140,40 +8140,40 @@
       <c r="AH4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="10" t="s">
+      <c r="A5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="9">
         <v>45762.0</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="7">
         <v>12.0</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="12">
         <v>881914.18</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="12">
         <v>881914.18</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="7">
         <v>0.0</v>
       </c>
       <c r="AB5" s="2"/>
@@ -8185,40 +8185,40 @@
       <c r="AH5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="10" t="s">
+      <c r="A6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="9">
         <v>45762.0</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="7">
         <v>12.0</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <v>750000.0</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="12">
         <v>750000.0</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="7">
         <v>0.0</v>
       </c>
       <c r="AB6" s="2"/>
@@ -8230,40 +8230,40 @@
       <c r="AH6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="9">
+        <v>45763.0</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7">
+        <v>12.0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>339039.0</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="13">
-        <v>45763.0</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>12.0</v>
-      </c>
-      <c r="H7" s="10">
-        <v>339039.0</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="14">
+      <c r="J7" s="12">
         <v>949835.78</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="12">
         <v>949835.78</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="7">
         <v>0.0</v>
       </c>
       <c r="AB7" s="2"/>
@@ -8275,43 +8275,43 @@
       <c r="AH7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="A8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="9">
         <v>45763.0</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="7">
         <v>12.0</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J8" s="14">
+      <c r="I8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="12">
         <v>524584.95</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="12">
         <v>524584.95</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="7">
         <v>0.0</v>
       </c>
-      <c r="O8" s="34"/>
+      <c r="O8" s="26"/>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
       <c r="AD8" s="2"/>
@@ -8321,40 +8321,40 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="A9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="9">
         <v>45792.0</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="7">
         <v>12.0</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="14">
+      <c r="I9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="12">
         <v>211614.23</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="12">
         <v>211614.23</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="7">
         <v>0.0</v>
       </c>
       <c r="AB9" s="2"/>
@@ -8366,40 +8366,40 @@
       <c r="AH9" s="2"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="A10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="10" t="s">
+      <c r="C10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="9">
         <v>45825.0</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="7">
         <v>12.0</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="12">
         <v>2391157.42</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="12">
         <v>2391157.41</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="12">
         <v>0.01</v>
       </c>
       <c r="AB10" s="2"/>
@@ -8411,40 +8411,40 @@
       <c r="AH10" s="2"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="A11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="9">
         <v>45825.0</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="7">
         <v>12.0</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="12">
         <v>618154.39</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="12">
         <v>618154.38</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="7">
         <v>0.01</v>
       </c>
       <c r="AB11" s="2"/>
@@ -8456,40 +8456,40 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="10" t="s">
+      <c r="A12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="9">
         <v>45832.0</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="7">
         <v>12.0</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="J12" s="14">
+      <c r="I12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="12">
         <v>1600334.09</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12" s="12">
         <v>1600334.09</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="7">
         <v>0.0</v>
       </c>
       <c r="AB12" s="2"/>
@@ -8501,43 +8501,43 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="10" t="s">
+      <c r="A13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="9">
         <v>45863.0</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="7">
         <v>12.0</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="12">
         <v>2364771.07</v>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="12">
         <v>2364771.07</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="12">
         <v>0.0</v>
       </c>
-      <c r="M13" s="42"/>
+      <c r="M13" s="38"/>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="2"/>
@@ -8547,40 +8547,40 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="A14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="9">
         <v>45887.0</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="7">
         <v>12.0</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J14" s="14">
+      <c r="I14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="12">
         <v>968237.39</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="12">
         <v>968237.39</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="7">
         <v>0.0</v>
       </c>
       <c r="AB14" s="2"/>
@@ -8592,40 +8592,40 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="10" t="s">
+      <c r="A15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="9">
         <v>45924.0</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="7">
         <v>12.0</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="14">
+      <c r="I15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J15" s="12">
         <v>1011677.95</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="12">
         <v>1011677.95</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="7">
         <v>0.0</v>
       </c>
       <c r="AB15" s="2"/>
@@ -8637,40 +8637,40 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="9">
         <v>45929.0</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="7">
         <v>12.0</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="12">
         <v>1580293.02</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="12">
         <v>1580293.02</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="12">
         <v>0.0</v>
       </c>
       <c r="AB16" s="2"/>
@@ -8682,40 +8682,40 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="A17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="9">
         <v>45930.0</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="7">
         <v>12.0</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="12">
         <v>34065.36</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="7">
         <v>0.0</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="12">
         <v>34065.36</v>
       </c>
       <c r="AB17" s="2"/>
@@ -8727,40 +8727,40 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="10" t="s">
+      <c r="A18" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="7">
         <v>12.0</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I18" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J18" s="14">
+      <c r="I18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="12">
         <v>63746.85</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="12">
         <v>63746.85</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="7">
         <v>0.0</v>
       </c>
       <c r="AB18" s="2"/>
@@ -8772,40 +8772,40 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="A19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="7">
         <v>12.0</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="J19" s="14">
+      <c r="I19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" s="12">
         <v>947931.1</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19" s="12">
         <v>947931.1</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="7">
         <v>0.0</v>
       </c>
       <c r="AB19" s="2"/>
@@ -8817,40 +8817,40 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="10" t="s">
+      <c r="A20" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="10" t="s">
+      <c r="C20" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="7">
         <v>12.0</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="12">
         <v>259790.57</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="12">
         <v>259790.57</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="7">
         <v>0.0</v>
       </c>
       <c r="AB20" s="2"/>
@@ -8862,40 +8862,40 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="A21" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="9">
         <v>45938.0</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="7">
         <v>12.0</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="12">
         <v>170479.3</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K21" s="12">
         <v>170479.3</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="7">
         <v>0.0</v>
       </c>
       <c r="AB21" s="2"/>
@@ -8907,40 +8907,40 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="A22" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="7">
         <v>12.0</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="7">
         <v>2000.0</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="12">
         <v>1500000.0</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="12">
         <v>1500000.0</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="12">
         <v>0.0</v>
       </c>
       <c r="AB22" s="2"/>
@@ -8952,40 +8952,40 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="A23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="50">
+      <c r="E23" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="7">
         <v>12.0</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J23" s="14">
+      <c r="I23" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J23" s="12">
         <v>1000001.64</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="12">
         <v>1000001.64</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="7">
         <v>0.0</v>
       </c>
       <c r="AB23" s="2"/>
@@ -8997,40 +8997,40 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="A24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="50">
+      <c r="E24" s="43">
         <v>45953.0</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="7">
         <v>12.0</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="12">
         <v>68405.66</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K24" s="12">
         <v>68405.66</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="7">
         <v>0.0</v>
       </c>
       <c r="AB24" s="2"/>
@@ -9042,40 +9042,40 @@
       <c r="AH24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="A25" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="50">
+      <c r="E25" s="43">
         <v>45975.0</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="7">
         <v>12.0</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J25" s="14">
+      <c r="I25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="12">
         <v>1157673.06</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="12">
         <v>1157673.06</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="7">
         <v>0.0</v>
       </c>
       <c r="AB25" s="2"/>
@@ -9087,40 +9087,40 @@
       <c r="AH25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="10" t="s">
+      <c r="A26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="50">
+      <c r="E26" s="43">
         <v>45989.0</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="7">
         <v>12.0</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="12">
         <v>34065.36</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="12">
         <v>34065.36</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="7">
         <v>0.0</v>
       </c>
       <c r="AB26" s="2"/>
@@ -9132,40 +9132,40 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="A27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="9">
         <v>46104.0</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="7">
         <v>12.0</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J27" s="14">
+      <c r="J27" s="12">
         <v>1770880.5</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="12">
         <v>843261.89</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="12">
         <v>927618.61</v>
       </c>
       <c r="AB27" s="2"/>
@@ -9177,40 +9177,40 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="A28" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="9">
         <v>46120.0</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="7">
         <v>12.0</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I28" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J28" s="14">
+      <c r="I28" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" s="12">
         <v>1912292.52</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="7">
         <v>0.0</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="12">
         <v>1912292.52</v>
       </c>
       <c r="AB28" s="2"/>
@@ -9222,40 +9222,40 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="A29" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="9">
         <v>46196.0</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="7">
         <v>12.0</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J29" s="14">
+      <c r="J29" s="12">
         <v>1496713.48</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="7">
         <v>0.0</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="12">
         <v>1496713.48</v>
       </c>
       <c r="AB29" s="2"/>
@@ -9267,40 +9267,40 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="A30" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="9">
         <v>46205.0</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="7">
         <v>12.0</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J30" s="14">
+      <c r="I30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="12">
         <v>624166.14</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="7">
         <v>0.0</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="12">
         <v>624166.14</v>
       </c>
       <c r="AB30" s="2"/>
@@ -9312,40 +9312,40 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D31" s="10" t="s">
+      <c r="A31" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="9">
         <v>46205.0</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="7">
         <v>12.0</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I31" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J31" s="14">
+      <c r="I31" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J31" s="12">
         <v>18462.36</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="7">
         <v>0.0</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="12">
         <v>18462.36</v>
       </c>
       <c r="AB31" s="2"/>
@@ -9357,40 +9357,40 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="A32" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="9">
         <v>46213.0</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="7">
         <v>12.0</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="J32" s="14">
+      <c r="I32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J32" s="12">
         <v>1530656.62</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="7">
         <v>0.0</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L32" s="12">
         <v>1530656.62</v>
       </c>
       <c r="AB32" s="2"/>
@@ -9402,40 +9402,40 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="A33" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="9">
         <v>46227.0</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="7">
         <v>12.0</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="7">
         <v>2048.0</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="12">
         <v>173846.38</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="7">
         <v>0.0</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="12">
         <v>173846.38</v>
       </c>
       <c r="AB33" s="2"/>
@@ -9447,40 +9447,40 @@
       <c r="AH33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="A34" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="9">
         <v>46240.0</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="7">
         <v>12.0</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="7">
         <v>339039.0</v>
       </c>
-      <c r="I34" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="J34" s="14">
+      <c r="I34" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J34" s="12">
         <v>236343.68</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="7">
         <v>0.0</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="12">
         <v>236343.68</v>
       </c>
       <c r="AB34" s="2"/>

--- a/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
+++ b/Contrato 005/Dashboard/01_Bases_Originais/005_CELOG_2025/005_CELOG-PAMALS_2025 online.xlsx
@@ -30,15 +30,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="216">
   <si>
+    <t>Controle de pagamentos</t>
+  </si>
+  <si>
     <t>Saldo</t>
   </si>
   <si>
     <t>025NE000005</t>
   </si>
   <si>
-    <t>Controle de pagamentos</t>
-  </si>
-  <si>
     <t>C25375</t>
   </si>
   <si>
@@ -48,94 +48,109 @@
     <t>S</t>
   </si>
   <si>
+    <t>Número Contrato</t>
+  </si>
+  <si>
     <t>2025NE000367</t>
   </si>
   <si>
+    <t>UG Executora</t>
+  </si>
+  <si>
     <t>C25512</t>
   </si>
   <si>
     <t>25E0385</t>
   </si>
   <si>
+    <t>UG Responsável</t>
+  </si>
+  <si>
+    <t>UG Fiscalizadora</t>
+  </si>
+  <si>
+    <t>Prazo Final de Execução</t>
+  </si>
+  <si>
+    <t>Prazo Final de Vigência</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Ação</t>
+  </si>
+  <si>
+    <t>PAG</t>
+  </si>
+  <si>
+    <t>Moeda</t>
+  </si>
+  <si>
+    <t>Valor Total do Contrato</t>
+  </si>
+  <